--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D325F8D9-5DB8-4230-B057-035682FD1491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5AF3AC5-BA51-4464-A8AD-078CE6583EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -397,960 +397,961 @@
     <t>3551102:1</t>
   </si>
   <si>
+    <t>3551301:1</t>
+  </si>
+  <si>
+    <t>3041101:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击速度提高</t>
+  </si>
+  <si>
+    <t>攻击提高</t>
+  </si>
+  <si>
+    <t>防御提高</t>
+  </si>
+  <si>
+    <t>生命提高</t>
+  </si>
+  <si>
+    <t>击中回血效果提高</t>
+  </si>
+  <si>
+    <t>暴击几率提高</t>
+  </si>
+  <si>
+    <t>暴击伤害提高</t>
+  </si>
+  <si>
+    <t>伤害提高</t>
+  </si>
+  <si>
+    <t>受到伤害提高</t>
+  </si>
+  <si>
+    <t>持续伤害提高</t>
+  </si>
+  <si>
+    <t>受到持续伤害提高</t>
+  </si>
+  <si>
+    <t>attr_value_7_variable_id</t>
+  </si>
+  <si>
+    <t>attr_value_7_type</t>
+  </si>
+  <si>
+    <t>attr_value_7</t>
+  </si>
+  <si>
+    <t>参数7关联的变量id</t>
+  </si>
+  <si>
+    <t>参数7数值类型</t>
+  </si>
+  <si>
+    <t>参数7</t>
+  </si>
+  <si>
+    <t>移动速度提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3540201:1</t>
+  </si>
+  <si>
+    <t>3540401:1</t>
+  </si>
+  <si>
+    <t>3540402:1</t>
+  </si>
+  <si>
+    <t>3540601:1</t>
+  </si>
+  <si>
+    <t>3540602:1</t>
+  </si>
+  <si>
+    <t>3540801:1</t>
+  </si>
+  <si>
+    <t>3540802:1</t>
+  </si>
+  <si>
+    <t>3541001:1</t>
+  </si>
+  <si>
+    <t>3541002:1</t>
+  </si>
+  <si>
+    <t>3541201:1</t>
+  </si>
+  <si>
+    <t>3541401:1</t>
+  </si>
+  <si>
+    <t>3541601:1</t>
+  </si>
+  <si>
+    <t>3541602:1</t>
+  </si>
+  <si>
+    <t>3541801:1</t>
+  </si>
+  <si>
+    <t>3541802:1</t>
+  </si>
+  <si>
+    <t>3542001:1</t>
+  </si>
+  <si>
+    <t>3542002:1</t>
+  </si>
+  <si>
+    <t>3542201:1</t>
+  </si>
+  <si>
+    <t>3542202:1</t>
+  </si>
+  <si>
+    <t>3542401:1</t>
+  </si>
+  <si>
+    <t>3540205:1</t>
+  </si>
+  <si>
+    <t>3540207:1</t>
+  </si>
+  <si>
+    <t>3540405:1</t>
+  </si>
+  <si>
+    <t>3540407:1</t>
+  </si>
+  <si>
+    <t>3540605:1</t>
+  </si>
+  <si>
+    <t>3540607:1</t>
+  </si>
+  <si>
+    <t>3540805:1</t>
+  </si>
+  <si>
+    <t>3540807:1</t>
+  </si>
+  <si>
+    <t>3541005:1</t>
+  </si>
+  <si>
+    <t>3541007:1</t>
+  </si>
+  <si>
+    <t>3541205:1</t>
+  </si>
+  <si>
+    <t>3541207:1</t>
+  </si>
+  <si>
+    <t>3541405:1</t>
+  </si>
+  <si>
+    <t>3541407:1</t>
+  </si>
+  <si>
+    <t>3541605:1</t>
+  </si>
+  <si>
+    <t>3541607:1</t>
+  </si>
+  <si>
+    <t>3541805:1</t>
+  </si>
+  <si>
+    <t>3541807:1</t>
+  </si>
+  <si>
+    <t>3542005:1</t>
+  </si>
+  <si>
+    <t>3542007:1</t>
+  </si>
+  <si>
+    <t>3542205:1</t>
+  </si>
+  <si>
+    <t>3542207:1</t>
+  </si>
+  <si>
+    <t>3542405:1</t>
+  </si>
+  <si>
+    <t>3542407:1</t>
+  </si>
+  <si>
+    <t>3551302:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3551501:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>多重冰霜新星</t>
+  </si>
+  <si>
+    <t>冰霜新星造成冰冻几率提高</t>
+  </si>
+  <si>
+    <t>冰冻时受到冰元素伤害</t>
+  </si>
+  <si>
+    <t>释放冰霜新星时，对敌人造成的冰冻几率增加【参数1万分比】</t>
+  </si>
+  <si>
+    <t>双重冰冻造成额外伤害</t>
+  </si>
+  <si>
+    <t>冰冻命中造成额外伤害</t>
+  </si>
+  <si>
+    <t>击中冰冻目标造成额外伤害</t>
+  </si>
+  <si>
+    <t>冰霜新星额外冰冻几率</t>
+  </si>
+  <si>
+    <t>攻击次数触发冰霜新星</t>
+  </si>
+  <si>
+    <t>攻击使目标冰冻</t>
+  </si>
+  <si>
+    <t>3550902:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击速度提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>攻击提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>防御提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>生命提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>击中回血效果提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>暴击几率提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>暴击伤害提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>受到伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>持续伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>受到持续伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>移动速度提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>获取护盾提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>全属性伤害提高</t>
+  </si>
+  <si>
+    <t>受到全属性伤害提高</t>
+  </si>
+  <si>
+    <t>全属性持续伤害提高</t>
+  </si>
+  <si>
+    <t>受到全属性持续伤害提高</t>
+  </si>
+  <si>
+    <t>移动速度提高</t>
+  </si>
+  <si>
+    <t>获取护盾提高</t>
+  </si>
+  <si>
+    <t>技能效果-通用</t>
+  </si>
+  <si>
+    <t>技能效果-冰</t>
+  </si>
+  <si>
+    <t>获取护盾提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>中毒死亡释放瘟疫</t>
+  </si>
+  <si>
+    <t>瘟疫状态</t>
+  </si>
+  <si>
+    <t>技能效果-火</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果-电</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果-毒</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧状态</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动释放陨石</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧状态受到伤害提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石造成燃烧命中率增加</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧时死亡触发死亡爆炸</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触电状态</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪电链弹射效果</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击触发释放闪电链</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触电时受到伤害提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发触电伤害时释放电磁爆炸</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>中毒状态</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击触发传染</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3560201:1</t>
+  </si>
+  <si>
+    <t>3560202:1</t>
+  </si>
+  <si>
+    <t>3560205:1</t>
+  </si>
+  <si>
+    <t>3560206:1</t>
+  </si>
+  <si>
+    <t>3560501:2</t>
+  </si>
+  <si>
+    <t>3560502:1</t>
+  </si>
+  <si>
+    <t>3560503:1</t>
+  </si>
+  <si>
+    <t>3560701:1</t>
+  </si>
+  <si>
+    <t>3560901:1</t>
+  </si>
+  <si>
+    <t>3570201:1</t>
+  </si>
+  <si>
+    <t>3570202:1</t>
+  </si>
+  <si>
+    <t>3570501:1</t>
+  </si>
+  <si>
+    <t>3570502:1</t>
+  </si>
+  <si>
+    <t>3570701:2</t>
+  </si>
+  <si>
+    <t>3570702:1</t>
+  </si>
+  <si>
+    <t>3570703:1</t>
+  </si>
+  <si>
+    <t>3570901:1</t>
+  </si>
+  <si>
+    <t>3571101:1</t>
+  </si>
+  <si>
+    <t>3571102:1</t>
+  </si>
+  <si>
+    <t>3571103:1</t>
+  </si>
+  <si>
+    <t>3580201:1</t>
+  </si>
+  <si>
+    <t>3580202:1</t>
+  </si>
+  <si>
+    <t>3580207:1</t>
+  </si>
+  <si>
+    <t>3580501:2</t>
+  </si>
+  <si>
+    <t>3580502:1</t>
+  </si>
+  <si>
+    <t>3580503:1</t>
+  </si>
+  <si>
+    <t>3580701:1</t>
+  </si>
+  <si>
+    <t>3580902:1</t>
+  </si>
+  <si>
+    <t>3580903:1</t>
+  </si>
+  <si>
+    <t>3561102:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3561103:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>每【参数1】次攻击，有【参数2万分比】的几率触发【参数3】次【参数4技能id】</t>
+  </si>
+  <si>
+    <t>燃烧时，受到全种类攻击承受伤害提高【参数1万分比】</t>
+  </si>
+  <si>
+    <t>陨石造成伤害时，燃烧效果的命中率提升【参数1万分比】</t>
+  </si>
+  <si>
+    <t>燃烧时，死亡，有【参数2万分比】的几率触发【参数3】次【参数4技能id】</t>
+  </si>
+  <si>
+    <t>每次受到攻击会额外受到等同于[电元素最终伤害]【参数1万分比】</t>
+  </si>
+  <si>
+    <t>闪电链可弹射【参数1】次，同1个目标最多可被选择【参数2】次，每次弹射造成的伤害降低第1次命中造成伤害的【参数3万分比】</t>
+  </si>
+  <si>
+    <t>触电时，触发触电伤害，有【参数2万分比】的几率触发【参数3】次【参数4技能id】</t>
+  </si>
+  <si>
+    <t>【瘟疫：附近任意目标施加瘟疫状态。】</t>
+  </si>
+  <si>
+    <t>3571302:1</t>
+  </si>
+  <si>
+    <t>3571303:1</t>
+  </si>
+  <si>
+    <t>技能效果-生存</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>损失血量触发获得护盾</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得护盾</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>有护盾时触发技能受到全属性伤害降低</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀触发额外回血</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>额外回复击回X倍的血量</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命值大于等于百万分比时触发技能触发全属性伤害提升</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命值低于百万分比时触发技能触发受到全属性伤害降低</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡时触发技能复活</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果-范围</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果-伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击伤害提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击触发释放技能多重打击</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>多重打击效果，额外造成X次X%的伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击触发释放旋风斩</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>旋风斩触发释放半月斩</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3600201:2</t>
+  </si>
+  <si>
+    <t>3600202:1</t>
+  </si>
+  <si>
+    <t>3600203:1</t>
+  </si>
+  <si>
+    <t>3600401:1</t>
+  </si>
+  <si>
+    <t>3600402:1</t>
+  </si>
+  <si>
+    <t>3600702:1</t>
+  </si>
+  <si>
+    <t>3600703:1</t>
+  </si>
+  <si>
+    <t>3601002:1</t>
+  </si>
+  <si>
+    <t>3601003:1</t>
+  </si>
+  <si>
+    <t>3601301:1</t>
+  </si>
+  <si>
+    <t>3601302:1</t>
+  </si>
+  <si>
+    <t>3601303:1</t>
+  </si>
+  <si>
+    <t>3610301:1</t>
+  </si>
+  <si>
+    <t>3610302:1</t>
+  </si>
+  <si>
+    <t>3610303:1</t>
+  </si>
+  <si>
+    <t>3610501:1</t>
+  </si>
+  <si>
+    <t>3610702:1</t>
+  </si>
+  <si>
+    <t>3610703:1</t>
+  </si>
+  <si>
+    <t>3590201:1</t>
+  </si>
+  <si>
+    <t>3590202:1</t>
+  </si>
+  <si>
+    <t>3590203:1</t>
+  </si>
+  <si>
+    <t>3590401:1</t>
+  </si>
+  <si>
+    <t>3590602:1</t>
+  </si>
+  <si>
+    <t>3590603:1</t>
+  </si>
+  <si>
+    <t>3590802:1</t>
+  </si>
+  <si>
+    <t>3590803:1</t>
+  </si>
+  <si>
+    <t>3591001:1</t>
+  </si>
+  <si>
+    <t>3591201:1</t>
+  </si>
+  <si>
+    <t>3591202:1</t>
+  </si>
+  <si>
+    <t>3591203:1</t>
+  </si>
+  <si>
+    <t>3591401:1</t>
+  </si>
+  <si>
+    <t>3591402:1</t>
+  </si>
+  <si>
+    <t>3591403:1</t>
+  </si>
+  <si>
+    <t>3591602:1</t>
+  </si>
+  <si>
+    <t>3591603:1</t>
+  </si>
+  <si>
+    <t>3591902:1</t>
+  </si>
+  <si>
+    <t>3600701:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击次数触发技能重击</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>重击技能暴击率提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能攻击累计额外次数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>斩杀暴击触发斩杀血线变化</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀触发暴击率提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击触发技能暴击伤害提高、致命暴击、额外次数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3590802:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3610901:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611301:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611303:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611701:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611502:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611503:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3590803:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能名称</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数描述</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>有护盾时受到伤害降低</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>低血时受到伤害降低</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能效果-敌人伤害降低</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能效果-敌人受到伤害提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能效果-光环效果影响范围变化</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标血量低于百万分比触发斩杀</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>斩杀血线提高效果</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581201:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581202:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581207:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3570902:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>MAP&lt;INT:INT&gt;_S</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT_S</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>attr_value_8_variable_id</t>
+  </si>
+  <si>
+    <t>attr_value_8_type</t>
+  </si>
+  <si>
+    <t>attr_value_8</t>
+  </si>
+  <si>
+    <t>参数8关联的变量id</t>
+  </si>
+  <si>
+    <t>参数8数值类型</t>
+  </si>
+  <si>
+    <t>参数8</t>
+  </si>
+  <si>
+    <t>每【参数8】毫秒，造成{[火元素直接伤害]【参数1万分比】}，【参数2】的[额外火元素持续伤害]，效果持续【参数5】毫秒，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>每【参数8】毫秒，触发等同于[毒元素直接伤害]*【参数1万分比毒持续buff系数】+【参数2】的[额外毒持续伤害]，效果持续【持续5】毫秒，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>每【参数8】毫秒，触发等同于[毒元素直接伤害]*【参数1万分比毒持续buff系数】+【参数2】的[额外毒持续伤害]，状态持续【持续5】毫秒，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>3041108:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>拥有这个技能效果时，命中敌人时，攻击者回复固定值【参数1固定值】的血量，触发冷却时间【参数8】毫秒</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3560208:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3580208:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581208:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3591002:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3591003:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧时，被攻击受到额外伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧时被攻击受到额外伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触电时，[受到所有类型伤害提高]【参数1万分比】+【参数2】受到[受到所有类型额外伤害固定值]</t>
+  </si>
+  <si>
+    <t>触电时受到伤害提高</t>
+  </si>
+  <si>
+    <t>3570503:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>使目标触电时，造成1次触电伤害</t>
+  </si>
+  <si>
+    <t>使目标触电时，造成1次触电伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰冻状态，持续时间【参数5】，冰冻状态命中率【参数6命中率】</t>
+  </si>
+  <si>
+    <t>每攻击【参数1】次，有【参数2】几率触发【参数3】次指定技能【参数4】</t>
+  </si>
+  <si>
+    <t>每【参数8】毫秒，在释放冰霜新星时有【参数2】几率，触发【参数3】次数，技能id【参数4】</t>
+  </si>
+  <si>
+    <t>对冰冻有配置标再次触发冰冻效果时，造成{[最终冰元素伤害]【参数1万分比】+【参数2固定值】}的[最终冰元素伤害</t>
+  </si>
+  <si>
+    <t>使目标冰冻时，触发目标{生命最大值【参数1百万分比】}的[冰元素基础伤害]+{【参数2固定值】}的[额外冰元素伤害固定值]</t>
+  </si>
+  <si>
+    <t>攻击冰冻目标时，造成{[冰元素最终伤害]【参数1万分比】+【参数2固定值】}的[额外最终冰元素伤害]，该效果每【参数8】毫秒触发1次。</t>
+  </si>
+  <si>
+    <t>攻击冰冻目标时造成额外伤害</t>
+  </si>
+  <si>
+    <t>中毒目标再次中毒受到额外中毒伤害</t>
+  </si>
+  <si>
+    <t>中毒目标再次中毒时，造成每次中毒结算伤害*【参数1】次数*【参数2万分比】的[最终毒元素伤害]</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3580702:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>复活回复血量、触发次数、触发间隔</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3591908:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3561401:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3561402:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3561408:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧时，被攻击会额外受到1次[最终火元素伤害]【参数1万分比】+【参数2固定值】的[额外最终火元素伤害]，该效果每【参数8】毫秒触发1次。</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3570205:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3580205:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581205:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3590405:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>致命暴击状态攻速提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3592101:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回血效果提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
     <t>3551103:2</t>
-  </si>
-  <si>
-    <t>3551301:1</t>
-  </si>
-  <si>
-    <t>3041101:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击速度提高</t>
-  </si>
-  <si>
-    <t>攻击提高</t>
-  </si>
-  <si>
-    <t>防御提高</t>
-  </si>
-  <si>
-    <t>生命提高</t>
-  </si>
-  <si>
-    <t>击中回血效果提高</t>
-  </si>
-  <si>
-    <t>暴击几率提高</t>
-  </si>
-  <si>
-    <t>暴击伤害提高</t>
-  </si>
-  <si>
-    <t>伤害提高</t>
-  </si>
-  <si>
-    <t>受到伤害提高</t>
-  </si>
-  <si>
-    <t>持续伤害提高</t>
-  </si>
-  <si>
-    <t>受到持续伤害提高</t>
-  </si>
-  <si>
-    <t>attr_value_7_variable_id</t>
-  </si>
-  <si>
-    <t>attr_value_7_type</t>
-  </si>
-  <si>
-    <t>attr_value_7</t>
-  </si>
-  <si>
-    <t>参数7关联的变量id</t>
-  </si>
-  <si>
-    <t>参数7数值类型</t>
-  </si>
-  <si>
-    <t>参数7</t>
-  </si>
-  <si>
-    <t>移动速度提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3540201:1</t>
-  </si>
-  <si>
-    <t>3540401:1</t>
-  </si>
-  <si>
-    <t>3540402:1</t>
-  </si>
-  <si>
-    <t>3540601:1</t>
-  </si>
-  <si>
-    <t>3540602:1</t>
-  </si>
-  <si>
-    <t>3540801:1</t>
-  </si>
-  <si>
-    <t>3540802:1</t>
-  </si>
-  <si>
-    <t>3541001:1</t>
-  </si>
-  <si>
-    <t>3541002:1</t>
-  </si>
-  <si>
-    <t>3541201:1</t>
-  </si>
-  <si>
-    <t>3541401:1</t>
-  </si>
-  <si>
-    <t>3541601:1</t>
-  </si>
-  <si>
-    <t>3541602:1</t>
-  </si>
-  <si>
-    <t>3541801:1</t>
-  </si>
-  <si>
-    <t>3541802:1</t>
-  </si>
-  <si>
-    <t>3542001:1</t>
-  </si>
-  <si>
-    <t>3542002:1</t>
-  </si>
-  <si>
-    <t>3542201:1</t>
-  </si>
-  <si>
-    <t>3542202:1</t>
-  </si>
-  <si>
-    <t>3542401:1</t>
-  </si>
-  <si>
-    <t>3540205:1</t>
-  </si>
-  <si>
-    <t>3540207:1</t>
-  </si>
-  <si>
-    <t>3540405:1</t>
-  </si>
-  <si>
-    <t>3540407:1</t>
-  </si>
-  <si>
-    <t>3540605:1</t>
-  </si>
-  <si>
-    <t>3540607:1</t>
-  </si>
-  <si>
-    <t>3540805:1</t>
-  </si>
-  <si>
-    <t>3540807:1</t>
-  </si>
-  <si>
-    <t>3541005:1</t>
-  </si>
-  <si>
-    <t>3541007:1</t>
-  </si>
-  <si>
-    <t>3541205:1</t>
-  </si>
-  <si>
-    <t>3541207:1</t>
-  </si>
-  <si>
-    <t>3541405:1</t>
-  </si>
-  <si>
-    <t>3541407:1</t>
-  </si>
-  <si>
-    <t>3541605:1</t>
-  </si>
-  <si>
-    <t>3541607:1</t>
-  </si>
-  <si>
-    <t>3541805:1</t>
-  </si>
-  <si>
-    <t>3541807:1</t>
-  </si>
-  <si>
-    <t>3542005:1</t>
-  </si>
-  <si>
-    <t>3542007:1</t>
-  </si>
-  <si>
-    <t>3542205:1</t>
-  </si>
-  <si>
-    <t>3542207:1</t>
-  </si>
-  <si>
-    <t>3542405:1</t>
-  </si>
-  <si>
-    <t>3542407:1</t>
-  </si>
-  <si>
-    <t>3551302:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3551501:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>多重冰霜新星</t>
-  </si>
-  <si>
-    <t>冰霜新星造成冰冻几率提高</t>
-  </si>
-  <si>
-    <t>冰冻时受到冰元素伤害</t>
-  </si>
-  <si>
-    <t>释放冰霜新星时，对敌人造成的冰冻几率增加【参数1万分比】</t>
-  </si>
-  <si>
-    <t>双重冰冻造成额外伤害</t>
-  </si>
-  <si>
-    <t>冰冻命中造成额外伤害</t>
-  </si>
-  <si>
-    <t>击中冰冻目标造成额外伤害</t>
-  </si>
-  <si>
-    <t>冰霜新星额外冰冻几率</t>
-  </si>
-  <si>
-    <t>攻击次数触发冰霜新星</t>
-  </si>
-  <si>
-    <t>攻击使目标冰冻</t>
-  </si>
-  <si>
-    <t>3550902:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击速度提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>攻击提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>防御提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>生命提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>击中回血效果提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>暴击几率提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>暴击伤害提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>受到伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>持续伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>受到持续伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>移动速度提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>获取护盾提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>全属性伤害提高</t>
-  </si>
-  <si>
-    <t>受到全属性伤害提高</t>
-  </si>
-  <si>
-    <t>全属性持续伤害提高</t>
-  </si>
-  <si>
-    <t>受到全属性持续伤害提高</t>
-  </si>
-  <si>
-    <t>移动速度提高</t>
-  </si>
-  <si>
-    <t>获取护盾提高</t>
-  </si>
-  <si>
-    <t>技能效果-通用</t>
-  </si>
-  <si>
-    <t>技能效果-冰</t>
-  </si>
-  <si>
-    <t>获取护盾提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>中毒死亡释放瘟疫</t>
-  </si>
-  <si>
-    <t>瘟疫状态</t>
-  </si>
-  <si>
-    <t>技能效果-火</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能效果-电</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能效果-毒</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧状态</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>自动释放陨石</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧状态受到伤害提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>陨石造成燃烧命中率增加</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧时死亡触发死亡爆炸</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>触电状态</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>闪电链弹射效果</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击触发释放闪电链</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>触电时受到伤害提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>触发触电伤害时释放电磁爆炸</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>中毒状态</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击触发传染</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3560201:1</t>
-  </si>
-  <si>
-    <t>3560202:1</t>
-  </si>
-  <si>
-    <t>3560205:1</t>
-  </si>
-  <si>
-    <t>3560206:1</t>
-  </si>
-  <si>
-    <t>3560501:2</t>
-  </si>
-  <si>
-    <t>3560502:1</t>
-  </si>
-  <si>
-    <t>3560503:1</t>
-  </si>
-  <si>
-    <t>3560701:1</t>
-  </si>
-  <si>
-    <t>3560901:1</t>
-  </si>
-  <si>
-    <t>3570201:1</t>
-  </si>
-  <si>
-    <t>3570202:1</t>
-  </si>
-  <si>
-    <t>3570501:1</t>
-  </si>
-  <si>
-    <t>3570502:1</t>
-  </si>
-  <si>
-    <t>3570701:2</t>
-  </si>
-  <si>
-    <t>3570702:1</t>
-  </si>
-  <si>
-    <t>3570703:1</t>
-  </si>
-  <si>
-    <t>3570901:1</t>
-  </si>
-  <si>
-    <t>3571101:1</t>
-  </si>
-  <si>
-    <t>3571102:1</t>
-  </si>
-  <si>
-    <t>3571103:1</t>
-  </si>
-  <si>
-    <t>3580201:1</t>
-  </si>
-  <si>
-    <t>3580202:1</t>
-  </si>
-  <si>
-    <t>3580207:1</t>
-  </si>
-  <si>
-    <t>3580501:2</t>
-  </si>
-  <si>
-    <t>3580502:1</t>
-  </si>
-  <si>
-    <t>3580503:1</t>
-  </si>
-  <si>
-    <t>3580701:1</t>
-  </si>
-  <si>
-    <t>3580902:1</t>
-  </si>
-  <si>
-    <t>3580903:1</t>
-  </si>
-  <si>
-    <t>3561102:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3561103:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>每【参数1】次攻击，有【参数2万分比】的几率触发【参数3】次【参数4技能id】</t>
-  </si>
-  <si>
-    <t>燃烧时，受到全种类攻击承受伤害提高【参数1万分比】</t>
-  </si>
-  <si>
-    <t>陨石造成伤害时，燃烧效果的命中率提升【参数1万分比】</t>
-  </si>
-  <si>
-    <t>燃烧时，死亡，有【参数2万分比】的几率触发【参数3】次【参数4技能id】</t>
-  </si>
-  <si>
-    <t>每次受到攻击会额外受到等同于[电元素最终伤害]【参数1万分比】</t>
-  </si>
-  <si>
-    <t>闪电链可弹射【参数1】次，同1个目标最多可被选择【参数2】次，每次弹射造成的伤害降低第1次命中造成伤害的【参数3万分比】</t>
-  </si>
-  <si>
-    <t>触电时，触发触电伤害，有【参数2万分比】的几率触发【参数3】次【参数4技能id】</t>
-  </si>
-  <si>
-    <t>【瘟疫：附近任意目标施加瘟疫状态。】</t>
-  </si>
-  <si>
-    <t>3571302:1</t>
-  </si>
-  <si>
-    <t>3571303:1</t>
-  </si>
-  <si>
-    <t>技能效果-生存</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>损失血量触发获得护盾</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得护盾</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>有护盾时触发技能受到全属性伤害降低</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀触发额外回血</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>额外回复击回X倍的血量</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>生命值大于等于百万分比时触发技能触发全属性伤害提升</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>生命值低于百万分比时触发技能触发受到全属性伤害降低</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>死亡时触发技能复活</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能效果-范围</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能效果-伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴击伤害提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击触发释放技能多重打击</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>多重打击效果，额外造成X次X%的伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击触发释放旋风斩</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>旋风斩触发释放半月斩</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3600201:2</t>
-  </si>
-  <si>
-    <t>3600202:1</t>
-  </si>
-  <si>
-    <t>3600203:1</t>
-  </si>
-  <si>
-    <t>3600401:1</t>
-  </si>
-  <si>
-    <t>3600402:1</t>
-  </si>
-  <si>
-    <t>3600702:1</t>
-  </si>
-  <si>
-    <t>3600703:1</t>
-  </si>
-  <si>
-    <t>3601002:1</t>
-  </si>
-  <si>
-    <t>3601003:1</t>
-  </si>
-  <si>
-    <t>3601301:1</t>
-  </si>
-  <si>
-    <t>3601302:1</t>
-  </si>
-  <si>
-    <t>3601303:1</t>
-  </si>
-  <si>
-    <t>3610301:1</t>
-  </si>
-  <si>
-    <t>3610302:1</t>
-  </si>
-  <si>
-    <t>3610303:1</t>
-  </si>
-  <si>
-    <t>3610501:1</t>
-  </si>
-  <si>
-    <t>3610702:1</t>
-  </si>
-  <si>
-    <t>3610703:1</t>
-  </si>
-  <si>
-    <t>3590201:1</t>
-  </si>
-  <si>
-    <t>3590202:1</t>
-  </si>
-  <si>
-    <t>3590203:1</t>
-  </si>
-  <si>
-    <t>3590401:1</t>
-  </si>
-  <si>
-    <t>3590602:1</t>
-  </si>
-  <si>
-    <t>3590603:1</t>
-  </si>
-  <si>
-    <t>3590802:1</t>
-  </si>
-  <si>
-    <t>3590803:1</t>
-  </si>
-  <si>
-    <t>3591001:1</t>
-  </si>
-  <si>
-    <t>3591201:1</t>
-  </si>
-  <si>
-    <t>3591202:1</t>
-  </si>
-  <si>
-    <t>3591203:1</t>
-  </si>
-  <si>
-    <t>3591401:1</t>
-  </si>
-  <si>
-    <t>3591402:1</t>
-  </si>
-  <si>
-    <t>3591403:1</t>
-  </si>
-  <si>
-    <t>3591602:1</t>
-  </si>
-  <si>
-    <t>3591603:1</t>
-  </si>
-  <si>
-    <t>3591902:1</t>
-  </si>
-  <si>
-    <t>3600701:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击次数触发技能重击</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>重击技能暴击率提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能攻击累计额外次数</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>斩杀暴击触发斩杀血线变化</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀触发暴击率提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴击触发技能暴击伤害提高、致命暴击、额外次数</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3590802:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3610901:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611301:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611303:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611701:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611502:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611503:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3590803:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能名称</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能效果</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数描述</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>有护盾时受到伤害降低</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>低血时受到伤害降低</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>光环技能效果-敌人伤害降低</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>光环技能效果-敌人受到伤害提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>光环技能效果-光环效果影响范围变化</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标血量低于百万分比触发斩杀</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>斩杀血线提高效果</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581201:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581202:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581207:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3570902:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>MAP&lt;INT:INT&gt;_S</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>INT_S</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>attr_value_8_variable_id</t>
-  </si>
-  <si>
-    <t>attr_value_8_type</t>
-  </si>
-  <si>
-    <t>attr_value_8</t>
-  </si>
-  <si>
-    <t>参数8关联的变量id</t>
-  </si>
-  <si>
-    <t>参数8数值类型</t>
-  </si>
-  <si>
-    <t>参数8</t>
-  </si>
-  <si>
-    <t>每【参数8】毫秒，造成{[火元素直接伤害]【参数1万分比】}，【参数2】的[额外火元素持续伤害]，效果持续【参数5】毫秒，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>每【参数8】毫秒，触发等同于[毒元素直接伤害]*【参数1万分比毒持续buff系数】+【参数2】的[额外毒持续伤害]，效果持续【持续5】毫秒，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>每【参数8】毫秒，触发等同于[毒元素直接伤害]*【参数1万分比毒持续buff系数】+【参数2】的[额外毒持续伤害]，状态持续【持续5】毫秒，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>3041108:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>拥有这个技能效果时，命中敌人时，攻击者回复固定值【参数1固定值】的血量，触发冷却时间【参数8】毫秒</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3560208:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3580208:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581208:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3591002:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3591003:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧时，被攻击受到额外伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧时被攻击受到额外伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>触电时，[受到所有类型伤害提高]【参数1万分比】+【参数2】受到[受到所有类型额外伤害固定值]</t>
-  </si>
-  <si>
-    <t>触电时受到伤害提高</t>
-  </si>
-  <si>
-    <t>3570503:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>使目标触电时，造成1次触电伤害</t>
-  </si>
-  <si>
-    <t>使目标触电时，造成1次触电伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰冻状态，持续时间【参数5】，冰冻状态命中率【参数6命中率】</t>
-  </si>
-  <si>
-    <t>每攻击【参数1】次，有【参数2】几率触发【参数3】次指定技能【参数4】</t>
-  </si>
-  <si>
-    <t>每【参数8】毫秒，在释放冰霜新星时有【参数2】几率，触发【参数3】次数，技能id【参数4】</t>
-  </si>
-  <si>
-    <t>对冰冻有配置标再次触发冰冻效果时，造成{[最终冰元素伤害]【参数1万分比】+【参数2固定值】}的[最终冰元素伤害</t>
-  </si>
-  <si>
-    <t>使目标冰冻时，触发目标{生命最大值【参数1百万分比】}的[冰元素基础伤害]+{【参数2固定值】}的[额外冰元素伤害固定值]</t>
-  </si>
-  <si>
-    <t>攻击冰冻目标时，造成{[冰元素最终伤害]【参数1万分比】+【参数2固定值】}的[额外最终冰元素伤害]，该效果每【参数8】毫秒触发1次。</t>
-  </si>
-  <si>
-    <t>攻击冰冻目标时造成额外伤害</t>
-  </si>
-  <si>
-    <t>中毒目标再次中毒受到额外中毒伤害</t>
-  </si>
-  <si>
-    <t>中毒目标再次中毒时，造成每次中毒结算伤害*【参数1】次数*【参数2万分比】的[最终毒元素伤害]</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3580702:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>复活回复血量、触发次数、触发间隔</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3591908:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3561401:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3561402:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3561408:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧时，被攻击会额外受到1次[最终火元素伤害]【参数1万分比】+【参数2固定值】的[额外最终火元素伤害]，该效果每【参数8】毫秒触发1次。</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3570205:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3580205:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581205:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3590405:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>致命暴击状态攻速提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3592101:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀回血效果提高</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -2116,13 +2117,13 @@
         <v>65</v>
       </c>
       <c r="AA2" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="AB2" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="AB2" s="7" t="s">
-        <v>328</v>
-      </c>
       <c r="AC2" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.2">
@@ -2196,22 +2197,22 @@
         <v>24</v>
       </c>
       <c r="X3" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y3" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="Y3" s="3" t="s">
+      <c r="Z3" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="Z3" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="AA3" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="AB3" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="AB3" s="7" t="s">
+      <c r="AC3" s="7" t="s">
         <v>330</v>
-      </c>
-      <c r="AC3" s="7" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.2">
@@ -2231,16 +2232,16 @@
         <v>64</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>30</v>
@@ -2285,22 +2286,22 @@
         <v>41</v>
       </c>
       <c r="X4" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y4" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="Y4" s="3" t="s">
+      <c r="Z4" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="Z4" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="AA4" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="AB4" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="AB4" s="7" t="s">
+      <c r="AC4" s="7" t="s">
         <v>333</v>
-      </c>
-      <c r="AC4" s="7" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.2">
@@ -2418,10 +2419,10 @@
         <v>47</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K6" s="6">
         <v>1</v>
@@ -2472,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="AA6" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AB6" s="6">
         <v>1</v>
@@ -2498,19 +2499,19 @@
         <v>3540200</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K7" s="15">
         <v>2</v>
@@ -2540,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="T7" s="15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="U7" s="15">
         <v>4000</v>
@@ -2552,7 +2553,7 @@
         <v>10000</v>
       </c>
       <c r="X7" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y7" s="15">
         <v>1</v>
@@ -2587,19 +2588,19 @@
         <v>3540400</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K8" s="15">
         <v>2</v>
@@ -2608,7 +2609,7 @@
         <v>500</v>
       </c>
       <c r="M8" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N8" s="15">
         <v>1</v>
@@ -2629,7 +2630,7 @@
         <v>0</v>
       </c>
       <c r="T8" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="U8" s="15">
         <v>4000</v>
@@ -2641,7 +2642,7 @@
         <v>10000</v>
       </c>
       <c r="X8" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Y8" s="15">
         <v>1</v>
@@ -2676,19 +2677,19 @@
         <v>3540600</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K9" s="15">
         <v>2</v>
@@ -2697,7 +2698,7 @@
         <v>500</v>
       </c>
       <c r="M9" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N9" s="15">
         <v>1</v>
@@ -2718,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="T9" s="15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="U9" s="15">
         <v>4000</v>
@@ -2730,7 +2731,7 @@
         <v>10000</v>
       </c>
       <c r="X9" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y9" s="15">
         <v>1</v>
@@ -2765,19 +2766,19 @@
         <v>3540800</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K10" s="15">
         <v>3</v>
@@ -2786,7 +2787,7 @@
         <v>50000</v>
       </c>
       <c r="M10" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N10" s="15">
         <v>1</v>
@@ -2807,7 +2808,7 @@
         <v>0</v>
       </c>
       <c r="T10" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U10" s="15">
         <v>4000</v>
@@ -2819,7 +2820,7 @@
         <v>10000</v>
       </c>
       <c r="X10" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Y10" s="15">
         <v>1</v>
@@ -2854,19 +2855,19 @@
         <v>3541000</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K11" s="15">
         <v>2</v>
@@ -2875,7 +2876,7 @@
         <v>500</v>
       </c>
       <c r="M11" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N11" s="15">
         <v>1</v>
@@ -2896,7 +2897,7 @@
         <v>0</v>
       </c>
       <c r="T11" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="U11" s="15">
         <v>4000</v>
@@ -2908,7 +2909,7 @@
         <v>10000</v>
       </c>
       <c r="X11" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Y11" s="15">
         <v>1</v>
@@ -2943,19 +2944,19 @@
         <v>3541200</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K12" s="15">
         <v>2</v>
@@ -2985,7 +2986,7 @@
         <v>0</v>
       </c>
       <c r="T12" s="15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="U12" s="15">
         <v>4000</v>
@@ -2997,7 +2998,7 @@
         <v>10000</v>
       </c>
       <c r="X12" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Y12" s="15">
         <v>1</v>
@@ -3032,19 +3033,19 @@
         <v>3541400</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K13" s="15">
         <v>2</v>
@@ -3074,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="T13" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="U13" s="15">
         <v>4000</v>
@@ -3086,7 +3087,7 @@
         <v>10000</v>
       </c>
       <c r="X13" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Y13" s="15">
         <v>1</v>
@@ -3121,19 +3122,19 @@
         <v>3541600</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J14" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K14" s="15">
         <v>2</v>
@@ -3142,7 +3143,7 @@
         <v>500</v>
       </c>
       <c r="M14" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N14" s="15">
         <v>1</v>
@@ -3163,7 +3164,7 @@
         <v>0</v>
       </c>
       <c r="T14" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="U14" s="15">
         <v>4000</v>
@@ -3175,7 +3176,7 @@
         <v>10000</v>
       </c>
       <c r="X14" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Y14" s="15">
         <v>1</v>
@@ -3210,19 +3211,19 @@
         <v>3541800</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K15" s="15">
         <v>2</v>
@@ -3231,7 +3232,7 @@
         <v>500</v>
       </c>
       <c r="M15" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N15" s="15">
         <v>1</v>
@@ -3252,7 +3253,7 @@
         <v>0</v>
       </c>
       <c r="T15" s="15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="U15" s="15">
         <v>4000</v>
@@ -3264,7 +3265,7 @@
         <v>10000</v>
       </c>
       <c r="X15" s="15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y15" s="15">
         <v>1</v>
@@ -3299,19 +3300,19 @@
         <v>3542000</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J16" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K16" s="15">
         <v>2</v>
@@ -3320,7 +3321,7 @@
         <v>500</v>
       </c>
       <c r="M16" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N16" s="15">
         <v>1</v>
@@ -3341,7 +3342,7 @@
         <v>0</v>
       </c>
       <c r="T16" s="15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="U16" s="15">
         <v>4000</v>
@@ -3353,7 +3354,7 @@
         <v>10000</v>
       </c>
       <c r="X16" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Y16" s="15">
         <v>1</v>
@@ -3388,19 +3389,19 @@
         <v>3542200</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K17" s="15">
         <v>2</v>
@@ -3409,7 +3410,7 @@
         <v>500</v>
       </c>
       <c r="M17" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N17" s="15">
         <v>1</v>
@@ -3430,7 +3431,7 @@
         <v>0</v>
       </c>
       <c r="T17" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="U17" s="15">
         <v>4000</v>
@@ -3442,7 +3443,7 @@
         <v>10000</v>
       </c>
       <c r="X17" s="15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Y17" s="15">
         <v>1</v>
@@ -3477,19 +3478,19 @@
         <v>3542400</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J18" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K18" s="15">
         <v>2</v>
@@ -3519,7 +3520,7 @@
         <v>0</v>
       </c>
       <c r="T18" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="U18" s="15">
         <v>4000</v>
@@ -3531,7 +3532,7 @@
         <v>10000</v>
       </c>
       <c r="X18" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Y18" s="15">
         <v>1</v>
@@ -3566,19 +3567,19 @@
         <v>3542600</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I19" s="16" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K19" s="15">
         <v>2</v>
@@ -3608,7 +3609,7 @@
         <v>0</v>
       </c>
       <c r="T19" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="U19" s="15">
         <v>4000</v>
@@ -3620,7 +3621,7 @@
         <v>10000</v>
       </c>
       <c r="X19" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Y19" s="15">
         <v>1</v>
@@ -3658,13 +3659,13 @@
         <v>69</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J20" s="17" t="s">
         <v>43</v>
@@ -3706,7 +3707,7 @@
         <v>79</v>
       </c>
       <c r="W20" s="17">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="X20" s="17" t="s">
         <v>43</v>
@@ -3747,13 +3748,13 @@
         <v>71</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J21" s="17" t="s">
         <v>80</v>
@@ -3762,7 +3763,7 @@
         <v>1</v>
       </c>
       <c r="L21" s="17">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M21" s="17" t="s">
         <v>81</v>
@@ -3836,13 +3837,13 @@
         <v>72</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="J22" s="17" t="s">
         <v>43</v>
@@ -3925,13 +3926,13 @@
         <v>74</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="J23" s="17" t="s">
         <v>85</v>
@@ -3943,7 +3944,7 @@
         <v>3000</v>
       </c>
       <c r="M23" s="17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N23" s="17">
         <v>0</v>
@@ -4011,16 +4012,16 @@
         <v>3551100</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J24" s="17" t="s">
         <v>86</v>
@@ -4029,7 +4030,7 @@
         <v>3</v>
       </c>
       <c r="L24" s="17">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="M24" s="17" t="s">
         <v>87</v>
@@ -4038,10 +4039,10 @@
         <v>1</v>
       </c>
       <c r="O24" s="17">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P24" s="17" t="s">
-        <v>88</v>
+        <v>374</v>
       </c>
       <c r="Q24" s="17">
         <v>1</v>
@@ -4100,19 +4101,19 @@
         <v>3551300</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K25" s="17">
         <v>2</v>
@@ -4121,7 +4122,7 @@
         <v>5000</v>
       </c>
       <c r="M25" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N25" s="17">
         <v>1</v>
@@ -4189,19 +4190,19 @@
         <v>3551500</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K26" s="17">
         <v>2</v>
@@ -4278,19 +4279,19 @@
         <v>3560200</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J27" s="18" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K27" s="18">
         <v>2</v>
@@ -4299,7 +4300,7 @@
         <v>5000</v>
       </c>
       <c r="M27" s="18" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N27" s="18">
         <v>1</v>
@@ -4320,13 +4321,13 @@
         <v>0</v>
       </c>
       <c r="T27" s="18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="U27" s="18">
         <v>4000</v>
       </c>
       <c r="V27" s="18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W27" s="18">
         <v>1500</v>
@@ -4341,7 +4342,7 @@
         <v>1</v>
       </c>
       <c r="AA27" s="18" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AB27" s="18">
         <v>1</v>
@@ -4367,19 +4368,19 @@
         <v>3560500</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J28" s="18" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K28" s="18">
         <v>1</v>
@@ -4388,16 +4389,16 @@
         <v>8</v>
       </c>
       <c r="M28" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="N28" s="18">
+        <v>1</v>
+      </c>
+      <c r="O28" s="18">
+        <v>10000</v>
+      </c>
+      <c r="P28" s="18" t="s">
         <v>210</v>
-      </c>
-      <c r="N28" s="18">
-        <v>1</v>
-      </c>
-      <c r="O28" s="18">
-        <v>10000</v>
-      </c>
-      <c r="P28" s="18" t="s">
-        <v>211</v>
       </c>
       <c r="Q28" s="18">
         <v>1</v>
@@ -4456,19 +4457,19 @@
         <v>3560700</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J29" s="18" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K29" s="18">
         <v>2</v>
@@ -4545,19 +4546,19 @@
         <v>3560900</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J30" s="18" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K30" s="18">
         <v>2</v>
@@ -4634,16 +4635,16 @@
         <v>3561100</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J31" s="18" t="s">
         <v>43</v>
@@ -4655,7 +4656,7 @@
         <v>0</v>
       </c>
       <c r="M31" s="18" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="N31" s="18">
         <v>2</v>
@@ -4664,7 +4665,7 @@
         <v>10000</v>
       </c>
       <c r="P31" s="18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Q31" s="18">
         <v>1</v>
@@ -4723,19 +4724,19 @@
         <v>3561400</v>
       </c>
       <c r="F32" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="H32" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="G32" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="H32" s="13" t="s">
-        <v>346</v>
-      </c>
       <c r="I32" s="13" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="J32" s="18" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K32" s="18">
         <v>2</v>
@@ -4744,7 +4745,7 @@
         <v>3500</v>
       </c>
       <c r="M32" s="18" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="N32" s="18">
         <v>35</v>
@@ -4786,7 +4787,7 @@
         <v>1</v>
       </c>
       <c r="AA32" s="18" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AB32" s="18">
         <v>1</v>
@@ -4812,19 +4813,19 @@
         <v>3570200</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J33" s="19" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K33" s="19">
         <v>2</v>
@@ -4833,7 +4834,7 @@
         <v>4000</v>
       </c>
       <c r="M33" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="N33" s="19">
         <v>1</v>
@@ -4854,7 +4855,7 @@
         <v>0</v>
       </c>
       <c r="T33" s="19" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="U33" s="19">
         <v>4000</v>
@@ -4901,19 +4902,19 @@
         <v>3570500</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J34" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K34" s="19">
         <v>1</v>
@@ -4922,7 +4923,7 @@
         <v>3</v>
       </c>
       <c r="M34" s="19" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N34" s="19">
         <v>1</v>
@@ -4931,7 +4932,7 @@
         <v>1</v>
       </c>
       <c r="P34" s="19" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="Q34" s="19">
         <v>2</v>
@@ -4990,19 +4991,19 @@
         <v>3570700</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J35" s="19" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K35" s="19">
         <v>1</v>
@@ -5011,7 +5012,7 @@
         <v>8</v>
       </c>
       <c r="M35" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N35" s="19">
         <v>2</v>
@@ -5020,7 +5021,7 @@
         <v>10000</v>
       </c>
       <c r="P35" s="19" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q35" s="19">
         <v>1</v>
@@ -5079,19 +5080,19 @@
         <v>3570900</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J36" s="19" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K36" s="19">
         <v>2</v>
@@ -5100,7 +5101,7 @@
         <v>2000</v>
       </c>
       <c r="M36" s="19" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N36" s="19">
         <v>1</v>
@@ -5168,19 +5169,19 @@
         <v>3571100</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J37" s="19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K37" s="19">
         <v>2</v>
@@ -5189,16 +5190,16 @@
         <v>10000</v>
       </c>
       <c r="M37" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="N37" s="19">
+        <v>1</v>
+      </c>
+      <c r="O37" s="19">
+        <v>1</v>
+      </c>
+      <c r="P37" s="19" t="s">
         <v>223</v>
-      </c>
-      <c r="N37" s="19">
-        <v>1</v>
-      </c>
-      <c r="O37" s="19">
-        <v>1</v>
-      </c>
-      <c r="P37" s="19" t="s">
-        <v>224</v>
       </c>
       <c r="Q37" s="19">
         <v>1</v>
@@ -5257,16 +5258,16 @@
         <v>3571300</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J38" s="19" t="s">
         <v>43</v>
@@ -5278,7 +5279,7 @@
         <v>0</v>
       </c>
       <c r="M38" s="19" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="N38" s="19">
         <v>2</v>
@@ -5287,7 +5288,7 @@
         <v>10000</v>
       </c>
       <c r="P38" s="19" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q38" s="19">
         <v>1</v>
@@ -5346,19 +5347,19 @@
         <v>3580200</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J39" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K39" s="20">
         <v>2</v>
@@ -5367,7 +5368,7 @@
         <v>3000</v>
       </c>
       <c r="M39" s="20" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="N39" s="20">
         <v>1</v>
@@ -5388,7 +5389,7 @@
         <v>0</v>
       </c>
       <c r="T39" s="20" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="U39" s="20">
         <v>4000</v>
@@ -5400,7 +5401,7 @@
         <v>10000</v>
       </c>
       <c r="X39" s="20" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Y39" s="20">
         <v>1</v>
@@ -5409,7 +5410,7 @@
         <v>1</v>
       </c>
       <c r="AA39" s="20" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AB39" s="20">
         <v>1</v>
@@ -5435,19 +5436,19 @@
         <v>3580500</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J40" s="20" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K40" s="20">
         <v>1</v>
@@ -5456,7 +5457,7 @@
         <v>8</v>
       </c>
       <c r="M40" s="20" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="N40" s="20">
         <v>2</v>
@@ -5465,7 +5466,7 @@
         <v>10000</v>
       </c>
       <c r="P40" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q40" s="20">
         <v>1</v>
@@ -5524,19 +5525,19 @@
         <v>3580700</v>
       </c>
       <c r="F41" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="H41" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="I41" s="13" t="s">
         <v>359</v>
       </c>
-      <c r="G41" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="H41" s="13" t="s">
-        <v>359</v>
-      </c>
-      <c r="I41" s="13" t="s">
-        <v>360</v>
-      </c>
       <c r="J41" s="20" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K41" s="20">
         <v>1</v>
@@ -5545,7 +5546,7 @@
         <v>5</v>
       </c>
       <c r="M41" s="20" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="N41" s="20">
         <v>2</v>
@@ -5613,16 +5614,16 @@
         <v>3580900</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J42" s="20" t="s">
         <v>43</v>
@@ -5634,7 +5635,7 @@
         <v>0</v>
       </c>
       <c r="M42" s="20" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N42" s="20">
         <v>2</v>
@@ -5643,7 +5644,7 @@
         <v>10000</v>
       </c>
       <c r="P42" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q42" s="20">
         <v>1</v>
@@ -5702,19 +5703,19 @@
         <v>3581200</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J43" s="20" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="K43" s="20">
         <v>2</v>
@@ -5723,7 +5724,7 @@
         <v>3000</v>
       </c>
       <c r="M43" s="20" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N43" s="20">
         <v>0</v>
@@ -5744,7 +5745,7 @@
         <v>0</v>
       </c>
       <c r="T43" s="20" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="U43" s="20">
         <v>4000</v>
@@ -5756,7 +5757,7 @@
         <v>10000</v>
       </c>
       <c r="X43" s="20" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Y43" s="20">
         <v>1</v>
@@ -5765,7 +5766,7 @@
         <v>10</v>
       </c>
       <c r="AA43" s="20" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AB43" s="20">
         <v>1</v>
@@ -5791,15 +5792,15 @@
         <v>3590200</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H44" s="13"/>
       <c r="I44" s="13"/>
       <c r="J44" s="24" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K44" s="24">
         <v>3</v>
@@ -5808,7 +5809,7 @@
         <v>200000</v>
       </c>
       <c r="M44" s="24" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N44" s="24">
         <v>2</v>
@@ -5817,7 +5818,7 @@
         <v>10000</v>
       </c>
       <c r="P44" s="24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q44" s="24">
         <v>1</v>
@@ -5876,15 +5877,15 @@
         <v>3590400</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H45" s="13"/>
       <c r="I45" s="13"/>
       <c r="J45" s="24" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K45" s="24">
         <v>3</v>
@@ -5914,7 +5915,7 @@
         <v>59030001</v>
       </c>
       <c r="T45" s="24" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="U45" s="24">
         <v>-1</v>
@@ -5961,10 +5962,10 @@
         <v>3590600</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H46" s="13"/>
       <c r="I46" s="13"/>
@@ -5978,7 +5979,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N46" s="24">
         <v>2</v>
@@ -5987,7 +5988,7 @@
         <v>10000</v>
       </c>
       <c r="P46" s="24" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q46" s="24">
         <v>1</v>
@@ -6046,10 +6047,10 @@
         <v>3590800</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H47" s="13"/>
       <c r="I47" s="13"/>
@@ -6063,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="24" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="N47" s="24">
         <v>2</v>
@@ -6072,7 +6073,7 @@
         <v>10000</v>
       </c>
       <c r="P47" s="24" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q47" s="24">
         <v>1</v>
@@ -6131,15 +6132,15 @@
         <v>3591000</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H48" s="13"/>
       <c r="I48" s="13"/>
       <c r="J48" s="24" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K48" s="24">
         <v>2</v>
@@ -6148,16 +6149,16 @@
         <v>0</v>
       </c>
       <c r="M48" s="24" t="s">
+        <v>342</v>
+      </c>
+      <c r="N48" s="24">
+        <v>1</v>
+      </c>
+      <c r="O48" s="24">
+        <v>0</v>
+      </c>
+      <c r="P48" s="24" t="s">
         <v>343</v>
-      </c>
-      <c r="N48" s="24">
-        <v>1</v>
-      </c>
-      <c r="O48" s="24">
-        <v>0</v>
-      </c>
-      <c r="P48" s="24" t="s">
-        <v>344</v>
       </c>
       <c r="Q48" s="24">
         <v>3</v>
@@ -6216,15 +6217,15 @@
         <v>3591200</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H49" s="13"/>
       <c r="I49" s="13"/>
       <c r="J49" s="24" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K49" s="24">
         <v>3</v>
@@ -6233,7 +6234,7 @@
         <v>1000000</v>
       </c>
       <c r="M49" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N49" s="24">
         <v>2</v>
@@ -6242,7 +6243,7 @@
         <v>10000</v>
       </c>
       <c r="P49" s="24" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q49" s="24">
         <v>1</v>
@@ -6301,15 +6302,15 @@
         <v>3591400</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H50" s="13"/>
       <c r="I50" s="13"/>
       <c r="J50" s="24" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K50" s="24">
         <v>3</v>
@@ -6318,7 +6319,7 @@
         <v>500000</v>
       </c>
       <c r="M50" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="N50" s="24">
         <v>2</v>
@@ -6327,7 +6328,7 @@
         <v>10000</v>
       </c>
       <c r="P50" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Q50" s="24">
         <v>1</v>
@@ -6386,10 +6387,10 @@
         <v>3591600</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H51" s="13"/>
       <c r="I51" s="13"/>
@@ -6403,7 +6404,7 @@
         <v>0</v>
       </c>
       <c r="M51" s="24" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="N51" s="24">
         <v>2</v>
@@ -6412,7 +6413,7 @@
         <v>10000</v>
       </c>
       <c r="P51" s="24" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q51" s="24">
         <v>1</v>
@@ -6471,10 +6472,10 @@
         <v>3591900</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H52" s="13"/>
       <c r="I52" s="13"/>
@@ -6488,7 +6489,7 @@
         <v>0</v>
       </c>
       <c r="M52" s="24" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="N52" s="24">
         <v>1</v>
@@ -6530,7 +6531,7 @@
         <v>1</v>
       </c>
       <c r="AA52" s="24" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AB52" s="24">
         <v>1</v>
@@ -6556,10 +6557,10 @@
         <v>3541800</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H53" s="13"/>
       <c r="I53" s="13"/>
@@ -6641,10 +6642,10 @@
         <v>3541800</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G54" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H54" s="13"/>
       <c r="I54" s="13"/>
@@ -6726,15 +6727,15 @@
         <v>3592100</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H55" s="13"/>
       <c r="I55" s="13"/>
       <c r="J55" s="24" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="K55" s="24">
         <v>2</v>
@@ -6811,15 +6812,15 @@
         <v>3600200</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H56" s="13"/>
       <c r="I56" s="13"/>
       <c r="J56" s="21" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K56" s="21">
         <v>1</v>
@@ -6828,7 +6829,7 @@
         <v>8</v>
       </c>
       <c r="M56" s="21" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N56" s="21">
         <v>2</v>
@@ -6837,7 +6838,7 @@
         <v>10000</v>
       </c>
       <c r="P56" s="21" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q56" s="21">
         <v>1</v>
@@ -6896,24 +6897,24 @@
         <v>3600400</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G57" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H57" s="13"/>
       <c r="I57" s="13"/>
       <c r="J57" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="K57" s="21">
+        <v>1</v>
+      </c>
+      <c r="L57" s="21">
+        <v>1</v>
+      </c>
+      <c r="M57" s="21" t="s">
         <v>265</v>
-      </c>
-      <c r="K57" s="21">
-        <v>1</v>
-      </c>
-      <c r="L57" s="21">
-        <v>1</v>
-      </c>
-      <c r="M57" s="21" t="s">
-        <v>266</v>
       </c>
       <c r="N57" s="21">
         <v>2</v>
@@ -6981,15 +6982,15 @@
         <v>3600700</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G58" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H58" s="13"/>
       <c r="I58" s="13"/>
       <c r="J58" s="21" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K58" s="21">
         <v>1</v>
@@ -6998,7 +6999,7 @@
         <v>8</v>
       </c>
       <c r="M58" s="21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N58" s="21">
         <v>2</v>
@@ -7007,7 +7008,7 @@
         <v>10000</v>
       </c>
       <c r="P58" s="21" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q58" s="21">
         <v>1</v>
@@ -7066,10 +7067,10 @@
         <v>3601000</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H59" s="13"/>
       <c r="I59" s="13"/>
@@ -7083,7 +7084,7 @@
         <v>0</v>
       </c>
       <c r="M59" s="21" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N59" s="21">
         <v>2</v>
@@ -7092,7 +7093,7 @@
         <v>10000</v>
       </c>
       <c r="P59" s="21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q59" s="21">
         <v>1</v>
@@ -7151,15 +7152,15 @@
         <v>3541600</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H60" s="13"/>
       <c r="I60" s="13"/>
       <c r="J60" s="21" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K60" s="21">
         <v>2</v>
@@ -7236,15 +7237,15 @@
         <v>3541800</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G61" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H61" s="13"/>
       <c r="I61" s="13"/>
       <c r="J61" s="21" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K61" s="21">
         <v>2</v>
@@ -7321,15 +7322,15 @@
         <v>3601300</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G62" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H62" s="13"/>
       <c r="I62" s="13"/>
       <c r="J62" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K62" s="21">
         <v>2</v>
@@ -7338,7 +7339,7 @@
         <v>10000</v>
       </c>
       <c r="M62" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N62" s="21">
         <v>2</v>
@@ -7347,7 +7348,7 @@
         <v>2000</v>
       </c>
       <c r="P62" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q62" s="21">
         <v>1</v>
@@ -7406,15 +7407,15 @@
         <v>3610300</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G63" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H63" s="13"/>
       <c r="I63" s="13"/>
       <c r="J63" s="22" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K63" s="22">
         <v>1</v>
@@ -7423,7 +7424,7 @@
         <v>8</v>
       </c>
       <c r="M63" s="22" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N63" s="22">
         <v>2</v>
@@ -7432,7 +7433,7 @@
         <v>10000</v>
       </c>
       <c r="P63" s="22" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q63" s="22">
         <v>1</v>
@@ -7491,15 +7492,15 @@
         <v>3610500</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G64" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H64" s="13"/>
       <c r="I64" s="13"/>
       <c r="J64" s="22" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K64" s="22">
         <v>2</v>
@@ -7576,10 +7577,10 @@
         <v>3610700</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G65" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H65" s="13"/>
       <c r="I65" s="13"/>
@@ -7593,7 +7594,7 @@
         <v>0</v>
       </c>
       <c r="M65" s="22" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="N65" s="22">
         <v>2</v>
@@ -7602,7 +7603,7 @@
         <v>10000</v>
       </c>
       <c r="P65" s="22" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q65" s="22">
         <v>1</v>
@@ -7661,15 +7662,15 @@
         <v>3541400</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H66" s="13"/>
       <c r="I66" s="13"/>
       <c r="J66" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K66" s="22">
         <v>2</v>
@@ -7746,15 +7747,15 @@
         <v>3610900</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H67" s="13"/>
       <c r="I67" s="13"/>
       <c r="J67" s="22" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K67" s="22">
         <v>1</v>
@@ -7831,10 +7832,10 @@
         <v>3611100</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G68" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H68" s="13"/>
       <c r="I68" s="13"/>
@@ -7916,15 +7917,15 @@
         <v>3611300</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G69" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H69" s="13"/>
       <c r="I69" s="13"/>
       <c r="J69" s="22" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K69" s="22">
         <v>3</v>
@@ -7942,7 +7943,7 @@
         <v>0</v>
       </c>
       <c r="P69" s="22" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q69" s="22">
         <v>1</v>
@@ -8001,10 +8002,10 @@
         <v>3611500</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G70" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H70" s="13"/>
       <c r="I70" s="13"/>
@@ -8018,7 +8019,7 @@
         <v>0</v>
       </c>
       <c r="M70" s="22" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N70" s="22">
         <v>2</v>
@@ -8027,7 +8028,7 @@
         <v>10000</v>
       </c>
       <c r="P70" s="22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q70" s="22">
         <v>1</v>
@@ -8086,15 +8087,15 @@
         <v>3611700</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G71" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H71" s="13"/>
       <c r="I71" s="13"/>
       <c r="J71" s="22" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K71" s="22">
         <v>3</v>
@@ -8171,10 +8172,10 @@
         <v>3590800</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G72" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H72" s="13"/>
       <c r="I72" s="13"/>
@@ -8188,7 +8189,7 @@
         <v>0</v>
       </c>
       <c r="M72" s="22" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="N72" s="22">
         <v>2</v>
@@ -8197,7 +8198,7 @@
         <v>10000</v>
       </c>
       <c r="P72" s="22" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q72" s="22">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5AF3AC5-BA51-4464-A8AD-078CE6583EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E89779E-6FAA-4DF9-B7FD-A79767996087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
-    <sheet name="备注" sheetId="2" r:id="rId2"/>
+    <sheet name="新表结构" sheetId="3" r:id="rId2"/>
+    <sheet name="备注" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skilleffect_v8!$A$4:$AC$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skilleffect_v8!$A$4:$AC$74</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -125,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="533">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1352,6 +1353,549 @@
   </si>
   <si>
     <t>3551103:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数8结算间隔时间</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>逻辑属性id</t>
+  </si>
+  <si>
+    <t>技能效果</t>
+  </si>
+  <si>
+    <t>技能名称</t>
+  </si>
+  <si>
+    <t>参数描述</t>
+  </si>
+  <si>
+    <t>效果叠加层数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>结算间隔时间（毫秒）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复中buff组的cd时间（毫秒）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数5</t>
+  </si>
+  <si>
+    <t>参数6</t>
+  </si>
+  <si>
+    <t>持续时间（毫秒）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果最大叠加层数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果基础命中率（万分比）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果触发间隔（毫秒）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数4LIST</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发的技能id</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数9</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数10</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数11</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数12</t>
+  </si>
+  <si>
+    <t>参数13</t>
+  </si>
+  <si>
+    <t>击中回复生命值-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击中回复效果提高万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回复生命-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数14</t>
+  </si>
+  <si>
+    <t>参数15</t>
+  </si>
+  <si>
+    <t>参数16</t>
+  </si>
+  <si>
+    <t>击中回复生命值-自身最大生命值百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回复生命-自身最大生命值百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回复生命-目标最大生命值百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数17</t>
+  </si>
+  <si>
+    <t>参数18</t>
+  </si>
+  <si>
+    <t>参数19</t>
+  </si>
+  <si>
+    <t>参数20</t>
+  </si>
+  <si>
+    <t>参数21</t>
+  </si>
+  <si>
+    <t>参数22</t>
+  </si>
+  <si>
+    <t>参数28</t>
+  </si>
+  <si>
+    <t>参数29</t>
+  </si>
+  <si>
+    <t>获得护盾-自身生命百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得护盾-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得护盾效果提高万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回复生命效果提高万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得护盾-自身已损失生命万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>复活</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发自动技能</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数30</t>
+  </si>
+  <si>
+    <t>参数31</t>
+  </si>
+  <si>
+    <t>参数32</t>
+  </si>
+  <si>
+    <t>参数33</t>
+  </si>
+  <si>
+    <t>参数34</t>
+  </si>
+  <si>
+    <t>参数35</t>
+  </si>
+  <si>
+    <t>参数36</t>
+  </si>
+  <si>
+    <t>参数37</t>
+  </si>
+  <si>
+    <t>参数38</t>
+  </si>
+  <si>
+    <t>参数39</t>
+  </si>
+  <si>
+    <t>参数40</t>
+  </si>
+  <si>
+    <t>参数41</t>
+  </si>
+  <si>
+    <t>参数42</t>
+  </si>
+  <si>
+    <t>参数43</t>
+  </si>
+  <si>
+    <t>参数44</t>
+  </si>
+  <si>
+    <t>主动技能</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>回复生命</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击中目标</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰霜新星</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪电链</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>传染</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>瘟疫</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>多重打击</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>旋风斩</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>斩杀</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>半月斩</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡爆炸</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>电磁爆发</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>重击</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能增加-万分比</t>
+  </si>
+  <si>
+    <t>技能增加-普通攻击范围万分比</t>
+  </si>
+  <si>
+    <t>攻击提高-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御提高-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击提高-攻击的元素类型</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数25LIST</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数45</t>
+  </si>
+  <si>
+    <t>参数46</t>
+  </si>
+  <si>
+    <t>参数47</t>
+  </si>
+  <si>
+    <t>参数48</t>
+  </si>
+  <si>
+    <t>参数49</t>
+  </si>
+  <si>
+    <t>参数50</t>
+  </si>
+  <si>
+    <t>参数51</t>
+  </si>
+  <si>
+    <t>参数52</t>
+  </si>
+  <si>
+    <t>参数53</t>
+  </si>
+  <si>
+    <t>参数54</t>
+  </si>
+  <si>
+    <t>参数55</t>
+  </si>
+  <si>
+    <t>参数56</t>
+  </si>
+  <si>
+    <t>生命上限提高-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命上限提高-百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击速度提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动速度提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击范围提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击目标数量提高-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能增加-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT_S</t>
+  </si>
+  <si>
+    <t>auto_cd</t>
+  </si>
+  <si>
+    <t>参数-重复触发自动释放冷却时间（毫秒）</t>
+  </si>
+  <si>
+    <t>release_ratio</t>
+  </si>
+  <si>
+    <t>参数-释放几率</t>
+  </si>
+  <si>
+    <t>release_num</t>
+  </si>
+  <si>
+    <t>参数-释放次数</t>
+  </si>
+  <si>
+    <t>LIST&lt;INT&gt;_S</t>
+  </si>
+  <si>
+    <t>skill_id</t>
+  </si>
+  <si>
+    <t>参数-释放的技能id</t>
+  </si>
+  <si>
+    <t>total_attack_num</t>
+  </si>
+  <si>
+    <t>参数-累计发起攻击次数时</t>
+  </si>
+  <si>
+    <t>lose_hp_ratio</t>
+  </si>
+  <si>
+    <t>参数-损失自身生命最大值百万分比时</t>
+  </si>
+  <si>
+    <t>kill_target_after</t>
+  </si>
+  <si>
+    <t>参数-击杀目标后</t>
+  </si>
+  <si>
+    <t>after_attack_crit</t>
+  </si>
+  <si>
+    <t>参数-攻击暴击后</t>
+  </si>
+  <si>
+    <t>after_use_skill</t>
+  </si>
+  <si>
+    <t>参数-释放【技能id】后</t>
+  </si>
+  <si>
+    <t>cycle_time</t>
+  </si>
+  <si>
+    <t>参数-每过固定时间（毫秒）时</t>
+  </si>
+  <si>
+    <t>after_skill_hit</t>
+  </si>
+  <si>
+    <t>参数-【技能id】命中后</t>
+  </si>
+  <si>
+    <t>after_self_death</t>
+  </si>
+  <si>
+    <t>参数-自身死亡后释放</t>
+  </si>
+  <si>
+    <t>MAP&lt;INT:INT&gt;_S</t>
+  </si>
+  <si>
+    <t>self_have_effect</t>
+  </si>
+  <si>
+    <t>参数-自身拥有【效果id：&gt;=层数】时</t>
+  </si>
+  <si>
+    <t>target_have_effect</t>
+  </si>
+  <si>
+    <t>参数-目标拥有【效果id：&gt;=层数】时</t>
+  </si>
+  <si>
+    <t>target_hp_ratio_over</t>
+  </si>
+  <si>
+    <t>参数-目标当前生命值&gt;=最大生命值的百万分之X时</t>
+  </si>
+  <si>
+    <t>target_hp_ratio_under</t>
+  </si>
+  <si>
+    <t>参数-目标当前生命值&lt;=最大生命值的百万分之X时</t>
+  </si>
+  <si>
+    <t>to_target_effect_hit</t>
+  </si>
+  <si>
+    <t>参数-对目标施加【效果id】命中时</t>
+  </si>
+  <si>
+    <t>order</t>
+  </si>
+  <si>
+    <t>自动</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>受到的伤害总加成</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成伤害总加成</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成的伤害总加成【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到的伤害总加成【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542801:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542601:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3543001:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542607:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542807:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3543007:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542605:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542805:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3543005:1</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -1974,7 +2518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:AC74"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -2301,7 +2845,7 @@
         <v>332</v>
       </c>
       <c r="AC4" s="7" t="s">
-        <v>333</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.2">
@@ -3579,7 +4123,7 @@
         <v>177</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>127</v>
+        <v>525</v>
       </c>
       <c r="K19" s="15">
         <v>2</v>
@@ -3609,7 +4153,7 @@
         <v>0</v>
       </c>
       <c r="T19" s="15" t="s">
-        <v>150</v>
+        <v>530</v>
       </c>
       <c r="U19" s="15">
         <v>4000</v>
@@ -3621,7 +4165,7 @@
         <v>10000</v>
       </c>
       <c r="X19" s="15" t="s">
-        <v>151</v>
+        <v>527</v>
       </c>
       <c r="Y19" s="15">
         <v>1</v>
@@ -3640,189 +4184,189 @@
       </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A20" s="17">
-        <v>55010001</v>
-      </c>
-      <c r="B20" s="17">
-        <v>5501</v>
-      </c>
-      <c r="C20" s="17">
-        <v>1</v>
-      </c>
-      <c r="D20" s="17">
-        <v>0</v>
-      </c>
-      <c r="E20" s="17">
-        <v>3550200</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>351</v>
-      </c>
-      <c r="J20" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="K20" s="17">
-        <v>0</v>
-      </c>
-      <c r="L20" s="17">
-        <v>0</v>
-      </c>
-      <c r="M20" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="N20" s="17">
-        <v>0</v>
-      </c>
-      <c r="O20" s="17">
-        <v>0</v>
-      </c>
-      <c r="P20" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q20" s="17">
-        <v>0</v>
-      </c>
-      <c r="R20" s="17">
-        <v>0</v>
-      </c>
-      <c r="S20" s="17">
-        <v>0</v>
-      </c>
-      <c r="T20" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="U20" s="17">
-        <v>2000</v>
-      </c>
-      <c r="V20" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="W20" s="17">
-        <v>1000</v>
-      </c>
-      <c r="X20" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y20" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="17">
-        <v>1</v>
-      </c>
-      <c r="AA20" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB20" s="17">
-        <v>1</v>
-      </c>
-      <c r="AC20" s="17">
+      <c r="A20" s="15">
+        <v>54140001</v>
+      </c>
+      <c r="B20" s="15">
+        <v>5414</v>
+      </c>
+      <c r="C20" s="15">
+        <v>1</v>
+      </c>
+      <c r="D20" s="15">
+        <v>0</v>
+      </c>
+      <c r="E20" s="15">
+        <v>3542800</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>522</v>
+      </c>
+      <c r="J20" s="15" t="s">
+        <v>524</v>
+      </c>
+      <c r="K20" s="15">
+        <v>2</v>
+      </c>
+      <c r="L20" s="15">
+        <v>5000</v>
+      </c>
+      <c r="M20" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="N20" s="15">
+        <v>0</v>
+      </c>
+      <c r="O20" s="15">
+        <v>0</v>
+      </c>
+      <c r="P20" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q20" s="15">
+        <v>0</v>
+      </c>
+      <c r="R20" s="15">
+        <v>0</v>
+      </c>
+      <c r="S20" s="15">
+        <v>0</v>
+      </c>
+      <c r="T20" s="15" t="s">
+        <v>531</v>
+      </c>
+      <c r="U20" s="15">
+        <v>-1</v>
+      </c>
+      <c r="V20" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="W20" s="15">
+        <v>10000</v>
+      </c>
+      <c r="X20" s="15" t="s">
+        <v>528</v>
+      </c>
+      <c r="Y20" s="15">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="15">
+        <v>3</v>
+      </c>
+      <c r="AA20" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB20" s="15">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A21" s="17">
-        <v>55020001</v>
-      </c>
-      <c r="B21" s="17">
-        <v>5502</v>
-      </c>
-      <c r="C21" s="17">
-        <v>1</v>
-      </c>
-      <c r="D21" s="17">
-        <v>0</v>
-      </c>
-      <c r="E21" s="17">
-        <v>3550500</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="H21" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="I21" s="13" t="s">
-        <v>352</v>
-      </c>
-      <c r="J21" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="K21" s="17">
-        <v>1</v>
-      </c>
-      <c r="L21" s="17">
-        <v>12</v>
-      </c>
-      <c r="M21" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="N21" s="17">
+      <c r="A21" s="15">
+        <v>54150001</v>
+      </c>
+      <c r="B21" s="15">
+        <v>5415</v>
+      </c>
+      <c r="C21" s="15">
+        <v>1</v>
+      </c>
+      <c r="D21" s="15">
+        <v>0</v>
+      </c>
+      <c r="E21" s="15">
+        <v>3543000</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>520</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>523</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>526</v>
+      </c>
+      <c r="K21" s="15">
         <v>2</v>
       </c>
-      <c r="O21" s="17">
+      <c r="L21" s="15">
         <v>10000</v>
       </c>
-      <c r="P21" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q21" s="17">
-        <v>1</v>
-      </c>
-      <c r="R21" s="17">
-        <v>1</v>
-      </c>
-      <c r="S21" s="17">
-        <v>5000001</v>
-      </c>
-      <c r="T21" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="U21" s="17">
-        <v>4000</v>
-      </c>
-      <c r="V21" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="W21" s="17">
+      <c r="M21" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="N21" s="15">
+        <v>0</v>
+      </c>
+      <c r="O21" s="15">
+        <v>0</v>
+      </c>
+      <c r="P21" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q21" s="15">
+        <v>0</v>
+      </c>
+      <c r="R21" s="15">
+        <v>0</v>
+      </c>
+      <c r="S21" s="15">
+        <v>0</v>
+      </c>
+      <c r="T21" s="15" t="s">
+        <v>532</v>
+      </c>
+      <c r="U21" s="15">
+        <v>-1</v>
+      </c>
+      <c r="V21" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="W21" s="15">
         <v>10000</v>
       </c>
-      <c r="X21" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y21" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="17">
-        <v>1</v>
-      </c>
-      <c r="AA21" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB21" s="17">
-        <v>1</v>
-      </c>
-      <c r="AC21" s="17">
+      <c r="X21" s="15" t="s">
+        <v>529</v>
+      </c>
+      <c r="Y21" s="15">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="15">
+        <v>3</v>
+      </c>
+      <c r="AA21" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB21" s="15">
+        <v>1</v>
+      </c>
+      <c r="AC21" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A22" s="17">
-        <v>55030001</v>
+        <v>55010001</v>
       </c>
       <c r="B22" s="17">
-        <v>5503</v>
+        <v>5501</v>
       </c>
       <c r="C22" s="17">
         <v>1</v>
@@ -3831,19 +4375,19 @@
         <v>0</v>
       </c>
       <c r="E22" s="17">
-        <v>3550700</v>
+        <v>3550200</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>185</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="J22" s="17" t="s">
         <v>43</v>
@@ -3852,40 +4396,40 @@
         <v>0</v>
       </c>
       <c r="L22" s="17">
+        <v>0</v>
+      </c>
+      <c r="M22" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="N22" s="17">
+        <v>0</v>
+      </c>
+      <c r="O22" s="17">
+        <v>0</v>
+      </c>
+      <c r="P22" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q22" s="17">
+        <v>0</v>
+      </c>
+      <c r="R22" s="17">
+        <v>0</v>
+      </c>
+      <c r="S22" s="17">
+        <v>0</v>
+      </c>
+      <c r="T22" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="U22" s="17">
+        <v>2000</v>
+      </c>
+      <c r="V22" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="W22" s="17">
         <v>1000</v>
-      </c>
-      <c r="M22" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="N22" s="17">
-        <v>2</v>
-      </c>
-      <c r="O22" s="17">
-        <v>10000</v>
-      </c>
-      <c r="P22" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q22" s="17">
-        <v>1</v>
-      </c>
-      <c r="R22" s="17">
-        <v>1</v>
-      </c>
-      <c r="S22" s="17">
-        <v>5000001</v>
-      </c>
-      <c r="T22" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="U22" s="17">
-        <v>4000</v>
-      </c>
-      <c r="V22" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="W22" s="17">
-        <v>10000</v>
       </c>
       <c r="X22" s="17" t="s">
         <v>43</v>
@@ -3908,10 +4452,10 @@
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A23" s="17">
-        <v>55040001</v>
+        <v>55020001</v>
       </c>
       <c r="B23" s="17">
-        <v>5504</v>
+        <v>5502</v>
       </c>
       <c r="C23" s="17">
         <v>1</v>
@@ -3920,58 +4464,58 @@
         <v>0</v>
       </c>
       <c r="E23" s="17">
-        <v>3550900</v>
+        <v>3550500</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>185</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="J23" s="17" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="K23" s="17">
+        <v>1</v>
+      </c>
+      <c r="L23" s="17">
+        <v>12</v>
+      </c>
+      <c r="M23" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="N23" s="17">
         <v>2</v>
       </c>
-      <c r="L23" s="17">
-        <v>3000</v>
-      </c>
-      <c r="M23" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="N23" s="17">
-        <v>0</v>
-      </c>
       <c r="O23" s="17">
-        <v>30</v>
+        <v>10000</v>
       </c>
       <c r="P23" s="17" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="Q23" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" s="17">
-        <v>0</v>
+        <v>5000001</v>
       </c>
       <c r="T23" s="17" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="U23" s="17">
-        <v>-1</v>
+        <v>4000</v>
       </c>
       <c r="V23" s="17" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="W23" s="17">
         <v>10000</v>
@@ -3997,10 +4541,10 @@
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A24" s="17">
-        <v>55050001</v>
+        <v>55030001</v>
       </c>
       <c r="B24" s="17">
-        <v>5505</v>
+        <v>5503</v>
       </c>
       <c r="C24" s="17">
         <v>1</v>
@@ -4009,55 +4553,55 @@
         <v>0</v>
       </c>
       <c r="E24" s="17">
-        <v>3551100</v>
+        <v>3550700</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>156</v>
+        <v>72</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>185</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="J24" s="17" t="s">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="K24" s="17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L24" s="17">
-        <v>100000</v>
+        <v>1000</v>
       </c>
       <c r="M24" s="17" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="N24" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O24" s="17">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P24" s="17" t="s">
-        <v>374</v>
+        <v>84</v>
       </c>
       <c r="Q24" s="17">
         <v>1</v>
       </c>
       <c r="R24" s="17">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="S24" s="17">
-        <v>0</v>
+        <v>5000001</v>
       </c>
       <c r="T24" s="17" t="s">
         <v>43</v>
       </c>
       <c r="U24" s="17">
-        <v>-1</v>
+        <v>4000</v>
       </c>
       <c r="V24" s="17" t="s">
         <v>43</v>
@@ -4086,10 +4630,10 @@
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A25" s="17">
-        <v>55060001</v>
+        <v>55040001</v>
       </c>
       <c r="B25" s="17">
-        <v>5506</v>
+        <v>5504</v>
       </c>
       <c r="C25" s="17">
         <v>1</v>
@@ -4098,37 +4642,37 @@
         <v>0</v>
       </c>
       <c r="E25" s="17">
-        <v>3551300</v>
+        <v>3550900</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>357</v>
+        <v>74</v>
       </c>
       <c r="G25" s="13" t="s">
         <v>185</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K25" s="17">
         <v>2</v>
       </c>
       <c r="L25" s="17">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="M25" s="17" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="N25" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" s="17">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P25" s="17" t="s">
         <v>43</v>
@@ -4175,10 +4719,10 @@
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A26" s="17">
-        <v>55070001</v>
+        <v>55050001</v>
       </c>
       <c r="B26" s="17">
-        <v>5507</v>
+        <v>5505</v>
       </c>
       <c r="C26" s="17">
         <v>1</v>
@@ -4187,265 +4731,265 @@
         <v>0</v>
       </c>
       <c r="E26" s="17">
-        <v>3551500</v>
+        <v>3551100</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G26" s="13" t="s">
         <v>185</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>157</v>
+        <v>355</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>153</v>
+        <v>86</v>
       </c>
       <c r="K26" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L26" s="17">
+        <v>100000</v>
+      </c>
+      <c r="M26" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="N26" s="17">
+        <v>1</v>
+      </c>
+      <c r="O26" s="17">
+        <v>0</v>
+      </c>
+      <c r="P26" s="17" t="s">
+        <v>374</v>
+      </c>
+      <c r="Q26" s="17">
+        <v>1</v>
+      </c>
+      <c r="R26" s="17">
         <v>2000</v>
       </c>
-      <c r="M26" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="N26" s="17">
-        <v>0</v>
-      </c>
-      <c r="O26" s="17">
-        <v>0</v>
-      </c>
-      <c r="P26" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q26" s="17">
-        <v>0</v>
-      </c>
-      <c r="R26" s="17">
-        <v>0</v>
-      </c>
       <c r="S26" s="17">
         <v>0</v>
       </c>
       <c r="T26" s="17" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="U26" s="17">
         <v>-1</v>
       </c>
       <c r="V26" s="17" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="W26" s="17">
         <v>10000</v>
       </c>
       <c r="X26" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y26" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="17">
+        <v>1</v>
+      </c>
+      <c r="AA26" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB26" s="17">
+        <v>1</v>
+      </c>
+      <c r="AC26" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A27" s="17">
+        <v>55060001</v>
+      </c>
+      <c r="B27" s="17">
+        <v>5506</v>
+      </c>
+      <c r="C27" s="17">
+        <v>1</v>
+      </c>
+      <c r="D27" s="17">
+        <v>0</v>
+      </c>
+      <c r="E27" s="17">
+        <v>3551300</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="J27" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="K27" s="17">
+        <v>2</v>
+      </c>
+      <c r="L27" s="17">
+        <v>5000</v>
+      </c>
+      <c r="M27" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="N27" s="17">
+        <v>1</v>
+      </c>
+      <c r="O27" s="17">
+        <v>50</v>
+      </c>
+      <c r="P27" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q27" s="17">
+        <v>0</v>
+      </c>
+      <c r="R27" s="17">
+        <v>0</v>
+      </c>
+      <c r="S27" s="17">
+        <v>0</v>
+      </c>
+      <c r="T27" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="U27" s="17">
+        <v>-1</v>
+      </c>
+      <c r="V27" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="W27" s="17">
+        <v>10000</v>
+      </c>
+      <c r="X27" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y27" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="17">
+        <v>1</v>
+      </c>
+      <c r="AA27" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB27" s="17">
+        <v>1</v>
+      </c>
+      <c r="AC27" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A28" s="17">
+        <v>55070001</v>
+      </c>
+      <c r="B28" s="17">
+        <v>5507</v>
+      </c>
+      <c r="C28" s="17">
+        <v>1</v>
+      </c>
+      <c r="D28" s="17">
+        <v>0</v>
+      </c>
+      <c r="E28" s="17">
+        <v>3551500</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="J28" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="K28" s="17">
+        <v>2</v>
+      </c>
+      <c r="L28" s="17">
+        <v>2000</v>
+      </c>
+      <c r="M28" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="Y26" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z26" s="17">
-        <v>1</v>
-      </c>
-      <c r="AA26" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB26" s="17">
-        <v>1</v>
-      </c>
-      <c r="AC26" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A27" s="18">
-        <v>56010001</v>
-      </c>
-      <c r="B27" s="18">
-        <v>5601</v>
-      </c>
-      <c r="C27" s="18">
-        <v>1</v>
-      </c>
-      <c r="D27" s="18">
-        <v>0</v>
-      </c>
-      <c r="E27" s="18">
-        <v>3560200</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="I27" s="13" t="s">
-        <v>334</v>
-      </c>
-      <c r="J27" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="K27" s="18">
-        <v>2</v>
-      </c>
-      <c r="L27" s="18">
-        <v>5000</v>
-      </c>
-      <c r="M27" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="N27" s="18">
-        <v>1</v>
-      </c>
-      <c r="O27" s="18">
-        <v>50</v>
-      </c>
-      <c r="P27" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q27" s="18">
-        <v>0</v>
-      </c>
-      <c r="R27" s="18">
-        <v>0</v>
-      </c>
-      <c r="S27" s="18">
-        <v>0</v>
-      </c>
-      <c r="T27" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="U27" s="18">
-        <v>4000</v>
-      </c>
-      <c r="V27" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="W27" s="18">
-        <v>1500</v>
-      </c>
-      <c r="X27" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y27" s="18">
-        <v>1</v>
-      </c>
-      <c r="Z27" s="18">
-        <v>1</v>
-      </c>
-      <c r="AA27" s="18" t="s">
-        <v>339</v>
-      </c>
-      <c r="AB27" s="18">
-        <v>1</v>
-      </c>
-      <c r="AC27" s="18">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A28" s="18">
-        <v>56020001</v>
-      </c>
-      <c r="B28" s="18">
-        <v>5602</v>
-      </c>
-      <c r="C28" s="18">
-        <v>1</v>
-      </c>
-      <c r="D28" s="18">
-        <v>0</v>
-      </c>
-      <c r="E28" s="18">
-        <v>3560500</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="I28" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="J28" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="K28" s="18">
-        <v>1</v>
-      </c>
-      <c r="L28" s="18">
-        <v>8</v>
-      </c>
-      <c r="M28" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="N28" s="18">
-        <v>1</v>
-      </c>
-      <c r="O28" s="18">
+      <c r="N28" s="17">
+        <v>0</v>
+      </c>
+      <c r="O28" s="17">
+        <v>0</v>
+      </c>
+      <c r="P28" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q28" s="17">
+        <v>0</v>
+      </c>
+      <c r="R28" s="17">
+        <v>0</v>
+      </c>
+      <c r="S28" s="17">
+        <v>0</v>
+      </c>
+      <c r="T28" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="U28" s="17">
+        <v>-1</v>
+      </c>
+      <c r="V28" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="W28" s="17">
         <v>10000</v>
       </c>
-      <c r="P28" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q28" s="18">
-        <v>1</v>
-      </c>
-      <c r="R28" s="18">
-        <v>1</v>
-      </c>
-      <c r="S28" s="18">
-        <v>0</v>
-      </c>
-      <c r="T28" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="U28" s="18">
-        <v>0</v>
-      </c>
-      <c r="V28" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="W28" s="18">
-        <v>10000</v>
-      </c>
-      <c r="X28" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y28" s="18">
-        <v>1</v>
-      </c>
-      <c r="Z28" s="18">
-        <v>1</v>
-      </c>
-      <c r="AA28" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB28" s="18">
-        <v>1</v>
-      </c>
-      <c r="AC28" s="18">
+      <c r="X28" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y28" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z28" s="17">
+        <v>1</v>
+      </c>
+      <c r="AA28" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB28" s="17">
+        <v>1</v>
+      </c>
+      <c r="AC28" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A29" s="18">
-        <v>56030001</v>
+        <v>56010001</v>
       </c>
       <c r="B29" s="18">
-        <v>5603</v>
+        <v>5601</v>
       </c>
       <c r="C29" s="18">
         <v>1</v>
@@ -4454,37 +4998,37 @@
         <v>0</v>
       </c>
       <c r="E29" s="18">
-        <v>3560700</v>
+        <v>3560200</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>189</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>236</v>
+        <v>334</v>
       </c>
       <c r="J29" s="18" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="K29" s="18">
         <v>2</v>
       </c>
       <c r="L29" s="18">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="M29" s="18" t="s">
-        <v>43</v>
+        <v>205</v>
       </c>
       <c r="N29" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29" s="18">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P29" s="18" t="s">
         <v>43</v>
@@ -4499,16 +5043,16 @@
         <v>0</v>
       </c>
       <c r="T29" s="18" t="s">
-        <v>43</v>
+        <v>206</v>
       </c>
       <c r="U29" s="18">
-        <v>-1</v>
+        <v>4000</v>
       </c>
       <c r="V29" s="18" t="s">
-        <v>43</v>
+        <v>207</v>
       </c>
       <c r="W29" s="18">
-        <v>10000</v>
+        <v>1500</v>
       </c>
       <c r="X29" s="18" t="s">
         <v>43</v>
@@ -4520,21 +5064,21 @@
         <v>1</v>
       </c>
       <c r="AA29" s="18" t="s">
-        <v>43</v>
+        <v>339</v>
       </c>
       <c r="AB29" s="18">
         <v>1</v>
       </c>
       <c r="AC29" s="18">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A30" s="18">
-        <v>56040001</v>
+        <v>56020001</v>
       </c>
       <c r="B30" s="18">
-        <v>5604</v>
+        <v>5602</v>
       </c>
       <c r="C30" s="18">
         <v>1</v>
@@ -4543,46 +5087,46 @@
         <v>0</v>
       </c>
       <c r="E30" s="18">
-        <v>3560900</v>
+        <v>3560500</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>189</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="J30" s="18" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="K30" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L30" s="18">
+        <v>8</v>
+      </c>
+      <c r="M30" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="N30" s="18">
+        <v>1</v>
+      </c>
+      <c r="O30" s="18">
         <v>10000</v>
       </c>
-      <c r="M30" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="N30" s="18">
-        <v>0</v>
-      </c>
-      <c r="O30" s="18">
-        <v>0</v>
-      </c>
       <c r="P30" s="18" t="s">
-        <v>43</v>
+        <v>210</v>
       </c>
       <c r="Q30" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" s="18">
         <v>0</v>
@@ -4591,7 +5135,7 @@
         <v>43</v>
       </c>
       <c r="U30" s="18">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="18" t="s">
         <v>43</v>
@@ -4620,10 +5164,10 @@
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A31" s="18">
-        <v>56050001</v>
+        <v>56030001</v>
       </c>
       <c r="B31" s="18">
-        <v>5605</v>
+        <v>5603</v>
       </c>
       <c r="C31" s="18">
         <v>1</v>
@@ -4632,46 +5176,46 @@
         <v>0</v>
       </c>
       <c r="E31" s="18">
-        <v>3561100</v>
+        <v>3560700</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>189</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J31" s="18" t="s">
-        <v>43</v>
+        <v>211</v>
       </c>
       <c r="K31" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" s="18">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="M31" s="18" t="s">
-        <v>233</v>
+        <v>43</v>
       </c>
       <c r="N31" s="18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O31" s="18">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="P31" s="18" t="s">
-        <v>234</v>
+        <v>43</v>
       </c>
       <c r="Q31" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" s="18">
         <v>0</v>
@@ -4680,7 +5224,7 @@
         <v>43</v>
       </c>
       <c r="U31" s="18">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V31" s="18" t="s">
         <v>43</v>
@@ -4709,10 +5253,10 @@
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A32" s="18">
-        <v>56060001</v>
+        <v>56040001</v>
       </c>
       <c r="B32" s="18">
-        <v>5606</v>
+        <v>5604</v>
       </c>
       <c r="C32" s="18">
         <v>1</v>
@@ -4721,37 +5265,37 @@
         <v>0</v>
       </c>
       <c r="E32" s="18">
-        <v>3561400</v>
+        <v>3560900</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>344</v>
+        <v>195</v>
       </c>
       <c r="G32" s="13" t="s">
         <v>189</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>345</v>
+        <v>195</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>366</v>
+        <v>237</v>
       </c>
       <c r="J32" s="18" t="s">
-        <v>363</v>
+        <v>212</v>
       </c>
       <c r="K32" s="18">
         <v>2</v>
       </c>
       <c r="L32" s="18">
-        <v>3500</v>
+        <v>10000</v>
       </c>
       <c r="M32" s="18" t="s">
-        <v>364</v>
+        <v>43</v>
       </c>
       <c r="N32" s="18">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="O32" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32" s="18" t="s">
         <v>43</v>
@@ -4769,7 +5313,7 @@
         <v>43</v>
       </c>
       <c r="U32" s="18">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V32" s="18" t="s">
         <v>43</v>
@@ -4787,199 +5331,199 @@
         <v>1</v>
       </c>
       <c r="AA32" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB32" s="18">
+        <v>1</v>
+      </c>
+      <c r="AC32" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A33" s="18">
+        <v>56050001</v>
+      </c>
+      <c r="B33" s="18">
+        <v>5605</v>
+      </c>
+      <c r="C33" s="18">
+        <v>1</v>
+      </c>
+      <c r="D33" s="18">
+        <v>0</v>
+      </c>
+      <c r="E33" s="18">
+        <v>3561100</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="I33" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="J33" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="K33" s="18">
+        <v>0</v>
+      </c>
+      <c r="L33" s="18">
+        <v>0</v>
+      </c>
+      <c r="M33" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="N33" s="18">
+        <v>2</v>
+      </c>
+      <c r="O33" s="18">
+        <v>10000</v>
+      </c>
+      <c r="P33" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q33" s="18">
+        <v>1</v>
+      </c>
+      <c r="R33" s="18">
+        <v>1</v>
+      </c>
+      <c r="S33" s="18">
+        <v>0</v>
+      </c>
+      <c r="T33" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="U33" s="18">
+        <v>0</v>
+      </c>
+      <c r="V33" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="W33" s="18">
+        <v>10000</v>
+      </c>
+      <c r="X33" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y33" s="18">
+        <v>1</v>
+      </c>
+      <c r="Z33" s="18">
+        <v>1</v>
+      </c>
+      <c r="AA33" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB33" s="18">
+        <v>1</v>
+      </c>
+      <c r="AC33" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A34" s="18">
+        <v>56060001</v>
+      </c>
+      <c r="B34" s="18">
+        <v>5606</v>
+      </c>
+      <c r="C34" s="18">
+        <v>1</v>
+      </c>
+      <c r="D34" s="18">
+        <v>0</v>
+      </c>
+      <c r="E34" s="18">
+        <v>3561400</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="J34" s="18" t="s">
+        <v>363</v>
+      </c>
+      <c r="K34" s="18">
+        <v>2</v>
+      </c>
+      <c r="L34" s="18">
+        <v>3500</v>
+      </c>
+      <c r="M34" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="N34" s="18">
+        <v>35</v>
+      </c>
+      <c r="O34" s="18">
+        <v>1</v>
+      </c>
+      <c r="P34" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q34" s="18">
+        <v>0</v>
+      </c>
+      <c r="R34" s="18">
+        <v>0</v>
+      </c>
+      <c r="S34" s="18">
+        <v>0</v>
+      </c>
+      <c r="T34" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="U34" s="18">
+        <v>0</v>
+      </c>
+      <c r="V34" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="W34" s="18">
+        <v>10000</v>
+      </c>
+      <c r="X34" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y34" s="18">
+        <v>1</v>
+      </c>
+      <c r="Z34" s="18">
+        <v>1</v>
+      </c>
+      <c r="AA34" s="18" t="s">
         <v>365</v>
       </c>
-      <c r="AB32" s="18">
-        <v>1</v>
-      </c>
-      <c r="AC32" s="18">
+      <c r="AB34" s="18">
+        <v>1</v>
+      </c>
+      <c r="AC34" s="18">
         <v>1000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A33" s="19">
-        <v>57010001</v>
-      </c>
-      <c r="B33" s="19">
-        <v>5701</v>
-      </c>
-      <c r="C33" s="19">
-        <v>1</v>
-      </c>
-      <c r="D33" s="19">
-        <v>0</v>
-      </c>
-      <c r="E33" s="19">
-        <v>3570200</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="G33" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="I33" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="J33" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="K33" s="19">
-        <v>2</v>
-      </c>
-      <c r="L33" s="19">
-        <v>4000</v>
-      </c>
-      <c r="M33" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="N33" s="19">
-        <v>1</v>
-      </c>
-      <c r="O33" s="19">
-        <v>3</v>
-      </c>
-      <c r="P33" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q33" s="19">
-        <v>0</v>
-      </c>
-      <c r="R33" s="19">
-        <v>0</v>
-      </c>
-      <c r="S33" s="19">
-        <v>0</v>
-      </c>
-      <c r="T33" s="19" t="s">
-        <v>367</v>
-      </c>
-      <c r="U33" s="19">
-        <v>4000</v>
-      </c>
-      <c r="V33" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="W33" s="19">
-        <v>10000</v>
-      </c>
-      <c r="X33" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y33" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z33" s="19">
-        <v>1</v>
-      </c>
-      <c r="AA33" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB33" s="19">
-        <v>1</v>
-      </c>
-      <c r="AC33" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A34" s="19">
-        <v>57020001</v>
-      </c>
-      <c r="B34" s="19">
-        <v>5702</v>
-      </c>
-      <c r="C34" s="19">
-        <v>1</v>
-      </c>
-      <c r="D34" s="19">
-        <v>0</v>
-      </c>
-      <c r="E34" s="19">
-        <v>3570500</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="G34" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="H34" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="J34" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="K34" s="19">
-        <v>1</v>
-      </c>
-      <c r="L34" s="19">
-        <v>3</v>
-      </c>
-      <c r="M34" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="N34" s="19">
-        <v>1</v>
-      </c>
-      <c r="O34" s="19">
-        <v>1</v>
-      </c>
-      <c r="P34" s="19" t="s">
-        <v>348</v>
-      </c>
-      <c r="Q34" s="19">
-        <v>2</v>
-      </c>
-      <c r="R34" s="19">
-        <v>2500</v>
-      </c>
-      <c r="S34" s="19">
-        <v>0</v>
-      </c>
-      <c r="T34" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="U34" s="19">
-        <v>-1</v>
-      </c>
-      <c r="V34" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="W34" s="19">
-        <v>10000</v>
-      </c>
-      <c r="X34" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y34" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z34" s="19">
-        <v>1</v>
-      </c>
-      <c r="AA34" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB34" s="19">
-        <v>1</v>
-      </c>
-      <c r="AC34" s="19">
-        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A35" s="19">
-        <v>57030001</v>
+        <v>57010001</v>
       </c>
       <c r="B35" s="19">
-        <v>5703</v>
+        <v>5701</v>
       </c>
       <c r="C35" s="19">
         <v>1</v>
@@ -4988,55 +5532,55 @@
         <v>0</v>
       </c>
       <c r="E35" s="19">
-        <v>3570700</v>
+        <v>3570200</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G35" s="13" t="s">
         <v>190</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="J35" s="19" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="K35" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L35" s="19">
-        <v>8</v>
+        <v>4000</v>
       </c>
       <c r="M35" s="19" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="N35" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O35" s="19">
-        <v>10000</v>
+        <v>3</v>
       </c>
       <c r="P35" s="19" t="s">
-        <v>219</v>
+        <v>43</v>
       </c>
       <c r="Q35" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" s="19">
         <v>0</v>
       </c>
       <c r="T35" s="19" t="s">
-        <v>43</v>
+        <v>367</v>
       </c>
       <c r="U35" s="19">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="V35" s="19" t="s">
         <v>43</v>
@@ -5065,10 +5609,10 @@
     </row>
     <row r="36" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A36" s="19">
-        <v>57040001</v>
+        <v>57020001</v>
       </c>
       <c r="B36" s="19">
-        <v>5704</v>
+        <v>5702</v>
       </c>
       <c r="C36" s="19">
         <v>1</v>
@@ -5077,46 +5621,46 @@
         <v>0</v>
       </c>
       <c r="E36" s="19">
-        <v>3570900</v>
+        <v>3570500</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>347</v>
+        <v>198</v>
       </c>
       <c r="G36" s="13" t="s">
         <v>190</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>346</v>
+        <v>240</v>
       </c>
       <c r="J36" s="19" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="K36" s="19">
+        <v>1</v>
+      </c>
+      <c r="L36" s="19">
+        <v>3</v>
+      </c>
+      <c r="M36" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="N36" s="19">
+        <v>1</v>
+      </c>
+      <c r="O36" s="19">
+        <v>1</v>
+      </c>
+      <c r="P36" s="19" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q36" s="19">
         <v>2</v>
       </c>
-      <c r="L36" s="19">
-        <v>2000</v>
-      </c>
-      <c r="M36" s="19" t="s">
-        <v>325</v>
-      </c>
-      <c r="N36" s="19">
-        <v>1</v>
-      </c>
-      <c r="O36" s="19">
-        <v>20</v>
-      </c>
-      <c r="P36" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q36" s="19">
-        <v>0</v>
-      </c>
       <c r="R36" s="19">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="S36" s="19">
         <v>0</v>
@@ -5154,10 +5698,10 @@
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A37" s="19">
-        <v>57050001</v>
+        <v>57030001</v>
       </c>
       <c r="B37" s="19">
-        <v>5705</v>
+        <v>5703</v>
       </c>
       <c r="C37" s="19">
         <v>1</v>
@@ -5166,46 +5710,46 @@
         <v>0</v>
       </c>
       <c r="E37" s="19">
-        <v>3571100</v>
+        <v>3570700</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>350</v>
+        <v>199</v>
       </c>
       <c r="G37" s="13" t="s">
         <v>190</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>349</v>
+        <v>199</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>349</v>
+        <v>235</v>
       </c>
       <c r="J37" s="19" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="K37" s="19">
+        <v>1</v>
+      </c>
+      <c r="L37" s="19">
+        <v>8</v>
+      </c>
+      <c r="M37" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="N37" s="19">
         <v>2</v>
       </c>
-      <c r="L37" s="19">
+      <c r="O37" s="19">
         <v>10000</v>
       </c>
-      <c r="M37" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="N37" s="19">
-        <v>1</v>
-      </c>
-      <c r="O37" s="19">
-        <v>1</v>
-      </c>
       <c r="P37" s="19" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="Q37" s="19">
         <v>1</v>
       </c>
       <c r="R37" s="19">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="S37" s="19">
         <v>0</v>
@@ -5214,7 +5758,7 @@
         <v>43</v>
       </c>
       <c r="U37" s="19">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V37" s="19" t="s">
         <v>43</v>
@@ -5243,10 +5787,10 @@
     </row>
     <row r="38" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A38" s="19">
-        <v>57060001</v>
+        <v>57040001</v>
       </c>
       <c r="B38" s="19">
-        <v>5706</v>
+        <v>5704</v>
       </c>
       <c r="C38" s="19">
         <v>1</v>
@@ -5255,46 +5799,46 @@
         <v>0</v>
       </c>
       <c r="E38" s="19">
-        <v>3571300</v>
+        <v>3570900</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>201</v>
+        <v>347</v>
       </c>
       <c r="G38" s="13" t="s">
         <v>190</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="J38" s="19" t="s">
-        <v>43</v>
+        <v>220</v>
       </c>
       <c r="K38" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" s="19">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="M38" s="19" t="s">
-        <v>243</v>
+        <v>325</v>
       </c>
       <c r="N38" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O38" s="19">
-        <v>10000</v>
+        <v>20</v>
       </c>
       <c r="P38" s="19" t="s">
-        <v>244</v>
+        <v>43</v>
       </c>
       <c r="Q38" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" s="19">
         <v>0</v>
@@ -5331,189 +5875,189 @@
       </c>
     </row>
     <row r="39" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A39" s="20">
-        <v>58010001</v>
-      </c>
-      <c r="B39" s="20">
-        <v>5801</v>
-      </c>
-      <c r="C39" s="20">
-        <v>1</v>
-      </c>
-      <c r="D39" s="20">
-        <v>0</v>
-      </c>
-      <c r="E39" s="20">
-        <v>3580200</v>
+      <c r="A39" s="19">
+        <v>57050001</v>
+      </c>
+      <c r="B39" s="19">
+        <v>5705</v>
+      </c>
+      <c r="C39" s="19">
+        <v>1</v>
+      </c>
+      <c r="D39" s="19">
+        <v>0</v>
+      </c>
+      <c r="E39" s="19">
+        <v>3571100</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>202</v>
+        <v>350</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>202</v>
+        <v>349</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="J39" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="K39" s="20">
+        <v>349</v>
+      </c>
+      <c r="J39" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="K39" s="19">
         <v>2</v>
       </c>
-      <c r="L39" s="20">
-        <v>3000</v>
-      </c>
-      <c r="M39" s="20" t="s">
-        <v>225</v>
-      </c>
-      <c r="N39" s="20">
-        <v>1</v>
-      </c>
-      <c r="O39" s="20">
-        <v>30</v>
-      </c>
-      <c r="P39" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q39" s="20">
-        <v>1</v>
-      </c>
-      <c r="R39" s="20">
-        <v>0</v>
-      </c>
-      <c r="S39" s="20">
-        <v>0</v>
-      </c>
-      <c r="T39" s="20" t="s">
-        <v>368</v>
-      </c>
-      <c r="U39" s="20">
-        <v>4000</v>
-      </c>
-      <c r="V39" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="W39" s="20">
+      <c r="L39" s="19">
         <v>10000</v>
       </c>
-      <c r="X39" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="Y39" s="20">
-        <v>1</v>
-      </c>
-      <c r="Z39" s="20">
-        <v>1</v>
-      </c>
-      <c r="AA39" s="20" t="s">
-        <v>340</v>
-      </c>
-      <c r="AB39" s="20">
-        <v>1</v>
-      </c>
-      <c r="AC39" s="20">
-        <v>1000</v>
+      <c r="M39" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="N39" s="19">
+        <v>1</v>
+      </c>
+      <c r="O39" s="19">
+        <v>1</v>
+      </c>
+      <c r="P39" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q39" s="19">
+        <v>1</v>
+      </c>
+      <c r="R39" s="19">
+        <v>100</v>
+      </c>
+      <c r="S39" s="19">
+        <v>0</v>
+      </c>
+      <c r="T39" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="U39" s="19">
+        <v>-1</v>
+      </c>
+      <c r="V39" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="W39" s="19">
+        <v>10000</v>
+      </c>
+      <c r="X39" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y39" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z39" s="19">
+        <v>1</v>
+      </c>
+      <c r="AA39" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB39" s="19">
+        <v>1</v>
+      </c>
+      <c r="AC39" s="19">
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A40" s="20">
-        <v>58020001</v>
-      </c>
-      <c r="B40" s="20">
-        <v>5802</v>
-      </c>
-      <c r="C40" s="20">
-        <v>1</v>
-      </c>
-      <c r="D40" s="20">
-        <v>0</v>
-      </c>
-      <c r="E40" s="20">
-        <v>3580500</v>
+      <c r="A40" s="19">
+        <v>57060001</v>
+      </c>
+      <c r="B40" s="19">
+        <v>5706</v>
+      </c>
+      <c r="C40" s="19">
+        <v>1</v>
+      </c>
+      <c r="D40" s="19">
+        <v>0</v>
+      </c>
+      <c r="E40" s="19">
+        <v>3571300</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="J40" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="K40" s="20">
-        <v>1</v>
-      </c>
-      <c r="L40" s="20">
-        <v>8</v>
-      </c>
-      <c r="M40" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="N40" s="20">
+        <v>241</v>
+      </c>
+      <c r="J40" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="K40" s="19">
+        <v>0</v>
+      </c>
+      <c r="L40" s="19">
+        <v>0</v>
+      </c>
+      <c r="M40" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="N40" s="19">
         <v>2</v>
       </c>
-      <c r="O40" s="20">
+      <c r="O40" s="19">
         <v>10000</v>
       </c>
-      <c r="P40" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q40" s="20">
-        <v>1</v>
-      </c>
-      <c r="R40" s="20">
-        <v>1</v>
-      </c>
-      <c r="S40" s="20">
-        <v>0</v>
-      </c>
-      <c r="T40" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="U40" s="20">
+      <c r="P40" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q40" s="19">
+        <v>1</v>
+      </c>
+      <c r="R40" s="19">
+        <v>1</v>
+      </c>
+      <c r="S40" s="19">
+        <v>0</v>
+      </c>
+      <c r="T40" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="U40" s="19">
         <v>-1</v>
       </c>
-      <c r="V40" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="W40" s="20">
+      <c r="V40" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="W40" s="19">
         <v>10000</v>
       </c>
-      <c r="X40" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y40" s="20">
-        <v>1</v>
-      </c>
-      <c r="Z40" s="20">
-        <v>1</v>
-      </c>
-      <c r="AA40" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB40" s="20">
-        <v>1</v>
-      </c>
-      <c r="AC40" s="20">
+      <c r="X40" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y40" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z40" s="19">
+        <v>1</v>
+      </c>
+      <c r="AA40" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB40" s="19">
+        <v>1</v>
+      </c>
+      <c r="AC40" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A41" s="20">
-        <v>58030001</v>
+        <v>58010001</v>
       </c>
       <c r="B41" s="20">
-        <v>5803</v>
+        <v>5801</v>
       </c>
       <c r="C41" s="20">
         <v>1</v>
@@ -5522,43 +6066,43 @@
         <v>0</v>
       </c>
       <c r="E41" s="20">
-        <v>3580700</v>
+        <v>3580200</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>358</v>
+        <v>202</v>
       </c>
       <c r="G41" s="13" t="s">
         <v>191</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>358</v>
+        <v>202</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>359</v>
+        <v>335</v>
       </c>
       <c r="J41" s="20" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="K41" s="20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L41" s="20">
-        <v>5</v>
+        <v>3000</v>
       </c>
       <c r="M41" s="20" t="s">
-        <v>360</v>
+        <v>225</v>
       </c>
       <c r="N41" s="20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O41" s="20">
-        <v>10000</v>
+        <v>30</v>
       </c>
       <c r="P41" s="20" t="s">
         <v>43</v>
       </c>
       <c r="Q41" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" s="20">
         <v>0</v>
@@ -5567,10 +6111,10 @@
         <v>0</v>
       </c>
       <c r="T41" s="20" t="s">
-        <v>43</v>
+        <v>368</v>
       </c>
       <c r="U41" s="20">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="V41" s="20" t="s">
         <v>43</v>
@@ -5579,7 +6123,7 @@
         <v>10000</v>
       </c>
       <c r="X41" s="20" t="s">
-        <v>43</v>
+        <v>226</v>
       </c>
       <c r="Y41" s="20">
         <v>1</v>
@@ -5588,21 +6132,21 @@
         <v>1</v>
       </c>
       <c r="AA41" s="20" t="s">
-        <v>43</v>
+        <v>340</v>
       </c>
       <c r="AB41" s="20">
         <v>1</v>
       </c>
       <c r="AC41" s="20">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="42" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A42" s="20">
-        <v>58040001</v>
+        <v>58020001</v>
       </c>
       <c r="B42" s="20">
-        <v>5804</v>
+        <v>5802</v>
       </c>
       <c r="C42" s="20">
         <v>1</v>
@@ -5611,31 +6155,31 @@
         <v>0</v>
       </c>
       <c r="E42" s="20">
-        <v>3580900</v>
+        <v>3580500</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="G42" s="13" t="s">
         <v>191</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="J42" s="20" t="s">
-        <v>43</v>
+        <v>227</v>
       </c>
       <c r="K42" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="20">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M42" s="20" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="N42" s="20">
         <v>2</v>
@@ -5644,7 +6188,7 @@
         <v>10000</v>
       </c>
       <c r="P42" s="20" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="Q42" s="20">
         <v>1</v>
@@ -5659,7 +6203,7 @@
         <v>43</v>
       </c>
       <c r="U42" s="20">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V42" s="20" t="s">
         <v>43</v>
@@ -5687,50 +6231,50 @@
       </c>
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A43" s="23">
-        <v>58050001</v>
-      </c>
-      <c r="B43" s="23">
-        <v>5805</v>
-      </c>
-      <c r="C43" s="23">
-        <v>1</v>
-      </c>
-      <c r="D43" s="23">
-        <v>0</v>
-      </c>
-      <c r="E43" s="23">
-        <v>3581200</v>
+      <c r="A43" s="20">
+        <v>58030001</v>
+      </c>
+      <c r="B43" s="20">
+        <v>5803</v>
+      </c>
+      <c r="C43" s="20">
+        <v>1</v>
+      </c>
+      <c r="D43" s="20">
+        <v>0</v>
+      </c>
+      <c r="E43" s="20">
+        <v>3580700</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>188</v>
+        <v>358</v>
       </c>
       <c r="G43" s="13" t="s">
         <v>191</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>188</v>
+        <v>358</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>336</v>
+        <v>359</v>
       </c>
       <c r="J43" s="20" t="s">
-        <v>322</v>
+        <v>230</v>
       </c>
       <c r="K43" s="20">
+        <v>1</v>
+      </c>
+      <c r="L43" s="20">
+        <v>5</v>
+      </c>
+      <c r="M43" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="N43" s="20">
         <v>2</v>
       </c>
-      <c r="L43" s="20">
-        <v>3000</v>
-      </c>
-      <c r="M43" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="N43" s="20">
-        <v>0</v>
-      </c>
       <c r="O43" s="20">
-        <v>30</v>
+        <v>10000</v>
       </c>
       <c r="P43" s="20" t="s">
         <v>43</v>
@@ -5745,10 +6289,10 @@
         <v>0</v>
       </c>
       <c r="T43" s="20" t="s">
-        <v>369</v>
+        <v>43</v>
       </c>
       <c r="U43" s="20">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="V43" s="20" t="s">
         <v>43</v>
@@ -5757,200 +6301,208 @@
         <v>10000</v>
       </c>
       <c r="X43" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y43" s="20">
+        <v>1</v>
+      </c>
+      <c r="Z43" s="20">
+        <v>1</v>
+      </c>
+      <c r="AA43" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB43" s="20">
+        <v>1</v>
+      </c>
+      <c r="AC43" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A44" s="20">
+        <v>58040001</v>
+      </c>
+      <c r="B44" s="20">
+        <v>5804</v>
+      </c>
+      <c r="C44" s="20">
+        <v>1</v>
+      </c>
+      <c r="D44" s="20">
+        <v>0</v>
+      </c>
+      <c r="E44" s="20">
+        <v>3580900</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="G44" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="H44" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="I44" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="J44" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="K44" s="20">
+        <v>0</v>
+      </c>
+      <c r="L44" s="20">
+        <v>0</v>
+      </c>
+      <c r="M44" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="N44" s="20">
+        <v>2</v>
+      </c>
+      <c r="O44" s="20">
+        <v>10000</v>
+      </c>
+      <c r="P44" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q44" s="20">
+        <v>1</v>
+      </c>
+      <c r="R44" s="20">
+        <v>1</v>
+      </c>
+      <c r="S44" s="20">
+        <v>0</v>
+      </c>
+      <c r="T44" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="U44" s="20">
+        <v>0</v>
+      </c>
+      <c r="V44" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="W44" s="20">
+        <v>10000</v>
+      </c>
+      <c r="X44" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y44" s="20">
+        <v>1</v>
+      </c>
+      <c r="Z44" s="20">
+        <v>1</v>
+      </c>
+      <c r="AA44" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB44" s="20">
+        <v>1</v>
+      </c>
+      <c r="AC44" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A45" s="23">
+        <v>58050001</v>
+      </c>
+      <c r="B45" s="23">
+        <v>5805</v>
+      </c>
+      <c r="C45" s="23">
+        <v>1</v>
+      </c>
+      <c r="D45" s="23">
+        <v>0</v>
+      </c>
+      <c r="E45" s="23">
+        <v>3581200</v>
+      </c>
+      <c r="F45" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="G45" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="H45" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="I45" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="J45" s="20" t="s">
+        <v>322</v>
+      </c>
+      <c r="K45" s="20">
+        <v>2</v>
+      </c>
+      <c r="L45" s="20">
+        <v>3000</v>
+      </c>
+      <c r="M45" s="20" t="s">
+        <v>323</v>
+      </c>
+      <c r="N45" s="20">
+        <v>0</v>
+      </c>
+      <c r="O45" s="20">
+        <v>30</v>
+      </c>
+      <c r="P45" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q45" s="20">
+        <v>0</v>
+      </c>
+      <c r="R45" s="20">
+        <v>0</v>
+      </c>
+      <c r="S45" s="20">
+        <v>0</v>
+      </c>
+      <c r="T45" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="U45" s="20">
+        <v>4000</v>
+      </c>
+      <c r="V45" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="W45" s="20">
+        <v>10000</v>
+      </c>
+      <c r="X45" s="20" t="s">
         <v>324</v>
       </c>
-      <c r="Y43" s="20">
-        <v>1</v>
-      </c>
-      <c r="Z43" s="20">
+      <c r="Y45" s="20">
+        <v>1</v>
+      </c>
+      <c r="Z45" s="20">
         <v>10</v>
       </c>
-      <c r="AA43" s="20" t="s">
+      <c r="AA45" s="20" t="s">
         <v>341</v>
       </c>
-      <c r="AB43" s="20">
-        <v>1</v>
-      </c>
-      <c r="AC43" s="20">
+      <c r="AB45" s="20">
+        <v>1</v>
+      </c>
+      <c r="AC45" s="20">
         <v>1000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A44" s="24">
-        <v>59010001</v>
-      </c>
-      <c r="B44" s="24">
-        <v>5901</v>
-      </c>
-      <c r="C44" s="24">
-        <v>1</v>
-      </c>
-      <c r="D44" s="24">
-        <v>0</v>
-      </c>
-      <c r="E44" s="24">
-        <v>3590200</v>
-      </c>
-      <c r="F44" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="G44" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="H44" s="13"/>
-      <c r="I44" s="13"/>
-      <c r="J44" s="24" t="s">
-        <v>279</v>
-      </c>
-      <c r="K44" s="24">
-        <v>3</v>
-      </c>
-      <c r="L44" s="24">
-        <v>200000</v>
-      </c>
-      <c r="M44" s="24" t="s">
-        <v>280</v>
-      </c>
-      <c r="N44" s="24">
-        <v>2</v>
-      </c>
-      <c r="O44" s="24">
-        <v>10000</v>
-      </c>
-      <c r="P44" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="Q44" s="24">
-        <v>1</v>
-      </c>
-      <c r="R44" s="24">
-        <v>1</v>
-      </c>
-      <c r="S44" s="24">
-        <v>0</v>
-      </c>
-      <c r="T44" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="U44" s="24">
-        <v>0</v>
-      </c>
-      <c r="V44" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="W44" s="24">
-        <v>10000</v>
-      </c>
-      <c r="X44" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y44" s="24">
-        <v>1</v>
-      </c>
-      <c r="Z44" s="24">
-        <v>1</v>
-      </c>
-      <c r="AA44" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB44" s="24">
-        <v>1</v>
-      </c>
-      <c r="AC44" s="24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A45" s="24">
-        <v>59020001</v>
-      </c>
-      <c r="B45" s="24">
-        <v>5902</v>
-      </c>
-      <c r="C45" s="24">
-        <v>1</v>
-      </c>
-      <c r="D45" s="24">
-        <v>0</v>
-      </c>
-      <c r="E45" s="24">
-        <v>3590400</v>
-      </c>
-      <c r="F45" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="G45" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="H45" s="13"/>
-      <c r="I45" s="13"/>
-      <c r="J45" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="K45" s="24">
-        <v>3</v>
-      </c>
-      <c r="L45" s="24">
-        <v>200000</v>
-      </c>
-      <c r="M45" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="N45" s="24">
-        <v>0</v>
-      </c>
-      <c r="O45" s="24">
-        <v>0</v>
-      </c>
-      <c r="P45" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q45" s="24">
-        <v>0</v>
-      </c>
-      <c r="R45" s="24">
-        <v>0</v>
-      </c>
-      <c r="S45" s="24">
-        <v>59030001</v>
-      </c>
-      <c r="T45" s="24" t="s">
-        <v>370</v>
-      </c>
-      <c r="U45" s="24">
-        <v>-1</v>
-      </c>
-      <c r="V45" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="W45" s="24">
-        <v>10000</v>
-      </c>
-      <c r="X45" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y45" s="24">
-        <v>1</v>
-      </c>
-      <c r="Z45" s="24">
-        <v>1</v>
-      </c>
-      <c r="AA45" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB45" s="24">
-        <v>1</v>
-      </c>
-      <c r="AC45" s="24">
-        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A46" s="24">
-        <v>59030001</v>
+        <v>59010001</v>
       </c>
       <c r="B46" s="24">
-        <v>5903</v>
+        <v>5901</v>
       </c>
       <c r="C46" s="24">
         <v>1</v>
@@ -5959,10 +6511,10 @@
         <v>0</v>
       </c>
       <c r="E46" s="24">
-        <v>3590600</v>
+        <v>3590200</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G46" s="13" t="s">
         <v>245</v>
@@ -5970,16 +6522,16 @@
       <c r="H46" s="13"/>
       <c r="I46" s="13"/>
       <c r="J46" s="24" t="s">
-        <v>43</v>
+        <v>279</v>
       </c>
       <c r="K46" s="24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L46" s="24">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="M46" s="24" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="N46" s="24">
         <v>2</v>
@@ -5988,7 +6540,7 @@
         <v>10000</v>
       </c>
       <c r="P46" s="24" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q46" s="24">
         <v>1</v>
@@ -5997,7 +6549,7 @@
         <v>1</v>
       </c>
       <c r="S46" s="24">
-        <v>59200001</v>
+        <v>0</v>
       </c>
       <c r="T46" s="24" t="s">
         <v>43</v>
@@ -6032,10 +6584,10 @@
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A47" s="24">
-        <v>59040001</v>
+        <v>59020001</v>
       </c>
       <c r="B47" s="24">
-        <v>5904</v>
+        <v>5902</v>
       </c>
       <c r="C47" s="24">
         <v>1</v>
@@ -6044,10 +6596,10 @@
         <v>0</v>
       </c>
       <c r="E47" s="24">
-        <v>3590800</v>
+        <v>3590400</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G47" s="13" t="s">
         <v>245</v>
@@ -6055,37 +6607,37 @@
       <c r="H47" s="13"/>
       <c r="I47" s="13"/>
       <c r="J47" s="24" t="s">
-        <v>43</v>
+        <v>282</v>
       </c>
       <c r="K47" s="24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L47" s="24">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="M47" s="24" t="s">
-        <v>285</v>
+        <v>43</v>
       </c>
       <c r="N47" s="24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O47" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="P47" s="24" t="s">
-        <v>286</v>
+        <v>43</v>
       </c>
       <c r="Q47" s="24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" s="24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" s="24">
-        <v>59090001</v>
+        <v>59030001</v>
       </c>
       <c r="T47" s="24" t="s">
-        <v>43</v>
+        <v>370</v>
       </c>
       <c r="U47" s="24">
         <v>-1</v>
@@ -6117,10 +6669,10 @@
     </row>
     <row r="48" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A48" s="24">
-        <v>59050001</v>
+        <v>59030001</v>
       </c>
       <c r="B48" s="24">
-        <v>5905</v>
+        <v>5903</v>
       </c>
       <c r="C48" s="24">
         <v>1</v>
@@ -6129,10 +6681,10 @@
         <v>0</v>
       </c>
       <c r="E48" s="24">
-        <v>3591000</v>
+        <v>3590600</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G48" s="13" t="s">
         <v>245</v>
@@ -6140,40 +6692,40 @@
       <c r="H48" s="13"/>
       <c r="I48" s="13"/>
       <c r="J48" s="24" t="s">
-        <v>287</v>
+        <v>43</v>
       </c>
       <c r="K48" s="24">
+        <v>0</v>
+      </c>
+      <c r="L48" s="24">
+        <v>0</v>
+      </c>
+      <c r="M48" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="N48" s="24">
         <v>2</v>
       </c>
-      <c r="L48" s="24">
-        <v>0</v>
-      </c>
-      <c r="M48" s="24" t="s">
-        <v>342</v>
-      </c>
-      <c r="N48" s="24">
-        <v>1</v>
-      </c>
       <c r="O48" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P48" s="24" t="s">
-        <v>343</v>
+        <v>284</v>
       </c>
       <c r="Q48" s="24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R48" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S48" s="24">
-        <v>0</v>
+        <v>59200001</v>
       </c>
       <c r="T48" s="24" t="s">
         <v>43</v>
       </c>
       <c r="U48" s="24">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V48" s="24" t="s">
         <v>43</v>
@@ -6202,10 +6754,10 @@
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A49" s="24">
-        <v>59060001</v>
+        <v>59040001</v>
       </c>
       <c r="B49" s="24">
-        <v>5906</v>
+        <v>5904</v>
       </c>
       <c r="C49" s="24">
         <v>1</v>
@@ -6214,10 +6766,10 @@
         <v>0</v>
       </c>
       <c r="E49" s="24">
-        <v>3591200</v>
+        <v>3590800</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G49" s="13" t="s">
         <v>245</v>
@@ -6225,16 +6777,16 @@
       <c r="H49" s="13"/>
       <c r="I49" s="13"/>
       <c r="J49" s="24" t="s">
-        <v>288</v>
+        <v>43</v>
       </c>
       <c r="K49" s="24">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L49" s="24">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="M49" s="24" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="N49" s="24">
         <v>2</v>
@@ -6243,7 +6795,7 @@
         <v>10000</v>
       </c>
       <c r="P49" s="24" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="Q49" s="24">
         <v>1</v>
@@ -6252,7 +6804,7 @@
         <v>1</v>
       </c>
       <c r="S49" s="24">
-        <v>0</v>
+        <v>59090001</v>
       </c>
       <c r="T49" s="24" t="s">
         <v>43</v>
@@ -6287,10 +6839,10 @@
     </row>
     <row r="50" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A50" s="24">
-        <v>59070001</v>
+        <v>59050001</v>
       </c>
       <c r="B50" s="24">
-        <v>5907</v>
+        <v>5905</v>
       </c>
       <c r="C50" s="24">
         <v>1</v>
@@ -6299,10 +6851,10 @@
         <v>0</v>
       </c>
       <c r="E50" s="24">
-        <v>3591400</v>
+        <v>3591000</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G50" s="13" t="s">
         <v>245</v>
@@ -6310,34 +6862,34 @@
       <c r="H50" s="13"/>
       <c r="I50" s="13"/>
       <c r="J50" s="24" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="K50" s="24">
+        <v>2</v>
+      </c>
+      <c r="L50" s="24">
+        <v>0</v>
+      </c>
+      <c r="M50" s="24" t="s">
+        <v>342</v>
+      </c>
+      <c r="N50" s="24">
+        <v>1</v>
+      </c>
+      <c r="O50" s="24">
+        <v>0</v>
+      </c>
+      <c r="P50" s="24" t="s">
+        <v>343</v>
+      </c>
+      <c r="Q50" s="24">
         <v>3</v>
       </c>
-      <c r="L50" s="24">
-        <v>500000</v>
-      </c>
-      <c r="M50" s="24" t="s">
-        <v>292</v>
-      </c>
-      <c r="N50" s="24">
-        <v>2</v>
-      </c>
-      <c r="O50" s="24">
-        <v>10000</v>
-      </c>
-      <c r="P50" s="24" t="s">
-        <v>293</v>
-      </c>
-      <c r="Q50" s="24">
-        <v>1</v>
-      </c>
       <c r="R50" s="24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" s="24">
-        <v>59200002</v>
+        <v>0</v>
       </c>
       <c r="T50" s="24" t="s">
         <v>43</v>
@@ -6372,10 +6924,10 @@
     </row>
     <row r="51" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A51" s="24">
-        <v>59080001</v>
+        <v>59060001</v>
       </c>
       <c r="B51" s="24">
-        <v>5908</v>
+        <v>5906</v>
       </c>
       <c r="C51" s="24">
         <v>1</v>
@@ -6384,10 +6936,10 @@
         <v>0</v>
       </c>
       <c r="E51" s="24">
-        <v>3591600</v>
+        <v>3591200</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G51" s="13" t="s">
         <v>245</v>
@@ -6395,16 +6947,16 @@
       <c r="H51" s="13"/>
       <c r="I51" s="13"/>
       <c r="J51" s="24" t="s">
-        <v>43</v>
+        <v>288</v>
       </c>
       <c r="K51" s="24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L51" s="24">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="M51" s="24" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="N51" s="24">
         <v>2</v>
@@ -6413,7 +6965,7 @@
         <v>10000</v>
       </c>
       <c r="P51" s="24" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="Q51" s="24">
         <v>1</v>
@@ -6422,13 +6974,13 @@
         <v>1</v>
       </c>
       <c r="S51" s="24">
-        <v>90000001</v>
+        <v>0</v>
       </c>
       <c r="T51" s="24" t="s">
         <v>43</v>
       </c>
       <c r="U51" s="24">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V51" s="24" t="s">
         <v>43</v>
@@ -6457,10 +7009,10 @@
     </row>
     <row r="52" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A52" s="24">
-        <v>59090001</v>
+        <v>59070001</v>
       </c>
       <c r="B52" s="24">
-        <v>5909</v>
+        <v>5907</v>
       </c>
       <c r="C52" s="24">
         <v>1</v>
@@ -6469,10 +7021,10 @@
         <v>0</v>
       </c>
       <c r="E52" s="24">
-        <v>3591900</v>
+        <v>3591400</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>361</v>
+        <v>252</v>
       </c>
       <c r="G52" s="13" t="s">
         <v>245</v>
@@ -6480,34 +7032,34 @@
       <c r="H52" s="13"/>
       <c r="I52" s="13"/>
       <c r="J52" s="24" t="s">
-        <v>43</v>
+        <v>291</v>
       </c>
       <c r="K52" s="24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L52" s="24">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="M52" s="24" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="N52" s="24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O52" s="24">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="P52" s="24" t="s">
-        <v>43</v>
+        <v>293</v>
       </c>
       <c r="Q52" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S52" s="24">
-        <v>0</v>
+        <v>59200002</v>
       </c>
       <c r="T52" s="24" t="s">
         <v>43</v>
@@ -6531,21 +7083,21 @@
         <v>1</v>
       </c>
       <c r="AA52" s="24" t="s">
-        <v>362</v>
+        <v>43</v>
       </c>
       <c r="AB52" s="24">
         <v>1</v>
       </c>
       <c r="AC52" s="24">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A53" s="24">
-        <v>59100001</v>
+        <v>59080001</v>
       </c>
       <c r="B53" s="24">
-        <v>5910</v>
+        <v>5908</v>
       </c>
       <c r="C53" s="24">
         <v>1</v>
@@ -6554,10 +7106,10 @@
         <v>0</v>
       </c>
       <c r="E53" s="24">
-        <v>3541800</v>
+        <v>3591600</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>315</v>
+        <v>253</v>
       </c>
       <c r="G53" s="13" t="s">
         <v>245</v>
@@ -6568,37 +7120,37 @@
         <v>43</v>
       </c>
       <c r="K53" s="24">
+        <v>0</v>
+      </c>
+      <c r="L53" s="24">
+        <v>0</v>
+      </c>
+      <c r="M53" s="24" t="s">
+        <v>294</v>
+      </c>
+      <c r="N53" s="24">
         <v>2</v>
       </c>
-      <c r="L53" s="24">
-        <v>1500</v>
-      </c>
-      <c r="M53" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="N53" s="24">
-        <v>0</v>
-      </c>
       <c r="O53" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P53" s="24" t="s">
-        <v>43</v>
+        <v>295</v>
       </c>
       <c r="Q53" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R53" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S53" s="24">
-        <v>0</v>
+        <v>90000001</v>
       </c>
       <c r="T53" s="24" t="s">
         <v>43</v>
       </c>
       <c r="U53" s="24">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V53" s="24" t="s">
         <v>43</v>
@@ -6627,10 +7179,10 @@
     </row>
     <row r="54" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A54" s="24">
-        <v>59110001</v>
+        <v>59090001</v>
       </c>
       <c r="B54" s="24">
-        <v>5911</v>
+        <v>5909</v>
       </c>
       <c r="C54" s="24">
         <v>1</v>
@@ -6639,10 +7191,10 @@
         <v>0</v>
       </c>
       <c r="E54" s="24">
-        <v>3541800</v>
+        <v>3591900</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>316</v>
+        <v>361</v>
       </c>
       <c r="G54" s="13" t="s">
         <v>245</v>
@@ -6653,19 +7205,19 @@
         <v>43</v>
       </c>
       <c r="K54" s="24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L54" s="24">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="M54" s="24" t="s">
-        <v>43</v>
+        <v>296</v>
       </c>
       <c r="N54" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P54" s="24" t="s">
         <v>43</v>
@@ -6701,21 +7253,21 @@
         <v>1</v>
       </c>
       <c r="AA54" s="24" t="s">
-        <v>43</v>
+        <v>362</v>
       </c>
       <c r="AB54" s="24">
         <v>1</v>
       </c>
       <c r="AC54" s="24">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A55" s="25">
-        <v>59120001</v>
+      <c r="A55" s="24">
+        <v>59100001</v>
       </c>
       <c r="B55" s="24">
-        <v>5912</v>
+        <v>5910</v>
       </c>
       <c r="C55" s="24">
         <v>1</v>
@@ -6724,10 +7276,10 @@
         <v>0</v>
       </c>
       <c r="E55" s="24">
-        <v>3592100</v>
+        <v>3541800</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>373</v>
+        <v>315</v>
       </c>
       <c r="G55" s="13" t="s">
         <v>245</v>
@@ -6735,13 +7287,13 @@
       <c r="H55" s="13"/>
       <c r="I55" s="13"/>
       <c r="J55" s="24" t="s">
-        <v>372</v>
+        <v>43</v>
       </c>
       <c r="K55" s="24">
         <v>2</v>
       </c>
       <c r="L55" s="24">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="M55" s="24" t="s">
         <v>43</v>
@@ -6796,181 +7348,181 @@
       </c>
     </row>
     <row r="56" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A56" s="21">
-        <v>60010001</v>
-      </c>
-      <c r="B56" s="21">
-        <v>6001</v>
-      </c>
-      <c r="C56" s="21">
-        <v>1</v>
-      </c>
-      <c r="D56" s="21">
-        <v>0</v>
-      </c>
-      <c r="E56" s="21">
-        <v>3600200</v>
+      <c r="A56" s="24">
+        <v>59110001</v>
+      </c>
+      <c r="B56" s="24">
+        <v>5911</v>
+      </c>
+      <c r="C56" s="24">
+        <v>1</v>
+      </c>
+      <c r="D56" s="24">
+        <v>0</v>
+      </c>
+      <c r="E56" s="24">
+        <v>3541800</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="H56" s="13"/>
       <c r="I56" s="13"/>
-      <c r="J56" s="21" t="s">
-        <v>261</v>
-      </c>
-      <c r="K56" s="21">
-        <v>1</v>
-      </c>
-      <c r="L56" s="21">
-        <v>8</v>
-      </c>
-      <c r="M56" s="21" t="s">
-        <v>262</v>
-      </c>
-      <c r="N56" s="21">
+      <c r="J56" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="K56" s="24">
         <v>2</v>
       </c>
-      <c r="O56" s="21">
+      <c r="L56" s="24">
+        <v>5000</v>
+      </c>
+      <c r="M56" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="N56" s="24">
+        <v>0</v>
+      </c>
+      <c r="O56" s="24">
+        <v>0</v>
+      </c>
+      <c r="P56" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q56" s="24">
+        <v>0</v>
+      </c>
+      <c r="R56" s="24">
+        <v>0</v>
+      </c>
+      <c r="S56" s="24">
+        <v>0</v>
+      </c>
+      <c r="T56" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="U56" s="24">
+        <v>-1</v>
+      </c>
+      <c r="V56" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="W56" s="24">
         <v>10000</v>
       </c>
-      <c r="P56" s="21" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q56" s="21">
-        <v>1</v>
-      </c>
-      <c r="R56" s="21">
-        <v>1</v>
-      </c>
-      <c r="S56" s="21">
-        <v>0</v>
-      </c>
-      <c r="T56" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="U56" s="21">
-        <v>0</v>
-      </c>
-      <c r="V56" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="W56" s="21">
-        <v>10000</v>
-      </c>
-      <c r="X56" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y56" s="21">
-        <v>1</v>
-      </c>
-      <c r="Z56" s="21">
-        <v>1</v>
-      </c>
-      <c r="AA56" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB56" s="21">
-        <v>1</v>
-      </c>
-      <c r="AC56" s="21">
+      <c r="X56" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y56" s="24">
+        <v>1</v>
+      </c>
+      <c r="Z56" s="24">
+        <v>1</v>
+      </c>
+      <c r="AA56" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB56" s="24">
+        <v>1</v>
+      </c>
+      <c r="AC56" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A57" s="21">
-        <v>60020001</v>
-      </c>
-      <c r="B57" s="21">
-        <v>6002</v>
-      </c>
-      <c r="C57" s="21">
-        <v>1</v>
-      </c>
-      <c r="D57" s="21">
-        <v>0</v>
-      </c>
-      <c r="E57" s="21">
-        <v>3600400</v>
+      <c r="A57" s="25">
+        <v>59120001</v>
+      </c>
+      <c r="B57" s="24">
+        <v>5912</v>
+      </c>
+      <c r="C57" s="24">
+        <v>1</v>
+      </c>
+      <c r="D57" s="24">
+        <v>0</v>
+      </c>
+      <c r="E57" s="24">
+        <v>3592100</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>258</v>
+        <v>373</v>
       </c>
       <c r="G57" s="13" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="H57" s="13"/>
       <c r="I57" s="13"/>
-      <c r="J57" s="21" t="s">
-        <v>264</v>
-      </c>
-      <c r="K57" s="21">
-        <v>1</v>
-      </c>
-      <c r="L57" s="21">
-        <v>1</v>
-      </c>
-      <c r="M57" s="21" t="s">
-        <v>265</v>
-      </c>
-      <c r="N57" s="21">
+      <c r="J57" s="24" t="s">
+        <v>372</v>
+      </c>
+      <c r="K57" s="24">
         <v>2</v>
       </c>
-      <c r="O57" s="21">
-        <v>15000</v>
-      </c>
-      <c r="P57" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q57" s="21">
-        <v>0</v>
-      </c>
-      <c r="R57" s="21">
-        <v>0</v>
-      </c>
-      <c r="S57" s="21">
-        <v>0</v>
-      </c>
-      <c r="T57" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="U57" s="21">
+      <c r="L57" s="24">
+        <v>0</v>
+      </c>
+      <c r="M57" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="N57" s="24">
+        <v>0</v>
+      </c>
+      <c r="O57" s="24">
+        <v>0</v>
+      </c>
+      <c r="P57" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q57" s="24">
+        <v>0</v>
+      </c>
+      <c r="R57" s="24">
+        <v>0</v>
+      </c>
+      <c r="S57" s="24">
+        <v>0</v>
+      </c>
+      <c r="T57" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="U57" s="24">
         <v>-1</v>
       </c>
-      <c r="V57" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="W57" s="21">
+      <c r="V57" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="W57" s="24">
         <v>10000</v>
       </c>
-      <c r="X57" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y57" s="21">
-        <v>1</v>
-      </c>
-      <c r="Z57" s="21">
-        <v>1</v>
-      </c>
-      <c r="AA57" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB57" s="21">
-        <v>1</v>
-      </c>
-      <c r="AC57" s="21">
+      <c r="X57" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y57" s="24">
+        <v>1</v>
+      </c>
+      <c r="Z57" s="24">
+        <v>1</v>
+      </c>
+      <c r="AA57" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB57" s="24">
+        <v>1</v>
+      </c>
+      <c r="AC57" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A58" s="21">
-        <v>60030001</v>
+        <v>60010001</v>
       </c>
       <c r="B58" s="21">
-        <v>6003</v>
+        <v>6001</v>
       </c>
       <c r="C58" s="21">
         <v>1</v>
@@ -6979,10 +7531,10 @@
         <v>0</v>
       </c>
       <c r="E58" s="21">
-        <v>3600700</v>
+        <v>3600200</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G58" s="13" t="s">
         <v>254</v>
@@ -6990,7 +7542,7 @@
       <c r="H58" s="13"/>
       <c r="I58" s="13"/>
       <c r="J58" s="21" t="s">
-        <v>297</v>
+        <v>261</v>
       </c>
       <c r="K58" s="21">
         <v>1</v>
@@ -6999,7 +7551,7 @@
         <v>8</v>
       </c>
       <c r="M58" s="21" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="N58" s="21">
         <v>2</v>
@@ -7008,7 +7560,7 @@
         <v>10000</v>
       </c>
       <c r="P58" s="21" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="Q58" s="21">
         <v>1</v>
@@ -7052,10 +7604,10 @@
     </row>
     <row r="59" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A59" s="21">
-        <v>60040001</v>
+        <v>60020001</v>
       </c>
       <c r="B59" s="21">
-        <v>6004</v>
+        <v>6002</v>
       </c>
       <c r="C59" s="21">
         <v>1</v>
@@ -7064,10 +7616,10 @@
         <v>0</v>
       </c>
       <c r="E59" s="21">
-        <v>3601000</v>
+        <v>3600400</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G59" s="13" t="s">
         <v>254</v>
@@ -7075,31 +7627,31 @@
       <c r="H59" s="13"/>
       <c r="I59" s="13"/>
       <c r="J59" s="21" t="s">
-        <v>43</v>
+        <v>264</v>
       </c>
       <c r="K59" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="21" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="N59" s="21">
         <v>2</v>
       </c>
       <c r="O59" s="21">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="P59" s="21" t="s">
-        <v>269</v>
+        <v>43</v>
       </c>
       <c r="Q59" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R59" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S59" s="21">
         <v>0</v>
@@ -7108,7 +7660,7 @@
         <v>43</v>
       </c>
       <c r="U59" s="21">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V59" s="21" t="s">
         <v>43</v>
@@ -7137,10 +7689,10 @@
     </row>
     <row r="60" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A60" s="21">
-        <v>60050001</v>
+        <v>60030001</v>
       </c>
       <c r="B60" s="21">
-        <v>6005</v>
+        <v>6003</v>
       </c>
       <c r="C60" s="21">
         <v>1</v>
@@ -7149,10 +7701,10 @@
         <v>0</v>
       </c>
       <c r="E60" s="21">
-        <v>3541600</v>
+        <v>3600700</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>317</v>
+        <v>259</v>
       </c>
       <c r="G60" s="13" t="s">
         <v>254</v>
@@ -7160,31 +7712,31 @@
       <c r="H60" s="13"/>
       <c r="I60" s="13"/>
       <c r="J60" s="21" t="s">
-        <v>119</v>
+        <v>297</v>
       </c>
       <c r="K60" s="21">
+        <v>1</v>
+      </c>
+      <c r="L60" s="21">
+        <v>8</v>
+      </c>
+      <c r="M60" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="N60" s="21">
         <v>2</v>
       </c>
-      <c r="L60" s="21">
-        <v>-2000</v>
-      </c>
-      <c r="M60" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="N60" s="21">
-        <v>0</v>
-      </c>
       <c r="O60" s="21">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P60" s="21" t="s">
-        <v>43</v>
+        <v>267</v>
       </c>
       <c r="Q60" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R60" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S60" s="21">
         <v>0</v>
@@ -7193,7 +7745,7 @@
         <v>43</v>
       </c>
       <c r="U60" s="21">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V60" s="21" t="s">
         <v>43</v>
@@ -7222,10 +7774,10 @@
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A61" s="21">
-        <v>60060001</v>
+        <v>60040001</v>
       </c>
       <c r="B61" s="21">
-        <v>6006</v>
+        <v>6004</v>
       </c>
       <c r="C61" s="21">
         <v>1</v>
@@ -7234,10 +7786,10 @@
         <v>0</v>
       </c>
       <c r="E61" s="21">
-        <v>3541800</v>
+        <v>3601000</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>318</v>
+        <v>260</v>
       </c>
       <c r="G61" s="13" t="s">
         <v>254</v>
@@ -7245,31 +7797,31 @@
       <c r="H61" s="13"/>
       <c r="I61" s="13"/>
       <c r="J61" s="21" t="s">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="K61" s="21">
+        <v>0</v>
+      </c>
+      <c r="L61" s="21">
+        <v>0</v>
+      </c>
+      <c r="M61" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="N61" s="21">
         <v>2</v>
       </c>
-      <c r="L61" s="21">
-        <v>2500</v>
-      </c>
-      <c r="M61" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="N61" s="21">
-        <v>0</v>
-      </c>
       <c r="O61" s="21">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P61" s="21" t="s">
-        <v>43</v>
+        <v>269</v>
       </c>
       <c r="Q61" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R61" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S61" s="21">
         <v>0</v>
@@ -7278,7 +7830,7 @@
         <v>43</v>
       </c>
       <c r="U61" s="21">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V61" s="21" t="s">
         <v>43</v>
@@ -7307,10 +7859,10 @@
     </row>
     <row r="62" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A62" s="21">
-        <v>60070001</v>
+        <v>60050001</v>
       </c>
       <c r="B62" s="21">
-        <v>6007</v>
+        <v>6005</v>
       </c>
       <c r="C62" s="21">
         <v>1</v>
@@ -7319,10 +7871,10 @@
         <v>0</v>
       </c>
       <c r="E62" s="21">
-        <v>3601300</v>
+        <v>3541600</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G62" s="13" t="s">
         <v>254</v>
@@ -7330,28 +7882,28 @@
       <c r="H62" s="13"/>
       <c r="I62" s="13"/>
       <c r="J62" s="21" t="s">
-        <v>270</v>
+        <v>119</v>
       </c>
       <c r="K62" s="21">
         <v>2</v>
       </c>
       <c r="L62" s="21">
-        <v>10000</v>
+        <v>-2000</v>
       </c>
       <c r="M62" s="21" t="s">
-        <v>271</v>
+        <v>43</v>
       </c>
       <c r="N62" s="21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O62" s="21">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="P62" s="21" t="s">
-        <v>272</v>
+        <v>43</v>
       </c>
       <c r="Q62" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R62" s="21">
         <v>0</v>
@@ -7391,181 +7943,181 @@
       </c>
     </row>
     <row r="63" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A63" s="22">
-        <v>61010001</v>
-      </c>
-      <c r="B63" s="22">
-        <v>6101</v>
-      </c>
-      <c r="C63" s="22">
-        <v>1</v>
-      </c>
-      <c r="D63" s="22">
-        <v>0</v>
-      </c>
-      <c r="E63" s="22">
-        <v>3610300</v>
+      <c r="A63" s="21">
+        <v>60060001</v>
+      </c>
+      <c r="B63" s="21">
+        <v>6006</v>
+      </c>
+      <c r="C63" s="21">
+        <v>1</v>
+      </c>
+      <c r="D63" s="21">
+        <v>0</v>
+      </c>
+      <c r="E63" s="21">
+        <v>3541800</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G63" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H63" s="13"/>
       <c r="I63" s="13"/>
-      <c r="J63" s="22" t="s">
-        <v>273</v>
-      </c>
-      <c r="K63" s="22">
-        <v>1</v>
-      </c>
-      <c r="L63" s="22">
-        <v>8</v>
-      </c>
-      <c r="M63" s="22" t="s">
-        <v>274</v>
-      </c>
-      <c r="N63" s="22">
+      <c r="J63" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="K63" s="21">
         <v>2</v>
       </c>
-      <c r="O63" s="22">
+      <c r="L63" s="21">
+        <v>2500</v>
+      </c>
+      <c r="M63" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="N63" s="21">
+        <v>0</v>
+      </c>
+      <c r="O63" s="21">
+        <v>0</v>
+      </c>
+      <c r="P63" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q63" s="21">
+        <v>0</v>
+      </c>
+      <c r="R63" s="21">
+        <v>0</v>
+      </c>
+      <c r="S63" s="21">
+        <v>0</v>
+      </c>
+      <c r="T63" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="U63" s="21">
+        <v>-1</v>
+      </c>
+      <c r="V63" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W63" s="21">
         <v>10000</v>
       </c>
-      <c r="P63" s="22" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q63" s="22">
-        <v>1</v>
-      </c>
-      <c r="R63" s="22">
-        <v>1</v>
-      </c>
-      <c r="S63" s="22">
-        <v>0</v>
-      </c>
-      <c r="T63" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="U63" s="22">
-        <v>0</v>
-      </c>
-      <c r="V63" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="W63" s="22">
-        <v>10000</v>
-      </c>
-      <c r="X63" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y63" s="22">
-        <v>1</v>
-      </c>
-      <c r="Z63" s="22">
-        <v>1</v>
-      </c>
-      <c r="AA63" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB63" s="22">
-        <v>1</v>
-      </c>
-      <c r="AC63" s="22">
+      <c r="X63" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y63" s="21">
+        <v>1</v>
+      </c>
+      <c r="Z63" s="21">
+        <v>1</v>
+      </c>
+      <c r="AA63" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB63" s="21">
+        <v>1</v>
+      </c>
+      <c r="AC63" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A64" s="22">
-        <v>61020001</v>
-      </c>
-      <c r="B64" s="22">
-        <v>6102</v>
-      </c>
-      <c r="C64" s="22">
-        <v>1</v>
-      </c>
-      <c r="D64" s="22">
-        <v>0</v>
-      </c>
-      <c r="E64" s="22">
-        <v>3610500</v>
+      <c r="A64" s="21">
+        <v>60070001</v>
+      </c>
+      <c r="B64" s="21">
+        <v>6007</v>
+      </c>
+      <c r="C64" s="21">
+        <v>1</v>
+      </c>
+      <c r="D64" s="21">
+        <v>0</v>
+      </c>
+      <c r="E64" s="21">
+        <v>3601300</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>299</v>
+        <v>319</v>
       </c>
       <c r="G64" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H64" s="13"/>
       <c r="I64" s="13"/>
-      <c r="J64" s="22" t="s">
-        <v>276</v>
-      </c>
-      <c r="K64" s="22">
+      <c r="J64" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="K64" s="21">
         <v>2</v>
       </c>
-      <c r="L64" s="22">
+      <c r="L64" s="21">
         <v>10000</v>
       </c>
-      <c r="M64" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="N64" s="22">
-        <v>0</v>
-      </c>
-      <c r="O64" s="22">
-        <v>0</v>
-      </c>
-      <c r="P64" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q64" s="22">
-        <v>0</v>
-      </c>
-      <c r="R64" s="22">
-        <v>0</v>
-      </c>
-      <c r="S64" s="22">
-        <v>0</v>
-      </c>
-      <c r="T64" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="U64" s="22">
+      <c r="M64" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="N64" s="21">
+        <v>2</v>
+      </c>
+      <c r="O64" s="21">
+        <v>2000</v>
+      </c>
+      <c r="P64" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q64" s="21">
+        <v>1</v>
+      </c>
+      <c r="R64" s="21">
+        <v>0</v>
+      </c>
+      <c r="S64" s="21">
+        <v>0</v>
+      </c>
+      <c r="T64" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="U64" s="21">
         <v>-1</v>
       </c>
-      <c r="V64" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="W64" s="22">
+      <c r="V64" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W64" s="21">
         <v>10000</v>
       </c>
-      <c r="X64" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y64" s="22">
-        <v>1</v>
-      </c>
-      <c r="Z64" s="22">
-        <v>1</v>
-      </c>
-      <c r="AA64" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB64" s="22">
-        <v>1</v>
-      </c>
-      <c r="AC64" s="22">
+      <c r="X64" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y64" s="21">
+        <v>1</v>
+      </c>
+      <c r="Z64" s="21">
+        <v>1</v>
+      </c>
+      <c r="AA64" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB64" s="21">
+        <v>1</v>
+      </c>
+      <c r="AC64" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A65" s="22">
-        <v>61030001</v>
+        <v>61010001</v>
       </c>
       <c r="B65" s="22">
-        <v>6103</v>
+        <v>6101</v>
       </c>
       <c r="C65" s="22">
         <v>1</v>
@@ -7574,10 +8126,10 @@
         <v>0</v>
       </c>
       <c r="E65" s="22">
-        <v>3610700</v>
+        <v>3610300</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="G65" s="13" t="s">
         <v>255</v>
@@ -7585,16 +8137,16 @@
       <c r="H65" s="13"/>
       <c r="I65" s="13"/>
       <c r="J65" s="22" t="s">
-        <v>43</v>
+        <v>273</v>
       </c>
       <c r="K65" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="22">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M65" s="22" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="N65" s="22">
         <v>2</v>
@@ -7603,7 +8155,7 @@
         <v>10000</v>
       </c>
       <c r="P65" s="22" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="Q65" s="22">
         <v>1</v>
@@ -7647,10 +8199,10 @@
     </row>
     <row r="66" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A66" s="22">
-        <v>61040001</v>
+        <v>61020001</v>
       </c>
       <c r="B66" s="22">
-        <v>6104</v>
+        <v>6102</v>
       </c>
       <c r="C66" s="22">
         <v>1</v>
@@ -7659,10 +8211,10 @@
         <v>0</v>
       </c>
       <c r="E66" s="22">
-        <v>3541400</v>
+        <v>3610500</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>256</v>
+        <v>299</v>
       </c>
       <c r="G66" s="13" t="s">
         <v>255</v>
@@ -7670,13 +8222,13 @@
       <c r="H66" s="13"/>
       <c r="I66" s="13"/>
       <c r="J66" s="22" t="s">
-        <v>118</v>
+        <v>276</v>
       </c>
       <c r="K66" s="22">
         <v>2</v>
       </c>
       <c r="L66" s="22">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="M66" s="22" t="s">
         <v>43</v>
@@ -7732,10 +8284,10 @@
     </row>
     <row r="67" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A67" s="22">
-        <v>61050001</v>
+        <v>61030001</v>
       </c>
       <c r="B67" s="22">
-        <v>6105</v>
+        <v>6103</v>
       </c>
       <c r="C67" s="22">
         <v>1</v>
@@ -7744,10 +8296,10 @@
         <v>0</v>
       </c>
       <c r="E67" s="22">
-        <v>3610900</v>
+        <v>3610700</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="G67" s="13" t="s">
         <v>255</v>
@@ -7755,31 +8307,31 @@
       <c r="H67" s="13"/>
       <c r="I67" s="13"/>
       <c r="J67" s="22" t="s">
-        <v>305</v>
+        <v>43</v>
       </c>
       <c r="K67" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" s="22" t="s">
-        <v>43</v>
+        <v>277</v>
       </c>
       <c r="N67" s="22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O67" s="22">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P67" s="22" t="s">
-        <v>43</v>
+        <v>278</v>
       </c>
       <c r="Q67" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R67" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S67" s="22">
         <v>0</v>
@@ -7788,7 +8340,7 @@
         <v>43</v>
       </c>
       <c r="U67" s="22">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V67" s="22" t="s">
         <v>43</v>
@@ -7817,10 +8369,10 @@
     </row>
     <row r="68" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A68" s="22">
-        <v>61060001</v>
+        <v>61040001</v>
       </c>
       <c r="B68" s="22">
-        <v>6106</v>
+        <v>6104</v>
       </c>
       <c r="C68" s="22">
         <v>1</v>
@@ -7829,10 +8381,10 @@
         <v>0</v>
       </c>
       <c r="E68" s="22">
-        <v>3611100</v>
+        <v>3541400</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>371</v>
+        <v>256</v>
       </c>
       <c r="G68" s="13" t="s">
         <v>255</v>
@@ -7840,13 +8392,13 @@
       <c r="H68" s="13"/>
       <c r="I68" s="13"/>
       <c r="J68" s="22" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="K68" s="22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L68" s="22">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="M68" s="22" t="s">
         <v>43</v>
@@ -7902,10 +8454,10 @@
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A69" s="22">
-        <v>61070001</v>
+        <v>61050001</v>
       </c>
       <c r="B69" s="22">
-        <v>6107</v>
+        <v>6105</v>
       </c>
       <c r="C69" s="22">
         <v>1</v>
@@ -7914,10 +8466,10 @@
         <v>0</v>
       </c>
       <c r="E69" s="22">
-        <v>3611300</v>
+        <v>3610900</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="G69" s="13" t="s">
         <v>255</v>
@@ -7925,13 +8477,13 @@
       <c r="H69" s="13"/>
       <c r="I69" s="13"/>
       <c r="J69" s="22" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K69" s="22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L69" s="22">
-        <v>300000</v>
+        <v>1</v>
       </c>
       <c r="M69" s="22" t="s">
         <v>43</v>
@@ -7943,13 +8495,13 @@
         <v>0</v>
       </c>
       <c r="P69" s="22" t="s">
-        <v>307</v>
+        <v>43</v>
       </c>
       <c r="Q69" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R69" s="22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S69" s="22">
         <v>0</v>
@@ -7987,10 +8539,10 @@
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A70" s="22">
-        <v>61080001</v>
+        <v>61060001</v>
       </c>
       <c r="B70" s="22">
-        <v>6108</v>
+        <v>6106</v>
       </c>
       <c r="C70" s="22">
         <v>1</v>
@@ -7999,10 +8551,10 @@
         <v>0</v>
       </c>
       <c r="E70" s="22">
-        <v>3611500</v>
+        <v>3611100</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>301</v>
+        <v>371</v>
       </c>
       <c r="G70" s="13" t="s">
         <v>255</v>
@@ -8019,22 +8571,22 @@
         <v>0</v>
       </c>
       <c r="M70" s="22" t="s">
-        <v>309</v>
+        <v>43</v>
       </c>
       <c r="N70" s="22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O70" s="22">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="P70" s="22" t="s">
-        <v>310</v>
+        <v>43</v>
       </c>
       <c r="Q70" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R70" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S70" s="22">
         <v>0</v>
@@ -8043,7 +8595,7 @@
         <v>43</v>
       </c>
       <c r="U70" s="22">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V70" s="22" t="s">
         <v>43</v>
@@ -8072,10 +8624,10 @@
     </row>
     <row r="71" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A71" s="22">
-        <v>61090001</v>
+        <v>61070001</v>
       </c>
       <c r="B71" s="22">
-        <v>6109</v>
+        <v>6107</v>
       </c>
       <c r="C71" s="22">
         <v>1</v>
@@ -8084,10 +8636,10 @@
         <v>0</v>
       </c>
       <c r="E71" s="22">
-        <v>3611700</v>
+        <v>3611300</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G71" s="13" t="s">
         <v>255</v>
@@ -8095,7 +8647,7 @@
       <c r="H71" s="13"/>
       <c r="I71" s="13"/>
       <c r="J71" s="22" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K71" s="22">
         <v>3</v>
@@ -8113,13 +8665,13 @@
         <v>0</v>
       </c>
       <c r="P71" s="22" t="s">
-        <v>43</v>
+        <v>307</v>
       </c>
       <c r="Q71" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71" s="22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S71" s="22">
         <v>0</v>
@@ -8157,10 +8709,10 @@
     </row>
     <row r="72" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A72" s="22">
-        <v>61100001</v>
+        <v>61080001</v>
       </c>
       <c r="B72" s="22">
-        <v>6110</v>
+        <v>6108</v>
       </c>
       <c r="C72" s="22">
         <v>1</v>
@@ -8169,10 +8721,10 @@
         <v>0</v>
       </c>
       <c r="E72" s="22">
-        <v>3590800</v>
+        <v>3611500</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G72" s="13" t="s">
         <v>255</v>
@@ -8189,7 +8741,7 @@
         <v>0</v>
       </c>
       <c r="M72" s="22" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="N72" s="22">
         <v>2</v>
@@ -8198,7 +8750,7 @@
         <v>10000</v>
       </c>
       <c r="P72" s="22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q72" s="22">
         <v>1</v>
@@ -8240,8 +8792,178 @@
         <v>0</v>
       </c>
     </row>
+    <row r="73" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A73" s="22">
+        <v>61090001</v>
+      </c>
+      <c r="B73" s="22">
+        <v>6109</v>
+      </c>
+      <c r="C73" s="22">
+        <v>1</v>
+      </c>
+      <c r="D73" s="22">
+        <v>0</v>
+      </c>
+      <c r="E73" s="22">
+        <v>3611700</v>
+      </c>
+      <c r="F73" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="G73" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="H73" s="13"/>
+      <c r="I73" s="13"/>
+      <c r="J73" s="22" t="s">
+        <v>308</v>
+      </c>
+      <c r="K73" s="22">
+        <v>3</v>
+      </c>
+      <c r="L73" s="22">
+        <v>300000</v>
+      </c>
+      <c r="M73" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="N73" s="22">
+        <v>0</v>
+      </c>
+      <c r="O73" s="22">
+        <v>0</v>
+      </c>
+      <c r="P73" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q73" s="22">
+        <v>0</v>
+      </c>
+      <c r="R73" s="22">
+        <v>0</v>
+      </c>
+      <c r="S73" s="22">
+        <v>0</v>
+      </c>
+      <c r="T73" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="U73" s="22">
+        <v>-1</v>
+      </c>
+      <c r="V73" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="W73" s="22">
+        <v>10000</v>
+      </c>
+      <c r="X73" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y73" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z73" s="22">
+        <v>1</v>
+      </c>
+      <c r="AA73" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB73" s="22">
+        <v>1</v>
+      </c>
+      <c r="AC73" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A74" s="22">
+        <v>61100001</v>
+      </c>
+      <c r="B74" s="22">
+        <v>6110</v>
+      </c>
+      <c r="C74" s="22">
+        <v>1</v>
+      </c>
+      <c r="D74" s="22">
+        <v>0</v>
+      </c>
+      <c r="E74" s="22">
+        <v>3590800</v>
+      </c>
+      <c r="F74" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="G74" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="H74" s="13"/>
+      <c r="I74" s="13"/>
+      <c r="J74" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="K74" s="22">
+        <v>0</v>
+      </c>
+      <c r="L74" s="22">
+        <v>0</v>
+      </c>
+      <c r="M74" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="N74" s="22">
+        <v>2</v>
+      </c>
+      <c r="O74" s="22">
+        <v>10000</v>
+      </c>
+      <c r="P74" s="22" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q74" s="22">
+        <v>1</v>
+      </c>
+      <c r="R74" s="22">
+        <v>1</v>
+      </c>
+      <c r="S74" s="22">
+        <v>0</v>
+      </c>
+      <c r="T74" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="U74" s="22">
+        <v>0</v>
+      </c>
+      <c r="V74" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="W74" s="22">
+        <v>10000</v>
+      </c>
+      <c r="X74" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y74" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z74" s="22">
+        <v>1</v>
+      </c>
+      <c r="AA74" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB74" s="22">
+        <v>1</v>
+      </c>
+      <c r="AC74" s="22">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:AC72" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:AC74" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -8249,6 +8971,1030 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE859F77-6529-4974-B226-877FAEE341A8}">
+  <dimension ref="E7:S71"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="27.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="1"/>
+    <col min="8" max="8" width="10.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="39.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9" style="1"/>
+    <col min="11" max="11" width="17.125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="7" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="11" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="12" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="13" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="14" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="15" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="16" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="17" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="18" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="19" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" s="1" t="str">
+        <f>H19&amp;"-"&amp;I19</f>
+        <v>参数4LIST-触发的技能id</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="20" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" s="1" t="str">
+        <f t="shared" ref="G20:G71" si="0">H20&amp;"-"&amp;I20</f>
+        <v>参数5-持续时间（毫秒）</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="21" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数6-效果基础命中率（万分比）</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="22" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数7-效果最大叠加层数</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="23" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数8-效果触发间隔（毫秒）</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="24" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数9-击中回复生命值-固定值</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="25" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数10-击中回复生命值-自身最大生命值百万分比</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="26" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数11-击中回复效果提高万分比</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="27" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E27" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数12-击杀回复生命-固定值</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="S27" s="1" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="28" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G28" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数13-击杀回复生命-自身最大生命值百万分比</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="29" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G29" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数14-击杀回复生命-目标最大生命值百万分比</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="S29" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="30" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E30" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G30" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数15-击杀回复生命效果提高万分比</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="31" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E31" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G31" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数16-获得护盾-固定值</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="S31" s="1" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="32" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E32" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="G32" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数17-获得护盾-自身生命百万分比</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="33" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="E33" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="G33" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数18-获得护盾-自身已损失生命万分比</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="34" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="E34" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G34" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数19-获得护盾效果提高万分比</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="35" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="E35" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="G35" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数20-技能增加-固定值</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="36" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="G36" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数21-技能增加-万分比</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="37" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="G37" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数22-技能增加-普通攻击范围万分比</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="38" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="G38" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数25LIST-攻击提高-攻击的元素类型</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="39" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="G39" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数25LIST-攻击提高-固定值</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="40" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="G40" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数25LIST-攻击提高-万分比</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="41" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="G41" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数28-防御提高-固定值</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="42" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="G42" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数29-防御提高-万分比</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="43" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="G43" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数30-生命上限提高-固定值</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="44" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="G44" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数31-生命上限提高-百万分比</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="45" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="G45" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数32-攻击速度提高-万分比</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="46" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="G46" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数33-移动速度提高-万分比</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="47" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="G47" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数34-攻击范围提高-万分比</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="48" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="G48" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数35-攻击目标数量提高-固定值</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="49" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G49" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数36-</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="50" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G50" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数37-</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="51" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G51" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数38-</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="52" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G52" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数39-</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="53" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G53" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数40-</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="54" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G54" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数41-</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="55" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G55" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数42-</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="56" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G56" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数41-</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="57" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G57" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数42-</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="58" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G58" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数43-</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="59" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G59" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数44-</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="60" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G60" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数45-</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="61" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G61" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数46-</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="62" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G62" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数47-</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="63" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G63" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数48-</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="64" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G64" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数49-</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="65" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G65" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数50-</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="66" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G66" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数51-</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="67" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G67" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数52-</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="68" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G68" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数53-</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="69" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G69" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数54-</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="70" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G70" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数55-</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="71" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G71" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数56-</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="12" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="D6:F43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E89779E-6FAA-4DF9-B7FD-A79767996087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D321BFCA-B977-4F35-86D2-C4FD31B67A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="备注" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skilleffect_v8!$A$4:$AC$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skilleffect_v8!$A$4:$AC$72</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="520">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1845,58 +1845,6 @@
   </si>
   <si>
     <t>备注</t>
-  </si>
-  <si>
-    <t>受到的伤害总加成</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成伤害总加成</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成的伤害总加成【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到的伤害总加成【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542801:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542601:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3543001:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542607:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542807:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3543007:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542605:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542805:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3543005:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2518,7 +2466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC74"/>
+  <dimension ref="A1:AC72"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -4123,7 +4071,7 @@
         <v>177</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>525</v>
+        <v>127</v>
       </c>
       <c r="K19" s="15">
         <v>2</v>
@@ -4153,7 +4101,7 @@
         <v>0</v>
       </c>
       <c r="T19" s="15" t="s">
-        <v>530</v>
+        <v>150</v>
       </c>
       <c r="U19" s="15">
         <v>4000</v>
@@ -4165,7 +4113,7 @@
         <v>10000</v>
       </c>
       <c r="X19" s="15" t="s">
-        <v>527</v>
+        <v>151</v>
       </c>
       <c r="Y19" s="15">
         <v>1</v>
@@ -4184,189 +4132,189 @@
       </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A20" s="15">
-        <v>54140001</v>
-      </c>
-      <c r="B20" s="15">
-        <v>5414</v>
-      </c>
-      <c r="C20" s="15">
-        <v>1</v>
-      </c>
-      <c r="D20" s="15">
-        <v>0</v>
-      </c>
-      <c r="E20" s="15">
-        <v>3542800</v>
-      </c>
-      <c r="F20" s="16" t="s">
-        <v>521</v>
-      </c>
-      <c r="G20" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="I20" s="16" t="s">
-        <v>522</v>
-      </c>
-      <c r="J20" s="15" t="s">
-        <v>524</v>
-      </c>
-      <c r="K20" s="15">
+      <c r="A20" s="17">
+        <v>55010001</v>
+      </c>
+      <c r="B20" s="17">
+        <v>5501</v>
+      </c>
+      <c r="C20" s="17">
+        <v>1</v>
+      </c>
+      <c r="D20" s="17">
+        <v>0</v>
+      </c>
+      <c r="E20" s="17">
+        <v>3550200</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="J20" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="K20" s="17">
+        <v>0</v>
+      </c>
+      <c r="L20" s="17">
+        <v>0</v>
+      </c>
+      <c r="M20" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="N20" s="17">
+        <v>0</v>
+      </c>
+      <c r="O20" s="17">
+        <v>0</v>
+      </c>
+      <c r="P20" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q20" s="17">
+        <v>0</v>
+      </c>
+      <c r="R20" s="17">
+        <v>0</v>
+      </c>
+      <c r="S20" s="17">
+        <v>0</v>
+      </c>
+      <c r="T20" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="U20" s="17">
+        <v>2000</v>
+      </c>
+      <c r="V20" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="W20" s="17">
+        <v>1000</v>
+      </c>
+      <c r="X20" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y20" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="17">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB20" s="17">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A21" s="17">
+        <v>55020001</v>
+      </c>
+      <c r="B21" s="17">
+        <v>5502</v>
+      </c>
+      <c r="C21" s="17">
+        <v>1</v>
+      </c>
+      <c r="D21" s="17">
+        <v>0</v>
+      </c>
+      <c r="E21" s="17">
+        <v>3550500</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="J21" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="K21" s="17">
+        <v>1</v>
+      </c>
+      <c r="L21" s="17">
+        <v>12</v>
+      </c>
+      <c r="M21" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="N21" s="17">
         <v>2</v>
       </c>
-      <c r="L20" s="15">
-        <v>5000</v>
-      </c>
-      <c r="M20" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="N20" s="15">
-        <v>0</v>
-      </c>
-      <c r="O20" s="15">
-        <v>0</v>
-      </c>
-      <c r="P20" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q20" s="15">
-        <v>0</v>
-      </c>
-      <c r="R20" s="15">
-        <v>0</v>
-      </c>
-      <c r="S20" s="15">
-        <v>0</v>
-      </c>
-      <c r="T20" s="15" t="s">
-        <v>531</v>
-      </c>
-      <c r="U20" s="15">
-        <v>-1</v>
-      </c>
-      <c r="V20" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="W20" s="15">
+      <c r="O21" s="17">
         <v>10000</v>
       </c>
-      <c r="X20" s="15" t="s">
-        <v>528</v>
-      </c>
-      <c r="Y20" s="15">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="15">
-        <v>3</v>
-      </c>
-      <c r="AA20" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB20" s="15">
-        <v>1</v>
-      </c>
-      <c r="AC20" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A21" s="15">
-        <v>54150001</v>
-      </c>
-      <c r="B21" s="15">
-        <v>5415</v>
-      </c>
-      <c r="C21" s="15">
-        <v>1</v>
-      </c>
-      <c r="D21" s="15">
-        <v>0</v>
-      </c>
-      <c r="E21" s="15">
-        <v>3543000</v>
-      </c>
-      <c r="F21" s="16" t="s">
-        <v>520</v>
-      </c>
-      <c r="G21" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="H21" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="I21" s="16" t="s">
-        <v>523</v>
-      </c>
-      <c r="J21" s="15" t="s">
-        <v>526</v>
-      </c>
-      <c r="K21" s="15">
-        <v>2</v>
-      </c>
-      <c r="L21" s="15">
+      <c r="P21" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q21" s="17">
+        <v>1</v>
+      </c>
+      <c r="R21" s="17">
+        <v>1</v>
+      </c>
+      <c r="S21" s="17">
+        <v>5000001</v>
+      </c>
+      <c r="T21" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="U21" s="17">
+        <v>4000</v>
+      </c>
+      <c r="V21" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="W21" s="17">
         <v>10000</v>
       </c>
-      <c r="M21" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="N21" s="15">
-        <v>0</v>
-      </c>
-      <c r="O21" s="15">
-        <v>0</v>
-      </c>
-      <c r="P21" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q21" s="15">
-        <v>0</v>
-      </c>
-      <c r="R21" s="15">
-        <v>0</v>
-      </c>
-      <c r="S21" s="15">
-        <v>0</v>
-      </c>
-      <c r="T21" s="15" t="s">
-        <v>532</v>
-      </c>
-      <c r="U21" s="15">
-        <v>-1</v>
-      </c>
-      <c r="V21" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="W21" s="15">
-        <v>10000</v>
-      </c>
-      <c r="X21" s="15" t="s">
-        <v>529</v>
-      </c>
-      <c r="Y21" s="15">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="15">
-        <v>3</v>
-      </c>
-      <c r="AA21" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB21" s="15">
-        <v>1</v>
-      </c>
-      <c r="AC21" s="15">
+      <c r="X21" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y21" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="17">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB21" s="17">
+        <v>1</v>
+      </c>
+      <c r="AC21" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A22" s="17">
-        <v>55010001</v>
+        <v>55030001</v>
       </c>
       <c r="B22" s="17">
-        <v>5501</v>
+        <v>5503</v>
       </c>
       <c r="C22" s="17">
         <v>1</v>
@@ -4375,19 +4323,19 @@
         <v>0</v>
       </c>
       <c r="E22" s="17">
-        <v>3550200</v>
+        <v>3550700</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>185</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="J22" s="17" t="s">
         <v>43</v>
@@ -4396,40 +4344,40 @@
         <v>0</v>
       </c>
       <c r="L22" s="17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="M22" s="17" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="N22" s="17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O22" s="17">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P22" s="17" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="Q22" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" s="17">
-        <v>0</v>
+        <v>5000001</v>
       </c>
       <c r="T22" s="17" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="U22" s="17">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="V22" s="17" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="W22" s="17">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="X22" s="17" t="s">
         <v>43</v>
@@ -4452,10 +4400,10 @@
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A23" s="17">
-        <v>55020001</v>
+        <v>55040001</v>
       </c>
       <c r="B23" s="17">
-        <v>5502</v>
+        <v>5504</v>
       </c>
       <c r="C23" s="17">
         <v>1</v>
@@ -4464,58 +4412,58 @@
         <v>0</v>
       </c>
       <c r="E23" s="17">
-        <v>3550500</v>
+        <v>3550900</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>185</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J23" s="17" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K23" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" s="17">
-        <v>12</v>
+        <v>3000</v>
       </c>
       <c r="M23" s="17" t="s">
-        <v>81</v>
+        <v>164</v>
       </c>
       <c r="N23" s="17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O23" s="17">
-        <v>10000</v>
+        <v>30</v>
       </c>
       <c r="P23" s="17" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="Q23" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" s="17">
-        <v>5000001</v>
+        <v>0</v>
       </c>
       <c r="T23" s="17" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="U23" s="17">
-        <v>4000</v>
+        <v>-1</v>
       </c>
       <c r="V23" s="17" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="W23" s="17">
         <v>10000</v>
@@ -4541,10 +4489,10 @@
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A24" s="17">
-        <v>55030001</v>
+        <v>55050001</v>
       </c>
       <c r="B24" s="17">
-        <v>5503</v>
+        <v>5505</v>
       </c>
       <c r="C24" s="17">
         <v>1</v>
@@ -4553,55 +4501,55 @@
         <v>0</v>
       </c>
       <c r="E24" s="17">
-        <v>3550700</v>
+        <v>3551100</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>72</v>
+        <v>156</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>185</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J24" s="17" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="K24" s="17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L24" s="17">
-        <v>1000</v>
+        <v>100000</v>
       </c>
       <c r="M24" s="17" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="N24" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O24" s="17">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="P24" s="17" t="s">
-        <v>84</v>
+        <v>374</v>
       </c>
       <c r="Q24" s="17">
         <v>1</v>
       </c>
       <c r="R24" s="17">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="S24" s="17">
-        <v>5000001</v>
+        <v>0</v>
       </c>
       <c r="T24" s="17" t="s">
         <v>43</v>
       </c>
       <c r="U24" s="17">
-        <v>4000</v>
+        <v>-1</v>
       </c>
       <c r="V24" s="17" t="s">
         <v>43</v>
@@ -4630,10 +4578,10 @@
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A25" s="17">
-        <v>55040001</v>
+        <v>55060001</v>
       </c>
       <c r="B25" s="17">
-        <v>5504</v>
+        <v>5506</v>
       </c>
       <c r="C25" s="17">
         <v>1</v>
@@ -4642,37 +4590,37 @@
         <v>0</v>
       </c>
       <c r="E25" s="17">
-        <v>3550900</v>
+        <v>3551300</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>74</v>
+        <v>357</v>
       </c>
       <c r="G25" s="13" t="s">
         <v>185</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K25" s="17">
         <v>2</v>
       </c>
       <c r="L25" s="17">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="M25" s="17" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="N25" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25" s="17">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="P25" s="17" t="s">
         <v>43</v>
@@ -4719,10 +4667,10 @@
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A26" s="17">
-        <v>55050001</v>
+        <v>55070001</v>
       </c>
       <c r="B26" s="17">
-        <v>5505</v>
+        <v>5507</v>
       </c>
       <c r="C26" s="17">
         <v>1</v>
@@ -4731,64 +4679,64 @@
         <v>0</v>
       </c>
       <c r="E26" s="17">
-        <v>3551100</v>
+        <v>3551500</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G26" s="13" t="s">
         <v>185</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>355</v>
+        <v>157</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>86</v>
+        <v>153</v>
       </c>
       <c r="K26" s="17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L26" s="17">
-        <v>100000</v>
+        <v>2000</v>
       </c>
       <c r="M26" s="17" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="N26" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" s="17">
         <v>0</v>
       </c>
       <c r="P26" s="17" t="s">
-        <v>374</v>
+        <v>70</v>
       </c>
       <c r="Q26" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" s="17">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="S26" s="17">
         <v>0</v>
       </c>
       <c r="T26" s="17" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="U26" s="17">
         <v>-1</v>
       </c>
       <c r="V26" s="17" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="W26" s="17">
         <v>10000</v>
       </c>
       <c r="X26" s="17" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="Y26" s="17">
         <v>1</v>
@@ -4807,189 +4755,189 @@
       </c>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A27" s="17">
-        <v>55060001</v>
-      </c>
-      <c r="B27" s="17">
-        <v>5506</v>
-      </c>
-      <c r="C27" s="17">
-        <v>1</v>
-      </c>
-      <c r="D27" s="17">
-        <v>0</v>
-      </c>
-      <c r="E27" s="17">
-        <v>3551300</v>
+      <c r="A27" s="18">
+        <v>56010001</v>
+      </c>
+      <c r="B27" s="18">
+        <v>5601</v>
+      </c>
+      <c r="C27" s="18">
+        <v>1</v>
+      </c>
+      <c r="D27" s="18">
+        <v>0</v>
+      </c>
+      <c r="E27" s="18">
+        <v>3560200</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>357</v>
+        <v>192</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>356</v>
-      </c>
-      <c r="J27" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="K27" s="17">
+        <v>334</v>
+      </c>
+      <c r="J27" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="K27" s="18">
         <v>2</v>
       </c>
-      <c r="L27" s="17">
+      <c r="L27" s="18">
         <v>5000</v>
       </c>
-      <c r="M27" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="N27" s="17">
-        <v>1</v>
-      </c>
-      <c r="O27" s="17">
+      <c r="M27" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="N27" s="18">
+        <v>1</v>
+      </c>
+      <c r="O27" s="18">
         <v>50</v>
       </c>
-      <c r="P27" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q27" s="17">
-        <v>0</v>
-      </c>
-      <c r="R27" s="17">
-        <v>0</v>
-      </c>
-      <c r="S27" s="17">
-        <v>0</v>
-      </c>
-      <c r="T27" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="U27" s="17">
-        <v>-1</v>
-      </c>
-      <c r="V27" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="W27" s="17">
+      <c r="P27" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q27" s="18">
+        <v>0</v>
+      </c>
+      <c r="R27" s="18">
+        <v>0</v>
+      </c>
+      <c r="S27" s="18">
+        <v>0</v>
+      </c>
+      <c r="T27" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="U27" s="18">
+        <v>4000</v>
+      </c>
+      <c r="V27" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="W27" s="18">
+        <v>1500</v>
+      </c>
+      <c r="X27" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y27" s="18">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="18">
+        <v>1</v>
+      </c>
+      <c r="AA27" s="18" t="s">
+        <v>339</v>
+      </c>
+      <c r="AB27" s="18">
+        <v>1</v>
+      </c>
+      <c r="AC27" s="18">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A28" s="18">
+        <v>56020001</v>
+      </c>
+      <c r="B28" s="18">
+        <v>5602</v>
+      </c>
+      <c r="C28" s="18">
+        <v>1</v>
+      </c>
+      <c r="D28" s="18">
+        <v>0</v>
+      </c>
+      <c r="E28" s="18">
+        <v>3560500</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="J28" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="K28" s="18">
+        <v>1</v>
+      </c>
+      <c r="L28" s="18">
+        <v>8</v>
+      </c>
+      <c r="M28" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="N28" s="18">
+        <v>1</v>
+      </c>
+      <c r="O28" s="18">
         <v>10000</v>
       </c>
-      <c r="X27" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y27" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z27" s="17">
-        <v>1</v>
-      </c>
-      <c r="AA27" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB27" s="17">
-        <v>1</v>
-      </c>
-      <c r="AC27" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A28" s="17">
-        <v>55070001</v>
-      </c>
-      <c r="B28" s="17">
-        <v>5507</v>
-      </c>
-      <c r="C28" s="17">
-        <v>1</v>
-      </c>
-      <c r="D28" s="17">
-        <v>0</v>
-      </c>
-      <c r="E28" s="17">
-        <v>3551500</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="I28" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="J28" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="K28" s="17">
-        <v>2</v>
-      </c>
-      <c r="L28" s="17">
-        <v>2000</v>
-      </c>
-      <c r="M28" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="N28" s="17">
-        <v>0</v>
-      </c>
-      <c r="O28" s="17">
-        <v>0</v>
-      </c>
-      <c r="P28" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q28" s="17">
-        <v>0</v>
-      </c>
-      <c r="R28" s="17">
-        <v>0</v>
-      </c>
-      <c r="S28" s="17">
-        <v>0</v>
-      </c>
-      <c r="T28" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="U28" s="17">
-        <v>-1</v>
-      </c>
-      <c r="V28" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="W28" s="17">
+      <c r="P28" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q28" s="18">
+        <v>1</v>
+      </c>
+      <c r="R28" s="18">
+        <v>1</v>
+      </c>
+      <c r="S28" s="18">
+        <v>0</v>
+      </c>
+      <c r="T28" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="U28" s="18">
+        <v>0</v>
+      </c>
+      <c r="V28" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="W28" s="18">
         <v>10000</v>
       </c>
-      <c r="X28" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y28" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z28" s="17">
-        <v>1</v>
-      </c>
-      <c r="AA28" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB28" s="17">
-        <v>1</v>
-      </c>
-      <c r="AC28" s="17">
+      <c r="X28" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y28" s="18">
+        <v>1</v>
+      </c>
+      <c r="Z28" s="18">
+        <v>1</v>
+      </c>
+      <c r="AA28" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB28" s="18">
+        <v>1</v>
+      </c>
+      <c r="AC28" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A29" s="18">
-        <v>56010001</v>
+        <v>56030001</v>
       </c>
       <c r="B29" s="18">
-        <v>5601</v>
+        <v>5603</v>
       </c>
       <c r="C29" s="18">
         <v>1</v>
@@ -4998,37 +4946,37 @@
         <v>0</v>
       </c>
       <c r="E29" s="18">
-        <v>3560200</v>
+        <v>3560700</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>189</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>334</v>
+        <v>236</v>
       </c>
       <c r="J29" s="18" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="K29" s="18">
         <v>2</v>
       </c>
       <c r="L29" s="18">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="M29" s="18" t="s">
-        <v>205</v>
+        <v>43</v>
       </c>
       <c r="N29" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" s="18">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P29" s="18" t="s">
         <v>43</v>
@@ -5043,16 +4991,16 @@
         <v>0</v>
       </c>
       <c r="T29" s="18" t="s">
-        <v>206</v>
+        <v>43</v>
       </c>
       <c r="U29" s="18">
-        <v>4000</v>
+        <v>-1</v>
       </c>
       <c r="V29" s="18" t="s">
-        <v>207</v>
+        <v>43</v>
       </c>
       <c r="W29" s="18">
-        <v>1500</v>
+        <v>10000</v>
       </c>
       <c r="X29" s="18" t="s">
         <v>43</v>
@@ -5064,21 +5012,21 @@
         <v>1</v>
       </c>
       <c r="AA29" s="18" t="s">
-        <v>339</v>
+        <v>43</v>
       </c>
       <c r="AB29" s="18">
         <v>1</v>
       </c>
       <c r="AC29" s="18">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A30" s="18">
-        <v>56020001</v>
+        <v>56040001</v>
       </c>
       <c r="B30" s="18">
-        <v>5602</v>
+        <v>5604</v>
       </c>
       <c r="C30" s="18">
         <v>1</v>
@@ -5087,46 +5035,46 @@
         <v>0</v>
       </c>
       <c r="E30" s="18">
-        <v>3560500</v>
+        <v>3560900</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>189</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="J30" s="18" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K30" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L30" s="18">
-        <v>8</v>
+        <v>10000</v>
       </c>
       <c r="M30" s="18" t="s">
-        <v>209</v>
+        <v>43</v>
       </c>
       <c r="N30" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30" s="18">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="P30" s="18" t="s">
-        <v>210</v>
+        <v>43</v>
       </c>
       <c r="Q30" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" s="18">
         <v>0</v>
@@ -5135,7 +5083,7 @@
         <v>43</v>
       </c>
       <c r="U30" s="18">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V30" s="18" t="s">
         <v>43</v>
@@ -5164,10 +5112,10 @@
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A31" s="18">
-        <v>56030001</v>
+        <v>56050001</v>
       </c>
       <c r="B31" s="18">
-        <v>5603</v>
+        <v>5605</v>
       </c>
       <c r="C31" s="18">
         <v>1</v>
@@ -5176,46 +5124,46 @@
         <v>0</v>
       </c>
       <c r="E31" s="18">
-        <v>3560700</v>
+        <v>3561100</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>189</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J31" s="18" t="s">
-        <v>211</v>
+        <v>43</v>
       </c>
       <c r="K31" s="18">
+        <v>0</v>
+      </c>
+      <c r="L31" s="18">
+        <v>0</v>
+      </c>
+      <c r="M31" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="N31" s="18">
         <v>2</v>
       </c>
-      <c r="L31" s="18">
-        <v>3000</v>
-      </c>
-      <c r="M31" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="N31" s="18">
-        <v>0</v>
-      </c>
       <c r="O31" s="18">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P31" s="18" t="s">
-        <v>43</v>
+        <v>234</v>
       </c>
       <c r="Q31" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" s="18">
         <v>0</v>
@@ -5224,7 +5172,7 @@
         <v>43</v>
       </c>
       <c r="U31" s="18">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="18" t="s">
         <v>43</v>
@@ -5253,10 +5201,10 @@
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A32" s="18">
-        <v>56040001</v>
+        <v>56060001</v>
       </c>
       <c r="B32" s="18">
-        <v>5604</v>
+        <v>5606</v>
       </c>
       <c r="C32" s="18">
         <v>1</v>
@@ -5265,37 +5213,37 @@
         <v>0</v>
       </c>
       <c r="E32" s="18">
-        <v>3560900</v>
+        <v>3561400</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>195</v>
+        <v>344</v>
       </c>
       <c r="G32" s="13" t="s">
         <v>189</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>195</v>
+        <v>345</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>237</v>
+        <v>366</v>
       </c>
       <c r="J32" s="18" t="s">
-        <v>212</v>
+        <v>363</v>
       </c>
       <c r="K32" s="18">
         <v>2</v>
       </c>
       <c r="L32" s="18">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="M32" s="18" t="s">
-        <v>43</v>
+        <v>364</v>
       </c>
       <c r="N32" s="18">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="O32" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P32" s="18" t="s">
         <v>43</v>
@@ -5313,7 +5261,7 @@
         <v>43</v>
       </c>
       <c r="U32" s="18">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V32" s="18" t="s">
         <v>43</v>
@@ -5331,199 +5279,199 @@
         <v>1</v>
       </c>
       <c r="AA32" s="18" t="s">
-        <v>43</v>
+        <v>365</v>
       </c>
       <c r="AB32" s="18">
         <v>1</v>
       </c>
       <c r="AC32" s="18">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="33" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A33" s="18">
-        <v>56050001</v>
-      </c>
-      <c r="B33" s="18">
-        <v>5605</v>
-      </c>
-      <c r="C33" s="18">
-        <v>1</v>
-      </c>
-      <c r="D33" s="18">
-        <v>0</v>
-      </c>
-      <c r="E33" s="18">
-        <v>3561100</v>
+      <c r="A33" s="19">
+        <v>57010001</v>
+      </c>
+      <c r="B33" s="19">
+        <v>5701</v>
+      </c>
+      <c r="C33" s="19">
+        <v>1</v>
+      </c>
+      <c r="D33" s="19">
+        <v>0</v>
+      </c>
+      <c r="E33" s="19">
+        <v>3570200</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="J33" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="K33" s="18">
-        <v>0</v>
-      </c>
-      <c r="L33" s="18">
-        <v>0</v>
-      </c>
-      <c r="M33" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="N33" s="18">
+        <v>239</v>
+      </c>
+      <c r="J33" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="K33" s="19">
         <v>2</v>
       </c>
-      <c r="O33" s="18">
+      <c r="L33" s="19">
+        <v>4000</v>
+      </c>
+      <c r="M33" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="N33" s="19">
+        <v>1</v>
+      </c>
+      <c r="O33" s="19">
+        <v>3</v>
+      </c>
+      <c r="P33" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q33" s="19">
+        <v>0</v>
+      </c>
+      <c r="R33" s="19">
+        <v>0</v>
+      </c>
+      <c r="S33" s="19">
+        <v>0</v>
+      </c>
+      <c r="T33" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="U33" s="19">
+        <v>4000</v>
+      </c>
+      <c r="V33" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="W33" s="19">
         <v>10000</v>
       </c>
-      <c r="P33" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q33" s="18">
-        <v>1</v>
-      </c>
-      <c r="R33" s="18">
-        <v>1</v>
-      </c>
-      <c r="S33" s="18">
-        <v>0</v>
-      </c>
-      <c r="T33" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="U33" s="18">
-        <v>0</v>
-      </c>
-      <c r="V33" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="W33" s="18">
+      <c r="X33" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y33" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z33" s="19">
+        <v>1</v>
+      </c>
+      <c r="AA33" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB33" s="19">
+        <v>1</v>
+      </c>
+      <c r="AC33" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A34" s="19">
+        <v>57020001</v>
+      </c>
+      <c r="B34" s="19">
+        <v>5702</v>
+      </c>
+      <c r="C34" s="19">
+        <v>1</v>
+      </c>
+      <c r="D34" s="19">
+        <v>0</v>
+      </c>
+      <c r="E34" s="19">
+        <v>3570500</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="J34" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="K34" s="19">
+        <v>1</v>
+      </c>
+      <c r="L34" s="19">
+        <v>3</v>
+      </c>
+      <c r="M34" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="N34" s="19">
+        <v>1</v>
+      </c>
+      <c r="O34" s="19">
+        <v>1</v>
+      </c>
+      <c r="P34" s="19" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q34" s="19">
+        <v>2</v>
+      </c>
+      <c r="R34" s="19">
+        <v>2500</v>
+      </c>
+      <c r="S34" s="19">
+        <v>0</v>
+      </c>
+      <c r="T34" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="U34" s="19">
+        <v>-1</v>
+      </c>
+      <c r="V34" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="W34" s="19">
         <v>10000</v>
       </c>
-      <c r="X33" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y33" s="18">
-        <v>1</v>
-      </c>
-      <c r="Z33" s="18">
-        <v>1</v>
-      </c>
-      <c r="AA33" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB33" s="18">
-        <v>1</v>
-      </c>
-      <c r="AC33" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A34" s="18">
-        <v>56060001</v>
-      </c>
-      <c r="B34" s="18">
-        <v>5606</v>
-      </c>
-      <c r="C34" s="18">
-        <v>1</v>
-      </c>
-      <c r="D34" s="18">
-        <v>0</v>
-      </c>
-      <c r="E34" s="18">
-        <v>3561400</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>344</v>
-      </c>
-      <c r="G34" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="H34" s="13" t="s">
-        <v>345</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>366</v>
-      </c>
-      <c r="J34" s="18" t="s">
-        <v>363</v>
-      </c>
-      <c r="K34" s="18">
-        <v>2</v>
-      </c>
-      <c r="L34" s="18">
-        <v>3500</v>
-      </c>
-      <c r="M34" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="N34" s="18">
-        <v>35</v>
-      </c>
-      <c r="O34" s="18">
-        <v>1</v>
-      </c>
-      <c r="P34" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q34" s="18">
-        <v>0</v>
-      </c>
-      <c r="R34" s="18">
-        <v>0</v>
-      </c>
-      <c r="S34" s="18">
-        <v>0</v>
-      </c>
-      <c r="T34" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="U34" s="18">
-        <v>0</v>
-      </c>
-      <c r="V34" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="W34" s="18">
-        <v>10000</v>
-      </c>
-      <c r="X34" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y34" s="18">
-        <v>1</v>
-      </c>
-      <c r="Z34" s="18">
-        <v>1</v>
-      </c>
-      <c r="AA34" s="18" t="s">
-        <v>365</v>
-      </c>
-      <c r="AB34" s="18">
-        <v>1</v>
-      </c>
-      <c r="AC34" s="18">
-        <v>1000</v>
+      <c r="X34" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y34" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z34" s="19">
+        <v>1</v>
+      </c>
+      <c r="AA34" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB34" s="19">
+        <v>1</v>
+      </c>
+      <c r="AC34" s="19">
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A35" s="19">
-        <v>57010001</v>
+        <v>57030001</v>
       </c>
       <c r="B35" s="19">
-        <v>5701</v>
+        <v>5703</v>
       </c>
       <c r="C35" s="19">
         <v>1</v>
@@ -5532,55 +5480,55 @@
         <v>0</v>
       </c>
       <c r="E35" s="19">
-        <v>3570200</v>
+        <v>3570700</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G35" s="13" t="s">
         <v>190</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="J35" s="19" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="K35" s="19">
+        <v>1</v>
+      </c>
+      <c r="L35" s="19">
+        <v>8</v>
+      </c>
+      <c r="M35" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="N35" s="19">
         <v>2</v>
       </c>
-      <c r="L35" s="19">
-        <v>4000</v>
-      </c>
-      <c r="M35" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="N35" s="19">
-        <v>1</v>
-      </c>
       <c r="O35" s="19">
-        <v>3</v>
+        <v>10000</v>
       </c>
       <c r="P35" s="19" t="s">
-        <v>43</v>
+        <v>219</v>
       </c>
       <c r="Q35" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" s="19">
         <v>0</v>
       </c>
       <c r="T35" s="19" t="s">
-        <v>367</v>
+        <v>43</v>
       </c>
       <c r="U35" s="19">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="V35" s="19" t="s">
         <v>43</v>
@@ -5609,10 +5557,10 @@
     </row>
     <row r="36" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A36" s="19">
-        <v>57020001</v>
+        <v>57040001</v>
       </c>
       <c r="B36" s="19">
-        <v>5702</v>
+        <v>5704</v>
       </c>
       <c r="C36" s="19">
         <v>1</v>
@@ -5621,46 +5569,46 @@
         <v>0</v>
       </c>
       <c r="E36" s="19">
-        <v>3570500</v>
+        <v>3570900</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>198</v>
+        <v>347</v>
       </c>
       <c r="G36" s="13" t="s">
         <v>190</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>240</v>
+        <v>346</v>
       </c>
       <c r="J36" s="19" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="K36" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L36" s="19">
-        <v>3</v>
+        <v>2000</v>
       </c>
       <c r="M36" s="19" t="s">
-        <v>216</v>
+        <v>325</v>
       </c>
       <c r="N36" s="19">
         <v>1</v>
       </c>
       <c r="O36" s="19">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="P36" s="19" t="s">
-        <v>348</v>
+        <v>43</v>
       </c>
       <c r="Q36" s="19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R36" s="19">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="S36" s="19">
         <v>0</v>
@@ -5698,10 +5646,10 @@
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A37" s="19">
-        <v>57030001</v>
+        <v>57050001</v>
       </c>
       <c r="B37" s="19">
-        <v>5703</v>
+        <v>5705</v>
       </c>
       <c r="C37" s="19">
         <v>1</v>
@@ -5710,46 +5658,46 @@
         <v>0</v>
       </c>
       <c r="E37" s="19">
-        <v>3570700</v>
+        <v>3571100</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>199</v>
+        <v>350</v>
       </c>
       <c r="G37" s="13" t="s">
         <v>190</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>199</v>
+        <v>349</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>235</v>
+        <v>349</v>
       </c>
       <c r="J37" s="19" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K37" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L37" s="19">
-        <v>8</v>
+        <v>10000</v>
       </c>
       <c r="M37" s="19" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="N37" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O37" s="19">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="P37" s="19" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q37" s="19">
         <v>1</v>
       </c>
       <c r="R37" s="19">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="S37" s="19">
         <v>0</v>
@@ -5758,7 +5706,7 @@
         <v>43</v>
       </c>
       <c r="U37" s="19">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V37" s="19" t="s">
         <v>43</v>
@@ -5787,10 +5735,10 @@
     </row>
     <row r="38" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A38" s="19">
-        <v>57040001</v>
+        <v>57060001</v>
       </c>
       <c r="B38" s="19">
-        <v>5704</v>
+        <v>5706</v>
       </c>
       <c r="C38" s="19">
         <v>1</v>
@@ -5799,46 +5747,46 @@
         <v>0</v>
       </c>
       <c r="E38" s="19">
-        <v>3570900</v>
+        <v>3571300</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>347</v>
+        <v>201</v>
       </c>
       <c r="G38" s="13" t="s">
         <v>190</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>346</v>
+        <v>241</v>
       </c>
       <c r="J38" s="19" t="s">
-        <v>220</v>
+        <v>43</v>
       </c>
       <c r="K38" s="19">
+        <v>0</v>
+      </c>
+      <c r="L38" s="19">
+        <v>0</v>
+      </c>
+      <c r="M38" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="N38" s="19">
         <v>2</v>
       </c>
-      <c r="L38" s="19">
-        <v>2000</v>
-      </c>
-      <c r="M38" s="19" t="s">
-        <v>325</v>
-      </c>
-      <c r="N38" s="19">
-        <v>1</v>
-      </c>
       <c r="O38" s="19">
-        <v>20</v>
+        <v>10000</v>
       </c>
       <c r="P38" s="19" t="s">
-        <v>43</v>
+        <v>244</v>
       </c>
       <c r="Q38" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S38" s="19">
         <v>0</v>
@@ -5875,189 +5823,189 @@
       </c>
     </row>
     <row r="39" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A39" s="19">
-        <v>57050001</v>
-      </c>
-      <c r="B39" s="19">
-        <v>5705</v>
-      </c>
-      <c r="C39" s="19">
-        <v>1</v>
-      </c>
-      <c r="D39" s="19">
-        <v>0</v>
-      </c>
-      <c r="E39" s="19">
-        <v>3571100</v>
+      <c r="A39" s="20">
+        <v>58010001</v>
+      </c>
+      <c r="B39" s="20">
+        <v>5801</v>
+      </c>
+      <c r="C39" s="20">
+        <v>1</v>
+      </c>
+      <c r="D39" s="20">
+        <v>0</v>
+      </c>
+      <c r="E39" s="20">
+        <v>3580200</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>350</v>
+        <v>202</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>349</v>
+        <v>202</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>349</v>
-      </c>
-      <c r="J39" s="19" t="s">
-        <v>221</v>
-      </c>
-      <c r="K39" s="19">
+        <v>335</v>
+      </c>
+      <c r="J39" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="K39" s="20">
         <v>2</v>
       </c>
-      <c r="L39" s="19">
+      <c r="L39" s="20">
+        <v>3000</v>
+      </c>
+      <c r="M39" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="N39" s="20">
+        <v>1</v>
+      </c>
+      <c r="O39" s="20">
+        <v>30</v>
+      </c>
+      <c r="P39" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q39" s="20">
+        <v>1</v>
+      </c>
+      <c r="R39" s="20">
+        <v>0</v>
+      </c>
+      <c r="S39" s="20">
+        <v>0</v>
+      </c>
+      <c r="T39" s="20" t="s">
+        <v>368</v>
+      </c>
+      <c r="U39" s="20">
+        <v>4000</v>
+      </c>
+      <c r="V39" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="W39" s="20">
         <v>10000</v>
       </c>
-      <c r="M39" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="N39" s="19">
-        <v>1</v>
-      </c>
-      <c r="O39" s="19">
-        <v>1</v>
-      </c>
-      <c r="P39" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q39" s="19">
-        <v>1</v>
-      </c>
-      <c r="R39" s="19">
-        <v>100</v>
-      </c>
-      <c r="S39" s="19">
-        <v>0</v>
-      </c>
-      <c r="T39" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="U39" s="19">
+      <c r="X39" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="Y39" s="20">
+        <v>1</v>
+      </c>
+      <c r="Z39" s="20">
+        <v>1</v>
+      </c>
+      <c r="AA39" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="AB39" s="20">
+        <v>1</v>
+      </c>
+      <c r="AC39" s="20">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A40" s="20">
+        <v>58020001</v>
+      </c>
+      <c r="B40" s="20">
+        <v>5802</v>
+      </c>
+      <c r="C40" s="20">
+        <v>1</v>
+      </c>
+      <c r="D40" s="20">
+        <v>0</v>
+      </c>
+      <c r="E40" s="20">
+        <v>3580500</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="I40" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="J40" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="K40" s="20">
+        <v>1</v>
+      </c>
+      <c r="L40" s="20">
+        <v>8</v>
+      </c>
+      <c r="M40" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="N40" s="20">
+        <v>2</v>
+      </c>
+      <c r="O40" s="20">
+        <v>10000</v>
+      </c>
+      <c r="P40" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q40" s="20">
+        <v>1</v>
+      </c>
+      <c r="R40" s="20">
+        <v>1</v>
+      </c>
+      <c r="S40" s="20">
+        <v>0</v>
+      </c>
+      <c r="T40" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="U40" s="20">
         <v>-1</v>
       </c>
-      <c r="V39" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="W39" s="19">
+      <c r="V40" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="W40" s="20">
         <v>10000</v>
       </c>
-      <c r="X39" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y39" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z39" s="19">
-        <v>1</v>
-      </c>
-      <c r="AA39" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB39" s="19">
-        <v>1</v>
-      </c>
-      <c r="AC39" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A40" s="19">
-        <v>57060001</v>
-      </c>
-      <c r="B40" s="19">
-        <v>5706</v>
-      </c>
-      <c r="C40" s="19">
-        <v>1</v>
-      </c>
-      <c r="D40" s="19">
-        <v>0</v>
-      </c>
-      <c r="E40" s="19">
-        <v>3571300</v>
-      </c>
-      <c r="F40" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="G40" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="H40" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="I40" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="J40" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="K40" s="19">
-        <v>0</v>
-      </c>
-      <c r="L40" s="19">
-        <v>0</v>
-      </c>
-      <c r="M40" s="19" t="s">
-        <v>243</v>
-      </c>
-      <c r="N40" s="19">
-        <v>2</v>
-      </c>
-      <c r="O40" s="19">
-        <v>10000</v>
-      </c>
-      <c r="P40" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q40" s="19">
-        <v>1</v>
-      </c>
-      <c r="R40" s="19">
-        <v>1</v>
-      </c>
-      <c r="S40" s="19">
-        <v>0</v>
-      </c>
-      <c r="T40" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="U40" s="19">
-        <v>-1</v>
-      </c>
-      <c r="V40" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="W40" s="19">
-        <v>10000</v>
-      </c>
-      <c r="X40" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y40" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z40" s="19">
-        <v>1</v>
-      </c>
-      <c r="AA40" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB40" s="19">
-        <v>1</v>
-      </c>
-      <c r="AC40" s="19">
+      <c r="X40" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y40" s="20">
+        <v>1</v>
+      </c>
+      <c r="Z40" s="20">
+        <v>1</v>
+      </c>
+      <c r="AA40" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB40" s="20">
+        <v>1</v>
+      </c>
+      <c r="AC40" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A41" s="20">
-        <v>58010001</v>
+        <v>58030001</v>
       </c>
       <c r="B41" s="20">
-        <v>5801</v>
+        <v>5803</v>
       </c>
       <c r="C41" s="20">
         <v>1</v>
@@ -6066,43 +6014,43 @@
         <v>0</v>
       </c>
       <c r="E41" s="20">
-        <v>3580200</v>
+        <v>3580700</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>202</v>
+        <v>358</v>
       </c>
       <c r="G41" s="13" t="s">
         <v>191</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>202</v>
+        <v>358</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>335</v>
+        <v>359</v>
       </c>
       <c r="J41" s="20" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="K41" s="20">
+        <v>1</v>
+      </c>
+      <c r="L41" s="20">
+        <v>5</v>
+      </c>
+      <c r="M41" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="N41" s="20">
         <v>2</v>
       </c>
-      <c r="L41" s="20">
-        <v>3000</v>
-      </c>
-      <c r="M41" s="20" t="s">
-        <v>225</v>
-      </c>
-      <c r="N41" s="20">
-        <v>1</v>
-      </c>
       <c r="O41" s="20">
-        <v>30</v>
+        <v>10000</v>
       </c>
       <c r="P41" s="20" t="s">
         <v>43</v>
       </c>
       <c r="Q41" s="20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" s="20">
         <v>0</v>
@@ -6111,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="T41" s="20" t="s">
-        <v>368</v>
+        <v>43</v>
       </c>
       <c r="U41" s="20">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="V41" s="20" t="s">
         <v>43</v>
@@ -6123,7 +6071,7 @@
         <v>10000</v>
       </c>
       <c r="X41" s="20" t="s">
-        <v>226</v>
+        <v>43</v>
       </c>
       <c r="Y41" s="20">
         <v>1</v>
@@ -6132,21 +6080,21 @@
         <v>1</v>
       </c>
       <c r="AA41" s="20" t="s">
-        <v>340</v>
+        <v>43</v>
       </c>
       <c r="AB41" s="20">
         <v>1</v>
       </c>
       <c r="AC41" s="20">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A42" s="20">
-        <v>58020001</v>
+        <v>58040001</v>
       </c>
       <c r="B42" s="20">
-        <v>5802</v>
+        <v>5804</v>
       </c>
       <c r="C42" s="20">
         <v>1</v>
@@ -6155,31 +6103,31 @@
         <v>0</v>
       </c>
       <c r="E42" s="20">
-        <v>3580500</v>
+        <v>3580900</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="G42" s="13" t="s">
         <v>191</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="J42" s="20" t="s">
-        <v>227</v>
+        <v>43</v>
       </c>
       <c r="K42" s="20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" s="20">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M42" s="20" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="N42" s="20">
         <v>2</v>
@@ -6188,7 +6136,7 @@
         <v>10000</v>
       </c>
       <c r="P42" s="20" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q42" s="20">
         <v>1</v>
@@ -6203,7 +6151,7 @@
         <v>43</v>
       </c>
       <c r="U42" s="20">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V42" s="20" t="s">
         <v>43</v>
@@ -6231,50 +6179,50 @@
       </c>
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A43" s="20">
-        <v>58030001</v>
-      </c>
-      <c r="B43" s="20">
-        <v>5803</v>
-      </c>
-      <c r="C43" s="20">
-        <v>1</v>
-      </c>
-      <c r="D43" s="20">
-        <v>0</v>
-      </c>
-      <c r="E43" s="20">
-        <v>3580700</v>
+      <c r="A43" s="23">
+        <v>58050001</v>
+      </c>
+      <c r="B43" s="23">
+        <v>5805</v>
+      </c>
+      <c r="C43" s="23">
+        <v>1</v>
+      </c>
+      <c r="D43" s="23">
+        <v>0</v>
+      </c>
+      <c r="E43" s="23">
+        <v>3581200</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>358</v>
+        <v>188</v>
       </c>
       <c r="G43" s="13" t="s">
         <v>191</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>358</v>
+        <v>188</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="J43" s="20" t="s">
-        <v>230</v>
+        <v>322</v>
       </c>
       <c r="K43" s="20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L43" s="20">
-        <v>5</v>
+        <v>3000</v>
       </c>
       <c r="M43" s="20" t="s">
-        <v>360</v>
+        <v>323</v>
       </c>
       <c r="N43" s="20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O43" s="20">
-        <v>10000</v>
+        <v>30</v>
       </c>
       <c r="P43" s="20" t="s">
         <v>43</v>
@@ -6289,10 +6237,10 @@
         <v>0</v>
       </c>
       <c r="T43" s="20" t="s">
-        <v>43</v>
+        <v>369</v>
       </c>
       <c r="U43" s="20">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="V43" s="20" t="s">
         <v>43</v>
@@ -6301,208 +6249,200 @@
         <v>10000</v>
       </c>
       <c r="X43" s="20" t="s">
-        <v>43</v>
+        <v>324</v>
       </c>
       <c r="Y43" s="20">
         <v>1</v>
       </c>
       <c r="Z43" s="20">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AA43" s="20" t="s">
-        <v>43</v>
+        <v>341</v>
       </c>
       <c r="AB43" s="20">
         <v>1</v>
       </c>
       <c r="AC43" s="20">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="44" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A44" s="20">
-        <v>58040001</v>
-      </c>
-      <c r="B44" s="20">
-        <v>5804</v>
-      </c>
-      <c r="C44" s="20">
-        <v>1</v>
-      </c>
-      <c r="D44" s="20">
-        <v>0</v>
-      </c>
-      <c r="E44" s="20">
-        <v>3580900</v>
+      <c r="A44" s="24">
+        <v>59010001</v>
+      </c>
+      <c r="B44" s="24">
+        <v>5901</v>
+      </c>
+      <c r="C44" s="24">
+        <v>1</v>
+      </c>
+      <c r="D44" s="24">
+        <v>0</v>
+      </c>
+      <c r="E44" s="24">
+        <v>3590200</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>187</v>
+        <v>246</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="H44" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="I44" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="J44" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="K44" s="20">
-        <v>0</v>
-      </c>
-      <c r="L44" s="20">
-        <v>0</v>
-      </c>
-      <c r="M44" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="N44" s="20">
+        <v>245</v>
+      </c>
+      <c r="H44" s="13"/>
+      <c r="I44" s="13"/>
+      <c r="J44" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="K44" s="24">
+        <v>3</v>
+      </c>
+      <c r="L44" s="24">
+        <v>200000</v>
+      </c>
+      <c r="M44" s="24" t="s">
+        <v>280</v>
+      </c>
+      <c r="N44" s="24">
         <v>2</v>
       </c>
-      <c r="O44" s="20">
+      <c r="O44" s="24">
         <v>10000</v>
       </c>
-      <c r="P44" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="Q44" s="20">
-        <v>1</v>
-      </c>
-      <c r="R44" s="20">
-        <v>1</v>
-      </c>
-      <c r="S44" s="20">
-        <v>0</v>
-      </c>
-      <c r="T44" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="U44" s="20">
-        <v>0</v>
-      </c>
-      <c r="V44" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="W44" s="20">
+      <c r="P44" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q44" s="24">
+        <v>1</v>
+      </c>
+      <c r="R44" s="24">
+        <v>1</v>
+      </c>
+      <c r="S44" s="24">
+        <v>0</v>
+      </c>
+      <c r="T44" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="U44" s="24">
+        <v>0</v>
+      </c>
+      <c r="V44" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="W44" s="24">
         <v>10000</v>
       </c>
-      <c r="X44" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y44" s="20">
-        <v>1</v>
-      </c>
-      <c r="Z44" s="20">
-        <v>1</v>
-      </c>
-      <c r="AA44" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB44" s="20">
-        <v>1</v>
-      </c>
-      <c r="AC44" s="20">
+      <c r="X44" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y44" s="24">
+        <v>1</v>
+      </c>
+      <c r="Z44" s="24">
+        <v>1</v>
+      </c>
+      <c r="AA44" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB44" s="24">
+        <v>1</v>
+      </c>
+      <c r="AC44" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A45" s="23">
-        <v>58050001</v>
-      </c>
-      <c r="B45" s="23">
-        <v>5805</v>
-      </c>
-      <c r="C45" s="23">
-        <v>1</v>
-      </c>
-      <c r="D45" s="23">
-        <v>0</v>
-      </c>
-      <c r="E45" s="23">
-        <v>3581200</v>
+      <c r="A45" s="24">
+        <v>59020001</v>
+      </c>
+      <c r="B45" s="24">
+        <v>5902</v>
+      </c>
+      <c r="C45" s="24">
+        <v>1</v>
+      </c>
+      <c r="D45" s="24">
+        <v>0</v>
+      </c>
+      <c r="E45" s="24">
+        <v>3590400</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>188</v>
+        <v>247</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="H45" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="I45" s="13" t="s">
-        <v>336</v>
-      </c>
-      <c r="J45" s="20" t="s">
-        <v>322</v>
-      </c>
-      <c r="K45" s="20">
-        <v>2</v>
-      </c>
-      <c r="L45" s="20">
-        <v>3000</v>
-      </c>
-      <c r="M45" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="N45" s="20">
-        <v>0</v>
-      </c>
-      <c r="O45" s="20">
-        <v>30</v>
-      </c>
-      <c r="P45" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q45" s="20">
-        <v>0</v>
-      </c>
-      <c r="R45" s="20">
-        <v>0</v>
-      </c>
-      <c r="S45" s="20">
-        <v>0</v>
-      </c>
-      <c r="T45" s="20" t="s">
-        <v>369</v>
-      </c>
-      <c r="U45" s="20">
-        <v>4000</v>
-      </c>
-      <c r="V45" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="W45" s="20">
+        <v>245</v>
+      </c>
+      <c r="H45" s="13"/>
+      <c r="I45" s="13"/>
+      <c r="J45" s="24" t="s">
+        <v>282</v>
+      </c>
+      <c r="K45" s="24">
+        <v>3</v>
+      </c>
+      <c r="L45" s="24">
+        <v>200000</v>
+      </c>
+      <c r="M45" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="N45" s="24">
+        <v>0</v>
+      </c>
+      <c r="O45" s="24">
+        <v>0</v>
+      </c>
+      <c r="P45" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q45" s="24">
+        <v>0</v>
+      </c>
+      <c r="R45" s="24">
+        <v>0</v>
+      </c>
+      <c r="S45" s="24">
+        <v>59030001</v>
+      </c>
+      <c r="T45" s="24" t="s">
+        <v>370</v>
+      </c>
+      <c r="U45" s="24">
+        <v>-1</v>
+      </c>
+      <c r="V45" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="W45" s="24">
         <v>10000</v>
       </c>
-      <c r="X45" s="20" t="s">
-        <v>324</v>
-      </c>
-      <c r="Y45" s="20">
-        <v>1</v>
-      </c>
-      <c r="Z45" s="20">
-        <v>10</v>
-      </c>
-      <c r="AA45" s="20" t="s">
-        <v>341</v>
-      </c>
-      <c r="AB45" s="20">
-        <v>1</v>
-      </c>
-      <c r="AC45" s="20">
-        <v>1000</v>
+      <c r="X45" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y45" s="24">
+        <v>1</v>
+      </c>
+      <c r="Z45" s="24">
+        <v>1</v>
+      </c>
+      <c r="AA45" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB45" s="24">
+        <v>1</v>
+      </c>
+      <c r="AC45" s="24">
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A46" s="24">
-        <v>59010001</v>
+        <v>59030001</v>
       </c>
       <c r="B46" s="24">
-        <v>5901</v>
+        <v>5903</v>
       </c>
       <c r="C46" s="24">
         <v>1</v>
@@ -6511,10 +6451,10 @@
         <v>0</v>
       </c>
       <c r="E46" s="24">
-        <v>3590200</v>
+        <v>3590600</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G46" s="13" t="s">
         <v>245</v>
@@ -6522,16 +6462,16 @@
       <c r="H46" s="13"/>
       <c r="I46" s="13"/>
       <c r="J46" s="24" t="s">
-        <v>279</v>
+        <v>43</v>
       </c>
       <c r="K46" s="24">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L46" s="24">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="M46" s="24" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="N46" s="24">
         <v>2</v>
@@ -6540,7 +6480,7 @@
         <v>10000</v>
       </c>
       <c r="P46" s="24" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q46" s="24">
         <v>1</v>
@@ -6549,7 +6489,7 @@
         <v>1</v>
       </c>
       <c r="S46" s="24">
-        <v>0</v>
+        <v>59200001</v>
       </c>
       <c r="T46" s="24" t="s">
         <v>43</v>
@@ -6584,10 +6524,10 @@
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A47" s="24">
-        <v>59020001</v>
+        <v>59040001</v>
       </c>
       <c r="B47" s="24">
-        <v>5902</v>
+        <v>5904</v>
       </c>
       <c r="C47" s="24">
         <v>1</v>
@@ -6596,10 +6536,10 @@
         <v>0</v>
       </c>
       <c r="E47" s="24">
-        <v>3590400</v>
+        <v>3590800</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G47" s="13" t="s">
         <v>245</v>
@@ -6607,37 +6547,37 @@
       <c r="H47" s="13"/>
       <c r="I47" s="13"/>
       <c r="J47" s="24" t="s">
-        <v>282</v>
+        <v>43</v>
       </c>
       <c r="K47" s="24">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L47" s="24">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="M47" s="24" t="s">
-        <v>43</v>
+        <v>285</v>
       </c>
       <c r="N47" s="24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O47" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P47" s="24" t="s">
-        <v>43</v>
+        <v>286</v>
       </c>
       <c r="Q47" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S47" s="24">
-        <v>59030001</v>
+        <v>59090001</v>
       </c>
       <c r="T47" s="24" t="s">
-        <v>370</v>
+        <v>43</v>
       </c>
       <c r="U47" s="24">
         <v>-1</v>
@@ -6669,10 +6609,10 @@
     </row>
     <row r="48" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A48" s="24">
-        <v>59030001</v>
+        <v>59050001</v>
       </c>
       <c r="B48" s="24">
-        <v>5903</v>
+        <v>5905</v>
       </c>
       <c r="C48" s="24">
         <v>1</v>
@@ -6681,10 +6621,10 @@
         <v>0</v>
       </c>
       <c r="E48" s="24">
-        <v>3590600</v>
+        <v>3591000</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G48" s="13" t="s">
         <v>245</v>
@@ -6692,40 +6632,40 @@
       <c r="H48" s="13"/>
       <c r="I48" s="13"/>
       <c r="J48" s="24" t="s">
-        <v>43</v>
+        <v>287</v>
       </c>
       <c r="K48" s="24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" s="24">
         <v>0</v>
       </c>
       <c r="M48" s="24" t="s">
-        <v>283</v>
+        <v>342</v>
       </c>
       <c r="N48" s="24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O48" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="P48" s="24" t="s">
-        <v>284</v>
+        <v>343</v>
       </c>
       <c r="Q48" s="24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R48" s="24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S48" s="24">
-        <v>59200001</v>
+        <v>0</v>
       </c>
       <c r="T48" s="24" t="s">
         <v>43</v>
       </c>
       <c r="U48" s="24">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V48" s="24" t="s">
         <v>43</v>
@@ -6754,10 +6694,10 @@
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A49" s="24">
-        <v>59040001</v>
+        <v>59060001</v>
       </c>
       <c r="B49" s="24">
-        <v>5904</v>
+        <v>5906</v>
       </c>
       <c r="C49" s="24">
         <v>1</v>
@@ -6766,10 +6706,10 @@
         <v>0</v>
       </c>
       <c r="E49" s="24">
-        <v>3590800</v>
+        <v>3591200</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G49" s="13" t="s">
         <v>245</v>
@@ -6777,16 +6717,16 @@
       <c r="H49" s="13"/>
       <c r="I49" s="13"/>
       <c r="J49" s="24" t="s">
-        <v>43</v>
+        <v>288</v>
       </c>
       <c r="K49" s="24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L49" s="24">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="M49" s="24" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="N49" s="24">
         <v>2</v>
@@ -6795,7 +6735,7 @@
         <v>10000</v>
       </c>
       <c r="P49" s="24" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q49" s="24">
         <v>1</v>
@@ -6804,7 +6744,7 @@
         <v>1</v>
       </c>
       <c r="S49" s="24">
-        <v>59090001</v>
+        <v>0</v>
       </c>
       <c r="T49" s="24" t="s">
         <v>43</v>
@@ -6839,10 +6779,10 @@
     </row>
     <row r="50" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A50" s="24">
-        <v>59050001</v>
+        <v>59070001</v>
       </c>
       <c r="B50" s="24">
-        <v>5905</v>
+        <v>5907</v>
       </c>
       <c r="C50" s="24">
         <v>1</v>
@@ -6851,10 +6791,10 @@
         <v>0</v>
       </c>
       <c r="E50" s="24">
-        <v>3591000</v>
+        <v>3591400</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G50" s="13" t="s">
         <v>245</v>
@@ -6862,34 +6802,34 @@
       <c r="H50" s="13"/>
       <c r="I50" s="13"/>
       <c r="J50" s="24" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="K50" s="24">
+        <v>3</v>
+      </c>
+      <c r="L50" s="24">
+        <v>500000</v>
+      </c>
+      <c r="M50" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="N50" s="24">
         <v>2</v>
       </c>
-      <c r="L50" s="24">
-        <v>0</v>
-      </c>
-      <c r="M50" s="24" t="s">
-        <v>342</v>
-      </c>
-      <c r="N50" s="24">
-        <v>1</v>
-      </c>
       <c r="O50" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P50" s="24" t="s">
-        <v>343</v>
+        <v>293</v>
       </c>
       <c r="Q50" s="24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R50" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50" s="24">
-        <v>0</v>
+        <v>59200002</v>
       </c>
       <c r="T50" s="24" t="s">
         <v>43</v>
@@ -6924,10 +6864,10 @@
     </row>
     <row r="51" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A51" s="24">
-        <v>59060001</v>
+        <v>59080001</v>
       </c>
       <c r="B51" s="24">
-        <v>5906</v>
+        <v>5908</v>
       </c>
       <c r="C51" s="24">
         <v>1</v>
@@ -6936,10 +6876,10 @@
         <v>0</v>
       </c>
       <c r="E51" s="24">
-        <v>3591200</v>
+        <v>3591600</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G51" s="13" t="s">
         <v>245</v>
@@ -6947,16 +6887,16 @@
       <c r="H51" s="13"/>
       <c r="I51" s="13"/>
       <c r="J51" s="24" t="s">
-        <v>288</v>
+        <v>43</v>
       </c>
       <c r="K51" s="24">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L51" s="24">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="M51" s="24" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="N51" s="24">
         <v>2</v>
@@ -6965,7 +6905,7 @@
         <v>10000</v>
       </c>
       <c r="P51" s="24" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="Q51" s="24">
         <v>1</v>
@@ -6974,13 +6914,13 @@
         <v>1</v>
       </c>
       <c r="S51" s="24">
-        <v>0</v>
+        <v>90000001</v>
       </c>
       <c r="T51" s="24" t="s">
         <v>43</v>
       </c>
       <c r="U51" s="24">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V51" s="24" t="s">
         <v>43</v>
@@ -7009,10 +6949,10 @@
     </row>
     <row r="52" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A52" s="24">
-        <v>59070001</v>
+        <v>59090001</v>
       </c>
       <c r="B52" s="24">
-        <v>5907</v>
+        <v>5909</v>
       </c>
       <c r="C52" s="24">
         <v>1</v>
@@ -7021,10 +6961,10 @@
         <v>0</v>
       </c>
       <c r="E52" s="24">
-        <v>3591400</v>
+        <v>3591900</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>252</v>
+        <v>361</v>
       </c>
       <c r="G52" s="13" t="s">
         <v>245</v>
@@ -7032,34 +6972,34 @@
       <c r="H52" s="13"/>
       <c r="I52" s="13"/>
       <c r="J52" s="24" t="s">
-        <v>291</v>
+        <v>43</v>
       </c>
       <c r="K52" s="24">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L52" s="24">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="M52" s="24" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="N52" s="24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O52" s="24">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="P52" s="24" t="s">
-        <v>293</v>
+        <v>43</v>
       </c>
       <c r="Q52" s="24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R52" s="24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S52" s="24">
-        <v>59200002</v>
+        <v>0</v>
       </c>
       <c r="T52" s="24" t="s">
         <v>43</v>
@@ -7083,21 +7023,21 @@
         <v>1</v>
       </c>
       <c r="AA52" s="24" t="s">
-        <v>43</v>
+        <v>362</v>
       </c>
       <c r="AB52" s="24">
         <v>1</v>
       </c>
       <c r="AC52" s="24">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A53" s="24">
-        <v>59080001</v>
+        <v>59100001</v>
       </c>
       <c r="B53" s="24">
-        <v>5908</v>
+        <v>5910</v>
       </c>
       <c r="C53" s="24">
         <v>1</v>
@@ -7106,10 +7046,10 @@
         <v>0</v>
       </c>
       <c r="E53" s="24">
-        <v>3591600</v>
+        <v>3541800</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>253</v>
+        <v>315</v>
       </c>
       <c r="G53" s="13" t="s">
         <v>245</v>
@@ -7120,37 +7060,37 @@
         <v>43</v>
       </c>
       <c r="K53" s="24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L53" s="24">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="M53" s="24" t="s">
-        <v>294</v>
+        <v>43</v>
       </c>
       <c r="N53" s="24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O53" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="P53" s="24" t="s">
-        <v>295</v>
+        <v>43</v>
       </c>
       <c r="Q53" s="24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R53" s="24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S53" s="24">
-        <v>90000001</v>
+        <v>0</v>
       </c>
       <c r="T53" s="24" t="s">
         <v>43</v>
       </c>
       <c r="U53" s="24">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V53" s="24" t="s">
         <v>43</v>
@@ -7179,10 +7119,10 @@
     </row>
     <row r="54" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A54" s="24">
-        <v>59090001</v>
+        <v>59110001</v>
       </c>
       <c r="B54" s="24">
-        <v>5909</v>
+        <v>5911</v>
       </c>
       <c r="C54" s="24">
         <v>1</v>
@@ -7191,10 +7131,10 @@
         <v>0</v>
       </c>
       <c r="E54" s="24">
-        <v>3591900</v>
+        <v>3541800</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="G54" s="13" t="s">
         <v>245</v>
@@ -7205,19 +7145,19 @@
         <v>43</v>
       </c>
       <c r="K54" s="24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L54" s="24">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="M54" s="24" t="s">
-        <v>296</v>
+        <v>43</v>
       </c>
       <c r="N54" s="24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O54" s="24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P54" s="24" t="s">
         <v>43</v>
@@ -7253,21 +7193,21 @@
         <v>1</v>
       </c>
       <c r="AA54" s="24" t="s">
-        <v>362</v>
+        <v>43</v>
       </c>
       <c r="AB54" s="24">
         <v>1</v>
       </c>
       <c r="AC54" s="24">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A55" s="24">
-        <v>59100001</v>
+      <c r="A55" s="25">
+        <v>59120001</v>
       </c>
       <c r="B55" s="24">
-        <v>5910</v>
+        <v>5912</v>
       </c>
       <c r="C55" s="24">
         <v>1</v>
@@ -7276,10 +7216,10 @@
         <v>0</v>
       </c>
       <c r="E55" s="24">
-        <v>3541800</v>
+        <v>3592100</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>315</v>
+        <v>373</v>
       </c>
       <c r="G55" s="13" t="s">
         <v>245</v>
@@ -7287,13 +7227,13 @@
       <c r="H55" s="13"/>
       <c r="I55" s="13"/>
       <c r="J55" s="24" t="s">
-        <v>43</v>
+        <v>372</v>
       </c>
       <c r="K55" s="24">
         <v>2</v>
       </c>
       <c r="L55" s="24">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="M55" s="24" t="s">
         <v>43</v>
@@ -7348,181 +7288,181 @@
       </c>
     </row>
     <row r="56" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A56" s="24">
-        <v>59110001</v>
-      </c>
-      <c r="B56" s="24">
-        <v>5911</v>
-      </c>
-      <c r="C56" s="24">
-        <v>1</v>
-      </c>
-      <c r="D56" s="24">
-        <v>0</v>
-      </c>
-      <c r="E56" s="24">
-        <v>3541800</v>
+      <c r="A56" s="21">
+        <v>60010001</v>
+      </c>
+      <c r="B56" s="21">
+        <v>6001</v>
+      </c>
+      <c r="C56" s="21">
+        <v>1</v>
+      </c>
+      <c r="D56" s="21">
+        <v>0</v>
+      </c>
+      <c r="E56" s="21">
+        <v>3600200</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>316</v>
+        <v>257</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="H56" s="13"/>
       <c r="I56" s="13"/>
-      <c r="J56" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="K56" s="24">
+      <c r="J56" s="21" t="s">
+        <v>261</v>
+      </c>
+      <c r="K56" s="21">
+        <v>1</v>
+      </c>
+      <c r="L56" s="21">
+        <v>8</v>
+      </c>
+      <c r="M56" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="N56" s="21">
         <v>2</v>
       </c>
-      <c r="L56" s="24">
-        <v>5000</v>
-      </c>
-      <c r="M56" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="N56" s="24">
-        <v>0</v>
-      </c>
-      <c r="O56" s="24">
-        <v>0</v>
-      </c>
-      <c r="P56" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q56" s="24">
-        <v>0</v>
-      </c>
-      <c r="R56" s="24">
-        <v>0</v>
-      </c>
-      <c r="S56" s="24">
-        <v>0</v>
-      </c>
-      <c r="T56" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="U56" s="24">
-        <v>-1</v>
-      </c>
-      <c r="V56" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="W56" s="24">
+      <c r="O56" s="21">
         <v>10000</v>
       </c>
-      <c r="X56" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y56" s="24">
-        <v>1</v>
-      </c>
-      <c r="Z56" s="24">
-        <v>1</v>
-      </c>
-      <c r="AA56" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB56" s="24">
-        <v>1</v>
-      </c>
-      <c r="AC56" s="24">
+      <c r="P56" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q56" s="21">
+        <v>1</v>
+      </c>
+      <c r="R56" s="21">
+        <v>1</v>
+      </c>
+      <c r="S56" s="21">
+        <v>0</v>
+      </c>
+      <c r="T56" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="U56" s="21">
+        <v>0</v>
+      </c>
+      <c r="V56" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W56" s="21">
+        <v>10000</v>
+      </c>
+      <c r="X56" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y56" s="21">
+        <v>1</v>
+      </c>
+      <c r="Z56" s="21">
+        <v>1</v>
+      </c>
+      <c r="AA56" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB56" s="21">
+        <v>1</v>
+      </c>
+      <c r="AC56" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A57" s="25">
-        <v>59120001</v>
-      </c>
-      <c r="B57" s="24">
-        <v>5912</v>
-      </c>
-      <c r="C57" s="24">
-        <v>1</v>
-      </c>
-      <c r="D57" s="24">
-        <v>0</v>
-      </c>
-      <c r="E57" s="24">
-        <v>3592100</v>
+      <c r="A57" s="21">
+        <v>60020001</v>
+      </c>
+      <c r="B57" s="21">
+        <v>6002</v>
+      </c>
+      <c r="C57" s="21">
+        <v>1</v>
+      </c>
+      <c r="D57" s="21">
+        <v>0</v>
+      </c>
+      <c r="E57" s="21">
+        <v>3600400</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>373</v>
+        <v>258</v>
       </c>
       <c r="G57" s="13" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="H57" s="13"/>
       <c r="I57" s="13"/>
-      <c r="J57" s="24" t="s">
-        <v>372</v>
-      </c>
-      <c r="K57" s="24">
+      <c r="J57" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="K57" s="21">
+        <v>1</v>
+      </c>
+      <c r="L57" s="21">
+        <v>1</v>
+      </c>
+      <c r="M57" s="21" t="s">
+        <v>265</v>
+      </c>
+      <c r="N57" s="21">
         <v>2</v>
       </c>
-      <c r="L57" s="24">
-        <v>0</v>
-      </c>
-      <c r="M57" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="N57" s="24">
-        <v>0</v>
-      </c>
-      <c r="O57" s="24">
-        <v>0</v>
-      </c>
-      <c r="P57" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q57" s="24">
-        <v>0</v>
-      </c>
-      <c r="R57" s="24">
-        <v>0</v>
-      </c>
-      <c r="S57" s="24">
-        <v>0</v>
-      </c>
-      <c r="T57" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="U57" s="24">
+      <c r="O57" s="21">
+        <v>15000</v>
+      </c>
+      <c r="P57" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q57" s="21">
+        <v>0</v>
+      </c>
+      <c r="R57" s="21">
+        <v>0</v>
+      </c>
+      <c r="S57" s="21">
+        <v>0</v>
+      </c>
+      <c r="T57" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="U57" s="21">
         <v>-1</v>
       </c>
-      <c r="V57" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="W57" s="24">
+      <c r="V57" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W57" s="21">
         <v>10000</v>
       </c>
-      <c r="X57" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y57" s="24">
-        <v>1</v>
-      </c>
-      <c r="Z57" s="24">
-        <v>1</v>
-      </c>
-      <c r="AA57" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB57" s="24">
-        <v>1</v>
-      </c>
-      <c r="AC57" s="24">
+      <c r="X57" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y57" s="21">
+        <v>1</v>
+      </c>
+      <c r="Z57" s="21">
+        <v>1</v>
+      </c>
+      <c r="AA57" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB57" s="21">
+        <v>1</v>
+      </c>
+      <c r="AC57" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A58" s="21">
-        <v>60010001</v>
+        <v>60030001</v>
       </c>
       <c r="B58" s="21">
-        <v>6001</v>
+        <v>6003</v>
       </c>
       <c r="C58" s="21">
         <v>1</v>
@@ -7531,10 +7471,10 @@
         <v>0</v>
       </c>
       <c r="E58" s="21">
-        <v>3600200</v>
+        <v>3600700</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="G58" s="13" t="s">
         <v>254</v>
@@ -7542,7 +7482,7 @@
       <c r="H58" s="13"/>
       <c r="I58" s="13"/>
       <c r="J58" s="21" t="s">
-        <v>261</v>
+        <v>297</v>
       </c>
       <c r="K58" s="21">
         <v>1</v>
@@ -7551,7 +7491,7 @@
         <v>8</v>
       </c>
       <c r="M58" s="21" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="N58" s="21">
         <v>2</v>
@@ -7560,7 +7500,7 @@
         <v>10000</v>
       </c>
       <c r="P58" s="21" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q58" s="21">
         <v>1</v>
@@ -7604,10 +7544,10 @@
     </row>
     <row r="59" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A59" s="21">
-        <v>60020001</v>
+        <v>60040001</v>
       </c>
       <c r="B59" s="21">
-        <v>6002</v>
+        <v>6004</v>
       </c>
       <c r="C59" s="21">
         <v>1</v>
@@ -7616,10 +7556,10 @@
         <v>0</v>
       </c>
       <c r="E59" s="21">
-        <v>3600400</v>
+        <v>3601000</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="G59" s="13" t="s">
         <v>254</v>
@@ -7627,31 +7567,31 @@
       <c r="H59" s="13"/>
       <c r="I59" s="13"/>
       <c r="J59" s="21" t="s">
-        <v>264</v>
+        <v>43</v>
       </c>
       <c r="K59" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59" s="21" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="N59" s="21">
         <v>2</v>
       </c>
       <c r="O59" s="21">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="P59" s="21" t="s">
-        <v>43</v>
+        <v>269</v>
       </c>
       <c r="Q59" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R59" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S59" s="21">
         <v>0</v>
@@ -7660,7 +7600,7 @@
         <v>43</v>
       </c>
       <c r="U59" s="21">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V59" s="21" t="s">
         <v>43</v>
@@ -7689,10 +7629,10 @@
     </row>
     <row r="60" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A60" s="21">
-        <v>60030001</v>
+        <v>60050001</v>
       </c>
       <c r="B60" s="21">
-        <v>6003</v>
+        <v>6005</v>
       </c>
       <c r="C60" s="21">
         <v>1</v>
@@ -7701,10 +7641,10 @@
         <v>0</v>
       </c>
       <c r="E60" s="21">
-        <v>3600700</v>
+        <v>3541600</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>259</v>
+        <v>317</v>
       </c>
       <c r="G60" s="13" t="s">
         <v>254</v>
@@ -7712,31 +7652,31 @@
       <c r="H60" s="13"/>
       <c r="I60" s="13"/>
       <c r="J60" s="21" t="s">
-        <v>297</v>
+        <v>119</v>
       </c>
       <c r="K60" s="21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L60" s="21">
-        <v>8</v>
+        <v>-2000</v>
       </c>
       <c r="M60" s="21" t="s">
-        <v>266</v>
+        <v>43</v>
       </c>
       <c r="N60" s="21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O60" s="21">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="P60" s="21" t="s">
-        <v>267</v>
+        <v>43</v>
       </c>
       <c r="Q60" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R60" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S60" s="21">
         <v>0</v>
@@ -7745,7 +7685,7 @@
         <v>43</v>
       </c>
       <c r="U60" s="21">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V60" s="21" t="s">
         <v>43</v>
@@ -7774,10 +7714,10 @@
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A61" s="21">
-        <v>60040001</v>
+        <v>60060001</v>
       </c>
       <c r="B61" s="21">
-        <v>6004</v>
+        <v>6006</v>
       </c>
       <c r="C61" s="21">
         <v>1</v>
@@ -7786,10 +7726,10 @@
         <v>0</v>
       </c>
       <c r="E61" s="21">
-        <v>3601000</v>
+        <v>3541800</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>260</v>
+        <v>318</v>
       </c>
       <c r="G61" s="13" t="s">
         <v>254</v>
@@ -7797,31 +7737,31 @@
       <c r="H61" s="13"/>
       <c r="I61" s="13"/>
       <c r="J61" s="21" t="s">
-        <v>43</v>
+        <v>121</v>
       </c>
       <c r="K61" s="21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L61" s="21">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="M61" s="21" t="s">
-        <v>268</v>
+        <v>43</v>
       </c>
       <c r="N61" s="21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O61" s="21">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="P61" s="21" t="s">
-        <v>269</v>
+        <v>43</v>
       </c>
       <c r="Q61" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R61" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61" s="21">
         <v>0</v>
@@ -7830,7 +7770,7 @@
         <v>43</v>
       </c>
       <c r="U61" s="21">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V61" s="21" t="s">
         <v>43</v>
@@ -7859,10 +7799,10 @@
     </row>
     <row r="62" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A62" s="21">
-        <v>60050001</v>
+        <v>60070001</v>
       </c>
       <c r="B62" s="21">
-        <v>6005</v>
+        <v>6007</v>
       </c>
       <c r="C62" s="21">
         <v>1</v>
@@ -7871,10 +7811,10 @@
         <v>0</v>
       </c>
       <c r="E62" s="21">
-        <v>3541600</v>
+        <v>3601300</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G62" s="13" t="s">
         <v>254</v>
@@ -7882,28 +7822,28 @@
       <c r="H62" s="13"/>
       <c r="I62" s="13"/>
       <c r="J62" s="21" t="s">
-        <v>119</v>
+        <v>270</v>
       </c>
       <c r="K62" s="21">
         <v>2</v>
       </c>
       <c r="L62" s="21">
-        <v>-2000</v>
+        <v>10000</v>
       </c>
       <c r="M62" s="21" t="s">
-        <v>43</v>
+        <v>271</v>
       </c>
       <c r="N62" s="21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O62" s="21">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="P62" s="21" t="s">
-        <v>43</v>
+        <v>272</v>
       </c>
       <c r="Q62" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R62" s="21">
         <v>0</v>
@@ -7943,181 +7883,181 @@
       </c>
     </row>
     <row r="63" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A63" s="21">
-        <v>60060001</v>
-      </c>
-      <c r="B63" s="21">
-        <v>6006</v>
-      </c>
-      <c r="C63" s="21">
-        <v>1</v>
-      </c>
-      <c r="D63" s="21">
-        <v>0</v>
-      </c>
-      <c r="E63" s="21">
-        <v>3541800</v>
+      <c r="A63" s="22">
+        <v>61010001</v>
+      </c>
+      <c r="B63" s="22">
+        <v>6101</v>
+      </c>
+      <c r="C63" s="22">
+        <v>1</v>
+      </c>
+      <c r="D63" s="22">
+        <v>0</v>
+      </c>
+      <c r="E63" s="22">
+        <v>3610300</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>318</v>
+        <v>298</v>
       </c>
       <c r="G63" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H63" s="13"/>
       <c r="I63" s="13"/>
-      <c r="J63" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="K63" s="21">
+      <c r="J63" s="22" t="s">
+        <v>273</v>
+      </c>
+      <c r="K63" s="22">
+        <v>1</v>
+      </c>
+      <c r="L63" s="22">
+        <v>8</v>
+      </c>
+      <c r="M63" s="22" t="s">
+        <v>274</v>
+      </c>
+      <c r="N63" s="22">
         <v>2</v>
       </c>
-      <c r="L63" s="21">
-        <v>2500</v>
-      </c>
-      <c r="M63" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="N63" s="21">
-        <v>0</v>
-      </c>
-      <c r="O63" s="21">
-        <v>0</v>
-      </c>
-      <c r="P63" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q63" s="21">
-        <v>0</v>
-      </c>
-      <c r="R63" s="21">
-        <v>0</v>
-      </c>
-      <c r="S63" s="21">
-        <v>0</v>
-      </c>
-      <c r="T63" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="U63" s="21">
-        <v>-1</v>
-      </c>
-      <c r="V63" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="W63" s="21">
+      <c r="O63" s="22">
         <v>10000</v>
       </c>
-      <c r="X63" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y63" s="21">
-        <v>1</v>
-      </c>
-      <c r="Z63" s="21">
-        <v>1</v>
-      </c>
-      <c r="AA63" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB63" s="21">
-        <v>1</v>
-      </c>
-      <c r="AC63" s="21">
+      <c r="P63" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q63" s="22">
+        <v>1</v>
+      </c>
+      <c r="R63" s="22">
+        <v>1</v>
+      </c>
+      <c r="S63" s="22">
+        <v>0</v>
+      </c>
+      <c r="T63" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="U63" s="22">
+        <v>0</v>
+      </c>
+      <c r="V63" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="W63" s="22">
+        <v>10000</v>
+      </c>
+      <c r="X63" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y63" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z63" s="22">
+        <v>1</v>
+      </c>
+      <c r="AA63" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB63" s="22">
+        <v>1</v>
+      </c>
+      <c r="AC63" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A64" s="21">
-        <v>60070001</v>
-      </c>
-      <c r="B64" s="21">
-        <v>6007</v>
-      </c>
-      <c r="C64" s="21">
-        <v>1</v>
-      </c>
-      <c r="D64" s="21">
-        <v>0</v>
-      </c>
-      <c r="E64" s="21">
-        <v>3601300</v>
+      <c r="A64" s="22">
+        <v>61020001</v>
+      </c>
+      <c r="B64" s="22">
+        <v>6102</v>
+      </c>
+      <c r="C64" s="22">
+        <v>1</v>
+      </c>
+      <c r="D64" s="22">
+        <v>0</v>
+      </c>
+      <c r="E64" s="22">
+        <v>3610500</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="G64" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H64" s="13"/>
       <c r="I64" s="13"/>
-      <c r="J64" s="21" t="s">
-        <v>270</v>
-      </c>
-      <c r="K64" s="21">
+      <c r="J64" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="K64" s="22">
         <v>2</v>
       </c>
-      <c r="L64" s="21">
+      <c r="L64" s="22">
         <v>10000</v>
       </c>
-      <c r="M64" s="21" t="s">
-        <v>271</v>
-      </c>
-      <c r="N64" s="21">
-        <v>2</v>
-      </c>
-      <c r="O64" s="21">
-        <v>2000</v>
-      </c>
-      <c r="P64" s="21" t="s">
-        <v>272</v>
-      </c>
-      <c r="Q64" s="21">
-        <v>1</v>
-      </c>
-      <c r="R64" s="21">
-        <v>0</v>
-      </c>
-      <c r="S64" s="21">
-        <v>0</v>
-      </c>
-      <c r="T64" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="U64" s="21">
+      <c r="M64" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="N64" s="22">
+        <v>0</v>
+      </c>
+      <c r="O64" s="22">
+        <v>0</v>
+      </c>
+      <c r="P64" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q64" s="22">
+        <v>0</v>
+      </c>
+      <c r="R64" s="22">
+        <v>0</v>
+      </c>
+      <c r="S64" s="22">
+        <v>0</v>
+      </c>
+      <c r="T64" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="U64" s="22">
         <v>-1</v>
       </c>
-      <c r="V64" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="W64" s="21">
+      <c r="V64" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="W64" s="22">
         <v>10000</v>
       </c>
-      <c r="X64" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y64" s="21">
-        <v>1</v>
-      </c>
-      <c r="Z64" s="21">
-        <v>1</v>
-      </c>
-      <c r="AA64" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB64" s="21">
-        <v>1</v>
-      </c>
-      <c r="AC64" s="21">
+      <c r="X64" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y64" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z64" s="22">
+        <v>1</v>
+      </c>
+      <c r="AA64" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB64" s="22">
+        <v>1</v>
+      </c>
+      <c r="AC64" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A65" s="22">
-        <v>61010001</v>
+        <v>61030001</v>
       </c>
       <c r="B65" s="22">
-        <v>6101</v>
+        <v>6103</v>
       </c>
       <c r="C65" s="22">
         <v>1</v>
@@ -8126,10 +8066,10 @@
         <v>0</v>
       </c>
       <c r="E65" s="22">
-        <v>3610300</v>
+        <v>3610700</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="G65" s="13" t="s">
         <v>255</v>
@@ -8137,16 +8077,16 @@
       <c r="H65" s="13"/>
       <c r="I65" s="13"/>
       <c r="J65" s="22" t="s">
-        <v>273</v>
+        <v>43</v>
       </c>
       <c r="K65" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" s="22">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M65" s="22" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="N65" s="22">
         <v>2</v>
@@ -8155,7 +8095,7 @@
         <v>10000</v>
       </c>
       <c r="P65" s="22" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q65" s="22">
         <v>1</v>
@@ -8199,10 +8139,10 @@
     </row>
     <row r="66" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A66" s="22">
-        <v>61020001</v>
+        <v>61040001</v>
       </c>
       <c r="B66" s="22">
-        <v>6102</v>
+        <v>6104</v>
       </c>
       <c r="C66" s="22">
         <v>1</v>
@@ -8211,10 +8151,10 @@
         <v>0</v>
       </c>
       <c r="E66" s="22">
-        <v>3610500</v>
+        <v>3541400</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>299</v>
+        <v>256</v>
       </c>
       <c r="G66" s="13" t="s">
         <v>255</v>
@@ -8222,13 +8162,13 @@
       <c r="H66" s="13"/>
       <c r="I66" s="13"/>
       <c r="J66" s="22" t="s">
-        <v>276</v>
+        <v>118</v>
       </c>
       <c r="K66" s="22">
         <v>2</v>
       </c>
       <c r="L66" s="22">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="M66" s="22" t="s">
         <v>43</v>
@@ -8284,10 +8224,10 @@
     </row>
     <row r="67" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A67" s="22">
-        <v>61030001</v>
+        <v>61050001</v>
       </c>
       <c r="B67" s="22">
-        <v>6103</v>
+        <v>6105</v>
       </c>
       <c r="C67" s="22">
         <v>1</v>
@@ -8296,10 +8236,10 @@
         <v>0</v>
       </c>
       <c r="E67" s="22">
-        <v>3610700</v>
+        <v>3610900</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G67" s="13" t="s">
         <v>255</v>
@@ -8307,31 +8247,31 @@
       <c r="H67" s="13"/>
       <c r="I67" s="13"/>
       <c r="J67" s="22" t="s">
-        <v>43</v>
+        <v>305</v>
       </c>
       <c r="K67" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="22" t="s">
-        <v>277</v>
+        <v>43</v>
       </c>
       <c r="N67" s="22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O67" s="22">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="P67" s="22" t="s">
-        <v>278</v>
+        <v>43</v>
       </c>
       <c r="Q67" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R67" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S67" s="22">
         <v>0</v>
@@ -8340,7 +8280,7 @@
         <v>43</v>
       </c>
       <c r="U67" s="22">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V67" s="22" t="s">
         <v>43</v>
@@ -8369,10 +8309,10 @@
     </row>
     <row r="68" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A68" s="22">
-        <v>61040001</v>
+        <v>61060001</v>
       </c>
       <c r="B68" s="22">
-        <v>6104</v>
+        <v>6106</v>
       </c>
       <c r="C68" s="22">
         <v>1</v>
@@ -8381,10 +8321,10 @@
         <v>0</v>
       </c>
       <c r="E68" s="22">
-        <v>3541400</v>
+        <v>3611100</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>256</v>
+        <v>371</v>
       </c>
       <c r="G68" s="13" t="s">
         <v>255</v>
@@ -8392,13 +8332,13 @@
       <c r="H68" s="13"/>
       <c r="I68" s="13"/>
       <c r="J68" s="22" t="s">
-        <v>118</v>
+        <v>43</v>
       </c>
       <c r="K68" s="22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L68" s="22">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="M68" s="22" t="s">
         <v>43</v>
@@ -8454,10 +8394,10 @@
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A69" s="22">
-        <v>61050001</v>
+        <v>61070001</v>
       </c>
       <c r="B69" s="22">
-        <v>6105</v>
+        <v>6107</v>
       </c>
       <c r="C69" s="22">
         <v>1</v>
@@ -8466,10 +8406,10 @@
         <v>0</v>
       </c>
       <c r="E69" s="22">
-        <v>3610900</v>
+        <v>3611300</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="G69" s="13" t="s">
         <v>255</v>
@@ -8477,13 +8417,13 @@
       <c r="H69" s="13"/>
       <c r="I69" s="13"/>
       <c r="J69" s="22" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K69" s="22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L69" s="22">
-        <v>1</v>
+        <v>300000</v>
       </c>
       <c r="M69" s="22" t="s">
         <v>43</v>
@@ -8495,13 +8435,13 @@
         <v>0</v>
       </c>
       <c r="P69" s="22" t="s">
-        <v>43</v>
+        <v>307</v>
       </c>
       <c r="Q69" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R69" s="22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S69" s="22">
         <v>0</v>
@@ -8539,10 +8479,10 @@
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A70" s="22">
-        <v>61060001</v>
+        <v>61080001</v>
       </c>
       <c r="B70" s="22">
-        <v>6106</v>
+        <v>6108</v>
       </c>
       <c r="C70" s="22">
         <v>1</v>
@@ -8551,10 +8491,10 @@
         <v>0</v>
       </c>
       <c r="E70" s="22">
-        <v>3611100</v>
+        <v>3611500</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>371</v>
+        <v>301</v>
       </c>
       <c r="G70" s="13" t="s">
         <v>255</v>
@@ -8571,22 +8511,22 @@
         <v>0</v>
       </c>
       <c r="M70" s="22" t="s">
-        <v>43</v>
+        <v>309</v>
       </c>
       <c r="N70" s="22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O70" s="22">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P70" s="22" t="s">
-        <v>43</v>
+        <v>310</v>
       </c>
       <c r="Q70" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R70" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S70" s="22">
         <v>0</v>
@@ -8595,7 +8535,7 @@
         <v>43</v>
       </c>
       <c r="U70" s="22">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V70" s="22" t="s">
         <v>43</v>
@@ -8624,10 +8564,10 @@
     </row>
     <row r="71" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A71" s="22">
-        <v>61070001</v>
+        <v>61090001</v>
       </c>
       <c r="B71" s="22">
-        <v>6107</v>
+        <v>6109</v>
       </c>
       <c r="C71" s="22">
         <v>1</v>
@@ -8636,10 +8576,10 @@
         <v>0</v>
       </c>
       <c r="E71" s="22">
-        <v>3611300</v>
+        <v>3611700</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G71" s="13" t="s">
         <v>255</v>
@@ -8647,7 +8587,7 @@
       <c r="H71" s="13"/>
       <c r="I71" s="13"/>
       <c r="J71" s="22" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="K71" s="22">
         <v>3</v>
@@ -8665,13 +8605,13 @@
         <v>0</v>
       </c>
       <c r="P71" s="22" t="s">
-        <v>307</v>
+        <v>43</v>
       </c>
       <c r="Q71" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R71" s="22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S71" s="22">
         <v>0</v>
@@ -8709,10 +8649,10 @@
     </row>
     <row r="72" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A72" s="22">
-        <v>61080001</v>
+        <v>61100001</v>
       </c>
       <c r="B72" s="22">
-        <v>6108</v>
+        <v>6110</v>
       </c>
       <c r="C72" s="22">
         <v>1</v>
@@ -8721,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="E72" s="22">
-        <v>3611500</v>
+        <v>3590800</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G72" s="13" t="s">
         <v>255</v>
@@ -8741,7 +8681,7 @@
         <v>0</v>
       </c>
       <c r="M72" s="22" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="N72" s="22">
         <v>2</v>
@@ -8750,7 +8690,7 @@
         <v>10000</v>
       </c>
       <c r="P72" s="22" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q72" s="22">
         <v>1</v>
@@ -8792,178 +8732,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A73" s="22">
-        <v>61090001</v>
-      </c>
-      <c r="B73" s="22">
-        <v>6109</v>
-      </c>
-      <c r="C73" s="22">
-        <v>1</v>
-      </c>
-      <c r="D73" s="22">
-        <v>0</v>
-      </c>
-      <c r="E73" s="22">
-        <v>3611700</v>
-      </c>
-      <c r="F73" s="13" t="s">
-        <v>321</v>
-      </c>
-      <c r="G73" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="H73" s="13"/>
-      <c r="I73" s="13"/>
-      <c r="J73" s="22" t="s">
-        <v>308</v>
-      </c>
-      <c r="K73" s="22">
-        <v>3</v>
-      </c>
-      <c r="L73" s="22">
-        <v>300000</v>
-      </c>
-      <c r="M73" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="N73" s="22">
-        <v>0</v>
-      </c>
-      <c r="O73" s="22">
-        <v>0</v>
-      </c>
-      <c r="P73" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q73" s="22">
-        <v>0</v>
-      </c>
-      <c r="R73" s="22">
-        <v>0</v>
-      </c>
-      <c r="S73" s="22">
-        <v>0</v>
-      </c>
-      <c r="T73" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="U73" s="22">
-        <v>-1</v>
-      </c>
-      <c r="V73" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="W73" s="22">
-        <v>10000</v>
-      </c>
-      <c r="X73" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y73" s="22">
-        <v>1</v>
-      </c>
-      <c r="Z73" s="22">
-        <v>1</v>
-      </c>
-      <c r="AA73" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB73" s="22">
-        <v>1</v>
-      </c>
-      <c r="AC73" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A74" s="22">
-        <v>61100001</v>
-      </c>
-      <c r="B74" s="22">
-        <v>6110</v>
-      </c>
-      <c r="C74" s="22">
-        <v>1</v>
-      </c>
-      <c r="D74" s="22">
-        <v>0</v>
-      </c>
-      <c r="E74" s="22">
-        <v>3590800</v>
-      </c>
-      <c r="F74" s="13" t="s">
-        <v>302</v>
-      </c>
-      <c r="G74" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="H74" s="13"/>
-      <c r="I74" s="13"/>
-      <c r="J74" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="K74" s="22">
-        <v>0</v>
-      </c>
-      <c r="L74" s="22">
-        <v>0</v>
-      </c>
-      <c r="M74" s="22" t="s">
-        <v>304</v>
-      </c>
-      <c r="N74" s="22">
-        <v>2</v>
-      </c>
-      <c r="O74" s="22">
-        <v>10000</v>
-      </c>
-      <c r="P74" s="22" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q74" s="22">
-        <v>1</v>
-      </c>
-      <c r="R74" s="22">
-        <v>1</v>
-      </c>
-      <c r="S74" s="22">
-        <v>0</v>
-      </c>
-      <c r="T74" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="U74" s="22">
-        <v>0</v>
-      </c>
-      <c r="V74" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="W74" s="22">
-        <v>10000</v>
-      </c>
-      <c r="X74" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y74" s="22">
-        <v>1</v>
-      </c>
-      <c r="Z74" s="22">
-        <v>1</v>
-      </c>
-      <c r="AA74" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB74" s="22">
-        <v>1</v>
-      </c>
-      <c r="AC74" s="22">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:AC74" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:AC72" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D321BFCA-B977-4F35-86D2-C4FD31B67A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E89779E-6FAA-4DF9-B7FD-A79767996087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="备注" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skilleffect_v8!$A$4:$AC$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skilleffect_v8!$A$4:$AC$74</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="533">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1845,6 +1845,58 @@
   </si>
   <si>
     <t>备注</t>
+  </si>
+  <si>
+    <t>受到的伤害总加成</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成伤害总加成</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成的伤害总加成【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到的伤害总加成【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542801:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542601:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3543001:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542607:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542807:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3543007:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542605:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542805:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3543005:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2466,7 +2518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:AC74"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -4071,7 +4123,7 @@
         <v>177</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>127</v>
+        <v>525</v>
       </c>
       <c r="K19" s="15">
         <v>2</v>
@@ -4101,7 +4153,7 @@
         <v>0</v>
       </c>
       <c r="T19" s="15" t="s">
-        <v>150</v>
+        <v>530</v>
       </c>
       <c r="U19" s="15">
         <v>4000</v>
@@ -4113,7 +4165,7 @@
         <v>10000</v>
       </c>
       <c r="X19" s="15" t="s">
-        <v>151</v>
+        <v>527</v>
       </c>
       <c r="Y19" s="15">
         <v>1</v>
@@ -4132,189 +4184,189 @@
       </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A20" s="17">
-        <v>55010001</v>
-      </c>
-      <c r="B20" s="17">
-        <v>5501</v>
-      </c>
-      <c r="C20" s="17">
-        <v>1</v>
-      </c>
-      <c r="D20" s="17">
-        <v>0</v>
-      </c>
-      <c r="E20" s="17">
-        <v>3550200</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>351</v>
-      </c>
-      <c r="J20" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="K20" s="17">
-        <v>0</v>
-      </c>
-      <c r="L20" s="17">
-        <v>0</v>
-      </c>
-      <c r="M20" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="N20" s="17">
-        <v>0</v>
-      </c>
-      <c r="O20" s="17">
-        <v>0</v>
-      </c>
-      <c r="P20" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q20" s="17">
-        <v>0</v>
-      </c>
-      <c r="R20" s="17">
-        <v>0</v>
-      </c>
-      <c r="S20" s="17">
-        <v>0</v>
-      </c>
-      <c r="T20" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="U20" s="17">
-        <v>2000</v>
-      </c>
-      <c r="V20" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="W20" s="17">
-        <v>1000</v>
-      </c>
-      <c r="X20" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y20" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="17">
-        <v>1</v>
-      </c>
-      <c r="AA20" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB20" s="17">
-        <v>1</v>
-      </c>
-      <c r="AC20" s="17">
+      <c r="A20" s="15">
+        <v>54140001</v>
+      </c>
+      <c r="B20" s="15">
+        <v>5414</v>
+      </c>
+      <c r="C20" s="15">
+        <v>1</v>
+      </c>
+      <c r="D20" s="15">
+        <v>0</v>
+      </c>
+      <c r="E20" s="15">
+        <v>3542800</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>522</v>
+      </c>
+      <c r="J20" s="15" t="s">
+        <v>524</v>
+      </c>
+      <c r="K20" s="15">
+        <v>2</v>
+      </c>
+      <c r="L20" s="15">
+        <v>5000</v>
+      </c>
+      <c r="M20" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="N20" s="15">
+        <v>0</v>
+      </c>
+      <c r="O20" s="15">
+        <v>0</v>
+      </c>
+      <c r="P20" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q20" s="15">
+        <v>0</v>
+      </c>
+      <c r="R20" s="15">
+        <v>0</v>
+      </c>
+      <c r="S20" s="15">
+        <v>0</v>
+      </c>
+      <c r="T20" s="15" t="s">
+        <v>531</v>
+      </c>
+      <c r="U20" s="15">
+        <v>-1</v>
+      </c>
+      <c r="V20" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="W20" s="15">
+        <v>10000</v>
+      </c>
+      <c r="X20" s="15" t="s">
+        <v>528</v>
+      </c>
+      <c r="Y20" s="15">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="15">
+        <v>3</v>
+      </c>
+      <c r="AA20" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB20" s="15">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A21" s="17">
-        <v>55020001</v>
-      </c>
-      <c r="B21" s="17">
-        <v>5502</v>
-      </c>
-      <c r="C21" s="17">
-        <v>1</v>
-      </c>
-      <c r="D21" s="17">
-        <v>0</v>
-      </c>
-      <c r="E21" s="17">
-        <v>3550500</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="H21" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="I21" s="13" t="s">
-        <v>352</v>
-      </c>
-      <c r="J21" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="K21" s="17">
-        <v>1</v>
-      </c>
-      <c r="L21" s="17">
-        <v>12</v>
-      </c>
-      <c r="M21" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="N21" s="17">
+      <c r="A21" s="15">
+        <v>54150001</v>
+      </c>
+      <c r="B21" s="15">
+        <v>5415</v>
+      </c>
+      <c r="C21" s="15">
+        <v>1</v>
+      </c>
+      <c r="D21" s="15">
+        <v>0</v>
+      </c>
+      <c r="E21" s="15">
+        <v>3543000</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>520</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>523</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>526</v>
+      </c>
+      <c r="K21" s="15">
         <v>2</v>
       </c>
-      <c r="O21" s="17">
+      <c r="L21" s="15">
         <v>10000</v>
       </c>
-      <c r="P21" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q21" s="17">
-        <v>1</v>
-      </c>
-      <c r="R21" s="17">
-        <v>1</v>
-      </c>
-      <c r="S21" s="17">
-        <v>5000001</v>
-      </c>
-      <c r="T21" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="U21" s="17">
-        <v>4000</v>
-      </c>
-      <c r="V21" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="W21" s="17">
+      <c r="M21" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="N21" s="15">
+        <v>0</v>
+      </c>
+      <c r="O21" s="15">
+        <v>0</v>
+      </c>
+      <c r="P21" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q21" s="15">
+        <v>0</v>
+      </c>
+      <c r="R21" s="15">
+        <v>0</v>
+      </c>
+      <c r="S21" s="15">
+        <v>0</v>
+      </c>
+      <c r="T21" s="15" t="s">
+        <v>532</v>
+      </c>
+      <c r="U21" s="15">
+        <v>-1</v>
+      </c>
+      <c r="V21" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="W21" s="15">
         <v>10000</v>
       </c>
-      <c r="X21" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y21" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="17">
-        <v>1</v>
-      </c>
-      <c r="AA21" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB21" s="17">
-        <v>1</v>
-      </c>
-      <c r="AC21" s="17">
+      <c r="X21" s="15" t="s">
+        <v>529</v>
+      </c>
+      <c r="Y21" s="15">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="15">
+        <v>3</v>
+      </c>
+      <c r="AA21" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB21" s="15">
+        <v>1</v>
+      </c>
+      <c r="AC21" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A22" s="17">
-        <v>55030001</v>
+        <v>55010001</v>
       </c>
       <c r="B22" s="17">
-        <v>5503</v>
+        <v>5501</v>
       </c>
       <c r="C22" s="17">
         <v>1</v>
@@ -4323,19 +4375,19 @@
         <v>0</v>
       </c>
       <c r="E22" s="17">
-        <v>3550700</v>
+        <v>3550200</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>185</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="J22" s="17" t="s">
         <v>43</v>
@@ -4344,40 +4396,40 @@
         <v>0</v>
       </c>
       <c r="L22" s="17">
+        <v>0</v>
+      </c>
+      <c r="M22" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="N22" s="17">
+        <v>0</v>
+      </c>
+      <c r="O22" s="17">
+        <v>0</v>
+      </c>
+      <c r="P22" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q22" s="17">
+        <v>0</v>
+      </c>
+      <c r="R22" s="17">
+        <v>0</v>
+      </c>
+      <c r="S22" s="17">
+        <v>0</v>
+      </c>
+      <c r="T22" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="U22" s="17">
+        <v>2000</v>
+      </c>
+      <c r="V22" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="W22" s="17">
         <v>1000</v>
-      </c>
-      <c r="M22" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="N22" s="17">
-        <v>2</v>
-      </c>
-      <c r="O22" s="17">
-        <v>10000</v>
-      </c>
-      <c r="P22" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q22" s="17">
-        <v>1</v>
-      </c>
-      <c r="R22" s="17">
-        <v>1</v>
-      </c>
-      <c r="S22" s="17">
-        <v>5000001</v>
-      </c>
-      <c r="T22" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="U22" s="17">
-        <v>4000</v>
-      </c>
-      <c r="V22" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="W22" s="17">
-        <v>10000</v>
       </c>
       <c r="X22" s="17" t="s">
         <v>43</v>
@@ -4400,10 +4452,10 @@
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A23" s="17">
-        <v>55040001</v>
+        <v>55020001</v>
       </c>
       <c r="B23" s="17">
-        <v>5504</v>
+        <v>5502</v>
       </c>
       <c r="C23" s="17">
         <v>1</v>
@@ -4412,58 +4464,58 @@
         <v>0</v>
       </c>
       <c r="E23" s="17">
-        <v>3550900</v>
+        <v>3550500</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>185</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="J23" s="17" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="K23" s="17">
+        <v>1</v>
+      </c>
+      <c r="L23" s="17">
+        <v>12</v>
+      </c>
+      <c r="M23" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="N23" s="17">
         <v>2</v>
       </c>
-      <c r="L23" s="17">
-        <v>3000</v>
-      </c>
-      <c r="M23" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="N23" s="17">
-        <v>0</v>
-      </c>
       <c r="O23" s="17">
-        <v>30</v>
+        <v>10000</v>
       </c>
       <c r="P23" s="17" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="Q23" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" s="17">
-        <v>0</v>
+        <v>5000001</v>
       </c>
       <c r="T23" s="17" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="U23" s="17">
-        <v>-1</v>
+        <v>4000</v>
       </c>
       <c r="V23" s="17" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="W23" s="17">
         <v>10000</v>
@@ -4489,10 +4541,10 @@
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A24" s="17">
-        <v>55050001</v>
+        <v>55030001</v>
       </c>
       <c r="B24" s="17">
-        <v>5505</v>
+        <v>5503</v>
       </c>
       <c r="C24" s="17">
         <v>1</v>
@@ -4501,55 +4553,55 @@
         <v>0</v>
       </c>
       <c r="E24" s="17">
-        <v>3551100</v>
+        <v>3550700</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>156</v>
+        <v>72</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>185</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="J24" s="17" t="s">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="K24" s="17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L24" s="17">
-        <v>100000</v>
+        <v>1000</v>
       </c>
       <c r="M24" s="17" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="N24" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O24" s="17">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P24" s="17" t="s">
-        <v>374</v>
+        <v>84</v>
       </c>
       <c r="Q24" s="17">
         <v>1</v>
       </c>
       <c r="R24" s="17">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="S24" s="17">
-        <v>0</v>
+        <v>5000001</v>
       </c>
       <c r="T24" s="17" t="s">
         <v>43</v>
       </c>
       <c r="U24" s="17">
-        <v>-1</v>
+        <v>4000</v>
       </c>
       <c r="V24" s="17" t="s">
         <v>43</v>
@@ -4578,10 +4630,10 @@
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A25" s="17">
-        <v>55060001</v>
+        <v>55040001</v>
       </c>
       <c r="B25" s="17">
-        <v>5506</v>
+        <v>5504</v>
       </c>
       <c r="C25" s="17">
         <v>1</v>
@@ -4590,37 +4642,37 @@
         <v>0</v>
       </c>
       <c r="E25" s="17">
-        <v>3551300</v>
+        <v>3550900</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>357</v>
+        <v>74</v>
       </c>
       <c r="G25" s="13" t="s">
         <v>185</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K25" s="17">
         <v>2</v>
       </c>
       <c r="L25" s="17">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="M25" s="17" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="N25" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" s="17">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P25" s="17" t="s">
         <v>43</v>
@@ -4667,10 +4719,10 @@
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A26" s="17">
-        <v>55070001</v>
+        <v>55050001</v>
       </c>
       <c r="B26" s="17">
-        <v>5507</v>
+        <v>5505</v>
       </c>
       <c r="C26" s="17">
         <v>1</v>
@@ -4679,265 +4731,265 @@
         <v>0</v>
       </c>
       <c r="E26" s="17">
-        <v>3551500</v>
+        <v>3551100</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G26" s="13" t="s">
         <v>185</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>157</v>
+        <v>355</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>153</v>
+        <v>86</v>
       </c>
       <c r="K26" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L26" s="17">
+        <v>100000</v>
+      </c>
+      <c r="M26" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="N26" s="17">
+        <v>1</v>
+      </c>
+      <c r="O26" s="17">
+        <v>0</v>
+      </c>
+      <c r="P26" s="17" t="s">
+        <v>374</v>
+      </c>
+      <c r="Q26" s="17">
+        <v>1</v>
+      </c>
+      <c r="R26" s="17">
         <v>2000</v>
       </c>
-      <c r="M26" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="N26" s="17">
-        <v>0</v>
-      </c>
-      <c r="O26" s="17">
-        <v>0</v>
-      </c>
-      <c r="P26" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q26" s="17">
-        <v>0</v>
-      </c>
-      <c r="R26" s="17">
-        <v>0</v>
-      </c>
       <c r="S26" s="17">
         <v>0</v>
       </c>
       <c r="T26" s="17" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="U26" s="17">
         <v>-1</v>
       </c>
       <c r="V26" s="17" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="W26" s="17">
         <v>10000</v>
       </c>
       <c r="X26" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y26" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="17">
+        <v>1</v>
+      </c>
+      <c r="AA26" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB26" s="17">
+        <v>1</v>
+      </c>
+      <c r="AC26" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A27" s="17">
+        <v>55060001</v>
+      </c>
+      <c r="B27" s="17">
+        <v>5506</v>
+      </c>
+      <c r="C27" s="17">
+        <v>1</v>
+      </c>
+      <c r="D27" s="17">
+        <v>0</v>
+      </c>
+      <c r="E27" s="17">
+        <v>3551300</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="J27" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="K27" s="17">
+        <v>2</v>
+      </c>
+      <c r="L27" s="17">
+        <v>5000</v>
+      </c>
+      <c r="M27" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="N27" s="17">
+        <v>1</v>
+      </c>
+      <c r="O27" s="17">
+        <v>50</v>
+      </c>
+      <c r="P27" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q27" s="17">
+        <v>0</v>
+      </c>
+      <c r="R27" s="17">
+        <v>0</v>
+      </c>
+      <c r="S27" s="17">
+        <v>0</v>
+      </c>
+      <c r="T27" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="U27" s="17">
+        <v>-1</v>
+      </c>
+      <c r="V27" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="W27" s="17">
+        <v>10000</v>
+      </c>
+      <c r="X27" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y27" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="17">
+        <v>1</v>
+      </c>
+      <c r="AA27" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB27" s="17">
+        <v>1</v>
+      </c>
+      <c r="AC27" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A28" s="17">
+        <v>55070001</v>
+      </c>
+      <c r="B28" s="17">
+        <v>5507</v>
+      </c>
+      <c r="C28" s="17">
+        <v>1</v>
+      </c>
+      <c r="D28" s="17">
+        <v>0</v>
+      </c>
+      <c r="E28" s="17">
+        <v>3551500</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="J28" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="K28" s="17">
+        <v>2</v>
+      </c>
+      <c r="L28" s="17">
+        <v>2000</v>
+      </c>
+      <c r="M28" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="Y26" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z26" s="17">
-        <v>1</v>
-      </c>
-      <c r="AA26" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB26" s="17">
-        <v>1</v>
-      </c>
-      <c r="AC26" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A27" s="18">
-        <v>56010001</v>
-      </c>
-      <c r="B27" s="18">
-        <v>5601</v>
-      </c>
-      <c r="C27" s="18">
-        <v>1</v>
-      </c>
-      <c r="D27" s="18">
-        <v>0</v>
-      </c>
-      <c r="E27" s="18">
-        <v>3560200</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="I27" s="13" t="s">
-        <v>334</v>
-      </c>
-      <c r="J27" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="K27" s="18">
-        <v>2</v>
-      </c>
-      <c r="L27" s="18">
-        <v>5000</v>
-      </c>
-      <c r="M27" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="N27" s="18">
-        <v>1</v>
-      </c>
-      <c r="O27" s="18">
-        <v>50</v>
-      </c>
-      <c r="P27" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q27" s="18">
-        <v>0</v>
-      </c>
-      <c r="R27" s="18">
-        <v>0</v>
-      </c>
-      <c r="S27" s="18">
-        <v>0</v>
-      </c>
-      <c r="T27" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="U27" s="18">
-        <v>4000</v>
-      </c>
-      <c r="V27" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="W27" s="18">
-        <v>1500</v>
-      </c>
-      <c r="X27" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y27" s="18">
-        <v>1</v>
-      </c>
-      <c r="Z27" s="18">
-        <v>1</v>
-      </c>
-      <c r="AA27" s="18" t="s">
-        <v>339</v>
-      </c>
-      <c r="AB27" s="18">
-        <v>1</v>
-      </c>
-      <c r="AC27" s="18">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A28" s="18">
-        <v>56020001</v>
-      </c>
-      <c r="B28" s="18">
-        <v>5602</v>
-      </c>
-      <c r="C28" s="18">
-        <v>1</v>
-      </c>
-      <c r="D28" s="18">
-        <v>0</v>
-      </c>
-      <c r="E28" s="18">
-        <v>3560500</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="I28" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="J28" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="K28" s="18">
-        <v>1</v>
-      </c>
-      <c r="L28" s="18">
-        <v>8</v>
-      </c>
-      <c r="M28" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="N28" s="18">
-        <v>1</v>
-      </c>
-      <c r="O28" s="18">
+      <c r="N28" s="17">
+        <v>0</v>
+      </c>
+      <c r="O28" s="17">
+        <v>0</v>
+      </c>
+      <c r="P28" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q28" s="17">
+        <v>0</v>
+      </c>
+      <c r="R28" s="17">
+        <v>0</v>
+      </c>
+      <c r="S28" s="17">
+        <v>0</v>
+      </c>
+      <c r="T28" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="U28" s="17">
+        <v>-1</v>
+      </c>
+      <c r="V28" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="W28" s="17">
         <v>10000</v>
       </c>
-      <c r="P28" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q28" s="18">
-        <v>1</v>
-      </c>
-      <c r="R28" s="18">
-        <v>1</v>
-      </c>
-      <c r="S28" s="18">
-        <v>0</v>
-      </c>
-      <c r="T28" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="U28" s="18">
-        <v>0</v>
-      </c>
-      <c r="V28" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="W28" s="18">
-        <v>10000</v>
-      </c>
-      <c r="X28" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y28" s="18">
-        <v>1</v>
-      </c>
-      <c r="Z28" s="18">
-        <v>1</v>
-      </c>
-      <c r="AA28" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB28" s="18">
-        <v>1</v>
-      </c>
-      <c r="AC28" s="18">
+      <c r="X28" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y28" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z28" s="17">
+        <v>1</v>
+      </c>
+      <c r="AA28" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB28" s="17">
+        <v>1</v>
+      </c>
+      <c r="AC28" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A29" s="18">
-        <v>56030001</v>
+        <v>56010001</v>
       </c>
       <c r="B29" s="18">
-        <v>5603</v>
+        <v>5601</v>
       </c>
       <c r="C29" s="18">
         <v>1</v>
@@ -4946,37 +4998,37 @@
         <v>0</v>
       </c>
       <c r="E29" s="18">
-        <v>3560700</v>
+        <v>3560200</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>189</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>236</v>
+        <v>334</v>
       </c>
       <c r="J29" s="18" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="K29" s="18">
         <v>2</v>
       </c>
       <c r="L29" s="18">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="M29" s="18" t="s">
-        <v>43</v>
+        <v>205</v>
       </c>
       <c r="N29" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29" s="18">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P29" s="18" t="s">
         <v>43</v>
@@ -4991,16 +5043,16 @@
         <v>0</v>
       </c>
       <c r="T29" s="18" t="s">
-        <v>43</v>
+        <v>206</v>
       </c>
       <c r="U29" s="18">
-        <v>-1</v>
+        <v>4000</v>
       </c>
       <c r="V29" s="18" t="s">
-        <v>43</v>
+        <v>207</v>
       </c>
       <c r="W29" s="18">
-        <v>10000</v>
+        <v>1500</v>
       </c>
       <c r="X29" s="18" t="s">
         <v>43</v>
@@ -5012,21 +5064,21 @@
         <v>1</v>
       </c>
       <c r="AA29" s="18" t="s">
-        <v>43</v>
+        <v>339</v>
       </c>
       <c r="AB29" s="18">
         <v>1</v>
       </c>
       <c r="AC29" s="18">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A30" s="18">
-        <v>56040001</v>
+        <v>56020001</v>
       </c>
       <c r="B30" s="18">
-        <v>5604</v>
+        <v>5602</v>
       </c>
       <c r="C30" s="18">
         <v>1</v>
@@ -5035,46 +5087,46 @@
         <v>0</v>
       </c>
       <c r="E30" s="18">
-        <v>3560900</v>
+        <v>3560500</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>189</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="J30" s="18" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="K30" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L30" s="18">
+        <v>8</v>
+      </c>
+      <c r="M30" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="N30" s="18">
+        <v>1</v>
+      </c>
+      <c r="O30" s="18">
         <v>10000</v>
       </c>
-      <c r="M30" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="N30" s="18">
-        <v>0</v>
-      </c>
-      <c r="O30" s="18">
-        <v>0</v>
-      </c>
       <c r="P30" s="18" t="s">
-        <v>43</v>
+        <v>210</v>
       </c>
       <c r="Q30" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" s="18">
         <v>0</v>
@@ -5083,7 +5135,7 @@
         <v>43</v>
       </c>
       <c r="U30" s="18">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="18" t="s">
         <v>43</v>
@@ -5112,10 +5164,10 @@
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A31" s="18">
-        <v>56050001</v>
+        <v>56030001</v>
       </c>
       <c r="B31" s="18">
-        <v>5605</v>
+        <v>5603</v>
       </c>
       <c r="C31" s="18">
         <v>1</v>
@@ -5124,46 +5176,46 @@
         <v>0</v>
       </c>
       <c r="E31" s="18">
-        <v>3561100</v>
+        <v>3560700</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>189</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J31" s="18" t="s">
-        <v>43</v>
+        <v>211</v>
       </c>
       <c r="K31" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" s="18">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="M31" s="18" t="s">
-        <v>233</v>
+        <v>43</v>
       </c>
       <c r="N31" s="18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O31" s="18">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="P31" s="18" t="s">
-        <v>234</v>
+        <v>43</v>
       </c>
       <c r="Q31" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" s="18">
         <v>0</v>
@@ -5172,7 +5224,7 @@
         <v>43</v>
       </c>
       <c r="U31" s="18">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V31" s="18" t="s">
         <v>43</v>
@@ -5201,10 +5253,10 @@
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A32" s="18">
-        <v>56060001</v>
+        <v>56040001</v>
       </c>
       <c r="B32" s="18">
-        <v>5606</v>
+        <v>5604</v>
       </c>
       <c r="C32" s="18">
         <v>1</v>
@@ -5213,37 +5265,37 @@
         <v>0</v>
       </c>
       <c r="E32" s="18">
-        <v>3561400</v>
+        <v>3560900</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>344</v>
+        <v>195</v>
       </c>
       <c r="G32" s="13" t="s">
         <v>189</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>345</v>
+        <v>195</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>366</v>
+        <v>237</v>
       </c>
       <c r="J32" s="18" t="s">
-        <v>363</v>
+        <v>212</v>
       </c>
       <c r="K32" s="18">
         <v>2</v>
       </c>
       <c r="L32" s="18">
-        <v>3500</v>
+        <v>10000</v>
       </c>
       <c r="M32" s="18" t="s">
-        <v>364</v>
+        <v>43</v>
       </c>
       <c r="N32" s="18">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="O32" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32" s="18" t="s">
         <v>43</v>
@@ -5261,7 +5313,7 @@
         <v>43</v>
       </c>
       <c r="U32" s="18">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V32" s="18" t="s">
         <v>43</v>
@@ -5279,199 +5331,199 @@
         <v>1</v>
       </c>
       <c r="AA32" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB32" s="18">
+        <v>1</v>
+      </c>
+      <c r="AC32" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A33" s="18">
+        <v>56050001</v>
+      </c>
+      <c r="B33" s="18">
+        <v>5605</v>
+      </c>
+      <c r="C33" s="18">
+        <v>1</v>
+      </c>
+      <c r="D33" s="18">
+        <v>0</v>
+      </c>
+      <c r="E33" s="18">
+        <v>3561100</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="I33" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="J33" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="K33" s="18">
+        <v>0</v>
+      </c>
+      <c r="L33" s="18">
+        <v>0</v>
+      </c>
+      <c r="M33" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="N33" s="18">
+        <v>2</v>
+      </c>
+      <c r="O33" s="18">
+        <v>10000</v>
+      </c>
+      <c r="P33" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q33" s="18">
+        <v>1</v>
+      </c>
+      <c r="R33" s="18">
+        <v>1</v>
+      </c>
+      <c r="S33" s="18">
+        <v>0</v>
+      </c>
+      <c r="T33" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="U33" s="18">
+        <v>0</v>
+      </c>
+      <c r="V33" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="W33" s="18">
+        <v>10000</v>
+      </c>
+      <c r="X33" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y33" s="18">
+        <v>1</v>
+      </c>
+      <c r="Z33" s="18">
+        <v>1</v>
+      </c>
+      <c r="AA33" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB33" s="18">
+        <v>1</v>
+      </c>
+      <c r="AC33" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A34" s="18">
+        <v>56060001</v>
+      </c>
+      <c r="B34" s="18">
+        <v>5606</v>
+      </c>
+      <c r="C34" s="18">
+        <v>1</v>
+      </c>
+      <c r="D34" s="18">
+        <v>0</v>
+      </c>
+      <c r="E34" s="18">
+        <v>3561400</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="J34" s="18" t="s">
+        <v>363</v>
+      </c>
+      <c r="K34" s="18">
+        <v>2</v>
+      </c>
+      <c r="L34" s="18">
+        <v>3500</v>
+      </c>
+      <c r="M34" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="N34" s="18">
+        <v>35</v>
+      </c>
+      <c r="O34" s="18">
+        <v>1</v>
+      </c>
+      <c r="P34" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q34" s="18">
+        <v>0</v>
+      </c>
+      <c r="R34" s="18">
+        <v>0</v>
+      </c>
+      <c r="S34" s="18">
+        <v>0</v>
+      </c>
+      <c r="T34" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="U34" s="18">
+        <v>0</v>
+      </c>
+      <c r="V34" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="W34" s="18">
+        <v>10000</v>
+      </c>
+      <c r="X34" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y34" s="18">
+        <v>1</v>
+      </c>
+      <c r="Z34" s="18">
+        <v>1</v>
+      </c>
+      <c r="AA34" s="18" t="s">
         <v>365</v>
       </c>
-      <c r="AB32" s="18">
-        <v>1</v>
-      </c>
-      <c r="AC32" s="18">
+      <c r="AB34" s="18">
+        <v>1</v>
+      </c>
+      <c r="AC34" s="18">
         <v>1000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A33" s="19">
-        <v>57010001</v>
-      </c>
-      <c r="B33" s="19">
-        <v>5701</v>
-      </c>
-      <c r="C33" s="19">
-        <v>1</v>
-      </c>
-      <c r="D33" s="19">
-        <v>0</v>
-      </c>
-      <c r="E33" s="19">
-        <v>3570200</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="G33" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="I33" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="J33" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="K33" s="19">
-        <v>2</v>
-      </c>
-      <c r="L33" s="19">
-        <v>4000</v>
-      </c>
-      <c r="M33" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="N33" s="19">
-        <v>1</v>
-      </c>
-      <c r="O33" s="19">
-        <v>3</v>
-      </c>
-      <c r="P33" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q33" s="19">
-        <v>0</v>
-      </c>
-      <c r="R33" s="19">
-        <v>0</v>
-      </c>
-      <c r="S33" s="19">
-        <v>0</v>
-      </c>
-      <c r="T33" s="19" t="s">
-        <v>367</v>
-      </c>
-      <c r="U33" s="19">
-        <v>4000</v>
-      </c>
-      <c r="V33" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="W33" s="19">
-        <v>10000</v>
-      </c>
-      <c r="X33" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y33" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z33" s="19">
-        <v>1</v>
-      </c>
-      <c r="AA33" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB33" s="19">
-        <v>1</v>
-      </c>
-      <c r="AC33" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A34" s="19">
-        <v>57020001</v>
-      </c>
-      <c r="B34" s="19">
-        <v>5702</v>
-      </c>
-      <c r="C34" s="19">
-        <v>1</v>
-      </c>
-      <c r="D34" s="19">
-        <v>0</v>
-      </c>
-      <c r="E34" s="19">
-        <v>3570500</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="G34" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="H34" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="J34" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="K34" s="19">
-        <v>1</v>
-      </c>
-      <c r="L34" s="19">
-        <v>3</v>
-      </c>
-      <c r="M34" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="N34" s="19">
-        <v>1</v>
-      </c>
-      <c r="O34" s="19">
-        <v>1</v>
-      </c>
-      <c r="P34" s="19" t="s">
-        <v>348</v>
-      </c>
-      <c r="Q34" s="19">
-        <v>2</v>
-      </c>
-      <c r="R34" s="19">
-        <v>2500</v>
-      </c>
-      <c r="S34" s="19">
-        <v>0</v>
-      </c>
-      <c r="T34" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="U34" s="19">
-        <v>-1</v>
-      </c>
-      <c r="V34" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="W34" s="19">
-        <v>10000</v>
-      </c>
-      <c r="X34" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y34" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z34" s="19">
-        <v>1</v>
-      </c>
-      <c r="AA34" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB34" s="19">
-        <v>1</v>
-      </c>
-      <c r="AC34" s="19">
-        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A35" s="19">
-        <v>57030001</v>
+        <v>57010001</v>
       </c>
       <c r="B35" s="19">
-        <v>5703</v>
+        <v>5701</v>
       </c>
       <c r="C35" s="19">
         <v>1</v>
@@ -5480,55 +5532,55 @@
         <v>0</v>
       </c>
       <c r="E35" s="19">
-        <v>3570700</v>
+        <v>3570200</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G35" s="13" t="s">
         <v>190</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="J35" s="19" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="K35" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L35" s="19">
-        <v>8</v>
+        <v>4000</v>
       </c>
       <c r="M35" s="19" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="N35" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O35" s="19">
-        <v>10000</v>
+        <v>3</v>
       </c>
       <c r="P35" s="19" t="s">
-        <v>219</v>
+        <v>43</v>
       </c>
       <c r="Q35" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" s="19">
         <v>0</v>
       </c>
       <c r="T35" s="19" t="s">
-        <v>43</v>
+        <v>367</v>
       </c>
       <c r="U35" s="19">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="V35" s="19" t="s">
         <v>43</v>
@@ -5557,10 +5609,10 @@
     </row>
     <row r="36" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A36" s="19">
-        <v>57040001</v>
+        <v>57020001</v>
       </c>
       <c r="B36" s="19">
-        <v>5704</v>
+        <v>5702</v>
       </c>
       <c r="C36" s="19">
         <v>1</v>
@@ -5569,46 +5621,46 @@
         <v>0</v>
       </c>
       <c r="E36" s="19">
-        <v>3570900</v>
+        <v>3570500</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>347</v>
+        <v>198</v>
       </c>
       <c r="G36" s="13" t="s">
         <v>190</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>346</v>
+        <v>240</v>
       </c>
       <c r="J36" s="19" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="K36" s="19">
+        <v>1</v>
+      </c>
+      <c r="L36" s="19">
+        <v>3</v>
+      </c>
+      <c r="M36" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="N36" s="19">
+        <v>1</v>
+      </c>
+      <c r="O36" s="19">
+        <v>1</v>
+      </c>
+      <c r="P36" s="19" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q36" s="19">
         <v>2</v>
       </c>
-      <c r="L36" s="19">
-        <v>2000</v>
-      </c>
-      <c r="M36" s="19" t="s">
-        <v>325</v>
-      </c>
-      <c r="N36" s="19">
-        <v>1</v>
-      </c>
-      <c r="O36" s="19">
-        <v>20</v>
-      </c>
-      <c r="P36" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q36" s="19">
-        <v>0</v>
-      </c>
       <c r="R36" s="19">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="S36" s="19">
         <v>0</v>
@@ -5646,10 +5698,10 @@
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A37" s="19">
-        <v>57050001</v>
+        <v>57030001</v>
       </c>
       <c r="B37" s="19">
-        <v>5705</v>
+        <v>5703</v>
       </c>
       <c r="C37" s="19">
         <v>1</v>
@@ -5658,46 +5710,46 @@
         <v>0</v>
       </c>
       <c r="E37" s="19">
-        <v>3571100</v>
+        <v>3570700</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>350</v>
+        <v>199</v>
       </c>
       <c r="G37" s="13" t="s">
         <v>190</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>349</v>
+        <v>199</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>349</v>
+        <v>235</v>
       </c>
       <c r="J37" s="19" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="K37" s="19">
+        <v>1</v>
+      </c>
+      <c r="L37" s="19">
+        <v>8</v>
+      </c>
+      <c r="M37" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="N37" s="19">
         <v>2</v>
       </c>
-      <c r="L37" s="19">
+      <c r="O37" s="19">
         <v>10000</v>
       </c>
-      <c r="M37" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="N37" s="19">
-        <v>1</v>
-      </c>
-      <c r="O37" s="19">
-        <v>1</v>
-      </c>
       <c r="P37" s="19" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="Q37" s="19">
         <v>1</v>
       </c>
       <c r="R37" s="19">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="S37" s="19">
         <v>0</v>
@@ -5706,7 +5758,7 @@
         <v>43</v>
       </c>
       <c r="U37" s="19">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V37" s="19" t="s">
         <v>43</v>
@@ -5735,10 +5787,10 @@
     </row>
     <row r="38" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A38" s="19">
-        <v>57060001</v>
+        <v>57040001</v>
       </c>
       <c r="B38" s="19">
-        <v>5706</v>
+        <v>5704</v>
       </c>
       <c r="C38" s="19">
         <v>1</v>
@@ -5747,46 +5799,46 @@
         <v>0</v>
       </c>
       <c r="E38" s="19">
-        <v>3571300</v>
+        <v>3570900</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>201</v>
+        <v>347</v>
       </c>
       <c r="G38" s="13" t="s">
         <v>190</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="J38" s="19" t="s">
-        <v>43</v>
+        <v>220</v>
       </c>
       <c r="K38" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" s="19">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="M38" s="19" t="s">
-        <v>243</v>
+        <v>325</v>
       </c>
       <c r="N38" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O38" s="19">
-        <v>10000</v>
+        <v>20</v>
       </c>
       <c r="P38" s="19" t="s">
-        <v>244</v>
+        <v>43</v>
       </c>
       <c r="Q38" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" s="19">
         <v>0</v>
@@ -5823,189 +5875,189 @@
       </c>
     </row>
     <row r="39" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A39" s="20">
-        <v>58010001</v>
-      </c>
-      <c r="B39" s="20">
-        <v>5801</v>
-      </c>
-      <c r="C39" s="20">
-        <v>1</v>
-      </c>
-      <c r="D39" s="20">
-        <v>0</v>
-      </c>
-      <c r="E39" s="20">
-        <v>3580200</v>
+      <c r="A39" s="19">
+        <v>57050001</v>
+      </c>
+      <c r="B39" s="19">
+        <v>5705</v>
+      </c>
+      <c r="C39" s="19">
+        <v>1</v>
+      </c>
+      <c r="D39" s="19">
+        <v>0</v>
+      </c>
+      <c r="E39" s="19">
+        <v>3571100</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>202</v>
+        <v>350</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>202</v>
+        <v>349</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="J39" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="K39" s="20">
+        <v>349</v>
+      </c>
+      <c r="J39" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="K39" s="19">
         <v>2</v>
       </c>
-      <c r="L39" s="20">
-        <v>3000</v>
-      </c>
-      <c r="M39" s="20" t="s">
-        <v>225</v>
-      </c>
-      <c r="N39" s="20">
-        <v>1</v>
-      </c>
-      <c r="O39" s="20">
-        <v>30</v>
-      </c>
-      <c r="P39" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q39" s="20">
-        <v>1</v>
-      </c>
-      <c r="R39" s="20">
-        <v>0</v>
-      </c>
-      <c r="S39" s="20">
-        <v>0</v>
-      </c>
-      <c r="T39" s="20" t="s">
-        <v>368</v>
-      </c>
-      <c r="U39" s="20">
-        <v>4000</v>
-      </c>
-      <c r="V39" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="W39" s="20">
+      <c r="L39" s="19">
         <v>10000</v>
       </c>
-      <c r="X39" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="Y39" s="20">
-        <v>1</v>
-      </c>
-      <c r="Z39" s="20">
-        <v>1</v>
-      </c>
-      <c r="AA39" s="20" t="s">
-        <v>340</v>
-      </c>
-      <c r="AB39" s="20">
-        <v>1</v>
-      </c>
-      <c r="AC39" s="20">
-        <v>1000</v>
+      <c r="M39" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="N39" s="19">
+        <v>1</v>
+      </c>
+      <c r="O39" s="19">
+        <v>1</v>
+      </c>
+      <c r="P39" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q39" s="19">
+        <v>1</v>
+      </c>
+      <c r="R39" s="19">
+        <v>100</v>
+      </c>
+      <c r="S39" s="19">
+        <v>0</v>
+      </c>
+      <c r="T39" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="U39" s="19">
+        <v>-1</v>
+      </c>
+      <c r="V39" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="W39" s="19">
+        <v>10000</v>
+      </c>
+      <c r="X39" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y39" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z39" s="19">
+        <v>1</v>
+      </c>
+      <c r="AA39" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB39" s="19">
+        <v>1</v>
+      </c>
+      <c r="AC39" s="19">
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A40" s="20">
-        <v>58020001</v>
-      </c>
-      <c r="B40" s="20">
-        <v>5802</v>
-      </c>
-      <c r="C40" s="20">
-        <v>1</v>
-      </c>
-      <c r="D40" s="20">
-        <v>0</v>
-      </c>
-      <c r="E40" s="20">
-        <v>3580500</v>
+      <c r="A40" s="19">
+        <v>57060001</v>
+      </c>
+      <c r="B40" s="19">
+        <v>5706</v>
+      </c>
+      <c r="C40" s="19">
+        <v>1</v>
+      </c>
+      <c r="D40" s="19">
+        <v>0</v>
+      </c>
+      <c r="E40" s="19">
+        <v>3571300</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="J40" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="K40" s="20">
-        <v>1</v>
-      </c>
-      <c r="L40" s="20">
-        <v>8</v>
-      </c>
-      <c r="M40" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="N40" s="20">
+        <v>241</v>
+      </c>
+      <c r="J40" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="K40" s="19">
+        <v>0</v>
+      </c>
+      <c r="L40" s="19">
+        <v>0</v>
+      </c>
+      <c r="M40" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="N40" s="19">
         <v>2</v>
       </c>
-      <c r="O40" s="20">
+      <c r="O40" s="19">
         <v>10000</v>
       </c>
-      <c r="P40" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q40" s="20">
-        <v>1</v>
-      </c>
-      <c r="R40" s="20">
-        <v>1</v>
-      </c>
-      <c r="S40" s="20">
-        <v>0</v>
-      </c>
-      <c r="T40" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="U40" s="20">
+      <c r="P40" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q40" s="19">
+        <v>1</v>
+      </c>
+      <c r="R40" s="19">
+        <v>1</v>
+      </c>
+      <c r="S40" s="19">
+        <v>0</v>
+      </c>
+      <c r="T40" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="U40" s="19">
         <v>-1</v>
       </c>
-      <c r="V40" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="W40" s="20">
+      <c r="V40" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="W40" s="19">
         <v>10000</v>
       </c>
-      <c r="X40" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y40" s="20">
-        <v>1</v>
-      </c>
-      <c r="Z40" s="20">
-        <v>1</v>
-      </c>
-      <c r="AA40" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB40" s="20">
-        <v>1</v>
-      </c>
-      <c r="AC40" s="20">
+      <c r="X40" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y40" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z40" s="19">
+        <v>1</v>
+      </c>
+      <c r="AA40" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB40" s="19">
+        <v>1</v>
+      </c>
+      <c r="AC40" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A41" s="20">
-        <v>58030001</v>
+        <v>58010001</v>
       </c>
       <c r="B41" s="20">
-        <v>5803</v>
+        <v>5801</v>
       </c>
       <c r="C41" s="20">
         <v>1</v>
@@ -6014,43 +6066,43 @@
         <v>0</v>
       </c>
       <c r="E41" s="20">
-        <v>3580700</v>
+        <v>3580200</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>358</v>
+        <v>202</v>
       </c>
       <c r="G41" s="13" t="s">
         <v>191</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>358</v>
+        <v>202</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>359</v>
+        <v>335</v>
       </c>
       <c r="J41" s="20" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="K41" s="20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L41" s="20">
-        <v>5</v>
+        <v>3000</v>
       </c>
       <c r="M41" s="20" t="s">
-        <v>360</v>
+        <v>225</v>
       </c>
       <c r="N41" s="20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O41" s="20">
-        <v>10000</v>
+        <v>30</v>
       </c>
       <c r="P41" s="20" t="s">
         <v>43</v>
       </c>
       <c r="Q41" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" s="20">
         <v>0</v>
@@ -6059,10 +6111,10 @@
         <v>0</v>
       </c>
       <c r="T41" s="20" t="s">
-        <v>43</v>
+        <v>368</v>
       </c>
       <c r="U41" s="20">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="V41" s="20" t="s">
         <v>43</v>
@@ -6071,7 +6123,7 @@
         <v>10000</v>
       </c>
       <c r="X41" s="20" t="s">
-        <v>43</v>
+        <v>226</v>
       </c>
       <c r="Y41" s="20">
         <v>1</v>
@@ -6080,21 +6132,21 @@
         <v>1</v>
       </c>
       <c r="AA41" s="20" t="s">
-        <v>43</v>
+        <v>340</v>
       </c>
       <c r="AB41" s="20">
         <v>1</v>
       </c>
       <c r="AC41" s="20">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="42" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A42" s="20">
-        <v>58040001</v>
+        <v>58020001</v>
       </c>
       <c r="B42" s="20">
-        <v>5804</v>
+        <v>5802</v>
       </c>
       <c r="C42" s="20">
         <v>1</v>
@@ -6103,31 +6155,31 @@
         <v>0</v>
       </c>
       <c r="E42" s="20">
-        <v>3580900</v>
+        <v>3580500</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="G42" s="13" t="s">
         <v>191</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="J42" s="20" t="s">
-        <v>43</v>
+        <v>227</v>
       </c>
       <c r="K42" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="20">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M42" s="20" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="N42" s="20">
         <v>2</v>
@@ -6136,7 +6188,7 @@
         <v>10000</v>
       </c>
       <c r="P42" s="20" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="Q42" s="20">
         <v>1</v>
@@ -6151,7 +6203,7 @@
         <v>43</v>
       </c>
       <c r="U42" s="20">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V42" s="20" t="s">
         <v>43</v>
@@ -6179,50 +6231,50 @@
       </c>
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A43" s="23">
-        <v>58050001</v>
-      </c>
-      <c r="B43" s="23">
-        <v>5805</v>
-      </c>
-      <c r="C43" s="23">
-        <v>1</v>
-      </c>
-      <c r="D43" s="23">
-        <v>0</v>
-      </c>
-      <c r="E43" s="23">
-        <v>3581200</v>
+      <c r="A43" s="20">
+        <v>58030001</v>
+      </c>
+      <c r="B43" s="20">
+        <v>5803</v>
+      </c>
+      <c r="C43" s="20">
+        <v>1</v>
+      </c>
+      <c r="D43" s="20">
+        <v>0</v>
+      </c>
+      <c r="E43" s="20">
+        <v>3580700</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>188</v>
+        <v>358</v>
       </c>
       <c r="G43" s="13" t="s">
         <v>191</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>188</v>
+        <v>358</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>336</v>
+        <v>359</v>
       </c>
       <c r="J43" s="20" t="s">
-        <v>322</v>
+        <v>230</v>
       </c>
       <c r="K43" s="20">
+        <v>1</v>
+      </c>
+      <c r="L43" s="20">
+        <v>5</v>
+      </c>
+      <c r="M43" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="N43" s="20">
         <v>2</v>
       </c>
-      <c r="L43" s="20">
-        <v>3000</v>
-      </c>
-      <c r="M43" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="N43" s="20">
-        <v>0</v>
-      </c>
       <c r="O43" s="20">
-        <v>30</v>
+        <v>10000</v>
       </c>
       <c r="P43" s="20" t="s">
         <v>43</v>
@@ -6237,10 +6289,10 @@
         <v>0</v>
       </c>
       <c r="T43" s="20" t="s">
-        <v>369</v>
+        <v>43</v>
       </c>
       <c r="U43" s="20">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="V43" s="20" t="s">
         <v>43</v>
@@ -6249,200 +6301,208 @@
         <v>10000</v>
       </c>
       <c r="X43" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y43" s="20">
+        <v>1</v>
+      </c>
+      <c r="Z43" s="20">
+        <v>1</v>
+      </c>
+      <c r="AA43" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB43" s="20">
+        <v>1</v>
+      </c>
+      <c r="AC43" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A44" s="20">
+        <v>58040001</v>
+      </c>
+      <c r="B44" s="20">
+        <v>5804</v>
+      </c>
+      <c r="C44" s="20">
+        <v>1</v>
+      </c>
+      <c r="D44" s="20">
+        <v>0</v>
+      </c>
+      <c r="E44" s="20">
+        <v>3580900</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="G44" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="H44" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="I44" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="J44" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="K44" s="20">
+        <v>0</v>
+      </c>
+      <c r="L44" s="20">
+        <v>0</v>
+      </c>
+      <c r="M44" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="N44" s="20">
+        <v>2</v>
+      </c>
+      <c r="O44" s="20">
+        <v>10000</v>
+      </c>
+      <c r="P44" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q44" s="20">
+        <v>1</v>
+      </c>
+      <c r="R44" s="20">
+        <v>1</v>
+      </c>
+      <c r="S44" s="20">
+        <v>0</v>
+      </c>
+      <c r="T44" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="U44" s="20">
+        <v>0</v>
+      </c>
+      <c r="V44" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="W44" s="20">
+        <v>10000</v>
+      </c>
+      <c r="X44" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y44" s="20">
+        <v>1</v>
+      </c>
+      <c r="Z44" s="20">
+        <v>1</v>
+      </c>
+      <c r="AA44" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB44" s="20">
+        <v>1</v>
+      </c>
+      <c r="AC44" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A45" s="23">
+        <v>58050001</v>
+      </c>
+      <c r="B45" s="23">
+        <v>5805</v>
+      </c>
+      <c r="C45" s="23">
+        <v>1</v>
+      </c>
+      <c r="D45" s="23">
+        <v>0</v>
+      </c>
+      <c r="E45" s="23">
+        <v>3581200</v>
+      </c>
+      <c r="F45" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="G45" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="H45" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="I45" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="J45" s="20" t="s">
+        <v>322</v>
+      </c>
+      <c r="K45" s="20">
+        <v>2</v>
+      </c>
+      <c r="L45" s="20">
+        <v>3000</v>
+      </c>
+      <c r="M45" s="20" t="s">
+        <v>323</v>
+      </c>
+      <c r="N45" s="20">
+        <v>0</v>
+      </c>
+      <c r="O45" s="20">
+        <v>30</v>
+      </c>
+      <c r="P45" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q45" s="20">
+        <v>0</v>
+      </c>
+      <c r="R45" s="20">
+        <v>0</v>
+      </c>
+      <c r="S45" s="20">
+        <v>0</v>
+      </c>
+      <c r="T45" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="U45" s="20">
+        <v>4000</v>
+      </c>
+      <c r="V45" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="W45" s="20">
+        <v>10000</v>
+      </c>
+      <c r="X45" s="20" t="s">
         <v>324</v>
       </c>
-      <c r="Y43" s="20">
-        <v>1</v>
-      </c>
-      <c r="Z43" s="20">
+      <c r="Y45" s="20">
+        <v>1</v>
+      </c>
+      <c r="Z45" s="20">
         <v>10</v>
       </c>
-      <c r="AA43" s="20" t="s">
+      <c r="AA45" s="20" t="s">
         <v>341</v>
       </c>
-      <c r="AB43" s="20">
-        <v>1</v>
-      </c>
-      <c r="AC43" s="20">
+      <c r="AB45" s="20">
+        <v>1</v>
+      </c>
+      <c r="AC45" s="20">
         <v>1000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A44" s="24">
-        <v>59010001</v>
-      </c>
-      <c r="B44" s="24">
-        <v>5901</v>
-      </c>
-      <c r="C44" s="24">
-        <v>1</v>
-      </c>
-      <c r="D44" s="24">
-        <v>0</v>
-      </c>
-      <c r="E44" s="24">
-        <v>3590200</v>
-      </c>
-      <c r="F44" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="G44" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="H44" s="13"/>
-      <c r="I44" s="13"/>
-      <c r="J44" s="24" t="s">
-        <v>279</v>
-      </c>
-      <c r="K44" s="24">
-        <v>3</v>
-      </c>
-      <c r="L44" s="24">
-        <v>200000</v>
-      </c>
-      <c r="M44" s="24" t="s">
-        <v>280</v>
-      </c>
-      <c r="N44" s="24">
-        <v>2</v>
-      </c>
-      <c r="O44" s="24">
-        <v>10000</v>
-      </c>
-      <c r="P44" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="Q44" s="24">
-        <v>1</v>
-      </c>
-      <c r="R44" s="24">
-        <v>1</v>
-      </c>
-      <c r="S44" s="24">
-        <v>0</v>
-      </c>
-      <c r="T44" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="U44" s="24">
-        <v>0</v>
-      </c>
-      <c r="V44" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="W44" s="24">
-        <v>10000</v>
-      </c>
-      <c r="X44" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y44" s="24">
-        <v>1</v>
-      </c>
-      <c r="Z44" s="24">
-        <v>1</v>
-      </c>
-      <c r="AA44" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB44" s="24">
-        <v>1</v>
-      </c>
-      <c r="AC44" s="24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A45" s="24">
-        <v>59020001</v>
-      </c>
-      <c r="B45" s="24">
-        <v>5902</v>
-      </c>
-      <c r="C45" s="24">
-        <v>1</v>
-      </c>
-      <c r="D45" s="24">
-        <v>0</v>
-      </c>
-      <c r="E45" s="24">
-        <v>3590400</v>
-      </c>
-      <c r="F45" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="G45" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="H45" s="13"/>
-      <c r="I45" s="13"/>
-      <c r="J45" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="K45" s="24">
-        <v>3</v>
-      </c>
-      <c r="L45" s="24">
-        <v>200000</v>
-      </c>
-      <c r="M45" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="N45" s="24">
-        <v>0</v>
-      </c>
-      <c r="O45" s="24">
-        <v>0</v>
-      </c>
-      <c r="P45" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q45" s="24">
-        <v>0</v>
-      </c>
-      <c r="R45" s="24">
-        <v>0</v>
-      </c>
-      <c r="S45" s="24">
-        <v>59030001</v>
-      </c>
-      <c r="T45" s="24" t="s">
-        <v>370</v>
-      </c>
-      <c r="U45" s="24">
-        <v>-1</v>
-      </c>
-      <c r="V45" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="W45" s="24">
-        <v>10000</v>
-      </c>
-      <c r="X45" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y45" s="24">
-        <v>1</v>
-      </c>
-      <c r="Z45" s="24">
-        <v>1</v>
-      </c>
-      <c r="AA45" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB45" s="24">
-        <v>1</v>
-      </c>
-      <c r="AC45" s="24">
-        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A46" s="24">
-        <v>59030001</v>
+        <v>59010001</v>
       </c>
       <c r="B46" s="24">
-        <v>5903</v>
+        <v>5901</v>
       </c>
       <c r="C46" s="24">
         <v>1</v>
@@ -6451,10 +6511,10 @@
         <v>0</v>
       </c>
       <c r="E46" s="24">
-        <v>3590600</v>
+        <v>3590200</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G46" s="13" t="s">
         <v>245</v>
@@ -6462,16 +6522,16 @@
       <c r="H46" s="13"/>
       <c r="I46" s="13"/>
       <c r="J46" s="24" t="s">
-        <v>43</v>
+        <v>279</v>
       </c>
       <c r="K46" s="24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L46" s="24">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="M46" s="24" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="N46" s="24">
         <v>2</v>
@@ -6480,7 +6540,7 @@
         <v>10000</v>
       </c>
       <c r="P46" s="24" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q46" s="24">
         <v>1</v>
@@ -6489,7 +6549,7 @@
         <v>1</v>
       </c>
       <c r="S46" s="24">
-        <v>59200001</v>
+        <v>0</v>
       </c>
       <c r="T46" s="24" t="s">
         <v>43</v>
@@ -6524,10 +6584,10 @@
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A47" s="24">
-        <v>59040001</v>
+        <v>59020001</v>
       </c>
       <c r="B47" s="24">
-        <v>5904</v>
+        <v>5902</v>
       </c>
       <c r="C47" s="24">
         <v>1</v>
@@ -6536,10 +6596,10 @@
         <v>0</v>
       </c>
       <c r="E47" s="24">
-        <v>3590800</v>
+        <v>3590400</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G47" s="13" t="s">
         <v>245</v>
@@ -6547,37 +6607,37 @@
       <c r="H47" s="13"/>
       <c r="I47" s="13"/>
       <c r="J47" s="24" t="s">
-        <v>43</v>
+        <v>282</v>
       </c>
       <c r="K47" s="24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L47" s="24">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="M47" s="24" t="s">
-        <v>285</v>
+        <v>43</v>
       </c>
       <c r="N47" s="24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O47" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="P47" s="24" t="s">
-        <v>286</v>
+        <v>43</v>
       </c>
       <c r="Q47" s="24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" s="24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" s="24">
-        <v>59090001</v>
+        <v>59030001</v>
       </c>
       <c r="T47" s="24" t="s">
-        <v>43</v>
+        <v>370</v>
       </c>
       <c r="U47" s="24">
         <v>-1</v>
@@ -6609,10 +6669,10 @@
     </row>
     <row r="48" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A48" s="24">
-        <v>59050001</v>
+        <v>59030001</v>
       </c>
       <c r="B48" s="24">
-        <v>5905</v>
+        <v>5903</v>
       </c>
       <c r="C48" s="24">
         <v>1</v>
@@ -6621,10 +6681,10 @@
         <v>0</v>
       </c>
       <c r="E48" s="24">
-        <v>3591000</v>
+        <v>3590600</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G48" s="13" t="s">
         <v>245</v>
@@ -6632,40 +6692,40 @@
       <c r="H48" s="13"/>
       <c r="I48" s="13"/>
       <c r="J48" s="24" t="s">
-        <v>287</v>
+        <v>43</v>
       </c>
       <c r="K48" s="24">
+        <v>0</v>
+      </c>
+      <c r="L48" s="24">
+        <v>0</v>
+      </c>
+      <c r="M48" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="N48" s="24">
         <v>2</v>
       </c>
-      <c r="L48" s="24">
-        <v>0</v>
-      </c>
-      <c r="M48" s="24" t="s">
-        <v>342</v>
-      </c>
-      <c r="N48" s="24">
-        <v>1</v>
-      </c>
       <c r="O48" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P48" s="24" t="s">
-        <v>343</v>
+        <v>284</v>
       </c>
       <c r="Q48" s="24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R48" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S48" s="24">
-        <v>0</v>
+        <v>59200001</v>
       </c>
       <c r="T48" s="24" t="s">
         <v>43</v>
       </c>
       <c r="U48" s="24">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V48" s="24" t="s">
         <v>43</v>
@@ -6694,10 +6754,10 @@
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A49" s="24">
-        <v>59060001</v>
+        <v>59040001</v>
       </c>
       <c r="B49" s="24">
-        <v>5906</v>
+        <v>5904</v>
       </c>
       <c r="C49" s="24">
         <v>1</v>
@@ -6706,10 +6766,10 @@
         <v>0</v>
       </c>
       <c r="E49" s="24">
-        <v>3591200</v>
+        <v>3590800</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G49" s="13" t="s">
         <v>245</v>
@@ -6717,16 +6777,16 @@
       <c r="H49" s="13"/>
       <c r="I49" s="13"/>
       <c r="J49" s="24" t="s">
-        <v>288</v>
+        <v>43</v>
       </c>
       <c r="K49" s="24">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L49" s="24">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="M49" s="24" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="N49" s="24">
         <v>2</v>
@@ -6735,7 +6795,7 @@
         <v>10000</v>
       </c>
       <c r="P49" s="24" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="Q49" s="24">
         <v>1</v>
@@ -6744,7 +6804,7 @@
         <v>1</v>
       </c>
       <c r="S49" s="24">
-        <v>0</v>
+        <v>59090001</v>
       </c>
       <c r="T49" s="24" t="s">
         <v>43</v>
@@ -6779,10 +6839,10 @@
     </row>
     <row r="50" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A50" s="24">
-        <v>59070001</v>
+        <v>59050001</v>
       </c>
       <c r="B50" s="24">
-        <v>5907</v>
+        <v>5905</v>
       </c>
       <c r="C50" s="24">
         <v>1</v>
@@ -6791,10 +6851,10 @@
         <v>0</v>
       </c>
       <c r="E50" s="24">
-        <v>3591400</v>
+        <v>3591000</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G50" s="13" t="s">
         <v>245</v>
@@ -6802,34 +6862,34 @@
       <c r="H50" s="13"/>
       <c r="I50" s="13"/>
       <c r="J50" s="24" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="K50" s="24">
+        <v>2</v>
+      </c>
+      <c r="L50" s="24">
+        <v>0</v>
+      </c>
+      <c r="M50" s="24" t="s">
+        <v>342</v>
+      </c>
+      <c r="N50" s="24">
+        <v>1</v>
+      </c>
+      <c r="O50" s="24">
+        <v>0</v>
+      </c>
+      <c r="P50" s="24" t="s">
+        <v>343</v>
+      </c>
+      <c r="Q50" s="24">
         <v>3</v>
       </c>
-      <c r="L50" s="24">
-        <v>500000</v>
-      </c>
-      <c r="M50" s="24" t="s">
-        <v>292</v>
-      </c>
-      <c r="N50" s="24">
-        <v>2</v>
-      </c>
-      <c r="O50" s="24">
-        <v>10000</v>
-      </c>
-      <c r="P50" s="24" t="s">
-        <v>293</v>
-      </c>
-      <c r="Q50" s="24">
-        <v>1</v>
-      </c>
       <c r="R50" s="24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" s="24">
-        <v>59200002</v>
+        <v>0</v>
       </c>
       <c r="T50" s="24" t="s">
         <v>43</v>
@@ -6864,10 +6924,10 @@
     </row>
     <row r="51" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A51" s="24">
-        <v>59080001</v>
+        <v>59060001</v>
       </c>
       <c r="B51" s="24">
-        <v>5908</v>
+        <v>5906</v>
       </c>
       <c r="C51" s="24">
         <v>1</v>
@@ -6876,10 +6936,10 @@
         <v>0</v>
       </c>
       <c r="E51" s="24">
-        <v>3591600</v>
+        <v>3591200</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G51" s="13" t="s">
         <v>245</v>
@@ -6887,16 +6947,16 @@
       <c r="H51" s="13"/>
       <c r="I51" s="13"/>
       <c r="J51" s="24" t="s">
-        <v>43</v>
+        <v>288</v>
       </c>
       <c r="K51" s="24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L51" s="24">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="M51" s="24" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="N51" s="24">
         <v>2</v>
@@ -6905,7 +6965,7 @@
         <v>10000</v>
       </c>
       <c r="P51" s="24" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="Q51" s="24">
         <v>1</v>
@@ -6914,13 +6974,13 @@
         <v>1</v>
       </c>
       <c r="S51" s="24">
-        <v>90000001</v>
+        <v>0</v>
       </c>
       <c r="T51" s="24" t="s">
         <v>43</v>
       </c>
       <c r="U51" s="24">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V51" s="24" t="s">
         <v>43</v>
@@ -6949,10 +7009,10 @@
     </row>
     <row r="52" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A52" s="24">
-        <v>59090001</v>
+        <v>59070001</v>
       </c>
       <c r="B52" s="24">
-        <v>5909</v>
+        <v>5907</v>
       </c>
       <c r="C52" s="24">
         <v>1</v>
@@ -6961,10 +7021,10 @@
         <v>0</v>
       </c>
       <c r="E52" s="24">
-        <v>3591900</v>
+        <v>3591400</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>361</v>
+        <v>252</v>
       </c>
       <c r="G52" s="13" t="s">
         <v>245</v>
@@ -6972,34 +7032,34 @@
       <c r="H52" s="13"/>
       <c r="I52" s="13"/>
       <c r="J52" s="24" t="s">
-        <v>43</v>
+        <v>291</v>
       </c>
       <c r="K52" s="24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L52" s="24">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="M52" s="24" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="N52" s="24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O52" s="24">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="P52" s="24" t="s">
-        <v>43</v>
+        <v>293</v>
       </c>
       <c r="Q52" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S52" s="24">
-        <v>0</v>
+        <v>59200002</v>
       </c>
       <c r="T52" s="24" t="s">
         <v>43</v>
@@ -7023,21 +7083,21 @@
         <v>1</v>
       </c>
       <c r="AA52" s="24" t="s">
-        <v>362</v>
+        <v>43</v>
       </c>
       <c r="AB52" s="24">
         <v>1</v>
       </c>
       <c r="AC52" s="24">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A53" s="24">
-        <v>59100001</v>
+        <v>59080001</v>
       </c>
       <c r="B53" s="24">
-        <v>5910</v>
+        <v>5908</v>
       </c>
       <c r="C53" s="24">
         <v>1</v>
@@ -7046,10 +7106,10 @@
         <v>0</v>
       </c>
       <c r="E53" s="24">
-        <v>3541800</v>
+        <v>3591600</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>315</v>
+        <v>253</v>
       </c>
       <c r="G53" s="13" t="s">
         <v>245</v>
@@ -7060,37 +7120,37 @@
         <v>43</v>
       </c>
       <c r="K53" s="24">
+        <v>0</v>
+      </c>
+      <c r="L53" s="24">
+        <v>0</v>
+      </c>
+      <c r="M53" s="24" t="s">
+        <v>294</v>
+      </c>
+      <c r="N53" s="24">
         <v>2</v>
       </c>
-      <c r="L53" s="24">
-        <v>1500</v>
-      </c>
-      <c r="M53" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="N53" s="24">
-        <v>0</v>
-      </c>
       <c r="O53" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P53" s="24" t="s">
-        <v>43</v>
+        <v>295</v>
       </c>
       <c r="Q53" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R53" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S53" s="24">
-        <v>0</v>
+        <v>90000001</v>
       </c>
       <c r="T53" s="24" t="s">
         <v>43</v>
       </c>
       <c r="U53" s="24">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V53" s="24" t="s">
         <v>43</v>
@@ -7119,10 +7179,10 @@
     </row>
     <row r="54" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A54" s="24">
-        <v>59110001</v>
+        <v>59090001</v>
       </c>
       <c r="B54" s="24">
-        <v>5911</v>
+        <v>5909</v>
       </c>
       <c r="C54" s="24">
         <v>1</v>
@@ -7131,10 +7191,10 @@
         <v>0</v>
       </c>
       <c r="E54" s="24">
-        <v>3541800</v>
+        <v>3591900</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>316</v>
+        <v>361</v>
       </c>
       <c r="G54" s="13" t="s">
         <v>245</v>
@@ -7145,19 +7205,19 @@
         <v>43</v>
       </c>
       <c r="K54" s="24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L54" s="24">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="M54" s="24" t="s">
-        <v>43</v>
+        <v>296</v>
       </c>
       <c r="N54" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P54" s="24" t="s">
         <v>43</v>
@@ -7193,21 +7253,21 @@
         <v>1</v>
       </c>
       <c r="AA54" s="24" t="s">
-        <v>43</v>
+        <v>362</v>
       </c>
       <c r="AB54" s="24">
         <v>1</v>
       </c>
       <c r="AC54" s="24">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A55" s="25">
-        <v>59120001</v>
+      <c r="A55" s="24">
+        <v>59100001</v>
       </c>
       <c r="B55" s="24">
-        <v>5912</v>
+        <v>5910</v>
       </c>
       <c r="C55" s="24">
         <v>1</v>
@@ -7216,10 +7276,10 @@
         <v>0</v>
       </c>
       <c r="E55" s="24">
-        <v>3592100</v>
+        <v>3541800</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>373</v>
+        <v>315</v>
       </c>
       <c r="G55" s="13" t="s">
         <v>245</v>
@@ -7227,13 +7287,13 @@
       <c r="H55" s="13"/>
       <c r="I55" s="13"/>
       <c r="J55" s="24" t="s">
-        <v>372</v>
+        <v>43</v>
       </c>
       <c r="K55" s="24">
         <v>2</v>
       </c>
       <c r="L55" s="24">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="M55" s="24" t="s">
         <v>43</v>
@@ -7288,181 +7348,181 @@
       </c>
     </row>
     <row r="56" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A56" s="21">
-        <v>60010001</v>
-      </c>
-      <c r="B56" s="21">
-        <v>6001</v>
-      </c>
-      <c r="C56" s="21">
-        <v>1</v>
-      </c>
-      <c r="D56" s="21">
-        <v>0</v>
-      </c>
-      <c r="E56" s="21">
-        <v>3600200</v>
+      <c r="A56" s="24">
+        <v>59110001</v>
+      </c>
+      <c r="B56" s="24">
+        <v>5911</v>
+      </c>
+      <c r="C56" s="24">
+        <v>1</v>
+      </c>
+      <c r="D56" s="24">
+        <v>0</v>
+      </c>
+      <c r="E56" s="24">
+        <v>3541800</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="H56" s="13"/>
       <c r="I56" s="13"/>
-      <c r="J56" s="21" t="s">
-        <v>261</v>
-      </c>
-      <c r="K56" s="21">
-        <v>1</v>
-      </c>
-      <c r="L56" s="21">
-        <v>8</v>
-      </c>
-      <c r="M56" s="21" t="s">
-        <v>262</v>
-      </c>
-      <c r="N56" s="21">
+      <c r="J56" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="K56" s="24">
         <v>2</v>
       </c>
-      <c r="O56" s="21">
+      <c r="L56" s="24">
+        <v>5000</v>
+      </c>
+      <c r="M56" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="N56" s="24">
+        <v>0</v>
+      </c>
+      <c r="O56" s="24">
+        <v>0</v>
+      </c>
+      <c r="P56" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q56" s="24">
+        <v>0</v>
+      </c>
+      <c r="R56" s="24">
+        <v>0</v>
+      </c>
+      <c r="S56" s="24">
+        <v>0</v>
+      </c>
+      <c r="T56" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="U56" s="24">
+        <v>-1</v>
+      </c>
+      <c r="V56" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="W56" s="24">
         <v>10000</v>
       </c>
-      <c r="P56" s="21" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q56" s="21">
-        <v>1</v>
-      </c>
-      <c r="R56" s="21">
-        <v>1</v>
-      </c>
-      <c r="S56" s="21">
-        <v>0</v>
-      </c>
-      <c r="T56" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="U56" s="21">
-        <v>0</v>
-      </c>
-      <c r="V56" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="W56" s="21">
-        <v>10000</v>
-      </c>
-      <c r="X56" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y56" s="21">
-        <v>1</v>
-      </c>
-      <c r="Z56" s="21">
-        <v>1</v>
-      </c>
-      <c r="AA56" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB56" s="21">
-        <v>1</v>
-      </c>
-      <c r="AC56" s="21">
+      <c r="X56" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y56" s="24">
+        <v>1</v>
+      </c>
+      <c r="Z56" s="24">
+        <v>1</v>
+      </c>
+      <c r="AA56" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB56" s="24">
+        <v>1</v>
+      </c>
+      <c r="AC56" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A57" s="21">
-        <v>60020001</v>
-      </c>
-      <c r="B57" s="21">
-        <v>6002</v>
-      </c>
-      <c r="C57" s="21">
-        <v>1</v>
-      </c>
-      <c r="D57" s="21">
-        <v>0</v>
-      </c>
-      <c r="E57" s="21">
-        <v>3600400</v>
+      <c r="A57" s="25">
+        <v>59120001</v>
+      </c>
+      <c r="B57" s="24">
+        <v>5912</v>
+      </c>
+      <c r="C57" s="24">
+        <v>1</v>
+      </c>
+      <c r="D57" s="24">
+        <v>0</v>
+      </c>
+      <c r="E57" s="24">
+        <v>3592100</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>258</v>
+        <v>373</v>
       </c>
       <c r="G57" s="13" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="H57" s="13"/>
       <c r="I57" s="13"/>
-      <c r="J57" s="21" t="s">
-        <v>264</v>
-      </c>
-      <c r="K57" s="21">
-        <v>1</v>
-      </c>
-      <c r="L57" s="21">
-        <v>1</v>
-      </c>
-      <c r="M57" s="21" t="s">
-        <v>265</v>
-      </c>
-      <c r="N57" s="21">
+      <c r="J57" s="24" t="s">
+        <v>372</v>
+      </c>
+      <c r="K57" s="24">
         <v>2</v>
       </c>
-      <c r="O57" s="21">
-        <v>15000</v>
-      </c>
-      <c r="P57" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q57" s="21">
-        <v>0</v>
-      </c>
-      <c r="R57" s="21">
-        <v>0</v>
-      </c>
-      <c r="S57" s="21">
-        <v>0</v>
-      </c>
-      <c r="T57" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="U57" s="21">
+      <c r="L57" s="24">
+        <v>0</v>
+      </c>
+      <c r="M57" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="N57" s="24">
+        <v>0</v>
+      </c>
+      <c r="O57" s="24">
+        <v>0</v>
+      </c>
+      <c r="P57" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q57" s="24">
+        <v>0</v>
+      </c>
+      <c r="R57" s="24">
+        <v>0</v>
+      </c>
+      <c r="S57" s="24">
+        <v>0</v>
+      </c>
+      <c r="T57" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="U57" s="24">
         <v>-1</v>
       </c>
-      <c r="V57" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="W57" s="21">
+      <c r="V57" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="W57" s="24">
         <v>10000</v>
       </c>
-      <c r="X57" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y57" s="21">
-        <v>1</v>
-      </c>
-      <c r="Z57" s="21">
-        <v>1</v>
-      </c>
-      <c r="AA57" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB57" s="21">
-        <v>1</v>
-      </c>
-      <c r="AC57" s="21">
+      <c r="X57" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y57" s="24">
+        <v>1</v>
+      </c>
+      <c r="Z57" s="24">
+        <v>1</v>
+      </c>
+      <c r="AA57" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB57" s="24">
+        <v>1</v>
+      </c>
+      <c r="AC57" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A58" s="21">
-        <v>60030001</v>
+        <v>60010001</v>
       </c>
       <c r="B58" s="21">
-        <v>6003</v>
+        <v>6001</v>
       </c>
       <c r="C58" s="21">
         <v>1</v>
@@ -7471,10 +7531,10 @@
         <v>0</v>
       </c>
       <c r="E58" s="21">
-        <v>3600700</v>
+        <v>3600200</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G58" s="13" t="s">
         <v>254</v>
@@ -7482,7 +7542,7 @@
       <c r="H58" s="13"/>
       <c r="I58" s="13"/>
       <c r="J58" s="21" t="s">
-        <v>297</v>
+        <v>261</v>
       </c>
       <c r="K58" s="21">
         <v>1</v>
@@ -7491,7 +7551,7 @@
         <v>8</v>
       </c>
       <c r="M58" s="21" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="N58" s="21">
         <v>2</v>
@@ -7500,7 +7560,7 @@
         <v>10000</v>
       </c>
       <c r="P58" s="21" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="Q58" s="21">
         <v>1</v>
@@ -7544,10 +7604,10 @@
     </row>
     <row r="59" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A59" s="21">
-        <v>60040001</v>
+        <v>60020001</v>
       </c>
       <c r="B59" s="21">
-        <v>6004</v>
+        <v>6002</v>
       </c>
       <c r="C59" s="21">
         <v>1</v>
@@ -7556,10 +7616,10 @@
         <v>0</v>
       </c>
       <c r="E59" s="21">
-        <v>3601000</v>
+        <v>3600400</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G59" s="13" t="s">
         <v>254</v>
@@ -7567,31 +7627,31 @@
       <c r="H59" s="13"/>
       <c r="I59" s="13"/>
       <c r="J59" s="21" t="s">
-        <v>43</v>
+        <v>264</v>
       </c>
       <c r="K59" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="21" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="N59" s="21">
         <v>2</v>
       </c>
       <c r="O59" s="21">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="P59" s="21" t="s">
-        <v>269</v>
+        <v>43</v>
       </c>
       <c r="Q59" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R59" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S59" s="21">
         <v>0</v>
@@ -7600,7 +7660,7 @@
         <v>43</v>
       </c>
       <c r="U59" s="21">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V59" s="21" t="s">
         <v>43</v>
@@ -7629,10 +7689,10 @@
     </row>
     <row r="60" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A60" s="21">
-        <v>60050001</v>
+        <v>60030001</v>
       </c>
       <c r="B60" s="21">
-        <v>6005</v>
+        <v>6003</v>
       </c>
       <c r="C60" s="21">
         <v>1</v>
@@ -7641,10 +7701,10 @@
         <v>0</v>
       </c>
       <c r="E60" s="21">
-        <v>3541600</v>
+        <v>3600700</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>317</v>
+        <v>259</v>
       </c>
       <c r="G60" s="13" t="s">
         <v>254</v>
@@ -7652,31 +7712,31 @@
       <c r="H60" s="13"/>
       <c r="I60" s="13"/>
       <c r="J60" s="21" t="s">
-        <v>119</v>
+        <v>297</v>
       </c>
       <c r="K60" s="21">
+        <v>1</v>
+      </c>
+      <c r="L60" s="21">
+        <v>8</v>
+      </c>
+      <c r="M60" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="N60" s="21">
         <v>2</v>
       </c>
-      <c r="L60" s="21">
-        <v>-2000</v>
-      </c>
-      <c r="M60" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="N60" s="21">
-        <v>0</v>
-      </c>
       <c r="O60" s="21">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P60" s="21" t="s">
-        <v>43</v>
+        <v>267</v>
       </c>
       <c r="Q60" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R60" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S60" s="21">
         <v>0</v>
@@ -7685,7 +7745,7 @@
         <v>43</v>
       </c>
       <c r="U60" s="21">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V60" s="21" t="s">
         <v>43</v>
@@ -7714,10 +7774,10 @@
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A61" s="21">
-        <v>60060001</v>
+        <v>60040001</v>
       </c>
       <c r="B61" s="21">
-        <v>6006</v>
+        <v>6004</v>
       </c>
       <c r="C61" s="21">
         <v>1</v>
@@ -7726,10 +7786,10 @@
         <v>0</v>
       </c>
       <c r="E61" s="21">
-        <v>3541800</v>
+        <v>3601000</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>318</v>
+        <v>260</v>
       </c>
       <c r="G61" s="13" t="s">
         <v>254</v>
@@ -7737,31 +7797,31 @@
       <c r="H61" s="13"/>
       <c r="I61" s="13"/>
       <c r="J61" s="21" t="s">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="K61" s="21">
+        <v>0</v>
+      </c>
+      <c r="L61" s="21">
+        <v>0</v>
+      </c>
+      <c r="M61" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="N61" s="21">
         <v>2</v>
       </c>
-      <c r="L61" s="21">
-        <v>2500</v>
-      </c>
-      <c r="M61" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="N61" s="21">
-        <v>0</v>
-      </c>
       <c r="O61" s="21">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P61" s="21" t="s">
-        <v>43</v>
+        <v>269</v>
       </c>
       <c r="Q61" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R61" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S61" s="21">
         <v>0</v>
@@ -7770,7 +7830,7 @@
         <v>43</v>
       </c>
       <c r="U61" s="21">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V61" s="21" t="s">
         <v>43</v>
@@ -7799,10 +7859,10 @@
     </row>
     <row r="62" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A62" s="21">
-        <v>60070001</v>
+        <v>60050001</v>
       </c>
       <c r="B62" s="21">
-        <v>6007</v>
+        <v>6005</v>
       </c>
       <c r="C62" s="21">
         <v>1</v>
@@ -7811,10 +7871,10 @@
         <v>0</v>
       </c>
       <c r="E62" s="21">
-        <v>3601300</v>
+        <v>3541600</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G62" s="13" t="s">
         <v>254</v>
@@ -7822,28 +7882,28 @@
       <c r="H62" s="13"/>
       <c r="I62" s="13"/>
       <c r="J62" s="21" t="s">
-        <v>270</v>
+        <v>119</v>
       </c>
       <c r="K62" s="21">
         <v>2</v>
       </c>
       <c r="L62" s="21">
-        <v>10000</v>
+        <v>-2000</v>
       </c>
       <c r="M62" s="21" t="s">
-        <v>271</v>
+        <v>43</v>
       </c>
       <c r="N62" s="21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O62" s="21">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="P62" s="21" t="s">
-        <v>272</v>
+        <v>43</v>
       </c>
       <c r="Q62" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R62" s="21">
         <v>0</v>
@@ -7883,181 +7943,181 @@
       </c>
     </row>
     <row r="63" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A63" s="22">
-        <v>61010001</v>
-      </c>
-      <c r="B63" s="22">
-        <v>6101</v>
-      </c>
-      <c r="C63" s="22">
-        <v>1</v>
-      </c>
-      <c r="D63" s="22">
-        <v>0</v>
-      </c>
-      <c r="E63" s="22">
-        <v>3610300</v>
+      <c r="A63" s="21">
+        <v>60060001</v>
+      </c>
+      <c r="B63" s="21">
+        <v>6006</v>
+      </c>
+      <c r="C63" s="21">
+        <v>1</v>
+      </c>
+      <c r="D63" s="21">
+        <v>0</v>
+      </c>
+      <c r="E63" s="21">
+        <v>3541800</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G63" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H63" s="13"/>
       <c r="I63" s="13"/>
-      <c r="J63" s="22" t="s">
-        <v>273</v>
-      </c>
-      <c r="K63" s="22">
-        <v>1</v>
-      </c>
-      <c r="L63" s="22">
-        <v>8</v>
-      </c>
-      <c r="M63" s="22" t="s">
-        <v>274</v>
-      </c>
-      <c r="N63" s="22">
+      <c r="J63" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="K63" s="21">
         <v>2</v>
       </c>
-      <c r="O63" s="22">
+      <c r="L63" s="21">
+        <v>2500</v>
+      </c>
+      <c r="M63" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="N63" s="21">
+        <v>0</v>
+      </c>
+      <c r="O63" s="21">
+        <v>0</v>
+      </c>
+      <c r="P63" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q63" s="21">
+        <v>0</v>
+      </c>
+      <c r="R63" s="21">
+        <v>0</v>
+      </c>
+      <c r="S63" s="21">
+        <v>0</v>
+      </c>
+      <c r="T63" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="U63" s="21">
+        <v>-1</v>
+      </c>
+      <c r="V63" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W63" s="21">
         <v>10000</v>
       </c>
-      <c r="P63" s="22" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q63" s="22">
-        <v>1</v>
-      </c>
-      <c r="R63" s="22">
-        <v>1</v>
-      </c>
-      <c r="S63" s="22">
-        <v>0</v>
-      </c>
-      <c r="T63" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="U63" s="22">
-        <v>0</v>
-      </c>
-      <c r="V63" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="W63" s="22">
-        <v>10000</v>
-      </c>
-      <c r="X63" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y63" s="22">
-        <v>1</v>
-      </c>
-      <c r="Z63" s="22">
-        <v>1</v>
-      </c>
-      <c r="AA63" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB63" s="22">
-        <v>1</v>
-      </c>
-      <c r="AC63" s="22">
+      <c r="X63" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y63" s="21">
+        <v>1</v>
+      </c>
+      <c r="Z63" s="21">
+        <v>1</v>
+      </c>
+      <c r="AA63" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB63" s="21">
+        <v>1</v>
+      </c>
+      <c r="AC63" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A64" s="22">
-        <v>61020001</v>
-      </c>
-      <c r="B64" s="22">
-        <v>6102</v>
-      </c>
-      <c r="C64" s="22">
-        <v>1</v>
-      </c>
-      <c r="D64" s="22">
-        <v>0</v>
-      </c>
-      <c r="E64" s="22">
-        <v>3610500</v>
+      <c r="A64" s="21">
+        <v>60070001</v>
+      </c>
+      <c r="B64" s="21">
+        <v>6007</v>
+      </c>
+      <c r="C64" s="21">
+        <v>1</v>
+      </c>
+      <c r="D64" s="21">
+        <v>0</v>
+      </c>
+      <c r="E64" s="21">
+        <v>3601300</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>299</v>
+        <v>319</v>
       </c>
       <c r="G64" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H64" s="13"/>
       <c r="I64" s="13"/>
-      <c r="J64" s="22" t="s">
-        <v>276</v>
-      </c>
-      <c r="K64" s="22">
+      <c r="J64" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="K64" s="21">
         <v>2</v>
       </c>
-      <c r="L64" s="22">
+      <c r="L64" s="21">
         <v>10000</v>
       </c>
-      <c r="M64" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="N64" s="22">
-        <v>0</v>
-      </c>
-      <c r="O64" s="22">
-        <v>0</v>
-      </c>
-      <c r="P64" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q64" s="22">
-        <v>0</v>
-      </c>
-      <c r="R64" s="22">
-        <v>0</v>
-      </c>
-      <c r="S64" s="22">
-        <v>0</v>
-      </c>
-      <c r="T64" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="U64" s="22">
+      <c r="M64" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="N64" s="21">
+        <v>2</v>
+      </c>
+      <c r="O64" s="21">
+        <v>2000</v>
+      </c>
+      <c r="P64" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q64" s="21">
+        <v>1</v>
+      </c>
+      <c r="R64" s="21">
+        <v>0</v>
+      </c>
+      <c r="S64" s="21">
+        <v>0</v>
+      </c>
+      <c r="T64" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="U64" s="21">
         <v>-1</v>
       </c>
-      <c r="V64" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="W64" s="22">
+      <c r="V64" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W64" s="21">
         <v>10000</v>
       </c>
-      <c r="X64" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y64" s="22">
-        <v>1</v>
-      </c>
-      <c r="Z64" s="22">
-        <v>1</v>
-      </c>
-      <c r="AA64" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB64" s="22">
-        <v>1</v>
-      </c>
-      <c r="AC64" s="22">
+      <c r="X64" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y64" s="21">
+        <v>1</v>
+      </c>
+      <c r="Z64" s="21">
+        <v>1</v>
+      </c>
+      <c r="AA64" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB64" s="21">
+        <v>1</v>
+      </c>
+      <c r="AC64" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A65" s="22">
-        <v>61030001</v>
+        <v>61010001</v>
       </c>
       <c r="B65" s="22">
-        <v>6103</v>
+        <v>6101</v>
       </c>
       <c r="C65" s="22">
         <v>1</v>
@@ -8066,10 +8126,10 @@
         <v>0</v>
       </c>
       <c r="E65" s="22">
-        <v>3610700</v>
+        <v>3610300</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="G65" s="13" t="s">
         <v>255</v>
@@ -8077,16 +8137,16 @@
       <c r="H65" s="13"/>
       <c r="I65" s="13"/>
       <c r="J65" s="22" t="s">
-        <v>43</v>
+        <v>273</v>
       </c>
       <c r="K65" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="22">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M65" s="22" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="N65" s="22">
         <v>2</v>
@@ -8095,7 +8155,7 @@
         <v>10000</v>
       </c>
       <c r="P65" s="22" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="Q65" s="22">
         <v>1</v>
@@ -8139,10 +8199,10 @@
     </row>
     <row r="66" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A66" s="22">
-        <v>61040001</v>
+        <v>61020001</v>
       </c>
       <c r="B66" s="22">
-        <v>6104</v>
+        <v>6102</v>
       </c>
       <c r="C66" s="22">
         <v>1</v>
@@ -8151,10 +8211,10 @@
         <v>0</v>
       </c>
       <c r="E66" s="22">
-        <v>3541400</v>
+        <v>3610500</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>256</v>
+        <v>299</v>
       </c>
       <c r="G66" s="13" t="s">
         <v>255</v>
@@ -8162,13 +8222,13 @@
       <c r="H66" s="13"/>
       <c r="I66" s="13"/>
       <c r="J66" s="22" t="s">
-        <v>118</v>
+        <v>276</v>
       </c>
       <c r="K66" s="22">
         <v>2</v>
       </c>
       <c r="L66" s="22">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="M66" s="22" t="s">
         <v>43</v>
@@ -8224,10 +8284,10 @@
     </row>
     <row r="67" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A67" s="22">
-        <v>61050001</v>
+        <v>61030001</v>
       </c>
       <c r="B67" s="22">
-        <v>6105</v>
+        <v>6103</v>
       </c>
       <c r="C67" s="22">
         <v>1</v>
@@ -8236,10 +8296,10 @@
         <v>0</v>
       </c>
       <c r="E67" s="22">
-        <v>3610900</v>
+        <v>3610700</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="G67" s="13" t="s">
         <v>255</v>
@@ -8247,31 +8307,31 @@
       <c r="H67" s="13"/>
       <c r="I67" s="13"/>
       <c r="J67" s="22" t="s">
-        <v>305</v>
+        <v>43</v>
       </c>
       <c r="K67" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" s="22" t="s">
-        <v>43</v>
+        <v>277</v>
       </c>
       <c r="N67" s="22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O67" s="22">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P67" s="22" t="s">
-        <v>43</v>
+        <v>278</v>
       </c>
       <c r="Q67" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R67" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S67" s="22">
         <v>0</v>
@@ -8280,7 +8340,7 @@
         <v>43</v>
       </c>
       <c r="U67" s="22">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V67" s="22" t="s">
         <v>43</v>
@@ -8309,10 +8369,10 @@
     </row>
     <row r="68" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A68" s="22">
-        <v>61060001</v>
+        <v>61040001</v>
       </c>
       <c r="B68" s="22">
-        <v>6106</v>
+        <v>6104</v>
       </c>
       <c r="C68" s="22">
         <v>1</v>
@@ -8321,10 +8381,10 @@
         <v>0</v>
       </c>
       <c r="E68" s="22">
-        <v>3611100</v>
+        <v>3541400</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>371</v>
+        <v>256</v>
       </c>
       <c r="G68" s="13" t="s">
         <v>255</v>
@@ -8332,13 +8392,13 @@
       <c r="H68" s="13"/>
       <c r="I68" s="13"/>
       <c r="J68" s="22" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="K68" s="22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L68" s="22">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="M68" s="22" t="s">
         <v>43</v>
@@ -8394,10 +8454,10 @@
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A69" s="22">
-        <v>61070001</v>
+        <v>61050001</v>
       </c>
       <c r="B69" s="22">
-        <v>6107</v>
+        <v>6105</v>
       </c>
       <c r="C69" s="22">
         <v>1</v>
@@ -8406,10 +8466,10 @@
         <v>0</v>
       </c>
       <c r="E69" s="22">
-        <v>3611300</v>
+        <v>3610900</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="G69" s="13" t="s">
         <v>255</v>
@@ -8417,13 +8477,13 @@
       <c r="H69" s="13"/>
       <c r="I69" s="13"/>
       <c r="J69" s="22" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K69" s="22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L69" s="22">
-        <v>300000</v>
+        <v>1</v>
       </c>
       <c r="M69" s="22" t="s">
         <v>43</v>
@@ -8435,13 +8495,13 @@
         <v>0</v>
       </c>
       <c r="P69" s="22" t="s">
-        <v>307</v>
+        <v>43</v>
       </c>
       <c r="Q69" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R69" s="22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S69" s="22">
         <v>0</v>
@@ -8479,10 +8539,10 @@
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A70" s="22">
-        <v>61080001</v>
+        <v>61060001</v>
       </c>
       <c r="B70" s="22">
-        <v>6108</v>
+        <v>6106</v>
       </c>
       <c r="C70" s="22">
         <v>1</v>
@@ -8491,10 +8551,10 @@
         <v>0</v>
       </c>
       <c r="E70" s="22">
-        <v>3611500</v>
+        <v>3611100</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>301</v>
+        <v>371</v>
       </c>
       <c r="G70" s="13" t="s">
         <v>255</v>
@@ -8511,22 +8571,22 @@
         <v>0</v>
       </c>
       <c r="M70" s="22" t="s">
-        <v>309</v>
+        <v>43</v>
       </c>
       <c r="N70" s="22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O70" s="22">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="P70" s="22" t="s">
-        <v>310</v>
+        <v>43</v>
       </c>
       <c r="Q70" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R70" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S70" s="22">
         <v>0</v>
@@ -8535,7 +8595,7 @@
         <v>43</v>
       </c>
       <c r="U70" s="22">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V70" s="22" t="s">
         <v>43</v>
@@ -8564,10 +8624,10 @@
     </row>
     <row r="71" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A71" s="22">
-        <v>61090001</v>
+        <v>61070001</v>
       </c>
       <c r="B71" s="22">
-        <v>6109</v>
+        <v>6107</v>
       </c>
       <c r="C71" s="22">
         <v>1</v>
@@ -8576,10 +8636,10 @@
         <v>0</v>
       </c>
       <c r="E71" s="22">
-        <v>3611700</v>
+        <v>3611300</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G71" s="13" t="s">
         <v>255</v>
@@ -8587,7 +8647,7 @@
       <c r="H71" s="13"/>
       <c r="I71" s="13"/>
       <c r="J71" s="22" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K71" s="22">
         <v>3</v>
@@ -8605,13 +8665,13 @@
         <v>0</v>
       </c>
       <c r="P71" s="22" t="s">
-        <v>43</v>
+        <v>307</v>
       </c>
       <c r="Q71" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71" s="22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S71" s="22">
         <v>0</v>
@@ -8649,10 +8709,10 @@
     </row>
     <row r="72" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A72" s="22">
-        <v>61100001</v>
+        <v>61080001</v>
       </c>
       <c r="B72" s="22">
-        <v>6110</v>
+        <v>6108</v>
       </c>
       <c r="C72" s="22">
         <v>1</v>
@@ -8661,10 +8721,10 @@
         <v>0</v>
       </c>
       <c r="E72" s="22">
-        <v>3590800</v>
+        <v>3611500</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G72" s="13" t="s">
         <v>255</v>
@@ -8681,7 +8741,7 @@
         <v>0</v>
       </c>
       <c r="M72" s="22" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="N72" s="22">
         <v>2</v>
@@ -8690,7 +8750,7 @@
         <v>10000</v>
       </c>
       <c r="P72" s="22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q72" s="22">
         <v>1</v>
@@ -8732,8 +8792,178 @@
         <v>0</v>
       </c>
     </row>
+    <row r="73" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A73" s="22">
+        <v>61090001</v>
+      </c>
+      <c r="B73" s="22">
+        <v>6109</v>
+      </c>
+      <c r="C73" s="22">
+        <v>1</v>
+      </c>
+      <c r="D73" s="22">
+        <v>0</v>
+      </c>
+      <c r="E73" s="22">
+        <v>3611700</v>
+      </c>
+      <c r="F73" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="G73" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="H73" s="13"/>
+      <c r="I73" s="13"/>
+      <c r="J73" s="22" t="s">
+        <v>308</v>
+      </c>
+      <c r="K73" s="22">
+        <v>3</v>
+      </c>
+      <c r="L73" s="22">
+        <v>300000</v>
+      </c>
+      <c r="M73" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="N73" s="22">
+        <v>0</v>
+      </c>
+      <c r="O73" s="22">
+        <v>0</v>
+      </c>
+      <c r="P73" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q73" s="22">
+        <v>0</v>
+      </c>
+      <c r="R73" s="22">
+        <v>0</v>
+      </c>
+      <c r="S73" s="22">
+        <v>0</v>
+      </c>
+      <c r="T73" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="U73" s="22">
+        <v>-1</v>
+      </c>
+      <c r="V73" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="W73" s="22">
+        <v>10000</v>
+      </c>
+      <c r="X73" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y73" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z73" s="22">
+        <v>1</v>
+      </c>
+      <c r="AA73" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB73" s="22">
+        <v>1</v>
+      </c>
+      <c r="AC73" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A74" s="22">
+        <v>61100001</v>
+      </c>
+      <c r="B74" s="22">
+        <v>6110</v>
+      </c>
+      <c r="C74" s="22">
+        <v>1</v>
+      </c>
+      <c r="D74" s="22">
+        <v>0</v>
+      </c>
+      <c r="E74" s="22">
+        <v>3590800</v>
+      </c>
+      <c r="F74" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="G74" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="H74" s="13"/>
+      <c r="I74" s="13"/>
+      <c r="J74" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="K74" s="22">
+        <v>0</v>
+      </c>
+      <c r="L74" s="22">
+        <v>0</v>
+      </c>
+      <c r="M74" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="N74" s="22">
+        <v>2</v>
+      </c>
+      <c r="O74" s="22">
+        <v>10000</v>
+      </c>
+      <c r="P74" s="22" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q74" s="22">
+        <v>1</v>
+      </c>
+      <c r="R74" s="22">
+        <v>1</v>
+      </c>
+      <c r="S74" s="22">
+        <v>0</v>
+      </c>
+      <c r="T74" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="U74" s="22">
+        <v>0</v>
+      </c>
+      <c r="V74" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="W74" s="22">
+        <v>10000</v>
+      </c>
+      <c r="X74" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y74" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z74" s="22">
+        <v>1</v>
+      </c>
+      <c r="AA74" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB74" s="22">
+        <v>1</v>
+      </c>
+      <c r="AC74" s="22">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:AC72" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:AC74" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E89779E-6FAA-4DF9-B7FD-A79767996087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{776A8CC2-4CF7-4493-B8DB-29542E5A2266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -460,1442 +460,1443 @@
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
+    <t>3540401:1</t>
+  </si>
+  <si>
+    <t>3540402:1</t>
+  </si>
+  <si>
+    <t>3540601:1</t>
+  </si>
+  <si>
+    <t>3540602:1</t>
+  </si>
+  <si>
+    <t>3540801:1</t>
+  </si>
+  <si>
+    <t>3540802:1</t>
+  </si>
+  <si>
+    <t>3541001:1</t>
+  </si>
+  <si>
+    <t>3541002:1</t>
+  </si>
+  <si>
+    <t>3541201:1</t>
+  </si>
+  <si>
+    <t>3541401:1</t>
+  </si>
+  <si>
+    <t>3541601:1</t>
+  </si>
+  <si>
+    <t>3541602:1</t>
+  </si>
+  <si>
+    <t>3541801:1</t>
+  </si>
+  <si>
+    <t>3541802:1</t>
+  </si>
+  <si>
+    <t>3542001:1</t>
+  </si>
+  <si>
+    <t>3542002:1</t>
+  </si>
+  <si>
+    <t>3542201:1</t>
+  </si>
+  <si>
+    <t>3542202:1</t>
+  </si>
+  <si>
+    <t>3542401:1</t>
+  </si>
+  <si>
+    <t>3540205:1</t>
+  </si>
+  <si>
+    <t>3540207:1</t>
+  </si>
+  <si>
+    <t>3540405:1</t>
+  </si>
+  <si>
+    <t>3540407:1</t>
+  </si>
+  <si>
+    <t>3540605:1</t>
+  </si>
+  <si>
+    <t>3540607:1</t>
+  </si>
+  <si>
+    <t>3540805:1</t>
+  </si>
+  <si>
+    <t>3540807:1</t>
+  </si>
+  <si>
+    <t>3541005:1</t>
+  </si>
+  <si>
+    <t>3541007:1</t>
+  </si>
+  <si>
+    <t>3541205:1</t>
+  </si>
+  <si>
+    <t>3541207:1</t>
+  </si>
+  <si>
+    <t>3541405:1</t>
+  </si>
+  <si>
+    <t>3541407:1</t>
+  </si>
+  <si>
+    <t>3541605:1</t>
+  </si>
+  <si>
+    <t>3541607:1</t>
+  </si>
+  <si>
+    <t>3541805:1</t>
+  </si>
+  <si>
+    <t>3541807:1</t>
+  </si>
+  <si>
+    <t>3542005:1</t>
+  </si>
+  <si>
+    <t>3542007:1</t>
+  </si>
+  <si>
+    <t>3542205:1</t>
+  </si>
+  <si>
+    <t>3542207:1</t>
+  </si>
+  <si>
+    <t>3542405:1</t>
+  </si>
+  <si>
+    <t>3542407:1</t>
+  </si>
+  <si>
+    <t>3551302:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3551501:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>多重冰霜新星</t>
+  </si>
+  <si>
+    <t>冰霜新星造成冰冻几率提高</t>
+  </si>
+  <si>
+    <t>冰冻时受到冰元素伤害</t>
+  </si>
+  <si>
+    <t>释放冰霜新星时，对敌人造成的冰冻几率增加【参数1万分比】</t>
+  </si>
+  <si>
+    <t>双重冰冻造成额外伤害</t>
+  </si>
+  <si>
+    <t>冰冻命中造成额外伤害</t>
+  </si>
+  <si>
+    <t>击中冰冻目标造成额外伤害</t>
+  </si>
+  <si>
+    <t>冰霜新星额外冰冻几率</t>
+  </si>
+  <si>
+    <t>攻击次数触发冰霜新星</t>
+  </si>
+  <si>
+    <t>攻击使目标冰冻</t>
+  </si>
+  <si>
+    <t>3550902:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击速度提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>攻击提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>防御提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>生命提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>击中回血效果提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>暴击几率提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>暴击伤害提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>受到伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>持续伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>受到持续伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>移动速度提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>获取护盾提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>全属性伤害提高</t>
+  </si>
+  <si>
+    <t>受到全属性伤害提高</t>
+  </si>
+  <si>
+    <t>全属性持续伤害提高</t>
+  </si>
+  <si>
+    <t>受到全属性持续伤害提高</t>
+  </si>
+  <si>
+    <t>移动速度提高</t>
+  </si>
+  <si>
+    <t>获取护盾提高</t>
+  </si>
+  <si>
+    <t>技能效果-通用</t>
+  </si>
+  <si>
+    <t>技能效果-冰</t>
+  </si>
+  <si>
+    <t>获取护盾提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>中毒死亡释放瘟疫</t>
+  </si>
+  <si>
+    <t>瘟疫状态</t>
+  </si>
+  <si>
+    <t>技能效果-火</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果-电</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果-毒</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧状态</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动释放陨石</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧状态受到伤害提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石造成燃烧命中率增加</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧时死亡触发死亡爆炸</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触电状态</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪电链弹射效果</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击触发释放闪电链</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触电时受到伤害提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发触电伤害时释放电磁爆炸</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>中毒状态</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击触发传染</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3560201:1</t>
+  </si>
+  <si>
+    <t>3560202:1</t>
+  </si>
+  <si>
+    <t>3560205:1</t>
+  </si>
+  <si>
+    <t>3560206:1</t>
+  </si>
+  <si>
+    <t>3560501:2</t>
+  </si>
+  <si>
+    <t>3560502:1</t>
+  </si>
+  <si>
+    <t>3560503:1</t>
+  </si>
+  <si>
+    <t>3560701:1</t>
+  </si>
+  <si>
+    <t>3560901:1</t>
+  </si>
+  <si>
+    <t>3570201:1</t>
+  </si>
+  <si>
+    <t>3570202:1</t>
+  </si>
+  <si>
+    <t>3570501:1</t>
+  </si>
+  <si>
+    <t>3570502:1</t>
+  </si>
+  <si>
+    <t>3570701:2</t>
+  </si>
+  <si>
+    <t>3570702:1</t>
+  </si>
+  <si>
+    <t>3570703:1</t>
+  </si>
+  <si>
+    <t>3570901:1</t>
+  </si>
+  <si>
+    <t>3571101:1</t>
+  </si>
+  <si>
+    <t>3571102:1</t>
+  </si>
+  <si>
+    <t>3571103:1</t>
+  </si>
+  <si>
+    <t>3580201:1</t>
+  </si>
+  <si>
+    <t>3580202:1</t>
+  </si>
+  <si>
+    <t>3580207:1</t>
+  </si>
+  <si>
+    <t>3580501:2</t>
+  </si>
+  <si>
+    <t>3580502:1</t>
+  </si>
+  <si>
+    <t>3580503:1</t>
+  </si>
+  <si>
+    <t>3580701:1</t>
+  </si>
+  <si>
+    <t>3580902:1</t>
+  </si>
+  <si>
+    <t>3580903:1</t>
+  </si>
+  <si>
+    <t>3561102:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3561103:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>每【参数1】次攻击，有【参数2万分比】的几率触发【参数3】次【参数4技能id】</t>
+  </si>
+  <si>
+    <t>燃烧时，受到全种类攻击承受伤害提高【参数1万分比】</t>
+  </si>
+  <si>
+    <t>陨石造成伤害时，燃烧效果的命中率提升【参数1万分比】</t>
+  </si>
+  <si>
+    <t>燃烧时，死亡，有【参数2万分比】的几率触发【参数3】次【参数4技能id】</t>
+  </si>
+  <si>
+    <t>每次受到攻击会额外受到等同于[电元素最终伤害]【参数1万分比】</t>
+  </si>
+  <si>
+    <t>闪电链可弹射【参数1】次，同1个目标最多可被选择【参数2】次，每次弹射造成的伤害降低第1次命中造成伤害的【参数3万分比】</t>
+  </si>
+  <si>
+    <t>触电时，触发触电伤害，有【参数2万分比】的几率触发【参数3】次【参数4技能id】</t>
+  </si>
+  <si>
+    <t>【瘟疫：附近任意目标施加瘟疫状态。】</t>
+  </si>
+  <si>
+    <t>3571302:1</t>
+  </si>
+  <si>
+    <t>3571303:1</t>
+  </si>
+  <si>
+    <t>技能效果-生存</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>损失血量触发获得护盾</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得护盾</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>有护盾时触发技能受到全属性伤害降低</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀触发额外回血</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>额外回复击回X倍的血量</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命值大于等于百万分比时触发技能触发全属性伤害提升</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命值低于百万分比时触发技能触发受到全属性伤害降低</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡时触发技能复活</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果-范围</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果-伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击伤害提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击触发释放技能多重打击</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>多重打击效果，额外造成X次X%的伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击触发释放旋风斩</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>旋风斩触发释放半月斩</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3600201:2</t>
+  </si>
+  <si>
+    <t>3600202:1</t>
+  </si>
+  <si>
+    <t>3600203:1</t>
+  </si>
+  <si>
+    <t>3600401:1</t>
+  </si>
+  <si>
+    <t>3600402:1</t>
+  </si>
+  <si>
+    <t>3600702:1</t>
+  </si>
+  <si>
+    <t>3600703:1</t>
+  </si>
+  <si>
+    <t>3601002:1</t>
+  </si>
+  <si>
+    <t>3601003:1</t>
+  </si>
+  <si>
+    <t>3601301:1</t>
+  </si>
+  <si>
+    <t>3601302:1</t>
+  </si>
+  <si>
+    <t>3601303:1</t>
+  </si>
+  <si>
+    <t>3610301:1</t>
+  </si>
+  <si>
+    <t>3610302:1</t>
+  </si>
+  <si>
+    <t>3610303:1</t>
+  </si>
+  <si>
+    <t>3610501:1</t>
+  </si>
+  <si>
+    <t>3610702:1</t>
+  </si>
+  <si>
+    <t>3610703:1</t>
+  </si>
+  <si>
+    <t>3590201:1</t>
+  </si>
+  <si>
+    <t>3590202:1</t>
+  </si>
+  <si>
+    <t>3590203:1</t>
+  </si>
+  <si>
+    <t>3590401:1</t>
+  </si>
+  <si>
+    <t>3590602:1</t>
+  </si>
+  <si>
+    <t>3590603:1</t>
+  </si>
+  <si>
+    <t>3590802:1</t>
+  </si>
+  <si>
+    <t>3590803:1</t>
+  </si>
+  <si>
+    <t>3591001:1</t>
+  </si>
+  <si>
+    <t>3591201:1</t>
+  </si>
+  <si>
+    <t>3591202:1</t>
+  </si>
+  <si>
+    <t>3591203:1</t>
+  </si>
+  <si>
+    <t>3591401:1</t>
+  </si>
+  <si>
+    <t>3591402:1</t>
+  </si>
+  <si>
+    <t>3591403:1</t>
+  </si>
+  <si>
+    <t>3591602:1</t>
+  </si>
+  <si>
+    <t>3591603:1</t>
+  </si>
+  <si>
+    <t>3591902:1</t>
+  </si>
+  <si>
+    <t>3600701:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击次数触发技能重击</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>重击技能暴击率提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能攻击累计额外次数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>斩杀暴击触发斩杀血线变化</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀触发暴击率提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击触发技能暴击伤害提高、致命暴击、额外次数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3590802:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3610901:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611301:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611303:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611701:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611502:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611503:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3590803:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能名称</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数描述</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>有护盾时受到伤害降低</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>低血时受到伤害降低</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能效果-敌人伤害降低</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能效果-敌人受到伤害提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能效果-光环效果影响范围变化</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标血量低于百万分比触发斩杀</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>斩杀血线提高效果</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581201:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581202:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581207:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3570902:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>MAP&lt;INT:INT&gt;_S</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT_S</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>attr_value_8_variable_id</t>
+  </si>
+  <si>
+    <t>attr_value_8_type</t>
+  </si>
+  <si>
+    <t>attr_value_8</t>
+  </si>
+  <si>
+    <t>参数8关联的变量id</t>
+  </si>
+  <si>
+    <t>参数8数值类型</t>
+  </si>
+  <si>
+    <t>参数8</t>
+  </si>
+  <si>
+    <t>每【参数8】毫秒，造成{[火元素直接伤害]【参数1万分比】}，【参数2】的[额外火元素持续伤害]，效果持续【参数5】毫秒，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>每【参数8】毫秒，触发等同于[毒元素直接伤害]*【参数1万分比毒持续buff系数】+【参数2】的[额外毒持续伤害]，效果持续【持续5】毫秒，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>每【参数8】毫秒，触发等同于[毒元素直接伤害]*【参数1万分比毒持续buff系数】+【参数2】的[额外毒持续伤害]，状态持续【持续5】毫秒，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>3041108:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>拥有这个技能效果时，命中敌人时，攻击者回复固定值【参数1固定值】的血量，触发冷却时间【参数8】毫秒</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3560208:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3580208:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581208:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3591002:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3591003:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧时，被攻击受到额外伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧时被攻击受到额外伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触电时，[受到所有类型伤害提高]【参数1万分比】+【参数2】受到[受到所有类型额外伤害固定值]</t>
+  </si>
+  <si>
+    <t>触电时受到伤害提高</t>
+  </si>
+  <si>
+    <t>3570503:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>使目标触电时，造成1次触电伤害</t>
+  </si>
+  <si>
+    <t>使目标触电时，造成1次触电伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰冻状态，持续时间【参数5】，冰冻状态命中率【参数6命中率】</t>
+  </si>
+  <si>
+    <t>每攻击【参数1】次，有【参数2】几率触发【参数3】次指定技能【参数4】</t>
+  </si>
+  <si>
+    <t>每【参数8】毫秒，在释放冰霜新星时有【参数2】几率，触发【参数3】次数，技能id【参数4】</t>
+  </si>
+  <si>
+    <t>对冰冻有配置标再次触发冰冻效果时，造成{[最终冰元素伤害]【参数1万分比】+【参数2固定值】}的[最终冰元素伤害</t>
+  </si>
+  <si>
+    <t>使目标冰冻时，触发目标{生命最大值【参数1百万分比】}的[冰元素基础伤害]+{【参数2固定值】}的[额外冰元素伤害固定值]</t>
+  </si>
+  <si>
+    <t>攻击冰冻目标时，造成{[冰元素最终伤害]【参数1万分比】+【参数2固定值】}的[额外最终冰元素伤害]，该效果每【参数8】毫秒触发1次。</t>
+  </si>
+  <si>
+    <t>攻击冰冻目标时造成额外伤害</t>
+  </si>
+  <si>
+    <t>中毒目标再次中毒受到额外中毒伤害</t>
+  </si>
+  <si>
+    <t>中毒目标再次中毒时，造成每次中毒结算伤害*【参数1】次数*【参数2万分比】的[最终毒元素伤害]</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3580702:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>复活回复血量、触发次数、触发间隔</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3591908:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3561401:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3561402:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3561408:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧时，被攻击会额外受到1次[最终火元素伤害]【参数1万分比】+【参数2固定值】的[额外最终火元素伤害]，该效果每【参数8】毫秒触发1次。</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3570205:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3580205:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581205:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3590405:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>致命暴击状态攻速提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3592101:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回血效果提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3551103:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数8结算间隔时间</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>逻辑属性id</t>
+  </si>
+  <si>
+    <t>技能效果</t>
+  </si>
+  <si>
+    <t>技能名称</t>
+  </si>
+  <si>
+    <t>参数描述</t>
+  </si>
+  <si>
+    <t>效果叠加层数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>结算间隔时间（毫秒）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复中buff组的cd时间（毫秒）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数5</t>
+  </si>
+  <si>
+    <t>参数6</t>
+  </si>
+  <si>
+    <t>持续时间（毫秒）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果最大叠加层数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果基础命中率（万分比）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果触发间隔（毫秒）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数4LIST</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发的技能id</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数9</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数10</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数11</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数12</t>
+  </si>
+  <si>
+    <t>参数13</t>
+  </si>
+  <si>
+    <t>击中回复生命值-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击中回复效果提高万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回复生命-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数14</t>
+  </si>
+  <si>
+    <t>参数15</t>
+  </si>
+  <si>
+    <t>参数16</t>
+  </si>
+  <si>
+    <t>击中回复生命值-自身最大生命值百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回复生命-自身最大生命值百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回复生命-目标最大生命值百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数17</t>
+  </si>
+  <si>
+    <t>参数18</t>
+  </si>
+  <si>
+    <t>参数19</t>
+  </si>
+  <si>
+    <t>参数20</t>
+  </si>
+  <si>
+    <t>参数21</t>
+  </si>
+  <si>
+    <t>参数22</t>
+  </si>
+  <si>
+    <t>参数28</t>
+  </si>
+  <si>
+    <t>参数29</t>
+  </si>
+  <si>
+    <t>获得护盾-自身生命百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得护盾-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得护盾效果提高万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回复生命效果提高万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得护盾-自身已损失生命万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>复活</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发自动技能</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数30</t>
+  </si>
+  <si>
+    <t>参数31</t>
+  </si>
+  <si>
+    <t>参数32</t>
+  </si>
+  <si>
+    <t>参数33</t>
+  </si>
+  <si>
+    <t>参数34</t>
+  </si>
+  <si>
+    <t>参数35</t>
+  </si>
+  <si>
+    <t>参数36</t>
+  </si>
+  <si>
+    <t>参数37</t>
+  </si>
+  <si>
+    <t>参数38</t>
+  </si>
+  <si>
+    <t>参数39</t>
+  </si>
+  <si>
+    <t>参数40</t>
+  </si>
+  <si>
+    <t>参数41</t>
+  </si>
+  <si>
+    <t>参数42</t>
+  </si>
+  <si>
+    <t>参数43</t>
+  </si>
+  <si>
+    <t>参数44</t>
+  </si>
+  <si>
+    <t>主动技能</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>回复生命</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击中目标</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰霜新星</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪电链</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>传染</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>瘟疫</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>多重打击</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>旋风斩</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>斩杀</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>半月斩</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡爆炸</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>电磁爆发</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>重击</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能增加-万分比</t>
+  </si>
+  <si>
+    <t>技能增加-普通攻击范围万分比</t>
+  </si>
+  <si>
+    <t>攻击提高-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御提高-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击提高-攻击的元素类型</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数25LIST</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数45</t>
+  </si>
+  <si>
+    <t>参数46</t>
+  </si>
+  <si>
+    <t>参数47</t>
+  </si>
+  <si>
+    <t>参数48</t>
+  </si>
+  <si>
+    <t>参数49</t>
+  </si>
+  <si>
+    <t>参数50</t>
+  </si>
+  <si>
+    <t>参数51</t>
+  </si>
+  <si>
+    <t>参数52</t>
+  </si>
+  <si>
+    <t>参数53</t>
+  </si>
+  <si>
+    <t>参数54</t>
+  </si>
+  <si>
+    <t>参数55</t>
+  </si>
+  <si>
+    <t>参数56</t>
+  </si>
+  <si>
+    <t>生命上限提高-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命上限提高-百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击速度提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动速度提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击范围提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击目标数量提高-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能增加-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT_S</t>
+  </si>
+  <si>
+    <t>auto_cd</t>
+  </si>
+  <si>
+    <t>参数-重复触发自动释放冷却时间（毫秒）</t>
+  </si>
+  <si>
+    <t>release_ratio</t>
+  </si>
+  <si>
+    <t>参数-释放几率</t>
+  </si>
+  <si>
+    <t>release_num</t>
+  </si>
+  <si>
+    <t>参数-释放次数</t>
+  </si>
+  <si>
+    <t>LIST&lt;INT&gt;_S</t>
+  </si>
+  <si>
+    <t>skill_id</t>
+  </si>
+  <si>
+    <t>参数-释放的技能id</t>
+  </si>
+  <si>
+    <t>total_attack_num</t>
+  </si>
+  <si>
+    <t>参数-累计发起攻击次数时</t>
+  </si>
+  <si>
+    <t>lose_hp_ratio</t>
+  </si>
+  <si>
+    <t>参数-损失自身生命最大值百万分比时</t>
+  </si>
+  <si>
+    <t>kill_target_after</t>
+  </si>
+  <si>
+    <t>参数-击杀目标后</t>
+  </si>
+  <si>
+    <t>after_attack_crit</t>
+  </si>
+  <si>
+    <t>参数-攻击暴击后</t>
+  </si>
+  <si>
+    <t>after_use_skill</t>
+  </si>
+  <si>
+    <t>参数-释放【技能id】后</t>
+  </si>
+  <si>
+    <t>cycle_time</t>
+  </si>
+  <si>
+    <t>参数-每过固定时间（毫秒）时</t>
+  </si>
+  <si>
+    <t>after_skill_hit</t>
+  </si>
+  <si>
+    <t>参数-【技能id】命中后</t>
+  </si>
+  <si>
+    <t>after_self_death</t>
+  </si>
+  <si>
+    <t>参数-自身死亡后释放</t>
+  </si>
+  <si>
+    <t>MAP&lt;INT:INT&gt;_S</t>
+  </si>
+  <si>
+    <t>self_have_effect</t>
+  </si>
+  <si>
+    <t>参数-自身拥有【效果id：&gt;=层数】时</t>
+  </si>
+  <si>
+    <t>target_have_effect</t>
+  </si>
+  <si>
+    <t>参数-目标拥有【效果id：&gt;=层数】时</t>
+  </si>
+  <si>
+    <t>target_hp_ratio_over</t>
+  </si>
+  <si>
+    <t>参数-目标当前生命值&gt;=最大生命值的百万分之X时</t>
+  </si>
+  <si>
+    <t>target_hp_ratio_under</t>
+  </si>
+  <si>
+    <t>参数-目标当前生命值&lt;=最大生命值的百万分之X时</t>
+  </si>
+  <si>
+    <t>to_target_effect_hit</t>
+  </si>
+  <si>
+    <t>参数-对目标施加【效果id】命中时</t>
+  </si>
+  <si>
+    <t>order</t>
+  </si>
+  <si>
+    <t>自动</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>受到的伤害总加成</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成伤害总加成</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成的伤害总加成【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到的伤害总加成【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542801:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542601:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3543001:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542607:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542807:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3543007:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542605:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542805:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3543005:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
     <t>3540201:1</t>
-  </si>
-  <si>
-    <t>3540401:1</t>
-  </si>
-  <si>
-    <t>3540402:1</t>
-  </si>
-  <si>
-    <t>3540601:1</t>
-  </si>
-  <si>
-    <t>3540602:1</t>
-  </si>
-  <si>
-    <t>3540801:1</t>
-  </si>
-  <si>
-    <t>3540802:1</t>
-  </si>
-  <si>
-    <t>3541001:1</t>
-  </si>
-  <si>
-    <t>3541002:1</t>
-  </si>
-  <si>
-    <t>3541201:1</t>
-  </si>
-  <si>
-    <t>3541401:1</t>
-  </si>
-  <si>
-    <t>3541601:1</t>
-  </si>
-  <si>
-    <t>3541602:1</t>
-  </si>
-  <si>
-    <t>3541801:1</t>
-  </si>
-  <si>
-    <t>3541802:1</t>
-  </si>
-  <si>
-    <t>3542001:1</t>
-  </si>
-  <si>
-    <t>3542002:1</t>
-  </si>
-  <si>
-    <t>3542201:1</t>
-  </si>
-  <si>
-    <t>3542202:1</t>
-  </si>
-  <si>
-    <t>3542401:1</t>
-  </si>
-  <si>
-    <t>3540205:1</t>
-  </si>
-  <si>
-    <t>3540207:1</t>
-  </si>
-  <si>
-    <t>3540405:1</t>
-  </si>
-  <si>
-    <t>3540407:1</t>
-  </si>
-  <si>
-    <t>3540605:1</t>
-  </si>
-  <si>
-    <t>3540607:1</t>
-  </si>
-  <si>
-    <t>3540805:1</t>
-  </si>
-  <si>
-    <t>3540807:1</t>
-  </si>
-  <si>
-    <t>3541005:1</t>
-  </si>
-  <si>
-    <t>3541007:1</t>
-  </si>
-  <si>
-    <t>3541205:1</t>
-  </si>
-  <si>
-    <t>3541207:1</t>
-  </si>
-  <si>
-    <t>3541405:1</t>
-  </si>
-  <si>
-    <t>3541407:1</t>
-  </si>
-  <si>
-    <t>3541605:1</t>
-  </si>
-  <si>
-    <t>3541607:1</t>
-  </si>
-  <si>
-    <t>3541805:1</t>
-  </si>
-  <si>
-    <t>3541807:1</t>
-  </si>
-  <si>
-    <t>3542005:1</t>
-  </si>
-  <si>
-    <t>3542007:1</t>
-  </si>
-  <si>
-    <t>3542205:1</t>
-  </si>
-  <si>
-    <t>3542207:1</t>
-  </si>
-  <si>
-    <t>3542405:1</t>
-  </si>
-  <si>
-    <t>3542407:1</t>
-  </si>
-  <si>
-    <t>3551302:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3551501:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>多重冰霜新星</t>
-  </si>
-  <si>
-    <t>冰霜新星造成冰冻几率提高</t>
-  </si>
-  <si>
-    <t>冰冻时受到冰元素伤害</t>
-  </si>
-  <si>
-    <t>释放冰霜新星时，对敌人造成的冰冻几率增加【参数1万分比】</t>
-  </si>
-  <si>
-    <t>双重冰冻造成额外伤害</t>
-  </si>
-  <si>
-    <t>冰冻命中造成额外伤害</t>
-  </si>
-  <si>
-    <t>击中冰冻目标造成额外伤害</t>
-  </si>
-  <si>
-    <t>冰霜新星额外冰冻几率</t>
-  </si>
-  <si>
-    <t>攻击次数触发冰霜新星</t>
-  </si>
-  <si>
-    <t>攻击使目标冰冻</t>
-  </si>
-  <si>
-    <t>3550902:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击速度提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>攻击提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>防御提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>生命提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>击中回血效果提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>暴击几率提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>暴击伤害提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>受到伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>持续伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>受到持续伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>移动速度提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>获取护盾提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>全属性伤害提高</t>
-  </si>
-  <si>
-    <t>受到全属性伤害提高</t>
-  </si>
-  <si>
-    <t>全属性持续伤害提高</t>
-  </si>
-  <si>
-    <t>受到全属性持续伤害提高</t>
-  </si>
-  <si>
-    <t>移动速度提高</t>
-  </si>
-  <si>
-    <t>获取护盾提高</t>
-  </si>
-  <si>
-    <t>技能效果-通用</t>
-  </si>
-  <si>
-    <t>技能效果-冰</t>
-  </si>
-  <si>
-    <t>获取护盾提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>中毒死亡释放瘟疫</t>
-  </si>
-  <si>
-    <t>瘟疫状态</t>
-  </si>
-  <si>
-    <t>技能效果-火</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能效果-电</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能效果-毒</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧状态</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>自动释放陨石</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧状态受到伤害提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>陨石造成燃烧命中率增加</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧时死亡触发死亡爆炸</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>触电状态</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>闪电链弹射效果</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击触发释放闪电链</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>触电时受到伤害提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>触发触电伤害时释放电磁爆炸</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>中毒状态</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击触发传染</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3560201:1</t>
-  </si>
-  <si>
-    <t>3560202:1</t>
-  </si>
-  <si>
-    <t>3560205:1</t>
-  </si>
-  <si>
-    <t>3560206:1</t>
-  </si>
-  <si>
-    <t>3560501:2</t>
-  </si>
-  <si>
-    <t>3560502:1</t>
-  </si>
-  <si>
-    <t>3560503:1</t>
-  </si>
-  <si>
-    <t>3560701:1</t>
-  </si>
-  <si>
-    <t>3560901:1</t>
-  </si>
-  <si>
-    <t>3570201:1</t>
-  </si>
-  <si>
-    <t>3570202:1</t>
-  </si>
-  <si>
-    <t>3570501:1</t>
-  </si>
-  <si>
-    <t>3570502:1</t>
-  </si>
-  <si>
-    <t>3570701:2</t>
-  </si>
-  <si>
-    <t>3570702:1</t>
-  </si>
-  <si>
-    <t>3570703:1</t>
-  </si>
-  <si>
-    <t>3570901:1</t>
-  </si>
-  <si>
-    <t>3571101:1</t>
-  </si>
-  <si>
-    <t>3571102:1</t>
-  </si>
-  <si>
-    <t>3571103:1</t>
-  </si>
-  <si>
-    <t>3580201:1</t>
-  </si>
-  <si>
-    <t>3580202:1</t>
-  </si>
-  <si>
-    <t>3580207:1</t>
-  </si>
-  <si>
-    <t>3580501:2</t>
-  </si>
-  <si>
-    <t>3580502:1</t>
-  </si>
-  <si>
-    <t>3580503:1</t>
-  </si>
-  <si>
-    <t>3580701:1</t>
-  </si>
-  <si>
-    <t>3580902:1</t>
-  </si>
-  <si>
-    <t>3580903:1</t>
-  </si>
-  <si>
-    <t>3561102:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3561103:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>每【参数1】次攻击，有【参数2万分比】的几率触发【参数3】次【参数4技能id】</t>
-  </si>
-  <si>
-    <t>燃烧时，受到全种类攻击承受伤害提高【参数1万分比】</t>
-  </si>
-  <si>
-    <t>陨石造成伤害时，燃烧效果的命中率提升【参数1万分比】</t>
-  </si>
-  <si>
-    <t>燃烧时，死亡，有【参数2万分比】的几率触发【参数3】次【参数4技能id】</t>
-  </si>
-  <si>
-    <t>每次受到攻击会额外受到等同于[电元素最终伤害]【参数1万分比】</t>
-  </si>
-  <si>
-    <t>闪电链可弹射【参数1】次，同1个目标最多可被选择【参数2】次，每次弹射造成的伤害降低第1次命中造成伤害的【参数3万分比】</t>
-  </si>
-  <si>
-    <t>触电时，触发触电伤害，有【参数2万分比】的几率触发【参数3】次【参数4技能id】</t>
-  </si>
-  <si>
-    <t>【瘟疫：附近任意目标施加瘟疫状态。】</t>
-  </si>
-  <si>
-    <t>3571302:1</t>
-  </si>
-  <si>
-    <t>3571303:1</t>
-  </si>
-  <si>
-    <t>技能效果-生存</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>损失血量触发获得护盾</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得护盾</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>有护盾时触发技能受到全属性伤害降低</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀触发额外回血</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>额外回复击回X倍的血量</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>生命值大于等于百万分比时触发技能触发全属性伤害提升</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>生命值低于百万分比时触发技能触发受到全属性伤害降低</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>死亡时触发技能复活</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能效果-范围</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能效果-伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴击伤害提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击触发释放技能多重打击</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>多重打击效果，额外造成X次X%的伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击触发释放旋风斩</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>旋风斩触发释放半月斩</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3600201:2</t>
-  </si>
-  <si>
-    <t>3600202:1</t>
-  </si>
-  <si>
-    <t>3600203:1</t>
-  </si>
-  <si>
-    <t>3600401:1</t>
-  </si>
-  <si>
-    <t>3600402:1</t>
-  </si>
-  <si>
-    <t>3600702:1</t>
-  </si>
-  <si>
-    <t>3600703:1</t>
-  </si>
-  <si>
-    <t>3601002:1</t>
-  </si>
-  <si>
-    <t>3601003:1</t>
-  </si>
-  <si>
-    <t>3601301:1</t>
-  </si>
-  <si>
-    <t>3601302:1</t>
-  </si>
-  <si>
-    <t>3601303:1</t>
-  </si>
-  <si>
-    <t>3610301:1</t>
-  </si>
-  <si>
-    <t>3610302:1</t>
-  </si>
-  <si>
-    <t>3610303:1</t>
-  </si>
-  <si>
-    <t>3610501:1</t>
-  </si>
-  <si>
-    <t>3610702:1</t>
-  </si>
-  <si>
-    <t>3610703:1</t>
-  </si>
-  <si>
-    <t>3590201:1</t>
-  </si>
-  <si>
-    <t>3590202:1</t>
-  </si>
-  <si>
-    <t>3590203:1</t>
-  </si>
-  <si>
-    <t>3590401:1</t>
-  </si>
-  <si>
-    <t>3590602:1</t>
-  </si>
-  <si>
-    <t>3590603:1</t>
-  </si>
-  <si>
-    <t>3590802:1</t>
-  </si>
-  <si>
-    <t>3590803:1</t>
-  </si>
-  <si>
-    <t>3591001:1</t>
-  </si>
-  <si>
-    <t>3591201:1</t>
-  </si>
-  <si>
-    <t>3591202:1</t>
-  </si>
-  <si>
-    <t>3591203:1</t>
-  </si>
-  <si>
-    <t>3591401:1</t>
-  </si>
-  <si>
-    <t>3591402:1</t>
-  </si>
-  <si>
-    <t>3591403:1</t>
-  </si>
-  <si>
-    <t>3591602:1</t>
-  </si>
-  <si>
-    <t>3591603:1</t>
-  </si>
-  <si>
-    <t>3591902:1</t>
-  </si>
-  <si>
-    <t>3600701:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击次数触发技能重击</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>重击技能暴击率提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能攻击累计额外次数</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>斩杀暴击触发斩杀血线变化</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀触发暴击率提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴击触发技能暴击伤害提高、致命暴击、额外次数</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3590802:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3610901:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611301:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611303:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611701:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611502:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611503:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3590803:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能名称</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能效果</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数描述</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>有护盾时受到伤害降低</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>低血时受到伤害降低</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>光环技能效果-敌人伤害降低</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>光环技能效果-敌人受到伤害提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>光环技能效果-光环效果影响范围变化</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标血量低于百万分比触发斩杀</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>斩杀血线提高效果</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581201:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581202:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581207:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3570902:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>MAP&lt;INT:INT&gt;_S</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>INT_S</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>attr_value_8_variable_id</t>
-  </si>
-  <si>
-    <t>attr_value_8_type</t>
-  </si>
-  <si>
-    <t>attr_value_8</t>
-  </si>
-  <si>
-    <t>参数8关联的变量id</t>
-  </si>
-  <si>
-    <t>参数8数值类型</t>
-  </si>
-  <si>
-    <t>参数8</t>
-  </si>
-  <si>
-    <t>每【参数8】毫秒，造成{[火元素直接伤害]【参数1万分比】}，【参数2】的[额外火元素持续伤害]，效果持续【参数5】毫秒，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>每【参数8】毫秒，触发等同于[毒元素直接伤害]*【参数1万分比毒持续buff系数】+【参数2】的[额外毒持续伤害]，效果持续【持续5】毫秒，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>每【参数8】毫秒，触发等同于[毒元素直接伤害]*【参数1万分比毒持续buff系数】+【参数2】的[额外毒持续伤害]，状态持续【持续5】毫秒，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>3041108:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>拥有这个技能效果时，命中敌人时，攻击者回复固定值【参数1固定值】的血量，触发冷却时间【参数8】毫秒</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3560208:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3580208:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581208:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3591002:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3591003:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧时，被攻击受到额外伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧时被攻击受到额外伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>触电时，[受到所有类型伤害提高]【参数1万分比】+【参数2】受到[受到所有类型额外伤害固定值]</t>
-  </si>
-  <si>
-    <t>触电时受到伤害提高</t>
-  </si>
-  <si>
-    <t>3570503:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>使目标触电时，造成1次触电伤害</t>
-  </si>
-  <si>
-    <t>使目标触电时，造成1次触电伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰冻状态，持续时间【参数5】，冰冻状态命中率【参数6命中率】</t>
-  </si>
-  <si>
-    <t>每攻击【参数1】次，有【参数2】几率触发【参数3】次指定技能【参数4】</t>
-  </si>
-  <si>
-    <t>每【参数8】毫秒，在释放冰霜新星时有【参数2】几率，触发【参数3】次数，技能id【参数4】</t>
-  </si>
-  <si>
-    <t>对冰冻有配置标再次触发冰冻效果时，造成{[最终冰元素伤害]【参数1万分比】+【参数2固定值】}的[最终冰元素伤害</t>
-  </si>
-  <si>
-    <t>使目标冰冻时，触发目标{生命最大值【参数1百万分比】}的[冰元素基础伤害]+{【参数2固定值】}的[额外冰元素伤害固定值]</t>
-  </si>
-  <si>
-    <t>攻击冰冻目标时，造成{[冰元素最终伤害]【参数1万分比】+【参数2固定值】}的[额外最终冰元素伤害]，该效果每【参数8】毫秒触发1次。</t>
-  </si>
-  <si>
-    <t>攻击冰冻目标时造成额外伤害</t>
-  </si>
-  <si>
-    <t>中毒目标再次中毒受到额外中毒伤害</t>
-  </si>
-  <si>
-    <t>中毒目标再次中毒时，造成每次中毒结算伤害*【参数1】次数*【参数2万分比】的[最终毒元素伤害]</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3580702:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>复活回复血量、触发次数、触发间隔</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3591908:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3561401:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3561402:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3561408:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧时，被攻击会额外受到1次[最终火元素伤害]【参数1万分比】+【参数2固定值】的[额外最终火元素伤害]，该效果每【参数8】毫秒触发1次。</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3570205:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3580205:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581205:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3590405:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>致命暴击状态攻速提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3592101:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀回血效果提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3551103:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数8结算间隔时间</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>逻辑属性id</t>
-  </si>
-  <si>
-    <t>技能效果</t>
-  </si>
-  <si>
-    <t>技能名称</t>
-  </si>
-  <si>
-    <t>参数描述</t>
-  </si>
-  <si>
-    <t>效果叠加层数</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>结算间隔时间（毫秒）</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>重复中buff组的cd时间（毫秒）</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数5</t>
-  </si>
-  <si>
-    <t>参数6</t>
-  </si>
-  <si>
-    <t>持续时间（毫秒）</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>效果最大叠加层数</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>效果基础命中率（万分比）</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>效果触发间隔（毫秒）</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数4LIST</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>触发的技能id</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数9</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数10</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数11</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数12</t>
-  </si>
-  <si>
-    <t>参数13</t>
-  </si>
-  <si>
-    <t>击中回复生命值-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击中回复效果提高万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀回复生命-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数14</t>
-  </si>
-  <si>
-    <t>参数15</t>
-  </si>
-  <si>
-    <t>参数16</t>
-  </si>
-  <si>
-    <t>击中回复生命值-自身最大生命值百万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀回复生命-自身最大生命值百万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀回复生命-目标最大生命值百万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数17</t>
-  </si>
-  <si>
-    <t>参数18</t>
-  </si>
-  <si>
-    <t>参数19</t>
-  </si>
-  <si>
-    <t>参数20</t>
-  </si>
-  <si>
-    <t>参数21</t>
-  </si>
-  <si>
-    <t>参数22</t>
-  </si>
-  <si>
-    <t>参数28</t>
-  </si>
-  <si>
-    <t>参数29</t>
-  </si>
-  <si>
-    <t>获得护盾-自身生命百万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得护盾-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得护盾效果提高万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀回复生命效果提高万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得护盾-自身已损失生命万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>复活</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>触发自动技能</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数30</t>
-  </si>
-  <si>
-    <t>参数31</t>
-  </si>
-  <si>
-    <t>参数32</t>
-  </si>
-  <si>
-    <t>参数33</t>
-  </si>
-  <si>
-    <t>参数34</t>
-  </si>
-  <si>
-    <t>参数35</t>
-  </si>
-  <si>
-    <t>参数36</t>
-  </si>
-  <si>
-    <t>参数37</t>
-  </si>
-  <si>
-    <t>参数38</t>
-  </si>
-  <si>
-    <t>参数39</t>
-  </si>
-  <si>
-    <t>参数40</t>
-  </si>
-  <si>
-    <t>参数41</t>
-  </si>
-  <si>
-    <t>参数42</t>
-  </si>
-  <si>
-    <t>参数43</t>
-  </si>
-  <si>
-    <t>参数44</t>
-  </si>
-  <si>
-    <t>主动技能</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>回复生命</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击中目标</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰霜新星</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>陨石</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>闪电链</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>传染</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>瘟疫</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>多重打击</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>旋风斩</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>斩杀</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>半月斩</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>死亡爆炸</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>电磁爆发</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>重击</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能增加-万分比</t>
-  </si>
-  <si>
-    <t>技能增加-普通攻击范围万分比</t>
-  </si>
-  <si>
-    <t>攻击提高-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击提高-万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>防御提高-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>防御提高-万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击提高-攻击的元素类型</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数25LIST</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数45</t>
-  </si>
-  <si>
-    <t>参数46</t>
-  </si>
-  <si>
-    <t>参数47</t>
-  </si>
-  <si>
-    <t>参数48</t>
-  </si>
-  <si>
-    <t>参数49</t>
-  </si>
-  <si>
-    <t>参数50</t>
-  </si>
-  <si>
-    <t>参数51</t>
-  </si>
-  <si>
-    <t>参数52</t>
-  </si>
-  <si>
-    <t>参数53</t>
-  </si>
-  <si>
-    <t>参数54</t>
-  </si>
-  <si>
-    <t>参数55</t>
-  </si>
-  <si>
-    <t>参数56</t>
-  </si>
-  <si>
-    <t>生命上限提高-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>生命上限提高-百万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击速度提高-万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>移动速度提高-万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击范围提高-万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击目标数量提高-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能增加-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>INT_S</t>
-  </si>
-  <si>
-    <t>auto_cd</t>
-  </si>
-  <si>
-    <t>参数-重复触发自动释放冷却时间（毫秒）</t>
-  </si>
-  <si>
-    <t>release_ratio</t>
-  </si>
-  <si>
-    <t>参数-释放几率</t>
-  </si>
-  <si>
-    <t>release_num</t>
-  </si>
-  <si>
-    <t>参数-释放次数</t>
-  </si>
-  <si>
-    <t>LIST&lt;INT&gt;_S</t>
-  </si>
-  <si>
-    <t>skill_id</t>
-  </si>
-  <si>
-    <t>参数-释放的技能id</t>
-  </si>
-  <si>
-    <t>total_attack_num</t>
-  </si>
-  <si>
-    <t>参数-累计发起攻击次数时</t>
-  </si>
-  <si>
-    <t>lose_hp_ratio</t>
-  </si>
-  <si>
-    <t>参数-损失自身生命最大值百万分比时</t>
-  </si>
-  <si>
-    <t>kill_target_after</t>
-  </si>
-  <si>
-    <t>参数-击杀目标后</t>
-  </si>
-  <si>
-    <t>after_attack_crit</t>
-  </si>
-  <si>
-    <t>参数-攻击暴击后</t>
-  </si>
-  <si>
-    <t>after_use_skill</t>
-  </si>
-  <si>
-    <t>参数-释放【技能id】后</t>
-  </si>
-  <si>
-    <t>cycle_time</t>
-  </si>
-  <si>
-    <t>参数-每过固定时间（毫秒）时</t>
-  </si>
-  <si>
-    <t>after_skill_hit</t>
-  </si>
-  <si>
-    <t>参数-【技能id】命中后</t>
-  </si>
-  <si>
-    <t>after_self_death</t>
-  </si>
-  <si>
-    <t>参数-自身死亡后释放</t>
-  </si>
-  <si>
-    <t>MAP&lt;INT:INT&gt;_S</t>
-  </si>
-  <si>
-    <t>self_have_effect</t>
-  </si>
-  <si>
-    <t>参数-自身拥有【效果id：&gt;=层数】时</t>
-  </si>
-  <si>
-    <t>target_have_effect</t>
-  </si>
-  <si>
-    <t>参数-目标拥有【效果id：&gt;=层数】时</t>
-  </si>
-  <si>
-    <t>target_hp_ratio_over</t>
-  </si>
-  <si>
-    <t>参数-目标当前生命值&gt;=最大生命值的百万分之X时</t>
-  </si>
-  <si>
-    <t>target_hp_ratio_under</t>
-  </si>
-  <si>
-    <t>参数-目标当前生命值&lt;=最大生命值的百万分之X时</t>
-  </si>
-  <si>
-    <t>to_target_effect_hit</t>
-  </si>
-  <si>
-    <t>参数-对目标施加【效果id】命中时</t>
-  </si>
-  <si>
-    <t>order</t>
-  </si>
-  <si>
-    <t>自动</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>受到的伤害总加成</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成伤害总加成</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成的伤害总加成【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到的伤害总加成【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542801:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542601:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3543001:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542607:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542807:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3543007:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542605:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542805:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3543005:1</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -2661,13 +2662,13 @@
         <v>65</v>
       </c>
       <c r="AA2" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="AB2" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="AB2" s="7" t="s">
-        <v>327</v>
-      </c>
       <c r="AC2" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.2">
@@ -2750,13 +2751,13 @@
         <v>103</v>
       </c>
       <c r="AA3" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="AB3" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="AB3" s="7" t="s">
+      <c r="AC3" s="7" t="s">
         <v>329</v>
-      </c>
-      <c r="AC3" s="7" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.2">
@@ -2776,16 +2777,16 @@
         <v>64</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>30</v>
@@ -2839,13 +2840,13 @@
         <v>106</v>
       </c>
       <c r="AA4" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="AB4" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="AB4" s="7" t="s">
-        <v>332</v>
-      </c>
       <c r="AC4" s="7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.2">
@@ -2883,7 +2884,7 @@
         <v>2</v>
       </c>
       <c r="L5" s="5">
-        <v>600000</v>
+        <v>300000</v>
       </c>
       <c r="M5" s="11" t="s">
         <v>43</v>
@@ -2963,7 +2964,7 @@
         <v>47</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J6" s="6" t="s">
         <v>89</v>
@@ -3017,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="AA6" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AB6" s="6">
         <v>1</v>
@@ -3046,22 +3047,22 @@
         <v>90</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H7" s="16" t="s">
         <v>90</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>108</v>
+        <v>532</v>
       </c>
       <c r="K7" s="15">
         <v>2</v>
       </c>
       <c r="L7" s="15">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="M7" s="15" t="s">
         <v>43</v>
@@ -3085,10 +3086,10 @@
         <v>0</v>
       </c>
       <c r="T7" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U7" s="15">
-        <v>4000</v>
+        <v>60000</v>
       </c>
       <c r="V7" s="15" t="s">
         <v>43</v>
@@ -3097,7 +3098,7 @@
         <v>10000</v>
       </c>
       <c r="X7" s="15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y7" s="15">
         <v>1</v>
@@ -3135,25 +3136,25 @@
         <v>91</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H8" s="16" t="s">
         <v>91</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K8" s="15">
         <v>2</v>
       </c>
       <c r="L8" s="15">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="M8" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N8" s="15">
         <v>1</v>
@@ -3174,10 +3175,10 @@
         <v>0</v>
       </c>
       <c r="T8" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="U8" s="15">
-        <v>4000</v>
+        <v>60000</v>
       </c>
       <c r="V8" s="15" t="s">
         <v>43</v>
@@ -3186,7 +3187,7 @@
         <v>10000</v>
       </c>
       <c r="X8" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y8" s="15">
         <v>1</v>
@@ -3224,25 +3225,25 @@
         <v>92</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H9" s="16" t="s">
         <v>92</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K9" s="15">
         <v>2</v>
       </c>
       <c r="L9" s="15">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="M9" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N9" s="15">
         <v>1</v>
@@ -3263,10 +3264,10 @@
         <v>0</v>
       </c>
       <c r="T9" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="U9" s="15">
-        <v>4000</v>
+        <v>60000</v>
       </c>
       <c r="V9" s="15" t="s">
         <v>43</v>
@@ -3275,7 +3276,7 @@
         <v>10000</v>
       </c>
       <c r="X9" s="15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Y9" s="15">
         <v>1</v>
@@ -3313,25 +3314,25 @@
         <v>93</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H10" s="16" t="s">
         <v>93</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K10" s="15">
         <v>3</v>
       </c>
       <c r="L10" s="15">
-        <v>50000</v>
+        <v>150000</v>
       </c>
       <c r="M10" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N10" s="15">
         <v>1</v>
@@ -3352,10 +3353,10 @@
         <v>0</v>
       </c>
       <c r="T10" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="U10" s="15">
-        <v>4000</v>
+        <v>60000</v>
       </c>
       <c r="V10" s="15" t="s">
         <v>43</v>
@@ -3364,7 +3365,7 @@
         <v>10000</v>
       </c>
       <c r="X10" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y10" s="15">
         <v>1</v>
@@ -3402,16 +3403,16 @@
         <v>94</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H11" s="16" t="s">
         <v>94</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K11" s="15">
         <v>2</v>
@@ -3420,7 +3421,7 @@
         <v>500</v>
       </c>
       <c r="M11" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N11" s="15">
         <v>1</v>
@@ -3441,7 +3442,7 @@
         <v>0</v>
       </c>
       <c r="T11" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="U11" s="15">
         <v>4000</v>
@@ -3453,7 +3454,7 @@
         <v>10000</v>
       </c>
       <c r="X11" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y11" s="15">
         <v>1</v>
@@ -3491,22 +3492,22 @@
         <v>95</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H12" s="16" t="s">
         <v>95</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K12" s="15">
         <v>2</v>
       </c>
       <c r="L12" s="15">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="M12" s="15" t="s">
         <v>43</v>
@@ -3530,10 +3531,10 @@
         <v>0</v>
       </c>
       <c r="T12" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="U12" s="15">
-        <v>4000</v>
+        <v>60000</v>
       </c>
       <c r="V12" s="15" t="s">
         <v>43</v>
@@ -3542,7 +3543,7 @@
         <v>10000</v>
       </c>
       <c r="X12" s="15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Y12" s="15">
         <v>1</v>
@@ -3580,16 +3581,16 @@
         <v>96</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H13" s="16" t="s">
         <v>96</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K13" s="15">
         <v>2</v>
@@ -3619,7 +3620,7 @@
         <v>0</v>
       </c>
       <c r="T13" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="U13" s="15">
         <v>4000</v>
@@ -3631,7 +3632,7 @@
         <v>10000</v>
       </c>
       <c r="X13" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Y13" s="15">
         <v>1</v>
@@ -3669,16 +3670,16 @@
         <v>97</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J14" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K14" s="15">
         <v>2</v>
@@ -3687,7 +3688,7 @@
         <v>500</v>
       </c>
       <c r="M14" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N14" s="15">
         <v>1</v>
@@ -3708,7 +3709,7 @@
         <v>0</v>
       </c>
       <c r="T14" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="U14" s="15">
         <v>4000</v>
@@ -3720,7 +3721,7 @@
         <v>10000</v>
       </c>
       <c r="X14" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Y14" s="15">
         <v>1</v>
@@ -3758,16 +3759,16 @@
         <v>98</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K15" s="15">
         <v>2</v>
@@ -3776,7 +3777,7 @@
         <v>500</v>
       </c>
       <c r="M15" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N15" s="15">
         <v>1</v>
@@ -3797,7 +3798,7 @@
         <v>0</v>
       </c>
       <c r="T15" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="U15" s="15">
         <v>4000</v>
@@ -3809,7 +3810,7 @@
         <v>10000</v>
       </c>
       <c r="X15" s="15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Y15" s="15">
         <v>1</v>
@@ -3847,16 +3848,16 @@
         <v>99</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J16" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K16" s="15">
         <v>2</v>
@@ -3865,7 +3866,7 @@
         <v>500</v>
       </c>
       <c r="M16" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N16" s="15">
         <v>1</v>
@@ -3886,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="T16" s="15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="U16" s="15">
         <v>4000</v>
@@ -3898,7 +3899,7 @@
         <v>10000</v>
       </c>
       <c r="X16" s="15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Y16" s="15">
         <v>1</v>
@@ -3936,16 +3937,16 @@
         <v>100</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K17" s="15">
         <v>2</v>
@@ -3954,7 +3955,7 @@
         <v>500</v>
       </c>
       <c r="M17" s="15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N17" s="15">
         <v>1</v>
@@ -3975,7 +3976,7 @@
         <v>0</v>
       </c>
       <c r="T17" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="U17" s="15">
         <v>4000</v>
@@ -3987,7 +3988,7 @@
         <v>10000</v>
       </c>
       <c r="X17" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Y17" s="15">
         <v>1</v>
@@ -4025,16 +4026,16 @@
         <v>107</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J18" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K18" s="15">
         <v>2</v>
@@ -4064,7 +4065,7 @@
         <v>0</v>
       </c>
       <c r="T18" s="15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="U18" s="15">
         <v>4000</v>
@@ -4076,7 +4077,7 @@
         <v>10000</v>
       </c>
       <c r="X18" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Y18" s="15">
         <v>1</v>
@@ -4111,19 +4112,19 @@
         <v>3542600</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I19" s="16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="K19" s="15">
         <v>2</v>
@@ -4153,7 +4154,7 @@
         <v>0</v>
       </c>
       <c r="T19" s="15" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="U19" s="15">
         <v>4000</v>
@@ -4165,7 +4166,7 @@
         <v>10000</v>
       </c>
       <c r="X19" s="15" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y19" s="15">
         <v>1</v>
@@ -4200,19 +4201,19 @@
         <v>3542800</v>
       </c>
       <c r="F20" s="16" t="s">
+        <v>520</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="I20" s="16" t="s">
         <v>521</v>
       </c>
-      <c r="G20" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="I20" s="16" t="s">
-        <v>522</v>
-      </c>
       <c r="J20" s="15" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="K20" s="15">
         <v>2</v>
@@ -4242,7 +4243,7 @@
         <v>0</v>
       </c>
       <c r="T20" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="U20" s="15">
         <v>-1</v>
@@ -4254,7 +4255,7 @@
         <v>10000</v>
       </c>
       <c r="X20" s="15" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Y20" s="15">
         <v>1</v>
@@ -4289,25 +4290,25 @@
         <v>3543000</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I21" s="16" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="J21" s="15" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="K21" s="15">
         <v>2</v>
       </c>
       <c r="L21" s="15">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="M21" s="15" t="s">
         <v>43</v>
@@ -4331,7 +4332,7 @@
         <v>0</v>
       </c>
       <c r="T21" s="15" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="U21" s="15">
         <v>-1</v>
@@ -4343,13 +4344,13 @@
         <v>10000</v>
       </c>
       <c r="X21" s="15" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="Y21" s="15">
         <v>1</v>
       </c>
       <c r="Z21" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA21" s="15" t="s">
         <v>43</v>
@@ -4381,13 +4382,13 @@
         <v>69</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J22" s="17" t="s">
         <v>43</v>
@@ -4470,13 +4471,13 @@
         <v>71</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J23" s="17" t="s">
         <v>80</v>
@@ -4559,13 +4560,13 @@
         <v>72</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J24" s="17" t="s">
         <v>43</v>
@@ -4648,13 +4649,13 @@
         <v>74</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="J25" s="17" t="s">
         <v>85</v>
@@ -4666,7 +4667,7 @@
         <v>3000</v>
       </c>
       <c r="M25" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N25" s="17">
         <v>0</v>
@@ -4734,16 +4735,16 @@
         <v>3551100</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="J26" s="17" t="s">
         <v>86</v>
@@ -4764,7 +4765,7 @@
         <v>0</v>
       </c>
       <c r="P26" s="17" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Q26" s="17">
         <v>1</v>
@@ -4823,16 +4824,16 @@
         <v>3551300</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J27" s="17" t="s">
         <v>88</v>
@@ -4844,7 +4845,7 @@
         <v>5000</v>
       </c>
       <c r="M27" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N27" s="17">
         <v>1</v>
@@ -4912,19 +4913,19 @@
         <v>3551500</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J28" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K28" s="17">
         <v>2</v>
@@ -5001,19 +5002,19 @@
         <v>3560200</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J29" s="18" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K29" s="18">
         <v>2</v>
@@ -5022,7 +5023,7 @@
         <v>5000</v>
       </c>
       <c r="M29" s="18" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="N29" s="18">
         <v>1</v>
@@ -5043,13 +5044,13 @@
         <v>0</v>
       </c>
       <c r="T29" s="18" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="U29" s="18">
         <v>4000</v>
       </c>
       <c r="V29" s="18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="W29" s="18">
         <v>1500</v>
@@ -5064,7 +5065,7 @@
         <v>1</v>
       </c>
       <c r="AA29" s="18" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AB29" s="18">
         <v>1</v>
@@ -5090,19 +5091,19 @@
         <v>3560500</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J30" s="18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K30" s="18">
         <v>1</v>
@@ -5111,7 +5112,7 @@
         <v>8</v>
       </c>
       <c r="M30" s="18" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="N30" s="18">
         <v>1</v>
@@ -5120,7 +5121,7 @@
         <v>10000</v>
       </c>
       <c r="P30" s="18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q30" s="18">
         <v>1</v>
@@ -5179,19 +5180,19 @@
         <v>3560700</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J31" s="18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K31" s="18">
         <v>2</v>
@@ -5268,19 +5269,19 @@
         <v>3560900</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J32" s="18" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K32" s="18">
         <v>2</v>
@@ -5357,16 +5358,16 @@
         <v>3561100</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J33" s="18" t="s">
         <v>43</v>
@@ -5378,7 +5379,7 @@
         <v>0</v>
       </c>
       <c r="M33" s="18" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N33" s="18">
         <v>2</v>
@@ -5387,7 +5388,7 @@
         <v>10000</v>
       </c>
       <c r="P33" s="18" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="Q33" s="18">
         <v>1</v>
@@ -5446,19 +5447,19 @@
         <v>3561400</v>
       </c>
       <c r="F34" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="H34" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="G34" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="H34" s="13" t="s">
-        <v>345</v>
-      </c>
       <c r="I34" s="13" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="J34" s="18" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="K34" s="18">
         <v>2</v>
@@ -5467,7 +5468,7 @@
         <v>3500</v>
       </c>
       <c r="M34" s="18" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="N34" s="18">
         <v>35</v>
@@ -5509,7 +5510,7 @@
         <v>1</v>
       </c>
       <c r="AA34" s="18" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AB34" s="18">
         <v>1</v>
@@ -5535,19 +5536,19 @@
         <v>3570200</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J35" s="19" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K35" s="19">
         <v>2</v>
@@ -5556,7 +5557,7 @@
         <v>4000</v>
       </c>
       <c r="M35" s="19" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N35" s="19">
         <v>1</v>
@@ -5577,7 +5578,7 @@
         <v>0</v>
       </c>
       <c r="T35" s="19" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="U35" s="19">
         <v>4000</v>
@@ -5624,19 +5625,19 @@
         <v>3570500</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J36" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K36" s="19">
         <v>1</v>
@@ -5645,7 +5646,7 @@
         <v>3</v>
       </c>
       <c r="M36" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N36" s="19">
         <v>1</v>
@@ -5654,7 +5655,7 @@
         <v>1</v>
       </c>
       <c r="P36" s="19" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q36" s="19">
         <v>2</v>
@@ -5713,19 +5714,19 @@
         <v>3570700</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J37" s="19" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K37" s="19">
         <v>1</v>
@@ -5734,7 +5735,7 @@
         <v>8</v>
       </c>
       <c r="M37" s="19" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N37" s="19">
         <v>2</v>
@@ -5743,7 +5744,7 @@
         <v>10000</v>
       </c>
       <c r="P37" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q37" s="19">
         <v>1</v>
@@ -5802,19 +5803,19 @@
         <v>3570900</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="J38" s="19" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K38" s="19">
         <v>2</v>
@@ -5823,7 +5824,7 @@
         <v>2000</v>
       </c>
       <c r="M38" s="19" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="N38" s="19">
         <v>1</v>
@@ -5891,19 +5892,19 @@
         <v>3571100</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J39" s="19" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K39" s="19">
         <v>2</v>
@@ -5912,16 +5913,16 @@
         <v>10000</v>
       </c>
       <c r="M39" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="N39" s="19">
+        <v>1</v>
+      </c>
+      <c r="O39" s="19">
+        <v>1</v>
+      </c>
+      <c r="P39" s="19" t="s">
         <v>222</v>
-      </c>
-      <c r="N39" s="19">
-        <v>1</v>
-      </c>
-      <c r="O39" s="19">
-        <v>1</v>
-      </c>
-      <c r="P39" s="19" t="s">
-        <v>223</v>
       </c>
       <c r="Q39" s="19">
         <v>1</v>
@@ -5980,16 +5981,16 @@
         <v>3571300</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J40" s="19" t="s">
         <v>43</v>
@@ -6001,7 +6002,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="N40" s="19">
         <v>2</v>
@@ -6010,7 +6011,7 @@
         <v>10000</v>
       </c>
       <c r="P40" s="19" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q40" s="19">
         <v>1</v>
@@ -6069,19 +6070,19 @@
         <v>3580200</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J41" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K41" s="20">
         <v>2</v>
@@ -6090,7 +6091,7 @@
         <v>3000</v>
       </c>
       <c r="M41" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N41" s="20">
         <v>1</v>
@@ -6111,7 +6112,7 @@
         <v>0</v>
       </c>
       <c r="T41" s="20" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="U41" s="20">
         <v>4000</v>
@@ -6123,7 +6124,7 @@
         <v>10000</v>
       </c>
       <c r="X41" s="20" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Y41" s="20">
         <v>1</v>
@@ -6132,7 +6133,7 @@
         <v>1</v>
       </c>
       <c r="AA41" s="20" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AB41" s="20">
         <v>1</v>
@@ -6158,19 +6159,19 @@
         <v>3580500</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J42" s="20" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K42" s="20">
         <v>1</v>
@@ -6179,7 +6180,7 @@
         <v>8</v>
       </c>
       <c r="M42" s="20" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="N42" s="20">
         <v>2</v>
@@ -6188,7 +6189,7 @@
         <v>10000</v>
       </c>
       <c r="P42" s="20" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q42" s="20">
         <v>1</v>
@@ -6247,19 +6248,19 @@
         <v>3580700</v>
       </c>
       <c r="F43" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="G43" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="I43" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="G43" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="H43" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="I43" s="13" t="s">
-        <v>359</v>
-      </c>
       <c r="J43" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K43" s="20">
         <v>1</v>
@@ -6268,7 +6269,7 @@
         <v>5</v>
       </c>
       <c r="M43" s="20" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="N43" s="20">
         <v>2</v>
@@ -6336,16 +6337,16 @@
         <v>3580900</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J44" s="20" t="s">
         <v>43</v>
@@ -6357,7 +6358,7 @@
         <v>0</v>
       </c>
       <c r="M44" s="20" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="N44" s="20">
         <v>2</v>
@@ -6366,7 +6367,7 @@
         <v>10000</v>
       </c>
       <c r="P44" s="20" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q44" s="20">
         <v>1</v>
@@ -6425,19 +6426,19 @@
         <v>3581200</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I45" s="13" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J45" s="20" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="K45" s="20">
         <v>2</v>
@@ -6446,7 +6447,7 @@
         <v>3000</v>
       </c>
       <c r="M45" s="20" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N45" s="20">
         <v>0</v>
@@ -6467,7 +6468,7 @@
         <v>0</v>
       </c>
       <c r="T45" s="20" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="U45" s="20">
         <v>4000</v>
@@ -6479,7 +6480,7 @@
         <v>10000</v>
       </c>
       <c r="X45" s="20" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Y45" s="20">
         <v>1</v>
@@ -6488,7 +6489,7 @@
         <v>10</v>
       </c>
       <c r="AA45" s="20" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AB45" s="20">
         <v>1</v>
@@ -6514,15 +6515,15 @@
         <v>3590200</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H46" s="13"/>
       <c r="I46" s="13"/>
       <c r="J46" s="24" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K46" s="24">
         <v>3</v>
@@ -6531,7 +6532,7 @@
         <v>200000</v>
       </c>
       <c r="M46" s="24" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="N46" s="24">
         <v>2</v>
@@ -6540,7 +6541,7 @@
         <v>10000</v>
       </c>
       <c r="P46" s="24" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q46" s="24">
         <v>1</v>
@@ -6599,15 +6600,15 @@
         <v>3590400</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H47" s="13"/>
       <c r="I47" s="13"/>
       <c r="J47" s="24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K47" s="24">
         <v>3</v>
@@ -6637,7 +6638,7 @@
         <v>59030001</v>
       </c>
       <c r="T47" s="24" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="U47" s="24">
         <v>-1</v>
@@ -6684,10 +6685,10 @@
         <v>3590600</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H48" s="13"/>
       <c r="I48" s="13"/>
@@ -6701,7 +6702,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="24" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N48" s="24">
         <v>2</v>
@@ -6710,7 +6711,7 @@
         <v>10000</v>
       </c>
       <c r="P48" s="24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q48" s="24">
         <v>1</v>
@@ -6769,10 +6770,10 @@
         <v>3590800</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H49" s="13"/>
       <c r="I49" s="13"/>
@@ -6786,7 +6787,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="24" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="N49" s="24">
         <v>2</v>
@@ -6795,7 +6796,7 @@
         <v>10000</v>
       </c>
       <c r="P49" s="24" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q49" s="24">
         <v>1</v>
@@ -6854,15 +6855,15 @@
         <v>3591000</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H50" s="13"/>
       <c r="I50" s="13"/>
       <c r="J50" s="24" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="K50" s="24">
         <v>2</v>
@@ -6871,16 +6872,16 @@
         <v>0</v>
       </c>
       <c r="M50" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="N50" s="24">
+        <v>1</v>
+      </c>
+      <c r="O50" s="24">
+        <v>0</v>
+      </c>
+      <c r="P50" s="24" t="s">
         <v>342</v>
-      </c>
-      <c r="N50" s="24">
-        <v>1</v>
-      </c>
-      <c r="O50" s="24">
-        <v>0</v>
-      </c>
-      <c r="P50" s="24" t="s">
-        <v>343</v>
       </c>
       <c r="Q50" s="24">
         <v>3</v>
@@ -6939,15 +6940,15 @@
         <v>3591200</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H51" s="13"/>
       <c r="I51" s="13"/>
       <c r="J51" s="24" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K51" s="24">
         <v>3</v>
@@ -6956,7 +6957,7 @@
         <v>1000000</v>
       </c>
       <c r="M51" s="24" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="N51" s="24">
         <v>2</v>
@@ -6965,7 +6966,7 @@
         <v>10000</v>
       </c>
       <c r="P51" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q51" s="24">
         <v>1</v>
@@ -7024,15 +7025,15 @@
         <v>3591400</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H52" s="13"/>
       <c r="I52" s="13"/>
       <c r="J52" s="24" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K52" s="24">
         <v>3</v>
@@ -7041,7 +7042,7 @@
         <v>500000</v>
       </c>
       <c r="M52" s="24" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N52" s="24">
         <v>2</v>
@@ -7050,7 +7051,7 @@
         <v>10000</v>
       </c>
       <c r="P52" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q52" s="24">
         <v>1</v>
@@ -7109,10 +7110,10 @@
         <v>3591600</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H53" s="13"/>
       <c r="I53" s="13"/>
@@ -7126,7 +7127,7 @@
         <v>0</v>
       </c>
       <c r="M53" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="N53" s="24">
         <v>2</v>
@@ -7135,7 +7136,7 @@
         <v>10000</v>
       </c>
       <c r="P53" s="24" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q53" s="24">
         <v>1</v>
@@ -7194,10 +7195,10 @@
         <v>3591900</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G54" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H54" s="13"/>
       <c r="I54" s="13"/>
@@ -7211,7 +7212,7 @@
         <v>0</v>
       </c>
       <c r="M54" s="24" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="N54" s="24">
         <v>1</v>
@@ -7253,7 +7254,7 @@
         <v>1</v>
       </c>
       <c r="AA54" s="24" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AB54" s="24">
         <v>1</v>
@@ -7279,10 +7280,10 @@
         <v>3541800</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H55" s="13"/>
       <c r="I55" s="13"/>
@@ -7364,10 +7365,10 @@
         <v>3541800</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H56" s="13"/>
       <c r="I56" s="13"/>
@@ -7449,15 +7450,15 @@
         <v>3592100</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G57" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H57" s="13"/>
       <c r="I57" s="13"/>
       <c r="J57" s="24" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="K57" s="24">
         <v>2</v>
@@ -7534,15 +7535,15 @@
         <v>3600200</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G58" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H58" s="13"/>
       <c r="I58" s="13"/>
       <c r="J58" s="21" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K58" s="21">
         <v>1</v>
@@ -7551,7 +7552,7 @@
         <v>8</v>
       </c>
       <c r="M58" s="21" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N58" s="21">
         <v>2</v>
@@ -7560,7 +7561,7 @@
         <v>10000</v>
       </c>
       <c r="P58" s="21" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q58" s="21">
         <v>1</v>
@@ -7619,24 +7620,24 @@
         <v>3600400</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H59" s="13"/>
       <c r="I59" s="13"/>
       <c r="J59" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="K59" s="21">
+        <v>1</v>
+      </c>
+      <c r="L59" s="21">
+        <v>1</v>
+      </c>
+      <c r="M59" s="21" t="s">
         <v>264</v>
-      </c>
-      <c r="K59" s="21">
-        <v>1</v>
-      </c>
-      <c r="L59" s="21">
-        <v>1</v>
-      </c>
-      <c r="M59" s="21" t="s">
-        <v>265</v>
       </c>
       <c r="N59" s="21">
         <v>2</v>
@@ -7704,15 +7705,15 @@
         <v>3600700</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H60" s="13"/>
       <c r="I60" s="13"/>
       <c r="J60" s="21" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="K60" s="21">
         <v>1</v>
@@ -7721,7 +7722,7 @@
         <v>8</v>
       </c>
       <c r="M60" s="21" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N60" s="21">
         <v>2</v>
@@ -7730,7 +7731,7 @@
         <v>10000</v>
       </c>
       <c r="P60" s="21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q60" s="21">
         <v>1</v>
@@ -7789,10 +7790,10 @@
         <v>3601000</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G61" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H61" s="13"/>
       <c r="I61" s="13"/>
@@ -7806,7 +7807,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="21" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="N61" s="21">
         <v>2</v>
@@ -7815,7 +7816,7 @@
         <v>10000</v>
       </c>
       <c r="P61" s="21" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q61" s="21">
         <v>1</v>
@@ -7874,15 +7875,15 @@
         <v>3541600</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G62" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H62" s="13"/>
       <c r="I62" s="13"/>
       <c r="J62" s="21" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K62" s="21">
         <v>2</v>
@@ -7959,15 +7960,15 @@
         <v>3541800</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G63" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H63" s="13"/>
       <c r="I63" s="13"/>
       <c r="J63" s="21" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K63" s="21">
         <v>2</v>
@@ -8044,15 +8045,15 @@
         <v>3601300</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G64" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H64" s="13"/>
       <c r="I64" s="13"/>
       <c r="J64" s="21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="K64" s="21">
         <v>2</v>
@@ -8061,7 +8062,7 @@
         <v>10000</v>
       </c>
       <c r="M64" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="N64" s="21">
         <v>2</v>
@@ -8070,7 +8071,7 @@
         <v>2000</v>
       </c>
       <c r="P64" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q64" s="21">
         <v>1</v>
@@ -8129,15 +8130,15 @@
         <v>3610300</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G65" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H65" s="13"/>
       <c r="I65" s="13"/>
       <c r="J65" s="22" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K65" s="22">
         <v>1</v>
@@ -8146,7 +8147,7 @@
         <v>8</v>
       </c>
       <c r="M65" s="22" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="N65" s="22">
         <v>2</v>
@@ -8155,7 +8156,7 @@
         <v>10000</v>
       </c>
       <c r="P65" s="22" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q65" s="22">
         <v>1</v>
@@ -8214,15 +8215,15 @@
         <v>3610500</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H66" s="13"/>
       <c r="I66" s="13"/>
       <c r="J66" s="22" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K66" s="22">
         <v>2</v>
@@ -8299,10 +8300,10 @@
         <v>3610700</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H67" s="13"/>
       <c r="I67" s="13"/>
@@ -8316,7 +8317,7 @@
         <v>0</v>
       </c>
       <c r="M67" s="22" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="N67" s="22">
         <v>2</v>
@@ -8325,7 +8326,7 @@
         <v>10000</v>
       </c>
       <c r="P67" s="22" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q67" s="22">
         <v>1</v>
@@ -8384,15 +8385,15 @@
         <v>3541400</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G68" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H68" s="13"/>
       <c r="I68" s="13"/>
       <c r="J68" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K68" s="22">
         <v>2</v>
@@ -8469,15 +8470,15 @@
         <v>3610900</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G69" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H69" s="13"/>
       <c r="I69" s="13"/>
       <c r="J69" s="22" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="K69" s="22">
         <v>1</v>
@@ -8554,10 +8555,10 @@
         <v>3611100</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G70" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H70" s="13"/>
       <c r="I70" s="13"/>
@@ -8639,15 +8640,15 @@
         <v>3611300</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G71" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H71" s="13"/>
       <c r="I71" s="13"/>
       <c r="J71" s="22" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K71" s="22">
         <v>3</v>
@@ -8665,7 +8666,7 @@
         <v>0</v>
       </c>
       <c r="P71" s="22" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q71" s="22">
         <v>1</v>
@@ -8724,10 +8725,10 @@
         <v>3611500</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G72" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H72" s="13"/>
       <c r="I72" s="13"/>
@@ -8741,7 +8742,7 @@
         <v>0</v>
       </c>
       <c r="M72" s="22" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="N72" s="22">
         <v>2</v>
@@ -8750,7 +8751,7 @@
         <v>10000</v>
       </c>
       <c r="P72" s="22" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q72" s="22">
         <v>1</v>
@@ -8809,15 +8810,15 @@
         <v>3611700</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G73" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H73" s="13"/>
       <c r="I73" s="13"/>
       <c r="J73" s="22" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="K73" s="22">
         <v>3</v>
@@ -8894,10 +8895,10 @@
         <v>3590800</v>
       </c>
       <c r="F74" s="13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G74" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H74" s="13"/>
       <c r="I74" s="13"/>
@@ -8911,7 +8912,7 @@
         <v>0</v>
       </c>
       <c r="M74" s="22" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="N74" s="22">
         <v>2</v>
@@ -8920,7 +8921,7 @@
         <v>10000</v>
       </c>
       <c r="P74" s="22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q74" s="22">
         <v>1</v>
@@ -9015,7 +9016,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="11" spans="5:19" x14ac:dyDescent="0.15">
@@ -9023,7 +9024,7 @@
         <v>6</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="12" spans="5:19" x14ac:dyDescent="0.15">
@@ -9031,7 +9032,7 @@
         <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="13" spans="5:19" x14ac:dyDescent="0.15">
@@ -9042,10 +9043,10 @@
         <v>29</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="14" spans="5:19" x14ac:dyDescent="0.15">
@@ -9053,19 +9054,19 @@
         <v>9</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>1</v>
       </c>
       <c r="K14" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="L14" s="1" t="s">
         <v>516</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="15" spans="5:19" x14ac:dyDescent="0.15">
@@ -9073,19 +9074,19 @@
         <v>10</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K15" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="L15" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="L15" s="1" t="s">
-        <v>519</v>
-      </c>
       <c r="S15" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="16" spans="5:19" x14ac:dyDescent="0.15">
@@ -9096,19 +9097,19 @@
         <v>30</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J16" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="L16" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="L16" s="1" t="s">
-        <v>481</v>
-      </c>
       <c r="S16" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="17" spans="5:19" x14ac:dyDescent="0.15">
@@ -9119,19 +9120,19 @@
         <v>31</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K17" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="L17" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="L17" s="1" t="s">
-        <v>483</v>
-      </c>
       <c r="S17" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="18" spans="5:19" x14ac:dyDescent="0.15">
@@ -9145,16 +9146,16 @@
         <v>38</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K18" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="L18" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="L18" s="1" t="s">
-        <v>485</v>
-      </c>
       <c r="S18" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="19" spans="5:19" x14ac:dyDescent="0.15">
@@ -9169,22 +9170,22 @@
         <v>参数4LIST-触发的技能id</v>
       </c>
       <c r="H19" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="I19" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="I19" s="1" t="s">
-        <v>391</v>
-      </c>
       <c r="J19" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="L19" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="L19" s="1" t="s">
-        <v>488</v>
-      </c>
       <c r="S19" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="20" spans="5:19" x14ac:dyDescent="0.15">
@@ -9199,22 +9200,22 @@
         <v>参数5-持续时间（毫秒）</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="K20" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="L20" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="L20" s="1" t="s">
-        <v>490</v>
-      </c>
       <c r="S20" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="21" spans="5:19" x14ac:dyDescent="0.15">
@@ -9229,22 +9230,22 @@
         <v>参数6-效果基础命中率（万分比）</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K21" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="L21" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="L21" s="1" t="s">
-        <v>492</v>
-      </c>
       <c r="S21" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="22" spans="5:19" x14ac:dyDescent="0.15">
@@ -9262,19 +9263,19 @@
         <v>106</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K22" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="L22" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="L22" s="1" t="s">
-        <v>494</v>
-      </c>
       <c r="S22" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="23" spans="5:19" x14ac:dyDescent="0.15">
@@ -9289,22 +9290,22 @@
         <v>参数8-效果触发间隔（毫秒）</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K23" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="L23" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="L23" s="1" t="s">
-        <v>496</v>
-      </c>
       <c r="S23" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="24" spans="5:19" x14ac:dyDescent="0.15">
@@ -9319,22 +9320,22 @@
         <v>参数9-击中回复生命值-固定值</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="K24" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="L24" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="L24" s="1" t="s">
-        <v>498</v>
-      </c>
       <c r="S24" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="25" spans="5:19" x14ac:dyDescent="0.15">
@@ -9349,22 +9350,22 @@
         <v>参数10-击中回复生命值-自身最大生命值百万分比</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K25" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="L25" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="L25" s="1" t="s">
-        <v>500</v>
-      </c>
       <c r="S25" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="26" spans="5:19" x14ac:dyDescent="0.15">
@@ -9379,22 +9380,22 @@
         <v>参数11-击中回复效果提高万分比</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="K26" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="L26" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="L26" s="1" t="s">
-        <v>502</v>
-      </c>
       <c r="S26" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="27" spans="5:19" x14ac:dyDescent="0.15">
@@ -9409,22 +9410,22 @@
         <v>参数12-击杀回复生命-固定值</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K27" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="L27" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="L27" s="1" t="s">
-        <v>504</v>
-      </c>
       <c r="S27" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="28" spans="5:19" x14ac:dyDescent="0.15">
@@ -9439,19 +9440,19 @@
         <v>参数13-击杀回复生命-自身最大生命值百万分比</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="J28" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="K28" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="L28" s="1" t="s">
         <v>506</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="29" spans="5:19" x14ac:dyDescent="0.15">
@@ -9466,22 +9467,22 @@
         <v>参数14-击杀回复生命-目标最大生命值百万分比</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="K29" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="L29" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="L29" s="1" t="s">
-        <v>509</v>
-      </c>
       <c r="S29" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="30" spans="5:19" x14ac:dyDescent="0.15">
@@ -9496,22 +9497,22 @@
         <v>参数15-击杀回复生命效果提高万分比</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K30" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="L30" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="L30" s="1" t="s">
-        <v>511</v>
-      </c>
       <c r="S30" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="31" spans="5:19" x14ac:dyDescent="0.15">
@@ -9526,22 +9527,22 @@
         <v>参数16-获得护盾-固定值</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K31" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="L31" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="L31" s="1" t="s">
-        <v>513</v>
-      </c>
       <c r="S31" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="32" spans="5:19" x14ac:dyDescent="0.15">
@@ -9549,80 +9550,80 @@
         <v>103</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G32" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数17-获得护盾-自身生命百万分比</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="K32" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="L32" s="1" t="s">
         <v>514</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="33" spans="5:9" x14ac:dyDescent="0.15">
       <c r="E33" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G33" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数18-获得护盾-自身已损失生命万分比</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="34" spans="5:9" x14ac:dyDescent="0.15">
       <c r="E34" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G34" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数19-获得护盾效果提高万分比</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="35" spans="5:9" x14ac:dyDescent="0.15">
       <c r="E35" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G35" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数20-技能增加-固定值</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="36" spans="5:9" x14ac:dyDescent="0.15">
@@ -9631,10 +9632,10 @@
         <v>参数21-技能增加-万分比</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="37" spans="5:9" x14ac:dyDescent="0.15">
@@ -9643,10 +9644,10 @@
         <v>参数22-技能增加-普通攻击范围万分比</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="38" spans="5:9" x14ac:dyDescent="0.15">
@@ -9655,10 +9656,10 @@
         <v>参数25LIST-攻击提高-攻击的元素类型</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="39" spans="5:9" x14ac:dyDescent="0.15">
@@ -9667,10 +9668,10 @@
         <v>参数25LIST-攻击提高-固定值</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="40" spans="5:9" x14ac:dyDescent="0.15">
@@ -9679,10 +9680,10 @@
         <v>参数25LIST-攻击提高-万分比</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="41" spans="5:9" x14ac:dyDescent="0.15">
@@ -9691,10 +9692,10 @@
         <v>参数28-防御提高-固定值</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="42" spans="5:9" x14ac:dyDescent="0.15">
@@ -9703,10 +9704,10 @@
         <v>参数29-防御提高-万分比</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="43" spans="5:9" x14ac:dyDescent="0.15">
@@ -9715,10 +9716,10 @@
         <v>参数30-生命上限提高-固定值</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="44" spans="5:9" x14ac:dyDescent="0.15">
@@ -9727,10 +9728,10 @@
         <v>参数31-生命上限提高-百万分比</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="45" spans="5:9" x14ac:dyDescent="0.15">
@@ -9739,10 +9740,10 @@
         <v>参数32-攻击速度提高-万分比</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="46" spans="5:9" x14ac:dyDescent="0.15">
@@ -9751,10 +9752,10 @@
         <v>参数33-移动速度提高-万分比</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="47" spans="5:9" x14ac:dyDescent="0.15">
@@ -9763,10 +9764,10 @@
         <v>参数34-攻击范围提高-万分比</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="48" spans="5:9" x14ac:dyDescent="0.15">
@@ -9775,10 +9776,10 @@
         <v>参数35-攻击目标数量提高-固定值</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="49" spans="7:8" x14ac:dyDescent="0.15">
@@ -9787,7 +9788,7 @@
         <v>参数36-</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="50" spans="7:8" x14ac:dyDescent="0.15">
@@ -9796,7 +9797,7 @@
         <v>参数37-</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="51" spans="7:8" x14ac:dyDescent="0.15">
@@ -9805,7 +9806,7 @@
         <v>参数38-</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="52" spans="7:8" x14ac:dyDescent="0.15">
@@ -9814,7 +9815,7 @@
         <v>参数39-</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="53" spans="7:8" x14ac:dyDescent="0.15">
@@ -9823,7 +9824,7 @@
         <v>参数40-</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="54" spans="7:8" x14ac:dyDescent="0.15">
@@ -9832,7 +9833,7 @@
         <v>参数41-</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="55" spans="7:8" x14ac:dyDescent="0.15">
@@ -9841,7 +9842,7 @@
         <v>参数42-</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="56" spans="7:8" x14ac:dyDescent="0.15">
@@ -9850,7 +9851,7 @@
         <v>参数41-</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="57" spans="7:8" x14ac:dyDescent="0.15">
@@ -9859,7 +9860,7 @@
         <v>参数42-</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="58" spans="7:8" x14ac:dyDescent="0.15">
@@ -9868,7 +9869,7 @@
         <v>参数43-</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="59" spans="7:8" x14ac:dyDescent="0.15">
@@ -9877,7 +9878,7 @@
         <v>参数44-</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="60" spans="7:8" x14ac:dyDescent="0.15">
@@ -9886,7 +9887,7 @@
         <v>参数45-</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="61" spans="7:8" x14ac:dyDescent="0.15">
@@ -9895,7 +9896,7 @@
         <v>参数46-</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="62" spans="7:8" x14ac:dyDescent="0.15">
@@ -9904,7 +9905,7 @@
         <v>参数47-</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="63" spans="7:8" x14ac:dyDescent="0.15">
@@ -9913,7 +9914,7 @@
         <v>参数48-</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="64" spans="7:8" x14ac:dyDescent="0.15">
@@ -9922,7 +9923,7 @@
         <v>参数49-</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="65" spans="7:8" x14ac:dyDescent="0.15">
@@ -9931,7 +9932,7 @@
         <v>参数50-</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="66" spans="7:8" x14ac:dyDescent="0.15">
@@ -9940,7 +9941,7 @@
         <v>参数51-</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="67" spans="7:8" x14ac:dyDescent="0.15">
@@ -9949,7 +9950,7 @@
         <v>参数52-</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="68" spans="7:8" x14ac:dyDescent="0.15">
@@ -9958,7 +9959,7 @@
         <v>参数53-</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="69" spans="7:8" x14ac:dyDescent="0.15">
@@ -9967,7 +9968,7 @@
         <v>参数54-</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="70" spans="7:8" x14ac:dyDescent="0.15">
@@ -9976,7 +9977,7 @@
         <v>参数55-</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="71" spans="7:8" x14ac:dyDescent="0.15">
@@ -9985,7 +9986,7 @@
         <v>参数56-</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{776A8CC2-4CF7-4493-B8DB-29542E5A2266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7BE97C8-F66C-42DD-B22F-E998273E3B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -2881,7 +2881,7 @@
         <v>43</v>
       </c>
       <c r="K5" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" s="5">
         <v>300000</v>
@@ -2979,7 +2979,7 @@
         <v>43</v>
       </c>
       <c r="N6" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" s="6">
         <v>0</v>
@@ -2988,7 +2988,7 @@
         <v>43</v>
       </c>
       <c r="Q6" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="6">
         <v>0</v>
@@ -3068,7 +3068,7 @@
         <v>43</v>
       </c>
       <c r="N7" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" s="15">
         <v>0</v>
@@ -3077,7 +3077,7 @@
         <v>43</v>
       </c>
       <c r="Q7" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" s="15">
         <v>0</v>
@@ -3166,7 +3166,7 @@
         <v>43</v>
       </c>
       <c r="Q8" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" s="15">
         <v>0</v>
@@ -3255,7 +3255,7 @@
         <v>43</v>
       </c>
       <c r="Q9" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="15">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         <v>112</v>
       </c>
       <c r="K10" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L10" s="15">
-        <v>150000</v>
+        <v>1500</v>
       </c>
       <c r="M10" s="15" t="s">
         <v>113</v>
@@ -3344,7 +3344,7 @@
         <v>43</v>
       </c>
       <c r="Q10" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="15">
         <v>0</v>
@@ -3433,7 +3433,7 @@
         <v>43</v>
       </c>
       <c r="Q11" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" s="15">
         <v>0</v>
@@ -3513,7 +3513,7 @@
         <v>43</v>
       </c>
       <c r="N12" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" s="15">
         <v>0</v>
@@ -3522,7 +3522,7 @@
         <v>43</v>
       </c>
       <c r="Q12" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" s="15">
         <v>0</v>
@@ -3602,7 +3602,7 @@
         <v>43</v>
       </c>
       <c r="N13" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="15">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         <v>43</v>
       </c>
       <c r="Q13" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" s="15">
         <v>0</v>
@@ -3700,7 +3700,7 @@
         <v>43</v>
       </c>
       <c r="Q14" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" s="15">
         <v>0</v>
@@ -3789,7 +3789,7 @@
         <v>43</v>
       </c>
       <c r="Q15" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" s="15">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>43</v>
       </c>
       <c r="Q16" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" s="15">
         <v>0</v>
@@ -3967,7 +3967,7 @@
         <v>43</v>
       </c>
       <c r="Q17" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="15">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>43</v>
       </c>
       <c r="N18" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" s="15">
         <v>0</v>
@@ -4056,7 +4056,7 @@
         <v>43</v>
       </c>
       <c r="Q18" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" s="15">
         <v>0</v>
@@ -4136,7 +4136,7 @@
         <v>43</v>
       </c>
       <c r="N19" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" s="15">
         <v>0</v>
@@ -4145,7 +4145,7 @@
         <v>43</v>
       </c>
       <c r="Q19" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" s="15">
         <v>0</v>
@@ -4225,7 +4225,7 @@
         <v>43</v>
       </c>
       <c r="N20" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" s="15">
         <v>0</v>
@@ -4234,7 +4234,7 @@
         <v>43</v>
       </c>
       <c r="Q20" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" s="15">
         <v>0</v>
@@ -4314,7 +4314,7 @@
         <v>43</v>
       </c>
       <c r="N21" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" s="15">
         <v>0</v>
@@ -4323,7 +4323,7 @@
         <v>43</v>
       </c>
       <c r="Q21" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" s="15">
         <v>0</v>
@@ -4394,7 +4394,7 @@
         <v>43</v>
       </c>
       <c r="K22" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="17">
         <v>0</v>
@@ -4403,7 +4403,7 @@
         <v>43</v>
       </c>
       <c r="N22" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" s="17">
         <v>0</v>
@@ -4412,7 +4412,7 @@
         <v>43</v>
       </c>
       <c r="Q22" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" s="17">
         <v>0</v>
@@ -4572,7 +4572,7 @@
         <v>43</v>
       </c>
       <c r="K24" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="17">
         <v>1000</v>
@@ -4670,7 +4670,7 @@
         <v>163</v>
       </c>
       <c r="N25" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25" s="17">
         <v>30</v>
@@ -4679,7 +4679,7 @@
         <v>43</v>
       </c>
       <c r="Q25" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" s="17">
         <v>0</v>
@@ -4857,7 +4857,7 @@
         <v>43</v>
       </c>
       <c r="Q27" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" s="17">
         <v>0</v>
@@ -4937,7 +4937,7 @@
         <v>70</v>
       </c>
       <c r="N28" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" s="17">
         <v>0</v>
@@ -4946,7 +4946,7 @@
         <v>70</v>
       </c>
       <c r="Q28" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" s="17">
         <v>0</v>
@@ -5035,7 +5035,7 @@
         <v>43</v>
       </c>
       <c r="Q29" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" s="18">
         <v>0</v>
@@ -5204,7 +5204,7 @@
         <v>43</v>
       </c>
       <c r="N31" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" s="18">
         <v>0</v>
@@ -5213,7 +5213,7 @@
         <v>43</v>
       </c>
       <c r="Q31" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" s="18">
         <v>0</v>
@@ -5293,7 +5293,7 @@
         <v>43</v>
       </c>
       <c r="N32" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" s="18">
         <v>0</v>
@@ -5302,7 +5302,7 @@
         <v>43</v>
       </c>
       <c r="Q32" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" s="18">
         <v>0</v>
@@ -5373,7 +5373,7 @@
         <v>43</v>
       </c>
       <c r="K33" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="18">
         <v>0</v>
@@ -5480,7 +5480,7 @@
         <v>43</v>
       </c>
       <c r="Q34" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" s="18">
         <v>0</v>
@@ -5569,7 +5569,7 @@
         <v>43</v>
       </c>
       <c r="Q35" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" s="19">
         <v>0</v>
@@ -5836,7 +5836,7 @@
         <v>43</v>
       </c>
       <c r="Q38" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" s="19">
         <v>0</v>
@@ -5996,7 +5996,7 @@
         <v>43</v>
       </c>
       <c r="K40" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="19">
         <v>0</v>
@@ -6281,7 +6281,7 @@
         <v>43</v>
       </c>
       <c r="Q43" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" s="20">
         <v>0</v>
@@ -6352,7 +6352,7 @@
         <v>43</v>
       </c>
       <c r="K44" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="20">
         <v>0</v>
@@ -6450,7 +6450,7 @@
         <v>322</v>
       </c>
       <c r="N45" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" s="20">
         <v>30</v>
@@ -6459,7 +6459,7 @@
         <v>43</v>
       </c>
       <c r="Q45" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" s="20">
         <v>0</v>
@@ -6620,7 +6620,7 @@
         <v>43</v>
       </c>
       <c r="N47" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O47" s="24">
         <v>0</v>
@@ -6629,7 +6629,7 @@
         <v>43</v>
       </c>
       <c r="Q47" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" s="24">
         <v>0</v>
@@ -6696,7 +6696,7 @@
         <v>43</v>
       </c>
       <c r="K48" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="24">
         <v>0</v>
@@ -6781,7 +6781,7 @@
         <v>43</v>
       </c>
       <c r="K49" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="24">
         <v>0</v>
@@ -7121,7 +7121,7 @@
         <v>43</v>
       </c>
       <c r="K53" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="24">
         <v>0</v>
@@ -7206,7 +7206,7 @@
         <v>43</v>
       </c>
       <c r="K54" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="24">
         <v>0</v>
@@ -7224,7 +7224,7 @@
         <v>43</v>
       </c>
       <c r="Q54" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R54" s="24">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>43</v>
       </c>
       <c r="N55" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O55" s="24">
         <v>0</v>
@@ -7309,7 +7309,7 @@
         <v>43</v>
       </c>
       <c r="Q55" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R55" s="24">
         <v>0</v>
@@ -7385,7 +7385,7 @@
         <v>43</v>
       </c>
       <c r="N56" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O56" s="24">
         <v>0</v>
@@ -7394,7 +7394,7 @@
         <v>43</v>
       </c>
       <c r="Q56" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" s="24">
         <v>0</v>
@@ -7470,7 +7470,7 @@
         <v>43</v>
       </c>
       <c r="N57" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O57" s="24">
         <v>0</v>
@@ -7479,7 +7479,7 @@
         <v>43</v>
       </c>
       <c r="Q57" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R57" s="24">
         <v>0</v>
@@ -7649,7 +7649,7 @@
         <v>43</v>
       </c>
       <c r="Q59" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R59" s="21">
         <v>0</v>
@@ -7801,7 +7801,7 @@
         <v>43</v>
       </c>
       <c r="K61" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="21">
         <v>0</v>
@@ -7895,7 +7895,7 @@
         <v>43</v>
       </c>
       <c r="N62" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O62" s="21">
         <v>0</v>
@@ -7904,7 +7904,7 @@
         <v>43</v>
       </c>
       <c r="Q62" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R62" s="21">
         <v>0</v>
@@ -7980,7 +7980,7 @@
         <v>43</v>
       </c>
       <c r="N63" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O63" s="21">
         <v>0</v>
@@ -7989,7 +7989,7 @@
         <v>43</v>
       </c>
       <c r="Q63" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R63" s="21">
         <v>0</v>
@@ -8235,7 +8235,7 @@
         <v>43</v>
       </c>
       <c r="N66" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O66" s="22">
         <v>0</v>
@@ -8244,7 +8244,7 @@
         <v>43</v>
       </c>
       <c r="Q66" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R66" s="22">
         <v>0</v>
@@ -8311,7 +8311,7 @@
         <v>43</v>
       </c>
       <c r="K67" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="22">
         <v>0</v>
@@ -8405,7 +8405,7 @@
         <v>43</v>
       </c>
       <c r="N68" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O68" s="22">
         <v>0</v>
@@ -8414,7 +8414,7 @@
         <v>43</v>
       </c>
       <c r="Q68" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R68" s="22">
         <v>0</v>
@@ -8490,7 +8490,7 @@
         <v>43</v>
       </c>
       <c r="N69" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69" s="22">
         <v>0</v>
@@ -8499,7 +8499,7 @@
         <v>43</v>
       </c>
       <c r="Q69" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R69" s="22">
         <v>0</v>
@@ -8566,7 +8566,7 @@
         <v>43</v>
       </c>
       <c r="K70" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="22">
         <v>0</v>
@@ -8575,7 +8575,7 @@
         <v>43</v>
       </c>
       <c r="N70" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O70" s="22">
         <v>0</v>
@@ -8584,7 +8584,7 @@
         <v>43</v>
       </c>
       <c r="Q70" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R70" s="22">
         <v>0</v>
@@ -8660,7 +8660,7 @@
         <v>43</v>
       </c>
       <c r="N71" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O71" s="22">
         <v>0</v>
@@ -8736,7 +8736,7 @@
         <v>43</v>
       </c>
       <c r="K72" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="22">
         <v>0</v>
@@ -8830,7 +8830,7 @@
         <v>43</v>
       </c>
       <c r="N73" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O73" s="22">
         <v>0</v>
@@ -8839,7 +8839,7 @@
         <v>43</v>
       </c>
       <c r="Q73" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R73" s="22">
         <v>0</v>
@@ -8906,7 +8906,7 @@
         <v>43</v>
       </c>
       <c r="K74" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="22">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7BE97C8-F66C-42DD-B22F-E998273E3B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1295B5FA-32A4-41A1-B14D-AD0647A11C55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -3089,7 +3089,7 @@
         <v>127</v>
       </c>
       <c r="U7" s="15">
-        <v>60000</v>
+        <v>1800000</v>
       </c>
       <c r="V7" s="15" t="s">
         <v>43</v>
@@ -3151,7 +3151,7 @@
         <v>2</v>
       </c>
       <c r="L8" s="15">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="M8" s="15" t="s">
         <v>109</v>
@@ -3178,7 +3178,7 @@
         <v>129</v>
       </c>
       <c r="U8" s="15">
-        <v>60000</v>
+        <v>1800000</v>
       </c>
       <c r="V8" s="15" t="s">
         <v>43</v>
@@ -3240,7 +3240,7 @@
         <v>2</v>
       </c>
       <c r="L9" s="15">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="M9" s="15" t="s">
         <v>111</v>
@@ -3267,7 +3267,7 @@
         <v>131</v>
       </c>
       <c r="U9" s="15">
-        <v>60000</v>
+        <v>1800000</v>
       </c>
       <c r="V9" s="15" t="s">
         <v>43</v>
@@ -3329,7 +3329,7 @@
         <v>2</v>
       </c>
       <c r="L10" s="15">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="M10" s="15" t="s">
         <v>113</v>
@@ -3356,7 +3356,7 @@
         <v>133</v>
       </c>
       <c r="U10" s="15">
-        <v>60000</v>
+        <v>1800000</v>
       </c>
       <c r="V10" s="15" t="s">
         <v>43</v>
@@ -3507,7 +3507,7 @@
         <v>2</v>
       </c>
       <c r="L12" s="15">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="M12" s="15" t="s">
         <v>43</v>
@@ -3534,7 +3534,7 @@
         <v>137</v>
       </c>
       <c r="U12" s="15">
-        <v>60000</v>
+        <v>1800000</v>
       </c>
       <c r="V12" s="15" t="s">
         <v>43</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1295B5FA-32A4-41A1-B14D-AD0647A11C55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9146632-634B-4302-B023-DA89408F2788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2884,7 +2884,7 @@
         <v>3</v>
       </c>
       <c r="L5" s="5">
-        <v>300000</v>
+        <v>400000</v>
       </c>
       <c r="M5" s="11" t="s">
         <v>43</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -2803,8 +2803,8 @@
     <col min="5" max="5" width="11" customWidth="1"/>
     <col min="6" max="6" width="29.75" customWidth="1"/>
     <col min="7" max="7" width="12.5" customWidth="1"/>
-    <col min="8" max="8" width="10.5" customWidth="1"/>
-    <col min="9" max="9" width="13.875" customWidth="1"/>
+    <col min="8" max="8" width="17.8571428571429" customWidth="1"/>
+    <col min="9" max="9" width="133.071428571429" customWidth="1"/>
     <col min="10" max="11" width="15.125" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="14" width="15.125" customWidth="1"/>
@@ -4903,7 +4903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" hidden="1" spans="1:29">
+    <row r="25" spans="1:29">
       <c r="A25" s="7">
         <v>55040001</v>
       </c>
@@ -4992,7 +4992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" hidden="1" spans="1:29">
+    <row r="26" spans="1:29">
       <c r="A26" s="7">
         <v>55050001</v>
       </c>
@@ -5081,7 +5081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" hidden="1" spans="1:29">
+    <row r="27" spans="1:29">
       <c r="A27" s="7">
         <v>55060001</v>
       </c>
@@ -5170,7 +5170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" hidden="1" spans="1:29">
+    <row r="28" spans="1:29">
       <c r="A28" s="7">
         <v>55070001</v>
       </c>
@@ -5205,7 +5205,7 @@
         <v>2</v>
       </c>
       <c r="L28" s="7">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="M28" s="7" t="s">
         <v>70</v>
@@ -9239,9 +9239,18 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:AC74" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="0">
+    <filterColumn colId="6">
       <filters>
-        <filter val="55010001"/>
+        <filter val="技能效果-冰"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="8">
+      <filters>
+        <filter val="释放冰霜新星时，对敌人造成的冰冻几率增加【参数1万分比】"/>
+        <filter val="冰冻状态，持续时间【参数5】，冰冻状态命中率【参数6命中率】"/>
+        <filter val="攻击冰冻目标时，造成{[冰元素最终伤害]【参数1万分比】+【参数2固定值】}的[额外最终冰元素伤害]，该效果每【参数8】毫秒触发1次。"/>
+        <filter val="对冰冻有配置标再次触发冰冻效果时，造成{[最终冰元素伤害]【参数1万分比】+【参数2固定值】}的[最终冰元素伤害"/>
+        <filter val="使目标冰冻时，触发目标{生命最大值【参数1百万分比】}的[冰元素基础伤害]+{【参数2固定值】}的[额外冰元素伤害固定值]"/>
       </filters>
     </filterColumn>
     <extLst/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9146632-634B-4302-B023-DA89408F2788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935FAF2D-F3C5-430F-AC51-F5F33F5307F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="备注" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skilleffect_v8!$A$4:$AC$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skilleffect_v8!$A$4:$AC$75</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1047" uniqueCount="535">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1897,6 +1897,14 @@
   </si>
   <si>
     <t>3540201:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能-正义光环</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>60120001,60130000</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -2183,7 +2191,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2220,6 +2228,7 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="差" xfId="4" builtinId="27"/>
@@ -2519,7 +2528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC74"/>
+  <dimension ref="A1:AC75"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -7916,7 +7925,7 @@
         <v>43</v>
       </c>
       <c r="U62" s="21">
-        <v>-1</v>
+        <v>1000</v>
       </c>
       <c r="V62" s="21" t="s">
         <v>43</v>
@@ -8001,7 +8010,7 @@
         <v>43</v>
       </c>
       <c r="U63" s="21">
-        <v>-1</v>
+        <v>1000</v>
       </c>
       <c r="V63" s="21" t="s">
         <v>43</v>
@@ -8086,7 +8095,7 @@
         <v>43</v>
       </c>
       <c r="U64" s="21">
-        <v>-1</v>
+        <v>1000</v>
       </c>
       <c r="V64" s="21" t="s">
         <v>43</v>
@@ -8114,96 +8123,96 @@
       </c>
     </row>
     <row r="65" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A65" s="22">
-        <v>61010001</v>
-      </c>
-      <c r="B65" s="22">
-        <v>6101</v>
-      </c>
-      <c r="C65" s="22">
-        <v>1</v>
-      </c>
-      <c r="D65" s="22">
-        <v>0</v>
-      </c>
-      <c r="E65" s="22">
-        <v>3610300</v>
+      <c r="A65" s="21">
+        <v>60080001</v>
+      </c>
+      <c r="B65" s="21">
+        <v>6008</v>
+      </c>
+      <c r="C65" s="21">
+        <v>1</v>
+      </c>
+      <c r="D65" s="21">
+        <v>0</v>
+      </c>
+      <c r="E65" s="21">
+        <v>3541600</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>297</v>
+        <v>533</v>
       </c>
       <c r="G65" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H65" s="13"/>
       <c r="I65" s="13"/>
-      <c r="J65" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="K65" s="22">
-        <v>1</v>
-      </c>
-      <c r="L65" s="22">
-        <v>8</v>
-      </c>
-      <c r="M65" s="22" t="s">
-        <v>273</v>
-      </c>
-      <c r="N65" s="22">
-        <v>2</v>
-      </c>
-      <c r="O65" s="22">
+      <c r="J65" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="K65" s="21">
+        <v>1</v>
+      </c>
+      <c r="L65" s="21">
+        <v>0</v>
+      </c>
+      <c r="M65" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="N65" s="21">
+        <v>1</v>
+      </c>
+      <c r="O65" s="21">
+        <v>0</v>
+      </c>
+      <c r="P65" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q65" s="21">
+        <v>1</v>
+      </c>
+      <c r="R65" s="21">
+        <v>0</v>
+      </c>
+      <c r="S65" s="26" t="s">
+        <v>534</v>
+      </c>
+      <c r="T65" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="U65" s="21">
+        <v>-1</v>
+      </c>
+      <c r="V65" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W65" s="21">
         <v>10000</v>
       </c>
-      <c r="P65" s="22" t="s">
-        <v>274</v>
-      </c>
-      <c r="Q65" s="22">
-        <v>1</v>
-      </c>
-      <c r="R65" s="22">
-        <v>1</v>
-      </c>
-      <c r="S65" s="22">
-        <v>0</v>
-      </c>
-      <c r="T65" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="U65" s="22">
-        <v>0</v>
-      </c>
-      <c r="V65" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="W65" s="22">
-        <v>10000</v>
-      </c>
-      <c r="X65" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y65" s="22">
-        <v>1</v>
-      </c>
-      <c r="Z65" s="22">
-        <v>1</v>
-      </c>
-      <c r="AA65" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB65" s="22">
-        <v>1</v>
-      </c>
-      <c r="AC65" s="22">
-        <v>0</v>
+      <c r="X65" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y65" s="21">
+        <v>1</v>
+      </c>
+      <c r="Z65" s="21">
+        <v>1</v>
+      </c>
+      <c r="AA65" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB65" s="21">
+        <v>1</v>
+      </c>
+      <c r="AC65" s="21">
+        <v>1000</v>
       </c>
     </row>
     <row r="66" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A66" s="22">
-        <v>61020001</v>
+        <v>61010001</v>
       </c>
       <c r="B66" s="22">
-        <v>6102</v>
+        <v>6101</v>
       </c>
       <c r="C66" s="22">
         <v>1</v>
@@ -8212,10 +8221,10 @@
         <v>0</v>
       </c>
       <c r="E66" s="22">
-        <v>3610500</v>
+        <v>3610300</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G66" s="13" t="s">
         <v>254</v>
@@ -8223,31 +8232,31 @@
       <c r="H66" s="13"/>
       <c r="I66" s="13"/>
       <c r="J66" s="22" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="K66" s="22">
+        <v>1</v>
+      </c>
+      <c r="L66" s="22">
+        <v>8</v>
+      </c>
+      <c r="M66" s="22" t="s">
+        <v>273</v>
+      </c>
+      <c r="N66" s="22">
         <v>2</v>
       </c>
-      <c r="L66" s="22">
+      <c r="O66" s="22">
         <v>10000</v>
       </c>
-      <c r="M66" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="N66" s="22">
-        <v>1</v>
-      </c>
-      <c r="O66" s="22">
-        <v>0</v>
-      </c>
       <c r="P66" s="22" t="s">
-        <v>43</v>
+        <v>274</v>
       </c>
       <c r="Q66" s="22">
         <v>1</v>
       </c>
       <c r="R66" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S66" s="22">
         <v>0</v>
@@ -8256,7 +8265,7 @@
         <v>43</v>
       </c>
       <c r="U66" s="22">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V66" s="22" t="s">
         <v>43</v>
@@ -8285,10 +8294,10 @@
     </row>
     <row r="67" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A67" s="22">
-        <v>61030001</v>
+        <v>61020001</v>
       </c>
       <c r="B67" s="22">
-        <v>6103</v>
+        <v>6102</v>
       </c>
       <c r="C67" s="22">
         <v>1</v>
@@ -8297,10 +8306,10 @@
         <v>0</v>
       </c>
       <c r="E67" s="22">
-        <v>3610700</v>
+        <v>3610500</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="G67" s="13" t="s">
         <v>254</v>
@@ -8308,31 +8317,31 @@
       <c r="H67" s="13"/>
       <c r="I67" s="13"/>
       <c r="J67" s="22" t="s">
-        <v>43</v>
+        <v>275</v>
       </c>
       <c r="K67" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L67" s="22">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="M67" s="22" t="s">
-        <v>276</v>
+        <v>43</v>
       </c>
       <c r="N67" s="22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O67" s="22">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="P67" s="22" t="s">
-        <v>277</v>
+        <v>43</v>
       </c>
       <c r="Q67" s="22">
         <v>1</v>
       </c>
       <c r="R67" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S67" s="22">
         <v>0</v>
@@ -8341,7 +8350,7 @@
         <v>43</v>
       </c>
       <c r="U67" s="22">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V67" s="22" t="s">
         <v>43</v>
@@ -8370,10 +8379,10 @@
     </row>
     <row r="68" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A68" s="22">
-        <v>61040001</v>
+        <v>61030001</v>
       </c>
       <c r="B68" s="22">
-        <v>6104</v>
+        <v>6103</v>
       </c>
       <c r="C68" s="22">
         <v>1</v>
@@ -8382,10 +8391,10 @@
         <v>0</v>
       </c>
       <c r="E68" s="22">
-        <v>3541400</v>
+        <v>3610700</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>255</v>
+        <v>302</v>
       </c>
       <c r="G68" s="13" t="s">
         <v>254</v>
@@ -8393,31 +8402,31 @@
       <c r="H68" s="13"/>
       <c r="I68" s="13"/>
       <c r="J68" s="22" t="s">
-        <v>117</v>
+        <v>43</v>
       </c>
       <c r="K68" s="22">
+        <v>1</v>
+      </c>
+      <c r="L68" s="22">
+        <v>0</v>
+      </c>
+      <c r="M68" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="N68" s="22">
         <v>2</v>
       </c>
-      <c r="L68" s="22">
-        <v>5000</v>
-      </c>
-      <c r="M68" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="N68" s="22">
-        <v>1</v>
-      </c>
       <c r="O68" s="22">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P68" s="22" t="s">
-        <v>43</v>
+        <v>277</v>
       </c>
       <c r="Q68" s="22">
         <v>1</v>
       </c>
       <c r="R68" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S68" s="22">
         <v>0</v>
@@ -8426,7 +8435,7 @@
         <v>43</v>
       </c>
       <c r="U68" s="22">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V68" s="22" t="s">
         <v>43</v>
@@ -8455,10 +8464,10 @@
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A69" s="22">
-        <v>61050001</v>
+        <v>61040001</v>
       </c>
       <c r="B69" s="22">
-        <v>6105</v>
+        <v>6104</v>
       </c>
       <c r="C69" s="22">
         <v>1</v>
@@ -8467,10 +8476,10 @@
         <v>0</v>
       </c>
       <c r="E69" s="22">
-        <v>3610900</v>
+        <v>3541400</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>299</v>
+        <v>255</v>
       </c>
       <c r="G69" s="13" t="s">
         <v>254</v>
@@ -8478,13 +8487,13 @@
       <c r="H69" s="13"/>
       <c r="I69" s="13"/>
       <c r="J69" s="22" t="s">
-        <v>304</v>
+        <v>117</v>
       </c>
       <c r="K69" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L69" s="22">
-        <v>1</v>
+        <v>5000</v>
       </c>
       <c r="M69" s="22" t="s">
         <v>43</v>
@@ -8540,10 +8549,10 @@
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A70" s="22">
-        <v>61060001</v>
+        <v>61050001</v>
       </c>
       <c r="B70" s="22">
-        <v>6106</v>
+        <v>6105</v>
       </c>
       <c r="C70" s="22">
         <v>1</v>
@@ -8552,10 +8561,10 @@
         <v>0</v>
       </c>
       <c r="E70" s="22">
-        <v>3611100</v>
+        <v>3610900</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>370</v>
+        <v>299</v>
       </c>
       <c r="G70" s="13" t="s">
         <v>254</v>
@@ -8563,13 +8572,13 @@
       <c r="H70" s="13"/>
       <c r="I70" s="13"/>
       <c r="J70" s="22" t="s">
-        <v>43</v>
+        <v>304</v>
       </c>
       <c r="K70" s="22">
         <v>1</v>
       </c>
       <c r="L70" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="22" t="s">
         <v>43</v>
@@ -8625,10 +8634,10 @@
     </row>
     <row r="71" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A71" s="22">
-        <v>61070001</v>
+        <v>61060001</v>
       </c>
       <c r="B71" s="22">
-        <v>6107</v>
+        <v>6106</v>
       </c>
       <c r="C71" s="22">
         <v>1</v>
@@ -8637,10 +8646,10 @@
         <v>0</v>
       </c>
       <c r="E71" s="22">
-        <v>3611300</v>
+        <v>3611100</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>319</v>
+        <v>370</v>
       </c>
       <c r="G71" s="13" t="s">
         <v>254</v>
@@ -8648,13 +8657,13 @@
       <c r="H71" s="13"/>
       <c r="I71" s="13"/>
       <c r="J71" s="22" t="s">
-        <v>305</v>
+        <v>43</v>
       </c>
       <c r="K71" s="22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L71" s="22">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="M71" s="22" t="s">
         <v>43</v>
@@ -8666,13 +8675,13 @@
         <v>0</v>
       </c>
       <c r="P71" s="22" t="s">
-        <v>306</v>
+        <v>43</v>
       </c>
       <c r="Q71" s="22">
         <v>1</v>
       </c>
       <c r="R71" s="22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S71" s="22">
         <v>0</v>
@@ -8710,10 +8719,10 @@
     </row>
     <row r="72" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A72" s="22">
-        <v>61080001</v>
+        <v>61070001</v>
       </c>
       <c r="B72" s="22">
-        <v>6108</v>
+        <v>6107</v>
       </c>
       <c r="C72" s="22">
         <v>1</v>
@@ -8722,10 +8731,10 @@
         <v>0</v>
       </c>
       <c r="E72" s="22">
-        <v>3611500</v>
+        <v>3611300</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="G72" s="13" t="s">
         <v>254</v>
@@ -8733,31 +8742,31 @@
       <c r="H72" s="13"/>
       <c r="I72" s="13"/>
       <c r="J72" s="22" t="s">
-        <v>43</v>
+        <v>305</v>
       </c>
       <c r="K72" s="22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L72" s="22">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="M72" s="22" t="s">
-        <v>308</v>
+        <v>43</v>
       </c>
       <c r="N72" s="22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O72" s="22">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="P72" s="22" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="Q72" s="22">
         <v>1</v>
       </c>
       <c r="R72" s="22">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="S72" s="22">
         <v>0</v>
@@ -8766,7 +8775,7 @@
         <v>43</v>
       </c>
       <c r="U72" s="22">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V72" s="22" t="s">
         <v>43</v>
@@ -8795,10 +8804,10 @@
     </row>
     <row r="73" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A73" s="22">
-        <v>61090001</v>
+        <v>61080001</v>
       </c>
       <c r="B73" s="22">
-        <v>6109</v>
+        <v>6108</v>
       </c>
       <c r="C73" s="22">
         <v>1</v>
@@ -8807,10 +8816,10 @@
         <v>0</v>
       </c>
       <c r="E73" s="22">
-        <v>3611700</v>
+        <v>3611500</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="G73" s="13" t="s">
         <v>254</v>
@@ -8818,31 +8827,31 @@
       <c r="H73" s="13"/>
       <c r="I73" s="13"/>
       <c r="J73" s="22" t="s">
-        <v>307</v>
+        <v>43</v>
       </c>
       <c r="K73" s="22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L73" s="22">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="M73" s="22" t="s">
-        <v>43</v>
+        <v>308</v>
       </c>
       <c r="N73" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O73" s="22">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P73" s="22" t="s">
-        <v>43</v>
+        <v>309</v>
       </c>
       <c r="Q73" s="22">
         <v>1</v>
       </c>
       <c r="R73" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S73" s="22">
         <v>0</v>
@@ -8851,7 +8860,7 @@
         <v>43</v>
       </c>
       <c r="U73" s="22">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V73" s="22" t="s">
         <v>43</v>
@@ -8880,10 +8889,10 @@
     </row>
     <row r="74" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A74" s="22">
-        <v>61100001</v>
+        <v>61090001</v>
       </c>
       <c r="B74" s="22">
-        <v>6110</v>
+        <v>6109</v>
       </c>
       <c r="C74" s="22">
         <v>1</v>
@@ -8892,10 +8901,10 @@
         <v>0</v>
       </c>
       <c r="E74" s="22">
-        <v>3590800</v>
+        <v>3611700</v>
       </c>
       <c r="F74" s="13" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="G74" s="13" t="s">
         <v>254</v>
@@ -8903,31 +8912,31 @@
       <c r="H74" s="13"/>
       <c r="I74" s="13"/>
       <c r="J74" s="22" t="s">
-        <v>43</v>
+        <v>307</v>
       </c>
       <c r="K74" s="22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L74" s="22">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="M74" s="22" t="s">
-        <v>303</v>
+        <v>43</v>
       </c>
       <c r="N74" s="22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O74" s="22">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="P74" s="22" t="s">
-        <v>310</v>
+        <v>43</v>
       </c>
       <c r="Q74" s="22">
         <v>1</v>
       </c>
       <c r="R74" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S74" s="22">
         <v>0</v>
@@ -8936,7 +8945,7 @@
         <v>43</v>
       </c>
       <c r="U74" s="22">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V74" s="22" t="s">
         <v>43</v>
@@ -8963,8 +8972,93 @@
         <v>0</v>
       </c>
     </row>
+    <row r="75" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A75" s="22">
+        <v>61100001</v>
+      </c>
+      <c r="B75" s="22">
+        <v>6110</v>
+      </c>
+      <c r="C75" s="22">
+        <v>1</v>
+      </c>
+      <c r="D75" s="22">
+        <v>0</v>
+      </c>
+      <c r="E75" s="22">
+        <v>3590800</v>
+      </c>
+      <c r="F75" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="G75" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="H75" s="13"/>
+      <c r="I75" s="13"/>
+      <c r="J75" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="K75" s="22">
+        <v>1</v>
+      </c>
+      <c r="L75" s="22">
+        <v>0</v>
+      </c>
+      <c r="M75" s="22" t="s">
+        <v>303</v>
+      </c>
+      <c r="N75" s="22">
+        <v>2</v>
+      </c>
+      <c r="O75" s="22">
+        <v>10000</v>
+      </c>
+      <c r="P75" s="22" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q75" s="22">
+        <v>1</v>
+      </c>
+      <c r="R75" s="22">
+        <v>1</v>
+      </c>
+      <c r="S75" s="22">
+        <v>0</v>
+      </c>
+      <c r="T75" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="U75" s="22">
+        <v>0</v>
+      </c>
+      <c r="V75" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="W75" s="22">
+        <v>10000</v>
+      </c>
+      <c r="X75" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y75" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z75" s="22">
+        <v>1</v>
+      </c>
+      <c r="AA75" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB75" s="22">
+        <v>1</v>
+      </c>
+      <c r="AC75" s="22">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:AC74" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:AC75" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935FAF2D-F3C5-430F-AC51-F5F33F5307F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09AA41F9-F4F7-4791-8C93-4D14E7CAA46E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1047" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="539">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1906,6 +1906,19 @@
   <si>
     <t>60120001,60130000</t>
     <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>护盾技能-每X秒获得最大生命值的护盾</t>
+  </si>
+  <si>
+    <t>955001002</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得护盾</t>
+  </si>
+  <si>
+    <t>3590405:1</t>
   </si>
 </sst>
 </file>
@@ -2528,7 +2541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC75"/>
+  <dimension ref="A1:AC77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -9057,6 +9070,172 @@
         <v>0</v>
       </c>
     </row>
+    <row r="76" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A76" s="21">
+        <v>855001001</v>
+      </c>
+      <c r="B76" s="21">
+        <v>7001</v>
+      </c>
+      <c r="C76" s="21">
+        <v>1</v>
+      </c>
+      <c r="D76" s="21">
+        <v>0</v>
+      </c>
+      <c r="E76" s="21">
+        <v>3541600</v>
+      </c>
+      <c r="F76" s="13" t="s">
+        <v>535</v>
+      </c>
+      <c r="G76" s="13"/>
+      <c r="H76" s="13"/>
+      <c r="I76" s="13"/>
+      <c r="J76" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="K76" s="21">
+        <v>1</v>
+      </c>
+      <c r="L76" s="21">
+        <v>0</v>
+      </c>
+      <c r="M76" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="N76" s="21">
+        <v>1</v>
+      </c>
+      <c r="O76" s="21">
+        <v>0</v>
+      </c>
+      <c r="P76" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q76" s="21">
+        <v>1</v>
+      </c>
+      <c r="R76" s="21">
+        <v>0</v>
+      </c>
+      <c r="S76" s="26" t="s">
+        <v>536</v>
+      </c>
+      <c r="T76" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="U76" s="21">
+        <v>-1</v>
+      </c>
+      <c r="V76" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W76" s="21">
+        <v>10000</v>
+      </c>
+      <c r="X76" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y76" s="21">
+        <v>1</v>
+      </c>
+      <c r="Z76" s="21">
+        <v>1</v>
+      </c>
+      <c r="AA76" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB76" s="21">
+        <v>1</v>
+      </c>
+      <c r="AC76" s="21">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A77" s="21">
+        <v>855001002</v>
+      </c>
+      <c r="B77" s="21">
+        <v>7002</v>
+      </c>
+      <c r="C77" s="21">
+        <v>1</v>
+      </c>
+      <c r="D77" s="21">
+        <v>0</v>
+      </c>
+      <c r="E77" s="21">
+        <v>3590400</v>
+      </c>
+      <c r="F77" s="13" t="s">
+        <v>537</v>
+      </c>
+      <c r="G77" s="13"/>
+      <c r="H77" s="13"/>
+      <c r="I77" s="13"/>
+      <c r="J77" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="K77" s="21">
+        <v>3</v>
+      </c>
+      <c r="L77" s="21">
+        <v>200000</v>
+      </c>
+      <c r="M77" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="N77" s="21">
+        <v>1</v>
+      </c>
+      <c r="O77" s="21">
+        <v>0</v>
+      </c>
+      <c r="P77" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q77" s="21">
+        <v>1</v>
+      </c>
+      <c r="R77" s="21">
+        <v>0</v>
+      </c>
+      <c r="S77" s="26">
+        <v>0</v>
+      </c>
+      <c r="T77" s="21" t="s">
+        <v>538</v>
+      </c>
+      <c r="U77" s="21">
+        <v>4000</v>
+      </c>
+      <c r="V77" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W77" s="21">
+        <v>10000</v>
+      </c>
+      <c r="X77" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y77" s="21">
+        <v>1</v>
+      </c>
+      <c r="Z77" s="21">
+        <v>1</v>
+      </c>
+      <c r="AA77" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB77" s="21">
+        <v>1</v>
+      </c>
+      <c r="AC77" s="21">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A4:AC75" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="12" type="noConversion"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09AA41F9-F4F7-4791-8C93-4D14E7CAA46E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B8E5BA-9B42-46DD-9D5E-2010119384DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="542">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1919,6 +1919,17 @@
   </si>
   <si>
     <t>3590405:1</t>
+  </si>
+  <si>
+    <t>（获得）雷击</t>
+  </si>
+  <si>
+    <t>（获得）冰弹</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>（获得）陨石</t>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2204,7 +2215,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2242,6 +2253,10 @@
     <xf numFmtId="0" fontId="15" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="3" fillId="3" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="差" xfId="4" builtinId="27"/>
@@ -2541,7 +2556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC77"/>
+  <dimension ref="A1:AC80"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -9236,6 +9251,255 @@
         <v>0</v>
       </c>
     </row>
+    <row r="78" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="27">
+        <v>855001003</v>
+      </c>
+      <c r="B78" s="27">
+        <v>7003</v>
+      </c>
+      <c r="C78" s="28">
+        <v>1</v>
+      </c>
+      <c r="D78" s="28">
+        <v>0</v>
+      </c>
+      <c r="E78" s="29">
+        <v>3541600</v>
+      </c>
+      <c r="F78" s="29" t="s">
+        <v>539</v>
+      </c>
+      <c r="G78" s="29" t="s">
+        <v>539</v>
+      </c>
+      <c r="J78" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="K78" s="27">
+        <v>1</v>
+      </c>
+      <c r="L78" s="27">
+        <v>0</v>
+      </c>
+      <c r="M78" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N78" s="27">
+        <v>1</v>
+      </c>
+      <c r="O78" s="27">
+        <v>0</v>
+      </c>
+      <c r="P78" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q78" s="27">
+        <v>1</v>
+      </c>
+      <c r="R78" s="27">
+        <v>0</v>
+      </c>
+      <c r="S78" s="28">
+        <v>955001004</v>
+      </c>
+      <c r="T78" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U78" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V78" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W78" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X78" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y78" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z78" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA78" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB78" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC78" s="27">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="27">
+        <v>855001004</v>
+      </c>
+      <c r="B79" s="27">
+        <v>7004</v>
+      </c>
+      <c r="C79" s="28">
+        <v>1</v>
+      </c>
+      <c r="D79" s="28">
+        <v>0</v>
+      </c>
+      <c r="E79" s="29">
+        <v>3541600</v>
+      </c>
+      <c r="F79" s="30" t="s">
+        <v>540</v>
+      </c>
+      <c r="G79" s="30" t="s">
+        <v>540</v>
+      </c>
+      <c r="J79" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="K79" s="27">
+        <v>1</v>
+      </c>
+      <c r="L79" s="27">
+        <v>0</v>
+      </c>
+      <c r="M79" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N79" s="27">
+        <v>1</v>
+      </c>
+      <c r="O79" s="27">
+        <v>0</v>
+      </c>
+      <c r="P79" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q79" s="27">
+        <v>1</v>
+      </c>
+      <c r="R79" s="27">
+        <v>0</v>
+      </c>
+      <c r="S79" s="28">
+        <v>955001004</v>
+      </c>
+      <c r="T79" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U79" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V79" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W79" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X79" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y79" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z79" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA79" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB79" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC79" s="27">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="27">
+        <v>855001005</v>
+      </c>
+      <c r="B80" s="27">
+        <v>7005</v>
+      </c>
+      <c r="C80" s="28">
+        <v>1</v>
+      </c>
+      <c r="D80" s="28">
+        <v>0</v>
+      </c>
+      <c r="E80" s="29">
+        <v>3541600</v>
+      </c>
+      <c r="F80" s="30" t="s">
+        <v>541</v>
+      </c>
+      <c r="G80" s="30" t="s">
+        <v>541</v>
+      </c>
+      <c r="J80" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="K80" s="27">
+        <v>1</v>
+      </c>
+      <c r="L80" s="27">
+        <v>0</v>
+      </c>
+      <c r="M80" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N80" s="27">
+        <v>1</v>
+      </c>
+      <c r="O80" s="27">
+        <v>0</v>
+      </c>
+      <c r="P80" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q80" s="27">
+        <v>1</v>
+      </c>
+      <c r="R80" s="27">
+        <v>0</v>
+      </c>
+      <c r="S80" s="28">
+        <v>955001004</v>
+      </c>
+      <c r="T80" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U80" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V80" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W80" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X80" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y80" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z80" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA80" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB80" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC80" s="27">
+        <v>10000</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A4:AC75" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="12" type="noConversion"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B8E5BA-9B42-46DD-9D5E-2010119384DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63ECEFA4-53D9-48E8-83BD-2F241907F6E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2215,7 +2215,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2255,8 +2255,7 @@
     <xf numFmtId="3" fontId="3" fillId="3" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="差" xfId="4" builtinId="27"/>
@@ -9251,7 +9250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A78" s="27">
         <v>855001003</v>
       </c>
@@ -9264,13 +9263,13 @@
       <c r="D78" s="28">
         <v>0</v>
       </c>
-      <c r="E78" s="29">
-        <v>3541600</v>
-      </c>
-      <c r="F78" s="29" t="s">
+      <c r="E78">
+        <v>3590401</v>
+      </c>
+      <c r="F78" t="s">
         <v>539</v>
       </c>
-      <c r="G78" s="29" t="s">
+      <c r="G78" t="s">
         <v>539</v>
       </c>
       <c r="J78" s="27" t="s">
@@ -9334,7 +9333,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="79" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A79" s="27">
         <v>855001004</v>
       </c>
@@ -9347,13 +9346,13 @@
       <c r="D79" s="28">
         <v>0</v>
       </c>
-      <c r="E79" s="29">
-        <v>3541600</v>
-      </c>
-      <c r="F79" s="30" t="s">
+      <c r="E79">
+        <v>3590401</v>
+      </c>
+      <c r="F79" s="29" t="s">
         <v>540</v>
       </c>
-      <c r="G79" s="30" t="s">
+      <c r="G79" s="29" t="s">
         <v>540</v>
       </c>
       <c r="J79" s="27" t="s">
@@ -9417,7 +9416,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="80" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A80" s="27">
         <v>855001005</v>
       </c>
@@ -9430,13 +9429,13 @@
       <c r="D80" s="28">
         <v>0</v>
       </c>
-      <c r="E80" s="29">
-        <v>3541600</v>
-      </c>
-      <c r="F80" s="30" t="s">
+      <c r="E80">
+        <v>3590401</v>
+      </c>
+      <c r="F80" s="29" t="s">
         <v>541</v>
       </c>
-      <c r="G80" s="30" t="s">
+      <c r="G80" s="29" t="s">
         <v>541</v>
       </c>
       <c r="J80" s="27" t="s">

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63ECEFA4-53D9-48E8-83BD-2F241907F6E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713E1096-DCA9-455A-92D2-68B8394B20E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="备注" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skilleffect_v8!$A$4:$AC$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skilleffect_v8!$A$4:$AC$77</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="547">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1025,67 +1025,907 @@
     <t>3590603:1</t>
   </si>
   <si>
+    <t>3590803:1</t>
+  </si>
+  <si>
+    <t>3591001:1</t>
+  </si>
+  <si>
+    <t>3591201:1</t>
+  </si>
+  <si>
+    <t>3591202:1</t>
+  </si>
+  <si>
+    <t>3591203:1</t>
+  </si>
+  <si>
+    <t>3591401:1</t>
+  </si>
+  <si>
+    <t>3591402:1</t>
+  </si>
+  <si>
+    <t>3591403:1</t>
+  </si>
+  <si>
+    <t>3591602:1</t>
+  </si>
+  <si>
+    <t>3591603:1</t>
+  </si>
+  <si>
+    <t>3591902:1</t>
+  </si>
+  <si>
+    <t>3600701:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击次数触发技能重击</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>重击技能暴击率提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能攻击累计额外次数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>斩杀暴击触发斩杀血线变化</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀触发暴击率提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击触发技能暴击伤害提高、致命暴击、额外次数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
     <t>3590802:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3610901:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611301:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611303:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611701:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611502:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611503:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>3590803:1</t>
-  </si>
-  <si>
-    <t>3591001:1</t>
-  </si>
-  <si>
-    <t>3591201:1</t>
-  </si>
-  <si>
-    <t>3591202:1</t>
-  </si>
-  <si>
-    <t>3591203:1</t>
-  </si>
-  <si>
-    <t>3591401:1</t>
-  </si>
-  <si>
-    <t>3591402:1</t>
-  </si>
-  <si>
-    <t>3591403:1</t>
-  </si>
-  <si>
-    <t>3591602:1</t>
-  </si>
-  <si>
-    <t>3591603:1</t>
-  </si>
-  <si>
-    <t>3591902:1</t>
-  </si>
-  <si>
-    <t>3600701:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击次数触发技能重击</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>重击技能暴击率提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能攻击累计额外次数</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>斩杀暴击触发斩杀血线变化</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀触发暴击率提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴击触发技能暴击伤害提高、致命暴击、额外次数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能名称</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数描述</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>有护盾时受到伤害降低</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>低血时受到伤害降低</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能效果-敌人伤害降低</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能效果-敌人受到伤害提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能效果-光环效果影响范围变化</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标血量低于百万分比触发斩杀</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>斩杀血线提高效果</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581201:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581202:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581207:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3570902:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>MAP&lt;INT:INT&gt;_S</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT_S</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>attr_value_8_variable_id</t>
+  </si>
+  <si>
+    <t>attr_value_8_type</t>
+  </si>
+  <si>
+    <t>attr_value_8</t>
+  </si>
+  <si>
+    <t>参数8关联的变量id</t>
+  </si>
+  <si>
+    <t>参数8数值类型</t>
+  </si>
+  <si>
+    <t>参数8</t>
+  </si>
+  <si>
+    <t>每【参数8】毫秒，造成{[火元素直接伤害]【参数1万分比】}，【参数2】的[额外火元素持续伤害]，效果持续【参数5】毫秒，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>每【参数8】毫秒，触发等同于[毒元素直接伤害]*【参数1万分比毒持续buff系数】+【参数2】的[额外毒持续伤害]，效果持续【持续5】毫秒，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>每【参数8】毫秒，触发等同于[毒元素直接伤害]*【参数1万分比毒持续buff系数】+【参数2】的[额外毒持续伤害]，状态持续【持续5】毫秒，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>3041108:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>拥有这个技能效果时，命中敌人时，攻击者回复固定值【参数1固定值】的血量，触发冷却时间【参数8】毫秒</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3560208:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3580208:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581208:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3591002:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3591003:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧时，被攻击受到额外伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧时被攻击受到额外伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触电时，[受到所有类型伤害提高]【参数1万分比】+【参数2】受到[受到所有类型额外伤害固定值]</t>
+  </si>
+  <si>
+    <t>触电时受到伤害提高</t>
+  </si>
+  <si>
+    <t>3570503:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>使目标触电时，造成1次触电伤害</t>
+  </si>
+  <si>
+    <t>使目标触电时，造成1次触电伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰冻状态，持续时间【参数5】，冰冻状态命中率【参数6命中率】</t>
+  </si>
+  <si>
+    <t>每攻击【参数1】次，有【参数2】几率触发【参数3】次指定技能【参数4】</t>
+  </si>
+  <si>
+    <t>每【参数8】毫秒，在释放冰霜新星时有【参数2】几率，触发【参数3】次数，技能id【参数4】</t>
+  </si>
+  <si>
+    <t>对冰冻有配置标再次触发冰冻效果时，造成{[最终冰元素伤害]【参数1万分比】+【参数2固定值】}的[最终冰元素伤害</t>
+  </si>
+  <si>
+    <t>使目标冰冻时，触发目标{生命最大值【参数1百万分比】}的[冰元素基础伤害]+{【参数2固定值】}的[额外冰元素伤害固定值]</t>
+  </si>
+  <si>
+    <t>攻击冰冻目标时，造成{[冰元素最终伤害]【参数1万分比】+【参数2固定值】}的[额外最终冰元素伤害]，该效果每【参数8】毫秒触发1次。</t>
+  </si>
+  <si>
+    <t>攻击冰冻目标时造成额外伤害</t>
+  </si>
+  <si>
+    <t>中毒目标再次中毒受到额外中毒伤害</t>
+  </si>
+  <si>
+    <t>中毒目标再次中毒时，造成每次中毒结算伤害*【参数1】次数*【参数2万分比】的[最终毒元素伤害]</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3580702:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>复活回复血量、触发次数、触发间隔</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3591908:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3561401:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3561402:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3561408:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧时，被攻击会额外受到1次[最终火元素伤害]【参数1万分比】+【参数2固定值】的[额外最终火元素伤害]，该效果每【参数8】毫秒触发1次。</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3570205:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3580205:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581205:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3590405:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>致命暴击状态攻速提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3592101:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回血效果提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3551103:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数8结算间隔时间</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>逻辑属性id</t>
+  </si>
+  <si>
+    <t>技能效果</t>
+  </si>
+  <si>
+    <t>技能名称</t>
+  </si>
+  <si>
+    <t>参数描述</t>
+  </si>
+  <si>
+    <t>效果叠加层数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>结算间隔时间（毫秒）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复中buff组的cd时间（毫秒）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数5</t>
+  </si>
+  <si>
+    <t>参数6</t>
+  </si>
+  <si>
+    <t>持续时间（毫秒）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果最大叠加层数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果基础命中率（万分比）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果触发间隔（毫秒）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数4LIST</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发的技能id</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数9</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数10</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数11</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数12</t>
+  </si>
+  <si>
+    <t>参数13</t>
+  </si>
+  <si>
+    <t>击中回复生命值-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击中回复效果提高万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回复生命-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数14</t>
+  </si>
+  <si>
+    <t>参数15</t>
+  </si>
+  <si>
+    <t>参数16</t>
+  </si>
+  <si>
+    <t>击中回复生命值-自身最大生命值百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回复生命-自身最大生命值百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回复生命-目标最大生命值百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数17</t>
+  </si>
+  <si>
+    <t>参数18</t>
+  </si>
+  <si>
+    <t>参数19</t>
+  </si>
+  <si>
+    <t>参数20</t>
+  </si>
+  <si>
+    <t>参数21</t>
+  </si>
+  <si>
+    <t>参数22</t>
+  </si>
+  <si>
+    <t>参数28</t>
+  </si>
+  <si>
+    <t>参数29</t>
+  </si>
+  <si>
+    <t>获得护盾-自身生命百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得护盾-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得护盾效果提高万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回复生命效果提高万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得护盾-自身已损失生命万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>复活</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发自动技能</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数30</t>
+  </si>
+  <si>
+    <t>参数31</t>
+  </si>
+  <si>
+    <t>参数32</t>
+  </si>
+  <si>
+    <t>参数33</t>
+  </si>
+  <si>
+    <t>参数34</t>
+  </si>
+  <si>
+    <t>参数35</t>
+  </si>
+  <si>
+    <t>参数36</t>
+  </si>
+  <si>
+    <t>参数37</t>
+  </si>
+  <si>
+    <t>参数38</t>
+  </si>
+  <si>
+    <t>参数39</t>
+  </si>
+  <si>
+    <t>参数40</t>
+  </si>
+  <si>
+    <t>参数41</t>
+  </si>
+  <si>
+    <t>参数42</t>
+  </si>
+  <si>
+    <t>参数43</t>
+  </si>
+  <si>
+    <t>参数44</t>
+  </si>
+  <si>
+    <t>主动技能</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>回复生命</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击中目标</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰霜新星</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪电链</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>传染</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>瘟疫</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>多重打击</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>旋风斩</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>斩杀</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>半月斩</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡爆炸</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>电磁爆发</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>重击</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能增加-万分比</t>
+  </si>
+  <si>
+    <t>技能增加-普通攻击范围万分比</t>
+  </si>
+  <si>
+    <t>攻击提高-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御提高-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击提高-攻击的元素类型</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数25LIST</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数45</t>
+  </si>
+  <si>
+    <t>参数46</t>
+  </si>
+  <si>
+    <t>参数47</t>
+  </si>
+  <si>
+    <t>参数48</t>
+  </si>
+  <si>
+    <t>参数49</t>
+  </si>
+  <si>
+    <t>参数50</t>
+  </si>
+  <si>
+    <t>参数51</t>
+  </si>
+  <si>
+    <t>参数52</t>
+  </si>
+  <si>
+    <t>参数53</t>
+  </si>
+  <si>
+    <t>参数54</t>
+  </si>
+  <si>
+    <t>参数55</t>
+  </si>
+  <si>
+    <t>参数56</t>
+  </si>
+  <si>
+    <t>生命上限提高-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命上限提高-百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击速度提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动速度提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击范围提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击目标数量提高-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能增加-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT_S</t>
+  </si>
+  <si>
+    <t>auto_cd</t>
+  </si>
+  <si>
+    <t>参数-重复触发自动释放冷却时间（毫秒）</t>
+  </si>
+  <si>
+    <t>release_ratio</t>
+  </si>
+  <si>
+    <t>参数-释放几率</t>
+  </si>
+  <si>
+    <t>release_num</t>
+  </si>
+  <si>
+    <t>参数-释放次数</t>
+  </si>
+  <si>
+    <t>LIST&lt;INT&gt;_S</t>
+  </si>
+  <si>
+    <t>skill_id</t>
+  </si>
+  <si>
+    <t>参数-释放的技能id</t>
+  </si>
+  <si>
+    <t>total_attack_num</t>
+  </si>
+  <si>
+    <t>参数-累计发起攻击次数时</t>
+  </si>
+  <si>
+    <t>lose_hp_ratio</t>
+  </si>
+  <si>
+    <t>参数-损失自身生命最大值百万分比时</t>
+  </si>
+  <si>
+    <t>kill_target_after</t>
+  </si>
+  <si>
+    <t>参数-击杀目标后</t>
+  </si>
+  <si>
+    <t>after_attack_crit</t>
+  </si>
+  <si>
+    <t>参数-攻击暴击后</t>
+  </si>
+  <si>
+    <t>after_use_skill</t>
+  </si>
+  <si>
+    <t>参数-释放【技能id】后</t>
+  </si>
+  <si>
+    <t>cycle_time</t>
+  </si>
+  <si>
+    <t>参数-每过固定时间（毫秒）时</t>
+  </si>
+  <si>
+    <t>after_skill_hit</t>
+  </si>
+  <si>
+    <t>参数-【技能id】命中后</t>
+  </si>
+  <si>
+    <t>after_self_death</t>
+  </si>
+  <si>
+    <t>参数-自身死亡后释放</t>
+  </si>
+  <si>
+    <t>MAP&lt;INT:INT&gt;_S</t>
+  </si>
+  <si>
+    <t>self_have_effect</t>
+  </si>
+  <si>
+    <t>参数-自身拥有【效果id：&gt;=层数】时</t>
+  </si>
+  <si>
+    <t>target_have_effect</t>
+  </si>
+  <si>
+    <t>参数-目标拥有【效果id：&gt;=层数】时</t>
+  </si>
+  <si>
+    <t>target_hp_ratio_over</t>
+  </si>
+  <si>
+    <t>参数-目标当前生命值&gt;=最大生命值的百万分之X时</t>
+  </si>
+  <si>
+    <t>target_hp_ratio_under</t>
+  </si>
+  <si>
+    <t>参数-目标当前生命值&lt;=最大生命值的百万分之X时</t>
+  </si>
+  <si>
+    <t>to_target_effect_hit</t>
+  </si>
+  <si>
+    <t>参数-对目标施加【效果id】命中时</t>
+  </si>
+  <si>
+    <t>order</t>
+  </si>
+  <si>
+    <t>自动</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>受到的伤害总加成</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成伤害总加成</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成的伤害总加成【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到的伤害总加成【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542801:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542601:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3543001:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542607:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542807:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3543007:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542605:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542805:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3543005:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3540201:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能-正义光环</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>60120001,60130000</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>护盾技能-每X秒获得最大生命值的护盾</t>
+  </si>
+  <si>
+    <t>955001002</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得护盾</t>
+  </si>
+  <si>
+    <t>3590405:1</t>
+  </si>
+  <si>
+    <t>（获得）雷击</t>
+  </si>
+  <si>
+    <t>（获得）冰弹</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>（获得）陨石</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
@@ -1093,842 +1933,23 @@
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
-    <t>3610901:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611301:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611303:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611701:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611502:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611503:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3590803:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能名称</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能效果</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数描述</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>有护盾时受到伤害降低</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>低血时受到伤害降低</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>光环技能效果-敌人伤害降低</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>光环技能效果-敌人受到伤害提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>光环技能效果-光环效果影响范围变化</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标血量低于百万分比触发斩杀</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>斩杀血线提高效果</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581201:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581202:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581207:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3570902:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>MAP&lt;INT:INT&gt;_S</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>INT_S</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>attr_value_8_variable_id</t>
-  </si>
-  <si>
-    <t>attr_value_8_type</t>
-  </si>
-  <si>
-    <t>attr_value_8</t>
-  </si>
-  <si>
-    <t>参数8关联的变量id</t>
-  </si>
-  <si>
-    <t>参数8数值类型</t>
-  </si>
-  <si>
-    <t>参数8</t>
-  </si>
-  <si>
-    <t>每【参数8】毫秒，造成{[火元素直接伤害]【参数1万分比】}，【参数2】的[额外火元素持续伤害]，效果持续【参数5】毫秒，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>每【参数8】毫秒，触发等同于[毒元素直接伤害]*【参数1万分比毒持续buff系数】+【参数2】的[额外毒持续伤害]，效果持续【持续5】毫秒，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>每【参数8】毫秒，触发等同于[毒元素直接伤害]*【参数1万分比毒持续buff系数】+【参数2】的[额外毒持续伤害]，状态持续【持续5】毫秒，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>3041108:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>拥有这个技能效果时，命中敌人时，攻击者回复固定值【参数1固定值】的血量，触发冷却时间【参数8】毫秒</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3560208:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3580208:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581208:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3591002:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3591003:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧时，被攻击受到额外伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧时被攻击受到额外伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>触电时，[受到所有类型伤害提高]【参数1万分比】+【参数2】受到[受到所有类型额外伤害固定值]</t>
-  </si>
-  <si>
-    <t>触电时受到伤害提高</t>
-  </si>
-  <si>
-    <t>3570503:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>使目标触电时，造成1次触电伤害</t>
-  </si>
-  <si>
-    <t>使目标触电时，造成1次触电伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰冻状态，持续时间【参数5】，冰冻状态命中率【参数6命中率】</t>
-  </si>
-  <si>
-    <t>每攻击【参数1】次，有【参数2】几率触发【参数3】次指定技能【参数4】</t>
-  </si>
-  <si>
-    <t>每【参数8】毫秒，在释放冰霜新星时有【参数2】几率，触发【参数3】次数，技能id【参数4】</t>
-  </si>
-  <si>
-    <t>对冰冻有配置标再次触发冰冻效果时，造成{[最终冰元素伤害]【参数1万分比】+【参数2固定值】}的[最终冰元素伤害</t>
-  </si>
-  <si>
-    <t>使目标冰冻时，触发目标{生命最大值【参数1百万分比】}的[冰元素基础伤害]+{【参数2固定值】}的[额外冰元素伤害固定值]</t>
-  </si>
-  <si>
-    <t>攻击冰冻目标时，造成{[冰元素最终伤害]【参数1万分比】+【参数2固定值】}的[额外最终冰元素伤害]，该效果每【参数8】毫秒触发1次。</t>
-  </si>
-  <si>
-    <t>攻击冰冻目标时造成额外伤害</t>
-  </si>
-  <si>
-    <t>中毒目标再次中毒受到额外中毒伤害</t>
-  </si>
-  <si>
-    <t>中毒目标再次中毒时，造成每次中毒结算伤害*【参数1】次数*【参数2万分比】的[最终毒元素伤害]</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3580702:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>复活回复血量、触发次数、触发间隔</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3591908:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3561401:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3561402:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3561408:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧时，被攻击会额外受到1次[最终火元素伤害]【参数1万分比】+【参数2固定值】的[额外最终火元素伤害]，该效果每【参数8】毫秒触发1次。</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3570205:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3580205:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581205:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3590405:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>致命暴击状态攻速提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3592101:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀回血效果提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3551103:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数8结算间隔时间</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>逻辑属性id</t>
-  </si>
-  <si>
-    <t>技能效果</t>
-  </si>
-  <si>
-    <t>技能名称</t>
-  </si>
-  <si>
-    <t>参数描述</t>
-  </si>
-  <si>
-    <t>效果叠加层数</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>结算间隔时间（毫秒）</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>重复中buff组的cd时间（毫秒）</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数5</t>
-  </si>
-  <si>
-    <t>参数6</t>
-  </si>
-  <si>
-    <t>持续时间（毫秒）</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>效果最大叠加层数</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>效果基础命中率（万分比）</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>效果触发间隔（毫秒）</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数4LIST</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>触发的技能id</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数9</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数10</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数11</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数12</t>
-  </si>
-  <si>
-    <t>参数13</t>
-  </si>
-  <si>
-    <t>击中回复生命值-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击中回复效果提高万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀回复生命-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数14</t>
-  </si>
-  <si>
-    <t>参数15</t>
-  </si>
-  <si>
-    <t>参数16</t>
-  </si>
-  <si>
-    <t>击中回复生命值-自身最大生命值百万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀回复生命-自身最大生命值百万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀回复生命-目标最大生命值百万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数17</t>
-  </si>
-  <si>
-    <t>参数18</t>
-  </si>
-  <si>
-    <t>参数19</t>
-  </si>
-  <si>
-    <t>参数20</t>
-  </si>
-  <si>
-    <t>参数21</t>
-  </si>
-  <si>
-    <t>参数22</t>
-  </si>
-  <si>
-    <t>参数28</t>
-  </si>
-  <si>
-    <t>参数29</t>
-  </si>
-  <si>
-    <t>获得护盾-自身生命百万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得护盾-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得护盾效果提高万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀回复生命效果提高万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得护盾-自身已损失生命万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>复活</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>触发自动技能</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数30</t>
-  </si>
-  <si>
-    <t>参数31</t>
-  </si>
-  <si>
-    <t>参数32</t>
-  </si>
-  <si>
-    <t>参数33</t>
-  </si>
-  <si>
-    <t>参数34</t>
-  </si>
-  <si>
-    <t>参数35</t>
-  </si>
-  <si>
-    <t>参数36</t>
-  </si>
-  <si>
-    <t>参数37</t>
-  </si>
-  <si>
-    <t>参数38</t>
-  </si>
-  <si>
-    <t>参数39</t>
-  </si>
-  <si>
-    <t>参数40</t>
-  </si>
-  <si>
-    <t>参数41</t>
-  </si>
-  <si>
-    <t>参数42</t>
-  </si>
-  <si>
-    <t>参数43</t>
-  </si>
-  <si>
-    <t>参数44</t>
-  </si>
-  <si>
-    <t>主动技能</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>回复生命</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击中目标</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰霜新星</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>陨石</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>闪电链</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>传染</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>瘟疫</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>多重打击</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>旋风斩</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>斩杀</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>半月斩</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>死亡爆炸</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>电磁爆发</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>重击</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能增加-万分比</t>
-  </si>
-  <si>
-    <t>技能增加-普通攻击范围万分比</t>
-  </si>
-  <si>
-    <t>攻击提高-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击提高-万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>防御提高-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>防御提高-万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击提高-攻击的元素类型</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数25LIST</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数45</t>
-  </si>
-  <si>
-    <t>参数46</t>
-  </si>
-  <si>
-    <t>参数47</t>
-  </si>
-  <si>
-    <t>参数48</t>
-  </si>
-  <si>
-    <t>参数49</t>
-  </si>
-  <si>
-    <t>参数50</t>
-  </si>
-  <si>
-    <t>参数51</t>
-  </si>
-  <si>
-    <t>参数52</t>
-  </si>
-  <si>
-    <t>参数53</t>
-  </si>
-  <si>
-    <t>参数54</t>
-  </si>
-  <si>
-    <t>参数55</t>
-  </si>
-  <si>
-    <t>参数56</t>
-  </si>
-  <si>
-    <t>生命上限提高-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>生命上限提高-百万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击速度提高-万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>移动速度提高-万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击范围提高-万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击目标数量提高-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能增加-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>INT_S</t>
-  </si>
-  <si>
-    <t>auto_cd</t>
-  </si>
-  <si>
-    <t>参数-重复触发自动释放冷却时间（毫秒）</t>
-  </si>
-  <si>
-    <t>release_ratio</t>
-  </si>
-  <si>
-    <t>参数-释放几率</t>
-  </si>
-  <si>
-    <t>release_num</t>
-  </si>
-  <si>
-    <t>参数-释放次数</t>
-  </si>
-  <si>
-    <t>LIST&lt;INT&gt;_S</t>
-  </si>
-  <si>
-    <t>skill_id</t>
-  </si>
-  <si>
-    <t>参数-释放的技能id</t>
-  </si>
-  <si>
-    <t>total_attack_num</t>
-  </si>
-  <si>
-    <t>参数-累计发起攻击次数时</t>
-  </si>
-  <si>
-    <t>lose_hp_ratio</t>
-  </si>
-  <si>
-    <t>参数-损失自身生命最大值百万分比时</t>
-  </si>
-  <si>
-    <t>kill_target_after</t>
-  </si>
-  <si>
-    <t>参数-击杀目标后</t>
-  </si>
-  <si>
-    <t>after_attack_crit</t>
-  </si>
-  <si>
-    <t>参数-攻击暴击后</t>
-  </si>
-  <si>
-    <t>after_use_skill</t>
-  </si>
-  <si>
-    <t>参数-释放【技能id】后</t>
-  </si>
-  <si>
-    <t>cycle_time</t>
-  </si>
-  <si>
-    <t>参数-每过固定时间（毫秒）时</t>
-  </si>
-  <si>
-    <t>after_skill_hit</t>
-  </si>
-  <si>
-    <t>参数-【技能id】命中后</t>
-  </si>
-  <si>
-    <t>after_self_death</t>
-  </si>
-  <si>
-    <t>参数-自身死亡后释放</t>
-  </si>
-  <si>
-    <t>MAP&lt;INT:INT&gt;_S</t>
-  </si>
-  <si>
-    <t>self_have_effect</t>
-  </si>
-  <si>
-    <t>参数-自身拥有【效果id：&gt;=层数】时</t>
-  </si>
-  <si>
-    <t>target_have_effect</t>
-  </si>
-  <si>
-    <t>参数-目标拥有【效果id：&gt;=层数】时</t>
-  </si>
-  <si>
-    <t>target_hp_ratio_over</t>
-  </si>
-  <si>
-    <t>参数-目标当前生命值&gt;=最大生命值的百万分之X时</t>
-  </si>
-  <si>
-    <t>target_hp_ratio_under</t>
-  </si>
-  <si>
-    <t>参数-目标当前生命值&lt;=最大生命值的百万分之X时</t>
-  </si>
-  <si>
-    <t>to_target_effect_hit</t>
-  </si>
-  <si>
-    <t>参数-对目标施加【效果id】命中时</t>
-  </si>
-  <si>
-    <t>order</t>
-  </si>
-  <si>
-    <t>自动</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>受到的伤害总加成</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成伤害总加成</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成的伤害总加成【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到的伤害总加成【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542801:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542601:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3543001:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542607:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542807:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3543007:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542605:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542805:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3543005:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3540201:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>光环技能-正义光环</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>60120001,60130000</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>护盾技能-每X秒获得最大生命值的护盾</t>
-  </si>
-  <si>
-    <t>955001002</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得护盾</t>
-  </si>
-  <si>
-    <t>3590405:1</t>
-  </si>
-  <si>
-    <t>（获得）雷击</t>
-  </si>
-  <si>
-    <t>（获得）冰弹</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>（获得）陨石</t>
+    <t>普攻击中回血效果提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻击中回血</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3592401:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3592201:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3592202:1</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -2555,7 +2576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC80"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -2698,13 +2719,13 @@
         <v>65</v>
       </c>
       <c r="AA2" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="AB2" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="AB2" s="7" t="s">
-        <v>326</v>
-      </c>
       <c r="AC2" s="7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.2">
@@ -2787,13 +2808,13 @@
         <v>103</v>
       </c>
       <c r="AA3" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="AB3" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="AB3" s="7" t="s">
+      <c r="AC3" s="7" t="s">
         <v>328</v>
-      </c>
-      <c r="AC3" s="7" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.2">
@@ -2813,16 +2834,16 @@
         <v>64</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>30</v>
@@ -2876,13 +2897,13 @@
         <v>106</v>
       </c>
       <c r="AA4" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="AB4" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="AB4" s="7" t="s">
-        <v>331</v>
-      </c>
       <c r="AC4" s="7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.2">
@@ -3000,7 +3021,7 @@
         <v>47</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J6" s="6" t="s">
         <v>89</v>
@@ -3054,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="AA6" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AB6" s="6">
         <v>1</v>
@@ -3092,7 +3113,7 @@
         <v>164</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="K7" s="15">
         <v>2</v>
@@ -4160,7 +4181,7 @@
         <v>176</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="K19" s="15">
         <v>2</v>
@@ -4190,7 +4211,7 @@
         <v>0</v>
       </c>
       <c r="T19" s="15" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="U19" s="15">
         <v>4000</v>
@@ -4202,7 +4223,7 @@
         <v>10000</v>
       </c>
       <c r="X19" s="15" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="Y19" s="15">
         <v>1</v>
@@ -4237,7 +4258,7 @@
         <v>3542800</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G20" s="16" t="s">
         <v>183</v>
@@ -4246,10 +4267,10 @@
         <v>182</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J20" s="15" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="K20" s="15">
         <v>2</v>
@@ -4279,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="T20" s="15" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="U20" s="15">
         <v>-1</v>
@@ -4291,7 +4312,7 @@
         <v>10000</v>
       </c>
       <c r="X20" s="15" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y20" s="15">
         <v>1</v>
@@ -4326,7 +4347,7 @@
         <v>3543000</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="G21" s="16" t="s">
         <v>183</v>
@@ -4335,10 +4356,10 @@
         <v>182</v>
       </c>
       <c r="I21" s="16" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J21" s="15" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="K21" s="15">
         <v>2</v>
@@ -4368,7 +4389,7 @@
         <v>0</v>
       </c>
       <c r="T21" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="U21" s="15">
         <v>-1</v>
@@ -4380,7 +4401,7 @@
         <v>10000</v>
       </c>
       <c r="X21" s="15" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Y21" s="15">
         <v>1</v>
@@ -4424,7 +4445,7 @@
         <v>162</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J22" s="17" t="s">
         <v>43</v>
@@ -4513,7 +4534,7 @@
         <v>161</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J23" s="17" t="s">
         <v>80</v>
@@ -4602,7 +4623,7 @@
         <v>153</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J24" s="17" t="s">
         <v>43</v>
@@ -4691,7 +4712,7 @@
         <v>157</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J25" s="17" t="s">
         <v>85</v>
@@ -4780,7 +4801,7 @@
         <v>158</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="J26" s="17" t="s">
         <v>86</v>
@@ -4801,7 +4822,7 @@
         <v>0</v>
       </c>
       <c r="P26" s="17" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q26" s="17">
         <v>1</v>
@@ -4860,7 +4881,7 @@
         <v>3551300</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>184</v>
@@ -4869,7 +4890,7 @@
         <v>159</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="J27" s="17" t="s">
         <v>88</v>
@@ -5047,7 +5068,7 @@
         <v>191</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J29" s="18" t="s">
         <v>203</v>
@@ -5101,7 +5122,7 @@
         <v>1</v>
       </c>
       <c r="AA29" s="18" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AB29" s="18">
         <v>1</v>
@@ -5483,19 +5504,19 @@
         <v>3561400</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G34" s="13" t="s">
         <v>188</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J34" s="18" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="K34" s="18">
         <v>2</v>
@@ -5504,7 +5525,7 @@
         <v>3500</v>
       </c>
       <c r="M34" s="18" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="N34" s="18">
         <v>35</v>
@@ -5546,7 +5567,7 @@
         <v>1</v>
       </c>
       <c r="AA34" s="18" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AB34" s="18">
         <v>1</v>
@@ -5614,7 +5635,7 @@
         <v>0</v>
       </c>
       <c r="T35" s="19" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="U35" s="19">
         <v>4000</v>
@@ -5691,7 +5712,7 @@
         <v>1</v>
       </c>
       <c r="P36" s="19" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Q36" s="19">
         <v>2</v>
@@ -5839,7 +5860,7 @@
         <v>3570900</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G38" s="13" t="s">
         <v>189</v>
@@ -5848,7 +5869,7 @@
         <v>199</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="J38" s="19" t="s">
         <v>219</v>
@@ -5860,7 +5881,7 @@
         <v>2000</v>
       </c>
       <c r="M38" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N38" s="19">
         <v>1</v>
@@ -5928,16 +5949,16 @@
         <v>3571100</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G39" s="13" t="s">
         <v>189</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J39" s="19" t="s">
         <v>220</v>
@@ -6115,7 +6136,7 @@
         <v>201</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J41" s="20" t="s">
         <v>223</v>
@@ -6148,7 +6169,7 @@
         <v>0</v>
       </c>
       <c r="T41" s="20" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="U41" s="20">
         <v>4000</v>
@@ -6169,7 +6190,7 @@
         <v>1</v>
       </c>
       <c r="AA41" s="20" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AB41" s="20">
         <v>1</v>
@@ -6284,16 +6305,16 @@
         <v>3580700</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G43" s="13" t="s">
         <v>190</v>
       </c>
       <c r="H43" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="I43" s="13" t="s">
         <v>357</v>
-      </c>
-      <c r="I43" s="13" t="s">
-        <v>358</v>
       </c>
       <c r="J43" s="20" t="s">
         <v>229</v>
@@ -6305,7 +6326,7 @@
         <v>5</v>
       </c>
       <c r="M43" s="20" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="N43" s="20">
         <v>2</v>
@@ -6471,10 +6492,10 @@
         <v>187</v>
       </c>
       <c r="I45" s="13" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J45" s="20" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="K45" s="20">
         <v>2</v>
@@ -6483,7 +6504,7 @@
         <v>3000</v>
       </c>
       <c r="M45" s="20" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N45" s="20">
         <v>1</v>
@@ -6504,7 +6525,7 @@
         <v>0</v>
       </c>
       <c r="T45" s="20" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="U45" s="20">
         <v>4000</v>
@@ -6516,7 +6537,7 @@
         <v>10000</v>
       </c>
       <c r="X45" s="20" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Y45" s="20">
         <v>1</v>
@@ -6525,7 +6546,7 @@
         <v>10</v>
       </c>
       <c r="AA45" s="20" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AB45" s="20">
         <v>1</v>
@@ -6674,7 +6695,7 @@
         <v>59030001</v>
       </c>
       <c r="T47" s="24" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="U47" s="24">
         <v>-1</v>
@@ -6823,7 +6844,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="24" t="s">
-        <v>284</v>
+        <v>541</v>
       </c>
       <c r="N49" s="24">
         <v>2</v>
@@ -6832,7 +6853,7 @@
         <v>10000</v>
       </c>
       <c r="P49" s="24" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q49" s="24">
         <v>1</v>
@@ -6899,7 +6920,7 @@
       <c r="H50" s="13"/>
       <c r="I50" s="13"/>
       <c r="J50" s="24" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K50" s="24">
         <v>2</v>
@@ -6908,16 +6929,16 @@
         <v>0</v>
       </c>
       <c r="M50" s="24" t="s">
+        <v>340</v>
+      </c>
+      <c r="N50" s="24">
+        <v>1</v>
+      </c>
+      <c r="O50" s="24">
+        <v>0</v>
+      </c>
+      <c r="P50" s="24" t="s">
         <v>341</v>
-      </c>
-      <c r="N50" s="24">
-        <v>1</v>
-      </c>
-      <c r="O50" s="24">
-        <v>0</v>
-      </c>
-      <c r="P50" s="24" t="s">
-        <v>342</v>
       </c>
       <c r="Q50" s="24">
         <v>3</v>
@@ -6984,7 +7005,7 @@
       <c r="H51" s="13"/>
       <c r="I51" s="13"/>
       <c r="J51" s="24" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="K51" s="24">
         <v>3</v>
@@ -6993,7 +7014,7 @@
         <v>1000000</v>
       </c>
       <c r="M51" s="24" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N51" s="24">
         <v>2</v>
@@ -7002,7 +7023,7 @@
         <v>10000</v>
       </c>
       <c r="P51" s="24" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Q51" s="24">
         <v>1</v>
@@ -7069,7 +7090,7 @@
       <c r="H52" s="13"/>
       <c r="I52" s="13"/>
       <c r="J52" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K52" s="24">
         <v>3</v>
@@ -7078,7 +7099,7 @@
         <v>500000</v>
       </c>
       <c r="M52" s="24" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N52" s="24">
         <v>2</v>
@@ -7087,7 +7108,7 @@
         <v>10000</v>
       </c>
       <c r="P52" s="24" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Q52" s="24">
         <v>1</v>
@@ -7163,7 +7184,7 @@
         <v>0</v>
       </c>
       <c r="M53" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="N53" s="24">
         <v>2</v>
@@ -7172,7 +7193,7 @@
         <v>10000</v>
       </c>
       <c r="P53" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Q53" s="24">
         <v>1</v>
@@ -7231,7 +7252,7 @@
         <v>3591900</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G54" s="13" t="s">
         <v>244</v>
@@ -7248,7 +7269,7 @@
         <v>0</v>
       </c>
       <c r="M54" s="24" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="N54" s="24">
         <v>1</v>
@@ -7290,7 +7311,7 @@
         <v>1</v>
       </c>
       <c r="AA54" s="24" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AB54" s="24">
         <v>1</v>
@@ -7316,7 +7337,7 @@
         <v>3541800</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G55" s="13" t="s">
         <v>244</v>
@@ -7401,7 +7422,7 @@
         <v>3541800</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G56" s="13" t="s">
         <v>244</v>
@@ -7486,7 +7507,7 @@
         <v>3592100</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G57" s="13" t="s">
         <v>244</v>
@@ -7494,7 +7515,7 @@
       <c r="H57" s="13"/>
       <c r="I57" s="13"/>
       <c r="J57" s="24" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="K57" s="24">
         <v>2</v>
@@ -7555,181 +7576,181 @@
       </c>
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A58" s="21">
-        <v>60010001</v>
-      </c>
-      <c r="B58" s="21">
-        <v>6001</v>
-      </c>
-      <c r="C58" s="21">
-        <v>1</v>
-      </c>
-      <c r="D58" s="21">
-        <v>0</v>
-      </c>
-      <c r="E58" s="21">
-        <v>3600200</v>
+      <c r="A58" s="25">
+        <v>59130001</v>
+      </c>
+      <c r="B58" s="24">
+        <v>5913</v>
+      </c>
+      <c r="C58" s="24">
+        <v>1</v>
+      </c>
+      <c r="D58" s="24">
+        <v>0</v>
+      </c>
+      <c r="E58" s="24">
+        <v>3591000</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>256</v>
+        <v>543</v>
       </c>
       <c r="G58" s="13" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="H58" s="13"/>
       <c r="I58" s="13"/>
-      <c r="J58" s="21" t="s">
-        <v>260</v>
-      </c>
-      <c r="K58" s="21">
-        <v>1</v>
-      </c>
-      <c r="L58" s="21">
-        <v>8</v>
-      </c>
-      <c r="M58" s="21" t="s">
-        <v>261</v>
-      </c>
-      <c r="N58" s="21">
-        <v>2</v>
-      </c>
-      <c r="O58" s="21">
+      <c r="J58" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="K58" s="24">
+        <v>1</v>
+      </c>
+      <c r="L58" s="24">
+        <v>0</v>
+      </c>
+      <c r="M58" s="24" t="s">
+        <v>545</v>
+      </c>
+      <c r="N58" s="24">
+        <v>1</v>
+      </c>
+      <c r="O58" s="24">
+        <v>0</v>
+      </c>
+      <c r="P58" s="24" t="s">
+        <v>546</v>
+      </c>
+      <c r="Q58" s="24">
+        <v>3</v>
+      </c>
+      <c r="R58" s="24">
+        <v>0</v>
+      </c>
+      <c r="S58" s="24">
+        <v>0</v>
+      </c>
+      <c r="T58" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="U58" s="24">
+        <v>-1</v>
+      </c>
+      <c r="V58" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="W58" s="24">
         <v>10000</v>
       </c>
-      <c r="P58" s="21" t="s">
-        <v>262</v>
-      </c>
-      <c r="Q58" s="21">
-        <v>1</v>
-      </c>
-      <c r="R58" s="21">
-        <v>1</v>
-      </c>
-      <c r="S58" s="21">
-        <v>0</v>
-      </c>
-      <c r="T58" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="U58" s="21">
-        <v>0</v>
-      </c>
-      <c r="V58" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="W58" s="21">
-        <v>10000</v>
-      </c>
-      <c r="X58" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y58" s="21">
-        <v>1</v>
-      </c>
-      <c r="Z58" s="21">
-        <v>1</v>
-      </c>
-      <c r="AA58" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB58" s="21">
-        <v>1</v>
-      </c>
-      <c r="AC58" s="21">
+      <c r="X58" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y58" s="24">
+        <v>1</v>
+      </c>
+      <c r="Z58" s="24">
+        <v>1</v>
+      </c>
+      <c r="AA58" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB58" s="24">
+        <v>1</v>
+      </c>
+      <c r="AC58" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A59" s="21">
-        <v>60020001</v>
-      </c>
-      <c r="B59" s="21">
-        <v>6002</v>
-      </c>
-      <c r="C59" s="21">
-        <v>1</v>
-      </c>
-      <c r="D59" s="21">
-        <v>0</v>
-      </c>
-      <c r="E59" s="21">
-        <v>3600400</v>
+      <c r="A59" s="25">
+        <v>59140001</v>
+      </c>
+      <c r="B59" s="24">
+        <v>5914</v>
+      </c>
+      <c r="C59" s="24">
+        <v>1</v>
+      </c>
+      <c r="D59" s="24">
+        <v>0</v>
+      </c>
+      <c r="E59" s="24">
+        <v>3592400</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>257</v>
+        <v>542</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="H59" s="13"/>
       <c r="I59" s="13"/>
-      <c r="J59" s="21" t="s">
-        <v>263</v>
-      </c>
-      <c r="K59" s="21">
-        <v>1</v>
-      </c>
-      <c r="L59" s="21">
-        <v>1</v>
-      </c>
-      <c r="M59" s="21" t="s">
-        <v>264</v>
-      </c>
-      <c r="N59" s="21">
+      <c r="J59" s="24" t="s">
+        <v>544</v>
+      </c>
+      <c r="K59" s="24">
         <v>2</v>
       </c>
-      <c r="O59" s="21">
-        <v>15000</v>
-      </c>
-      <c r="P59" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q59" s="21">
-        <v>1</v>
-      </c>
-      <c r="R59" s="21">
-        <v>0</v>
-      </c>
-      <c r="S59" s="21">
-        <v>0</v>
-      </c>
-      <c r="T59" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="U59" s="21">
+      <c r="L59" s="24">
+        <v>0</v>
+      </c>
+      <c r="M59" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="N59" s="24">
+        <v>1</v>
+      </c>
+      <c r="O59" s="24">
+        <v>0</v>
+      </c>
+      <c r="P59" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q59" s="24">
+        <v>1</v>
+      </c>
+      <c r="R59" s="24">
+        <v>0</v>
+      </c>
+      <c r="S59" s="24">
+        <v>0</v>
+      </c>
+      <c r="T59" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="U59" s="24">
         <v>-1</v>
       </c>
-      <c r="V59" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="W59" s="21">
+      <c r="V59" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="W59" s="24">
         <v>10000</v>
       </c>
-      <c r="X59" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y59" s="21">
-        <v>1</v>
-      </c>
-      <c r="Z59" s="21">
-        <v>1</v>
-      </c>
-      <c r="AA59" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB59" s="21">
-        <v>1</v>
-      </c>
-      <c r="AC59" s="21">
+      <c r="X59" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y59" s="24">
+        <v>1</v>
+      </c>
+      <c r="Z59" s="24">
+        <v>1</v>
+      </c>
+      <c r="AA59" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB59" s="24">
+        <v>1</v>
+      </c>
+      <c r="AC59" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A60" s="21">
-        <v>60030001</v>
+        <v>60010001</v>
       </c>
       <c r="B60" s="21">
-        <v>6003</v>
+        <v>6001</v>
       </c>
       <c r="C60" s="21">
         <v>1</v>
@@ -7738,10 +7759,10 @@
         <v>0</v>
       </c>
       <c r="E60" s="21">
-        <v>3600700</v>
+        <v>3600200</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G60" s="13" t="s">
         <v>253</v>
@@ -7749,7 +7770,7 @@
       <c r="H60" s="13"/>
       <c r="I60" s="13"/>
       <c r="J60" s="21" t="s">
-        <v>296</v>
+        <v>260</v>
       </c>
       <c r="K60" s="21">
         <v>1</v>
@@ -7758,7 +7779,7 @@
         <v>8</v>
       </c>
       <c r="M60" s="21" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="N60" s="21">
         <v>2</v>
@@ -7767,7 +7788,7 @@
         <v>10000</v>
       </c>
       <c r="P60" s="21" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="Q60" s="21">
         <v>1</v>
@@ -7811,10 +7832,10 @@
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A61" s="21">
-        <v>60040001</v>
+        <v>60020001</v>
       </c>
       <c r="B61" s="21">
-        <v>6004</v>
+        <v>6002</v>
       </c>
       <c r="C61" s="21">
         <v>1</v>
@@ -7823,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="E61" s="21">
-        <v>3601000</v>
+        <v>3600400</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G61" s="13" t="s">
         <v>253</v>
@@ -7834,31 +7855,31 @@
       <c r="H61" s="13"/>
       <c r="I61" s="13"/>
       <c r="J61" s="21" t="s">
-        <v>43</v>
+        <v>263</v>
       </c>
       <c r="K61" s="21">
         <v>1</v>
       </c>
       <c r="L61" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="21" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="N61" s="21">
         <v>2</v>
       </c>
       <c r="O61" s="21">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="P61" s="21" t="s">
-        <v>268</v>
+        <v>43</v>
       </c>
       <c r="Q61" s="21">
         <v>1</v>
       </c>
       <c r="R61" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61" s="21">
         <v>0</v>
@@ -7867,7 +7888,7 @@
         <v>43</v>
       </c>
       <c r="U61" s="21">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V61" s="21" t="s">
         <v>43</v>
@@ -7896,10 +7917,10 @@
     </row>
     <row r="62" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A62" s="21">
-        <v>60050001</v>
+        <v>60030001</v>
       </c>
       <c r="B62" s="21">
-        <v>6005</v>
+        <v>6003</v>
       </c>
       <c r="C62" s="21">
         <v>1</v>
@@ -7908,10 +7929,10 @@
         <v>0</v>
       </c>
       <c r="E62" s="21">
-        <v>3541600</v>
+        <v>3600700</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>316</v>
+        <v>258</v>
       </c>
       <c r="G62" s="13" t="s">
         <v>253</v>
@@ -7919,31 +7940,31 @@
       <c r="H62" s="13"/>
       <c r="I62" s="13"/>
       <c r="J62" s="21" t="s">
-        <v>118</v>
+        <v>295</v>
       </c>
       <c r="K62" s="21">
+        <v>1</v>
+      </c>
+      <c r="L62" s="21">
+        <v>8</v>
+      </c>
+      <c r="M62" s="21" t="s">
+        <v>265</v>
+      </c>
+      <c r="N62" s="21">
         <v>2</v>
       </c>
-      <c r="L62" s="21">
-        <v>-2000</v>
-      </c>
-      <c r="M62" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="N62" s="21">
-        <v>1</v>
-      </c>
       <c r="O62" s="21">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P62" s="21" t="s">
-        <v>43</v>
+        <v>266</v>
       </c>
       <c r="Q62" s="21">
         <v>1</v>
       </c>
       <c r="R62" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S62" s="21">
         <v>0</v>
@@ -7952,7 +7973,7 @@
         <v>43</v>
       </c>
       <c r="U62" s="21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V62" s="21" t="s">
         <v>43</v>
@@ -7981,10 +8002,10 @@
     </row>
     <row r="63" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A63" s="21">
-        <v>60060001</v>
+        <v>60040001</v>
       </c>
       <c r="B63" s="21">
-        <v>6006</v>
+        <v>6004</v>
       </c>
       <c r="C63" s="21">
         <v>1</v>
@@ -7993,10 +8014,10 @@
         <v>0</v>
       </c>
       <c r="E63" s="21">
-        <v>3541800</v>
+        <v>3601000</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>317</v>
+        <v>259</v>
       </c>
       <c r="G63" s="13" t="s">
         <v>253</v>
@@ -8004,31 +8025,31 @@
       <c r="H63" s="13"/>
       <c r="I63" s="13"/>
       <c r="J63" s="21" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="K63" s="21">
+        <v>1</v>
+      </c>
+      <c r="L63" s="21">
+        <v>0</v>
+      </c>
+      <c r="M63" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="N63" s="21">
         <v>2</v>
       </c>
-      <c r="L63" s="21">
-        <v>2500</v>
-      </c>
-      <c r="M63" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="N63" s="21">
-        <v>1</v>
-      </c>
       <c r="O63" s="21">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P63" s="21" t="s">
-        <v>43</v>
+        <v>268</v>
       </c>
       <c r="Q63" s="21">
         <v>1</v>
       </c>
       <c r="R63" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S63" s="21">
         <v>0</v>
@@ -8037,7 +8058,7 @@
         <v>43</v>
       </c>
       <c r="U63" s="21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V63" s="21" t="s">
         <v>43</v>
@@ -8066,10 +8087,10 @@
     </row>
     <row r="64" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A64" s="21">
-        <v>60070001</v>
+        <v>60050001</v>
       </c>
       <c r="B64" s="21">
-        <v>6007</v>
+        <v>6005</v>
       </c>
       <c r="C64" s="21">
         <v>1</v>
@@ -8078,10 +8099,10 @@
         <v>0</v>
       </c>
       <c r="E64" s="21">
-        <v>3601300</v>
+        <v>3541600</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="G64" s="13" t="s">
         <v>253</v>
@@ -8089,25 +8110,25 @@
       <c r="H64" s="13"/>
       <c r="I64" s="13"/>
       <c r="J64" s="21" t="s">
-        <v>269</v>
+        <v>118</v>
       </c>
       <c r="K64" s="21">
         <v>2</v>
       </c>
       <c r="L64" s="21">
-        <v>10000</v>
+        <v>-2000</v>
       </c>
       <c r="M64" s="21" t="s">
-        <v>270</v>
+        <v>43</v>
       </c>
       <c r="N64" s="21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O64" s="21">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="P64" s="21" t="s">
-        <v>271</v>
+        <v>43</v>
       </c>
       <c r="Q64" s="21">
         <v>1</v>
@@ -8151,10 +8172,10 @@
     </row>
     <row r="65" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A65" s="21">
-        <v>60080001</v>
+        <v>60060001</v>
       </c>
       <c r="B65" s="21">
-        <v>6008</v>
+        <v>6006</v>
       </c>
       <c r="C65" s="21">
         <v>1</v>
@@ -8163,10 +8184,10 @@
         <v>0</v>
       </c>
       <c r="E65" s="21">
-        <v>3541600</v>
+        <v>3541800</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>533</v>
+        <v>316</v>
       </c>
       <c r="G65" s="13" t="s">
         <v>253</v>
@@ -8174,13 +8195,13 @@
       <c r="H65" s="13"/>
       <c r="I65" s="13"/>
       <c r="J65" s="21" t="s">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="K65" s="21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L65" s="21">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="M65" s="21" t="s">
         <v>43</v>
@@ -8200,14 +8221,14 @@
       <c r="R65" s="21">
         <v>0</v>
       </c>
-      <c r="S65" s="26" t="s">
-        <v>534</v>
+      <c r="S65" s="21">
+        <v>0</v>
       </c>
       <c r="T65" s="21" t="s">
         <v>43</v>
       </c>
       <c r="U65" s="21">
-        <v>-1</v>
+        <v>1000</v>
       </c>
       <c r="V65" s="21" t="s">
         <v>43</v>
@@ -8231,185 +8252,185 @@
         <v>1</v>
       </c>
       <c r="AC65" s="21">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A66" s="22">
-        <v>61010001</v>
-      </c>
-      <c r="B66" s="22">
-        <v>6101</v>
-      </c>
-      <c r="C66" s="22">
-        <v>1</v>
-      </c>
-      <c r="D66" s="22">
-        <v>0</v>
-      </c>
-      <c r="E66" s="22">
-        <v>3610300</v>
+      <c r="A66" s="21">
+        <v>60070001</v>
+      </c>
+      <c r="B66" s="21">
+        <v>6007</v>
+      </c>
+      <c r="C66" s="21">
+        <v>1</v>
+      </c>
+      <c r="D66" s="21">
+        <v>0</v>
+      </c>
+      <c r="E66" s="21">
+        <v>3601300</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H66" s="13"/>
       <c r="I66" s="13"/>
-      <c r="J66" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="K66" s="22">
-        <v>1</v>
-      </c>
-      <c r="L66" s="22">
-        <v>8</v>
-      </c>
-      <c r="M66" s="22" t="s">
-        <v>273</v>
-      </c>
-      <c r="N66" s="22">
+      <c r="J66" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="K66" s="21">
         <v>2</v>
       </c>
-      <c r="O66" s="22">
+      <c r="L66" s="21">
         <v>10000</v>
       </c>
-      <c r="P66" s="22" t="s">
-        <v>274</v>
-      </c>
-      <c r="Q66" s="22">
-        <v>1</v>
-      </c>
-      <c r="R66" s="22">
-        <v>1</v>
-      </c>
-      <c r="S66" s="22">
-        <v>0</v>
-      </c>
-      <c r="T66" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="U66" s="22">
-        <v>0</v>
-      </c>
-      <c r="V66" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="W66" s="22">
+      <c r="M66" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="N66" s="21">
+        <v>2</v>
+      </c>
+      <c r="O66" s="21">
+        <v>2000</v>
+      </c>
+      <c r="P66" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q66" s="21">
+        <v>1</v>
+      </c>
+      <c r="R66" s="21">
+        <v>0</v>
+      </c>
+      <c r="S66" s="21">
+        <v>0</v>
+      </c>
+      <c r="T66" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="U66" s="21">
+        <v>1000</v>
+      </c>
+      <c r="V66" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W66" s="21">
         <v>10000</v>
       </c>
-      <c r="X66" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y66" s="22">
-        <v>1</v>
-      </c>
-      <c r="Z66" s="22">
-        <v>1</v>
-      </c>
-      <c r="AA66" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB66" s="22">
-        <v>1</v>
-      </c>
-      <c r="AC66" s="22">
+      <c r="X66" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y66" s="21">
+        <v>1</v>
+      </c>
+      <c r="Z66" s="21">
+        <v>1</v>
+      </c>
+      <c r="AA66" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB66" s="21">
+        <v>1</v>
+      </c>
+      <c r="AC66" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A67" s="22">
-        <v>61020001</v>
-      </c>
-      <c r="B67" s="22">
-        <v>6102</v>
-      </c>
-      <c r="C67" s="22">
-        <v>1</v>
-      </c>
-      <c r="D67" s="22">
-        <v>0</v>
-      </c>
-      <c r="E67" s="22">
-        <v>3610500</v>
+      <c r="A67" s="21">
+        <v>60080001</v>
+      </c>
+      <c r="B67" s="21">
+        <v>6008</v>
+      </c>
+      <c r="C67" s="21">
+        <v>1</v>
+      </c>
+      <c r="D67" s="21">
+        <v>0</v>
+      </c>
+      <c r="E67" s="21">
+        <v>3541600</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>298</v>
+        <v>532</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H67" s="13"/>
       <c r="I67" s="13"/>
-      <c r="J67" s="22" t="s">
-        <v>275</v>
-      </c>
-      <c r="K67" s="22">
-        <v>2</v>
-      </c>
-      <c r="L67" s="22">
+      <c r="J67" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="K67" s="21">
+        <v>1</v>
+      </c>
+      <c r="L67" s="21">
+        <v>0</v>
+      </c>
+      <c r="M67" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="N67" s="21">
+        <v>1</v>
+      </c>
+      <c r="O67" s="21">
+        <v>0</v>
+      </c>
+      <c r="P67" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q67" s="21">
+        <v>1</v>
+      </c>
+      <c r="R67" s="21">
+        <v>0</v>
+      </c>
+      <c r="S67" s="26" t="s">
+        <v>533</v>
+      </c>
+      <c r="T67" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="U67" s="21">
+        <v>-1</v>
+      </c>
+      <c r="V67" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W67" s="21">
         <v>10000</v>
       </c>
-      <c r="M67" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="N67" s="22">
-        <v>1</v>
-      </c>
-      <c r="O67" s="22">
-        <v>0</v>
-      </c>
-      <c r="P67" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q67" s="22">
-        <v>1</v>
-      </c>
-      <c r="R67" s="22">
-        <v>0</v>
-      </c>
-      <c r="S67" s="22">
-        <v>0</v>
-      </c>
-      <c r="T67" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="U67" s="22">
-        <v>-1</v>
-      </c>
-      <c r="V67" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="W67" s="22">
-        <v>10000</v>
-      </c>
-      <c r="X67" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y67" s="22">
-        <v>1</v>
-      </c>
-      <c r="Z67" s="22">
-        <v>1</v>
-      </c>
-      <c r="AA67" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB67" s="22">
-        <v>1</v>
-      </c>
-      <c r="AC67" s="22">
-        <v>0</v>
+      <c r="X67" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y67" s="21">
+        <v>1</v>
+      </c>
+      <c r="Z67" s="21">
+        <v>1</v>
+      </c>
+      <c r="AA67" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB67" s="21">
+        <v>1</v>
+      </c>
+      <c r="AC67" s="21">
+        <v>1000</v>
       </c>
     </row>
     <row r="68" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A68" s="22">
-        <v>61030001</v>
+        <v>61010001</v>
       </c>
       <c r="B68" s="22">
-        <v>6103</v>
+        <v>6101</v>
       </c>
       <c r="C68" s="22">
         <v>1</v>
@@ -8418,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="E68" s="22">
-        <v>3610700</v>
+        <v>3610300</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="G68" s="13" t="s">
         <v>254</v>
@@ -8429,16 +8450,16 @@
       <c r="H68" s="13"/>
       <c r="I68" s="13"/>
       <c r="J68" s="22" t="s">
-        <v>43</v>
+        <v>272</v>
       </c>
       <c r="K68" s="22">
         <v>1</v>
       </c>
       <c r="L68" s="22">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M68" s="22" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="N68" s="22">
         <v>2</v>
@@ -8447,7 +8468,7 @@
         <v>10000</v>
       </c>
       <c r="P68" s="22" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="Q68" s="22">
         <v>1</v>
@@ -8491,10 +8512,10 @@
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A69" s="22">
-        <v>61040001</v>
+        <v>61020001</v>
       </c>
       <c r="B69" s="22">
-        <v>6104</v>
+        <v>6102</v>
       </c>
       <c r="C69" s="22">
         <v>1</v>
@@ -8503,10 +8524,10 @@
         <v>0</v>
       </c>
       <c r="E69" s="22">
-        <v>3541400</v>
+        <v>3610500</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>255</v>
+        <v>297</v>
       </c>
       <c r="G69" s="13" t="s">
         <v>254</v>
@@ -8514,13 +8535,13 @@
       <c r="H69" s="13"/>
       <c r="I69" s="13"/>
       <c r="J69" s="22" t="s">
-        <v>117</v>
+        <v>275</v>
       </c>
       <c r="K69" s="22">
         <v>2</v>
       </c>
       <c r="L69" s="22">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="M69" s="22" t="s">
         <v>43</v>
@@ -8576,10 +8597,10 @@
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A70" s="22">
-        <v>61050001</v>
+        <v>61030001</v>
       </c>
       <c r="B70" s="22">
-        <v>6105</v>
+        <v>6103</v>
       </c>
       <c r="C70" s="22">
         <v>1</v>
@@ -8588,10 +8609,10 @@
         <v>0</v>
       </c>
       <c r="E70" s="22">
-        <v>3610900</v>
+        <v>3610700</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G70" s="13" t="s">
         <v>254</v>
@@ -8599,31 +8620,31 @@
       <c r="H70" s="13"/>
       <c r="I70" s="13"/>
       <c r="J70" s="22" t="s">
-        <v>304</v>
+        <v>43</v>
       </c>
       <c r="K70" s="22">
         <v>1</v>
       </c>
       <c r="L70" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" s="22" t="s">
-        <v>43</v>
+        <v>276</v>
       </c>
       <c r="N70" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O70" s="22">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P70" s="22" t="s">
-        <v>43</v>
+        <v>277</v>
       </c>
       <c r="Q70" s="22">
         <v>1</v>
       </c>
       <c r="R70" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S70" s="22">
         <v>0</v>
@@ -8632,7 +8653,7 @@
         <v>43</v>
       </c>
       <c r="U70" s="22">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V70" s="22" t="s">
         <v>43</v>
@@ -8661,10 +8682,10 @@
     </row>
     <row r="71" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A71" s="22">
-        <v>61060001</v>
+        <v>61040001</v>
       </c>
       <c r="B71" s="22">
-        <v>6106</v>
+        <v>6104</v>
       </c>
       <c r="C71" s="22">
         <v>1</v>
@@ -8673,10 +8694,10 @@
         <v>0</v>
       </c>
       <c r="E71" s="22">
-        <v>3611100</v>
+        <v>3541400</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>370</v>
+        <v>255</v>
       </c>
       <c r="G71" s="13" t="s">
         <v>254</v>
@@ -8684,13 +8705,13 @@
       <c r="H71" s="13"/>
       <c r="I71" s="13"/>
       <c r="J71" s="22" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="K71" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L71" s="22">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="M71" s="22" t="s">
         <v>43</v>
@@ -8746,10 +8767,10 @@
     </row>
     <row r="72" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A72" s="22">
-        <v>61070001</v>
+        <v>61050001</v>
       </c>
       <c r="B72" s="22">
-        <v>6107</v>
+        <v>6105</v>
       </c>
       <c r="C72" s="22">
         <v>1</v>
@@ -8758,10 +8779,10 @@
         <v>0</v>
       </c>
       <c r="E72" s="22">
-        <v>3611300</v>
+        <v>3610900</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>319</v>
+        <v>298</v>
       </c>
       <c r="G72" s="13" t="s">
         <v>254</v>
@@ -8769,13 +8790,13 @@
       <c r="H72" s="13"/>
       <c r="I72" s="13"/>
       <c r="J72" s="22" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="K72" s="22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L72" s="22">
-        <v>300000</v>
+        <v>1</v>
       </c>
       <c r="M72" s="22" t="s">
         <v>43</v>
@@ -8787,13 +8808,13 @@
         <v>0</v>
       </c>
       <c r="P72" s="22" t="s">
-        <v>306</v>
+        <v>43</v>
       </c>
       <c r="Q72" s="22">
         <v>1</v>
       </c>
       <c r="R72" s="22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S72" s="22">
         <v>0</v>
@@ -8831,10 +8852,10 @@
     </row>
     <row r="73" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A73" s="22">
-        <v>61080001</v>
+        <v>61060001</v>
       </c>
       <c r="B73" s="22">
-        <v>6108</v>
+        <v>6106</v>
       </c>
       <c r="C73" s="22">
         <v>1</v>
@@ -8843,10 +8864,10 @@
         <v>0</v>
       </c>
       <c r="E73" s="22">
-        <v>3611500</v>
+        <v>3611100</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>300</v>
+        <v>369</v>
       </c>
       <c r="G73" s="13" t="s">
         <v>254</v>
@@ -8863,22 +8884,22 @@
         <v>0</v>
       </c>
       <c r="M73" s="22" t="s">
-        <v>308</v>
+        <v>43</v>
       </c>
       <c r="N73" s="22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O73" s="22">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="P73" s="22" t="s">
-        <v>309</v>
+        <v>43</v>
       </c>
       <c r="Q73" s="22">
         <v>1</v>
       </c>
       <c r="R73" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S73" s="22">
         <v>0</v>
@@ -8887,7 +8908,7 @@
         <v>43</v>
       </c>
       <c r="U73" s="22">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V73" s="22" t="s">
         <v>43</v>
@@ -8916,10 +8937,10 @@
     </row>
     <row r="74" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A74" s="22">
-        <v>61090001</v>
+        <v>61070001</v>
       </c>
       <c r="B74" s="22">
-        <v>6109</v>
+        <v>6107</v>
       </c>
       <c r="C74" s="22">
         <v>1</v>
@@ -8928,10 +8949,10 @@
         <v>0</v>
       </c>
       <c r="E74" s="22">
-        <v>3611700</v>
+        <v>3611300</v>
       </c>
       <c r="F74" s="13" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G74" s="13" t="s">
         <v>254</v>
@@ -8939,7 +8960,7 @@
       <c r="H74" s="13"/>
       <c r="I74" s="13"/>
       <c r="J74" s="22" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="K74" s="22">
         <v>3</v>
@@ -8957,13 +8978,13 @@
         <v>0</v>
       </c>
       <c r="P74" s="22" t="s">
-        <v>43</v>
+        <v>305</v>
       </c>
       <c r="Q74" s="22">
         <v>1</v>
       </c>
       <c r="R74" s="22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S74" s="22">
         <v>0</v>
@@ -9001,10 +9022,10 @@
     </row>
     <row r="75" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A75" s="22">
-        <v>61100001</v>
+        <v>61080001</v>
       </c>
       <c r="B75" s="22">
-        <v>6110</v>
+        <v>6108</v>
       </c>
       <c r="C75" s="22">
         <v>1</v>
@@ -9013,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="E75" s="22">
-        <v>3590800</v>
+        <v>3611500</v>
       </c>
       <c r="F75" s="13" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G75" s="13" t="s">
         <v>254</v>
@@ -9033,7 +9054,7 @@
         <v>0</v>
       </c>
       <c r="M75" s="22" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="N75" s="22">
         <v>2</v>
@@ -9042,7 +9063,7 @@
         <v>10000</v>
       </c>
       <c r="P75" s="22" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="Q75" s="22">
         <v>1</v>
@@ -9085,343 +9106,347 @@
       </c>
     </row>
     <row r="76" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A76" s="21">
-        <v>855001001</v>
-      </c>
-      <c r="B76" s="21">
-        <v>7001</v>
-      </c>
-      <c r="C76" s="21">
-        <v>1</v>
-      </c>
-      <c r="D76" s="21">
-        <v>0</v>
-      </c>
-      <c r="E76" s="21">
-        <v>3541600</v>
+      <c r="A76" s="22">
+        <v>61090001</v>
+      </c>
+      <c r="B76" s="22">
+        <v>6109</v>
+      </c>
+      <c r="C76" s="22">
+        <v>1</v>
+      </c>
+      <c r="D76" s="22">
+        <v>0</v>
+      </c>
+      <c r="E76" s="22">
+        <v>3611700</v>
       </c>
       <c r="F76" s="13" t="s">
-        <v>535</v>
-      </c>
-      <c r="G76" s="13"/>
+        <v>319</v>
+      </c>
+      <c r="G76" s="13" t="s">
+        <v>254</v>
+      </c>
       <c r="H76" s="13"/>
       <c r="I76" s="13"/>
-      <c r="J76" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="K76" s="21">
-        <v>1</v>
-      </c>
-      <c r="L76" s="21">
-        <v>0</v>
-      </c>
-      <c r="M76" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="N76" s="21">
-        <v>1</v>
-      </c>
-      <c r="O76" s="21">
-        <v>0</v>
-      </c>
-      <c r="P76" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q76" s="21">
-        <v>1</v>
-      </c>
-      <c r="R76" s="21">
-        <v>0</v>
-      </c>
-      <c r="S76" s="26" t="s">
-        <v>536</v>
-      </c>
-      <c r="T76" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="U76" s="21">
+      <c r="J76" s="22" t="s">
+        <v>306</v>
+      </c>
+      <c r="K76" s="22">
+        <v>3</v>
+      </c>
+      <c r="L76" s="22">
+        <v>300000</v>
+      </c>
+      <c r="M76" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="N76" s="22">
+        <v>1</v>
+      </c>
+      <c r="O76" s="22">
+        <v>0</v>
+      </c>
+      <c r="P76" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q76" s="22">
+        <v>1</v>
+      </c>
+      <c r="R76" s="22">
+        <v>0</v>
+      </c>
+      <c r="S76" s="22">
+        <v>0</v>
+      </c>
+      <c r="T76" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="U76" s="22">
         <v>-1</v>
       </c>
-      <c r="V76" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="W76" s="21">
+      <c r="V76" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="W76" s="22">
         <v>10000</v>
       </c>
-      <c r="X76" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y76" s="21">
-        <v>1</v>
-      </c>
-      <c r="Z76" s="21">
-        <v>1</v>
-      </c>
-      <c r="AA76" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB76" s="21">
-        <v>1</v>
-      </c>
-      <c r="AC76" s="21">
-        <v>8000</v>
+      <c r="X76" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y76" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z76" s="22">
+        <v>1</v>
+      </c>
+      <c r="AA76" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB76" s="22">
+        <v>1</v>
+      </c>
+      <c r="AC76" s="22">
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A77" s="21">
-        <v>855001002</v>
-      </c>
-      <c r="B77" s="21">
-        <v>7002</v>
-      </c>
-      <c r="C77" s="21">
-        <v>1</v>
-      </c>
-      <c r="D77" s="21">
-        <v>0</v>
-      </c>
-      <c r="E77" s="21">
-        <v>3590400</v>
+      <c r="A77" s="22">
+        <v>61100001</v>
+      </c>
+      <c r="B77" s="22">
+        <v>6110</v>
+      </c>
+      <c r="C77" s="22">
+        <v>1</v>
+      </c>
+      <c r="D77" s="22">
+        <v>0</v>
+      </c>
+      <c r="E77" s="22">
+        <v>3590800</v>
       </c>
       <c r="F77" s="13" t="s">
-        <v>537</v>
-      </c>
-      <c r="G77" s="13"/>
+        <v>300</v>
+      </c>
+      <c r="G77" s="13" t="s">
+        <v>254</v>
+      </c>
       <c r="H77" s="13"/>
       <c r="I77" s="13"/>
-      <c r="J77" s="21" t="s">
+      <c r="J77" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="K77" s="22">
+        <v>1</v>
+      </c>
+      <c r="L77" s="22">
+        <v>0</v>
+      </c>
+      <c r="M77" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="N77" s="22">
+        <v>2</v>
+      </c>
+      <c r="O77" s="22">
+        <v>10000</v>
+      </c>
+      <c r="P77" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q77" s="22">
+        <v>1</v>
+      </c>
+      <c r="R77" s="22">
+        <v>1</v>
+      </c>
+      <c r="S77" s="22">
+        <v>0</v>
+      </c>
+      <c r="T77" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="U77" s="22">
+        <v>0</v>
+      </c>
+      <c r="V77" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="W77" s="22">
+        <v>10000</v>
+      </c>
+      <c r="X77" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y77" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z77" s="22">
+        <v>1</v>
+      </c>
+      <c r="AA77" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB77" s="22">
+        <v>1</v>
+      </c>
+      <c r="AC77" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A78" s="21">
+        <v>855001001</v>
+      </c>
+      <c r="B78" s="21">
+        <v>7001</v>
+      </c>
+      <c r="C78" s="21">
+        <v>1</v>
+      </c>
+      <c r="D78" s="21">
+        <v>0</v>
+      </c>
+      <c r="E78" s="21">
+        <v>3541600</v>
+      </c>
+      <c r="F78" s="13" t="s">
+        <v>534</v>
+      </c>
+      <c r="G78" s="13"/>
+      <c r="H78" s="13"/>
+      <c r="I78" s="13"/>
+      <c r="J78" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="K78" s="21">
+        <v>1</v>
+      </c>
+      <c r="L78" s="21">
+        <v>0</v>
+      </c>
+      <c r="M78" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="N78" s="21">
+        <v>1</v>
+      </c>
+      <c r="O78" s="21">
+        <v>0</v>
+      </c>
+      <c r="P78" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q78" s="21">
+        <v>1</v>
+      </c>
+      <c r="R78" s="21">
+        <v>0</v>
+      </c>
+      <c r="S78" s="26" t="s">
+        <v>535</v>
+      </c>
+      <c r="T78" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="U78" s="21">
+        <v>-1</v>
+      </c>
+      <c r="V78" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W78" s="21">
+        <v>10000</v>
+      </c>
+      <c r="X78" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y78" s="21">
+        <v>1</v>
+      </c>
+      <c r="Z78" s="21">
+        <v>1</v>
+      </c>
+      <c r="AA78" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB78" s="21">
+        <v>1</v>
+      </c>
+      <c r="AC78" s="21">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A79" s="21">
+        <v>855001002</v>
+      </c>
+      <c r="B79" s="21">
+        <v>7002</v>
+      </c>
+      <c r="C79" s="21">
+        <v>1</v>
+      </c>
+      <c r="D79" s="21">
+        <v>0</v>
+      </c>
+      <c r="E79" s="21">
+        <v>3590400</v>
+      </c>
+      <c r="F79" s="13" t="s">
+        <v>536</v>
+      </c>
+      <c r="G79" s="13"/>
+      <c r="H79" s="13"/>
+      <c r="I79" s="13"/>
+      <c r="J79" s="21" t="s">
         <v>281</v>
       </c>
-      <c r="K77" s="21">
+      <c r="K79" s="21">
         <v>3</v>
       </c>
-      <c r="L77" s="21">
+      <c r="L79" s="21">
         <v>200000</v>
       </c>
-      <c r="M77" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="N77" s="21">
-        <v>1</v>
-      </c>
-      <c r="O77" s="21">
-        <v>0</v>
-      </c>
-      <c r="P77" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q77" s="21">
-        <v>1</v>
-      </c>
-      <c r="R77" s="21">
-        <v>0</v>
-      </c>
-      <c r="S77" s="26">
-        <v>0</v>
-      </c>
-      <c r="T77" s="21" t="s">
-        <v>538</v>
-      </c>
-      <c r="U77" s="21">
+      <c r="M79" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="N79" s="21">
+        <v>1</v>
+      </c>
+      <c r="O79" s="21">
+        <v>0</v>
+      </c>
+      <c r="P79" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q79" s="21">
+        <v>1</v>
+      </c>
+      <c r="R79" s="21">
+        <v>0</v>
+      </c>
+      <c r="S79" s="26">
+        <v>0</v>
+      </c>
+      <c r="T79" s="21" t="s">
+        <v>537</v>
+      </c>
+      <c r="U79" s="21">
         <v>4000</v>
       </c>
-      <c r="V77" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="W77" s="21">
+      <c r="V79" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W79" s="21">
         <v>10000</v>
       </c>
-      <c r="X77" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y77" s="21">
-        <v>1</v>
-      </c>
-      <c r="Z77" s="21">
-        <v>1</v>
-      </c>
-      <c r="AA77" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB77" s="21">
-        <v>1</v>
-      </c>
-      <c r="AC77" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A78" s="27">
-        <v>855001003</v>
-      </c>
-      <c r="B78" s="27">
-        <v>7003</v>
-      </c>
-      <c r="C78" s="28">
-        <v>1</v>
-      </c>
-      <c r="D78" s="28">
-        <v>0</v>
-      </c>
-      <c r="E78">
-        <v>3590401</v>
-      </c>
-      <c r="F78" t="s">
-        <v>539</v>
-      </c>
-      <c r="G78" t="s">
-        <v>539</v>
-      </c>
-      <c r="J78" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="K78" s="27">
-        <v>1</v>
-      </c>
-      <c r="L78" s="27">
-        <v>0</v>
-      </c>
-      <c r="M78" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="N78" s="27">
-        <v>1</v>
-      </c>
-      <c r="O78" s="27">
-        <v>0</v>
-      </c>
-      <c r="P78" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q78" s="27">
-        <v>1</v>
-      </c>
-      <c r="R78" s="27">
-        <v>0</v>
-      </c>
-      <c r="S78" s="28">
-        <v>955001004</v>
-      </c>
-      <c r="T78" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="U78" s="27">
-        <v>-1</v>
-      </c>
-      <c r="V78" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="W78" s="27">
-        <v>10000</v>
-      </c>
-      <c r="X78" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y78" s="27">
-        <v>1</v>
-      </c>
-      <c r="Z78" s="27">
-        <v>1</v>
-      </c>
-      <c r="AA78" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB78" s="27">
-        <v>1</v>
-      </c>
-      <c r="AC78" s="27">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="79" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A79" s="27">
-        <v>855001004</v>
-      </c>
-      <c r="B79" s="27">
-        <v>7004</v>
-      </c>
-      <c r="C79" s="28">
-        <v>1</v>
-      </c>
-      <c r="D79" s="28">
-        <v>0</v>
-      </c>
-      <c r="E79">
-        <v>3590401</v>
-      </c>
-      <c r="F79" s="29" t="s">
-        <v>540</v>
-      </c>
-      <c r="G79" s="29" t="s">
-        <v>540</v>
-      </c>
-      <c r="J79" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="K79" s="27">
-        <v>1</v>
-      </c>
-      <c r="L79" s="27">
-        <v>0</v>
-      </c>
-      <c r="M79" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="N79" s="27">
-        <v>1</v>
-      </c>
-      <c r="O79" s="27">
-        <v>0</v>
-      </c>
-      <c r="P79" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q79" s="27">
-        <v>1</v>
-      </c>
-      <c r="R79" s="27">
-        <v>0</v>
-      </c>
-      <c r="S79" s="28">
-        <v>955001004</v>
-      </c>
-      <c r="T79" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="U79" s="27">
-        <v>-1</v>
-      </c>
-      <c r="V79" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="W79" s="27">
-        <v>10000</v>
-      </c>
-      <c r="X79" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y79" s="27">
-        <v>1</v>
-      </c>
-      <c r="Z79" s="27">
-        <v>1</v>
-      </c>
-      <c r="AA79" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB79" s="27">
-        <v>1</v>
-      </c>
-      <c r="AC79" s="27">
-        <v>10000</v>
+      <c r="X79" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y79" s="21">
+        <v>1</v>
+      </c>
+      <c r="Z79" s="21">
+        <v>1</v>
+      </c>
+      <c r="AA79" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB79" s="21">
+        <v>1</v>
+      </c>
+      <c r="AC79" s="21">
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A80" s="27">
-        <v>855001005</v>
+        <v>855001003</v>
       </c>
       <c r="B80" s="27">
-        <v>7005</v>
+        <v>7003</v>
       </c>
       <c r="C80" s="28">
         <v>1</v>
@@ -9432,11 +9457,11 @@
       <c r="E80">
         <v>3590401</v>
       </c>
-      <c r="F80" s="29" t="s">
-        <v>541</v>
-      </c>
-      <c r="G80" s="29" t="s">
-        <v>541</v>
+      <c r="F80" t="s">
+        <v>538</v>
+      </c>
+      <c r="G80" t="s">
+        <v>538</v>
       </c>
       <c r="J80" s="27" t="s">
         <v>43</v>
@@ -9499,8 +9524,174 @@
         <v>10000</v>
       </c>
     </row>
+    <row r="81" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A81" s="27">
+        <v>855001004</v>
+      </c>
+      <c r="B81" s="27">
+        <v>7004</v>
+      </c>
+      <c r="C81" s="28">
+        <v>1</v>
+      </c>
+      <c r="D81" s="28">
+        <v>0</v>
+      </c>
+      <c r="E81">
+        <v>3590401</v>
+      </c>
+      <c r="F81" s="29" t="s">
+        <v>539</v>
+      </c>
+      <c r="G81" s="29" t="s">
+        <v>539</v>
+      </c>
+      <c r="J81" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="K81" s="27">
+        <v>1</v>
+      </c>
+      <c r="L81" s="27">
+        <v>0</v>
+      </c>
+      <c r="M81" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N81" s="27">
+        <v>1</v>
+      </c>
+      <c r="O81" s="27">
+        <v>0</v>
+      </c>
+      <c r="P81" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q81" s="27">
+        <v>1</v>
+      </c>
+      <c r="R81" s="27">
+        <v>0</v>
+      </c>
+      <c r="S81" s="28">
+        <v>955001004</v>
+      </c>
+      <c r="T81" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U81" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V81" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W81" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X81" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y81" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z81" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA81" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB81" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC81" s="27">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A82" s="27">
+        <v>855001005</v>
+      </c>
+      <c r="B82" s="27">
+        <v>7005</v>
+      </c>
+      <c r="C82" s="28">
+        <v>1</v>
+      </c>
+      <c r="D82" s="28">
+        <v>0</v>
+      </c>
+      <c r="E82">
+        <v>3590401</v>
+      </c>
+      <c r="F82" s="29" t="s">
+        <v>540</v>
+      </c>
+      <c r="G82" s="29" t="s">
+        <v>540</v>
+      </c>
+      <c r="J82" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="K82" s="27">
+        <v>1</v>
+      </c>
+      <c r="L82" s="27">
+        <v>0</v>
+      </c>
+      <c r="M82" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N82" s="27">
+        <v>1</v>
+      </c>
+      <c r="O82" s="27">
+        <v>0</v>
+      </c>
+      <c r="P82" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q82" s="27">
+        <v>1</v>
+      </c>
+      <c r="R82" s="27">
+        <v>0</v>
+      </c>
+      <c r="S82" s="28">
+        <v>955001004</v>
+      </c>
+      <c r="T82" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U82" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V82" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W82" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X82" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y82" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z82" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA82" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB82" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC82" s="27">
+        <v>10000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:AC75" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:AC77" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -9552,7 +9743,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="11" spans="5:19" x14ac:dyDescent="0.15">
@@ -9560,7 +9751,7 @@
         <v>6</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="12" spans="5:19" x14ac:dyDescent="0.15">
@@ -9568,7 +9759,7 @@
         <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="13" spans="5:19" x14ac:dyDescent="0.15">
@@ -9579,10 +9770,10 @@
         <v>29</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="14" spans="5:19" x14ac:dyDescent="0.15">
@@ -9590,19 +9781,19 @@
         <v>9</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>1</v>
       </c>
       <c r="K14" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="L14" s="1" t="s">
         <v>515</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="15" spans="5:19" x14ac:dyDescent="0.15">
@@ -9610,19 +9801,19 @@
         <v>10</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K15" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="L15" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="L15" s="1" t="s">
-        <v>518</v>
-      </c>
       <c r="S15" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="16" spans="5:19" x14ac:dyDescent="0.15">
@@ -9633,19 +9824,19 @@
         <v>30</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J16" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="L16" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="L16" s="1" t="s">
-        <v>480</v>
-      </c>
       <c r="S16" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="17" spans="5:19" x14ac:dyDescent="0.15">
@@ -9656,19 +9847,19 @@
         <v>31</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K17" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="L17" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="L17" s="1" t="s">
-        <v>482</v>
-      </c>
       <c r="S17" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="18" spans="5:19" x14ac:dyDescent="0.15">
@@ -9682,16 +9873,16 @@
         <v>38</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K18" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="L18" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="L18" s="1" t="s">
-        <v>484</v>
-      </c>
       <c r="S18" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="19" spans="5:19" x14ac:dyDescent="0.15">
@@ -9706,22 +9897,22 @@
         <v>参数4LIST-触发的技能id</v>
       </c>
       <c r="H19" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="I19" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="I19" s="1" t="s">
-        <v>390</v>
-      </c>
       <c r="J19" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="L19" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="L19" s="1" t="s">
-        <v>487</v>
-      </c>
       <c r="S19" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="20" spans="5:19" x14ac:dyDescent="0.15">
@@ -9736,22 +9927,22 @@
         <v>参数5-持续时间（毫秒）</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="K20" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="L20" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="L20" s="1" t="s">
-        <v>489</v>
-      </c>
       <c r="S20" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="21" spans="5:19" x14ac:dyDescent="0.15">
@@ -9766,22 +9957,22 @@
         <v>参数6-效果基础命中率（万分比）</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K21" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="L21" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="L21" s="1" t="s">
-        <v>491</v>
-      </c>
       <c r="S21" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="22" spans="5:19" x14ac:dyDescent="0.15">
@@ -9799,19 +9990,19 @@
         <v>106</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K22" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="L22" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="L22" s="1" t="s">
-        <v>493</v>
-      </c>
       <c r="S22" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="23" spans="5:19" x14ac:dyDescent="0.15">
@@ -9826,22 +10017,22 @@
         <v>参数8-效果触发间隔（毫秒）</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K23" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="L23" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="L23" s="1" t="s">
-        <v>495</v>
-      </c>
       <c r="S23" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="24" spans="5:19" x14ac:dyDescent="0.15">
@@ -9856,22 +10047,22 @@
         <v>参数9-击中回复生命值-固定值</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="K24" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="L24" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="L24" s="1" t="s">
-        <v>497</v>
-      </c>
       <c r="S24" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="25" spans="5:19" x14ac:dyDescent="0.15">
@@ -9886,22 +10077,22 @@
         <v>参数10-击中回复生命值-自身最大生命值百万分比</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K25" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="L25" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="L25" s="1" t="s">
-        <v>499</v>
-      </c>
       <c r="S25" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="26" spans="5:19" x14ac:dyDescent="0.15">
@@ -9916,22 +10107,22 @@
         <v>参数11-击中回复效果提高万分比</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="K26" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="L26" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="L26" s="1" t="s">
-        <v>501</v>
-      </c>
       <c r="S26" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="27" spans="5:19" x14ac:dyDescent="0.15">
@@ -9946,22 +10137,22 @@
         <v>参数12-击杀回复生命-固定值</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K27" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="L27" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="L27" s="1" t="s">
-        <v>503</v>
-      </c>
       <c r="S27" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="28" spans="5:19" x14ac:dyDescent="0.15">
@@ -9976,19 +10167,19 @@
         <v>参数13-击杀回复生命-自身最大生命值百万分比</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J28" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="K28" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="L28" s="1" t="s">
         <v>505</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="29" spans="5:19" x14ac:dyDescent="0.15">
@@ -10003,19 +10194,19 @@
         <v>参数14-击杀回复生命-目标最大生命值百万分比</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K29" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="L29" s="1" t="s">
         <v>507</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>508</v>
       </c>
       <c r="S29" s="1" t="s">
         <v>246</v>
@@ -10033,22 +10224,22 @@
         <v>参数15-击杀回复生命效果提高万分比</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K30" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="L30" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="L30" s="1" t="s">
-        <v>510</v>
-      </c>
       <c r="S30" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="31" spans="5:19" x14ac:dyDescent="0.15">
@@ -10063,22 +10254,22 @@
         <v>参数16-获得护盾-固定值</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K31" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="L31" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="L31" s="1" t="s">
-        <v>512</v>
-      </c>
       <c r="S31" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="32" spans="5:19" x14ac:dyDescent="0.15">
@@ -10086,80 +10277,80 @@
         <v>103</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G32" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数17-获得护盾-自身生命百万分比</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="K32" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="L32" s="1" t="s">
         <v>513</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="33" spans="5:9" x14ac:dyDescent="0.15">
       <c r="E33" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G33" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数18-获得护盾-自身已损失生命万分比</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="34" spans="5:9" x14ac:dyDescent="0.15">
       <c r="E34" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G34" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数19-获得护盾效果提高万分比</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="35" spans="5:9" x14ac:dyDescent="0.15">
       <c r="E35" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G35" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数20-技能增加-固定值</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="36" spans="5:9" x14ac:dyDescent="0.15">
@@ -10168,10 +10359,10 @@
         <v>参数21-技能增加-万分比</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="37" spans="5:9" x14ac:dyDescent="0.15">
@@ -10180,10 +10371,10 @@
         <v>参数22-技能增加-普通攻击范围万分比</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="38" spans="5:9" x14ac:dyDescent="0.15">
@@ -10192,10 +10383,10 @@
         <v>参数25LIST-攻击提高-攻击的元素类型</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="39" spans="5:9" x14ac:dyDescent="0.15">
@@ -10204,10 +10395,10 @@
         <v>参数25LIST-攻击提高-固定值</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="40" spans="5:9" x14ac:dyDescent="0.15">
@@ -10216,10 +10407,10 @@
         <v>参数25LIST-攻击提高-万分比</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="41" spans="5:9" x14ac:dyDescent="0.15">
@@ -10228,10 +10419,10 @@
         <v>参数28-防御提高-固定值</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="42" spans="5:9" x14ac:dyDescent="0.15">
@@ -10240,10 +10431,10 @@
         <v>参数29-防御提高-万分比</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="43" spans="5:9" x14ac:dyDescent="0.15">
@@ -10252,10 +10443,10 @@
         <v>参数30-生命上限提高-固定值</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="44" spans="5:9" x14ac:dyDescent="0.15">
@@ -10264,10 +10455,10 @@
         <v>参数31-生命上限提高-百万分比</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="45" spans="5:9" x14ac:dyDescent="0.15">
@@ -10276,10 +10467,10 @@
         <v>参数32-攻击速度提高-万分比</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="46" spans="5:9" x14ac:dyDescent="0.15">
@@ -10288,10 +10479,10 @@
         <v>参数33-移动速度提高-万分比</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="47" spans="5:9" x14ac:dyDescent="0.15">
@@ -10300,10 +10491,10 @@
         <v>参数34-攻击范围提高-万分比</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="48" spans="5:9" x14ac:dyDescent="0.15">
@@ -10312,10 +10503,10 @@
         <v>参数35-攻击目标数量提高-固定值</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="49" spans="7:8" x14ac:dyDescent="0.15">
@@ -10324,7 +10515,7 @@
         <v>参数36-</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="50" spans="7:8" x14ac:dyDescent="0.15">
@@ -10333,7 +10524,7 @@
         <v>参数37-</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="51" spans="7:8" x14ac:dyDescent="0.15">
@@ -10342,7 +10533,7 @@
         <v>参数38-</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="52" spans="7:8" x14ac:dyDescent="0.15">
@@ -10351,7 +10542,7 @@
         <v>参数39-</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="53" spans="7:8" x14ac:dyDescent="0.15">
@@ -10360,7 +10551,7 @@
         <v>参数40-</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="54" spans="7:8" x14ac:dyDescent="0.15">
@@ -10369,7 +10560,7 @@
         <v>参数41-</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="55" spans="7:8" x14ac:dyDescent="0.15">
@@ -10378,7 +10569,7 @@
         <v>参数42-</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="56" spans="7:8" x14ac:dyDescent="0.15">
@@ -10387,7 +10578,7 @@
         <v>参数41-</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="57" spans="7:8" x14ac:dyDescent="0.15">
@@ -10396,7 +10587,7 @@
         <v>参数42-</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="58" spans="7:8" x14ac:dyDescent="0.15">
@@ -10405,7 +10596,7 @@
         <v>参数43-</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="59" spans="7:8" x14ac:dyDescent="0.15">
@@ -10414,7 +10605,7 @@
         <v>参数44-</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="60" spans="7:8" x14ac:dyDescent="0.15">
@@ -10423,7 +10614,7 @@
         <v>参数45-</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="61" spans="7:8" x14ac:dyDescent="0.15">
@@ -10432,7 +10623,7 @@
         <v>参数46-</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="62" spans="7:8" x14ac:dyDescent="0.15">
@@ -10441,7 +10632,7 @@
         <v>参数47-</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="63" spans="7:8" x14ac:dyDescent="0.15">
@@ -10450,7 +10641,7 @@
         <v>参数48-</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="64" spans="7:8" x14ac:dyDescent="0.15">
@@ -10459,7 +10650,7 @@
         <v>参数49-</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="65" spans="7:8" x14ac:dyDescent="0.15">
@@ -10468,7 +10659,7 @@
         <v>参数50-</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="66" spans="7:8" x14ac:dyDescent="0.15">
@@ -10477,7 +10668,7 @@
         <v>参数51-</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="67" spans="7:8" x14ac:dyDescent="0.15">
@@ -10486,7 +10677,7 @@
         <v>参数52-</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="68" spans="7:8" x14ac:dyDescent="0.15">
@@ -10495,7 +10686,7 @@
         <v>参数53-</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="69" spans="7:8" x14ac:dyDescent="0.15">
@@ -10504,7 +10695,7 @@
         <v>参数54-</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="70" spans="7:8" x14ac:dyDescent="0.15">
@@ -10513,7 +10704,7 @@
         <v>参数55-</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="71" spans="7:8" x14ac:dyDescent="0.15">
@@ -10522,7 +10713,7 @@
         <v>参数56-</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713E1096-DCA9-455A-92D2-68B8394B20E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5185E3A3-C78C-4B27-945F-816E7ADB134E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5185E3A3-C78C-4B27-945F-816E7ADB134E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF90AFC1-C7F2-40A3-AB77-CA2E682F3D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1127" uniqueCount="552">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1950,6 +1950,24 @@
   </si>
   <si>
     <t>3592202:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷击目标数量</t>
+  </si>
+  <si>
+    <t>雷击伤害</t>
+  </si>
+  <si>
+    <t>技能效果-数量</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5200301:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5200501:1</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -2236,7 +2254,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2276,7 +2294,6 @@
     <xf numFmtId="3" fontId="3" fillId="3" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="差" xfId="4" builtinId="27"/>
@@ -2576,7 +2593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC84"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -9443,10 +9460,10 @@
     </row>
     <row r="80" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A80" s="27">
-        <v>855001003</v>
+        <v>85001000</v>
       </c>
       <c r="B80" s="27">
-        <v>7003</v>
+        <v>7004</v>
       </c>
       <c r="C80" s="28">
         <v>1</v>
@@ -9454,15 +9471,17 @@
       <c r="D80" s="28">
         <v>0</v>
       </c>
-      <c r="E80">
+      <c r="E80" s="27">
         <v>3590401</v>
       </c>
-      <c r="F80" t="s">
-        <v>538</v>
-      </c>
-      <c r="G80" t="s">
-        <v>538</v>
-      </c>
+      <c r="F80" s="27" t="s">
+        <v>539</v>
+      </c>
+      <c r="G80" s="27" t="s">
+        <v>539</v>
+      </c>
+      <c r="H80" s="27"/>
+      <c r="I80" s="27"/>
       <c r="J80" s="27" t="s">
         <v>43</v>
       </c>
@@ -9491,7 +9510,7 @@
         <v>0</v>
       </c>
       <c r="S80" s="28">
-        <v>955001004</v>
+        <v>95000101</v>
       </c>
       <c r="T80" s="27" t="s">
         <v>43</v>
@@ -9521,15 +9540,15 @@
         <v>1</v>
       </c>
       <c r="AC80" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A81" s="27">
-        <v>855001004</v>
+        <v>85100100</v>
       </c>
       <c r="B81" s="27">
-        <v>7004</v>
+        <v>7005</v>
       </c>
       <c r="C81" s="28">
         <v>1</v>
@@ -9537,15 +9556,17 @@
       <c r="D81" s="28">
         <v>0</v>
       </c>
-      <c r="E81">
+      <c r="E81" s="27">
         <v>3590401</v>
       </c>
-      <c r="F81" s="29" t="s">
-        <v>539</v>
-      </c>
-      <c r="G81" s="29" t="s">
-        <v>539</v>
-      </c>
+      <c r="F81" s="27" t="s">
+        <v>540</v>
+      </c>
+      <c r="G81" s="27" t="s">
+        <v>540</v>
+      </c>
+      <c r="H81" s="27"/>
+      <c r="I81" s="27"/>
       <c r="J81" s="27" t="s">
         <v>43</v>
       </c>
@@ -9574,7 +9595,7 @@
         <v>0</v>
       </c>
       <c r="S81" s="28">
-        <v>955001004</v>
+        <v>95100101</v>
       </c>
       <c r="T81" s="27" t="s">
         <v>43</v>
@@ -9604,15 +9625,15 @@
         <v>1</v>
       </c>
       <c r="AC81" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A82" s="27">
-        <v>855001005</v>
+        <v>85200100</v>
       </c>
       <c r="B82" s="27">
-        <v>7005</v>
+        <v>7003</v>
       </c>
       <c r="C82" s="28">
         <v>1</v>
@@ -9620,15 +9641,17 @@
       <c r="D82" s="28">
         <v>0</v>
       </c>
-      <c r="E82">
+      <c r="E82" s="27">
         <v>3590401</v>
       </c>
-      <c r="F82" s="29" t="s">
-        <v>540</v>
-      </c>
-      <c r="G82" s="29" t="s">
-        <v>540</v>
-      </c>
+      <c r="F82" s="27" t="s">
+        <v>538</v>
+      </c>
+      <c r="G82" s="27" t="s">
+        <v>538</v>
+      </c>
+      <c r="H82" s="27"/>
+      <c r="I82" s="27"/>
       <c r="J82" s="27" t="s">
         <v>43</v>
       </c>
@@ -9657,7 +9680,7 @@
         <v>0</v>
       </c>
       <c r="S82" s="28">
-        <v>955001004</v>
+        <v>95200101</v>
       </c>
       <c r="T82" s="27" t="s">
         <v>43</v>
@@ -9687,7 +9710,177 @@
         <v>1</v>
       </c>
       <c r="AC82" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A83" s="27">
+        <v>85200300</v>
+      </c>
+      <c r="B83" s="27">
+        <v>7006</v>
+      </c>
+      <c r="C83" s="28">
+        <v>1</v>
+      </c>
+      <c r="D83" s="28">
+        <v>0</v>
+      </c>
+      <c r="E83" s="27">
+        <v>5200400</v>
+      </c>
+      <c r="F83" s="27" t="s">
+        <v>547</v>
+      </c>
+      <c r="G83" s="13" t="s">
+        <v>549</v>
+      </c>
+      <c r="H83" s="27"/>
+      <c r="I83" s="27"/>
+      <c r="J83" s="27" t="s">
+        <v>550</v>
+      </c>
+      <c r="K83" s="27">
+        <v>1</v>
+      </c>
+      <c r="L83" s="27">
+        <v>0</v>
+      </c>
+      <c r="M83" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N83" s="27">
+        <v>1</v>
+      </c>
+      <c r="O83" s="27">
+        <v>0</v>
+      </c>
+      <c r="P83" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q83" s="27">
+        <v>1</v>
+      </c>
+      <c r="R83" s="27">
+        <v>0</v>
+      </c>
+      <c r="S83" s="28">
+        <v>0</v>
+      </c>
+      <c r="T83" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U83" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V83" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W83" s="27">
         <v>10000</v>
+      </c>
+      <c r="X83" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y83" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z83" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA83" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB83" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC83" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A84" s="27">
+        <v>85200500</v>
+      </c>
+      <c r="B84" s="27">
+        <v>7007</v>
+      </c>
+      <c r="C84" s="28">
+        <v>1</v>
+      </c>
+      <c r="D84" s="28">
+        <v>0</v>
+      </c>
+      <c r="E84" s="27">
+        <v>5200600</v>
+      </c>
+      <c r="F84" s="27" t="s">
+        <v>548</v>
+      </c>
+      <c r="G84" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="H84" s="27"/>
+      <c r="I84" s="27"/>
+      <c r="J84" s="27" t="s">
+        <v>551</v>
+      </c>
+      <c r="K84" s="27">
+        <v>2</v>
+      </c>
+      <c r="L84" s="27">
+        <v>0</v>
+      </c>
+      <c r="M84" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N84" s="27">
+        <v>1</v>
+      </c>
+      <c r="O84" s="27">
+        <v>0</v>
+      </c>
+      <c r="P84" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q84" s="27">
+        <v>1</v>
+      </c>
+      <c r="R84" s="27">
+        <v>0</v>
+      </c>
+      <c r="S84" s="28">
+        <v>0</v>
+      </c>
+      <c r="T84" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U84" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V84" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W84" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X84" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y84" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z84" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA84" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB84" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC84" s="27">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF90AFC1-C7F2-40A3-AB77-CA2E682F3D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D29EB0DF-0CB9-42E5-AFC1-A829F2690588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9472,7 +9472,7 @@
         <v>0</v>
       </c>
       <c r="E80" s="27">
-        <v>3590401</v>
+        <v>5000200</v>
       </c>
       <c r="F80" s="27" t="s">
         <v>539</v>
@@ -9540,7 +9540,7 @@
         <v>1</v>
       </c>
       <c r="AC80" s="27">
-        <v>0</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="81" spans="1:29" x14ac:dyDescent="0.2">
@@ -9557,7 +9557,7 @@
         <v>0</v>
       </c>
       <c r="E81" s="27">
-        <v>3590401</v>
+        <v>5000200</v>
       </c>
       <c r="F81" s="27" t="s">
         <v>540</v>
@@ -9625,7 +9625,7 @@
         <v>1</v>
       </c>
       <c r="AC81" s="27">
-        <v>0</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="82" spans="1:29" x14ac:dyDescent="0.2">
@@ -9642,7 +9642,7 @@
         <v>0</v>
       </c>
       <c r="E82" s="27">
-        <v>3590401</v>
+        <v>5000200</v>
       </c>
       <c r="F82" s="27" t="s">
         <v>538</v>
@@ -9710,7 +9710,7 @@
         <v>1</v>
       </c>
       <c r="AC82" s="27">
-        <v>0</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="83" spans="1:29" x14ac:dyDescent="0.2">

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D29EB0DF-0CB9-42E5-AFC1-A829F2690588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F72139-C5D7-423A-B303-B4D423576F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1127" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="563">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1968,6 +1968,46 @@
   </si>
   <si>
     <t>5200501:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰弹数量</t>
+  </si>
+  <si>
+    <t>冰弹伤害</t>
+  </si>
+  <si>
+    <t>冰弹范围</t>
+  </si>
+  <si>
+    <t>追加冰弹次数&amp;伤害</t>
+  </si>
+  <si>
+    <t>技能效果-次数&amp;伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000301:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000501:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000701:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000901:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000902:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000903:1</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -2593,7 +2633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC84"/>
+  <dimension ref="A1:AC88"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -9477,9 +9517,7 @@
       <c r="F80" s="27" t="s">
         <v>539</v>
       </c>
-      <c r="G80" s="27" t="s">
-        <v>539</v>
-      </c>
+      <c r="G80" s="27"/>
       <c r="H80" s="27"/>
       <c r="I80" s="27"/>
       <c r="J80" s="27" t="s">
@@ -9545,10 +9583,10 @@
     </row>
     <row r="81" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A81" s="27">
-        <v>85100100</v>
+        <v>85000300</v>
       </c>
       <c r="B81" s="27">
-        <v>7005</v>
+        <v>7006</v>
       </c>
       <c r="C81" s="28">
         <v>1</v>
@@ -9557,18 +9595,18 @@
         <v>0</v>
       </c>
       <c r="E81" s="27">
-        <v>5000200</v>
+        <v>5000400</v>
       </c>
       <c r="F81" s="27" t="s">
-        <v>540</v>
-      </c>
-      <c r="G81" s="27" t="s">
-        <v>540</v>
+        <v>552</v>
+      </c>
+      <c r="G81" s="13" t="s">
+        <v>549</v>
       </c>
       <c r="H81" s="27"/>
       <c r="I81" s="27"/>
       <c r="J81" s="27" t="s">
-        <v>43</v>
+        <v>557</v>
       </c>
       <c r="K81" s="27">
         <v>1</v>
@@ -9595,7 +9633,7 @@
         <v>0</v>
       </c>
       <c r="S81" s="28">
-        <v>95100101</v>
+        <v>0</v>
       </c>
       <c r="T81" s="27" t="s">
         <v>43</v>
@@ -9625,15 +9663,15 @@
         <v>1</v>
       </c>
       <c r="AC81" s="27">
-        <v>7000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A82" s="27">
-        <v>85200100</v>
+        <v>85000500</v>
       </c>
       <c r="B82" s="27">
-        <v>7003</v>
+        <v>7008</v>
       </c>
       <c r="C82" s="28">
         <v>1</v>
@@ -9642,21 +9680,21 @@
         <v>0</v>
       </c>
       <c r="E82" s="27">
-        <v>5000200</v>
+        <v>5000600</v>
       </c>
       <c r="F82" s="27" t="s">
-        <v>538</v>
-      </c>
-      <c r="G82" s="27" t="s">
-        <v>538</v>
+        <v>553</v>
+      </c>
+      <c r="G82" s="13" t="s">
+        <v>254</v>
       </c>
       <c r="H82" s="27"/>
       <c r="I82" s="27"/>
       <c r="J82" s="27" t="s">
-        <v>43</v>
+        <v>558</v>
       </c>
       <c r="K82" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L82" s="27">
         <v>0</v>
@@ -9680,7 +9718,7 @@
         <v>0</v>
       </c>
       <c r="S82" s="28">
-        <v>95200101</v>
+        <v>0</v>
       </c>
       <c r="T82" s="27" t="s">
         <v>43</v>
@@ -9710,15 +9748,15 @@
         <v>1</v>
       </c>
       <c r="AC82" s="27">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A83" s="27">
-        <v>85200300</v>
+        <v>85000700</v>
       </c>
       <c r="B83" s="27">
-        <v>7006</v>
+        <v>7009</v>
       </c>
       <c r="C83" s="28">
         <v>1</v>
@@ -9727,18 +9765,18 @@
         <v>0</v>
       </c>
       <c r="E83" s="27">
-        <v>5200400</v>
+        <v>5000800</v>
       </c>
       <c r="F83" s="27" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="G83" s="13" t="s">
-        <v>549</v>
+        <v>253</v>
       </c>
       <c r="H83" s="27"/>
       <c r="I83" s="27"/>
       <c r="J83" s="27" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="K83" s="27">
         <v>1</v>
@@ -9800,10 +9838,10 @@
     </row>
     <row r="84" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A84" s="27">
-        <v>85200500</v>
+        <v>85000900</v>
       </c>
       <c r="B84" s="27">
-        <v>7007</v>
+        <v>7010</v>
       </c>
       <c r="C84" s="28">
         <v>1</v>
@@ -9812,42 +9850,42 @@
         <v>0</v>
       </c>
       <c r="E84" s="27">
-        <v>5200600</v>
+        <v>5001000</v>
       </c>
       <c r="F84" s="27" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="G84" s="13" t="s">
-        <v>254</v>
+        <v>556</v>
       </c>
       <c r="H84" s="27"/>
       <c r="I84" s="27"/>
       <c r="J84" s="27" t="s">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="K84" s="27">
+        <v>1</v>
+      </c>
+      <c r="L84" s="27">
+        <v>0</v>
+      </c>
+      <c r="M84" s="27" t="s">
+        <v>561</v>
+      </c>
+      <c r="N84" s="27">
         <v>2</v>
       </c>
-      <c r="L84" s="27">
-        <v>0</v>
-      </c>
-      <c r="M84" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="N84" s="27">
-        <v>1</v>
-      </c>
       <c r="O84" s="27">
         <v>0</v>
       </c>
       <c r="P84" s="27" t="s">
-        <v>43</v>
+        <v>562</v>
       </c>
       <c r="Q84" s="27">
         <v>1</v>
       </c>
       <c r="R84" s="27">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="S84" s="28">
         <v>0</v>
@@ -9880,6 +9918,342 @@
         <v>1</v>
       </c>
       <c r="AC84" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A85" s="27">
+        <v>85100100</v>
+      </c>
+      <c r="B85" s="27">
+        <v>7011</v>
+      </c>
+      <c r="C85" s="28">
+        <v>1</v>
+      </c>
+      <c r="D85" s="28">
+        <v>0</v>
+      </c>
+      <c r="E85" s="27">
+        <v>5000200</v>
+      </c>
+      <c r="F85" s="27" t="s">
+        <v>540</v>
+      </c>
+      <c r="G85" s="27"/>
+      <c r="H85" s="27"/>
+      <c r="I85" s="27"/>
+      <c r="J85" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="K85" s="27">
+        <v>1</v>
+      </c>
+      <c r="L85" s="27">
+        <v>0</v>
+      </c>
+      <c r="M85" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N85" s="27">
+        <v>1</v>
+      </c>
+      <c r="O85" s="27">
+        <v>0</v>
+      </c>
+      <c r="P85" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q85" s="27">
+        <v>1</v>
+      </c>
+      <c r="R85" s="27">
+        <v>0</v>
+      </c>
+      <c r="S85" s="28">
+        <v>95100101</v>
+      </c>
+      <c r="T85" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U85" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V85" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W85" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X85" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y85" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z85" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA85" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB85" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC85" s="27">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A86" s="27">
+        <v>85200100</v>
+      </c>
+      <c r="B86" s="27">
+        <v>7003</v>
+      </c>
+      <c r="C86" s="28">
+        <v>1</v>
+      </c>
+      <c r="D86" s="28">
+        <v>0</v>
+      </c>
+      <c r="E86" s="27">
+        <v>5000200</v>
+      </c>
+      <c r="F86" s="27" t="s">
+        <v>538</v>
+      </c>
+      <c r="G86" s="27"/>
+      <c r="H86" s="27"/>
+      <c r="I86" s="27"/>
+      <c r="J86" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="K86" s="27">
+        <v>1</v>
+      </c>
+      <c r="L86" s="27">
+        <v>0</v>
+      </c>
+      <c r="M86" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N86" s="27">
+        <v>1</v>
+      </c>
+      <c r="O86" s="27">
+        <v>0</v>
+      </c>
+      <c r="P86" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q86" s="27">
+        <v>1</v>
+      </c>
+      <c r="R86" s="27">
+        <v>0</v>
+      </c>
+      <c r="S86" s="28">
+        <v>95200101</v>
+      </c>
+      <c r="T86" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U86" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V86" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W86" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X86" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y86" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z86" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA86" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB86" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC86" s="27">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="87" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A87" s="27">
+        <v>85200300</v>
+      </c>
+      <c r="B87" s="27">
+        <v>7006</v>
+      </c>
+      <c r="C87" s="28">
+        <v>1</v>
+      </c>
+      <c r="D87" s="28">
+        <v>0</v>
+      </c>
+      <c r="E87" s="27">
+        <v>5200400</v>
+      </c>
+      <c r="F87" s="27" t="s">
+        <v>547</v>
+      </c>
+      <c r="G87" s="13" t="s">
+        <v>549</v>
+      </c>
+      <c r="H87" s="27"/>
+      <c r="I87" s="27"/>
+      <c r="J87" s="27" t="s">
+        <v>550</v>
+      </c>
+      <c r="K87" s="27">
+        <v>1</v>
+      </c>
+      <c r="L87" s="27">
+        <v>0</v>
+      </c>
+      <c r="M87" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N87" s="27">
+        <v>1</v>
+      </c>
+      <c r="O87" s="27">
+        <v>0</v>
+      </c>
+      <c r="P87" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q87" s="27">
+        <v>1</v>
+      </c>
+      <c r="R87" s="27">
+        <v>0</v>
+      </c>
+      <c r="S87" s="28">
+        <v>0</v>
+      </c>
+      <c r="T87" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U87" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V87" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W87" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X87" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y87" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z87" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA87" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB87" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC87" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A88" s="27">
+        <v>85200500</v>
+      </c>
+      <c r="B88" s="27">
+        <v>7007</v>
+      </c>
+      <c r="C88" s="28">
+        <v>1</v>
+      </c>
+      <c r="D88" s="28">
+        <v>0</v>
+      </c>
+      <c r="E88" s="27">
+        <v>5200600</v>
+      </c>
+      <c r="F88" s="27" t="s">
+        <v>548</v>
+      </c>
+      <c r="G88" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="H88" s="27"/>
+      <c r="I88" s="27"/>
+      <c r="J88" s="27" t="s">
+        <v>551</v>
+      </c>
+      <c r="K88" s="27">
+        <v>2</v>
+      </c>
+      <c r="L88" s="27">
+        <v>0</v>
+      </c>
+      <c r="M88" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N88" s="27">
+        <v>1</v>
+      </c>
+      <c r="O88" s="27">
+        <v>0</v>
+      </c>
+      <c r="P88" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q88" s="27">
+        <v>1</v>
+      </c>
+      <c r="R88" s="27">
+        <v>0</v>
+      </c>
+      <c r="S88" s="28">
+        <v>0</v>
+      </c>
+      <c r="T88" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U88" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V88" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W88" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X88" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y88" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z88" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA88" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB88" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC88" s="27">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F72139-C5D7-423A-B303-B4D423576F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1E59C19-A2E7-417C-9AA3-7B211215AAEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="564">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1980,13 +1980,6 @@
     <t>冰弹范围</t>
   </si>
   <si>
-    <t>追加冰弹次数&amp;伤害</t>
-  </si>
-  <si>
-    <t>技能效果-次数&amp;伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
     <t>5000301:1</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
@@ -2003,11 +1996,23 @@
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
-    <t>5000902:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
     <t>5000903:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>追加冰弹次数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>追加冰弹伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果-追加次数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5001101:1</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -2633,7 +2638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC88"/>
+  <dimension ref="A1:AC89"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -9500,7 +9505,7 @@
     </row>
     <row r="80" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A80" s="27">
-        <v>85001000</v>
+        <v>85000100</v>
       </c>
       <c r="B80" s="27">
         <v>7004</v>
@@ -9606,7 +9611,7 @@
       <c r="H81" s="27"/>
       <c r="I81" s="27"/>
       <c r="J81" s="27" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="K81" s="27">
         <v>1</v>
@@ -9691,7 +9696,7 @@
       <c r="H82" s="27"/>
       <c r="I82" s="27"/>
       <c r="J82" s="27" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="K82" s="27">
         <v>2</v>
@@ -9776,7 +9781,7 @@
       <c r="H83" s="27"/>
       <c r="I83" s="27"/>
       <c r="J83" s="27" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="K83" s="27">
         <v>1</v>
@@ -9853,15 +9858,15 @@
         <v>5001000</v>
       </c>
       <c r="F84" s="27" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="G84" s="13" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="H84" s="27"/>
       <c r="I84" s="27"/>
       <c r="J84" s="27" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="K84" s="27">
         <v>1</v>
@@ -9870,16 +9875,16 @@
         <v>0</v>
       </c>
       <c r="M84" s="27" t="s">
-        <v>561</v>
+        <v>43</v>
       </c>
       <c r="N84" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O84" s="27">
         <v>0</v>
       </c>
       <c r="P84" s="27" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="Q84" s="27">
         <v>1</v>
@@ -9923,10 +9928,10 @@
     </row>
     <row r="85" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A85" s="27">
-        <v>85100100</v>
+        <v>85001100</v>
       </c>
       <c r="B85" s="27">
-        <v>7011</v>
+        <v>7012</v>
       </c>
       <c r="C85" s="28">
         <v>1</v>
@@ -9935,12 +9940,14 @@
         <v>0</v>
       </c>
       <c r="E85" s="27">
-        <v>5000200</v>
+        <v>5001200</v>
       </c>
       <c r="F85" s="27" t="s">
-        <v>540</v>
-      </c>
-      <c r="G85" s="27"/>
+        <v>561</v>
+      </c>
+      <c r="G85" s="13" t="s">
+        <v>254</v>
+      </c>
       <c r="H85" s="27"/>
       <c r="I85" s="27"/>
       <c r="J85" s="27" t="s">
@@ -9953,10 +9960,10 @@
         <v>0</v>
       </c>
       <c r="M85" s="27" t="s">
-        <v>43</v>
+        <v>563</v>
       </c>
       <c r="N85" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O85" s="27">
         <v>0</v>
@@ -9971,7 +9978,7 @@
         <v>0</v>
       </c>
       <c r="S85" s="28">
-        <v>95100101</v>
+        <v>0</v>
       </c>
       <c r="T85" s="27" t="s">
         <v>43</v>
@@ -10001,15 +10008,15 @@
         <v>1</v>
       </c>
       <c r="AC85" s="27">
-        <v>7000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A86" s="27">
-        <v>85200100</v>
+        <v>85100100</v>
       </c>
       <c r="B86" s="27">
-        <v>7003</v>
+        <v>7011</v>
       </c>
       <c r="C86" s="28">
         <v>1</v>
@@ -10021,7 +10028,7 @@
         <v>5000200</v>
       </c>
       <c r="F86" s="27" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G86" s="27"/>
       <c r="H86" s="27"/>
@@ -10054,7 +10061,7 @@
         <v>0</v>
       </c>
       <c r="S86" s="28">
-        <v>95200101</v>
+        <v>95100101</v>
       </c>
       <c r="T86" s="27" t="s">
         <v>43</v>
@@ -10084,15 +10091,15 @@
         <v>1</v>
       </c>
       <c r="AC86" s="27">
-        <v>6000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="87" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A87" s="27">
-        <v>85200300</v>
+        <v>85200100</v>
       </c>
       <c r="B87" s="27">
-        <v>7006</v>
+        <v>7003</v>
       </c>
       <c r="C87" s="28">
         <v>1</v>
@@ -10101,18 +10108,16 @@
         <v>0</v>
       </c>
       <c r="E87" s="27">
-        <v>5200400</v>
+        <v>5000200</v>
       </c>
       <c r="F87" s="27" t="s">
-        <v>547</v>
-      </c>
-      <c r="G87" s="13" t="s">
-        <v>549</v>
-      </c>
+        <v>538</v>
+      </c>
+      <c r="G87" s="27"/>
       <c r="H87" s="27"/>
       <c r="I87" s="27"/>
       <c r="J87" s="27" t="s">
-        <v>550</v>
+        <v>43</v>
       </c>
       <c r="K87" s="27">
         <v>1</v>
@@ -10139,7 +10144,7 @@
         <v>0</v>
       </c>
       <c r="S87" s="28">
-        <v>0</v>
+        <v>95200101</v>
       </c>
       <c r="T87" s="27" t="s">
         <v>43</v>
@@ -10169,15 +10174,15 @@
         <v>1</v>
       </c>
       <c r="AC87" s="27">
-        <v>0</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="88" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A88" s="27">
-        <v>85200500</v>
+        <v>85200300</v>
       </c>
       <c r="B88" s="27">
-        <v>7007</v>
+        <v>7006</v>
       </c>
       <c r="C88" s="28">
         <v>1</v>
@@ -10186,21 +10191,21 @@
         <v>0</v>
       </c>
       <c r="E88" s="27">
-        <v>5200600</v>
+        <v>5200400</v>
       </c>
       <c r="F88" s="27" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G88" s="13" t="s">
-        <v>254</v>
+        <v>549</v>
       </c>
       <c r="H88" s="27"/>
       <c r="I88" s="27"/>
       <c r="J88" s="27" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="K88" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L88" s="27">
         <v>0</v>
@@ -10254,6 +10259,91 @@
         <v>1</v>
       </c>
       <c r="AC88" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A89" s="27">
+        <v>85200500</v>
+      </c>
+      <c r="B89" s="27">
+        <v>7007</v>
+      </c>
+      <c r="C89" s="28">
+        <v>1</v>
+      </c>
+      <c r="D89" s="28">
+        <v>0</v>
+      </c>
+      <c r="E89" s="27">
+        <v>5200600</v>
+      </c>
+      <c r="F89" s="27" t="s">
+        <v>548</v>
+      </c>
+      <c r="G89" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="H89" s="27"/>
+      <c r="I89" s="27"/>
+      <c r="J89" s="27" t="s">
+        <v>551</v>
+      </c>
+      <c r="K89" s="27">
+        <v>2</v>
+      </c>
+      <c r="L89" s="27">
+        <v>0</v>
+      </c>
+      <c r="M89" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N89" s="27">
+        <v>1</v>
+      </c>
+      <c r="O89" s="27">
+        <v>0</v>
+      </c>
+      <c r="P89" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q89" s="27">
+        <v>1</v>
+      </c>
+      <c r="R89" s="27">
+        <v>0</v>
+      </c>
+      <c r="S89" s="28">
+        <v>0</v>
+      </c>
+      <c r="T89" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U89" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V89" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W89" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X89" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y89" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z89" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA89" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB89" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC89" s="27">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1E59C19-A2E7-417C-9AA3-7B211215AAEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4FA6D6-2E4F-4948-91DC-E68BE795649C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="566">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2013,6 +2013,13 @@
   </si>
   <si>
     <t>5001101:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰弹命中后产生冰爆</t>
+  </si>
+  <si>
+    <t>5001301:1</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -2638,7 +2645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC89"/>
+  <dimension ref="A1:AC90"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -9583,7 +9590,7 @@
         <v>1</v>
       </c>
       <c r="AC80" s="27">
-        <v>7000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="81" spans="1:29" x14ac:dyDescent="0.2">
@@ -10013,10 +10020,10 @@
     </row>
     <row r="86" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A86" s="27">
-        <v>85100100</v>
+        <v>85001300</v>
       </c>
       <c r="B86" s="27">
-        <v>7011</v>
+        <v>7013</v>
       </c>
       <c r="C86" s="28">
         <v>1</v>
@@ -10025,12 +10032,14 @@
         <v>0</v>
       </c>
       <c r="E86" s="27">
-        <v>5000200</v>
+        <v>5001400</v>
       </c>
       <c r="F86" s="27" t="s">
-        <v>540</v>
-      </c>
-      <c r="G86" s="27"/>
+        <v>564</v>
+      </c>
+      <c r="G86" s="13" t="s">
+        <v>254</v>
+      </c>
       <c r="H86" s="27"/>
       <c r="I86" s="27"/>
       <c r="J86" s="27" t="s">
@@ -10043,13 +10052,13 @@
         <v>0</v>
       </c>
       <c r="M86" s="27" t="s">
-        <v>43</v>
+        <v>565</v>
       </c>
       <c r="N86" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O86" s="27">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="P86" s="27" t="s">
         <v>43</v>
@@ -10061,7 +10070,7 @@
         <v>0</v>
       </c>
       <c r="S86" s="28">
-        <v>95100101</v>
+        <v>0</v>
       </c>
       <c r="T86" s="27" t="s">
         <v>43</v>
@@ -10091,15 +10100,15 @@
         <v>1</v>
       </c>
       <c r="AC86" s="27">
-        <v>7000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A87" s="27">
-        <v>85200100</v>
+        <v>85100100</v>
       </c>
       <c r="B87" s="27">
-        <v>7003</v>
+        <v>7011</v>
       </c>
       <c r="C87" s="28">
         <v>1</v>
@@ -10111,7 +10120,7 @@
         <v>5000200</v>
       </c>
       <c r="F87" s="27" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G87" s="27"/>
       <c r="H87" s="27"/>
@@ -10144,7 +10153,7 @@
         <v>0</v>
       </c>
       <c r="S87" s="28">
-        <v>95200101</v>
+        <v>95100101</v>
       </c>
       <c r="T87" s="27" t="s">
         <v>43</v>
@@ -10174,15 +10183,15 @@
         <v>1</v>
       </c>
       <c r="AC87" s="27">
-        <v>6000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="88" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A88" s="27">
-        <v>85200300</v>
+        <v>85200100</v>
       </c>
       <c r="B88" s="27">
-        <v>7006</v>
+        <v>7003</v>
       </c>
       <c r="C88" s="28">
         <v>1</v>
@@ -10191,18 +10200,16 @@
         <v>0</v>
       </c>
       <c r="E88" s="27">
-        <v>5200400</v>
+        <v>5000200</v>
       </c>
       <c r="F88" s="27" t="s">
-        <v>547</v>
-      </c>
-      <c r="G88" s="13" t="s">
-        <v>549</v>
-      </c>
+        <v>538</v>
+      </c>
+      <c r="G88" s="27"/>
       <c r="H88" s="27"/>
       <c r="I88" s="27"/>
       <c r="J88" s="27" t="s">
-        <v>550</v>
+        <v>43</v>
       </c>
       <c r="K88" s="27">
         <v>1</v>
@@ -10229,7 +10236,7 @@
         <v>0</v>
       </c>
       <c r="S88" s="28">
-        <v>0</v>
+        <v>95200101</v>
       </c>
       <c r="T88" s="27" t="s">
         <v>43</v>
@@ -10259,15 +10266,15 @@
         <v>1</v>
       </c>
       <c r="AC88" s="27">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="89" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A89" s="27">
-        <v>85200500</v>
+        <v>85200300</v>
       </c>
       <c r="B89" s="27">
-        <v>7007</v>
+        <v>7006</v>
       </c>
       <c r="C89" s="28">
         <v>1</v>
@@ -10276,21 +10283,21 @@
         <v>0</v>
       </c>
       <c r="E89" s="27">
-        <v>5200600</v>
+        <v>5200400</v>
       </c>
       <c r="F89" s="27" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G89" s="13" t="s">
-        <v>254</v>
+        <v>549</v>
       </c>
       <c r="H89" s="27"/>
       <c r="I89" s="27"/>
       <c r="J89" s="27" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="K89" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L89" s="27">
         <v>0</v>
@@ -10344,6 +10351,91 @@
         <v>1</v>
       </c>
       <c r="AC89" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A90" s="27">
+        <v>85200500</v>
+      </c>
+      <c r="B90" s="27">
+        <v>7007</v>
+      </c>
+      <c r="C90" s="28">
+        <v>1</v>
+      </c>
+      <c r="D90" s="28">
+        <v>0</v>
+      </c>
+      <c r="E90" s="27">
+        <v>5200600</v>
+      </c>
+      <c r="F90" s="27" t="s">
+        <v>548</v>
+      </c>
+      <c r="G90" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="H90" s="27"/>
+      <c r="I90" s="27"/>
+      <c r="J90" s="27" t="s">
+        <v>551</v>
+      </c>
+      <c r="K90" s="27">
+        <v>2</v>
+      </c>
+      <c r="L90" s="27">
+        <v>0</v>
+      </c>
+      <c r="M90" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N90" s="27">
+        <v>1</v>
+      </c>
+      <c r="O90" s="27">
+        <v>0</v>
+      </c>
+      <c r="P90" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q90" s="27">
+        <v>1</v>
+      </c>
+      <c r="R90" s="27">
+        <v>0</v>
+      </c>
+      <c r="S90" s="28">
+        <v>0</v>
+      </c>
+      <c r="T90" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U90" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V90" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W90" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X90" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y90" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z90" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA90" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB90" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC90" s="27">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4FA6D6-2E4F-4948-91DC-E68BE795649C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17D80138-AA52-4856-8B1F-81563A2A8272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="576">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2020,6 +2020,46 @@
   </si>
   <si>
     <t>5001301:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数1】额外冰弹数量</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数1】冰弹伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数1】冰弹额外范围</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数1】追加冰弹次数，【参数3】释放冰弹延迟时间后追加冰弹</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数2】追加冰弹调整伤害，如果0则和原冰弹伤害相等</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数2】冰爆调整伤害，如果0则和原冰弹伤害相等</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>麻痹状态（无法攻击和移动），持续时间【参数5】，状态命中率【参数6】</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷击概率附加麻痹</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5200701:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5200702:1</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -2027,7 +2067,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2157,8 +2197,16 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2220,6 +2268,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2291,7 +2345,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
@@ -2303,6 +2357,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2347,8 +2404,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="6">
     <cellStyle name="差" xfId="4" builtinId="27"/>
+    <cellStyle name="差 2" xfId="5" xr:uid="{4CD9D8B4-CD25-459C-86C6-6BA0747D60BF}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="适中" xfId="2" builtinId="28"/>
     <cellStyle name="输入" xfId="1" builtinId="20"/>
@@ -2645,7 +2703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC90"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -2656,7 +2714,7 @@
     <col min="6" max="6" width="29.75" customWidth="1"/>
     <col min="7" max="7" width="12.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.875" customWidth="1"/>
+    <col min="9" max="9" width="30.125" customWidth="1"/>
     <col min="10" max="11" width="15.125" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="14" width="15.125" customWidth="1"/>
@@ -9616,7 +9674,9 @@
         <v>549</v>
       </c>
       <c r="H81" s="27"/>
-      <c r="I81" s="27"/>
+      <c r="I81" s="27" t="s">
+        <v>566</v>
+      </c>
       <c r="J81" s="27" t="s">
         <v>555</v>
       </c>
@@ -9701,7 +9761,9 @@
         <v>254</v>
       </c>
       <c r="H82" s="27"/>
-      <c r="I82" s="27"/>
+      <c r="I82" s="27" t="s">
+        <v>567</v>
+      </c>
       <c r="J82" s="27" t="s">
         <v>556</v>
       </c>
@@ -9786,7 +9848,9 @@
         <v>253</v>
       </c>
       <c r="H83" s="27"/>
-      <c r="I83" s="27"/>
+      <c r="I83" s="27" t="s">
+        <v>568</v>
+      </c>
       <c r="J83" s="27" t="s">
         <v>557</v>
       </c>
@@ -9871,7 +9935,9 @@
         <v>562</v>
       </c>
       <c r="H84" s="27"/>
-      <c r="I84" s="27"/>
+      <c r="I84" s="27" t="s">
+        <v>569</v>
+      </c>
       <c r="J84" s="27" t="s">
         <v>558</v>
       </c>
@@ -9956,7 +10022,9 @@
         <v>254</v>
       </c>
       <c r="H85" s="27"/>
-      <c r="I85" s="27"/>
+      <c r="I85" s="27" t="s">
+        <v>570</v>
+      </c>
       <c r="J85" s="27" t="s">
         <v>43</v>
       </c>
@@ -10041,7 +10109,9 @@
         <v>254</v>
       </c>
       <c r="H86" s="27"/>
-      <c r="I86" s="27"/>
+      <c r="I86" s="27" t="s">
+        <v>571</v>
+      </c>
       <c r="J86" s="27" t="s">
         <v>43</v>
       </c>
@@ -10436,6 +10506,91 @@
         <v>1</v>
       </c>
       <c r="AC90" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A91" s="27">
+        <v>85200700</v>
+      </c>
+      <c r="B91" s="27">
+        <v>7014</v>
+      </c>
+      <c r="C91" s="28">
+        <v>1</v>
+      </c>
+      <c r="D91" s="28">
+        <v>0</v>
+      </c>
+      <c r="E91" s="27">
+        <v>5200800</v>
+      </c>
+      <c r="F91" s="27" t="s">
+        <v>573</v>
+      </c>
+      <c r="G91" s="13"/>
+      <c r="H91" s="27"/>
+      <c r="I91" s="27" t="s">
+        <v>572</v>
+      </c>
+      <c r="J91" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="K91" s="27">
+        <v>1</v>
+      </c>
+      <c r="L91" s="27">
+        <v>0</v>
+      </c>
+      <c r="M91" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N91" s="27">
+        <v>1</v>
+      </c>
+      <c r="O91" s="27">
+        <v>0</v>
+      </c>
+      <c r="P91" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q91" s="27">
+        <v>1</v>
+      </c>
+      <c r="R91" s="27">
+        <v>0</v>
+      </c>
+      <c r="S91" s="28">
+        <v>0</v>
+      </c>
+      <c r="T91" s="27" t="s">
+        <v>575</v>
+      </c>
+      <c r="U91" s="27">
+        <v>2000</v>
+      </c>
+      <c r="V91" s="27" t="s">
+        <v>574</v>
+      </c>
+      <c r="W91" s="27">
+        <v>7500</v>
+      </c>
+      <c r="X91" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y91" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z91" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA91" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB91" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC91" s="27">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17D80138-AA52-4856-8B1F-81563A2A8272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB2C580-3D04-4F60-A750-008935FB9DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1235" uniqueCount="592">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2031,10 +2031,6 @@
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
-    <t>【参数1】冰弹额外范围</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
     <t>【参数1】追加冰弹次数，【参数3】释放冰弹延迟时间后追加冰弹</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
@@ -2043,10 +2039,6 @@
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
-    <t>【参数2】冰爆调整伤害，如果0则和原冰弹伤害相等</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
     <t>麻痹状态（无法攻击和移动），持续时间【参数5】，状态命中率【参数6】</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
@@ -2060,6 +2052,74 @@
   </si>
   <si>
     <t>5200702:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石额外范围</t>
+  </si>
+  <si>
+    <t>陨石伤害</t>
+  </si>
+  <si>
+    <t>陨石数量</t>
+  </si>
+  <si>
+    <t>陨石落地后产生冲击波</t>
+  </si>
+  <si>
+    <t>技能效果-额外效果</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5100301:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5100501:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5100701:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5100901:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5100902:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数1】陨石伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数1】陨石数量</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数1】冰弹额外范围（度数）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数1】陨石额外范围（半径）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数1】雷击目标数量</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数1】雷击伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石落地后产生冲击波，【参数1】冲击波相对于陨石的额外范围（半径），【参数2】冲击波调整伤害，如果0则和原陨石伤害相等</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数2】冰爆调整伤害，如果0则和原冰弹伤害相等；默认值-60%</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -2703,7 +2763,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AC95"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -9573,7 +9633,7 @@
         <v>85000100</v>
       </c>
       <c r="B80" s="27">
-        <v>7004</v>
+        <v>7003</v>
       </c>
       <c r="C80" s="28">
         <v>1</v>
@@ -9656,7 +9716,7 @@
         <v>85000300</v>
       </c>
       <c r="B81" s="27">
-        <v>7006</v>
+        <v>7004</v>
       </c>
       <c r="C81" s="28">
         <v>1</v>
@@ -9743,7 +9803,7 @@
         <v>85000500</v>
       </c>
       <c r="B82" s="27">
-        <v>7008</v>
+        <v>7005</v>
       </c>
       <c r="C82" s="28">
         <v>1</v>
@@ -9830,7 +9890,7 @@
         <v>85000700</v>
       </c>
       <c r="B83" s="27">
-        <v>7009</v>
+        <v>7006</v>
       </c>
       <c r="C83" s="28">
         <v>1</v>
@@ -9849,7 +9909,7 @@
       </c>
       <c r="H83" s="27"/>
       <c r="I83" s="27" t="s">
-        <v>568</v>
+        <v>586</v>
       </c>
       <c r="J83" s="27" t="s">
         <v>557</v>
@@ -9917,7 +9977,7 @@
         <v>85000900</v>
       </c>
       <c r="B84" s="27">
-        <v>7010</v>
+        <v>7007</v>
       </c>
       <c r="C84" s="28">
         <v>1</v>
@@ -9936,7 +9996,7 @@
       </c>
       <c r="H84" s="27"/>
       <c r="I84" s="27" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="J84" s="27" t="s">
         <v>558</v>
@@ -10004,7 +10064,7 @@
         <v>85001100</v>
       </c>
       <c r="B85" s="27">
-        <v>7012</v>
+        <v>7008</v>
       </c>
       <c r="C85" s="28">
         <v>1</v>
@@ -10023,7 +10083,7 @@
       </c>
       <c r="H85" s="27"/>
       <c r="I85" s="27" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="J85" s="27" t="s">
         <v>43</v>
@@ -10091,7 +10151,7 @@
         <v>85001300</v>
       </c>
       <c r="B86" s="27">
-        <v>7013</v>
+        <v>7009</v>
       </c>
       <c r="C86" s="28">
         <v>1</v>
@@ -10106,11 +10166,11 @@
         <v>564</v>
       </c>
       <c r="G86" s="13" t="s">
-        <v>254</v>
+        <v>578</v>
       </c>
       <c r="H86" s="27"/>
       <c r="I86" s="27" t="s">
-        <v>571</v>
+        <v>591</v>
       </c>
       <c r="J86" s="27" t="s">
         <v>43</v>
@@ -10178,7 +10238,7 @@
         <v>85100100</v>
       </c>
       <c r="B87" s="27">
-        <v>7011</v>
+        <v>7010</v>
       </c>
       <c r="C87" s="28">
         <v>1</v>
@@ -10258,10 +10318,10 @@
     </row>
     <row r="88" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A88" s="27">
-        <v>85200100</v>
+        <v>85100300</v>
       </c>
       <c r="B88" s="27">
-        <v>7003</v>
+        <v>7011</v>
       </c>
       <c r="C88" s="28">
         <v>1</v>
@@ -10270,16 +10330,20 @@
         <v>0</v>
       </c>
       <c r="E88" s="27">
-        <v>5000200</v>
+        <v>5100400</v>
       </c>
       <c r="F88" s="27" t="s">
-        <v>538</v>
-      </c>
-      <c r="G88" s="27"/>
+        <v>574</v>
+      </c>
+      <c r="G88" s="13" t="s">
+        <v>253</v>
+      </c>
       <c r="H88" s="27"/>
-      <c r="I88" s="27"/>
+      <c r="I88" s="27" t="s">
+        <v>587</v>
+      </c>
       <c r="J88" s="27" t="s">
-        <v>43</v>
+        <v>579</v>
       </c>
       <c r="K88" s="27">
         <v>1</v>
@@ -10306,7 +10370,7 @@
         <v>0</v>
       </c>
       <c r="S88" s="28">
-        <v>95200101</v>
+        <v>0</v>
       </c>
       <c r="T88" s="27" t="s">
         <v>43</v>
@@ -10336,15 +10400,15 @@
         <v>1</v>
       </c>
       <c r="AC88" s="27">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A89" s="27">
-        <v>85200300</v>
+        <v>85100500</v>
       </c>
       <c r="B89" s="27">
-        <v>7006</v>
+        <v>7012</v>
       </c>
       <c r="C89" s="28">
         <v>1</v>
@@ -10353,21 +10417,23 @@
         <v>0</v>
       </c>
       <c r="E89" s="27">
-        <v>5200400</v>
+        <v>5100600</v>
       </c>
       <c r="F89" s="27" t="s">
-        <v>547</v>
+        <v>575</v>
       </c>
       <c r="G89" s="13" t="s">
-        <v>549</v>
+        <v>254</v>
       </c>
       <c r="H89" s="27"/>
-      <c r="I89" s="27"/>
+      <c r="I89" s="27" t="s">
+        <v>584</v>
+      </c>
       <c r="J89" s="27" t="s">
-        <v>550</v>
+        <v>580</v>
       </c>
       <c r="K89" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L89" s="27">
         <v>0</v>
@@ -10426,10 +10492,10 @@
     </row>
     <row r="90" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A90" s="27">
-        <v>85200500</v>
+        <v>85100700</v>
       </c>
       <c r="B90" s="27">
-        <v>7007</v>
+        <v>7013</v>
       </c>
       <c r="C90" s="28">
         <v>1</v>
@@ -10438,21 +10504,23 @@
         <v>0</v>
       </c>
       <c r="E90" s="27">
-        <v>5200600</v>
+        <v>5100800</v>
       </c>
       <c r="F90" s="27" t="s">
-        <v>548</v>
+        <v>576</v>
       </c>
       <c r="G90" s="13" t="s">
-        <v>254</v>
+        <v>549</v>
       </c>
       <c r="H90" s="27"/>
-      <c r="I90" s="27"/>
+      <c r="I90" s="27" t="s">
+        <v>585</v>
+      </c>
       <c r="J90" s="27" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="K90" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L90" s="27">
         <v>0</v>
@@ -10511,7 +10579,7 @@
     </row>
     <row r="91" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A91" s="27">
-        <v>85200700</v>
+        <v>85100900</v>
       </c>
       <c r="B91" s="27">
         <v>7014</v>
@@ -10523,74 +10591,418 @@
         <v>0</v>
       </c>
       <c r="E91" s="27">
-        <v>5200800</v>
+        <v>5101000</v>
       </c>
       <c r="F91" s="27" t="s">
-        <v>573</v>
-      </c>
-      <c r="G91" s="13"/>
+        <v>577</v>
+      </c>
+      <c r="G91" s="13" t="s">
+        <v>578</v>
+      </c>
       <c r="H91" s="27"/>
       <c r="I91" s="27" t="s">
+        <v>590</v>
+      </c>
+      <c r="J91" s="27" t="s">
+        <v>582</v>
+      </c>
+      <c r="K91" s="27">
+        <v>1</v>
+      </c>
+      <c r="L91" s="27">
+        <v>0</v>
+      </c>
+      <c r="M91" s="27" t="s">
+        <v>583</v>
+      </c>
+      <c r="N91" s="27">
+        <v>2</v>
+      </c>
+      <c r="O91" s="27">
+        <v>0</v>
+      </c>
+      <c r="P91" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q91" s="27">
+        <v>1</v>
+      </c>
+      <c r="R91" s="27">
+        <v>0</v>
+      </c>
+      <c r="S91" s="28">
+        <v>0</v>
+      </c>
+      <c r="T91" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U91" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V91" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W91" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X91" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y91" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z91" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA91" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB91" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC91" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A92" s="27">
+        <v>85200100</v>
+      </c>
+      <c r="B92" s="27">
+        <v>7015</v>
+      </c>
+      <c r="C92" s="28">
+        <v>1</v>
+      </c>
+      <c r="D92" s="28">
+        <v>0</v>
+      </c>
+      <c r="E92" s="27">
+        <v>5000200</v>
+      </c>
+      <c r="F92" s="27" t="s">
+        <v>538</v>
+      </c>
+      <c r="G92" s="27"/>
+      <c r="H92" s="27"/>
+      <c r="I92" s="27"/>
+      <c r="J92" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="K92" s="27">
+        <v>1</v>
+      </c>
+      <c r="L92" s="27">
+        <v>0</v>
+      </c>
+      <c r="M92" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N92" s="27">
+        <v>1</v>
+      </c>
+      <c r="O92" s="27">
+        <v>0</v>
+      </c>
+      <c r="P92" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q92" s="27">
+        <v>1</v>
+      </c>
+      <c r="R92" s="27">
+        <v>0</v>
+      </c>
+      <c r="S92" s="28">
+        <v>95200101</v>
+      </c>
+      <c r="T92" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U92" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V92" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W92" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X92" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y92" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z92" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA92" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB92" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC92" s="27">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="93" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A93" s="27">
+        <v>85200300</v>
+      </c>
+      <c r="B93" s="27">
+        <v>7016</v>
+      </c>
+      <c r="C93" s="28">
+        <v>1</v>
+      </c>
+      <c r="D93" s="28">
+        <v>0</v>
+      </c>
+      <c r="E93" s="27">
+        <v>5200400</v>
+      </c>
+      <c r="F93" s="27" t="s">
+        <v>547</v>
+      </c>
+      <c r="G93" s="13" t="s">
+        <v>549</v>
+      </c>
+      <c r="H93" s="27"/>
+      <c r="I93" s="27" t="s">
+        <v>588</v>
+      </c>
+      <c r="J93" s="27" t="s">
+        <v>550</v>
+      </c>
+      <c r="K93" s="27">
+        <v>1</v>
+      </c>
+      <c r="L93" s="27">
+        <v>0</v>
+      </c>
+      <c r="M93" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N93" s="27">
+        <v>1</v>
+      </c>
+      <c r="O93" s="27">
+        <v>0</v>
+      </c>
+      <c r="P93" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q93" s="27">
+        <v>1</v>
+      </c>
+      <c r="R93" s="27">
+        <v>0</v>
+      </c>
+      <c r="S93" s="28">
+        <v>0</v>
+      </c>
+      <c r="T93" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U93" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V93" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W93" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X93" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y93" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z93" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA93" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB93" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC93" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A94" s="27">
+        <v>85200500</v>
+      </c>
+      <c r="B94" s="27">
+        <v>7017</v>
+      </c>
+      <c r="C94" s="28">
+        <v>1</v>
+      </c>
+      <c r="D94" s="28">
+        <v>0</v>
+      </c>
+      <c r="E94" s="27">
+        <v>5200600</v>
+      </c>
+      <c r="F94" s="27" t="s">
+        <v>548</v>
+      </c>
+      <c r="G94" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="H94" s="27"/>
+      <c r="I94" s="27" t="s">
+        <v>589</v>
+      </c>
+      <c r="J94" s="27" t="s">
+        <v>551</v>
+      </c>
+      <c r="K94" s="27">
+        <v>2</v>
+      </c>
+      <c r="L94" s="27">
+        <v>0</v>
+      </c>
+      <c r="M94" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N94" s="27">
+        <v>1</v>
+      </c>
+      <c r="O94" s="27">
+        <v>0</v>
+      </c>
+      <c r="P94" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q94" s="27">
+        <v>1</v>
+      </c>
+      <c r="R94" s="27">
+        <v>0</v>
+      </c>
+      <c r="S94" s="28">
+        <v>0</v>
+      </c>
+      <c r="T94" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U94" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V94" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W94" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X94" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y94" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z94" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA94" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB94" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC94" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A95" s="27">
+        <v>85200700</v>
+      </c>
+      <c r="B95" s="27">
+        <v>7018</v>
+      </c>
+      <c r="C95" s="28">
+        <v>1</v>
+      </c>
+      <c r="D95" s="28">
+        <v>0</v>
+      </c>
+      <c r="E95" s="27">
+        <v>5200800</v>
+      </c>
+      <c r="F95" s="27" t="s">
+        <v>571</v>
+      </c>
+      <c r="G95" s="13"/>
+      <c r="H95" s="27"/>
+      <c r="I95" s="27" t="s">
+        <v>570</v>
+      </c>
+      <c r="J95" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="K95" s="27">
+        <v>1</v>
+      </c>
+      <c r="L95" s="27">
+        <v>0</v>
+      </c>
+      <c r="M95" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N95" s="27">
+        <v>1</v>
+      </c>
+      <c r="O95" s="27">
+        <v>0</v>
+      </c>
+      <c r="P95" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q95" s="27">
+        <v>1</v>
+      </c>
+      <c r="R95" s="27">
+        <v>0</v>
+      </c>
+      <c r="S95" s="28">
+        <v>0</v>
+      </c>
+      <c r="T95" s="27" t="s">
+        <v>573</v>
+      </c>
+      <c r="U95" s="27">
+        <v>2000</v>
+      </c>
+      <c r="V95" s="27" t="s">
         <v>572</v>
       </c>
-      <c r="J91" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="K91" s="27">
-        <v>1</v>
-      </c>
-      <c r="L91" s="27">
-        <v>0</v>
-      </c>
-      <c r="M91" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="N91" s="27">
-        <v>1</v>
-      </c>
-      <c r="O91" s="27">
-        <v>0</v>
-      </c>
-      <c r="P91" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q91" s="27">
-        <v>1</v>
-      </c>
-      <c r="R91" s="27">
-        <v>0</v>
-      </c>
-      <c r="S91" s="28">
-        <v>0</v>
-      </c>
-      <c r="T91" s="27" t="s">
-        <v>575</v>
-      </c>
-      <c r="U91" s="27">
-        <v>2000</v>
-      </c>
-      <c r="V91" s="27" t="s">
-        <v>574</v>
-      </c>
-      <c r="W91" s="27">
+      <c r="W95" s="27">
         <v>7500</v>
       </c>
-      <c r="X91" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y91" s="27">
-        <v>1</v>
-      </c>
-      <c r="Z91" s="27">
-        <v>1</v>
-      </c>
-      <c r="AA91" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB91" s="27">
-        <v>1</v>
-      </c>
-      <c r="AC91" s="27">
+      <c r="X95" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y95" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z95" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA95" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB95" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC95" s="27">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB2C580-3D04-4F60-A750-008935FB9DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6762F9B4-1051-49BF-9F90-277551F4CFFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1235" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="605">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2120,6 +2120,57 @@
   </si>
   <si>
     <t>【参数2】冰爆调整伤害，如果0则和原冰弹伤害相等；默认值-60%</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰弹CD</t>
+  </si>
+  <si>
+    <t>技能效果-冷却</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数1】冰弹CD，正为加，负为减</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5020301:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石CD</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数1】陨石CD，正为加，负为减</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5120301:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5220301:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷击CD</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数1】雷击CD，正为加，负为减</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>7000101:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数1】普攻伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻伤害</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -2763,7 +2814,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC95"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -10235,7 +10286,7 @@
     </row>
     <row r="87" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A87" s="27">
-        <v>85100100</v>
+        <v>85020300</v>
       </c>
       <c r="B87" s="27">
         <v>7010</v>
@@ -10247,19 +10298,23 @@
         <v>0</v>
       </c>
       <c r="E87" s="27">
-        <v>5000200</v>
+        <v>5020400</v>
       </c>
       <c r="F87" s="27" t="s">
-        <v>540</v>
-      </c>
-      <c r="G87" s="27"/>
+        <v>592</v>
+      </c>
+      <c r="G87" s="13" t="s">
+        <v>593</v>
+      </c>
       <c r="H87" s="27"/>
-      <c r="I87" s="27"/>
+      <c r="I87" s="27" t="s">
+        <v>594</v>
+      </c>
       <c r="J87" s="27" t="s">
-        <v>43</v>
+        <v>595</v>
       </c>
       <c r="K87" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L87" s="27">
         <v>0</v>
@@ -10283,7 +10338,7 @@
         <v>0</v>
       </c>
       <c r="S87" s="28">
-        <v>95100101</v>
+        <v>0</v>
       </c>
       <c r="T87" s="27" t="s">
         <v>43</v>
@@ -10313,12 +10368,12 @@
         <v>1</v>
       </c>
       <c r="AC87" s="27">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A88" s="27">
-        <v>85100300</v>
+        <v>85100100</v>
       </c>
       <c r="B88" s="27">
         <v>7011</v>
@@ -10330,20 +10385,16 @@
         <v>0</v>
       </c>
       <c r="E88" s="27">
-        <v>5100400</v>
+        <v>5000200</v>
       </c>
       <c r="F88" s="27" t="s">
-        <v>574</v>
-      </c>
-      <c r="G88" s="13" t="s">
-        <v>253</v>
-      </c>
+        <v>540</v>
+      </c>
+      <c r="G88" s="27"/>
       <c r="H88" s="27"/>
-      <c r="I88" s="27" t="s">
-        <v>587</v>
-      </c>
+      <c r="I88" s="27"/>
       <c r="J88" s="27" t="s">
-        <v>579</v>
+        <v>43</v>
       </c>
       <c r="K88" s="27">
         <v>1</v>
@@ -10370,7 +10421,7 @@
         <v>0</v>
       </c>
       <c r="S88" s="28">
-        <v>0</v>
+        <v>95100101</v>
       </c>
       <c r="T88" s="27" t="s">
         <v>43</v>
@@ -10400,12 +10451,12 @@
         <v>1</v>
       </c>
       <c r="AC88" s="27">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="89" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A89" s="27">
-        <v>85100500</v>
+        <v>85100300</v>
       </c>
       <c r="B89" s="27">
         <v>7012</v>
@@ -10417,23 +10468,23 @@
         <v>0</v>
       </c>
       <c r="E89" s="27">
-        <v>5100600</v>
+        <v>5100400</v>
       </c>
       <c r="F89" s="27" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="G89" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H89" s="27"/>
       <c r="I89" s="27" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="J89" s="27" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="K89" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L89" s="27">
         <v>0</v>
@@ -10492,7 +10543,7 @@
     </row>
     <row r="90" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A90" s="27">
-        <v>85100700</v>
+        <v>85100500</v>
       </c>
       <c r="B90" s="27">
         <v>7013</v>
@@ -10504,23 +10555,23 @@
         <v>0</v>
       </c>
       <c r="E90" s="27">
-        <v>5100800</v>
+        <v>5100600</v>
       </c>
       <c r="F90" s="27" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="G90" s="13" t="s">
-        <v>549</v>
+        <v>254</v>
       </c>
       <c r="H90" s="27"/>
       <c r="I90" s="27" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="J90" s="27" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="K90" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L90" s="27">
         <v>0</v>
@@ -10579,7 +10630,7 @@
     </row>
     <row r="91" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A91" s="27">
-        <v>85100900</v>
+        <v>85100700</v>
       </c>
       <c r="B91" s="27">
         <v>7014</v>
@@ -10591,20 +10642,20 @@
         <v>0</v>
       </c>
       <c r="E91" s="27">
-        <v>5101000</v>
+        <v>5100800</v>
       </c>
       <c r="F91" s="27" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="G91" s="13" t="s">
-        <v>578</v>
+        <v>549</v>
       </c>
       <c r="H91" s="27"/>
       <c r="I91" s="27" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="J91" s="27" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="K91" s="27">
         <v>1</v>
@@ -10613,10 +10664,10 @@
         <v>0</v>
       </c>
       <c r="M91" s="27" t="s">
-        <v>583</v>
+        <v>43</v>
       </c>
       <c r="N91" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O91" s="27">
         <v>0</v>
@@ -10666,7 +10717,7 @@
     </row>
     <row r="92" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A92" s="27">
-        <v>85200100</v>
+        <v>85100900</v>
       </c>
       <c r="B92" s="27">
         <v>7015</v>
@@ -10678,16 +10729,20 @@
         <v>0</v>
       </c>
       <c r="E92" s="27">
-        <v>5000200</v>
+        <v>5101000</v>
       </c>
       <c r="F92" s="27" t="s">
-        <v>538</v>
-      </c>
-      <c r="G92" s="27"/>
+        <v>577</v>
+      </c>
+      <c r="G92" s="13" t="s">
+        <v>578</v>
+      </c>
       <c r="H92" s="27"/>
-      <c r="I92" s="27"/>
+      <c r="I92" s="27" t="s">
+        <v>590</v>
+      </c>
       <c r="J92" s="27" t="s">
-        <v>43</v>
+        <v>582</v>
       </c>
       <c r="K92" s="27">
         <v>1</v>
@@ -10696,13 +10751,13 @@
         <v>0</v>
       </c>
       <c r="M92" s="27" t="s">
-        <v>43</v>
+        <v>583</v>
       </c>
       <c r="N92" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O92" s="27">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="P92" s="27" t="s">
         <v>43</v>
@@ -10714,7 +10769,7 @@
         <v>0</v>
       </c>
       <c r="S92" s="28">
-        <v>95200101</v>
+        <v>0</v>
       </c>
       <c r="T92" s="27" t="s">
         <v>43</v>
@@ -10744,12 +10799,12 @@
         <v>1</v>
       </c>
       <c r="AC92" s="27">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A93" s="27">
-        <v>85200300</v>
+        <v>85120300</v>
       </c>
       <c r="B93" s="27">
         <v>7016</v>
@@ -10761,23 +10816,23 @@
         <v>0</v>
       </c>
       <c r="E93" s="27">
-        <v>5200400</v>
+        <v>5120400</v>
       </c>
       <c r="F93" s="27" t="s">
-        <v>547</v>
+        <v>596</v>
       </c>
       <c r="G93" s="13" t="s">
-        <v>549</v>
+        <v>593</v>
       </c>
       <c r="H93" s="27"/>
       <c r="I93" s="27" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="J93" s="27" t="s">
-        <v>550</v>
+        <v>598</v>
       </c>
       <c r="K93" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L93" s="27">
         <v>0</v>
@@ -10836,7 +10891,7 @@
     </row>
     <row r="94" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A94" s="27">
-        <v>85200500</v>
+        <v>85200100</v>
       </c>
       <c r="B94" s="27">
         <v>7017</v>
@@ -10848,23 +10903,19 @@
         <v>0</v>
       </c>
       <c r="E94" s="27">
-        <v>5200600</v>
+        <v>5000200</v>
       </c>
       <c r="F94" s="27" t="s">
-        <v>548</v>
-      </c>
-      <c r="G94" s="13" t="s">
-        <v>254</v>
-      </c>
+        <v>538</v>
+      </c>
+      <c r="G94" s="27"/>
       <c r="H94" s="27"/>
-      <c r="I94" s="27" t="s">
-        <v>589</v>
-      </c>
+      <c r="I94" s="27"/>
       <c r="J94" s="27" t="s">
-        <v>551</v>
+        <v>43</v>
       </c>
       <c r="K94" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L94" s="27">
         <v>0</v>
@@ -10888,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="S94" s="28">
-        <v>0</v>
+        <v>95200101</v>
       </c>
       <c r="T94" s="27" t="s">
         <v>43</v>
@@ -10918,12 +10969,12 @@
         <v>1</v>
       </c>
       <c r="AC94" s="27">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="95" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A95" s="27">
-        <v>85200700</v>
+        <v>85200300</v>
       </c>
       <c r="B95" s="27">
         <v>7018</v>
@@ -10935,74 +10986,422 @@
         <v>0</v>
       </c>
       <c r="E95" s="27">
-        <v>5200800</v>
+        <v>5200400</v>
       </c>
       <c r="F95" s="27" t="s">
-        <v>571</v>
-      </c>
-      <c r="G95" s="13"/>
+        <v>547</v>
+      </c>
+      <c r="G95" s="13" t="s">
+        <v>549</v>
+      </c>
       <c r="H95" s="27"/>
       <c r="I95" s="27" t="s">
+        <v>588</v>
+      </c>
+      <c r="J95" s="27" t="s">
+        <v>550</v>
+      </c>
+      <c r="K95" s="27">
+        <v>1</v>
+      </c>
+      <c r="L95" s="27">
+        <v>0</v>
+      </c>
+      <c r="M95" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N95" s="27">
+        <v>1</v>
+      </c>
+      <c r="O95" s="27">
+        <v>0</v>
+      </c>
+      <c r="P95" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q95" s="27">
+        <v>1</v>
+      </c>
+      <c r="R95" s="27">
+        <v>0</v>
+      </c>
+      <c r="S95" s="28">
+        <v>0</v>
+      </c>
+      <c r="T95" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U95" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V95" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W95" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X95" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y95" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z95" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA95" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB95" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC95" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A96" s="27">
+        <v>85200500</v>
+      </c>
+      <c r="B96" s="27">
+        <v>7019</v>
+      </c>
+      <c r="C96" s="28">
+        <v>1</v>
+      </c>
+      <c r="D96" s="28">
+        <v>0</v>
+      </c>
+      <c r="E96" s="27">
+        <v>5200600</v>
+      </c>
+      <c r="F96" s="27" t="s">
+        <v>548</v>
+      </c>
+      <c r="G96" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="H96" s="27"/>
+      <c r="I96" s="27" t="s">
+        <v>589</v>
+      </c>
+      <c r="J96" s="27" t="s">
+        <v>551</v>
+      </c>
+      <c r="K96" s="27">
+        <v>2</v>
+      </c>
+      <c r="L96" s="27">
+        <v>0</v>
+      </c>
+      <c r="M96" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N96" s="27">
+        <v>1</v>
+      </c>
+      <c r="O96" s="27">
+        <v>0</v>
+      </c>
+      <c r="P96" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q96" s="27">
+        <v>1</v>
+      </c>
+      <c r="R96" s="27">
+        <v>0</v>
+      </c>
+      <c r="S96" s="28">
+        <v>0</v>
+      </c>
+      <c r="T96" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U96" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V96" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W96" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X96" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y96" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z96" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA96" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB96" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC96" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A97" s="27">
+        <v>85200700</v>
+      </c>
+      <c r="B97" s="27">
+        <v>7020</v>
+      </c>
+      <c r="C97" s="28">
+        <v>1</v>
+      </c>
+      <c r="D97" s="28">
+        <v>0</v>
+      </c>
+      <c r="E97" s="27">
+        <v>5200800</v>
+      </c>
+      <c r="F97" s="27" t="s">
+        <v>571</v>
+      </c>
+      <c r="G97" s="13"/>
+      <c r="H97" s="27"/>
+      <c r="I97" s="27" t="s">
         <v>570</v>
       </c>
-      <c r="J95" s="27" t="s">
+      <c r="J97" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="K95" s="27">
-        <v>1</v>
-      </c>
-      <c r="L95" s="27">
-        <v>0</v>
-      </c>
-      <c r="M95" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="N95" s="27">
-        <v>1</v>
-      </c>
-      <c r="O95" s="27">
-        <v>0</v>
-      </c>
-      <c r="P95" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q95" s="27">
-        <v>1</v>
-      </c>
-      <c r="R95" s="27">
-        <v>0</v>
-      </c>
-      <c r="S95" s="28">
-        <v>0</v>
-      </c>
-      <c r="T95" s="27" t="s">
+      <c r="K97" s="27">
+        <v>1</v>
+      </c>
+      <c r="L97" s="27">
+        <v>0</v>
+      </c>
+      <c r="M97" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N97" s="27">
+        <v>1</v>
+      </c>
+      <c r="O97" s="27">
+        <v>0</v>
+      </c>
+      <c r="P97" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q97" s="27">
+        <v>1</v>
+      </c>
+      <c r="R97" s="27">
+        <v>0</v>
+      </c>
+      <c r="S97" s="28">
+        <v>0</v>
+      </c>
+      <c r="T97" s="27" t="s">
         <v>573</v>
       </c>
-      <c r="U95" s="27">
+      <c r="U97" s="27">
         <v>2000</v>
       </c>
-      <c r="V95" s="27" t="s">
+      <c r="V97" s="27" t="s">
         <v>572</v>
       </c>
-      <c r="W95" s="27">
+      <c r="W97" s="27">
         <v>7500</v>
       </c>
-      <c r="X95" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y95" s="27">
-        <v>1</v>
-      </c>
-      <c r="Z95" s="27">
-        <v>1</v>
-      </c>
-      <c r="AA95" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB95" s="27">
-        <v>1</v>
-      </c>
-      <c r="AC95" s="27">
+      <c r="X97" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y97" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z97" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA97" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB97" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC97" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A98" s="27">
+        <v>85220300</v>
+      </c>
+      <c r="B98" s="27">
+        <v>7021</v>
+      </c>
+      <c r="C98" s="28">
+        <v>1</v>
+      </c>
+      <c r="D98" s="28">
+        <v>0</v>
+      </c>
+      <c r="E98" s="27">
+        <v>5220400</v>
+      </c>
+      <c r="F98" s="27" t="s">
+        <v>600</v>
+      </c>
+      <c r="G98" s="13" t="s">
+        <v>593</v>
+      </c>
+      <c r="H98" s="27"/>
+      <c r="I98" s="27" t="s">
+        <v>601</v>
+      </c>
+      <c r="J98" s="27" t="s">
+        <v>599</v>
+      </c>
+      <c r="K98" s="27">
+        <v>2</v>
+      </c>
+      <c r="L98" s="27">
+        <v>0</v>
+      </c>
+      <c r="M98" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N98" s="27">
+        <v>1</v>
+      </c>
+      <c r="O98" s="27">
+        <v>0</v>
+      </c>
+      <c r="P98" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q98" s="27">
+        <v>1</v>
+      </c>
+      <c r="R98" s="27">
+        <v>0</v>
+      </c>
+      <c r="S98" s="28">
+        <v>0</v>
+      </c>
+      <c r="T98" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U98" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V98" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W98" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X98" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y98" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z98" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA98" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB98" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC98" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A99" s="27">
+        <v>87000100</v>
+      </c>
+      <c r="B99" s="27">
+        <v>7022</v>
+      </c>
+      <c r="C99" s="28">
+        <v>1</v>
+      </c>
+      <c r="D99" s="28">
+        <v>0</v>
+      </c>
+      <c r="E99" s="27">
+        <v>7000200</v>
+      </c>
+      <c r="F99" s="27" t="s">
+        <v>604</v>
+      </c>
+      <c r="G99" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="H99" s="27"/>
+      <c r="I99" s="27" t="s">
+        <v>603</v>
+      </c>
+      <c r="J99" s="27" t="s">
+        <v>602</v>
+      </c>
+      <c r="K99" s="27">
+        <v>2</v>
+      </c>
+      <c r="L99" s="27">
+        <v>0</v>
+      </c>
+      <c r="M99" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N99" s="27">
+        <v>1</v>
+      </c>
+      <c r="O99" s="27">
+        <v>0</v>
+      </c>
+      <c r="P99" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q99" s="27">
+        <v>1</v>
+      </c>
+      <c r="R99" s="27">
+        <v>0</v>
+      </c>
+      <c r="S99" s="28">
+        <v>0</v>
+      </c>
+      <c r="T99" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U99" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V99" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W99" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X99" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y99" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z99" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA99" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB99" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC99" s="27">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6762F9B4-1051-49BF-9F90-277551F4CFFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1CC00D-67D1-431E-8514-CFEDF4F96E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10385,7 +10385,7 @@
         <v>0</v>
       </c>
       <c r="E88" s="27">
-        <v>5000200</v>
+        <v>5100200</v>
       </c>
       <c r="F88" s="27" t="s">
         <v>540</v>
@@ -10903,7 +10903,7 @@
         <v>0</v>
       </c>
       <c r="E94" s="27">
-        <v>5000200</v>
+        <v>5200200</v>
       </c>
       <c r="F94" s="27" t="s">
         <v>538</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1CC00D-67D1-431E-8514-CFEDF4F96E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA6548A-99D1-4419-8993-8602D60C8907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -11236,7 +11236,7 @@
         <v>85220300</v>
       </c>
       <c r="B98" s="27">
-        <v>7021</v>
+        <v>7022</v>
       </c>
       <c r="C98" s="28">
         <v>1</v>
@@ -11323,7 +11323,7 @@
         <v>87000100</v>
       </c>
       <c r="B99" s="27">
-        <v>7022</v>
+        <v>7023</v>
       </c>
       <c r="C99" s="28">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA6548A-99D1-4419-8993-8602D60C8907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC69D2CD-6CF5-4D0A-B824-4DD253E881F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="615">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2171,6 +2171,46 @@
   </si>
   <si>
     <t>普攻伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰弹概率附加冰冻</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰冻状态（无法攻击和移动），持续时间【参数5】，状态命中率【参数6】</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5001501:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5001502:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5101201:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5101202:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5101205:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5101206:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5101208:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>每【参数8】（默认1000）毫秒，造成{[攻击直接伤害+火元素直接伤害]【参数1万分比】（默认30%）}，【参数2】（默认0）的[额外火元素持续伤害]，效果持续【参数5】（默认3）毫秒，最大可叠加【参数7】（默认1）层</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -2814,7 +2854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:AC101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -10286,7 +10326,7 @@
     </row>
     <row r="87" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A87" s="27">
-        <v>85020300</v>
+        <v>85001500</v>
       </c>
       <c r="B87" s="27">
         <v>7010</v>
@@ -10298,23 +10338,23 @@
         <v>0</v>
       </c>
       <c r="E87" s="27">
-        <v>5020400</v>
+        <v>5001600</v>
       </c>
       <c r="F87" s="27" t="s">
-        <v>592</v>
+        <v>605</v>
       </c>
       <c r="G87" s="13" t="s">
-        <v>593</v>
+        <v>578</v>
       </c>
       <c r="H87" s="27"/>
       <c r="I87" s="27" t="s">
-        <v>594</v>
+        <v>606</v>
       </c>
       <c r="J87" s="27" t="s">
-        <v>595</v>
+        <v>70</v>
       </c>
       <c r="K87" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L87" s="27">
         <v>0</v>
@@ -10341,16 +10381,16 @@
         <v>0</v>
       </c>
       <c r="T87" s="27" t="s">
-        <v>43</v>
+        <v>608</v>
       </c>
       <c r="U87" s="27">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V87" s="27" t="s">
-        <v>43</v>
+        <v>607</v>
       </c>
       <c r="W87" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X87" s="27" t="s">
         <v>43</v>
@@ -10373,7 +10413,7 @@
     </row>
     <row r="88" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A88" s="27">
-        <v>85100100</v>
+        <v>85020300</v>
       </c>
       <c r="B88" s="27">
         <v>7011</v>
@@ -10385,19 +10425,23 @@
         <v>0</v>
       </c>
       <c r="E88" s="27">
-        <v>5100200</v>
+        <v>5020400</v>
       </c>
       <c r="F88" s="27" t="s">
-        <v>540</v>
-      </c>
-      <c r="G88" s="27"/>
+        <v>592</v>
+      </c>
+      <c r="G88" s="13" t="s">
+        <v>593</v>
+      </c>
       <c r="H88" s="27"/>
-      <c r="I88" s="27"/>
+      <c r="I88" s="27" t="s">
+        <v>594</v>
+      </c>
       <c r="J88" s="27" t="s">
-        <v>43</v>
+        <v>595</v>
       </c>
       <c r="K88" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L88" s="27">
         <v>0</v>
@@ -10421,7 +10465,7 @@
         <v>0</v>
       </c>
       <c r="S88" s="28">
-        <v>95100101</v>
+        <v>0</v>
       </c>
       <c r="T88" s="27" t="s">
         <v>43</v>
@@ -10451,12 +10495,12 @@
         <v>1</v>
       </c>
       <c r="AC88" s="27">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A89" s="27">
-        <v>85100300</v>
+        <v>85100100</v>
       </c>
       <c r="B89" s="27">
         <v>7012</v>
@@ -10468,20 +10512,16 @@
         <v>0</v>
       </c>
       <c r="E89" s="27">
-        <v>5100400</v>
+        <v>5100200</v>
       </c>
       <c r="F89" s="27" t="s">
-        <v>574</v>
-      </c>
-      <c r="G89" s="13" t="s">
-        <v>253</v>
-      </c>
+        <v>540</v>
+      </c>
+      <c r="G89" s="27"/>
       <c r="H89" s="27"/>
-      <c r="I89" s="27" t="s">
-        <v>587</v>
-      </c>
+      <c r="I89" s="27"/>
       <c r="J89" s="27" t="s">
-        <v>579</v>
+        <v>43</v>
       </c>
       <c r="K89" s="27">
         <v>1</v>
@@ -10508,7 +10548,7 @@
         <v>0</v>
       </c>
       <c r="S89" s="28">
-        <v>0</v>
+        <v>95100101</v>
       </c>
       <c r="T89" s="27" t="s">
         <v>43</v>
@@ -10538,12 +10578,12 @@
         <v>1</v>
       </c>
       <c r="AC89" s="27">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="90" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A90" s="27">
-        <v>85100500</v>
+        <v>85100300</v>
       </c>
       <c r="B90" s="27">
         <v>7013</v>
@@ -10555,23 +10595,23 @@
         <v>0</v>
       </c>
       <c r="E90" s="27">
-        <v>5100600</v>
+        <v>5100400</v>
       </c>
       <c r="F90" s="27" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="G90" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H90" s="27"/>
       <c r="I90" s="27" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="J90" s="27" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="K90" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L90" s="27">
         <v>0</v>
@@ -10630,7 +10670,7 @@
     </row>
     <row r="91" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A91" s="27">
-        <v>85100700</v>
+        <v>85100500</v>
       </c>
       <c r="B91" s="27">
         <v>7014</v>
@@ -10642,23 +10682,23 @@
         <v>0</v>
       </c>
       <c r="E91" s="27">
-        <v>5100800</v>
+        <v>5100600</v>
       </c>
       <c r="F91" s="27" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="G91" s="13" t="s">
-        <v>549</v>
+        <v>254</v>
       </c>
       <c r="H91" s="27"/>
       <c r="I91" s="27" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="J91" s="27" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="K91" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L91" s="27">
         <v>0</v>
@@ -10717,7 +10757,7 @@
     </row>
     <row r="92" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A92" s="27">
-        <v>85100900</v>
+        <v>85100700</v>
       </c>
       <c r="B92" s="27">
         <v>7015</v>
@@ -10729,20 +10769,20 @@
         <v>0</v>
       </c>
       <c r="E92" s="27">
-        <v>5101000</v>
+        <v>5100800</v>
       </c>
       <c r="F92" s="27" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="G92" s="13" t="s">
-        <v>578</v>
+        <v>549</v>
       </c>
       <c r="H92" s="27"/>
       <c r="I92" s="27" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="J92" s="27" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="K92" s="27">
         <v>1</v>
@@ -10751,13 +10791,13 @@
         <v>0</v>
       </c>
       <c r="M92" s="27" t="s">
-        <v>583</v>
+        <v>43</v>
       </c>
       <c r="N92" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O92" s="27">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="P92" s="27" t="s">
         <v>43</v>
@@ -10804,7 +10844,7 @@
     </row>
     <row r="93" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A93" s="27">
-        <v>85120300</v>
+        <v>85100900</v>
       </c>
       <c r="B93" s="27">
         <v>7016</v>
@@ -10816,35 +10856,35 @@
         <v>0</v>
       </c>
       <c r="E93" s="27">
-        <v>5120400</v>
+        <v>5101000</v>
       </c>
       <c r="F93" s="27" t="s">
-        <v>596</v>
+        <v>577</v>
       </c>
       <c r="G93" s="13" t="s">
-        <v>593</v>
+        <v>578</v>
       </c>
       <c r="H93" s="27"/>
       <c r="I93" s="27" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="J93" s="27" t="s">
-        <v>598</v>
+        <v>582</v>
       </c>
       <c r="K93" s="27">
+        <v>1</v>
+      </c>
+      <c r="L93" s="27">
+        <v>0</v>
+      </c>
+      <c r="M93" s="27" t="s">
+        <v>583</v>
+      </c>
+      <c r="N93" s="27">
         <v>2</v>
       </c>
-      <c r="L93" s="27">
-        <v>0</v>
-      </c>
-      <c r="M93" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="N93" s="27">
-        <v>1</v>
-      </c>
       <c r="O93" s="27">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="P93" s="27" t="s">
         <v>43</v>
@@ -10891,10 +10931,10 @@
     </row>
     <row r="94" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A94" s="27">
-        <v>85200100</v>
+        <v>85101100</v>
       </c>
       <c r="B94" s="27">
-        <v>7017</v>
+        <v>5601</v>
       </c>
       <c r="C94" s="28">
         <v>1</v>
@@ -10903,25 +10943,31 @@
         <v>0</v>
       </c>
       <c r="E94" s="27">
-        <v>5200200</v>
+        <v>5101200</v>
       </c>
       <c r="F94" s="27" t="s">
-        <v>538</v>
-      </c>
-      <c r="G94" s="27"/>
-      <c r="H94" s="27"/>
-      <c r="I94" s="27"/>
+        <v>191</v>
+      </c>
+      <c r="G94" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="H94" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="I94" s="27" t="s">
+        <v>614</v>
+      </c>
       <c r="J94" s="27" t="s">
-        <v>43</v>
+        <v>609</v>
       </c>
       <c r="K94" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L94" s="27">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="M94" s="27" t="s">
-        <v>43</v>
+        <v>610</v>
       </c>
       <c r="N94" s="27">
         <v>1</v>
@@ -10939,16 +10985,16 @@
         <v>0</v>
       </c>
       <c r="S94" s="28">
-        <v>95200101</v>
+        <v>0</v>
       </c>
       <c r="T94" s="27" t="s">
-        <v>43</v>
+        <v>611</v>
       </c>
       <c r="U94" s="27">
-        <v>-1</v>
+        <v>3000</v>
       </c>
       <c r="V94" s="27" t="s">
-        <v>43</v>
+        <v>612</v>
       </c>
       <c r="W94" s="27">
         <v>10000</v>
@@ -10963,21 +11009,21 @@
         <v>1</v>
       </c>
       <c r="AA94" s="27" t="s">
-        <v>43</v>
+        <v>613</v>
       </c>
       <c r="AB94" s="27">
         <v>1</v>
       </c>
       <c r="AC94" s="27">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="95" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A95" s="27">
-        <v>85200300</v>
+        <v>85120300</v>
       </c>
       <c r="B95" s="27">
-        <v>7018</v>
+        <v>7017</v>
       </c>
       <c r="C95" s="28">
         <v>1</v>
@@ -10986,23 +11032,23 @@
         <v>0</v>
       </c>
       <c r="E95" s="27">
-        <v>5200400</v>
+        <v>5120400</v>
       </c>
       <c r="F95" s="27" t="s">
-        <v>547</v>
+        <v>596</v>
       </c>
       <c r="G95" s="13" t="s">
-        <v>549</v>
+        <v>593</v>
       </c>
       <c r="H95" s="27"/>
       <c r="I95" s="27" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="J95" s="27" t="s">
-        <v>550</v>
+        <v>598</v>
       </c>
       <c r="K95" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L95" s="27">
         <v>0</v>
@@ -11061,10 +11107,10 @@
     </row>
     <row r="96" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A96" s="27">
-        <v>85200500</v>
+        <v>85200100</v>
       </c>
       <c r="B96" s="27">
-        <v>7019</v>
+        <v>7018</v>
       </c>
       <c r="C96" s="28">
         <v>1</v>
@@ -11073,23 +11119,19 @@
         <v>0</v>
       </c>
       <c r="E96" s="27">
-        <v>5200600</v>
+        <v>5200200</v>
       </c>
       <c r="F96" s="27" t="s">
-        <v>548</v>
-      </c>
-      <c r="G96" s="13" t="s">
-        <v>254</v>
-      </c>
+        <v>538</v>
+      </c>
+      <c r="G96" s="27"/>
       <c r="H96" s="27"/>
-      <c r="I96" s="27" t="s">
-        <v>589</v>
-      </c>
+      <c r="I96" s="27"/>
       <c r="J96" s="27" t="s">
-        <v>551</v>
+        <v>43</v>
       </c>
       <c r="K96" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L96" s="27">
         <v>0</v>
@@ -11113,7 +11155,7 @@
         <v>0</v>
       </c>
       <c r="S96" s="28">
-        <v>0</v>
+        <v>95200101</v>
       </c>
       <c r="T96" s="27" t="s">
         <v>43</v>
@@ -11143,15 +11185,15 @@
         <v>1</v>
       </c>
       <c r="AC96" s="27">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="97" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A97" s="27">
-        <v>85200700</v>
+        <v>85200300</v>
       </c>
       <c r="B97" s="27">
-        <v>7020</v>
+        <v>7019</v>
       </c>
       <c r="C97" s="28">
         <v>1</v>
@@ -11160,18 +11202,20 @@
         <v>0</v>
       </c>
       <c r="E97" s="27">
-        <v>5200800</v>
+        <v>5200400</v>
       </c>
       <c r="F97" s="27" t="s">
-        <v>571</v>
-      </c>
-      <c r="G97" s="13"/>
+        <v>547</v>
+      </c>
+      <c r="G97" s="13" t="s">
+        <v>549</v>
+      </c>
       <c r="H97" s="27"/>
       <c r="I97" s="27" t="s">
-        <v>570</v>
+        <v>588</v>
       </c>
       <c r="J97" s="27" t="s">
-        <v>70</v>
+        <v>550</v>
       </c>
       <c r="K97" s="27">
         <v>1</v>
@@ -11201,16 +11245,16 @@
         <v>0</v>
       </c>
       <c r="T97" s="27" t="s">
-        <v>573</v>
+        <v>43</v>
       </c>
       <c r="U97" s="27">
-        <v>2000</v>
+        <v>-1</v>
       </c>
       <c r="V97" s="27" t="s">
-        <v>572</v>
+        <v>43</v>
       </c>
       <c r="W97" s="27">
-        <v>7500</v>
+        <v>10000</v>
       </c>
       <c r="X97" s="27" t="s">
         <v>43</v>
@@ -11233,10 +11277,10 @@
     </row>
     <row r="98" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A98" s="27">
-        <v>85220300</v>
+        <v>85200500</v>
       </c>
       <c r="B98" s="27">
-        <v>7022</v>
+        <v>7020</v>
       </c>
       <c r="C98" s="28">
         <v>1</v>
@@ -11245,20 +11289,20 @@
         <v>0</v>
       </c>
       <c r="E98" s="27">
-        <v>5220400</v>
+        <v>5200600</v>
       </c>
       <c r="F98" s="27" t="s">
-        <v>600</v>
+        <v>548</v>
       </c>
       <c r="G98" s="13" t="s">
-        <v>593</v>
+        <v>254</v>
       </c>
       <c r="H98" s="27"/>
       <c r="I98" s="27" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="J98" s="27" t="s">
-        <v>599</v>
+        <v>551</v>
       </c>
       <c r="K98" s="27">
         <v>2</v>
@@ -11320,10 +11364,10 @@
     </row>
     <row r="99" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A99" s="27">
-        <v>87000100</v>
+        <v>85200700</v>
       </c>
       <c r="B99" s="27">
-        <v>7023</v>
+        <v>7021</v>
       </c>
       <c r="C99" s="28">
         <v>1</v>
@@ -11332,76 +11376,250 @@
         <v>0</v>
       </c>
       <c r="E99" s="27">
-        <v>7000200</v>
+        <v>5200800</v>
       </c>
       <c r="F99" s="27" t="s">
-        <v>604</v>
+        <v>571</v>
       </c>
       <c r="G99" s="13" t="s">
-        <v>254</v>
+        <v>578</v>
       </c>
       <c r="H99" s="27"/>
       <c r="I99" s="27" t="s">
+        <v>570</v>
+      </c>
+      <c r="J99" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="K99" s="27">
+        <v>1</v>
+      </c>
+      <c r="L99" s="27">
+        <v>0</v>
+      </c>
+      <c r="M99" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N99" s="27">
+        <v>1</v>
+      </c>
+      <c r="O99" s="27">
+        <v>0</v>
+      </c>
+      <c r="P99" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q99" s="27">
+        <v>1</v>
+      </c>
+      <c r="R99" s="27">
+        <v>0</v>
+      </c>
+      <c r="S99" s="28">
+        <v>0</v>
+      </c>
+      <c r="T99" s="27" t="s">
+        <v>573</v>
+      </c>
+      <c r="U99" s="27">
+        <v>0</v>
+      </c>
+      <c r="V99" s="27" t="s">
+        <v>572</v>
+      </c>
+      <c r="W99" s="27">
+        <v>0</v>
+      </c>
+      <c r="X99" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y99" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z99" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA99" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB99" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC99" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A100" s="27">
+        <v>85220300</v>
+      </c>
+      <c r="B100" s="27">
+        <v>7022</v>
+      </c>
+      <c r="C100" s="28">
+        <v>1</v>
+      </c>
+      <c r="D100" s="28">
+        <v>0</v>
+      </c>
+      <c r="E100" s="27">
+        <v>5220400</v>
+      </c>
+      <c r="F100" s="27" t="s">
+        <v>600</v>
+      </c>
+      <c r="G100" s="13" t="s">
+        <v>593</v>
+      </c>
+      <c r="H100" s="27"/>
+      <c r="I100" s="27" t="s">
+        <v>601</v>
+      </c>
+      <c r="J100" s="27" t="s">
+        <v>599</v>
+      </c>
+      <c r="K100" s="27">
+        <v>2</v>
+      </c>
+      <c r="L100" s="27">
+        <v>0</v>
+      </c>
+      <c r="M100" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N100" s="27">
+        <v>1</v>
+      </c>
+      <c r="O100" s="27">
+        <v>0</v>
+      </c>
+      <c r="P100" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q100" s="27">
+        <v>1</v>
+      </c>
+      <c r="R100" s="27">
+        <v>0</v>
+      </c>
+      <c r="S100" s="28">
+        <v>0</v>
+      </c>
+      <c r="T100" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U100" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V100" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W100" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X100" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y100" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z100" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA100" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB100" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC100" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A101" s="27">
+        <v>87000100</v>
+      </c>
+      <c r="B101" s="27">
+        <v>7023</v>
+      </c>
+      <c r="C101" s="28">
+        <v>1</v>
+      </c>
+      <c r="D101" s="28">
+        <v>0</v>
+      </c>
+      <c r="E101" s="27">
+        <v>7000200</v>
+      </c>
+      <c r="F101" s="27" t="s">
+        <v>604</v>
+      </c>
+      <c r="G101" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="H101" s="27"/>
+      <c r="I101" s="27" t="s">
         <v>603</v>
       </c>
-      <c r="J99" s="27" t="s">
+      <c r="J101" s="27" t="s">
         <v>602</v>
       </c>
-      <c r="K99" s="27">
+      <c r="K101" s="27">
         <v>2</v>
       </c>
-      <c r="L99" s="27">
-        <v>0</v>
-      </c>
-      <c r="M99" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="N99" s="27">
-        <v>1</v>
-      </c>
-      <c r="O99" s="27">
-        <v>0</v>
-      </c>
-      <c r="P99" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q99" s="27">
-        <v>1</v>
-      </c>
-      <c r="R99" s="27">
-        <v>0</v>
-      </c>
-      <c r="S99" s="28">
-        <v>0</v>
-      </c>
-      <c r="T99" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="U99" s="27">
+      <c r="L101" s="27">
+        <v>0</v>
+      </c>
+      <c r="M101" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N101" s="27">
+        <v>1</v>
+      </c>
+      <c r="O101" s="27">
+        <v>0</v>
+      </c>
+      <c r="P101" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q101" s="27">
+        <v>1</v>
+      </c>
+      <c r="R101" s="27">
+        <v>0</v>
+      </c>
+      <c r="S101" s="28">
+        <v>0</v>
+      </c>
+      <c r="T101" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U101" s="27">
         <v>-1</v>
       </c>
-      <c r="V99" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="W99" s="27">
+      <c r="V101" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W101" s="27">
         <v>10000</v>
       </c>
-      <c r="X99" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y99" s="27">
-        <v>1</v>
-      </c>
-      <c r="Z99" s="27">
-        <v>1</v>
-      </c>
-      <c r="AA99" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB99" s="27">
-        <v>1</v>
-      </c>
-      <c r="AC99" s="27">
+      <c r="X101" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y101" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z101" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA101" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB101" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC101" s="27">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC69D2CD-6CF5-4D0A-B824-4DD253E881F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC4C66D-06EF-4462-B320-59527651275E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="616">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2103,10 +2103,6 @@
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
-    <t>【参数1】陨石额外范围（半径）</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
     <t>【参数1】雷击目标数量</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
@@ -2211,6 +2207,14 @@
   </si>
   <si>
     <t>每【参数8】（默认1000）毫秒，造成{[攻击直接伤害+火元素直接伤害]【参数1万分比】（默认30%）}，【参数2】（默认0）的[额外火元素持续伤害]，效果持续【参数5】（默认3）毫秒，最大可叠加【参数7】（默认1）层</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数1】陨石额外范围（半径）,【参数2】陨石特效放大万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5100302:1</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -10261,7 +10265,7 @@
       </c>
       <c r="H86" s="27"/>
       <c r="I86" s="27" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="J86" s="27" t="s">
         <v>43</v>
@@ -10341,14 +10345,14 @@
         <v>5001600</v>
       </c>
       <c r="F87" s="27" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G87" s="13" t="s">
         <v>578</v>
       </c>
       <c r="H87" s="27"/>
       <c r="I87" s="27" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="J87" s="27" t="s">
         <v>70</v>
@@ -10381,13 +10385,13 @@
         <v>0</v>
       </c>
       <c r="T87" s="27" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="U87" s="27">
         <v>0</v>
       </c>
       <c r="V87" s="27" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="W87" s="27">
         <v>0</v>
@@ -10428,17 +10432,17 @@
         <v>5020400</v>
       </c>
       <c r="F88" s="27" t="s">
+        <v>591</v>
+      </c>
+      <c r="G88" s="13" t="s">
         <v>592</v>
-      </c>
-      <c r="G88" s="13" t="s">
-        <v>593</v>
       </c>
       <c r="H88" s="27"/>
       <c r="I88" s="27" t="s">
+        <v>593</v>
+      </c>
+      <c r="J88" s="27" t="s">
         <v>594</v>
-      </c>
-      <c r="J88" s="27" t="s">
-        <v>595</v>
       </c>
       <c r="K88" s="27">
         <v>2</v>
@@ -10605,7 +10609,7 @@
       </c>
       <c r="H90" s="27"/>
       <c r="I90" s="27" t="s">
-        <v>587</v>
+        <v>614</v>
       </c>
       <c r="J90" s="27" t="s">
         <v>579</v>
@@ -10617,10 +10621,10 @@
         <v>0</v>
       </c>
       <c r="M90" s="27" t="s">
-        <v>43</v>
+        <v>615</v>
       </c>
       <c r="N90" s="27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O90" s="27">
         <v>0</v>
@@ -10866,7 +10870,7 @@
       </c>
       <c r="H93" s="27"/>
       <c r="I93" s="27" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J93" s="27" t="s">
         <v>582</v>
@@ -10955,10 +10959,10 @@
         <v>191</v>
       </c>
       <c r="I94" s="27" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="J94" s="27" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K94" s="27">
         <v>2</v>
@@ -10967,34 +10971,34 @@
         <v>3000</v>
       </c>
       <c r="M94" s="27" t="s">
+        <v>609</v>
+      </c>
+      <c r="N94" s="27">
+        <v>1</v>
+      </c>
+      <c r="O94" s="27">
+        <v>0</v>
+      </c>
+      <c r="P94" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q94" s="27">
+        <v>1</v>
+      </c>
+      <c r="R94" s="27">
+        <v>0</v>
+      </c>
+      <c r="S94" s="28">
+        <v>0</v>
+      </c>
+      <c r="T94" s="27" t="s">
         <v>610</v>
-      </c>
-      <c r="N94" s="27">
-        <v>1</v>
-      </c>
-      <c r="O94" s="27">
-        <v>0</v>
-      </c>
-      <c r="P94" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q94" s="27">
-        <v>1</v>
-      </c>
-      <c r="R94" s="27">
-        <v>0</v>
-      </c>
-      <c r="S94" s="28">
-        <v>0</v>
-      </c>
-      <c r="T94" s="27" t="s">
-        <v>611</v>
       </c>
       <c r="U94" s="27">
         <v>3000</v>
       </c>
       <c r="V94" s="27" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="W94" s="27">
         <v>10000</v>
@@ -11009,7 +11013,7 @@
         <v>1</v>
       </c>
       <c r="AA94" s="27" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AB94" s="27">
         <v>1</v>
@@ -11035,17 +11039,17 @@
         <v>5120400</v>
       </c>
       <c r="F95" s="27" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G95" s="13" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H95" s="27"/>
       <c r="I95" s="27" t="s">
+        <v>596</v>
+      </c>
+      <c r="J95" s="27" t="s">
         <v>597</v>
-      </c>
-      <c r="J95" s="27" t="s">
-        <v>598</v>
       </c>
       <c r="K95" s="27">
         <v>2</v>
@@ -11212,7 +11216,7 @@
       </c>
       <c r="H97" s="27"/>
       <c r="I97" s="27" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="J97" s="27" t="s">
         <v>550</v>
@@ -11299,7 +11303,7 @@
       </c>
       <c r="H98" s="27"/>
       <c r="I98" s="27" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="J98" s="27" t="s">
         <v>551</v>
@@ -11466,17 +11470,17 @@
         <v>5220400</v>
       </c>
       <c r="F100" s="27" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G100" s="13" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H100" s="27"/>
       <c r="I100" s="27" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J100" s="27" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="K100" s="27">
         <v>2</v>
@@ -11553,17 +11557,17 @@
         <v>7000200</v>
       </c>
       <c r="F101" s="27" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G101" s="13" t="s">
         <v>254</v>
       </c>
       <c r="H101" s="27"/>
       <c r="I101" s="27" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="J101" s="27" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K101" s="27">
         <v>2</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC4C66D-06EF-4462-B320-59527651275E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E0E5A3-B23D-4274-968C-80CB2DFD8D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10118,7 +10118,7 @@
         <v>1</v>
       </c>
       <c r="R84" s="27">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="S84" s="28">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E0E5A3-B23D-4274-968C-80CB2DFD8D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD91194E-BDF2-4409-95B1-89923D0E91EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -3499,7 +3499,7 @@
         <v>1</v>
       </c>
       <c r="O8" s="15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P8" s="15" t="s">
         <v>43</v>
@@ -3588,7 +3588,7 @@
         <v>1</v>
       </c>
       <c r="O9" s="15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P9" s="15" t="s">
         <v>43</v>
@@ -3677,7 +3677,7 @@
         <v>1</v>
       </c>
       <c r="O10" s="15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P10" s="15" t="s">
         <v>43</v>
@@ -3766,7 +3766,7 @@
         <v>1</v>
       </c>
       <c r="O11" s="15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P11" s="15" t="s">
         <v>43</v>
@@ -4033,7 +4033,7 @@
         <v>1</v>
       </c>
       <c r="O14" s="15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P14" s="15" t="s">
         <v>43</v>
@@ -4122,7 +4122,7 @@
         <v>1</v>
       </c>
       <c r="O15" s="15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P15" s="15" t="s">
         <v>43</v>
@@ -4211,7 +4211,7 @@
         <v>1</v>
       </c>
       <c r="O16" s="15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P16" s="15" t="s">
         <v>43</v>
@@ -4300,7 +4300,7 @@
         <v>1</v>
       </c>
       <c r="O17" s="15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P17" s="15" t="s">
         <v>43</v>
@@ -11628,7 +11628,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AC77" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD91194E-BDF2-4409-95B1-89923D0E91EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F9FD415-0770-4CA9-8180-D1AED8B07CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10118,7 +10118,7 @@
         <v>1</v>
       </c>
       <c r="R84" s="27">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="S84" s="28">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F9FD415-0770-4CA9-8180-D1AED8B07CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB153C14-2A2C-4820-9B41-19282C0EE019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3428,7 +3428,7 @@
         <v>127</v>
       </c>
       <c r="U7" s="15">
-        <v>1800000</v>
+        <v>7200000</v>
       </c>
       <c r="V7" s="15" t="s">
         <v>43</v>
@@ -3517,7 +3517,7 @@
         <v>129</v>
       </c>
       <c r="U8" s="15">
-        <v>1800000</v>
+        <v>7200000</v>
       </c>
       <c r="V8" s="15" t="s">
         <v>43</v>
@@ -3606,7 +3606,7 @@
         <v>131</v>
       </c>
       <c r="U9" s="15">
-        <v>1800000</v>
+        <v>7200000</v>
       </c>
       <c r="V9" s="15" t="s">
         <v>43</v>
@@ -3695,7 +3695,7 @@
         <v>133</v>
       </c>
       <c r="U10" s="15">
-        <v>1800000</v>
+        <v>7200000</v>
       </c>
       <c r="V10" s="15" t="s">
         <v>43</v>
@@ -3873,7 +3873,7 @@
         <v>137</v>
       </c>
       <c r="U12" s="15">
-        <v>1800000</v>
+        <v>7200000</v>
       </c>
       <c r="V12" s="15" t="s">
         <v>43</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB153C14-2A2C-4820-9B41-19282C0EE019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23C82E54-80F6-452D-9DCC-7F9F8E95F6AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -10118,7 +10118,7 @@
         <v>1</v>
       </c>
       <c r="R84" s="27">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="S84" s="28">
         <v>0</v>
@@ -10283,7 +10283,7 @@
         <v>2</v>
       </c>
       <c r="O86" s="27">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="P86" s="27" t="s">
         <v>43</v>
@@ -10888,7 +10888,7 @@
         <v>2</v>
       </c>
       <c r="O93" s="27">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="P93" s="27" t="s">
         <v>43</v>
@@ -10968,7 +10968,7 @@
         <v>2</v>
       </c>
       <c r="L94" s="27">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="M94" s="27" t="s">
         <v>609</v>
@@ -10995,7 +10995,7 @@
         <v>610</v>
       </c>
       <c r="U94" s="27">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="V94" s="27" t="s">
         <v>611</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23C82E54-80F6-452D-9DCC-7F9F8E95F6AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D65E31F-5F77-4E54-A89D-19698567FE0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2206,15 +2206,15 @@
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
-    <t>每【参数8】（默认1000）毫秒，造成{[攻击直接伤害+火元素直接伤害]【参数1万分比】（默认30%）}，【参数2】（默认0）的[额外火元素持续伤害]，效果持续【参数5】（默认3）毫秒，最大可叠加【参数7】（默认1）层</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
     <t>【参数1】陨石额外范围（半径）,【参数2】陨石特效放大万分比</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>5100302:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>每【参数8】（默认1000）毫秒，造成{[火元素直接伤害]【参数1万分比】（默认30%）}，【参数2】（默认0）的[额外火元素持续伤害]，效果持续【参数5】（默认3）毫秒，最大可叠加【参数7】（默认1）层</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -10609,7 +10609,7 @@
       </c>
       <c r="H90" s="27"/>
       <c r="I90" s="27" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="J90" s="27" t="s">
         <v>579</v>
@@ -10621,7 +10621,7 @@
         <v>0</v>
       </c>
       <c r="M90" s="27" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="N90" s="27">
         <v>2</v>
@@ -10959,7 +10959,7 @@
         <v>191</v>
       </c>
       <c r="I94" s="27" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="J94" s="27" t="s">
         <v>608</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D65E31F-5F77-4E54-A89D-19698567FE0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E644769-2513-4AA1-BC09-AF2E4671AE83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2214,7 +2214,7 @@
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
-    <t>每【参数8】（默认1000）毫秒，造成{[火元素直接伤害]【参数1万分比】（默认30%）}，【参数2】（默认0）的[额外火元素持续伤害]，效果持续【参数5】（默认3）毫秒，最大可叠加【参数7】（默认1）层</t>
+    <t>每【参数8】（默认1000）毫秒，造成{[火元素直接伤害]【参数1万分比】（默认0%）}，【参数2】（默认0）的[额外火元素持续伤害]，效果持续【参数5】（默认3）毫秒，最大可叠加【参数7】（默认1）层</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E644769-2513-4AA1-BC09-AF2E4671AE83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A11BE2-E1AE-492A-90EE-643BD3432365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -10333,7 +10333,7 @@
         <v>85001500</v>
       </c>
       <c r="B87" s="27">
-        <v>7010</v>
+        <v>5501</v>
       </c>
       <c r="C87" s="28">
         <v>1</v>
@@ -11371,7 +11371,7 @@
         <v>85200700</v>
       </c>
       <c r="B99" s="27">
-        <v>7021</v>
+        <v>5701</v>
       </c>
       <c r="C99" s="28">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltx\Desktop\高宁剑\【地宫】正式内容\分支表格\新技能配置\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A11BE2-E1AE-492A-90EE-643BD3432365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{099934CD-E0B8-4228-8CF1-56671BFD9AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1697" uniqueCount="677">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2215,6 +2215,197 @@
   </si>
   <si>
     <t>每【参数8】（默认1000）毫秒，造成{[火元素直接伤害]【参数1万分比】（默认0%）}，【参数2】（默认0）的[额外火元素持续伤害]，效果持续【参数5】（默认3）毫秒，最大可叠加【参数7】（默认1）层</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改属性关联变量id</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改属性数值类型</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改属性影响属性id</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改属性影响数值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>modify_attr_value_variable_id</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>modify_attr_value_type</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>modify_attr_value_attr_id</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3540401:2</t>
+  </si>
+  <si>
+    <t>3041101:1</t>
+  </si>
+  <si>
+    <t>3540201:1</t>
+  </si>
+  <si>
+    <t>3542601:1</t>
+  </si>
+  <si>
+    <t>3542801:1</t>
+  </si>
+  <si>
+    <t>3543001:1</t>
+  </si>
+  <si>
+    <t>3540401:3010101</t>
+  </si>
+  <si>
+    <t>3041101:2</t>
+  </si>
+  <si>
+    <t>3540201:2</t>
+  </si>
+  <si>
+    <t>3540601:2</t>
+  </si>
+  <si>
+    <t>3540801:2</t>
+  </si>
+  <si>
+    <t>3541001:2</t>
+  </si>
+  <si>
+    <t>3541201:2</t>
+  </si>
+  <si>
+    <t>3541401:2</t>
+  </si>
+  <si>
+    <t>3541601:2</t>
+  </si>
+  <si>
+    <t>3541801:2</t>
+  </si>
+  <si>
+    <t>3542001:2</t>
+  </si>
+  <si>
+    <t>3542201:2</t>
+  </si>
+  <si>
+    <t>3542401:2</t>
+  </si>
+  <si>
+    <t>3542601:2</t>
+  </si>
+  <si>
+    <t>3542801:2</t>
+  </si>
+  <si>
+    <t>3543001:2</t>
+  </si>
+  <si>
+    <t>3041101:3010101</t>
+  </si>
+  <si>
+    <t>3540201:3010101</t>
+  </si>
+  <si>
+    <t>3540601:3010101</t>
+  </si>
+  <si>
+    <t>3540801:3010101</t>
+  </si>
+  <si>
+    <t>3541001:3010101</t>
+  </si>
+  <si>
+    <t>3541201:3010101</t>
+  </si>
+  <si>
+    <t>3541401:3010101</t>
+  </si>
+  <si>
+    <t>3541601:3010101</t>
+  </si>
+  <si>
+    <t>3541801:3010101</t>
+  </si>
+  <si>
+    <t>3542001:3010101</t>
+  </si>
+  <si>
+    <t>3542201:3010101</t>
+  </si>
+  <si>
+    <t>3542401:3010101</t>
+  </si>
+  <si>
+    <t>3542601:3010101</t>
+  </si>
+  <si>
+    <t>3542801:3010101</t>
+  </si>
+  <si>
+    <t>3543001:3010101</t>
+  </si>
+  <si>
+    <t>3041101:2000</t>
+  </si>
+  <si>
+    <t>3540201:2000</t>
+  </si>
+  <si>
+    <t>3540401:2000</t>
+  </si>
+  <si>
+    <t>3540601:2000</t>
+  </si>
+  <si>
+    <t>3540801:2000</t>
+  </si>
+  <si>
+    <t>3541001:2000</t>
+  </si>
+  <si>
+    <t>3541201:2000</t>
+  </si>
+  <si>
+    <t>3541401:2000</t>
+  </si>
+  <si>
+    <t>3541601:2000</t>
+  </si>
+  <si>
+    <t>3541801:2000</t>
+  </si>
+  <si>
+    <t>3542001:2000</t>
+  </si>
+  <si>
+    <t>3542201:2000</t>
+  </si>
+  <si>
+    <t>3542401:2000</t>
+  </si>
+  <si>
+    <t>3542601:2000</t>
+  </si>
+  <si>
+    <t>3542801:2000</t>
+  </si>
+  <si>
+    <t>3543001:2000</t>
+  </si>
+  <si>
+    <t>modify_attr_value</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -2518,7 +2709,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2558,6 +2749,12 @@
     <xf numFmtId="3" fontId="3" fillId="3" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="差" xfId="4" builtinId="27"/>
@@ -2858,7 +3055,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC101"/>
+  <dimension ref="A1:AG101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -2884,9 +3081,13 @@
     <col min="27" max="27" width="23.875" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="17.125" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="28.75" style="30" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="21.875" style="30" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="24.875" style="30" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.125" style="30" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2921,7 +3122,7 @@
       <c r="AB1" s="3"/>
       <c r="AC1" s="3"/>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -3009,8 +3210,20 @@
       <c r="AC2" s="7" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD2" s="29" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE2" s="29" t="s">
+        <v>324</v>
+      </c>
+      <c r="AF2" s="29" t="s">
+        <v>324</v>
+      </c>
+      <c r="AG2" s="29" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -3098,8 +3311,20 @@
       <c r="AC3" s="7" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD3" s="29" t="s">
+        <v>620</v>
+      </c>
+      <c r="AE3" s="29" t="s">
+        <v>621</v>
+      </c>
+      <c r="AF3" s="29" t="s">
+        <v>622</v>
+      </c>
+      <c r="AG3" s="29" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>26</v>
       </c>
@@ -3187,8 +3412,20 @@
       <c r="AC4" s="7" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD4" s="29" t="s">
+        <v>616</v>
+      </c>
+      <c r="AE4" s="29" t="s">
+        <v>617</v>
+      </c>
+      <c r="AF4" s="29" t="s">
+        <v>618</v>
+      </c>
+      <c r="AG4" s="29" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>1000001</v>
       </c>
@@ -3276,8 +3513,20 @@
       <c r="AC5" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD5" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE5" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF5" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG5" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>2000001</v>
       </c>
@@ -3365,8 +3614,20 @@
       <c r="AC6" s="6">
         <v>1000</v>
       </c>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD6" s="15" t="s">
+        <v>624</v>
+      </c>
+      <c r="AE6" s="15" t="s">
+        <v>630</v>
+      </c>
+      <c r="AF6" s="15" t="s">
+        <v>645</v>
+      </c>
+      <c r="AG6" s="15" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A7" s="15">
         <v>54010001</v>
       </c>
@@ -3454,8 +3715,20 @@
       <c r="AC7" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="15" t="s">
+        <v>625</v>
+      </c>
+      <c r="AE7" s="15" t="s">
+        <v>631</v>
+      </c>
+      <c r="AF7" s="15" t="s">
+        <v>646</v>
+      </c>
+      <c r="AG7" s="15" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A8" s="15">
         <v>54020001</v>
       </c>
@@ -3543,8 +3816,20 @@
       <c r="AC8" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="AE8" s="15" t="s">
+        <v>623</v>
+      </c>
+      <c r="AF8" s="15" t="s">
+        <v>629</v>
+      </c>
+      <c r="AG8" s="15" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A9" s="15">
         <v>54030001</v>
       </c>
@@ -3632,8 +3917,20 @@
       <c r="AC9" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE9" s="15" t="s">
+        <v>632</v>
+      </c>
+      <c r="AF9" s="15" t="s">
+        <v>647</v>
+      </c>
+      <c r="AG9" s="15" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A10" s="15">
         <v>54040001</v>
       </c>
@@ -3721,8 +4018,20 @@
       <c r="AC10" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="AE10" s="15" t="s">
+        <v>633</v>
+      </c>
+      <c r="AF10" s="15" t="s">
+        <v>648</v>
+      </c>
+      <c r="AG10" s="15" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A11" s="15">
         <v>54050001</v>
       </c>
@@ -3810,8 +4119,20 @@
       <c r="AC11" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="AE11" s="15" t="s">
+        <v>634</v>
+      </c>
+      <c r="AF11" s="15" t="s">
+        <v>649</v>
+      </c>
+      <c r="AG11" s="15" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A12" s="15">
         <v>54060001</v>
       </c>
@@ -3899,8 +4220,20 @@
       <c r="AC12" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE12" s="15" t="s">
+        <v>635</v>
+      </c>
+      <c r="AF12" s="15" t="s">
+        <v>650</v>
+      </c>
+      <c r="AG12" s="15" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A13" s="15">
         <v>54070001</v>
       </c>
@@ -3988,8 +4321,20 @@
       <c r="AC13" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="AE13" s="15" t="s">
+        <v>636</v>
+      </c>
+      <c r="AF13" s="15" t="s">
+        <v>651</v>
+      </c>
+      <c r="AG13" s="15" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A14" s="15">
         <v>54080001</v>
       </c>
@@ -4077,8 +4422,20 @@
       <c r="AC14" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="AE14" s="15" t="s">
+        <v>637</v>
+      </c>
+      <c r="AF14" s="15" t="s">
+        <v>652</v>
+      </c>
+      <c r="AG14" s="15" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A15" s="15">
         <v>54090001</v>
       </c>
@@ -4166,8 +4523,20 @@
       <c r="AC15" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="AE15" s="15" t="s">
+        <v>638</v>
+      </c>
+      <c r="AF15" s="15" t="s">
+        <v>653</v>
+      </c>
+      <c r="AG15" s="15" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A16" s="15">
         <v>54100001</v>
       </c>
@@ -4255,8 +4624,20 @@
       <c r="AC16" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="AE16" s="15" t="s">
+        <v>639</v>
+      </c>
+      <c r="AF16" s="15" t="s">
+        <v>654</v>
+      </c>
+      <c r="AG16" s="15" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A17" s="15">
         <v>54110001</v>
       </c>
@@ -4344,8 +4725,20 @@
       <c r="AC17" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="AE17" s="15" t="s">
+        <v>640</v>
+      </c>
+      <c r="AF17" s="15" t="s">
+        <v>655</v>
+      </c>
+      <c r="AG17" s="15" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A18" s="15">
         <v>54120001</v>
       </c>
@@ -4433,8 +4826,20 @@
       <c r="AC18" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="AE18" s="15" t="s">
+        <v>641</v>
+      </c>
+      <c r="AF18" s="15" t="s">
+        <v>656</v>
+      </c>
+      <c r="AG18" s="15" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A19" s="15">
         <v>54130001</v>
       </c>
@@ -4522,8 +4927,20 @@
       <c r="AC19" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="15" t="s">
+        <v>626</v>
+      </c>
+      <c r="AE19" s="15" t="s">
+        <v>642</v>
+      </c>
+      <c r="AF19" s="15" t="s">
+        <v>657</v>
+      </c>
+      <c r="AG19" s="15" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A20" s="15">
         <v>54140001</v>
       </c>
@@ -4611,8 +5028,20 @@
       <c r="AC20" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="15" t="s">
+        <v>627</v>
+      </c>
+      <c r="AE20" s="15" t="s">
+        <v>643</v>
+      </c>
+      <c r="AF20" s="15" t="s">
+        <v>658</v>
+      </c>
+      <c r="AG20" s="15" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A21" s="15">
         <v>54150001</v>
       </c>
@@ -4700,8 +5129,20 @@
       <c r="AC21" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="15" t="s">
+        <v>628</v>
+      </c>
+      <c r="AE21" s="15" t="s">
+        <v>644</v>
+      </c>
+      <c r="AF21" s="15" t="s">
+        <v>659</v>
+      </c>
+      <c r="AG21" s="15" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A22" s="17">
         <v>55010001</v>
       </c>
@@ -4789,8 +5230,20 @@
       <c r="AC22" s="17">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE22" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF22" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG22" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A23" s="17">
         <v>55020001</v>
       </c>
@@ -4878,8 +5331,20 @@
       <c r="AC23" s="17">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE23" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF23" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG23" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A24" s="17">
         <v>55030001</v>
       </c>
@@ -4967,8 +5432,20 @@
       <c r="AC24" s="17">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE24" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF24" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG24" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A25" s="17">
         <v>55040001</v>
       </c>
@@ -5056,8 +5533,20 @@
       <c r="AC25" s="17">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE25" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF25" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG25" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A26" s="17">
         <v>55050001</v>
       </c>
@@ -5145,8 +5634,20 @@
       <c r="AC26" s="17">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE26" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF26" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG26" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A27" s="17">
         <v>55060001</v>
       </c>
@@ -5234,8 +5735,20 @@
       <c r="AC27" s="17">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE27" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF27" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG27" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A28" s="17">
         <v>55070001</v>
       </c>
@@ -5323,8 +5836,20 @@
       <c r="AC28" s="17">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE28" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF28" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG28" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A29" s="18">
         <v>56010001</v>
       </c>
@@ -5412,8 +5937,20 @@
       <c r="AC29" s="18">
         <v>1000</v>
       </c>
-    </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE29" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF29" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG29" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A30" s="18">
         <v>56020001</v>
       </c>
@@ -5501,8 +6038,20 @@
       <c r="AC30" s="18">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE30" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF30" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG30" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A31" s="18">
         <v>56030001</v>
       </c>
@@ -5590,8 +6139,20 @@
       <c r="AC31" s="18">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE31" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF31" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG31" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A32" s="18">
         <v>56040001</v>
       </c>
@@ -5679,8 +6240,20 @@
       <c r="AC32" s="18">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE32" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF32" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG32" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A33" s="18">
         <v>56050001</v>
       </c>
@@ -5768,8 +6341,20 @@
       <c r="AC33" s="18">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE33" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF33" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG33" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A34" s="18">
         <v>56060001</v>
       </c>
@@ -5857,8 +6442,20 @@
       <c r="AC34" s="18">
         <v>1000</v>
       </c>
-    </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE34" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF34" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG34" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A35" s="19">
         <v>57010001</v>
       </c>
@@ -5946,8 +6543,20 @@
       <c r="AC35" s="19">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE35" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF35" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG35" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A36" s="19">
         <v>57020001</v>
       </c>
@@ -6035,8 +6644,20 @@
       <c r="AC36" s="19">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD36" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE36" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF36" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG36" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A37" s="19">
         <v>57030001</v>
       </c>
@@ -6124,8 +6745,20 @@
       <c r="AC37" s="19">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD37" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE37" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF37" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG37" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A38" s="19">
         <v>57040001</v>
       </c>
@@ -6213,8 +6846,20 @@
       <c r="AC38" s="19">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE38" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF38" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG38" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A39" s="19">
         <v>57050001</v>
       </c>
@@ -6302,8 +6947,20 @@
       <c r="AC39" s="19">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE39" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF39" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG39" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="40" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A40" s="19">
         <v>57060001</v>
       </c>
@@ -6391,8 +7048,20 @@
       <c r="AC40" s="19">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE40" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF40" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG40" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A41" s="20">
         <v>58010001</v>
       </c>
@@ -6480,8 +7149,20 @@
       <c r="AC41" s="20">
         <v>1000</v>
       </c>
-    </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE41" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF41" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG41" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A42" s="20">
         <v>58020001</v>
       </c>
@@ -6569,8 +7250,20 @@
       <c r="AC42" s="20">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE42" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF42" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG42" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A43" s="20">
         <v>58030001</v>
       </c>
@@ -6658,8 +7351,20 @@
       <c r="AC43" s="20">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE43" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF43" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG43" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A44" s="20">
         <v>58040001</v>
       </c>
@@ -6747,8 +7452,20 @@
       <c r="AC44" s="20">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE44" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF44" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG44" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A45" s="23">
         <v>58050001</v>
       </c>
@@ -6836,8 +7553,20 @@
       <c r="AC45" s="20">
         <v>1000</v>
       </c>
-    </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE45" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF45" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG45" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A46" s="24">
         <v>59010001</v>
       </c>
@@ -6921,8 +7650,20 @@
       <c r="AC46" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE46" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF46" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG46" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="47" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A47" s="24">
         <v>59020001</v>
       </c>
@@ -7006,8 +7747,20 @@
       <c r="AC47" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE47" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF47" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG47" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="48" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A48" s="24">
         <v>59030001</v>
       </c>
@@ -7091,8 +7844,20 @@
       <c r="AC48" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE48" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF48" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG48" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A49" s="24">
         <v>59040001</v>
       </c>
@@ -7176,8 +7941,20 @@
       <c r="AC49" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE49" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF49" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG49" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="50" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A50" s="24">
         <v>59050001</v>
       </c>
@@ -7261,8 +8038,20 @@
       <c r="AC50" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE50" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF50" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG50" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="51" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A51" s="24">
         <v>59060001</v>
       </c>
@@ -7346,8 +8135,20 @@
       <c r="AC51" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE51" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF51" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG51" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="52" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A52" s="24">
         <v>59070001</v>
       </c>
@@ -7431,8 +8232,20 @@
       <c r="AC52" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE52" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF52" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG52" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="53" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A53" s="24">
         <v>59080001</v>
       </c>
@@ -7516,8 +8329,20 @@
       <c r="AC53" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE53" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF53" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG53" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="54" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A54" s="24">
         <v>59090001</v>
       </c>
@@ -7601,8 +8426,20 @@
       <c r="AC54" s="24">
         <v>1000</v>
       </c>
-    </row>
-    <row r="55" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE54" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF54" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG54" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="55" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A55" s="24">
         <v>59100001</v>
       </c>
@@ -7686,8 +8523,20 @@
       <c r="AC55" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE55" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF55" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG55" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="56" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A56" s="24">
         <v>59110001</v>
       </c>
@@ -7771,8 +8620,20 @@
       <c r="AC56" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE56" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF56" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG56" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="57" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A57" s="25">
         <v>59120001</v>
       </c>
@@ -7856,8 +8717,20 @@
       <c r="AC57" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE57" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF57" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG57" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="58" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A58" s="25">
         <v>59130001</v>
       </c>
@@ -7941,8 +8814,20 @@
       <c r="AC58" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE58" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF58" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG58" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="59" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A59" s="25">
         <v>59140001</v>
       </c>
@@ -8026,8 +8911,20 @@
       <c r="AC59" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE59" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF59" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG59" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="60" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A60" s="21">
         <v>60010001</v>
       </c>
@@ -8111,8 +9008,20 @@
       <c r="AC60" s="21">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE60" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF60" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG60" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="61" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A61" s="21">
         <v>60020001</v>
       </c>
@@ -8196,8 +9105,20 @@
       <c r="AC61" s="21">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE61" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF61" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG61" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="62" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A62" s="21">
         <v>60030001</v>
       </c>
@@ -8281,8 +9202,20 @@
       <c r="AC62" s="21">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE62" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF62" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG62" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="63" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A63" s="21">
         <v>60040001</v>
       </c>
@@ -8366,8 +9299,20 @@
       <c r="AC63" s="21">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE63" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF63" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG63" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="64" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A64" s="21">
         <v>60050001</v>
       </c>
@@ -8451,8 +9396,20 @@
       <c r="AC64" s="21">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE64" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF64" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG64" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="65" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A65" s="21">
         <v>60060001</v>
       </c>
@@ -8536,8 +9493,20 @@
       <c r="AC65" s="21">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE65" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF65" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG65" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="66" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A66" s="21">
         <v>60070001</v>
       </c>
@@ -8621,8 +9590,20 @@
       <c r="AC66" s="21">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE66" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF66" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG66" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="67" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A67" s="21">
         <v>60080001</v>
       </c>
@@ -8706,8 +9687,20 @@
       <c r="AC67" s="21">
         <v>1000</v>
       </c>
-    </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE67" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF67" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG67" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="68" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A68" s="22">
         <v>61010001</v>
       </c>
@@ -8791,8 +9784,20 @@
       <c r="AC68" s="22">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE68" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF68" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG68" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="69" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A69" s="22">
         <v>61020001</v>
       </c>
@@ -8876,8 +9881,20 @@
       <c r="AC69" s="22">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE69" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF69" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG69" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="70" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A70" s="22">
         <v>61030001</v>
       </c>
@@ -8961,8 +9978,20 @@
       <c r="AC70" s="22">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE70" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF70" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG70" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="71" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A71" s="22">
         <v>61040001</v>
       </c>
@@ -9046,8 +10075,20 @@
       <c r="AC71" s="22">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE71" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF71" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG71" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="72" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A72" s="22">
         <v>61050001</v>
       </c>
@@ -9131,8 +10172,20 @@
       <c r="AC72" s="22">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE72" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF72" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG72" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="73" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A73" s="22">
         <v>61060001</v>
       </c>
@@ -9216,8 +10269,20 @@
       <c r="AC73" s="22">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE73" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF73" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG73" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="74" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A74" s="22">
         <v>61070001</v>
       </c>
@@ -9301,8 +10366,20 @@
       <c r="AC74" s="22">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE74" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF74" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG74" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="75" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A75" s="22">
         <v>61080001</v>
       </c>
@@ -9386,8 +10463,20 @@
       <c r="AC75" s="22">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE75" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF75" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG75" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="76" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A76" s="22">
         <v>61090001</v>
       </c>
@@ -9471,8 +10560,20 @@
       <c r="AC76" s="22">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE76" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF76" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG76" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="77" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A77" s="22">
         <v>61100001</v>
       </c>
@@ -9556,8 +10657,20 @@
       <c r="AC77" s="22">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE77" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF77" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG77" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="78" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A78" s="21">
         <v>855001001</v>
       </c>
@@ -9639,8 +10752,20 @@
       <c r="AC78" s="21">
         <v>8000</v>
       </c>
-    </row>
-    <row r="79" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD78" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE78" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF78" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG78" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="79" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A79" s="21">
         <v>855001002</v>
       </c>
@@ -9722,8 +10847,20 @@
       <c r="AC79" s="21">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD79" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE79" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF79" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG79" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="80" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A80" s="27">
         <v>85000100</v>
       </c>
@@ -9805,8 +10942,20 @@
       <c r="AC80" s="27">
         <v>500</v>
       </c>
-    </row>
-    <row r="81" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE80" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF80" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG80" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="81" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A81" s="27">
         <v>85000300</v>
       </c>
@@ -9892,8 +11041,20 @@
       <c r="AC81" s="27">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE81" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF81" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG81" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="82" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A82" s="27">
         <v>85000500</v>
       </c>
@@ -9979,8 +11140,20 @@
       <c r="AC82" s="27">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE82" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF82" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG82" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="83" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A83" s="27">
         <v>85000700</v>
       </c>
@@ -10066,8 +11239,20 @@
       <c r="AC83" s="27">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE83" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF83" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG83" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="84" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A84" s="27">
         <v>85000900</v>
       </c>
@@ -10153,8 +11338,20 @@
       <c r="AC84" s="27">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE84" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF84" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG84" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="85" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A85" s="27">
         <v>85001100</v>
       </c>
@@ -10240,8 +11437,20 @@
       <c r="AC85" s="27">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE85" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF85" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG85" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="86" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A86" s="27">
         <v>85001300</v>
       </c>
@@ -10327,8 +11536,20 @@
       <c r="AC86" s="27">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE86" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF86" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG86" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="87" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A87" s="27">
         <v>85001500</v>
       </c>
@@ -10414,8 +11635,20 @@
       <c r="AC87" s="27">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE87" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF87" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG87" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="88" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A88" s="27">
         <v>85020300</v>
       </c>
@@ -10501,8 +11734,20 @@
       <c r="AC88" s="27">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE88" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF88" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG88" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="89" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A89" s="27">
         <v>85100100</v>
       </c>
@@ -10584,8 +11829,20 @@
       <c r="AC89" s="27">
         <v>500</v>
       </c>
-    </row>
-    <row r="90" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE89" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF89" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG89" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="90" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A90" s="27">
         <v>85100300</v>
       </c>
@@ -10671,8 +11928,20 @@
       <c r="AC90" s="27">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE90" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF90" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG90" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="91" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A91" s="27">
         <v>85100500</v>
       </c>
@@ -10758,8 +12027,20 @@
       <c r="AC91" s="27">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE91" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF91" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG91" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="92" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A92" s="27">
         <v>85100700</v>
       </c>
@@ -10845,8 +12126,20 @@
       <c r="AC92" s="27">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE92" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF92" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG92" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="93" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A93" s="27">
         <v>85100900</v>
       </c>
@@ -10932,8 +12225,20 @@
       <c r="AC93" s="27">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE93" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF93" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG93" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="94" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A94" s="27">
         <v>85101100</v>
       </c>
@@ -11021,8 +12326,20 @@
       <c r="AC94" s="27">
         <v>1000</v>
       </c>
-    </row>
-    <row r="95" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE94" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF94" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG94" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="95" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A95" s="27">
         <v>85120300</v>
       </c>
@@ -11108,8 +12425,20 @@
       <c r="AC95" s="27">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE95" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF95" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG95" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="96" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A96" s="27">
         <v>85200100</v>
       </c>
@@ -11191,8 +12520,20 @@
       <c r="AC96" s="27">
         <v>500</v>
       </c>
-    </row>
-    <row r="97" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE96" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF96" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG96" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="97" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A97" s="27">
         <v>85200300</v>
       </c>
@@ -11278,8 +12619,20 @@
       <c r="AC97" s="27">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE97" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF97" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG97" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="98" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A98" s="27">
         <v>85200500</v>
       </c>
@@ -11365,8 +12718,20 @@
       <c r="AC98" s="27">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE98" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF98" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG98" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="99" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A99" s="27">
         <v>85200700</v>
       </c>
@@ -11452,8 +12817,20 @@
       <c r="AC99" s="27">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE99" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF99" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG99" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="100" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A100" s="27">
         <v>85220300</v>
       </c>
@@ -11539,8 +12916,20 @@
       <c r="AC100" s="27">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE100" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF100" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG100" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="101" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A101" s="27">
         <v>87000100</v>
       </c>
@@ -11625,6 +13014,18 @@
       </c>
       <c r="AC101" s="27">
         <v>0</v>
+      </c>
+      <c r="AD101" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE101" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF101" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG101" s="15" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60663F17-68EC-4CC6-9DA6-927AE6ABB673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83834D5A-5EFF-4B55-8044-BD54F1C97E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="427">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1497,15 +1497,39 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <t>每【参数8】（默认1000）毫秒，造成{[火元素直接伤害]【参数1万分比】（默认50%）}，【参数2】（默认0）的[额外火元素持续伤害]，效果持续【参数5】（默认1.2）毫秒，最大可叠加【参数7】（默认1）层</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
     <t>8200015:1</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>8200018:1</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>毒爆</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果-毒</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>8200111:1</t>
+  </si>
+  <si>
+    <t>8200112:1</t>
+  </si>
+  <si>
+    <t>8200115:1</t>
+  </si>
+  <si>
+    <t>8200118:1</t>
+  </si>
+  <si>
+    <t>每【参数8】（默认1000）毫秒，造成{[毒元素直接伤害]【参数1万分比】（默认25%）}，【参数2】（默认0）的[额外毒元素持续伤害]，效果持续【参数5】（默认4000）毫秒，最大可叠加【参数7】（默认1）层；持续时间结束前目标死亡触发技能毒爆【参数4】</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>每【参数8】（默认1000）毫秒，造成{[火元素直接伤害]【参数1万分比】（默认50%）}，【参数2】（默认0）的[额外火元素持续伤害]，效果持续【参数5】（默认1200）毫秒，最大可叠加【参数7】（默认1）层</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -2076,7 +2100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG27"/>
+  <dimension ref="A1:AG28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -4659,7 +4683,7 @@
         <v>820001</v>
       </c>
       <c r="B27" s="19">
-        <v>5601</v>
+        <v>20001</v>
       </c>
       <c r="C27" s="20">
         <v>1</v>
@@ -4680,7 +4704,7 @@
         <v>414</v>
       </c>
       <c r="I27" s="19" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>415</v>
@@ -4713,7 +4737,7 @@
         <v>0</v>
       </c>
       <c r="T27" s="19" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="U27" s="19">
         <v>1200</v>
@@ -4734,7 +4758,7 @@
         <v>1</v>
       </c>
       <c r="AA27" s="19" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AB27" s="19">
         <v>1</v>
@@ -4752,6 +4776,105 @@
         <v>43</v>
       </c>
       <c r="AG27" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A28" s="19">
+        <v>820011</v>
+      </c>
+      <c r="B28" s="19">
+        <v>20011</v>
+      </c>
+      <c r="C28" s="20">
+        <v>1</v>
+      </c>
+      <c r="D28" s="20">
+        <v>0</v>
+      </c>
+      <c r="E28" s="19">
+        <v>820011</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19" t="s">
+        <v>425</v>
+      </c>
+      <c r="J28" s="19" t="s">
+        <v>421</v>
+      </c>
+      <c r="K28" s="19">
+        <v>2</v>
+      </c>
+      <c r="L28" s="19">
+        <v>2500</v>
+      </c>
+      <c r="M28" s="19" t="s">
+        <v>422</v>
+      </c>
+      <c r="N28" s="19">
+        <v>1</v>
+      </c>
+      <c r="O28" s="19">
+        <v>0</v>
+      </c>
+      <c r="P28" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q28" s="19">
+        <v>1</v>
+      </c>
+      <c r="R28" s="19">
+        <v>0</v>
+      </c>
+      <c r="S28" s="20">
+        <v>20012</v>
+      </c>
+      <c r="T28" s="19" t="s">
+        <v>423</v>
+      </c>
+      <c r="U28" s="19">
+        <v>4000</v>
+      </c>
+      <c r="V28" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="W28" s="19">
+        <v>10000</v>
+      </c>
+      <c r="X28" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y28" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z28" s="19">
+        <v>1</v>
+      </c>
+      <c r="AA28" s="19" t="s">
+        <v>424</v>
+      </c>
+      <c r="AB28" s="19">
+        <v>1</v>
+      </c>
+      <c r="AC28" s="19">
+        <v>1000</v>
+      </c>
+      <c r="AD28" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE28" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF28" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG28" s="15" t="s">
         <v>43</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83834D5A-5EFF-4B55-8044-BD54F1C97E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54611D6D-7575-46EC-9CAB-7A46A9AA3424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="429">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1530,6 +1530,14 @@
   </si>
   <si>
     <t>每【参数8】（默认1000）毫秒，造成{[火元素直接伤害]【参数1万分比】（默认50%）}，【参数2】（默认0）的[额外火元素持续伤害]，效果持续【参数5】（默认1200）毫秒，最大可叠加【参数7】（默认1）层</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>追加释放技能升龙击【参数4】</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>追加升龙击</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -2100,7 +2108,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG28"/>
+  <dimension ref="A1:AG29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -4878,6 +4886,105 @@
         <v>43</v>
       </c>
     </row>
+    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A29" s="19">
+        <v>820021</v>
+      </c>
+      <c r="B29" s="19">
+        <v>20021</v>
+      </c>
+      <c r="C29" s="20">
+        <v>1</v>
+      </c>
+      <c r="D29" s="20">
+        <v>0</v>
+      </c>
+      <c r="E29" s="19">
+        <v>820011</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19" t="s">
+        <v>427</v>
+      </c>
+      <c r="J29" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="K29" s="19">
+        <v>1</v>
+      </c>
+      <c r="L29" s="19">
+        <v>0</v>
+      </c>
+      <c r="M29" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="N29" s="19">
+        <v>1</v>
+      </c>
+      <c r="O29" s="19">
+        <v>0</v>
+      </c>
+      <c r="P29" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q29" s="19">
+        <v>1</v>
+      </c>
+      <c r="R29" s="19">
+        <v>0</v>
+      </c>
+      <c r="S29" s="20">
+        <v>20022</v>
+      </c>
+      <c r="T29" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="U29" s="19">
+        <v>1</v>
+      </c>
+      <c r="V29" s="19">
+        <v>0</v>
+      </c>
+      <c r="W29" s="19">
+        <v>10000</v>
+      </c>
+      <c r="X29" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y29" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z29" s="19">
+        <v>1</v>
+      </c>
+      <c r="AA29" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB29" s="19">
+        <v>1</v>
+      </c>
+      <c r="AC29" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE29" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF29" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG29" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54611D6D-7575-46EC-9CAB-7A46A9AA3424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7BF59D-C788-4A8F-B657-053A648DDA27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4900,7 +4900,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="19">
-        <v>820011</v>
+        <v>820021</v>
       </c>
       <c r="F29" s="19" t="s">
         <v>428</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7BF59D-C788-4A8F-B657-053A648DDA27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB2A8776-B4D1-40A6-90B5-D8DB7C6DE10A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="429">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -4946,10 +4946,10 @@
         <v>43</v>
       </c>
       <c r="U29" s="19">
-        <v>1</v>
-      </c>
-      <c r="V29" s="19">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V29" s="15" t="s">
+        <v>43</v>
       </c>
       <c r="W29" s="19">
         <v>10000</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB2A8776-B4D1-40A6-90B5-D8DB7C6DE10A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2597007D-F7C3-424B-B8A1-A36B7B397E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="427">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1530,14 +1530,6 @@
   </si>
   <si>
     <t>每【参数8】（默认1000）毫秒，造成{[火元素直接伤害]【参数1万分比】（默认50%）}，【参数2】（默认0）的[额外火元素持续伤害]，效果持续【参数5】（默认1200）毫秒，最大可叠加【参数7】（默认1）层</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>追加释放技能升龙击【参数4】</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>追加升龙击</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -2108,7 +2100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG29"/>
+  <dimension ref="A1:AG28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -4886,105 +4878,6 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A29" s="19">
-        <v>820021</v>
-      </c>
-      <c r="B29" s="19">
-        <v>20021</v>
-      </c>
-      <c r="C29" s="20">
-        <v>1</v>
-      </c>
-      <c r="D29" s="20">
-        <v>0</v>
-      </c>
-      <c r="E29" s="19">
-        <v>820021</v>
-      </c>
-      <c r="F29" s="19" t="s">
-        <v>428</v>
-      </c>
-      <c r="G29" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19" t="s">
-        <v>427</v>
-      </c>
-      <c r="J29" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="K29" s="19">
-        <v>1</v>
-      </c>
-      <c r="L29" s="19">
-        <v>0</v>
-      </c>
-      <c r="M29" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="N29" s="19">
-        <v>1</v>
-      </c>
-      <c r="O29" s="19">
-        <v>0</v>
-      </c>
-      <c r="P29" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q29" s="19">
-        <v>1</v>
-      </c>
-      <c r="R29" s="19">
-        <v>0</v>
-      </c>
-      <c r="S29" s="20">
-        <v>20022</v>
-      </c>
-      <c r="T29" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="U29" s="19">
-        <v>0</v>
-      </c>
-      <c r="V29" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="W29" s="19">
-        <v>10000</v>
-      </c>
-      <c r="X29" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y29" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z29" s="19">
-        <v>1</v>
-      </c>
-      <c r="AA29" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB29" s="19">
-        <v>1</v>
-      </c>
-      <c r="AC29" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE29" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF29" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG29" s="15" t="s">
-        <v>43</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2597007D-F7C3-424B-B8A1-A36B7B397E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C479F8B0-E312-4095-8681-A832A6B27FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="431">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1530,6 +1530,22 @@
   </si>
   <si>
     <t>每【参数8】（默认1000）毫秒，造成{[火元素直接伤害]【参数1万分比】（默认50%）}，【参数2】（默认0）的[额外火元素持续伤害]，效果持续【参数5】（默认1200）毫秒，最大可叠加【参数7】（默认1）层</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪电链概率附加麻痹</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>麻痹状态（无法攻击和移动），持续时间【参数5】（默认1000）毫秒，状态命中率【参数6】（默认20%）</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>连环闪电</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀敌人时再次释放闪电链【参数4】</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -2100,7 +2116,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG28"/>
+  <dimension ref="A1:AG30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -4878,6 +4894,204 @@
         <v>43</v>
       </c>
     </row>
+    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A29" s="19">
+        <v>820031</v>
+      </c>
+      <c r="B29" s="19">
+        <v>5701</v>
+      </c>
+      <c r="C29" s="20">
+        <v>1</v>
+      </c>
+      <c r="D29" s="20">
+        <v>0</v>
+      </c>
+      <c r="E29" s="19">
+        <v>5200800</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>427</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="J29" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="K29" s="19">
+        <v>1</v>
+      </c>
+      <c r="L29" s="19">
+        <v>0</v>
+      </c>
+      <c r="M29" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="N29" s="19">
+        <v>1</v>
+      </c>
+      <c r="O29" s="19">
+        <v>0</v>
+      </c>
+      <c r="P29" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q29" s="19">
+        <v>1</v>
+      </c>
+      <c r="R29" s="19">
+        <v>0</v>
+      </c>
+      <c r="S29" s="20">
+        <v>0</v>
+      </c>
+      <c r="T29" s="19" t="s">
+        <v>341</v>
+      </c>
+      <c r="U29" s="19">
+        <v>1000</v>
+      </c>
+      <c r="V29" s="19" t="s">
+        <v>340</v>
+      </c>
+      <c r="W29" s="19">
+        <v>2000</v>
+      </c>
+      <c r="X29" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y29" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z29" s="19">
+        <v>1</v>
+      </c>
+      <c r="AA29" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB29" s="19">
+        <v>1</v>
+      </c>
+      <c r="AC29" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE29" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF29" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG29" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A30" s="19">
+        <v>820034</v>
+      </c>
+      <c r="B30" s="19">
+        <v>20034</v>
+      </c>
+      <c r="C30" s="20">
+        <v>1</v>
+      </c>
+      <c r="D30" s="20">
+        <v>0</v>
+      </c>
+      <c r="E30" s="19">
+        <v>820034</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>429</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19" t="s">
+        <v>430</v>
+      </c>
+      <c r="J30" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="K30" s="19">
+        <v>1</v>
+      </c>
+      <c r="L30" s="19">
+        <v>0</v>
+      </c>
+      <c r="M30" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="N30" s="19">
+        <v>1</v>
+      </c>
+      <c r="O30" s="19">
+        <v>0</v>
+      </c>
+      <c r="P30" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q30" s="19">
+        <v>1</v>
+      </c>
+      <c r="R30" s="19">
+        <v>0</v>
+      </c>
+      <c r="S30" s="20">
+        <v>20031</v>
+      </c>
+      <c r="T30" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="U30" s="19">
+        <v>-1</v>
+      </c>
+      <c r="V30" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="W30" s="19">
+        <v>10000</v>
+      </c>
+      <c r="X30" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y30" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z30" s="19">
+        <v>1</v>
+      </c>
+      <c r="AA30" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB30" s="19">
+        <v>1</v>
+      </c>
+      <c r="AC30" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE30" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF30" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG30" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C479F8B0-E312-4095-8681-A832A6B27FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CC6FBCA-4896-4B17-B71C-99FA647F837F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -103,30 +103,8 @@
 </comments>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="439">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1546,6 +1524,38 @@
   </si>
   <si>
     <t>击杀敌人时再次释放闪电链【参数4】</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff组id</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>麻痹</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>中毒</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>5200712:1</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>5200711:1</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀敌人时再次释放超强电刃【参数4】</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>天罚</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -2116,7 +2126,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG30"/>
+  <dimension ref="A1:AG32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -4899,7 +4909,7 @@
         <v>820031</v>
       </c>
       <c r="B29" s="19">
-        <v>5701</v>
+        <v>101</v>
       </c>
       <c r="C29" s="20">
         <v>1</v>
@@ -5089,6 +5099,204 @@
         <v>43</v>
       </c>
       <c r="AG30" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A31" s="3">
+        <v>820051</v>
+      </c>
+      <c r="B31" s="19">
+        <v>101</v>
+      </c>
+      <c r="C31" s="20">
+        <v>1</v>
+      </c>
+      <c r="D31" s="20">
+        <v>0</v>
+      </c>
+      <c r="E31" s="19">
+        <v>5200800</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>427</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="J31" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="K31" s="19">
+        <v>1</v>
+      </c>
+      <c r="L31" s="19">
+        <v>0</v>
+      </c>
+      <c r="M31" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="N31" s="19">
+        <v>1</v>
+      </c>
+      <c r="O31" s="19">
+        <v>0</v>
+      </c>
+      <c r="P31" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q31" s="19">
+        <v>1</v>
+      </c>
+      <c r="R31" s="19">
+        <v>0</v>
+      </c>
+      <c r="S31" s="20">
+        <v>0</v>
+      </c>
+      <c r="T31" s="19" t="s">
+        <v>435</v>
+      </c>
+      <c r="U31" s="19">
+        <v>1000</v>
+      </c>
+      <c r="V31" s="19" t="s">
+        <v>436</v>
+      </c>
+      <c r="W31" s="19">
+        <v>2000</v>
+      </c>
+      <c r="X31" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y31" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z31" s="19">
+        <v>1</v>
+      </c>
+      <c r="AA31" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB31" s="19">
+        <v>1</v>
+      </c>
+      <c r="AC31" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE31" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF31" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG31" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A32" s="19">
+        <v>820054</v>
+      </c>
+      <c r="B32" s="19">
+        <v>20034</v>
+      </c>
+      <c r="C32" s="20">
+        <v>1</v>
+      </c>
+      <c r="D32" s="20">
+        <v>0</v>
+      </c>
+      <c r="E32" s="19">
+        <v>820054</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>438</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19" t="s">
+        <v>437</v>
+      </c>
+      <c r="J32" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="K32" s="19">
+        <v>1</v>
+      </c>
+      <c r="L32" s="19">
+        <v>0</v>
+      </c>
+      <c r="M32" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="N32" s="19">
+        <v>1</v>
+      </c>
+      <c r="O32" s="19">
+        <v>0</v>
+      </c>
+      <c r="P32" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q32" s="19">
+        <v>1</v>
+      </c>
+      <c r="R32" s="19">
+        <v>0</v>
+      </c>
+      <c r="S32" s="20">
+        <v>20053</v>
+      </c>
+      <c r="T32" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="U32" s="19">
+        <v>-1</v>
+      </c>
+      <c r="V32" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="W32" s="19">
+        <v>10000</v>
+      </c>
+      <c r="X32" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y32" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z32" s="19">
+        <v>1</v>
+      </c>
+      <c r="AA32" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB32" s="19">
+        <v>1</v>
+      </c>
+      <c r="AC32" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE32" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF32" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG32" s="15" t="s">
         <v>43</v>
       </c>
     </row>
@@ -6214,7 +6422,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="4:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D17" s="2" t="s">
         <v>60</v>
       </c>
@@ -6222,7 +6430,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="4:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D18" s="2" t="s">
         <v>62</v>
       </c>
@@ -6230,200 +6438,60 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="4:6" x14ac:dyDescent="0.15">
-      <c r="E24" s="1" t="e">
-        <f>_xlfn.TEXTJOIN(",",TRUE,E25:E43)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F24" s="1" t="e">
-        <f>_xlfn.TEXTJOIN(",",TRUE,F25:F43)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="25" spans="4:6" x14ac:dyDescent="0.15">
-      <c r="D25" s="1">
-        <v>101000101</v>
-      </c>
-      <c r="E25" s="1" t="e">
-        <f>VLOOKUP(D25,maze_skilleffect_v8!$A$5:$E$5,4,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F25" s="1" t="e" cm="1">
-        <f t="array" ref="F25">_xlfn.UNIQUE(E25:E43)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="26" spans="4:6" x14ac:dyDescent="0.15">
-      <c r="D26" s="1">
-        <v>102000101</v>
-      </c>
-      <c r="E26" s="1" t="e">
-        <f>VLOOKUP(D26,maze_skilleffect_v8!$A$5:$E$5,4,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="27" spans="4:6" x14ac:dyDescent="0.15">
-      <c r="D27" s="1">
-        <v>103000201</v>
-      </c>
-      <c r="E27" s="1" t="e">
-        <f>VLOOKUP(D27,maze_skilleffect_v8!$A$5:$E$5,4,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="28" spans="4:6" x14ac:dyDescent="0.15">
-      <c r="D28" s="1">
-        <v>104000101</v>
-      </c>
-      <c r="E28" s="1" t="e">
-        <f>VLOOKUP(D28,maze_skilleffect_v8!$A$5:$E$5,4,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="29" spans="4:6" x14ac:dyDescent="0.15">
-      <c r="D29" s="1">
-        <v>1002000001</v>
-      </c>
-      <c r="E29" s="1" t="e">
-        <f>VLOOKUP(D29,maze_skilleffect_v8!$A$5:$E$5,4,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="30" spans="4:6" x14ac:dyDescent="0.15">
-      <c r="D30" s="1">
-        <v>1002000002</v>
-      </c>
-      <c r="E30" s="1" t="e">
-        <f>VLOOKUP(D30,maze_skilleffect_v8!$A$5:$E$5,4,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="31" spans="4:6" x14ac:dyDescent="0.15">
-      <c r="D31" s="1">
-        <v>1002000003</v>
-      </c>
-      <c r="E31" s="1" t="e">
-        <f>VLOOKUP(D31,maze_skilleffect_v8!$A$5:$E$5,4,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="32" spans="4:6" x14ac:dyDescent="0.15">
-      <c r="D32" s="1">
-        <v>1003000001</v>
-      </c>
-      <c r="E32" s="1" t="e">
-        <f>VLOOKUP(D32,maze_skilleffect_v8!$A$5:$E$5,4,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="33" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="D33" s="1">
-        <v>1003000002</v>
-      </c>
-      <c r="E33" s="1" t="e">
-        <f>VLOOKUP(D33,maze_skilleffect_v8!$A$5:$E$5,4,FALSE)</f>
-        <v>#N/A</v>
-      </c>
+    <row r="28" spans="4:5" x14ac:dyDescent="0.15">
+      <c r="D28" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="29" spans="4:5" x14ac:dyDescent="0.15">
+      <c r="D29" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="E29" s="1">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="4:5" x14ac:dyDescent="0.15">
+      <c r="D30" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="31" spans="4:5" x14ac:dyDescent="0.15">
+      <c r="D31" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="33" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F33"/>
     </row>
-    <row r="34" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="D34" s="1">
-        <v>1003000003</v>
-      </c>
-      <c r="E34" s="1" t="e">
-        <f>VLOOKUP(D34,maze_skilleffect_v8!$A$5:$E$5,4,FALSE)</f>
-        <v>#N/A</v>
-      </c>
+    <row r="34" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F34"/>
     </row>
-    <row r="35" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="D35" s="1">
-        <v>1004000001</v>
-      </c>
-      <c r="E35" s="1" t="e">
-        <f>VLOOKUP(D35,maze_skilleffect_v8!$A$5:$E$5,4,FALSE)</f>
-        <v>#N/A</v>
-      </c>
+    <row r="35" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F35"/>
     </row>
-    <row r="36" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="D36" s="1">
-        <v>1004000002</v>
-      </c>
-      <c r="E36" s="1" t="e">
-        <f>VLOOKUP(D36,maze_skilleffect_v8!$A$5:$E$5,4,FALSE)</f>
-        <v>#N/A</v>
-      </c>
+    <row r="36" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F36"/>
     </row>
-    <row r="37" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="D37" s="1">
-        <v>1004000003</v>
-      </c>
-      <c r="E37" s="1" t="e">
-        <f>VLOOKUP(D37,maze_skilleffect_v8!$A$5:$E$5,4,FALSE)</f>
-        <v>#N/A</v>
-      </c>
+    <row r="37" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F37"/>
     </row>
-    <row r="38" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="D38" s="1">
-        <v>1005000001</v>
-      </c>
-      <c r="E38" s="1" t="e">
-        <f>VLOOKUP(D38,maze_skilleffect_v8!$A$5:$E$5,4,FALSE)</f>
-        <v>#N/A</v>
-      </c>
+    <row r="38" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F38"/>
     </row>
-    <row r="39" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="D39" s="1">
-        <v>1005000002</v>
-      </c>
-      <c r="E39" s="1" t="e">
-        <f>VLOOKUP(D39,maze_skilleffect_v8!$A$5:$E$5,4,FALSE)</f>
-        <v>#N/A</v>
-      </c>
+    <row r="39" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F39"/>
     </row>
-    <row r="40" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="D40" s="1">
-        <v>1005000003</v>
-      </c>
-      <c r="E40" s="1" t="e">
-        <f>VLOOKUP(D40,maze_skilleffect_v8!$A$5:$E$5,4,FALSE)</f>
-        <v>#N/A</v>
-      </c>
+    <row r="40" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F40"/>
     </row>
-    <row r="41" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="D41" s="1">
-        <v>1006000001</v>
-      </c>
-      <c r="E41" s="1" t="e">
-        <f>VLOOKUP(D41,maze_skilleffect_v8!$A$5:$E$5,4,FALSE)</f>
-        <v>#N/A</v>
-      </c>
+    <row r="41" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F41"/>
     </row>
-    <row r="42" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="D42" s="1">
-        <v>1006000002</v>
-      </c>
-      <c r="E42" s="1" t="e">
-        <f>VLOOKUP(D42,maze_skilleffect_v8!$A$5:$E$5,4,FALSE)</f>
-        <v>#N/A</v>
-      </c>
+    <row r="42" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F42"/>
     </row>
-    <row r="43" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="D43" s="1">
-        <v>1006000003</v>
-      </c>
-      <c r="E43" s="1" t="e">
-        <f>VLOOKUP(D43,maze_skilleffect_v8!$A$5:$E$5,4,FALSE)</f>
-        <v>#N/A</v>
-      </c>
+    <row r="43" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F43"/>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CC6FBCA-4896-4B17-B71C-99FA647F837F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1ECEB6B-BB80-4914-A003-FB1BF07E6701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="445">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1515,10 +1515,6 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <t>麻痹状态（无法攻击和移动），持续时间【参数5】（默认1000）毫秒，状态命中率【参数6】（默认20%）</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
     <t>连环闪电</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
@@ -1547,15 +1543,43 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <t>5200711:1</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
     <t>击杀敌人时再次释放超强电刃【参数4】</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>天罚</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷神附体</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪电链附加麻痹状态（无法攻击和移动），持续时间【参数5】（默认1000）毫秒，状态命中率【参数6】（默认20%）</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻概率【参数6】释放电波【参数4】</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>8200551:1</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>电刃普攻概率附加麻痹</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>电刃普攻麻痹状态（无法攻击和移动），持续时间【参数5】（默认1000）毫秒，状态命中率【参数6】（默认20%）</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>5200701:0</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>5200702:0</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -2126,7 +2150,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG32"/>
+  <dimension ref="A1:AG33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -4928,7 +4952,7 @@
       </c>
       <c r="H29" s="19"/>
       <c r="I29" s="19" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="J29" s="19" t="s">
         <v>69</v>
@@ -4967,7 +4991,7 @@
         <v>1000</v>
       </c>
       <c r="V29" s="19" t="s">
-        <v>340</v>
+        <v>443</v>
       </c>
       <c r="W29" s="19">
         <v>2000</v>
@@ -5020,14 +5044,14 @@
         <v>820034</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>342</v>
       </c>
       <c r="H30" s="19"/>
       <c r="I30" s="19" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="J30" s="19" t="s">
         <v>69</v>
@@ -5119,14 +5143,14 @@
         <v>5200800</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>342</v>
       </c>
       <c r="H31" s="19"/>
       <c r="I31" s="19" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="J31" s="19" t="s">
         <v>69</v>
@@ -5159,16 +5183,16 @@
         <v>0</v>
       </c>
       <c r="T31" s="19" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="U31" s="19">
         <v>1000</v>
       </c>
       <c r="V31" s="19" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="W31" s="19">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="X31" s="19" t="s">
         <v>43</v>
@@ -5206,7 +5230,7 @@
         <v>820054</v>
       </c>
       <c r="B32" s="19">
-        <v>20034</v>
+        <v>20054</v>
       </c>
       <c r="C32" s="20">
         <v>1</v>
@@ -5218,14 +5242,14 @@
         <v>820054</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="G32" s="13" t="s">
         <v>342</v>
       </c>
       <c r="H32" s="19"/>
       <c r="I32" s="19" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="J32" s="19" t="s">
         <v>69</v>
@@ -5297,6 +5321,105 @@
         <v>43</v>
       </c>
       <c r="AG32" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A33" s="19">
+        <v>820055</v>
+      </c>
+      <c r="B33" s="19">
+        <v>20055</v>
+      </c>
+      <c r="C33" s="20">
+        <v>1</v>
+      </c>
+      <c r="D33" s="20">
+        <v>0</v>
+      </c>
+      <c r="E33" s="19">
+        <v>820055</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>437</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19" t="s">
+        <v>439</v>
+      </c>
+      <c r="J33" s="19" t="s">
+        <v>440</v>
+      </c>
+      <c r="K33" s="19">
+        <v>1</v>
+      </c>
+      <c r="L33" s="19">
+        <v>2000</v>
+      </c>
+      <c r="M33" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="N33" s="19">
+        <v>1</v>
+      </c>
+      <c r="O33" s="19">
+        <v>0</v>
+      </c>
+      <c r="P33" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q33" s="19">
+        <v>1</v>
+      </c>
+      <c r="R33" s="19">
+        <v>0</v>
+      </c>
+      <c r="S33" s="20">
+        <v>20052</v>
+      </c>
+      <c r="T33" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="U33" s="19">
+        <v>-1</v>
+      </c>
+      <c r="V33" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="W33" s="19">
+        <v>10000</v>
+      </c>
+      <c r="X33" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y33" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z33" s="19">
+        <v>1</v>
+      </c>
+      <c r="AA33" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB33" s="19">
+        <v>1</v>
+      </c>
+      <c r="AC33" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE33" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF33" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG33" s="15" t="s">
         <v>43</v>
       </c>
     </row>
@@ -6440,12 +6563,12 @@
     </row>
     <row r="28" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D28" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="29" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D29" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E29" s="1">
         <v>101</v>
@@ -6453,12 +6576,12 @@
     </row>
     <row r="30" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D30" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="31" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D31" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="33" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1ECEB6B-BB80-4914-A003-FB1BF07E6701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C6384E-AFA9-41BC-A48D-C4F300CFC4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1579,7 +1579,7 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <t>5200702:0</t>
+    <t>5200711:0</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11280" windowHeight="11820"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -1601,18 +1601,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1700,12 +1700,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2032,64 +2026,64 @@
     <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF2426C-BC0A-4775-A657-F8B9BDC7AFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -23,8 +29,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -32,32 +36,34 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>pe</author>
     <author>cltx</author>
   </authors>
   <commentList>
-    <comment ref="C4" authorId="0">
+    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>数字越大，优先级越高</t>
         </r>
       </text>
     </comment>
-    <comment ref="K4" authorId="1">
+    <comment ref="K4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>cltx:</t>
@@ -66,6 +72,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -75,12 +82,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="0">
+    <comment ref="U4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">&gt;0，持续时间
@@ -95,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="426">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -899,15 +907,6 @@
   </si>
   <si>
     <t>击杀敌人时再次释放超强电刃【参数4】</t>
-  </si>
-  <si>
-    <t>雷神附体</t>
-  </si>
-  <si>
-    <t>普攻概率【参数6】释放电波【参数4】</t>
-  </si>
-  <si>
-    <t>8200551:1</t>
   </si>
   <si>
     <t>重复中buff组的cd时间（毫秒）</t>
@@ -1387,14 +1386,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="31">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1406,30 +1399,35 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF9C5700"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <color theme="0" tint="-0.0499893185216834"/>
+      <color theme="0" tint="-4.9989318521683403E-2"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1437,12 +1435,14 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1450,153 +1450,35 @@
       <sz val="9"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1604,15 +1486,24 @@
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1621,13 +1512,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.349986266670736"/>
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799737540818506"/>
+        <fgColor theme="8" tint="0.79970702230903046"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1645,31 +1536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1679,146 +1546,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1856,241 +1585,23 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2105,8 +1616,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="24" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2114,77 +1625,36 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="23" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="24" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="24" applyFont="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="5">
+    <cellStyle name="差" xfId="2" builtinId="27"/>
+    <cellStyle name="差 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="差 2" xfId="49"/>
+    <cellStyle name="适中" xfId="3" builtinId="28"/>
+    <cellStyle name="输入" xfId="1" builtinId="20"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2462,14 +1932,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:AG33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AG32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -2500,7 +1970,7 @@
     <col min="33" max="33" width="17.125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2533,7 +2003,7 @@
       <c r="AB1" s="4"/>
       <c r="AC1" s="4"/>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -2634,7 +2104,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:33">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
@@ -2735,7 +2205,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:33">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>41</v>
       </c>
@@ -2836,7 +2306,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:33">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>1000001</v>
       </c>
@@ -2937,7 +2407,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:33">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>2000001</v>
       </c>
@@ -3038,7 +2508,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:33">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>54010001</v>
       </c>
@@ -3139,7 +2609,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="1:33">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
         <v>54020001</v>
       </c>
@@ -3240,7 +2710,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:33">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>54030001</v>
       </c>
@@ -3341,7 +2811,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:33">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A10" s="8">
         <v>54040001</v>
       </c>
@@ -3442,7 +2912,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:33">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>54050001</v>
       </c>
@@ -3543,7 +3013,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:33">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>54060001</v>
       </c>
@@ -3644,7 +3114,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="13" spans="1:33">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>54070001</v>
       </c>
@@ -3745,7 +3215,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:33">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>54080001</v>
       </c>
@@ -3846,7 +3316,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="15" spans="1:33">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>54090001</v>
       </c>
@@ -3947,7 +3417,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="16" spans="1:33">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A16" s="8">
         <v>54100001</v>
       </c>
@@ -4048,7 +3518,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="17" spans="1:33">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A17" s="8">
         <v>54110001</v>
       </c>
@@ -4149,7 +3619,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="18" spans="1:33">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A18" s="8">
         <v>54120001</v>
       </c>
@@ -4250,7 +3720,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="19" spans="1:33">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A19" s="8">
         <v>54130001</v>
       </c>
@@ -4351,7 +3821,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="20" spans="1:33">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A20" s="8">
         <v>54140001</v>
       </c>
@@ -4452,7 +3922,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="21" spans="1:33">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A21" s="8">
         <v>54150001</v>
       </c>
@@ -4553,7 +4023,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="22" spans="1:33">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A22" s="10">
         <v>59130001</v>
       </c>
@@ -4650,7 +4120,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" spans="1:33">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A23" s="10">
         <v>59140001</v>
       </c>
@@ -4747,7 +4217,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:33">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A24" s="13">
         <v>85001500</v>
       </c>
@@ -4846,7 +4316,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:33">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A25" s="13">
         <v>85101100</v>
       </c>
@@ -4947,7 +4417,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:33">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A26" s="13">
         <v>85200700</v>
       </c>
@@ -5046,7 +4516,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:33">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A27" s="13">
         <v>820001</v>
       </c>
@@ -5147,7 +4617,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:33">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A28" s="13">
         <v>820011</v>
       </c>
@@ -5246,7 +4716,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:33">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A29" s="13">
         <v>820031</v>
       </c>
@@ -5345,7 +4815,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:33">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A30" s="13">
         <v>820034</v>
       </c>
@@ -5444,7 +4914,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="31" spans="1:33">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>820051</v>
       </c>
@@ -5543,7 +5013,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:33">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A32" s="13">
         <v>820054</v>
       </c>
@@ -5642,117 +5112,17 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" spans="1:33">
-      <c r="A33" s="13">
-        <v>820055</v>
-      </c>
-      <c r="B33" s="13">
-        <v>20055</v>
-      </c>
-      <c r="C33" s="14">
-        <v>1</v>
-      </c>
-      <c r="D33" s="14">
-        <v>0</v>
-      </c>
-      <c r="E33" s="13">
-        <v>820055</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="G33" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="J33" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="K33" s="13">
-        <v>1</v>
-      </c>
-      <c r="L33" s="13">
-        <v>2000</v>
-      </c>
-      <c r="M33" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="N33" s="13">
-        <v>1</v>
-      </c>
-      <c r="O33" s="13">
-        <v>0</v>
-      </c>
-      <c r="P33" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q33" s="13">
-        <v>1</v>
-      </c>
-      <c r="R33" s="13">
-        <v>0</v>
-      </c>
-      <c r="S33" s="14">
-        <v>20052</v>
-      </c>
-      <c r="T33" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="U33" s="13">
-        <v>-1</v>
-      </c>
-      <c r="V33" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="W33" s="13">
-        <v>10000</v>
-      </c>
-      <c r="X33" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y33" s="13">
-        <v>1</v>
-      </c>
-      <c r="Z33" s="13">
-        <v>1</v>
-      </c>
-      <c r="AA33" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB33" s="13">
-        <v>1</v>
-      </c>
-      <c r="AC33" s="13">
-        <v>0</v>
-      </c>
-      <c r="AD33" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="AE33" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF33" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG33" s="8" t="s">
-        <v>78</v>
-      </c>
-    </row>
   </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="E7:S71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
     <col min="5" max="5" width="27.25" style="1" customWidth="1"/>
@@ -5765,7 +5135,7 @@
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="5:6">
+    <row r="7" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E7" s="1" t="s">
         <v>8</v>
       </c>
@@ -5773,7 +5143,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="5:6">
+    <row r="8" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E8" s="1" t="s">
         <v>9</v>
       </c>
@@ -5781,7 +5151,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="5:6">
+    <row r="9" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E9" s="1" t="s">
         <v>10</v>
       </c>
@@ -5789,15 +5159,15 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="5:6">
+    <row r="10" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="11" spans="5:6">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="11" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E11" s="1" t="s">
         <v>12</v>
       </c>
@@ -5805,7 +5175,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="5:6">
+    <row r="12" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E12" s="1" t="s">
         <v>13</v>
       </c>
@@ -5813,7 +5183,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="5:19">
+    <row r="13" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E13" s="1" t="s">
         <v>14</v>
       </c>
@@ -5821,13 +5191,13 @@
         <v>47</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="14" spans="5:12">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="14" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E14" s="1" t="s">
         <v>15</v>
       </c>
@@ -5841,13 +5211,13 @@
         <v>1</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="15" spans="5:19">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="15" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E15" s="1" t="s">
         <v>16</v>
       </c>
@@ -5858,16 +5228,16 @@
         <v>3</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="16" spans="5:19">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="16" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E16" s="1" t="s">
         <v>17</v>
       </c>
@@ -5881,16 +5251,16 @@
         <v>7</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="17" spans="5:19">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="17" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E17" s="1" t="s">
         <v>18</v>
       </c>
@@ -5904,16 +5274,16 @@
         <v>7</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="18" spans="5:19">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="18" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E18" s="1" t="s">
         <v>19</v>
       </c>
@@ -5927,16 +5297,16 @@
         <v>7</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="19" spans="5:19">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="19" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E19" s="1" t="s">
         <v>20</v>
       </c>
@@ -5948,25 +5318,25 @@
         <v>参数4LIST-触发的技能id</v>
       </c>
       <c r="H19" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="L19" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="S19" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="20" spans="5:19">
+    </row>
+    <row r="20" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E20" s="1" t="s">
         <v>21</v>
       </c>
@@ -5978,25 +5348,25 @@
         <v>参数5-持续时间（毫秒）</v>
       </c>
       <c r="H20" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="L20" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="S20" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="21" spans="5:19">
+    </row>
+    <row r="21" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E21" s="1" t="s">
         <v>22</v>
       </c>
@@ -6008,25 +5378,25 @@
         <v>参数6-效果基础命中率（万分比）</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="22" spans="5:19">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E22" s="1" t="s">
         <v>23</v>
       </c>
@@ -6041,22 +5411,22 @@
         <v>66</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="23" spans="5:19">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="23" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E23" s="1" t="s">
         <v>24</v>
       </c>
@@ -6068,25 +5438,25 @@
         <v>参数8-效果触发间隔（毫秒）</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="24" spans="5:19">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="24" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E24" s="1" t="s">
         <v>25</v>
       </c>
@@ -6098,25 +5468,25 @@
         <v>参数9-击中回复生命值-固定值</v>
       </c>
       <c r="H24" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="L24" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="S24" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="J24" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="S24" s="1" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="25" spans="5:19">
+    </row>
+    <row r="25" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E25" s="1" t="s">
         <v>26</v>
       </c>
@@ -6128,25 +5498,25 @@
         <v>参数10-击中回复生命值-自身最大生命值百万分比</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="26" spans="5:19">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="26" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E26" s="1" t="s">
         <v>27</v>
       </c>
@@ -6158,25 +5528,25 @@
         <v>参数11-击中回复效果提高万分比</v>
       </c>
       <c r="H26" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="L26" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="S26" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="J26" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="S26" s="1" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="27" spans="5:19">
+    </row>
+    <row r="27" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E27" s="1" t="s">
         <v>28</v>
       </c>
@@ -6188,25 +5558,25 @@
         <v>参数12-击杀回复生命-固定值</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="28" spans="5:12">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="28" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E28" s="1" t="s">
         <v>29</v>
       </c>
@@ -6218,22 +5588,22 @@
         <v>参数13-击杀回复生命-自身最大生命值百万分比</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="29" spans="5:19">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="29" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E29" s="1" t="s">
         <v>30</v>
       </c>
@@ -6245,25 +5615,25 @@
         <v>参数14-击杀回复生命-目标最大生命值百万分比</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="30" spans="5:19">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="30" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E30" s="1" t="s">
         <v>31</v>
       </c>
@@ -6275,25 +5645,25 @@
         <v>参数15-击杀回复生命效果提高万分比</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="31" spans="5:19">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="31" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E31" s="1" t="s">
         <v>32</v>
       </c>
@@ -6305,52 +5675,52 @@
         <v>参数16-获得护盾-固定值</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="32" spans="5:12">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="32" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E32" s="1" t="s">
         <v>33</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="G32" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数17-获得护盾-自身生命百万分比</v>
       </c>
       <c r="H32" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="L32" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="I32" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="33" spans="5:9">
+    </row>
+    <row r="33" spans="5:9" x14ac:dyDescent="0.15">
       <c r="E33" s="1" t="s">
         <v>34</v>
       </c>
@@ -6362,13 +5732,13 @@
         <v>参数18-获得护盾-自身已损失生命万分比</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="34" spans="5:9">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="34" spans="5:9" x14ac:dyDescent="0.15">
       <c r="E34" s="1" t="s">
         <v>35</v>
       </c>
@@ -6380,404 +5750,403 @@
         <v>参数19-获得护盾效果提高万分比</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="35" spans="5:9">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="35" spans="5:9" x14ac:dyDescent="0.15">
       <c r="E35" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="G35" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数20-技能增加-固定值</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="36" spans="7:9">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="36" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G36" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数21-技能增加-万分比</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="37" spans="7:9">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="37" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G37" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数22-技能增加-普通攻击范围万分比</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="38" spans="7:9">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="38" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G38" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数25LIST-攻击提高-攻击的元素类型</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="39" spans="7:9">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="39" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G39" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数25LIST-攻击提高-固定值</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="40" spans="7:9">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="40" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G40" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数25LIST-攻击提高-万分比</v>
       </c>
       <c r="H40" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="I40" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="I40" s="1" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="41" spans="7:9">
+    </row>
+    <row r="41" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G41" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数28-防御提高-固定值</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="42" spans="7:9">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="42" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G42" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数29-防御提高-万分比</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="43" spans="7:9">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="43" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G43" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数30-生命上限提高-固定值</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="44" spans="7:9">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="44" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G44" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数31-生命上限提高-百万分比</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="45" spans="7:9">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="45" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G45" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数32-攻击速度提高-万分比</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="46" spans="7:9">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="46" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G46" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数33-移动速度提高-万分比</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="47" spans="7:9">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="47" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G47" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数34-攻击范围提高-万分比</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="48" spans="7:9">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="48" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G48" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数35-攻击目标数量提高-固定值</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="49" spans="7:8">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="49" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G49" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数36-</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="50" spans="7:8">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="50" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G50" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数37-</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="51" spans="7:8">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="51" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G51" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数38-</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="52" spans="7:8">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="52" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G52" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数39-</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="53" spans="7:8">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="53" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G53" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数40-</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="54" spans="7:8">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="54" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G54" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数41-</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="55" spans="7:8">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="55" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G55" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数42-</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="56" spans="7:8">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="56" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G56" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数41-</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="57" spans="7:8">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="57" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G57" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数42-</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="58" spans="7:8">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="58" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G58" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数43-</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="59" spans="7:8">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="59" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G59" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数44-</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="60" spans="7:8">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="60" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G60" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数45-</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="61" spans="7:8">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="61" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G61" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数46-</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="62" spans="7:8">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="62" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G62" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数47-</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="63" spans="7:8">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="63" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G63" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数48-</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="64" spans="7:8">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="64" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G64" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数49-</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="65" spans="7:8">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="65" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G65" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数50-</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="66" spans="7:8">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="66" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G66" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数51-</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="67" spans="7:8">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="67" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G67" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数52-</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="68" spans="7:8">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="68" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G68" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数53-</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="69" spans="7:8">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="69" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G69" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数54-</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="70" spans="7:8">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="70" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G70" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数55-</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="71" spans="7:8">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="71" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G71" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数56-</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="D6:F43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="11.25" style="1" customWidth="1"/>
@@ -6787,158 +6156,158 @@
     <col min="23" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="4:5">
+    <row r="6" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D6" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="4:5">
+    <row r="7" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D7" s="2">
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="8" spans="4:5">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="8" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="4:5">
+    <row r="9" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D9" s="2">
         <v>2</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="10" spans="4:5">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="10" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D10" s="2">
         <v>2.1</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="11" spans="4:5" x14ac:dyDescent="0.15">
+      <c r="D11" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="12" spans="4:5" x14ac:dyDescent="0.15">
+      <c r="D12" s="2" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="11" spans="4:5">
-      <c r="D11" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="E11" s="2" t="s">
+    </row>
+    <row r="13" spans="4:5" x14ac:dyDescent="0.15">
+      <c r="D13" s="2" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="12" spans="4:5">
-      <c r="D12" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="13" spans="4:5">
-      <c r="D13" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="14" spans="4:5">
+    </row>
+    <row r="14" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="4:5">
+    <row r="15" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D15" s="2">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="16" spans="4:5" x14ac:dyDescent="0.15">
+      <c r="D16" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="17" spans="4:5" x14ac:dyDescent="0.15">
+      <c r="D17" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="16" spans="4:5">
-      <c r="D16" s="2" t="s">
+    <row r="18" spans="4:5" x14ac:dyDescent="0.15">
+      <c r="D18" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="17" spans="4:5">
-      <c r="D17" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="E17" s="2" t="s">
+    </row>
+    <row r="28" spans="4:5" x14ac:dyDescent="0.15">
+      <c r="D28" s="1" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="18" spans="4:5">
-      <c r="D18" s="2" t="s">
+    <row r="29" spans="4:5" x14ac:dyDescent="0.15">
+      <c r="D29" s="1" t="s">
         <v>423</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="28" spans="4:4">
-      <c r="D28" s="1" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="29" spans="4:5">
-      <c r="D29" s="1" t="s">
-        <v>426</v>
       </c>
       <c r="E29" s="1">
         <v>101</v>
       </c>
     </row>
-    <row r="30" spans="4:4">
+    <row r="30" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D30" s="1" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="31" spans="4:4">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="31" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D31" s="1" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="33" ht="14.25" spans="6:6">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="33" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F33"/>
     </row>
-    <row r="34" ht="14.25" spans="6:6">
+    <row r="34" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F34"/>
     </row>
-    <row r="35" ht="14.25" spans="6:6">
+    <row r="35" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F35"/>
     </row>
-    <row r="36" ht="14.25" spans="6:6">
+    <row r="36" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F36"/>
     </row>
-    <row r="37" ht="14.25" spans="6:6">
+    <row r="37" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F37"/>
     </row>
-    <row r="38" ht="14.25" spans="6:6">
+    <row r="38" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F38"/>
     </row>
-    <row r="39" ht="14.25" spans="6:6">
+    <row r="39" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F39"/>
     </row>
-    <row r="40" ht="14.25" spans="6:6">
+    <row r="40" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F40"/>
     </row>
-    <row r="41" ht="14.25" spans="6:6">
+    <row r="41" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F41"/>
     </row>
-    <row r="42" ht="14.25" spans="6:6">
+    <row r="42" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F42"/>
     </row>
-    <row r="43" ht="14.25" spans="6:6">
+    <row r="43" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F43"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF2426C-BC0A-4775-A657-F8B9BDC7AFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D3FB15A-E738-4A45-A640-8F502DB34723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="440">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -879,508 +879,565 @@
     <t>闪电链概率附加麻痹</t>
   </si>
   <si>
+    <t>5200701:0</t>
+  </si>
+  <si>
+    <t>连环闪电</t>
+  </si>
+  <si>
+    <t>击杀敌人时再次释放闪电链【参数4】</t>
+  </si>
+  <si>
+    <t>电刃普攻概率附加麻痹</t>
+  </si>
+  <si>
+    <t>电刃普攻麻痹状态（无法攻击和移动），持续时间【参数5】（默认1000）毫秒，状态命中率【参数6】（默认20%）</t>
+  </si>
+  <si>
+    <t>5200712:1</t>
+  </si>
+  <si>
+    <t>5200711:0</t>
+  </si>
+  <si>
+    <t>天罚</t>
+  </si>
+  <si>
+    <t>击杀敌人时再次释放超强电刃【参数4】</t>
+  </si>
+  <si>
+    <t>重复中buff组的cd时间（毫秒）</t>
+  </si>
+  <si>
+    <t>触发自动技能</t>
+  </si>
+  <si>
+    <t>主动技能</t>
+  </si>
+  <si>
+    <t>order</t>
+  </si>
+  <si>
+    <t>自动</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>冰霜新星</t>
+  </si>
+  <si>
+    <t>auto_cd</t>
+  </si>
+  <si>
+    <t>参数-重复触发自动释放冷却时间（毫秒）</t>
+  </si>
+  <si>
+    <t>陨石</t>
+  </si>
+  <si>
+    <t>release_ratio</t>
+  </si>
+  <si>
+    <t>参数-释放几率</t>
+  </si>
+  <si>
+    <t>死亡爆炸</t>
+  </si>
+  <si>
+    <t>release_num</t>
+  </si>
+  <si>
+    <t>参数-释放次数</t>
+  </si>
+  <si>
+    <t>闪电链</t>
+  </si>
+  <si>
+    <t>参数4LIST</t>
+  </si>
+  <si>
+    <t>触发的技能id</t>
+  </si>
+  <si>
+    <t>LIST&lt;INT&gt;_S</t>
+  </si>
+  <si>
+    <t>skill_id</t>
+  </si>
+  <si>
+    <t>参数-释放的技能id</t>
+  </si>
+  <si>
+    <t>电磁爆发</t>
+  </si>
+  <si>
+    <t>参数5</t>
+  </si>
+  <si>
+    <t>持续时间（毫秒）</t>
+  </si>
+  <si>
+    <t>total_attack_num</t>
+  </si>
+  <si>
+    <t>参数-累计发起攻击次数时</t>
+  </si>
+  <si>
+    <t>传染</t>
+  </si>
+  <si>
+    <t>参数6</t>
+  </si>
+  <si>
+    <t>效果基础命中率（万分比）</t>
+  </si>
+  <si>
+    <t>lose_hp_ratio</t>
+  </si>
+  <si>
+    <t>参数-损失自身生命最大值百万分比时</t>
+  </si>
+  <si>
+    <t>瘟疫</t>
+  </si>
+  <si>
+    <t>效果最大叠加层数</t>
+  </si>
+  <si>
+    <t>kill_target_after</t>
+  </si>
+  <si>
+    <t>参数-击杀目标后</t>
+  </si>
+  <si>
+    <t>复活</t>
+  </si>
+  <si>
+    <t>参数8</t>
+  </si>
+  <si>
+    <t>效果触发间隔（毫秒）</t>
+  </si>
+  <si>
+    <t>after_attack_crit</t>
+  </si>
+  <si>
+    <t>参数-攻击暴击后</t>
+  </si>
+  <si>
+    <t>半月斩</t>
+  </si>
+  <si>
+    <t>参数9</t>
+  </si>
+  <si>
+    <t>击中回复生命值-固定值</t>
+  </si>
+  <si>
+    <t>after_use_skill</t>
+  </si>
+  <si>
+    <t>参数-释放【技能id】后</t>
+  </si>
+  <si>
+    <t>旋风斩</t>
+  </si>
+  <si>
+    <t>参数10</t>
+  </si>
+  <si>
+    <t>击中回复生命值-自身最大生命值百万分比</t>
+  </si>
+  <si>
+    <t>cycle_time</t>
+  </si>
+  <si>
+    <t>参数-每过固定时间（毫秒）时</t>
+  </si>
+  <si>
+    <t>重击</t>
+  </si>
+  <si>
+    <t>参数11</t>
+  </si>
+  <si>
+    <t>击中回复效果提高万分比</t>
+  </si>
+  <si>
+    <t>after_skill_hit</t>
+  </si>
+  <si>
+    <t>参数-【技能id】命中后</t>
+  </si>
+  <si>
+    <t>多重打击</t>
+  </si>
+  <si>
+    <t>参数12</t>
+  </si>
+  <si>
+    <t>击杀回复生命-固定值</t>
+  </si>
+  <si>
+    <t>after_self_death</t>
+  </si>
+  <si>
+    <t>参数-自身死亡后释放</t>
+  </si>
+  <si>
+    <t>斩杀</t>
+  </si>
+  <si>
+    <t>参数13</t>
+  </si>
+  <si>
+    <t>击杀回复生命-自身最大生命值百万分比</t>
+  </si>
+  <si>
+    <t>self_have_effect</t>
+  </si>
+  <si>
+    <t>参数-自身拥有【效果id：&gt;=层数】时</t>
+  </si>
+  <si>
+    <t>参数14</t>
+  </si>
+  <si>
+    <t>击杀回复生命-目标最大生命值百万分比</t>
+  </si>
+  <si>
+    <t>target_have_effect</t>
+  </si>
+  <si>
+    <t>参数-目标拥有【效果id：&gt;=层数】时</t>
+  </si>
+  <si>
+    <t>获得护盾</t>
+  </si>
+  <si>
+    <t>参数15</t>
+  </si>
+  <si>
+    <t>击杀回复生命效果提高万分比</t>
+  </si>
+  <si>
+    <t>target_hp_ratio_over</t>
+  </si>
+  <si>
+    <t>参数-目标当前生命值&gt;=最大生命值的百万分之X时</t>
+  </si>
+  <si>
+    <t>回复生命</t>
+  </si>
+  <si>
+    <t>参数16</t>
+  </si>
+  <si>
+    <t>获得护盾-固定值</t>
+  </si>
+  <si>
+    <t>target_hp_ratio_under</t>
+  </si>
+  <si>
+    <t>参数-目标当前生命值&lt;=最大生命值的百万分之X时</t>
+  </si>
+  <si>
+    <t>击中目标</t>
+  </si>
+  <si>
+    <t>效果叠加层数</t>
+  </si>
+  <si>
+    <t>参数17</t>
+  </si>
+  <si>
+    <t>获得护盾-自身生命百万分比</t>
+  </si>
+  <si>
+    <t>to_target_effect_hit</t>
+  </si>
+  <si>
+    <t>参数-对目标施加【效果id】命中时</t>
+  </si>
+  <si>
+    <t>参数18</t>
+  </si>
+  <si>
+    <t>获得护盾-自身已损失生命万分比</t>
+  </si>
+  <si>
+    <t>参数19</t>
+  </si>
+  <si>
+    <t>获得护盾效果提高万分比</t>
+  </si>
+  <si>
+    <t>结算间隔时间（毫秒）</t>
+  </si>
+  <si>
+    <t>参数20</t>
+  </si>
+  <si>
+    <t>技能增加-固定值</t>
+  </si>
+  <si>
+    <t>参数21</t>
+  </si>
+  <si>
+    <t>技能增加-万分比</t>
+  </si>
+  <si>
+    <t>参数22</t>
+  </si>
+  <si>
+    <t>技能增加-普通攻击范围万分比</t>
+  </si>
+  <si>
+    <t>参数25LIST</t>
+  </si>
+  <si>
+    <t>攻击提高-攻击的元素类型</t>
+  </si>
+  <si>
+    <t>攻击提高-固定值</t>
+  </si>
+  <si>
+    <t>攻击提高-万分比</t>
+  </si>
+  <si>
+    <t>参数28</t>
+  </si>
+  <si>
+    <t>防御提高-固定值</t>
+  </si>
+  <si>
+    <t>参数29</t>
+  </si>
+  <si>
+    <t>防御提高-万分比</t>
+  </si>
+  <si>
+    <t>参数30</t>
+  </si>
+  <si>
+    <t>生命上限提高-固定值</t>
+  </si>
+  <si>
+    <t>参数31</t>
+  </si>
+  <si>
+    <t>生命上限提高-百万分比</t>
+  </si>
+  <si>
+    <t>参数32</t>
+  </si>
+  <si>
+    <t>攻击速度提高-万分比</t>
+  </si>
+  <si>
+    <t>参数33</t>
+  </si>
+  <si>
+    <t>移动速度提高-万分比</t>
+  </si>
+  <si>
+    <t>参数34</t>
+  </si>
+  <si>
+    <t>攻击范围提高-万分比</t>
+  </si>
+  <si>
+    <t>参数35</t>
+  </si>
+  <si>
+    <t>攻击目标数量提高-固定值</t>
+  </si>
+  <si>
+    <t>参数36</t>
+  </si>
+  <si>
+    <t>参数37</t>
+  </si>
+  <si>
+    <t>参数38</t>
+  </si>
+  <si>
+    <t>参数39</t>
+  </si>
+  <si>
+    <t>参数40</t>
+  </si>
+  <si>
+    <t>参数41</t>
+  </si>
+  <si>
+    <t>参数42</t>
+  </si>
+  <si>
+    <t>参数43</t>
+  </si>
+  <si>
+    <t>参数44</t>
+  </si>
+  <si>
+    <t>参数45</t>
+  </si>
+  <si>
+    <t>参数46</t>
+  </si>
+  <si>
+    <t>参数47</t>
+  </si>
+  <si>
+    <t>参数48</t>
+  </si>
+  <si>
+    <t>参数49</t>
+  </si>
+  <si>
+    <t>参数50</t>
+  </si>
+  <si>
+    <t>参数51</t>
+  </si>
+  <si>
+    <t>参数52</t>
+  </si>
+  <si>
+    <t>参数53</t>
+  </si>
+  <si>
+    <t>参数54</t>
+  </si>
+  <si>
+    <t>参数55</t>
+  </si>
+  <si>
+    <t>参数56</t>
+  </si>
+  <si>
+    <t>buff处理逻辑</t>
+  </si>
+  <si>
+    <t>不同组所有buff可叠加同时生效</t>
+  </si>
+  <si>
+    <t>同组buff是否互斥</t>
+  </si>
+  <si>
+    <t>同组buff不互斥时：结算buff时先时候查看同组重复cd</t>
+  </si>
+  <si>
+    <t>2.1.1</t>
+  </si>
+  <si>
+    <t>buff有cd，且同组重复cd&gt;0：直接把后来的buff丢掉</t>
+  </si>
+  <si>
+    <t>2.1.2</t>
+  </si>
+  <si>
+    <t>buff有cd，且同组重复cd=0：单个buff直接增加，多个buff增加优先级高的那个</t>
+  </si>
+  <si>
+    <t>2.1.3</t>
+  </si>
+  <si>
+    <t>buff没有cd：多个buff直接添加</t>
+  </si>
+  <si>
+    <t>同组buff互斥时，结算buff时先查看同组重复cd</t>
+  </si>
+  <si>
+    <t>2.2.1</t>
+  </si>
+  <si>
+    <t>2.2.2</t>
+  </si>
+  <si>
+    <t>buff有cd，且同组重复cd=0：单个buff直接增加，多个buff增加优先级高的那个，效果、持续时间、cd时间按优先级最高的时间</t>
+  </si>
+  <si>
+    <t>2.2.3</t>
+  </si>
+  <si>
+    <t>buff没有cd：同上，同2.2.2</t>
+  </si>
+  <si>
+    <t>buff组id</t>
+  </si>
+  <si>
+    <t>麻痹</t>
+  </si>
+  <si>
+    <t>燃烧</t>
+  </si>
+  <si>
+    <t>中毒</t>
+  </si>
+  <si>
+    <t>冰冻</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果-额外效果</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴风雪概率附加减速</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>减速</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>5001701:1</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>5001702:1</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>5001705:1</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>5001706:1</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴风雪概率附加冰冻</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
     <t>闪电链附加麻痹状态（无法攻击和移动），持续时间【参数5】（默认1000）毫秒，状态命中率【参数6】（默认20%）</t>
-  </si>
-  <si>
-    <t>5200701:0</t>
-  </si>
-  <si>
-    <t>连环闪电</t>
-  </si>
-  <si>
-    <t>击杀敌人时再次释放闪电链【参数4】</t>
-  </si>
-  <si>
-    <t>电刃普攻概率附加麻痹</t>
-  </si>
-  <si>
-    <t>电刃普攻麻痹状态（无法攻击和移动），持续时间【参数5】（默认1000）毫秒，状态命中率【参数6】（默认20%）</t>
-  </si>
-  <si>
-    <t>5200712:1</t>
-  </si>
-  <si>
-    <t>5200711:0</t>
-  </si>
-  <si>
-    <t>天罚</t>
-  </si>
-  <si>
-    <t>击杀敌人时再次释放超强电刃【参数4】</t>
-  </si>
-  <si>
-    <t>重复中buff组的cd时间（毫秒）</t>
-  </si>
-  <si>
-    <t>触发自动技能</t>
-  </si>
-  <si>
-    <t>主动技能</t>
-  </si>
-  <si>
-    <t>order</t>
-  </si>
-  <si>
-    <t>自动</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>冰霜新星</t>
-  </si>
-  <si>
-    <t>auto_cd</t>
-  </si>
-  <si>
-    <t>参数-重复触发自动释放冷却时间（毫秒）</t>
-  </si>
-  <si>
-    <t>陨石</t>
-  </si>
-  <si>
-    <t>release_ratio</t>
-  </si>
-  <si>
-    <t>参数-释放几率</t>
-  </si>
-  <si>
-    <t>死亡爆炸</t>
-  </si>
-  <si>
-    <t>release_num</t>
-  </si>
-  <si>
-    <t>参数-释放次数</t>
-  </si>
-  <si>
-    <t>闪电链</t>
-  </si>
-  <si>
-    <t>参数4LIST</t>
-  </si>
-  <si>
-    <t>触发的技能id</t>
-  </si>
-  <si>
-    <t>LIST&lt;INT&gt;_S</t>
-  </si>
-  <si>
-    <t>skill_id</t>
-  </si>
-  <si>
-    <t>参数-释放的技能id</t>
-  </si>
-  <si>
-    <t>电磁爆发</t>
-  </si>
-  <si>
-    <t>参数5</t>
-  </si>
-  <si>
-    <t>持续时间（毫秒）</t>
-  </si>
-  <si>
-    <t>total_attack_num</t>
-  </si>
-  <si>
-    <t>参数-累计发起攻击次数时</t>
-  </si>
-  <si>
-    <t>传染</t>
-  </si>
-  <si>
-    <t>参数6</t>
-  </si>
-  <si>
-    <t>效果基础命中率（万分比）</t>
-  </si>
-  <si>
-    <t>lose_hp_ratio</t>
-  </si>
-  <si>
-    <t>参数-损失自身生命最大值百万分比时</t>
-  </si>
-  <si>
-    <t>瘟疫</t>
-  </si>
-  <si>
-    <t>效果最大叠加层数</t>
-  </si>
-  <si>
-    <t>kill_target_after</t>
-  </si>
-  <si>
-    <t>参数-击杀目标后</t>
-  </si>
-  <si>
-    <t>复活</t>
-  </si>
-  <si>
-    <t>参数8</t>
-  </si>
-  <si>
-    <t>效果触发间隔（毫秒）</t>
-  </si>
-  <si>
-    <t>after_attack_crit</t>
-  </si>
-  <si>
-    <t>参数-攻击暴击后</t>
-  </si>
-  <si>
-    <t>半月斩</t>
-  </si>
-  <si>
-    <t>参数9</t>
-  </si>
-  <si>
-    <t>击中回复生命值-固定值</t>
-  </si>
-  <si>
-    <t>after_use_skill</t>
-  </si>
-  <si>
-    <t>参数-释放【技能id】后</t>
-  </si>
-  <si>
-    <t>旋风斩</t>
-  </si>
-  <si>
-    <t>参数10</t>
-  </si>
-  <si>
-    <t>击中回复生命值-自身最大生命值百万分比</t>
-  </si>
-  <si>
-    <t>cycle_time</t>
-  </si>
-  <si>
-    <t>参数-每过固定时间（毫秒）时</t>
-  </si>
-  <si>
-    <t>重击</t>
-  </si>
-  <si>
-    <t>参数11</t>
-  </si>
-  <si>
-    <t>击中回复效果提高万分比</t>
-  </si>
-  <si>
-    <t>after_skill_hit</t>
-  </si>
-  <si>
-    <t>参数-【技能id】命中后</t>
-  </si>
-  <si>
-    <t>多重打击</t>
-  </si>
-  <si>
-    <t>参数12</t>
-  </si>
-  <si>
-    <t>击杀回复生命-固定值</t>
-  </si>
-  <si>
-    <t>after_self_death</t>
-  </si>
-  <si>
-    <t>参数-自身死亡后释放</t>
-  </si>
-  <si>
-    <t>斩杀</t>
-  </si>
-  <si>
-    <t>参数13</t>
-  </si>
-  <si>
-    <t>击杀回复生命-自身最大生命值百万分比</t>
-  </si>
-  <si>
-    <t>self_have_effect</t>
-  </si>
-  <si>
-    <t>参数-自身拥有【效果id：&gt;=层数】时</t>
-  </si>
-  <si>
-    <t>参数14</t>
-  </si>
-  <si>
-    <t>击杀回复生命-目标最大生命值百万分比</t>
-  </si>
-  <si>
-    <t>target_have_effect</t>
-  </si>
-  <si>
-    <t>参数-目标拥有【效果id：&gt;=层数】时</t>
-  </si>
-  <si>
-    <t>获得护盾</t>
-  </si>
-  <si>
-    <t>参数15</t>
-  </si>
-  <si>
-    <t>击杀回复生命效果提高万分比</t>
-  </si>
-  <si>
-    <t>target_hp_ratio_over</t>
-  </si>
-  <si>
-    <t>参数-目标当前生命值&gt;=最大生命值的百万分之X时</t>
-  </si>
-  <si>
-    <t>回复生命</t>
-  </si>
-  <si>
-    <t>参数16</t>
-  </si>
-  <si>
-    <t>获得护盾-固定值</t>
-  </si>
-  <si>
-    <t>target_hp_ratio_under</t>
-  </si>
-  <si>
-    <t>参数-目标当前生命值&lt;=最大生命值的百万分之X时</t>
-  </si>
-  <si>
-    <t>击中目标</t>
-  </si>
-  <si>
-    <t>效果叠加层数</t>
-  </si>
-  <si>
-    <t>参数17</t>
-  </si>
-  <si>
-    <t>获得护盾-自身生命百万分比</t>
-  </si>
-  <si>
-    <t>to_target_effect_hit</t>
-  </si>
-  <si>
-    <t>参数-对目标施加【效果id】命中时</t>
-  </si>
-  <si>
-    <t>参数18</t>
-  </si>
-  <si>
-    <t>获得护盾-自身已损失生命万分比</t>
-  </si>
-  <si>
-    <t>参数19</t>
-  </si>
-  <si>
-    <t>获得护盾效果提高万分比</t>
-  </si>
-  <si>
-    <t>结算间隔时间（毫秒）</t>
-  </si>
-  <si>
-    <t>参数20</t>
-  </si>
-  <si>
-    <t>技能增加-固定值</t>
-  </si>
-  <si>
-    <t>参数21</t>
-  </si>
-  <si>
-    <t>技能增加-万分比</t>
-  </si>
-  <si>
-    <t>参数22</t>
-  </si>
-  <si>
-    <t>技能增加-普通攻击范围万分比</t>
-  </si>
-  <si>
-    <t>参数25LIST</t>
-  </si>
-  <si>
-    <t>攻击提高-攻击的元素类型</t>
-  </si>
-  <si>
-    <t>攻击提高-固定值</t>
-  </si>
-  <si>
-    <t>攻击提高-万分比</t>
-  </si>
-  <si>
-    <t>参数28</t>
-  </si>
-  <si>
-    <t>防御提高-固定值</t>
-  </si>
-  <si>
-    <t>参数29</t>
-  </si>
-  <si>
-    <t>防御提高-万分比</t>
-  </si>
-  <si>
-    <t>参数30</t>
-  </si>
-  <si>
-    <t>生命上限提高-固定值</t>
-  </si>
-  <si>
-    <t>参数31</t>
-  </si>
-  <si>
-    <t>生命上限提高-百万分比</t>
-  </si>
-  <si>
-    <t>参数32</t>
-  </si>
-  <si>
-    <t>攻击速度提高-万分比</t>
-  </si>
-  <si>
-    <t>参数33</t>
-  </si>
-  <si>
-    <t>移动速度提高-万分比</t>
-  </si>
-  <si>
-    <t>参数34</t>
-  </si>
-  <si>
-    <t>攻击范围提高-万分比</t>
-  </si>
-  <si>
-    <t>参数35</t>
-  </si>
-  <si>
-    <t>攻击目标数量提高-固定值</t>
-  </si>
-  <si>
-    <t>参数36</t>
-  </si>
-  <si>
-    <t>参数37</t>
-  </si>
-  <si>
-    <t>参数38</t>
-  </si>
-  <si>
-    <t>参数39</t>
-  </si>
-  <si>
-    <t>参数40</t>
-  </si>
-  <si>
-    <t>参数41</t>
-  </si>
-  <si>
-    <t>参数42</t>
-  </si>
-  <si>
-    <t>参数43</t>
-  </si>
-  <si>
-    <t>参数44</t>
-  </si>
-  <si>
-    <t>参数45</t>
-  </si>
-  <si>
-    <t>参数46</t>
-  </si>
-  <si>
-    <t>参数47</t>
-  </si>
-  <si>
-    <t>参数48</t>
-  </si>
-  <si>
-    <t>参数49</t>
-  </si>
-  <si>
-    <t>参数50</t>
-  </si>
-  <si>
-    <t>参数51</t>
-  </si>
-  <si>
-    <t>参数52</t>
-  </si>
-  <si>
-    <t>参数53</t>
-  </si>
-  <si>
-    <t>参数54</t>
-  </si>
-  <si>
-    <t>参数55</t>
-  </si>
-  <si>
-    <t>参数56</t>
-  </si>
-  <si>
-    <t>buff处理逻辑</t>
-  </si>
-  <si>
-    <t>不同组所有buff可叠加同时生效</t>
-  </si>
-  <si>
-    <t>同组buff是否互斥</t>
-  </si>
-  <si>
-    <t>同组buff不互斥时：结算buff时先时候查看同组重复cd</t>
-  </si>
-  <si>
-    <t>2.1.1</t>
-  </si>
-  <si>
-    <t>buff有cd，且同组重复cd&gt;0：直接把后来的buff丢掉</t>
-  </si>
-  <si>
-    <t>2.1.2</t>
-  </si>
-  <si>
-    <t>buff有cd，且同组重复cd=0：单个buff直接增加，多个buff增加优先级高的那个</t>
-  </si>
-  <si>
-    <t>2.1.3</t>
-  </si>
-  <si>
-    <t>buff没有cd：多个buff直接添加</t>
-  </si>
-  <si>
-    <t>同组buff互斥时，结算buff时先查看同组重复cd</t>
-  </si>
-  <si>
-    <t>2.2.1</t>
-  </si>
-  <si>
-    <t>2.2.2</t>
-  </si>
-  <si>
-    <t>buff有cd，且同组重复cd=0：单个buff直接增加，多个buff增加优先级高的那个，效果、持续时间、cd时间按优先级最高的时间</t>
-  </si>
-  <si>
-    <t>2.2.3</t>
-  </si>
-  <si>
-    <t>buff没有cd：同上，同2.2.2</t>
-  </si>
-  <si>
-    <t>buff组id</t>
-  </si>
-  <si>
-    <t>麻痹</t>
-  </si>
-  <si>
-    <t>燃烧</t>
-  </si>
-  <si>
-    <t>中毒</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴风雪减速状态（万分比降低攻速【参数1】和移速【参数2】），持续时间【参数5】毫秒，状态命中率【参数6】</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴风雪冰冻状态（无法攻击和移动），持续时间【参数5】毫秒，状态命中率【参数6】</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>5001502:1</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰爆被动</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰冻状态结束时触发冰爆技能【参数4】</t>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1601,7 +1658,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1639,6 +1696,9 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="差" xfId="2" builtinId="27"/>
@@ -1938,7 +1998,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG32"/>
+  <dimension ref="A1:AG35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -4740,7 +4800,7 @@
       </c>
       <c r="H29" s="13"/>
       <c r="I29" s="13" t="s">
-        <v>258</v>
+        <v>434</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>78</v>
@@ -4779,7 +4839,7 @@
         <v>1000</v>
       </c>
       <c r="V29" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="W29" s="13">
         <v>1500</v>
@@ -4832,14 +4892,14 @@
         <v>820034</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>228</v>
       </c>
       <c r="H30" s="13"/>
       <c r="I30" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>78</v>
@@ -4931,53 +4991,53 @@
         <v>5200800</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G31" s="12" t="s">
         <v>228</v>
       </c>
       <c r="H31" s="13"/>
       <c r="I31" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="J31" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="K31" s="13">
+        <v>1</v>
+      </c>
+      <c r="L31" s="13">
+        <v>0</v>
+      </c>
+      <c r="M31" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="N31" s="13">
+        <v>1</v>
+      </c>
+      <c r="O31" s="13">
+        <v>0</v>
+      </c>
+      <c r="P31" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q31" s="13">
+        <v>1</v>
+      </c>
+      <c r="R31" s="13">
+        <v>0</v>
+      </c>
+      <c r="S31" s="14">
+        <v>0</v>
+      </c>
+      <c r="T31" s="13" t="s">
         <v>263</v>
-      </c>
-      <c r="J31" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="K31" s="13">
-        <v>1</v>
-      </c>
-      <c r="L31" s="13">
-        <v>0</v>
-      </c>
-      <c r="M31" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="N31" s="13">
-        <v>1</v>
-      </c>
-      <c r="O31" s="13">
-        <v>0</v>
-      </c>
-      <c r="P31" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q31" s="13">
-        <v>1</v>
-      </c>
-      <c r="R31" s="13">
-        <v>0</v>
-      </c>
-      <c r="S31" s="14">
-        <v>0</v>
-      </c>
-      <c r="T31" s="13" t="s">
-        <v>264</v>
       </c>
       <c r="U31" s="13">
         <v>1000</v>
       </c>
       <c r="V31" s="13" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="W31" s="13">
         <v>0</v>
@@ -5030,14 +5090,14 @@
         <v>820054</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G32" s="12" t="s">
         <v>228</v>
       </c>
       <c r="H32" s="13"/>
       <c r="I32" s="13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J32" s="13" t="s">
         <v>78</v>
@@ -5109,6 +5169,303 @@
         <v>78</v>
       </c>
       <c r="AG32" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A33" s="4">
+        <v>820061</v>
+      </c>
+      <c r="B33" s="13">
+        <v>102</v>
+      </c>
+      <c r="C33" s="14">
+        <v>1</v>
+      </c>
+      <c r="D33" s="14">
+        <v>0</v>
+      </c>
+      <c r="E33" s="13">
+        <v>5001800</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="J33" s="13" t="s">
+        <v>429</v>
+      </c>
+      <c r="K33" s="13">
+        <v>1</v>
+      </c>
+      <c r="L33" s="13">
+        <v>2000</v>
+      </c>
+      <c r="M33" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="N33" s="13">
+        <v>1</v>
+      </c>
+      <c r="O33" s="13">
+        <v>2000</v>
+      </c>
+      <c r="P33" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q33" s="13">
+        <v>1</v>
+      </c>
+      <c r="R33" s="13">
+        <v>0</v>
+      </c>
+      <c r="S33" s="14">
+        <v>0</v>
+      </c>
+      <c r="T33" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="U33" s="13">
+        <v>3000</v>
+      </c>
+      <c r="V33" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="W33" s="13">
+        <v>2000</v>
+      </c>
+      <c r="X33" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y33" s="13">
+        <v>1</v>
+      </c>
+      <c r="Z33" s="13">
+        <v>1</v>
+      </c>
+      <c r="AA33" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB33" s="13">
+        <v>1</v>
+      </c>
+      <c r="AC33" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE33" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF33" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG33" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A34" s="4">
+        <v>821061</v>
+      </c>
+      <c r="B34" s="13">
+        <v>102</v>
+      </c>
+      <c r="C34" s="14">
+        <v>1</v>
+      </c>
+      <c r="D34" s="14">
+        <v>0</v>
+      </c>
+      <c r="E34" s="13">
+        <v>5001600</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="J34" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="K34" s="13">
+        <v>1</v>
+      </c>
+      <c r="L34" s="13">
+        <v>0</v>
+      </c>
+      <c r="M34" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="N34" s="13">
+        <v>1</v>
+      </c>
+      <c r="O34" s="13">
+        <v>0</v>
+      </c>
+      <c r="P34" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q34" s="13">
+        <v>1</v>
+      </c>
+      <c r="R34" s="13">
+        <v>0</v>
+      </c>
+      <c r="S34" s="14">
+        <v>0</v>
+      </c>
+      <c r="T34" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="U34" s="13">
+        <v>1000</v>
+      </c>
+      <c r="V34" s="13" t="s">
+        <v>429</v>
+      </c>
+      <c r="W34" s="13">
+        <v>0</v>
+      </c>
+      <c r="X34" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y34" s="13">
+        <v>1</v>
+      </c>
+      <c r="Z34" s="13">
+        <v>1</v>
+      </c>
+      <c r="AA34" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB34" s="13">
+        <v>1</v>
+      </c>
+      <c r="AC34" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE34" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF34" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG34" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="35" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A35" s="13">
+        <v>820072</v>
+      </c>
+      <c r="B35" s="13">
+        <v>20072</v>
+      </c>
+      <c r="C35" s="14">
+        <v>1</v>
+      </c>
+      <c r="D35" s="14">
+        <v>0</v>
+      </c>
+      <c r="E35" s="23">
+        <v>820072</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="J35" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="K35" s="13">
+        <v>1</v>
+      </c>
+      <c r="L35" s="13">
+        <v>0</v>
+      </c>
+      <c r="M35" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="N35" s="13">
+        <v>1</v>
+      </c>
+      <c r="O35" s="13">
+        <v>0</v>
+      </c>
+      <c r="P35" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q35" s="13">
+        <v>1</v>
+      </c>
+      <c r="R35" s="13">
+        <v>0</v>
+      </c>
+      <c r="S35" s="14">
+        <v>20071</v>
+      </c>
+      <c r="T35" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="U35" s="13">
+        <v>-1</v>
+      </c>
+      <c r="V35" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="W35" s="13">
+        <v>10000</v>
+      </c>
+      <c r="X35" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y35" s="13">
+        <v>1</v>
+      </c>
+      <c r="Z35" s="13">
+        <v>1</v>
+      </c>
+      <c r="AA35" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB35" s="13">
+        <v>1</v>
+      </c>
+      <c r="AC35" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE35" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF35" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG35" s="8" t="s">
         <v>78</v>
       </c>
     </row>
@@ -5164,7 +5521,7 @@
         <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11" spans="5:19" x14ac:dyDescent="0.15">
@@ -5191,10 +5548,10 @@
         <v>47</v>
       </c>
       <c r="J13" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="S13" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="14" spans="5:19" x14ac:dyDescent="0.15">
@@ -5211,10 +5568,10 @@
         <v>1</v>
       </c>
       <c r="K14" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="L14" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="15" spans="5:19" x14ac:dyDescent="0.15">
@@ -5228,13 +5585,13 @@
         <v>3</v>
       </c>
       <c r="K15" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="L15" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="S15" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="16" spans="5:19" x14ac:dyDescent="0.15">
@@ -5251,13 +5608,13 @@
         <v>7</v>
       </c>
       <c r="K16" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="L16" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="L16" s="1" t="s">
+      <c r="S16" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="17" spans="5:19" x14ac:dyDescent="0.15">
@@ -5274,13 +5631,13 @@
         <v>7</v>
       </c>
       <c r="K17" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="L17" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="L17" s="1" t="s">
+      <c r="S17" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="S17" s="1" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="18" spans="5:19" x14ac:dyDescent="0.15">
@@ -5297,13 +5654,13 @@
         <v>7</v>
       </c>
       <c r="K18" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="L18" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="L18" s="1" t="s">
+      <c r="S18" s="1" t="s">
         <v>283</v>
-      </c>
-      <c r="S18" s="1" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="19" spans="5:19" x14ac:dyDescent="0.15">
@@ -5318,22 +5675,22 @@
         <v>参数4LIST-触发的技能id</v>
       </c>
       <c r="H19" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="I19" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="J19" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="K19" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="L19" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="L19" s="1" t="s">
+      <c r="S19" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="20" spans="5:19" x14ac:dyDescent="0.15">
@@ -5348,22 +5705,22 @@
         <v>参数5-持续时间（毫秒）</v>
       </c>
       <c r="H20" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="I20" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="J20" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="K20" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="K20" s="1" t="s">
+      <c r="L20" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="L20" s="1" t="s">
+      <c r="S20" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="21" spans="5:19" x14ac:dyDescent="0.15">
@@ -5378,22 +5735,22 @@
         <v>参数6-效果基础命中率（万分比）</v>
       </c>
       <c r="H21" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>297</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K21" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="L21" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="L21" s="1" t="s">
+      <c r="S21" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="22" spans="5:19" x14ac:dyDescent="0.15">
@@ -5411,19 +5768,19 @@
         <v>66</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K22" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="L22" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="L22" s="1" t="s">
+      <c r="S22" s="1" t="s">
         <v>303</v>
-      </c>
-      <c r="S22" s="1" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="23" spans="5:19" x14ac:dyDescent="0.15">
@@ -5438,22 +5795,22 @@
         <v>参数8-效果触发间隔（毫秒）</v>
       </c>
       <c r="H23" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="I23" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>306</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K23" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="L23" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="L23" s="1" t="s">
+      <c r="S23" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="S23" s="1" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="24" spans="5:19" x14ac:dyDescent="0.15">
@@ -5468,22 +5825,22 @@
         <v>参数9-击中回复生命值-固定值</v>
       </c>
       <c r="H24" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="I24" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="J24" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="K24" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="J24" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="K24" s="1" t="s">
+      <c r="L24" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="L24" s="1" t="s">
+      <c r="S24" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="S24" s="1" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="25" spans="5:19" x14ac:dyDescent="0.15">
@@ -5498,22 +5855,22 @@
         <v>参数10-击中回复生命值-自身最大生命值百万分比</v>
       </c>
       <c r="H25" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="I25" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>316</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K25" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="L25" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="L25" s="1" t="s">
+      <c r="S25" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="S25" s="1" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="26" spans="5:19" x14ac:dyDescent="0.15">
@@ -5528,22 +5885,22 @@
         <v>参数11-击中回复效果提高万分比</v>
       </c>
       <c r="H26" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="I26" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="J26" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="K26" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="J26" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="K26" s="1" t="s">
+      <c r="L26" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="L26" s="1" t="s">
+      <c r="S26" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="S26" s="1" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="27" spans="5:19" x14ac:dyDescent="0.15">
@@ -5558,22 +5915,22 @@
         <v>参数12-击杀回复生命-固定值</v>
       </c>
       <c r="H27" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="I27" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>326</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K27" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="L27" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L27" s="1" t="s">
+      <c r="S27" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="S27" s="1" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="28" spans="5:19" x14ac:dyDescent="0.15">
@@ -5588,19 +5945,19 @@
         <v>参数13-击杀回复生命-自身最大生命值百万分比</v>
       </c>
       <c r="H28" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="I28" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>331</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K28" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="L28" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="29" spans="5:19" x14ac:dyDescent="0.15">
@@ -5615,22 +5972,22 @@
         <v>参数14-击杀回复生命-目标最大生命值百万分比</v>
       </c>
       <c r="H29" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="I29" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>335</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K29" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="L29" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="L29" s="1" t="s">
+      <c r="S29" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="30" spans="5:19" x14ac:dyDescent="0.15">
@@ -5645,22 +6002,22 @@
         <v>参数15-击杀回复生命效果提高万分比</v>
       </c>
       <c r="H30" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="I30" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>340</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K30" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="L30" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="L30" s="1" t="s">
+      <c r="S30" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="31" spans="5:19" x14ac:dyDescent="0.15">
@@ -5675,22 +6032,22 @@
         <v>参数16-获得护盾-固定值</v>
       </c>
       <c r="H31" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="I31" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>345</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K31" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="L31" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="L31" s="1" t="s">
+      <c r="S31" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="S31" s="1" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="32" spans="5:19" x14ac:dyDescent="0.15">
@@ -5698,26 +6055,26 @@
         <v>33</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G32" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数17-获得护盾-自身生命百万分比</v>
       </c>
       <c r="H32" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="I32" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="J32" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="K32" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="J32" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="K32" s="1" t="s">
+      <c r="L32" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="33" spans="5:9" x14ac:dyDescent="0.15">
@@ -5732,10 +6089,10 @@
         <v>参数18-获得护盾-自身已损失生命万分比</v>
       </c>
       <c r="H33" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="I33" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="34" spans="5:9" x14ac:dyDescent="0.15">
@@ -5750,10 +6107,10 @@
         <v>参数19-获得护盾效果提高万分比</v>
       </c>
       <c r="H34" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="I34" s="1" t="s">
         <v>356</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="35" spans="5:9" x14ac:dyDescent="0.15">
@@ -5761,17 +6118,17 @@
         <v>36</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G35" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数20-技能增加-固定值</v>
       </c>
       <c r="H35" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="I35" s="1" t="s">
         <v>359</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="36" spans="5:9" x14ac:dyDescent="0.15">
@@ -5780,10 +6137,10 @@
         <v>参数21-技能增加-万分比</v>
       </c>
       <c r="H36" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="I36" s="1" t="s">
         <v>361</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="37" spans="5:9" x14ac:dyDescent="0.15">
@@ -5792,10 +6149,10 @@
         <v>参数22-技能增加-普通攻击范围万分比</v>
       </c>
       <c r="H37" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="I37" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="38" spans="5:9" x14ac:dyDescent="0.15">
@@ -5804,10 +6161,10 @@
         <v>参数25LIST-攻击提高-攻击的元素类型</v>
       </c>
       <c r="H38" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>365</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="39" spans="5:9" x14ac:dyDescent="0.15">
@@ -5816,10 +6173,10 @@
         <v>参数25LIST-攻击提高-固定值</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="40" spans="5:9" x14ac:dyDescent="0.15">
@@ -5828,10 +6185,10 @@
         <v>参数25LIST-攻击提高-万分比</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="41" spans="5:9" x14ac:dyDescent="0.15">
@@ -5840,10 +6197,10 @@
         <v>参数28-防御提高-固定值</v>
       </c>
       <c r="H41" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="I41" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="42" spans="5:9" x14ac:dyDescent="0.15">
@@ -5852,10 +6209,10 @@
         <v>参数29-防御提高-万分比</v>
       </c>
       <c r="H42" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="I42" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="43" spans="5:9" x14ac:dyDescent="0.15">
@@ -5864,10 +6221,10 @@
         <v>参数30-生命上限提高-固定值</v>
       </c>
       <c r="H43" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="I43" s="1" t="s">
         <v>373</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="44" spans="5:9" x14ac:dyDescent="0.15">
@@ -5876,10 +6233,10 @@
         <v>参数31-生命上限提高-百万分比</v>
       </c>
       <c r="H44" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="I44" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="45" spans="5:9" x14ac:dyDescent="0.15">
@@ -5888,10 +6245,10 @@
         <v>参数32-攻击速度提高-万分比</v>
       </c>
       <c r="H45" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="I45" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="46" spans="5:9" x14ac:dyDescent="0.15">
@@ -5900,10 +6257,10 @@
         <v>参数33-移动速度提高-万分比</v>
       </c>
       <c r="H46" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="I46" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="47" spans="5:9" x14ac:dyDescent="0.15">
@@ -5912,10 +6269,10 @@
         <v>参数34-攻击范围提高-万分比</v>
       </c>
       <c r="H47" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="I47" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="48" spans="5:9" x14ac:dyDescent="0.15">
@@ -5924,10 +6281,10 @@
         <v>参数35-攻击目标数量提高-固定值</v>
       </c>
       <c r="H48" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="I48" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="49" spans="7:8" x14ac:dyDescent="0.15">
@@ -5936,7 +6293,7 @@
         <v>参数36-</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="50" spans="7:8" x14ac:dyDescent="0.15">
@@ -5945,7 +6302,7 @@
         <v>参数37-</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="51" spans="7:8" x14ac:dyDescent="0.15">
@@ -5954,7 +6311,7 @@
         <v>参数38-</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="52" spans="7:8" x14ac:dyDescent="0.15">
@@ -5963,7 +6320,7 @@
         <v>参数39-</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="53" spans="7:8" x14ac:dyDescent="0.15">
@@ -5972,7 +6329,7 @@
         <v>参数40-</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="54" spans="7:8" x14ac:dyDescent="0.15">
@@ -5981,7 +6338,7 @@
         <v>参数41-</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="55" spans="7:8" x14ac:dyDescent="0.15">
@@ -5990,7 +6347,7 @@
         <v>参数42-</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="56" spans="7:8" x14ac:dyDescent="0.15">
@@ -5999,7 +6356,7 @@
         <v>参数41-</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="57" spans="7:8" x14ac:dyDescent="0.15">
@@ -6008,7 +6365,7 @@
         <v>参数42-</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="58" spans="7:8" x14ac:dyDescent="0.15">
@@ -6017,7 +6374,7 @@
         <v>参数43-</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="59" spans="7:8" x14ac:dyDescent="0.15">
@@ -6026,7 +6383,7 @@
         <v>参数44-</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="60" spans="7:8" x14ac:dyDescent="0.15">
@@ -6035,7 +6392,7 @@
         <v>参数45-</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="61" spans="7:8" x14ac:dyDescent="0.15">
@@ -6044,7 +6401,7 @@
         <v>参数46-</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="62" spans="7:8" x14ac:dyDescent="0.15">
@@ -6053,7 +6410,7 @@
         <v>参数47-</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="63" spans="7:8" x14ac:dyDescent="0.15">
@@ -6062,7 +6419,7 @@
         <v>参数48-</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="64" spans="7:8" x14ac:dyDescent="0.15">
@@ -6071,7 +6428,7 @@
         <v>参数49-</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="65" spans="7:8" x14ac:dyDescent="0.15">
@@ -6080,7 +6437,7 @@
         <v>参数50-</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="66" spans="7:8" x14ac:dyDescent="0.15">
@@ -6089,7 +6446,7 @@
         <v>参数51-</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="67" spans="7:8" x14ac:dyDescent="0.15">
@@ -6098,7 +6455,7 @@
         <v>参数52-</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="68" spans="7:8" x14ac:dyDescent="0.15">
@@ -6107,7 +6464,7 @@
         <v>参数53-</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="69" spans="7:8" x14ac:dyDescent="0.15">
@@ -6116,7 +6473,7 @@
         <v>参数54-</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="70" spans="7:8" x14ac:dyDescent="0.15">
@@ -6125,7 +6482,7 @@
         <v>参数55-</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="71" spans="7:8" x14ac:dyDescent="0.15">
@@ -6134,7 +6491,7 @@
         <v>参数56-</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -6158,7 +6515,7 @@
   <sheetData>
     <row r="6" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D6" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -6167,7 +6524,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="8" spans="4:5" x14ac:dyDescent="0.15">
@@ -6179,7 +6536,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="10" spans="4:5" x14ac:dyDescent="0.15">
@@ -6187,31 +6544,31 @@
         <v>2.1</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="11" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D11" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>410</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="12" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D12" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>412</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="13" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D13" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>414</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="14" spans="4:5" x14ac:dyDescent="0.15">
@@ -6223,41 +6580,41 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="16" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D16" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="17" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D17" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>418</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="18" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D18" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>420</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="28" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D28" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="29" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D29" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E29" s="1">
         <v>101</v>
@@ -6265,45 +6622,59 @@
     </row>
     <row r="30" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D30" s="1" t="s">
-        <v>424</v>
+        <v>428</v>
+      </c>
+      <c r="E30" s="1">
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D31" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="32" spans="4:5" x14ac:dyDescent="0.15">
+      <c r="D32" s="1" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="33" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="D33" s="1" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="33" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="E33" s="1">
+        <v>105</v>
+      </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="34" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F34"/>
     </row>
-    <row r="35" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="35" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F35"/>
     </row>
-    <row r="36" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="36" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F36"/>
     </row>
-    <row r="37" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="37" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F37"/>
     </row>
-    <row r="38" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="38" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F38"/>
     </row>
-    <row r="39" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="39" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F39"/>
     </row>
-    <row r="40" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="40" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F40"/>
     </row>
-    <row r="41" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="41" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F41"/>
     </row>
-    <row r="42" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="42" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F42"/>
     </row>
-    <row r="43" spans="6:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="43" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F43"/>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D3FB15A-E738-4A45-A640-8F502DB34723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -29,6 +23,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,34 +32,32 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>pe</author>
     <author>cltx</author>
   </authors>
   <commentList>
-    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="C4" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>数字越大，优先级越高</t>
         </r>
       </text>
     </comment>
-    <comment ref="K4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="K4" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>cltx:</t>
@@ -72,7 +66,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -82,13 +75,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="U4" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">&gt;0，持续时间
@@ -103,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="438">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -879,6 +871,9 @@
     <t>闪电链概率附加麻痹</t>
   </si>
   <si>
+    <t>闪电链附加麻痹状态（无法攻击和移动），持续时间【参数5】（默认1000）毫秒，状态命中率【参数6】（默认20%）</t>
+  </si>
+  <si>
     <t>5200701:0</t>
   </si>
   <si>
@@ -906,6 +901,36 @@
     <t>击杀敌人时再次释放超强电刃【参数4】</t>
   </si>
   <si>
+    <t>暴风雪概率附加减速</t>
+  </si>
+  <si>
+    <t>暴风雪减速状态（万分比降低攻速【参数1】和移速【参数2】），持续时间【参数5】毫秒，状态命中率【参数6】</t>
+  </si>
+  <si>
+    <t>5001701:1</t>
+  </si>
+  <si>
+    <t>5001702:1</t>
+  </si>
+  <si>
+    <t>5001705:1</t>
+  </si>
+  <si>
+    <t>5001706:1</t>
+  </si>
+  <si>
+    <t>暴风雪概率附加冰冻</t>
+  </si>
+  <si>
+    <t>暴风雪冰冻状态（无法攻击和移动），持续时间【参数5】毫秒，状态命中率【参数6】</t>
+  </si>
+  <si>
+    <t>冰爆被动</t>
+  </si>
+  <si>
+    <t>冰冻状态结束时触发冰爆技能【参数4】</t>
+  </si>
+  <si>
     <t>重复中buff组的cd时间（毫秒）</t>
   </si>
   <si>
@@ -1374,6 +1399,9 @@
     <t>麻痹</t>
   </si>
   <si>
+    <t>减速</t>
+  </si>
+  <si>
     <t>燃烧</t>
   </si>
   <si>
@@ -1381,70 +1409,19 @@
   </si>
   <si>
     <t>冰冻</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能效果-额外效果</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴风雪概率附加减速</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>减速</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>5001701:1</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>5001702:1</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>5001705:1</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>5001706:1</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴风雪概率附加冰冻</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>闪电链附加麻痹状态（无法攻击和移动），持续时间【参数5】（默认1000）毫秒，状态命中率【参数6】（默认20%）</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴风雪减速状态（万分比降低攻速【参数1】和移速【参数2】），持续时间【参数5】毫秒，状态命中率【参数6】</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴风雪冰冻状态（无法攻击和移动），持续时间【参数5】毫秒，状态命中率【参数6】</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>5001502:1</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰爆被动</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰冻状态结束时触发冰爆技能【参数4】</t>
-    <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1456,35 +1433,30 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF9C5700"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <color theme="0" tint="-4.9989318521683403E-2"/>
+      <color theme="0" tint="-0.0499893185216834"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1492,14 +1464,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1507,35 +1477,153 @@
       <sz val="9"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1543,24 +1631,15 @@
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1569,13 +1648,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <fgColor theme="0" tint="-0.349986266670736"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79970702230903046"/>
+        <fgColor theme="8" tint="0.79970702230903"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1593,7 +1672,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1603,8 +1706,152 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1642,23 +1889,241 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1673,8 +2138,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="24" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1682,39 +2147,80 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="23" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="24" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="24" applyFont="1" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="5">
-    <cellStyle name="差" xfId="2" builtinId="27"/>
-    <cellStyle name="差 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="适中" xfId="3" builtinId="28"/>
-    <cellStyle name="输入" xfId="1" builtinId="20"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="差 2" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1992,14 +2498,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AG35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -2030,7 +2536,7 @@
     <col min="33" max="33" width="17.125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2063,7 +2569,7 @@
       <c r="AB1" s="4"/>
       <c r="AC1" s="4"/>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:33">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -2100,13 +2606,13 @@
       <c r="L2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="M2" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="N2" s="15" t="s">
+      <c r="N2" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="15" t="s">
+      <c r="O2" s="16" t="s">
         <v>2</v>
       </c>
       <c r="P2" s="4" t="s">
@@ -2118,7 +2624,7 @@
       <c r="R2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="S2" s="15" t="s">
+      <c r="S2" s="16" t="s">
         <v>5</v>
       </c>
       <c r="T2" s="4" t="s">
@@ -2142,29 +2648,29 @@
       <c r="Z2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="AA2" s="15" t="s">
+      <c r="AA2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="AB2" s="15" t="s">
+      <c r="AB2" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="AC2" s="15" t="s">
+      <c r="AC2" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="AD2" s="19" t="s">
+      <c r="AD2" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="AE2" s="19" t="s">
+      <c r="AE2" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="AF2" s="19" t="s">
+      <c r="AF2" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="AG2" s="19" t="s">
+      <c r="AG2" s="20" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:33">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
@@ -2201,13 +2707,13 @@
       <c r="L3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="15" t="s">
+      <c r="N3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="15" t="s">
+      <c r="O3" s="16" t="s">
         <v>22</v>
       </c>
       <c r="P3" s="4" t="s">
@@ -2219,7 +2725,7 @@
       <c r="R3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="S3" s="15" t="s">
+      <c r="S3" s="16" t="s">
         <v>26</v>
       </c>
       <c r="T3" s="4" t="s">
@@ -2243,29 +2749,29 @@
       <c r="Z3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="AA3" s="15" t="s">
+      <c r="AA3" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="AB3" s="15" t="s">
+      <c r="AB3" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="AC3" s="15" t="s">
+      <c r="AC3" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="AD3" s="19" t="s">
+      <c r="AD3" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="AE3" s="19" t="s">
+      <c r="AE3" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="AF3" s="19" t="s">
+      <c r="AF3" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="AG3" s="19" t="s">
+      <c r="AG3" s="20" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:33">
       <c r="A4" s="4" t="s">
         <v>41</v>
       </c>
@@ -2302,13 +2808,13 @@
       <c r="L4" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="M4" s="15" t="s">
+      <c r="M4" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="N4" s="15" t="s">
+      <c r="N4" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="O4" s="15" t="s">
+      <c r="O4" s="16" t="s">
         <v>55</v>
       </c>
       <c r="P4" s="4" t="s">
@@ -2320,7 +2826,7 @@
       <c r="R4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="S4" s="15" t="s">
+      <c r="S4" s="16" t="s">
         <v>59</v>
       </c>
       <c r="T4" s="4" t="s">
@@ -2344,29 +2850,29 @@
       <c r="Z4" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AA4" s="15" t="s">
+      <c r="AA4" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="AB4" s="15" t="s">
+      <c r="AB4" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="AC4" s="15" t="s">
+      <c r="AC4" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="AD4" s="19" t="s">
+      <c r="AD4" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="AE4" s="19" t="s">
+      <c r="AE4" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="AF4" s="19" t="s">
+      <c r="AF4" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="AG4" s="19" t="s">
+      <c r="AG4" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33">
       <c r="A5" s="6">
         <v>1000001</v>
       </c>
@@ -2394,7 +2900,7 @@
       <c r="I5" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="J5" s="20" t="s">
+      <c r="J5" s="21" t="s">
         <v>78</v>
       </c>
       <c r="K5" s="6">
@@ -2403,16 +2909,16 @@
       <c r="L5" s="6">
         <v>400000</v>
       </c>
-      <c r="M5" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="N5" s="16">
-        <v>1</v>
-      </c>
-      <c r="O5" s="16">
-        <v>0</v>
-      </c>
-      <c r="P5" s="20" t="s">
+      <c r="M5" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="N5" s="17">
+        <v>1</v>
+      </c>
+      <c r="O5" s="17">
+        <v>0</v>
+      </c>
+      <c r="P5" s="21" t="s">
         <v>78</v>
       </c>
       <c r="Q5" s="6">
@@ -2421,16 +2927,16 @@
       <c r="R5" s="6">
         <v>0</v>
       </c>
-      <c r="S5" s="17">
-        <v>0</v>
-      </c>
-      <c r="T5" s="20" t="s">
+      <c r="S5" s="18">
+        <v>0</v>
+      </c>
+      <c r="T5" s="21" t="s">
         <v>78</v>
       </c>
       <c r="U5" s="6">
         <v>0</v>
       </c>
-      <c r="V5" s="20" t="s">
+      <c r="V5" s="21" t="s">
         <v>78</v>
       </c>
       <c r="W5" s="6">
@@ -2445,13 +2951,13 @@
       <c r="Z5" s="6">
         <v>0</v>
       </c>
-      <c r="AA5" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB5" s="16">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="16">
+      <c r="AA5" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB5" s="17">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="17">
         <v>0</v>
       </c>
       <c r="AD5" s="8" t="s">
@@ -2467,7 +2973,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33">
       <c r="A6" s="7">
         <v>2000001</v>
       </c>
@@ -2513,7 +3019,7 @@
       <c r="O6" s="7">
         <v>0</v>
       </c>
-      <c r="P6" s="22" t="s">
+      <c r="P6" s="23" t="s">
         <v>78</v>
       </c>
       <c r="Q6" s="7">
@@ -2522,22 +3028,22 @@
       <c r="R6" s="7">
         <v>0</v>
       </c>
-      <c r="S6" s="18">
-        <v>0</v>
-      </c>
-      <c r="T6" s="22" t="s">
+      <c r="S6" s="19">
+        <v>0</v>
+      </c>
+      <c r="T6" s="23" t="s">
         <v>78</v>
       </c>
       <c r="U6" s="7">
         <v>0</v>
       </c>
-      <c r="V6" s="22" t="s">
+      <c r="V6" s="23" t="s">
         <v>78</v>
       </c>
       <c r="W6" s="7">
         <v>10000</v>
       </c>
-      <c r="X6" s="22" t="s">
+      <c r="X6" s="23" t="s">
         <v>78</v>
       </c>
       <c r="Y6" s="7">
@@ -2568,7 +3074,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33">
       <c r="A7" s="8">
         <v>54010001</v>
       </c>
@@ -2669,7 +3175,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33">
       <c r="A8" s="8">
         <v>54020001</v>
       </c>
@@ -2770,7 +3276,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33">
       <c r="A9" s="8">
         <v>54030001</v>
       </c>
@@ -2871,7 +3377,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33">
       <c r="A10" s="8">
         <v>54040001</v>
       </c>
@@ -2972,7 +3478,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33">
       <c r="A11" s="8">
         <v>54050001</v>
       </c>
@@ -3073,7 +3579,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:33">
       <c r="A12" s="8">
         <v>54060001</v>
       </c>
@@ -3174,7 +3680,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33">
       <c r="A13" s="8">
         <v>54070001</v>
       </c>
@@ -3275,7 +3781,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:33">
       <c r="A14" s="8">
         <v>54080001</v>
       </c>
@@ -3376,7 +3882,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33">
       <c r="A15" s="8">
         <v>54090001</v>
       </c>
@@ -3477,7 +3983,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33">
       <c r="A16" s="8">
         <v>54100001</v>
       </c>
@@ -3578,7 +4084,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:33">
       <c r="A17" s="8">
         <v>54110001</v>
       </c>
@@ -3679,7 +4185,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:33">
       <c r="A18" s="8">
         <v>54120001</v>
       </c>
@@ -3780,7 +4286,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:33">
       <c r="A19" s="8">
         <v>54130001</v>
       </c>
@@ -3881,7 +4387,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:33">
       <c r="A20" s="8">
         <v>54140001</v>
       </c>
@@ -3982,7 +4488,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:33">
       <c r="A21" s="8">
         <v>54150001</v>
       </c>
@@ -4083,7 +4589,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:33">
       <c r="A22" s="10">
         <v>59130001</v>
       </c>
@@ -4180,7 +4686,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:33">
       <c r="A23" s="10">
         <v>59140001</v>
       </c>
@@ -4277,7 +4783,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:33">
       <c r="A24" s="13">
         <v>85001500</v>
       </c>
@@ -4376,7 +4882,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:33">
       <c r="A25" s="13">
         <v>85101100</v>
       </c>
@@ -4477,7 +4983,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:33">
       <c r="A26" s="13">
         <v>85200700</v>
       </c>
@@ -4576,7 +5082,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:33">
       <c r="A27" s="13">
         <v>820001</v>
       </c>
@@ -4677,7 +5183,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:33">
       <c r="A28" s="13">
         <v>820011</v>
       </c>
@@ -4776,7 +5282,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:33">
       <c r="A29" s="13">
         <v>820031</v>
       </c>
@@ -4800,7 +5306,7 @@
       </c>
       <c r="H29" s="13"/>
       <c r="I29" s="13" t="s">
-        <v>434</v>
+        <v>258</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>78</v>
@@ -4839,7 +5345,7 @@
         <v>1000</v>
       </c>
       <c r="V29" s="13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="W29" s="13">
         <v>1500</v>
@@ -4875,7 +5381,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:33">
       <c r="A30" s="13">
         <v>820034</v>
       </c>
@@ -4892,14 +5398,14 @@
         <v>820034</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>228</v>
       </c>
       <c r="H30" s="13"/>
       <c r="I30" s="13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>78</v>
@@ -4974,7 +5480,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:33">
       <c r="A31" s="4">
         <v>820051</v>
       </c>
@@ -4991,14 +5497,14 @@
         <v>5200800</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G31" s="12" t="s">
         <v>228</v>
       </c>
       <c r="H31" s="13"/>
       <c r="I31" s="13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>78</v>
@@ -5031,13 +5537,13 @@
         <v>0</v>
       </c>
       <c r="T31" s="13" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="U31" s="13">
         <v>1000</v>
       </c>
       <c r="V31" s="13" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="W31" s="13">
         <v>0</v>
@@ -5073,7 +5579,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:33">
       <c r="A32" s="13">
         <v>820054</v>
       </c>
@@ -5090,14 +5596,14 @@
         <v>820054</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G32" s="12" t="s">
         <v>228</v>
       </c>
       <c r="H32" s="13"/>
       <c r="I32" s="13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J32" s="13" t="s">
         <v>78</v>
@@ -5172,7 +5678,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:33">
       <c r="A33" s="4">
         <v>820061</v>
       </c>
@@ -5189,17 +5695,17 @@
         <v>5001800</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>427</v>
+        <v>268</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>426</v>
+        <v>228</v>
       </c>
       <c r="H33" s="13"/>
       <c r="I33" s="13" t="s">
-        <v>435</v>
+        <v>269</v>
       </c>
       <c r="J33" s="13" t="s">
-        <v>429</v>
+        <v>270</v>
       </c>
       <c r="K33" s="13">
         <v>1</v>
@@ -5208,7 +5714,7 @@
         <v>2000</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>430</v>
+        <v>271</v>
       </c>
       <c r="N33" s="13">
         <v>1</v>
@@ -5229,13 +5735,13 @@
         <v>0</v>
       </c>
       <c r="T33" s="13" t="s">
-        <v>431</v>
+        <v>272</v>
       </c>
       <c r="U33" s="13">
         <v>3000</v>
       </c>
       <c r="V33" s="13" t="s">
-        <v>432</v>
+        <v>273</v>
       </c>
       <c r="W33" s="13">
         <v>2000</v>
@@ -5271,7 +5777,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:33">
       <c r="A34" s="4">
         <v>821061</v>
       </c>
@@ -5288,14 +5794,14 @@
         <v>5001600</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>433</v>
+        <v>274</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>426</v>
+        <v>228</v>
       </c>
       <c r="H34" s="13"/>
       <c r="I34" s="13" t="s">
-        <v>436</v>
+        <v>275</v>
       </c>
       <c r="J34" s="13" t="s">
         <v>78</v>
@@ -5328,13 +5834,13 @@
         <v>0</v>
       </c>
       <c r="T34" s="13" t="s">
-        <v>437</v>
+        <v>230</v>
       </c>
       <c r="U34" s="13">
         <v>1000</v>
       </c>
       <c r="V34" s="13" t="s">
-        <v>429</v>
+        <v>270</v>
       </c>
       <c r="W34" s="13">
         <v>0</v>
@@ -5370,7 +5876,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:33">
       <c r="A35" s="13">
         <v>820072</v>
       </c>
@@ -5383,18 +5889,18 @@
       <c r="D35" s="14">
         <v>0</v>
       </c>
-      <c r="E35" s="23">
+      <c r="E35" s="15">
         <v>820072</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>438</v>
+        <v>276</v>
       </c>
       <c r="G35" s="12" t="s">
         <v>228</v>
       </c>
       <c r="H35" s="13"/>
       <c r="I35" s="13" t="s">
-        <v>439</v>
+        <v>277</v>
       </c>
       <c r="J35" s="13" t="s">
         <v>78</v>
@@ -5470,16 +5976,17 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="E7:S71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
     <col min="5" max="5" width="27.25" style="1" customWidth="1"/>
@@ -5492,7 +5999,7 @@
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="5:19" x14ac:dyDescent="0.15">
+    <row r="7" spans="5:6">
       <c r="E7" s="1" t="s">
         <v>8</v>
       </c>
@@ -5500,7 +6007,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="5:19" x14ac:dyDescent="0.15">
+    <row r="8" spans="5:6">
       <c r="E8" s="1" t="s">
         <v>9</v>
       </c>
@@ -5508,7 +6015,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="5:19" x14ac:dyDescent="0.15">
+    <row r="9" spans="5:6">
       <c r="E9" s="1" t="s">
         <v>10</v>
       </c>
@@ -5516,15 +6023,15 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="5:19" x14ac:dyDescent="0.15">
+    <row r="10" spans="5:6">
       <c r="E10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="11" spans="5:19" x14ac:dyDescent="0.15">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="11" spans="5:6">
       <c r="E11" s="1" t="s">
         <v>12</v>
       </c>
@@ -5532,7 +6039,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="5:19" x14ac:dyDescent="0.15">
+    <row r="12" spans="5:6">
       <c r="E12" s="1" t="s">
         <v>13</v>
       </c>
@@ -5540,7 +6047,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="5:19" x14ac:dyDescent="0.15">
+    <row r="13" spans="5:19">
       <c r="E13" s="1" t="s">
         <v>14</v>
       </c>
@@ -5548,13 +6055,13 @@
         <v>47</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="14" spans="5:19" x14ac:dyDescent="0.15">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="14" spans="5:12">
       <c r="E14" s="1" t="s">
         <v>15</v>
       </c>
@@ -5568,13 +6075,13 @@
         <v>1</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="15" spans="5:19" x14ac:dyDescent="0.15">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="15" spans="5:19">
       <c r="E15" s="1" t="s">
         <v>16</v>
       </c>
@@ -5585,16 +6092,16 @@
         <v>3</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="16" spans="5:19" x14ac:dyDescent="0.15">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="16" spans="5:19">
       <c r="E16" s="1" t="s">
         <v>17</v>
       </c>
@@ -5608,16 +6115,16 @@
         <v>7</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="17" spans="5:19" x14ac:dyDescent="0.15">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="17" spans="5:19">
       <c r="E17" s="1" t="s">
         <v>18</v>
       </c>
@@ -5631,16 +6138,16 @@
         <v>7</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="18" spans="5:19" x14ac:dyDescent="0.15">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="18" spans="5:19">
       <c r="E18" s="1" t="s">
         <v>19</v>
       </c>
@@ -5654,16 +6161,16 @@
         <v>7</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="19" spans="5:19" x14ac:dyDescent="0.15">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="19" spans="5:19">
       <c r="E19" s="1" t="s">
         <v>20</v>
       </c>
@@ -5675,25 +6182,25 @@
         <v>参数4LIST-触发的技能id</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="20" spans="5:19" x14ac:dyDescent="0.15">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20" spans="5:19">
       <c r="E20" s="1" t="s">
         <v>21</v>
       </c>
@@ -5705,25 +6212,25 @@
         <v>参数5-持续时间（毫秒）</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="21" spans="5:19" x14ac:dyDescent="0.15">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="21" spans="5:19">
       <c r="E21" s="1" t="s">
         <v>22</v>
       </c>
@@ -5735,25 +6242,25 @@
         <v>参数6-效果基础命中率（万分比）</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="22" spans="5:19" x14ac:dyDescent="0.15">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="22" spans="5:19">
       <c r="E22" s="1" t="s">
         <v>23</v>
       </c>
@@ -5768,22 +6275,22 @@
         <v>66</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="23" spans="5:19" x14ac:dyDescent="0.15">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="23" spans="5:19">
       <c r="E23" s="1" t="s">
         <v>24</v>
       </c>
@@ -5795,25 +6302,25 @@
         <v>参数8-效果触发间隔（毫秒）</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="24" spans="5:19" x14ac:dyDescent="0.15">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="24" spans="5:19">
       <c r="E24" s="1" t="s">
         <v>25</v>
       </c>
@@ -5825,25 +6332,25 @@
         <v>参数9-击中回复生命值-固定值</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="25" spans="5:19" x14ac:dyDescent="0.15">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="25" spans="5:19">
       <c r="E25" s="1" t="s">
         <v>26</v>
       </c>
@@ -5855,25 +6362,25 @@
         <v>参数10-击中回复生命值-自身最大生命值百万分比</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="26" spans="5:19" x14ac:dyDescent="0.15">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="26" spans="5:19">
       <c r="E26" s="1" t="s">
         <v>27</v>
       </c>
@@ -5885,25 +6392,25 @@
         <v>参数11-击中回复效果提高万分比</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="27" spans="5:19" x14ac:dyDescent="0.15">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="27" spans="5:19">
       <c r="E27" s="1" t="s">
         <v>28</v>
       </c>
@@ -5915,25 +6422,25 @@
         <v>参数12-击杀回复生命-固定值</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="28" spans="5:19" x14ac:dyDescent="0.15">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="28" spans="5:12">
       <c r="E28" s="1" t="s">
         <v>29</v>
       </c>
@@ -5945,22 +6452,22 @@
         <v>参数13-击杀回复生命-自身最大生命值百万分比</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="29" spans="5:19" x14ac:dyDescent="0.15">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="29" spans="5:19">
       <c r="E29" s="1" t="s">
         <v>30</v>
       </c>
@@ -5972,25 +6479,25 @@
         <v>参数14-击杀回复生命-目标最大生命值百万分比</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="30" spans="5:19" x14ac:dyDescent="0.15">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="30" spans="5:19">
       <c r="E30" s="1" t="s">
         <v>31</v>
       </c>
@@ -6002,25 +6509,25 @@
         <v>参数15-击杀回复生命效果提高万分比</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="31" spans="5:19" x14ac:dyDescent="0.15">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="31" spans="5:19">
       <c r="E31" s="1" t="s">
         <v>32</v>
       </c>
@@ -6032,52 +6539,52 @@
         <v>参数16-获得护盾-固定值</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="32" spans="5:19" x14ac:dyDescent="0.15">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="32" spans="5:12">
       <c r="E32" s="1" t="s">
         <v>33</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="G32" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数17-获得护盾-自身生命百万分比</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="33" spans="5:9" x14ac:dyDescent="0.15">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="33" spans="5:9">
       <c r="E33" s="1" t="s">
         <v>34</v>
       </c>
@@ -6089,13 +6596,13 @@
         <v>参数18-获得护盾-自身已损失生命万分比</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="34" spans="5:9" x14ac:dyDescent="0.15">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="34" spans="5:9">
       <c r="E34" s="1" t="s">
         <v>35</v>
       </c>
@@ -6107,403 +6614,404 @@
         <v>参数19-获得护盾效果提高万分比</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="35" spans="5:9" x14ac:dyDescent="0.15">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="35" spans="5:9">
       <c r="E35" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="G35" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数20-技能增加-固定值</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="36" spans="5:9" x14ac:dyDescent="0.15">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="36" spans="7:9">
       <c r="G36" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数21-技能增加-万分比</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="37" spans="5:9" x14ac:dyDescent="0.15">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="37" spans="7:9">
       <c r="G37" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数22-技能增加-普通攻击范围万分比</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="38" spans="5:9" x14ac:dyDescent="0.15">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="38" spans="7:9">
       <c r="G38" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数25LIST-攻击提高-攻击的元素类型</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="39" spans="5:9" x14ac:dyDescent="0.15">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="39" spans="7:9">
       <c r="G39" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数25LIST-攻击提高-固定值</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="40" spans="5:9" x14ac:dyDescent="0.15">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="40" spans="7:9">
       <c r="G40" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数25LIST-攻击提高-万分比</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="41" spans="5:9" x14ac:dyDescent="0.15">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="41" spans="7:9">
       <c r="G41" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数28-防御提高-固定值</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="42" spans="5:9" x14ac:dyDescent="0.15">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="42" spans="7:9">
       <c r="G42" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数29-防御提高-万分比</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="43" spans="5:9" x14ac:dyDescent="0.15">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="43" spans="7:9">
       <c r="G43" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数30-生命上限提高-固定值</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="44" spans="5:9" x14ac:dyDescent="0.15">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="44" spans="7:9">
       <c r="G44" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数31-生命上限提高-百万分比</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="45" spans="5:9" x14ac:dyDescent="0.15">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="45" spans="7:9">
       <c r="G45" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数32-攻击速度提高-万分比</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="46" spans="5:9" x14ac:dyDescent="0.15">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="46" spans="7:9">
       <c r="G46" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数33-移动速度提高-万分比</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="47" spans="5:9" x14ac:dyDescent="0.15">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="47" spans="7:9">
       <c r="G47" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数34-攻击范围提高-万分比</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="48" spans="5:9" x14ac:dyDescent="0.15">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="48" spans="7:9">
       <c r="G48" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数35-攻击目标数量提高-固定值</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="49" spans="7:8" x14ac:dyDescent="0.15">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="49" spans="7:8">
       <c r="G49" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数36-</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="50" spans="7:8" x14ac:dyDescent="0.15">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="50" spans="7:8">
       <c r="G50" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数37-</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="51" spans="7:8" x14ac:dyDescent="0.15">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="51" spans="7:8">
       <c r="G51" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数38-</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="52" spans="7:8" x14ac:dyDescent="0.15">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="52" spans="7:8">
       <c r="G52" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数39-</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="53" spans="7:8" x14ac:dyDescent="0.15">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="53" spans="7:8">
       <c r="G53" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数40-</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="54" spans="7:8" x14ac:dyDescent="0.15">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="54" spans="7:8">
       <c r="G54" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数41-</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="55" spans="7:8" x14ac:dyDescent="0.15">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="55" spans="7:8">
       <c r="G55" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数42-</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="56" spans="7:8" x14ac:dyDescent="0.15">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="56" spans="7:8">
       <c r="G56" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数41-</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="57" spans="7:8" x14ac:dyDescent="0.15">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="57" spans="7:8">
       <c r="G57" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数42-</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="58" spans="7:8" x14ac:dyDescent="0.15">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="58" spans="7:8">
       <c r="G58" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数43-</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="59" spans="7:8" x14ac:dyDescent="0.15">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="59" spans="7:8">
       <c r="G59" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数44-</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="60" spans="7:8" x14ac:dyDescent="0.15">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="60" spans="7:8">
       <c r="G60" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数45-</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="61" spans="7:8" x14ac:dyDescent="0.15">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="61" spans="7:8">
       <c r="G61" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数46-</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="62" spans="7:8" x14ac:dyDescent="0.15">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="62" spans="7:8">
       <c r="G62" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数47-</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="63" spans="7:8" x14ac:dyDescent="0.15">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="63" spans="7:8">
       <c r="G63" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数48-</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="64" spans="7:8" x14ac:dyDescent="0.15">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="64" spans="7:8">
       <c r="G64" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数49-</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="65" spans="7:8" x14ac:dyDescent="0.15">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="65" spans="7:8">
       <c r="G65" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数50-</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="66" spans="7:8" x14ac:dyDescent="0.15">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="66" spans="7:8">
       <c r="G66" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数51-</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="67" spans="7:8" x14ac:dyDescent="0.15">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="67" spans="7:8">
       <c r="G67" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数52-</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="68" spans="7:8" x14ac:dyDescent="0.15">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="68" spans="7:8">
       <c r="G68" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数53-</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="69" spans="7:8" x14ac:dyDescent="0.15">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="69" spans="7:8">
       <c r="G69" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数54-</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="70" spans="7:8" x14ac:dyDescent="0.15">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="70" spans="7:8">
       <c r="G70" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数55-</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="71" spans="7:8" x14ac:dyDescent="0.15">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="71" spans="7:8">
       <c r="G71" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数56-</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="D6:F43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="11.25" style="1" customWidth="1"/>
@@ -6513,172 +7021,172 @@
     <col min="23" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="4:5" x14ac:dyDescent="0.15">
+    <row r="6" spans="4:5">
       <c r="D6" s="2" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="4:5" x14ac:dyDescent="0.15">
+    <row r="7" spans="4:5">
       <c r="D7" s="2">
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="8" spans="4:5" x14ac:dyDescent="0.15">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="8" spans="4:5">
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="4:5" x14ac:dyDescent="0.15">
+    <row r="9" spans="4:5">
       <c r="D9" s="2">
         <v>2</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="10" spans="4:5" x14ac:dyDescent="0.15">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="10" spans="4:5">
       <c r="D10" s="2">
         <v>2.1</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="11" spans="4:5" x14ac:dyDescent="0.15">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="11" spans="4:5">
       <c r="D11" s="2" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="12" spans="4:5" x14ac:dyDescent="0.15">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="12" spans="4:5">
       <c r="D12" s="2" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="13" spans="4:5" x14ac:dyDescent="0.15">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="13" spans="4:5">
       <c r="D13" s="2" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="14" spans="4:5" x14ac:dyDescent="0.15">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="14" spans="4:5">
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="4:5" x14ac:dyDescent="0.15">
+    <row r="15" spans="4:5">
       <c r="D15" s="2">
-        <v>2.2000000000000002</v>
+        <v>2.2</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="16" spans="4:5" x14ac:dyDescent="0.15">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="16" spans="4:5">
       <c r="D16" s="2" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.15">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="17" spans="4:5">
       <c r="D17" s="2" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.15">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="18" spans="4:5">
       <c r="D18" s="2" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="28" spans="4:5" x14ac:dyDescent="0.15">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="28" spans="4:4">
       <c r="D28" s="1" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="29" spans="4:5" x14ac:dyDescent="0.15">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="29" spans="4:5">
       <c r="D29" s="1" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="E29" s="1">
         <v>101</v>
       </c>
     </row>
-    <row r="30" spans="4:5" x14ac:dyDescent="0.15">
+    <row r="30" spans="4:5">
       <c r="D30" s="1" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="E30" s="1">
         <v>102</v>
       </c>
     </row>
-    <row r="31" spans="4:5" x14ac:dyDescent="0.15">
+    <row r="31" spans="4:4">
       <c r="D31" s="1" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="32" spans="4:5" x14ac:dyDescent="0.15">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="32" spans="4:4">
       <c r="D32" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="33" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25" spans="4:6">
       <c r="D33" s="1" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="E33" s="1">
         <v>105</v>
       </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="34" ht="14.25" spans="6:6">
       <c r="F34"/>
     </row>
-    <row r="35" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="35" ht="14.25" spans="6:6">
       <c r="F35"/>
     </row>
-    <row r="36" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="36" ht="14.25" spans="6:6">
       <c r="F36"/>
     </row>
-    <row r="37" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="37" ht="14.25" spans="6:6">
       <c r="F37"/>
     </row>
-    <row r="38" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="38" ht="14.25" spans="6:6">
       <c r="F38"/>
     </row>
-    <row r="39" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="39" ht="14.25" spans="6:6">
       <c r="F39"/>
     </row>
-    <row r="40" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="40" ht="14.25" spans="6:6">
       <c r="F40"/>
     </row>
-    <row r="41" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="41" ht="14.25" spans="6:6">
       <c r="F41"/>
     </row>
-    <row r="42" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="42" ht="14.25" spans="6:6">
       <c r="F42"/>
     </row>
-    <row r="43" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="43" ht="14.25" spans="6:6">
       <c r="F43"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2064E22E-108A-4C13-8B11-A9B2FBCC5A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -23,8 +29,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -32,32 +36,34 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>pe</author>
     <author>cltx</author>
   </authors>
   <commentList>
-    <comment ref="C4" authorId="0">
+    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>数字越大，优先级越高</t>
         </r>
       </text>
     </comment>
-    <comment ref="K4" authorId="1">
+    <comment ref="K4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>cltx:</t>
@@ -66,6 +72,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -75,12 +82,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="0">
+    <comment ref="U4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">&gt;0，持续时间
@@ -874,9 +882,6 @@
     <t>闪电链附加麻痹状态（无法攻击和移动），持续时间【参数5】（默认1000）毫秒，状态命中率【参数6】（默认20%）</t>
   </si>
   <si>
-    <t>5200701:0</t>
-  </si>
-  <si>
     <t>连环闪电</t>
   </si>
   <si>
@@ -889,539 +894,539 @@
     <t>电刃普攻麻痹状态（无法攻击和移动），持续时间【参数5】（默认1000）毫秒，状态命中率【参数6】（默认20%）</t>
   </si>
   <si>
+    <t>天罚</t>
+  </si>
+  <si>
+    <t>击杀敌人时再次释放超强电刃【参数4】</t>
+  </si>
+  <si>
+    <t>暴风雪概率附加减速</t>
+  </si>
+  <si>
+    <t>暴风雪减速状态（万分比降低攻速【参数1】和移速【参数2】），持续时间【参数5】毫秒，状态命中率【参数6】</t>
+  </si>
+  <si>
+    <t>5001701:1</t>
+  </si>
+  <si>
+    <t>5001702:1</t>
+  </si>
+  <si>
+    <t>5001705:1</t>
+  </si>
+  <si>
+    <t>5001706:1</t>
+  </si>
+  <si>
+    <t>暴风雪概率附加冰冻</t>
+  </si>
+  <si>
+    <t>暴风雪冰冻状态（无法攻击和移动），持续时间【参数5】毫秒，状态命中率【参数6】</t>
+  </si>
+  <si>
+    <t>冰爆被动</t>
+  </si>
+  <si>
+    <t>冰冻状态结束时触发冰爆技能【参数4】</t>
+  </si>
+  <si>
+    <t>重复中buff组的cd时间（毫秒）</t>
+  </si>
+  <si>
+    <t>触发自动技能</t>
+  </si>
+  <si>
+    <t>主动技能</t>
+  </si>
+  <si>
+    <t>order</t>
+  </si>
+  <si>
+    <t>自动</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>冰霜新星</t>
+  </si>
+  <si>
+    <t>auto_cd</t>
+  </si>
+  <si>
+    <t>参数-重复触发自动释放冷却时间（毫秒）</t>
+  </si>
+  <si>
+    <t>陨石</t>
+  </si>
+  <si>
+    <t>release_ratio</t>
+  </si>
+  <si>
+    <t>参数-释放几率</t>
+  </si>
+  <si>
+    <t>死亡爆炸</t>
+  </si>
+  <si>
+    <t>release_num</t>
+  </si>
+  <si>
+    <t>参数-释放次数</t>
+  </si>
+  <si>
+    <t>闪电链</t>
+  </si>
+  <si>
+    <t>参数4LIST</t>
+  </si>
+  <si>
+    <t>触发的技能id</t>
+  </si>
+  <si>
+    <t>LIST&lt;INT&gt;_S</t>
+  </si>
+  <si>
+    <t>skill_id</t>
+  </si>
+  <si>
+    <t>参数-释放的技能id</t>
+  </si>
+  <si>
+    <t>电磁爆发</t>
+  </si>
+  <si>
+    <t>参数5</t>
+  </si>
+  <si>
+    <t>持续时间（毫秒）</t>
+  </si>
+  <si>
+    <t>total_attack_num</t>
+  </si>
+  <si>
+    <t>参数-累计发起攻击次数时</t>
+  </si>
+  <si>
+    <t>传染</t>
+  </si>
+  <si>
+    <t>参数6</t>
+  </si>
+  <si>
+    <t>效果基础命中率（万分比）</t>
+  </si>
+  <si>
+    <t>lose_hp_ratio</t>
+  </si>
+  <si>
+    <t>参数-损失自身生命最大值百万分比时</t>
+  </si>
+  <si>
+    <t>瘟疫</t>
+  </si>
+  <si>
+    <t>效果最大叠加层数</t>
+  </si>
+  <si>
+    <t>kill_target_after</t>
+  </si>
+  <si>
+    <t>参数-击杀目标后</t>
+  </si>
+  <si>
+    <t>复活</t>
+  </si>
+  <si>
+    <t>参数8</t>
+  </si>
+  <si>
+    <t>效果触发间隔（毫秒）</t>
+  </si>
+  <si>
+    <t>after_attack_crit</t>
+  </si>
+  <si>
+    <t>参数-攻击暴击后</t>
+  </si>
+  <si>
+    <t>半月斩</t>
+  </si>
+  <si>
+    <t>参数9</t>
+  </si>
+  <si>
+    <t>击中回复生命值-固定值</t>
+  </si>
+  <si>
+    <t>after_use_skill</t>
+  </si>
+  <si>
+    <t>参数-释放【技能id】后</t>
+  </si>
+  <si>
+    <t>旋风斩</t>
+  </si>
+  <si>
+    <t>参数10</t>
+  </si>
+  <si>
+    <t>击中回复生命值-自身最大生命值百万分比</t>
+  </si>
+  <si>
+    <t>cycle_time</t>
+  </si>
+  <si>
+    <t>参数-每过固定时间（毫秒）时</t>
+  </si>
+  <si>
+    <t>重击</t>
+  </si>
+  <si>
+    <t>参数11</t>
+  </si>
+  <si>
+    <t>击中回复效果提高万分比</t>
+  </si>
+  <si>
+    <t>after_skill_hit</t>
+  </si>
+  <si>
+    <t>参数-【技能id】命中后</t>
+  </si>
+  <si>
+    <t>多重打击</t>
+  </si>
+  <si>
+    <t>参数12</t>
+  </si>
+  <si>
+    <t>击杀回复生命-固定值</t>
+  </si>
+  <si>
+    <t>after_self_death</t>
+  </si>
+  <si>
+    <t>参数-自身死亡后释放</t>
+  </si>
+  <si>
+    <t>斩杀</t>
+  </si>
+  <si>
+    <t>参数13</t>
+  </si>
+  <si>
+    <t>击杀回复生命-自身最大生命值百万分比</t>
+  </si>
+  <si>
+    <t>self_have_effect</t>
+  </si>
+  <si>
+    <t>参数-自身拥有【效果id：&gt;=层数】时</t>
+  </si>
+  <si>
+    <t>参数14</t>
+  </si>
+  <si>
+    <t>击杀回复生命-目标最大生命值百万分比</t>
+  </si>
+  <si>
+    <t>target_have_effect</t>
+  </si>
+  <si>
+    <t>参数-目标拥有【效果id：&gt;=层数】时</t>
+  </si>
+  <si>
+    <t>获得护盾</t>
+  </si>
+  <si>
+    <t>参数15</t>
+  </si>
+  <si>
+    <t>击杀回复生命效果提高万分比</t>
+  </si>
+  <si>
+    <t>target_hp_ratio_over</t>
+  </si>
+  <si>
+    <t>参数-目标当前生命值&gt;=最大生命值的百万分之X时</t>
+  </si>
+  <si>
+    <t>回复生命</t>
+  </si>
+  <si>
+    <t>参数16</t>
+  </si>
+  <si>
+    <t>获得护盾-固定值</t>
+  </si>
+  <si>
+    <t>target_hp_ratio_under</t>
+  </si>
+  <si>
+    <t>参数-目标当前生命值&lt;=最大生命值的百万分之X时</t>
+  </si>
+  <si>
+    <t>击中目标</t>
+  </si>
+  <si>
+    <t>效果叠加层数</t>
+  </si>
+  <si>
+    <t>参数17</t>
+  </si>
+  <si>
+    <t>获得护盾-自身生命百万分比</t>
+  </si>
+  <si>
+    <t>to_target_effect_hit</t>
+  </si>
+  <si>
+    <t>参数-对目标施加【效果id】命中时</t>
+  </si>
+  <si>
+    <t>参数18</t>
+  </si>
+  <si>
+    <t>获得护盾-自身已损失生命万分比</t>
+  </si>
+  <si>
+    <t>参数19</t>
+  </si>
+  <si>
+    <t>获得护盾效果提高万分比</t>
+  </si>
+  <si>
+    <t>结算间隔时间（毫秒）</t>
+  </si>
+  <si>
+    <t>参数20</t>
+  </si>
+  <si>
+    <t>技能增加-固定值</t>
+  </si>
+  <si>
+    <t>参数21</t>
+  </si>
+  <si>
+    <t>技能增加-万分比</t>
+  </si>
+  <si>
+    <t>参数22</t>
+  </si>
+  <si>
+    <t>技能增加-普通攻击范围万分比</t>
+  </si>
+  <si>
+    <t>参数25LIST</t>
+  </si>
+  <si>
+    <t>攻击提高-攻击的元素类型</t>
+  </si>
+  <si>
+    <t>攻击提高-固定值</t>
+  </si>
+  <si>
+    <t>攻击提高-万分比</t>
+  </si>
+  <si>
+    <t>参数28</t>
+  </si>
+  <si>
+    <t>防御提高-固定值</t>
+  </si>
+  <si>
+    <t>参数29</t>
+  </si>
+  <si>
+    <t>防御提高-万分比</t>
+  </si>
+  <si>
+    <t>参数30</t>
+  </si>
+  <si>
+    <t>生命上限提高-固定值</t>
+  </si>
+  <si>
+    <t>参数31</t>
+  </si>
+  <si>
+    <t>生命上限提高-百万分比</t>
+  </si>
+  <si>
+    <t>参数32</t>
+  </si>
+  <si>
+    <t>攻击速度提高-万分比</t>
+  </si>
+  <si>
+    <t>参数33</t>
+  </si>
+  <si>
+    <t>移动速度提高-万分比</t>
+  </si>
+  <si>
+    <t>参数34</t>
+  </si>
+  <si>
+    <t>攻击范围提高-万分比</t>
+  </si>
+  <si>
+    <t>参数35</t>
+  </si>
+  <si>
+    <t>攻击目标数量提高-固定值</t>
+  </si>
+  <si>
+    <t>参数36</t>
+  </si>
+  <si>
+    <t>参数37</t>
+  </si>
+  <si>
+    <t>参数38</t>
+  </si>
+  <si>
+    <t>参数39</t>
+  </si>
+  <si>
+    <t>参数40</t>
+  </si>
+  <si>
+    <t>参数41</t>
+  </si>
+  <si>
+    <t>参数42</t>
+  </si>
+  <si>
+    <t>参数43</t>
+  </si>
+  <si>
+    <t>参数44</t>
+  </si>
+  <si>
+    <t>参数45</t>
+  </si>
+  <si>
+    <t>参数46</t>
+  </si>
+  <si>
+    <t>参数47</t>
+  </si>
+  <si>
+    <t>参数48</t>
+  </si>
+  <si>
+    <t>参数49</t>
+  </si>
+  <si>
+    <t>参数50</t>
+  </si>
+  <si>
+    <t>参数51</t>
+  </si>
+  <si>
+    <t>参数52</t>
+  </si>
+  <si>
+    <t>参数53</t>
+  </si>
+  <si>
+    <t>参数54</t>
+  </si>
+  <si>
+    <t>参数55</t>
+  </si>
+  <si>
+    <t>参数56</t>
+  </si>
+  <si>
+    <t>buff处理逻辑</t>
+  </si>
+  <si>
+    <t>不同组所有buff可叠加同时生效</t>
+  </si>
+  <si>
+    <t>同组buff是否互斥</t>
+  </si>
+  <si>
+    <t>同组buff不互斥时：结算buff时先时候查看同组重复cd</t>
+  </si>
+  <si>
+    <t>2.1.1</t>
+  </si>
+  <si>
+    <t>buff有cd，且同组重复cd&gt;0：直接把后来的buff丢掉</t>
+  </si>
+  <si>
+    <t>2.1.2</t>
+  </si>
+  <si>
+    <t>buff有cd，且同组重复cd=0：单个buff直接增加，多个buff增加优先级高的那个</t>
+  </si>
+  <si>
+    <t>2.1.3</t>
+  </si>
+  <si>
+    <t>buff没有cd：多个buff直接添加</t>
+  </si>
+  <si>
+    <t>同组buff互斥时，结算buff时先查看同组重复cd</t>
+  </si>
+  <si>
+    <t>2.2.1</t>
+  </si>
+  <si>
+    <t>2.2.2</t>
+  </si>
+  <si>
+    <t>buff有cd，且同组重复cd=0：单个buff直接增加，多个buff增加优先级高的那个，效果、持续时间、cd时间按优先级最高的时间</t>
+  </si>
+  <si>
+    <t>2.2.3</t>
+  </si>
+  <si>
+    <t>buff没有cd：同上，同2.2.2</t>
+  </si>
+  <si>
+    <t>buff组id</t>
+  </si>
+  <si>
+    <t>麻痹</t>
+  </si>
+  <si>
+    <t>减速</t>
+  </si>
+  <si>
+    <t>燃烧</t>
+  </si>
+  <si>
+    <t>中毒</t>
+  </si>
+  <si>
+    <t>冰冻</t>
+  </si>
+  <si>
+    <t>5200701:1</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
     <t>5200712:1</t>
-  </si>
-  <si>
-    <t>5200711:0</t>
-  </si>
-  <si>
-    <t>天罚</t>
-  </si>
-  <si>
-    <t>击杀敌人时再次释放超强电刃【参数4】</t>
-  </si>
-  <si>
-    <t>暴风雪概率附加减速</t>
-  </si>
-  <si>
-    <t>暴风雪减速状态（万分比降低攻速【参数1】和移速【参数2】），持续时间【参数5】毫秒，状态命中率【参数6】</t>
-  </si>
-  <si>
-    <t>5001701:1</t>
-  </si>
-  <si>
-    <t>5001702:1</t>
-  </si>
-  <si>
-    <t>5001705:1</t>
-  </si>
-  <si>
-    <t>5001706:1</t>
-  </si>
-  <si>
-    <t>暴风雪概率附加冰冻</t>
-  </si>
-  <si>
-    <t>暴风雪冰冻状态（无法攻击和移动），持续时间【参数5】毫秒，状态命中率【参数6】</t>
-  </si>
-  <si>
-    <t>冰爆被动</t>
-  </si>
-  <si>
-    <t>冰冻状态结束时触发冰爆技能【参数4】</t>
-  </si>
-  <si>
-    <t>重复中buff组的cd时间（毫秒）</t>
-  </si>
-  <si>
-    <t>触发自动技能</t>
-  </si>
-  <si>
-    <t>主动技能</t>
-  </si>
-  <si>
-    <t>order</t>
-  </si>
-  <si>
-    <t>自动</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>冰霜新星</t>
-  </si>
-  <si>
-    <t>auto_cd</t>
-  </si>
-  <si>
-    <t>参数-重复触发自动释放冷却时间（毫秒）</t>
-  </si>
-  <si>
-    <t>陨石</t>
-  </si>
-  <si>
-    <t>release_ratio</t>
-  </si>
-  <si>
-    <t>参数-释放几率</t>
-  </si>
-  <si>
-    <t>死亡爆炸</t>
-  </si>
-  <si>
-    <t>release_num</t>
-  </si>
-  <si>
-    <t>参数-释放次数</t>
-  </si>
-  <si>
-    <t>闪电链</t>
-  </si>
-  <si>
-    <t>参数4LIST</t>
-  </si>
-  <si>
-    <t>触发的技能id</t>
-  </si>
-  <si>
-    <t>LIST&lt;INT&gt;_S</t>
-  </si>
-  <si>
-    <t>skill_id</t>
-  </si>
-  <si>
-    <t>参数-释放的技能id</t>
-  </si>
-  <si>
-    <t>电磁爆发</t>
-  </si>
-  <si>
-    <t>参数5</t>
-  </si>
-  <si>
-    <t>持续时间（毫秒）</t>
-  </si>
-  <si>
-    <t>total_attack_num</t>
-  </si>
-  <si>
-    <t>参数-累计发起攻击次数时</t>
-  </si>
-  <si>
-    <t>传染</t>
-  </si>
-  <si>
-    <t>参数6</t>
-  </si>
-  <si>
-    <t>效果基础命中率（万分比）</t>
-  </si>
-  <si>
-    <t>lose_hp_ratio</t>
-  </si>
-  <si>
-    <t>参数-损失自身生命最大值百万分比时</t>
-  </si>
-  <si>
-    <t>瘟疫</t>
-  </si>
-  <si>
-    <t>效果最大叠加层数</t>
-  </si>
-  <si>
-    <t>kill_target_after</t>
-  </si>
-  <si>
-    <t>参数-击杀目标后</t>
-  </si>
-  <si>
-    <t>复活</t>
-  </si>
-  <si>
-    <t>参数8</t>
-  </si>
-  <si>
-    <t>效果触发间隔（毫秒）</t>
-  </si>
-  <si>
-    <t>after_attack_crit</t>
-  </si>
-  <si>
-    <t>参数-攻击暴击后</t>
-  </si>
-  <si>
-    <t>半月斩</t>
-  </si>
-  <si>
-    <t>参数9</t>
-  </si>
-  <si>
-    <t>击中回复生命值-固定值</t>
-  </si>
-  <si>
-    <t>after_use_skill</t>
-  </si>
-  <si>
-    <t>参数-释放【技能id】后</t>
-  </si>
-  <si>
-    <t>旋风斩</t>
-  </si>
-  <si>
-    <t>参数10</t>
-  </si>
-  <si>
-    <t>击中回复生命值-自身最大生命值百万分比</t>
-  </si>
-  <si>
-    <t>cycle_time</t>
-  </si>
-  <si>
-    <t>参数-每过固定时间（毫秒）时</t>
-  </si>
-  <si>
-    <t>重击</t>
-  </si>
-  <si>
-    <t>参数11</t>
-  </si>
-  <si>
-    <t>击中回复效果提高万分比</t>
-  </si>
-  <si>
-    <t>after_skill_hit</t>
-  </si>
-  <si>
-    <t>参数-【技能id】命中后</t>
-  </si>
-  <si>
-    <t>多重打击</t>
-  </si>
-  <si>
-    <t>参数12</t>
-  </si>
-  <si>
-    <t>击杀回复生命-固定值</t>
-  </si>
-  <si>
-    <t>after_self_death</t>
-  </si>
-  <si>
-    <t>参数-自身死亡后释放</t>
-  </si>
-  <si>
-    <t>斩杀</t>
-  </si>
-  <si>
-    <t>参数13</t>
-  </si>
-  <si>
-    <t>击杀回复生命-自身最大生命值百万分比</t>
-  </si>
-  <si>
-    <t>self_have_effect</t>
-  </si>
-  <si>
-    <t>参数-自身拥有【效果id：&gt;=层数】时</t>
-  </si>
-  <si>
-    <t>参数14</t>
-  </si>
-  <si>
-    <t>击杀回复生命-目标最大生命值百万分比</t>
-  </si>
-  <si>
-    <t>target_have_effect</t>
-  </si>
-  <si>
-    <t>参数-目标拥有【效果id：&gt;=层数】时</t>
-  </si>
-  <si>
-    <t>获得护盾</t>
-  </si>
-  <si>
-    <t>参数15</t>
-  </si>
-  <si>
-    <t>击杀回复生命效果提高万分比</t>
-  </si>
-  <si>
-    <t>target_hp_ratio_over</t>
-  </si>
-  <si>
-    <t>参数-目标当前生命值&gt;=最大生命值的百万分之X时</t>
-  </si>
-  <si>
-    <t>回复生命</t>
-  </si>
-  <si>
-    <t>参数16</t>
-  </si>
-  <si>
-    <t>获得护盾-固定值</t>
-  </si>
-  <si>
-    <t>target_hp_ratio_under</t>
-  </si>
-  <si>
-    <t>参数-目标当前生命值&lt;=最大生命值的百万分之X时</t>
-  </si>
-  <si>
-    <t>击中目标</t>
-  </si>
-  <si>
-    <t>效果叠加层数</t>
-  </si>
-  <si>
-    <t>参数17</t>
-  </si>
-  <si>
-    <t>获得护盾-自身生命百万分比</t>
-  </si>
-  <si>
-    <t>to_target_effect_hit</t>
-  </si>
-  <si>
-    <t>参数-对目标施加【效果id】命中时</t>
-  </si>
-  <si>
-    <t>参数18</t>
-  </si>
-  <si>
-    <t>获得护盾-自身已损失生命万分比</t>
-  </si>
-  <si>
-    <t>参数19</t>
-  </si>
-  <si>
-    <t>获得护盾效果提高万分比</t>
-  </si>
-  <si>
-    <t>结算间隔时间（毫秒）</t>
-  </si>
-  <si>
-    <t>参数20</t>
-  </si>
-  <si>
-    <t>技能增加-固定值</t>
-  </si>
-  <si>
-    <t>参数21</t>
-  </si>
-  <si>
-    <t>技能增加-万分比</t>
-  </si>
-  <si>
-    <t>参数22</t>
-  </si>
-  <si>
-    <t>技能增加-普通攻击范围万分比</t>
-  </si>
-  <si>
-    <t>参数25LIST</t>
-  </si>
-  <si>
-    <t>攻击提高-攻击的元素类型</t>
-  </si>
-  <si>
-    <t>攻击提高-固定值</t>
-  </si>
-  <si>
-    <t>攻击提高-万分比</t>
-  </si>
-  <si>
-    <t>参数28</t>
-  </si>
-  <si>
-    <t>防御提高-固定值</t>
-  </si>
-  <si>
-    <t>参数29</t>
-  </si>
-  <si>
-    <t>防御提高-万分比</t>
-  </si>
-  <si>
-    <t>参数30</t>
-  </si>
-  <si>
-    <t>生命上限提高-固定值</t>
-  </si>
-  <si>
-    <t>参数31</t>
-  </si>
-  <si>
-    <t>生命上限提高-百万分比</t>
-  </si>
-  <si>
-    <t>参数32</t>
-  </si>
-  <si>
-    <t>攻击速度提高-万分比</t>
-  </si>
-  <si>
-    <t>参数33</t>
-  </si>
-  <si>
-    <t>移动速度提高-万分比</t>
-  </si>
-  <si>
-    <t>参数34</t>
-  </si>
-  <si>
-    <t>攻击范围提高-万分比</t>
-  </si>
-  <si>
-    <t>参数35</t>
-  </si>
-  <si>
-    <t>攻击目标数量提高-固定值</t>
-  </si>
-  <si>
-    <t>参数36</t>
-  </si>
-  <si>
-    <t>参数37</t>
-  </si>
-  <si>
-    <t>参数38</t>
-  </si>
-  <si>
-    <t>参数39</t>
-  </si>
-  <si>
-    <t>参数40</t>
-  </si>
-  <si>
-    <t>参数41</t>
-  </si>
-  <si>
-    <t>参数42</t>
-  </si>
-  <si>
-    <t>参数43</t>
-  </si>
-  <si>
-    <t>参数44</t>
-  </si>
-  <si>
-    <t>参数45</t>
-  </si>
-  <si>
-    <t>参数46</t>
-  </si>
-  <si>
-    <t>参数47</t>
-  </si>
-  <si>
-    <t>参数48</t>
-  </si>
-  <si>
-    <t>参数49</t>
-  </si>
-  <si>
-    <t>参数50</t>
-  </si>
-  <si>
-    <t>参数51</t>
-  </si>
-  <si>
-    <t>参数52</t>
-  </si>
-  <si>
-    <t>参数53</t>
-  </si>
-  <si>
-    <t>参数54</t>
-  </si>
-  <si>
-    <t>参数55</t>
-  </si>
-  <si>
-    <t>参数56</t>
-  </si>
-  <si>
-    <t>buff处理逻辑</t>
-  </si>
-  <si>
-    <t>不同组所有buff可叠加同时生效</t>
-  </si>
-  <si>
-    <t>同组buff是否互斥</t>
-  </si>
-  <si>
-    <t>同组buff不互斥时：结算buff时先时候查看同组重复cd</t>
-  </si>
-  <si>
-    <t>2.1.1</t>
-  </si>
-  <si>
-    <t>buff有cd，且同组重复cd&gt;0：直接把后来的buff丢掉</t>
-  </si>
-  <si>
-    <t>2.1.2</t>
-  </si>
-  <si>
-    <t>buff有cd，且同组重复cd=0：单个buff直接增加，多个buff增加优先级高的那个</t>
-  </si>
-  <si>
-    <t>2.1.3</t>
-  </si>
-  <si>
-    <t>buff没有cd：多个buff直接添加</t>
-  </si>
-  <si>
-    <t>同组buff互斥时，结算buff时先查看同组重复cd</t>
-  </si>
-  <si>
-    <t>2.2.1</t>
-  </si>
-  <si>
-    <t>2.2.2</t>
-  </si>
-  <si>
-    <t>buff有cd，且同组重复cd=0：单个buff直接增加，多个buff增加优先级高的那个，效果、持续时间、cd时间按优先级最高的时间</t>
-  </si>
-  <si>
-    <t>2.2.3</t>
-  </si>
-  <si>
-    <t>buff没有cd：同上，同2.2.2</t>
-  </si>
-  <si>
-    <t>buff组id</t>
-  </si>
-  <si>
-    <t>麻痹</t>
-  </si>
-  <si>
-    <t>减速</t>
-  </si>
-  <si>
-    <t>燃烧</t>
-  </si>
-  <si>
-    <t>中毒</t>
-  </si>
-  <si>
-    <t>冰冻</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>5200711:1</t>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="31">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1433,30 +1438,35 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF9C5700"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <color theme="0" tint="-0.0499893185216834"/>
+      <color theme="0" tint="-4.9989318521683403E-2"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1464,12 +1474,14 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1477,153 +1489,35 @@
       <sz val="9"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1631,15 +1525,24 @@
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1648,13 +1551,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.349986266670736"/>
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79970702230903"/>
+        <fgColor theme="8" tint="0.79967650379955446"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1672,31 +1575,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1706,152 +1585,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1889,241 +1624,23 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2138,8 +1655,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="24" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2147,80 +1664,39 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="23" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="24" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="24" applyFont="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="5">
+    <cellStyle name="差" xfId="2" builtinId="27"/>
+    <cellStyle name="差 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="差 2" xfId="49"/>
+    <cellStyle name="适中" xfId="3" builtinId="28"/>
+    <cellStyle name="输入" xfId="1" builtinId="20"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2498,14 +1974,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AG35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -2536,7 +2012,7 @@
     <col min="33" max="33" width="17.125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2569,7 +2045,7 @@
       <c r="AB1" s="4"/>
       <c r="AC1" s="4"/>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -2670,7 +2146,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:33">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
@@ -2771,7 +2247,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:33">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>41</v>
       </c>
@@ -2872,7 +2348,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:33">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>1000001</v>
       </c>
@@ -2973,7 +2449,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:33">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>2000001</v>
       </c>
@@ -3074,7 +2550,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:33">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>54010001</v>
       </c>
@@ -3175,7 +2651,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="1:33">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
         <v>54020001</v>
       </c>
@@ -3276,7 +2752,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:33">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>54030001</v>
       </c>
@@ -3377,7 +2853,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:33">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A10" s="8">
         <v>54040001</v>
       </c>
@@ -3478,7 +2954,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:33">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>54050001</v>
       </c>
@@ -3579,7 +3055,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:33">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>54060001</v>
       </c>
@@ -3680,7 +3156,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="13" spans="1:33">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>54070001</v>
       </c>
@@ -3781,7 +3257,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:33">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>54080001</v>
       </c>
@@ -3882,7 +3358,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="15" spans="1:33">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>54090001</v>
       </c>
@@ -3983,7 +3459,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="16" spans="1:33">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A16" s="8">
         <v>54100001</v>
       </c>
@@ -4084,7 +3560,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="17" spans="1:33">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A17" s="8">
         <v>54110001</v>
       </c>
@@ -4185,7 +3661,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="18" spans="1:33">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A18" s="8">
         <v>54120001</v>
       </c>
@@ -4286,7 +3762,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="19" spans="1:33">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A19" s="8">
         <v>54130001</v>
       </c>
@@ -4387,7 +3863,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="20" spans="1:33">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A20" s="8">
         <v>54140001</v>
       </c>
@@ -4488,7 +3964,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="21" spans="1:33">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A21" s="8">
         <v>54150001</v>
       </c>
@@ -4589,7 +4065,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="22" spans="1:33">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A22" s="10">
         <v>59130001</v>
       </c>
@@ -4686,7 +4162,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" spans="1:33">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A23" s="10">
         <v>59140001</v>
       </c>
@@ -4783,7 +4259,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:33">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A24" s="13">
         <v>85001500</v>
       </c>
@@ -4882,7 +4358,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:33">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A25" s="13">
         <v>85101100</v>
       </c>
@@ -4983,7 +4459,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:33">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A26" s="13">
         <v>85200700</v>
       </c>
@@ -5082,7 +4558,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:33">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A27" s="13">
         <v>820001</v>
       </c>
@@ -5183,7 +4659,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:33">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A28" s="13">
         <v>820011</v>
       </c>
@@ -5282,7 +4758,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:33">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A29" s="13">
         <v>820031</v>
       </c>
@@ -5345,7 +4821,7 @@
         <v>1000</v>
       </c>
       <c r="V29" s="13" t="s">
-        <v>259</v>
+        <v>435</v>
       </c>
       <c r="W29" s="13">
         <v>1500</v>
@@ -5381,7 +4857,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:33">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A30" s="13">
         <v>820034</v>
       </c>
@@ -5398,14 +4874,14 @@
         <v>820034</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>228</v>
       </c>
       <c r="H30" s="13"/>
       <c r="I30" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>78</v>
@@ -5480,7 +4956,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="31" spans="1:33">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>820051</v>
       </c>
@@ -5497,14 +4973,14 @@
         <v>5200800</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G31" s="12" t="s">
         <v>228</v>
       </c>
       <c r="H31" s="13"/>
       <c r="I31" s="13" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>78</v>
@@ -5537,13 +5013,13 @@
         <v>0</v>
       </c>
       <c r="T31" s="13" t="s">
-        <v>264</v>
+        <v>436</v>
       </c>
       <c r="U31" s="13">
         <v>1000</v>
       </c>
       <c r="V31" s="13" t="s">
-        <v>265</v>
+        <v>437</v>
       </c>
       <c r="W31" s="13">
         <v>0</v>
@@ -5579,7 +5055,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:33">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A32" s="13">
         <v>820054</v>
       </c>
@@ -5596,14 +5072,14 @@
         <v>820054</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="G32" s="12" t="s">
         <v>228</v>
       </c>
       <c r="H32" s="13"/>
       <c r="I32" s="13" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="J32" s="13" t="s">
         <v>78</v>
@@ -5678,7 +5154,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" spans="1:33">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>820061</v>
       </c>
@@ -5695,17 +5171,17 @@
         <v>5001800</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>228</v>
       </c>
       <c r="H33" s="13"/>
       <c r="I33" s="13" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="J33" s="13" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="K33" s="13">
         <v>1</v>
@@ -5714,7 +5190,7 @@
         <v>2000</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="N33" s="13">
         <v>1</v>
@@ -5735,13 +5211,13 @@
         <v>0</v>
       </c>
       <c r="T33" s="13" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="U33" s="13">
         <v>3000</v>
       </c>
       <c r="V33" s="13" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="W33" s="13">
         <v>2000</v>
@@ -5777,7 +5253,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="34" spans="1:33">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>821061</v>
       </c>
@@ -5794,14 +5270,14 @@
         <v>5001600</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="G34" s="12" t="s">
         <v>228</v>
       </c>
       <c r="H34" s="13"/>
       <c r="I34" s="13" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="J34" s="13" t="s">
         <v>78</v>
@@ -5840,7 +5316,7 @@
         <v>1000</v>
       </c>
       <c r="V34" s="13" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="W34" s="13">
         <v>0</v>
@@ -5876,7 +5352,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35" spans="1:33">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A35" s="13">
         <v>820072</v>
       </c>
@@ -5893,14 +5369,14 @@
         <v>820072</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G35" s="12" t="s">
         <v>228</v>
       </c>
       <c r="H35" s="13"/>
       <c r="I35" s="13" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="J35" s="13" t="s">
         <v>78</v>
@@ -5976,17 +5452,16 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="E7:S71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
     <col min="5" max="5" width="27.25" style="1" customWidth="1"/>
@@ -5999,7 +5474,7 @@
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="5:6">
+    <row r="7" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E7" s="1" t="s">
         <v>8</v>
       </c>
@@ -6007,7 +5482,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="5:6">
+    <row r="8" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E8" s="1" t="s">
         <v>9</v>
       </c>
@@ -6015,7 +5490,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="5:6">
+    <row r="9" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E9" s="1" t="s">
         <v>10</v>
       </c>
@@ -6023,15 +5498,15 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="5:6">
+    <row r="10" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="11" spans="5:6">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="11" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E11" s="1" t="s">
         <v>12</v>
       </c>
@@ -6039,7 +5514,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="5:6">
+    <row r="12" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E12" s="1" t="s">
         <v>13</v>
       </c>
@@ -6047,7 +5522,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="5:19">
+    <row r="13" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E13" s="1" t="s">
         <v>14</v>
       </c>
@@ -6055,13 +5530,13 @@
         <v>47</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="14" spans="5:12">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="14" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E14" s="1" t="s">
         <v>15</v>
       </c>
@@ -6075,13 +5550,13 @@
         <v>1</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="15" spans="5:19">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="15" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E15" s="1" t="s">
         <v>16</v>
       </c>
@@ -6092,16 +5567,16 @@
         <v>3</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="16" spans="5:19">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="16" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E16" s="1" t="s">
         <v>17</v>
       </c>
@@ -6115,16 +5590,16 @@
         <v>7</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="17" spans="5:19">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="17" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E17" s="1" t="s">
         <v>18</v>
       </c>
@@ -6138,16 +5613,16 @@
         <v>7</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="18" spans="5:19">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="18" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E18" s="1" t="s">
         <v>19</v>
       </c>
@@ -6161,16 +5636,16 @@
         <v>7</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="19" spans="5:19">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="19" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E19" s="1" t="s">
         <v>20</v>
       </c>
@@ -6182,25 +5657,25 @@
         <v>参数4LIST-触发的技能id</v>
       </c>
       <c r="H19" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="L19" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="S19" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="20" spans="5:19">
+    </row>
+    <row r="20" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E20" s="1" t="s">
         <v>21</v>
       </c>
@@ -6212,25 +5687,25 @@
         <v>参数5-持续时间（毫秒）</v>
       </c>
       <c r="H20" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="L20" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="S20" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="21" spans="5:19">
+    </row>
+    <row r="21" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E21" s="1" t="s">
         <v>22</v>
       </c>
@@ -6242,25 +5717,25 @@
         <v>参数6-效果基础命中率（万分比）</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="22" spans="5:19">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="22" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E22" s="1" t="s">
         <v>23</v>
       </c>
@@ -6275,22 +5750,22 @@
         <v>66</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="23" spans="5:19">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="23" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E23" s="1" t="s">
         <v>24</v>
       </c>
@@ -6302,25 +5777,25 @@
         <v>参数8-效果触发间隔（毫秒）</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="24" spans="5:19">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="24" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E24" s="1" t="s">
         <v>25</v>
       </c>
@@ -6332,25 +5807,25 @@
         <v>参数9-击中回复生命值-固定值</v>
       </c>
       <c r="H24" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="L24" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="S24" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="J24" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="S24" s="1" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="25" spans="5:19">
+    </row>
+    <row r="25" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E25" s="1" t="s">
         <v>26</v>
       </c>
@@ -6362,25 +5837,25 @@
         <v>参数10-击中回复生命值-自身最大生命值百万分比</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="26" spans="5:19">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="26" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E26" s="1" t="s">
         <v>27</v>
       </c>
@@ -6392,25 +5867,25 @@
         <v>参数11-击中回复效果提高万分比</v>
       </c>
       <c r="H26" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="L26" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="S26" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="J26" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="S26" s="1" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="27" spans="5:19">
+    </row>
+    <row r="27" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E27" s="1" t="s">
         <v>28</v>
       </c>
@@ -6422,25 +5897,25 @@
         <v>参数12-击杀回复生命-固定值</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="28" spans="5:12">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="28" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E28" s="1" t="s">
         <v>29</v>
       </c>
@@ -6452,22 +5927,22 @@
         <v>参数13-击杀回复生命-自身最大生命值百万分比</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="29" spans="5:19">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="29" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E29" s="1" t="s">
         <v>30</v>
       </c>
@@ -6479,25 +5954,25 @@
         <v>参数14-击杀回复生命-目标最大生命值百万分比</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="30" spans="5:19">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="30" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E30" s="1" t="s">
         <v>31</v>
       </c>
@@ -6509,25 +5984,25 @@
         <v>参数15-击杀回复生命效果提高万分比</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="31" spans="5:19">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="31" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E31" s="1" t="s">
         <v>32</v>
       </c>
@@ -6539,52 +6014,52 @@
         <v>参数16-获得护盾-固定值</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="32" spans="5:12">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="32" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E32" s="1" t="s">
         <v>33</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="G32" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数17-获得护盾-自身生命百万分比</v>
       </c>
       <c r="H32" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="L32" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="I32" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="33" spans="5:9">
+    </row>
+    <row r="33" spans="5:9" x14ac:dyDescent="0.15">
       <c r="E33" s="1" t="s">
         <v>34</v>
       </c>
@@ -6596,13 +6071,13 @@
         <v>参数18-获得护盾-自身已损失生命万分比</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="34" spans="5:9">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="34" spans="5:9" x14ac:dyDescent="0.15">
       <c r="E34" s="1" t="s">
         <v>35</v>
       </c>
@@ -6614,404 +6089,403 @@
         <v>参数19-获得护盾效果提高万分比</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="35" spans="5:9">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="35" spans="5:9" x14ac:dyDescent="0.15">
       <c r="E35" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="G35" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数20-技能增加-固定值</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="36" spans="7:9">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="36" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G36" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数21-技能增加-万分比</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="37" spans="7:9">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="37" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G37" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数22-技能增加-普通攻击范围万分比</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="38" spans="7:9">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="38" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G38" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数25LIST-攻击提高-攻击的元素类型</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="39" spans="7:9">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="39" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G39" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数25LIST-攻击提高-固定值</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="40" spans="7:9">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="40" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G40" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数25LIST-攻击提高-万分比</v>
       </c>
       <c r="H40" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="I40" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="I40" s="1" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="41" spans="7:9">
+    </row>
+    <row r="41" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G41" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数28-防御提高-固定值</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="42" spans="7:9">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="42" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G42" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数29-防御提高-万分比</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="43" spans="7:9">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="43" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G43" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数30-生命上限提高-固定值</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="44" spans="7:9">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="44" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G44" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数31-生命上限提高-百万分比</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="45" spans="7:9">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="45" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G45" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数32-攻击速度提高-万分比</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="46" spans="7:9">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="46" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G46" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数33-移动速度提高-万分比</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="47" spans="7:9">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="47" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G47" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数34-攻击范围提高-万分比</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="48" spans="7:9">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="48" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G48" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数35-攻击目标数量提高-固定值</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="49" spans="7:8">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="49" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G49" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数36-</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="50" spans="7:8">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="50" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G50" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数37-</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="51" spans="7:8">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="51" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G51" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数38-</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="52" spans="7:8">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="52" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G52" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数39-</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="53" spans="7:8">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="53" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G53" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数40-</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="54" spans="7:8">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="54" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G54" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数41-</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="55" spans="7:8">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="55" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G55" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数42-</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="56" spans="7:8">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="56" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G56" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数41-</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="57" spans="7:8">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="57" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G57" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数42-</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="58" spans="7:8">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="58" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G58" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数43-</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="59" spans="7:8">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="59" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G59" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数44-</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="60" spans="7:8">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="60" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G60" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数45-</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="61" spans="7:8">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="61" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G61" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数46-</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="62" spans="7:8">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="62" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G62" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数47-</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="63" spans="7:8">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="63" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G63" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数48-</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="64" spans="7:8">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="64" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G64" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数49-</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="65" spans="7:8">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="65" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G65" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数50-</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="66" spans="7:8">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="66" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G66" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数51-</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="67" spans="7:8">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="67" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G67" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数52-</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="68" spans="7:8">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="68" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G68" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数53-</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="69" spans="7:8">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="69" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G69" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数54-</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="70" spans="7:8">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="70" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G70" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数55-</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="71" spans="7:8">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="71" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G71" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数56-</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="D6:F43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="11.25" style="1" customWidth="1"/>
@@ -7021,172 +6495,172 @@
     <col min="23" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="4:5">
+    <row r="6" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D6" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="4:5">
+    <row r="7" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D7" s="2">
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="8" spans="4:5">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="8" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="4:5">
+    <row r="9" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D9" s="2">
         <v>2</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="10" spans="4:5">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="10" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D10" s="2">
         <v>2.1</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="11" spans="4:5" x14ac:dyDescent="0.15">
+      <c r="D11" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="12" spans="4:5" x14ac:dyDescent="0.15">
+      <c r="D12" s="2" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="11" spans="4:5">
-      <c r="D11" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="E11" s="2" t="s">
+    </row>
+    <row r="13" spans="4:5" x14ac:dyDescent="0.15">
+      <c r="D13" s="2" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="12" spans="4:5">
-      <c r="D12" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="13" spans="4:5">
-      <c r="D13" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="14" spans="4:5">
+    </row>
+    <row r="14" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="4:5">
+    <row r="15" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D15" s="2">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="16" spans="4:5" x14ac:dyDescent="0.15">
+      <c r="D16" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="17" spans="4:5" x14ac:dyDescent="0.15">
+      <c r="D17" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="16" spans="4:5">
-      <c r="D16" s="2" t="s">
+    <row r="18" spans="4:5" x14ac:dyDescent="0.15">
+      <c r="D18" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="17" spans="4:5">
-      <c r="D17" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="E17" s="2" t="s">
+    </row>
+    <row r="28" spans="4:5" x14ac:dyDescent="0.15">
+      <c r="D28" s="1" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="18" spans="4:5">
-      <c r="D18" s="2" t="s">
+    <row r="29" spans="4:5" x14ac:dyDescent="0.15">
+      <c r="D29" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="28" spans="4:4">
-      <c r="D28" s="1" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="29" spans="4:5">
-      <c r="D29" s="1" t="s">
-        <v>433</v>
       </c>
       <c r="E29" s="1">
         <v>101</v>
       </c>
     </row>
-    <row r="30" spans="4:5">
+    <row r="30" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D30" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E30" s="1">
         <v>102</v>
       </c>
     </row>
-    <row r="31" spans="4:4">
+    <row r="31" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D31" s="1" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="32" spans="4:4">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="32" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D32" s="1" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="33" ht="14.25" spans="4:6">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="33" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="D33" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E33" s="1">
         <v>105</v>
       </c>
       <c r="F33"/>
     </row>
-    <row r="34" ht="14.25" spans="6:6">
+    <row r="34" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F34"/>
     </row>
-    <row r="35" ht="14.25" spans="6:6">
+    <row r="35" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F35"/>
     </row>
-    <row r="36" ht="14.25" spans="6:6">
+    <row r="36" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F36"/>
     </row>
-    <row r="37" ht="14.25" spans="6:6">
+    <row r="37" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F37"/>
     </row>
-    <row r="38" ht="14.25" spans="6:6">
+    <row r="38" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F38"/>
     </row>
-    <row r="39" ht="14.25" spans="6:6">
+    <row r="39" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F39"/>
     </row>
-    <row r="40" ht="14.25" spans="6:6">
+    <row r="40" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F40"/>
     </row>
-    <row r="41" ht="14.25" spans="6:6">
+    <row r="41" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F41"/>
     </row>
-    <row r="42" ht="14.25" spans="6:6">
+    <row r="42" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F42"/>
     </row>
-    <row r="43" ht="14.25" spans="6:6">
+    <row r="43" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F43"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2064E22E-108A-4C13-8B11-A9B2FBCC5A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -29,6 +23,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,34 +32,32 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>pe</author>
     <author>cltx</author>
   </authors>
   <commentList>
-    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="C4" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>数字越大，优先级越高</t>
         </r>
       </text>
     </comment>
-    <comment ref="K4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="K4" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>cltx:</t>
@@ -72,7 +66,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -82,13 +75,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="U4" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">&gt;0，持续时间
@@ -103,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="437">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -894,6 +886,12 @@
     <t>电刃普攻麻痹状态（无法攻击和移动），持续时间【参数5】（默认1000）毫秒，状态命中率【参数6】（默认20%）</t>
   </si>
   <si>
+    <t>5200712:1</t>
+  </si>
+  <si>
+    <t>5200711:1</t>
+  </si>
+  <si>
     <t>天罚</t>
   </si>
   <si>
@@ -1408,25 +1406,19 @@
   </si>
   <si>
     <t>冰冻</t>
-  </si>
-  <si>
-    <t>5200701:1</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>5200712:1</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>5200711:1</t>
-    <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1438,35 +1430,30 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF9C5700"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <color theme="0" tint="-4.9989318521683403E-2"/>
+      <color theme="0" tint="-0.0499893185216834"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1474,14 +1461,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1489,60 +1474,169 @@
       <sz val="9"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1551,13 +1645,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <fgColor theme="0" tint="-0.349986266670736"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79967650379955446"/>
+        <fgColor theme="8" tint="0.799676503799554"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1575,7 +1669,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1585,8 +1703,152 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1624,23 +1886,241 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1655,8 +2135,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="24" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1664,39 +2144,80 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="23" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="24" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="24" applyFont="1" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="5">
-    <cellStyle name="差" xfId="2" builtinId="27"/>
-    <cellStyle name="差 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="适中" xfId="3" builtinId="28"/>
-    <cellStyle name="输入" xfId="1" builtinId="20"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="差 2" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1974,14 +2495,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AG35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -2012,7 +2533,7 @@
     <col min="33" max="33" width="17.125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2045,7 +2566,7 @@
       <c r="AB1" s="4"/>
       <c r="AC1" s="4"/>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:33">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -2146,7 +2667,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:33">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
@@ -2247,7 +2768,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:33">
       <c r="A4" s="4" t="s">
         <v>41</v>
       </c>
@@ -2348,7 +2869,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33">
       <c r="A5" s="6">
         <v>1000001</v>
       </c>
@@ -2449,7 +2970,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33">
       <c r="A6" s="7">
         <v>2000001</v>
       </c>
@@ -2550,7 +3071,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33">
       <c r="A7" s="8">
         <v>54010001</v>
       </c>
@@ -2651,7 +3172,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33">
       <c r="A8" s="8">
         <v>54020001</v>
       </c>
@@ -2752,7 +3273,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33">
       <c r="A9" s="8">
         <v>54030001</v>
       </c>
@@ -2853,7 +3374,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33">
       <c r="A10" s="8">
         <v>54040001</v>
       </c>
@@ -2954,7 +3475,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33">
       <c r="A11" s="8">
         <v>54050001</v>
       </c>
@@ -3055,7 +3576,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:33">
       <c r="A12" s="8">
         <v>54060001</v>
       </c>
@@ -3156,7 +3677,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33">
       <c r="A13" s="8">
         <v>54070001</v>
       </c>
@@ -3257,7 +3778,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:33">
       <c r="A14" s="8">
         <v>54080001</v>
       </c>
@@ -3358,7 +3879,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33">
       <c r="A15" s="8">
         <v>54090001</v>
       </c>
@@ -3459,7 +3980,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33">
       <c r="A16" s="8">
         <v>54100001</v>
       </c>
@@ -3560,7 +4081,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:33">
       <c r="A17" s="8">
         <v>54110001</v>
       </c>
@@ -3661,7 +4182,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:33">
       <c r="A18" s="8">
         <v>54120001</v>
       </c>
@@ -3762,7 +4283,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:33">
       <c r="A19" s="8">
         <v>54130001</v>
       </c>
@@ -3863,7 +4384,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:33">
       <c r="A20" s="8">
         <v>54140001</v>
       </c>
@@ -3964,7 +4485,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:33">
       <c r="A21" s="8">
         <v>54150001</v>
       </c>
@@ -4065,7 +4586,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:33">
       <c r="A22" s="10">
         <v>59130001</v>
       </c>
@@ -4162,7 +4683,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:33">
       <c r="A23" s="10">
         <v>59140001</v>
       </c>
@@ -4259,7 +4780,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:33">
       <c r="A24" s="13">
         <v>85001500</v>
       </c>
@@ -4358,7 +4879,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:33">
       <c r="A25" s="13">
         <v>85101100</v>
       </c>
@@ -4459,7 +4980,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:33">
       <c r="A26" s="13">
         <v>85200700</v>
       </c>
@@ -4558,7 +5079,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:33">
       <c r="A27" s="13">
         <v>820001</v>
       </c>
@@ -4659,7 +5180,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:33">
       <c r="A28" s="13">
         <v>820011</v>
       </c>
@@ -4758,7 +5279,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:33">
       <c r="A29" s="13">
         <v>820031</v>
       </c>
@@ -4821,10 +5342,10 @@
         <v>1000</v>
       </c>
       <c r="V29" s="13" t="s">
-        <v>435</v>
+        <v>243</v>
       </c>
       <c r="W29" s="13">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="X29" s="13" t="s">
         <v>78</v>
@@ -4857,7 +5378,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:33">
       <c r="A30" s="13">
         <v>820034</v>
       </c>
@@ -4956,7 +5477,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:33">
       <c r="A31" s="4">
         <v>820051</v>
       </c>
@@ -5013,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="T31" s="13" t="s">
-        <v>436</v>
+        <v>263</v>
       </c>
       <c r="U31" s="13">
         <v>1000</v>
       </c>
       <c r="V31" s="13" t="s">
-        <v>437</v>
+        <v>264</v>
       </c>
       <c r="W31" s="13">
         <v>0</v>
@@ -5055,7 +5576,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:33">
       <c r="A32" s="13">
         <v>820054</v>
       </c>
@@ -5072,14 +5593,14 @@
         <v>820054</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G32" s="12" t="s">
         <v>228</v>
       </c>
       <c r="H32" s="13"/>
       <c r="I32" s="13" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J32" s="13" t="s">
         <v>78</v>
@@ -5154,7 +5675,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:33">
       <c r="A33" s="4">
         <v>820061</v>
       </c>
@@ -5171,17 +5692,17 @@
         <v>5001800</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>228</v>
       </c>
       <c r="H33" s="13"/>
       <c r="I33" s="13" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="J33" s="13" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="K33" s="13">
         <v>1</v>
@@ -5190,7 +5711,7 @@
         <v>2000</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N33" s="13">
         <v>1</v>
@@ -5211,13 +5732,13 @@
         <v>0</v>
       </c>
       <c r="T33" s="13" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="U33" s="13">
         <v>3000</v>
       </c>
       <c r="V33" s="13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="W33" s="13">
         <v>2000</v>
@@ -5253,7 +5774,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:33">
       <c r="A34" s="4">
         <v>821061</v>
       </c>
@@ -5270,14 +5791,14 @@
         <v>5001600</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G34" s="12" t="s">
         <v>228</v>
       </c>
       <c r="H34" s="13"/>
       <c r="I34" s="13" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="J34" s="13" t="s">
         <v>78</v>
@@ -5316,7 +5837,7 @@
         <v>1000</v>
       </c>
       <c r="V34" s="13" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="W34" s="13">
         <v>0</v>
@@ -5352,7 +5873,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:33">
       <c r="A35" s="13">
         <v>820072</v>
       </c>
@@ -5369,14 +5890,14 @@
         <v>820072</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G35" s="12" t="s">
         <v>228</v>
       </c>
       <c r="H35" s="13"/>
       <c r="I35" s="13" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="J35" s="13" t="s">
         <v>78</v>
@@ -5452,16 +5973,17 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="E7:S71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
     <col min="5" max="5" width="27.25" style="1" customWidth="1"/>
@@ -5474,7 +5996,7 @@
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="5:19" x14ac:dyDescent="0.15">
+    <row r="7" spans="5:6">
       <c r="E7" s="1" t="s">
         <v>8</v>
       </c>
@@ -5482,7 +6004,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="5:19" x14ac:dyDescent="0.15">
+    <row r="8" spans="5:6">
       <c r="E8" s="1" t="s">
         <v>9</v>
       </c>
@@ -5490,7 +6012,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="5:19" x14ac:dyDescent="0.15">
+    <row r="9" spans="5:6">
       <c r="E9" s="1" t="s">
         <v>10</v>
       </c>
@@ -5498,15 +6020,15 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="5:19" x14ac:dyDescent="0.15">
+    <row r="10" spans="5:6">
       <c r="E10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="11" spans="5:19" x14ac:dyDescent="0.15">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="11" spans="5:6">
       <c r="E11" s="1" t="s">
         <v>12</v>
       </c>
@@ -5514,7 +6036,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="5:19" x14ac:dyDescent="0.15">
+    <row r="12" spans="5:6">
       <c r="E12" s="1" t="s">
         <v>13</v>
       </c>
@@ -5522,7 +6044,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="5:19" x14ac:dyDescent="0.15">
+    <row r="13" spans="5:19">
       <c r="E13" s="1" t="s">
         <v>14</v>
       </c>
@@ -5530,13 +6052,13 @@
         <v>47</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="14" spans="5:19" x14ac:dyDescent="0.15">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="14" spans="5:12">
       <c r="E14" s="1" t="s">
         <v>15</v>
       </c>
@@ -5550,13 +6072,13 @@
         <v>1</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="15" spans="5:19" x14ac:dyDescent="0.15">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="15" spans="5:19">
       <c r="E15" s="1" t="s">
         <v>16</v>
       </c>
@@ -5567,16 +6089,16 @@
         <v>3</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="16" spans="5:19" x14ac:dyDescent="0.15">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="16" spans="5:19">
       <c r="E16" s="1" t="s">
         <v>17</v>
       </c>
@@ -5590,16 +6112,16 @@
         <v>7</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="17" spans="5:19" x14ac:dyDescent="0.15">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="17" spans="5:19">
       <c r="E17" s="1" t="s">
         <v>18</v>
       </c>
@@ -5613,16 +6135,16 @@
         <v>7</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="18" spans="5:19" x14ac:dyDescent="0.15">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="18" spans="5:19">
       <c r="E18" s="1" t="s">
         <v>19</v>
       </c>
@@ -5636,16 +6158,16 @@
         <v>7</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="19" spans="5:19" x14ac:dyDescent="0.15">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="19" spans="5:19">
       <c r="E19" s="1" t="s">
         <v>20</v>
       </c>
@@ -5657,25 +6179,25 @@
         <v>参数4LIST-触发的技能id</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="20" spans="5:19" x14ac:dyDescent="0.15">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="20" spans="5:19">
       <c r="E20" s="1" t="s">
         <v>21</v>
       </c>
@@ -5687,25 +6209,25 @@
         <v>参数5-持续时间（毫秒）</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="21" spans="5:19" x14ac:dyDescent="0.15">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="21" spans="5:19">
       <c r="E21" s="1" t="s">
         <v>22</v>
       </c>
@@ -5717,25 +6239,25 @@
         <v>参数6-效果基础命中率（万分比）</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="22" spans="5:19" x14ac:dyDescent="0.15">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="22" spans="5:19">
       <c r="E22" s="1" t="s">
         <v>23</v>
       </c>
@@ -5750,22 +6272,22 @@
         <v>66</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="23" spans="5:19" x14ac:dyDescent="0.15">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="23" spans="5:19">
       <c r="E23" s="1" t="s">
         <v>24</v>
       </c>
@@ -5777,25 +6299,25 @@
         <v>参数8-效果触发间隔（毫秒）</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="24" spans="5:19" x14ac:dyDescent="0.15">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="24" spans="5:19">
       <c r="E24" s="1" t="s">
         <v>25</v>
       </c>
@@ -5807,25 +6329,25 @@
         <v>参数9-击中回复生命值-固定值</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="25" spans="5:19" x14ac:dyDescent="0.15">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="25" spans="5:19">
       <c r="E25" s="1" t="s">
         <v>26</v>
       </c>
@@ -5837,25 +6359,25 @@
         <v>参数10-击中回复生命值-自身最大生命值百万分比</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="26" spans="5:19" x14ac:dyDescent="0.15">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="26" spans="5:19">
       <c r="E26" s="1" t="s">
         <v>27</v>
       </c>
@@ -5867,25 +6389,25 @@
         <v>参数11-击中回复效果提高万分比</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="27" spans="5:19" x14ac:dyDescent="0.15">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="27" spans="5:19">
       <c r="E27" s="1" t="s">
         <v>28</v>
       </c>
@@ -5897,25 +6419,25 @@
         <v>参数12-击杀回复生命-固定值</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="28" spans="5:19" x14ac:dyDescent="0.15">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="28" spans="5:12">
       <c r="E28" s="1" t="s">
         <v>29</v>
       </c>
@@ -5927,22 +6449,22 @@
         <v>参数13-击杀回复生命-自身最大生命值百万分比</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="29" spans="5:19" x14ac:dyDescent="0.15">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="29" spans="5:19">
       <c r="E29" s="1" t="s">
         <v>30</v>
       </c>
@@ -5954,25 +6476,25 @@
         <v>参数14-击杀回复生命-目标最大生命值百万分比</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="30" spans="5:19" x14ac:dyDescent="0.15">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="30" spans="5:19">
       <c r="E30" s="1" t="s">
         <v>31</v>
       </c>
@@ -5984,25 +6506,25 @@
         <v>参数15-击杀回复生命效果提高万分比</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="31" spans="5:19" x14ac:dyDescent="0.15">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="31" spans="5:19">
       <c r="E31" s="1" t="s">
         <v>32</v>
       </c>
@@ -6014,52 +6536,52 @@
         <v>参数16-获得护盾-固定值</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="32" spans="5:19" x14ac:dyDescent="0.15">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="32" spans="5:12">
       <c r="E32" s="1" t="s">
         <v>33</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G32" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数17-获得护盾-自身生命百万分比</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="33" spans="5:9" x14ac:dyDescent="0.15">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="33" spans="5:9">
       <c r="E33" s="1" t="s">
         <v>34</v>
       </c>
@@ -6071,13 +6593,13 @@
         <v>参数18-获得护盾-自身已损失生命万分比</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="34" spans="5:9" x14ac:dyDescent="0.15">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="34" spans="5:9">
       <c r="E34" s="1" t="s">
         <v>35</v>
       </c>
@@ -6089,403 +6611,404 @@
         <v>参数19-获得护盾效果提高万分比</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="35" spans="5:9" x14ac:dyDescent="0.15">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="35" spans="5:9">
       <c r="E35" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G35" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数20-技能增加-固定值</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="36" spans="5:9" x14ac:dyDescent="0.15">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="36" spans="7:9">
       <c r="G36" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数21-技能增加-万分比</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="37" spans="5:9" x14ac:dyDescent="0.15">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="37" spans="7:9">
       <c r="G37" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数22-技能增加-普通攻击范围万分比</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="38" spans="5:9" x14ac:dyDescent="0.15">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="38" spans="7:9">
       <c r="G38" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数25LIST-攻击提高-攻击的元素类型</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="39" spans="5:9" x14ac:dyDescent="0.15">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="39" spans="7:9">
       <c r="G39" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数25LIST-攻击提高-固定值</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="40" spans="5:9" x14ac:dyDescent="0.15">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="40" spans="7:9">
       <c r="G40" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数25LIST-攻击提高-万分比</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="41" spans="5:9" x14ac:dyDescent="0.15">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="41" spans="7:9">
       <c r="G41" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数28-防御提高-固定值</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="42" spans="5:9" x14ac:dyDescent="0.15">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="42" spans="7:9">
       <c r="G42" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数29-防御提高-万分比</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="43" spans="5:9" x14ac:dyDescent="0.15">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="43" spans="7:9">
       <c r="G43" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数30-生命上限提高-固定值</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="44" spans="5:9" x14ac:dyDescent="0.15">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="44" spans="7:9">
       <c r="G44" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数31-生命上限提高-百万分比</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="45" spans="5:9" x14ac:dyDescent="0.15">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="45" spans="7:9">
       <c r="G45" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数32-攻击速度提高-万分比</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="46" spans="5:9" x14ac:dyDescent="0.15">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="46" spans="7:9">
       <c r="G46" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数33-移动速度提高-万分比</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="47" spans="5:9" x14ac:dyDescent="0.15">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="47" spans="7:9">
       <c r="G47" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数34-攻击范围提高-万分比</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="48" spans="5:9" x14ac:dyDescent="0.15">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="48" spans="7:9">
       <c r="G48" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数35-攻击目标数量提高-固定值</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="49" spans="7:8" x14ac:dyDescent="0.15">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="49" spans="7:8">
       <c r="G49" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数36-</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="50" spans="7:8" x14ac:dyDescent="0.15">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="50" spans="7:8">
       <c r="G50" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数37-</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="51" spans="7:8" x14ac:dyDescent="0.15">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="51" spans="7:8">
       <c r="G51" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数38-</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="52" spans="7:8" x14ac:dyDescent="0.15">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="52" spans="7:8">
       <c r="G52" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数39-</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="53" spans="7:8" x14ac:dyDescent="0.15">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="53" spans="7:8">
       <c r="G53" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数40-</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="54" spans="7:8" x14ac:dyDescent="0.15">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="54" spans="7:8">
       <c r="G54" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数41-</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="55" spans="7:8" x14ac:dyDescent="0.15">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="55" spans="7:8">
       <c r="G55" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数42-</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="56" spans="7:8" x14ac:dyDescent="0.15">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="56" spans="7:8">
       <c r="G56" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数41-</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="57" spans="7:8" x14ac:dyDescent="0.15">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="57" spans="7:8">
       <c r="G57" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数42-</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="58" spans="7:8" x14ac:dyDescent="0.15">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="58" spans="7:8">
       <c r="G58" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数43-</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="59" spans="7:8" x14ac:dyDescent="0.15">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="59" spans="7:8">
       <c r="G59" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数44-</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="60" spans="7:8" x14ac:dyDescent="0.15">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="60" spans="7:8">
       <c r="G60" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数45-</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="61" spans="7:8" x14ac:dyDescent="0.15">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="61" spans="7:8">
       <c r="G61" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数46-</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="62" spans="7:8" x14ac:dyDescent="0.15">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="62" spans="7:8">
       <c r="G62" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数47-</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="63" spans="7:8" x14ac:dyDescent="0.15">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="63" spans="7:8">
       <c r="G63" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数48-</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="64" spans="7:8" x14ac:dyDescent="0.15">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="64" spans="7:8">
       <c r="G64" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数49-</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="65" spans="7:8" x14ac:dyDescent="0.15">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="65" spans="7:8">
       <c r="G65" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数50-</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="66" spans="7:8" x14ac:dyDescent="0.15">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="66" spans="7:8">
       <c r="G66" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数51-</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="67" spans="7:8" x14ac:dyDescent="0.15">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="67" spans="7:8">
       <c r="G67" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数52-</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="68" spans="7:8" x14ac:dyDescent="0.15">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="68" spans="7:8">
       <c r="G68" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数53-</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="69" spans="7:8" x14ac:dyDescent="0.15">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="69" spans="7:8">
       <c r="G69" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数54-</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="70" spans="7:8" x14ac:dyDescent="0.15">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="70" spans="7:8">
       <c r="G70" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数55-</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="71" spans="7:8" x14ac:dyDescent="0.15">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="71" spans="7:8">
       <c r="G71" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数56-</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="D6:F43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="11.25" style="1" customWidth="1"/>
@@ -6495,172 +7018,172 @@
     <col min="23" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="4:5" x14ac:dyDescent="0.15">
+    <row r="6" spans="4:5">
       <c r="D6" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="4:5" x14ac:dyDescent="0.15">
+    <row r="7" spans="4:5">
       <c r="D7" s="2">
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="8" spans="4:5" x14ac:dyDescent="0.15">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="8" spans="4:5">
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="4:5" x14ac:dyDescent="0.15">
+    <row r="9" spans="4:5">
       <c r="D9" s="2">
         <v>2</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="10" spans="4:5" x14ac:dyDescent="0.15">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="10" spans="4:5">
       <c r="D10" s="2">
         <v>2.1</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="11" spans="4:5" x14ac:dyDescent="0.15">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="11" spans="4:5">
       <c r="D11" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="12" spans="4:5" x14ac:dyDescent="0.15">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="12" spans="4:5">
       <c r="D12" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="13" spans="4:5" x14ac:dyDescent="0.15">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="13" spans="4:5">
       <c r="D13" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="14" spans="4:5" x14ac:dyDescent="0.15">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="14" spans="4:5">
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="4:5" x14ac:dyDescent="0.15">
+    <row r="15" spans="4:5">
       <c r="D15" s="2">
-        <v>2.2000000000000002</v>
+        <v>2.2</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="16" spans="4:5" x14ac:dyDescent="0.15">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="16" spans="4:5">
       <c r="D16" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.15">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="17" spans="4:5">
       <c r="D17" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.15">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="18" spans="4:5">
       <c r="D18" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="28" spans="4:5" x14ac:dyDescent="0.15">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="28" spans="4:4">
       <c r="D28" s="1" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="29" spans="4:5" x14ac:dyDescent="0.15">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="29" spans="4:5">
       <c r="D29" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E29" s="1">
         <v>101</v>
       </c>
     </row>
-    <row r="30" spans="4:5" x14ac:dyDescent="0.15">
+    <row r="30" spans="4:5">
       <c r="D30" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E30" s="1">
         <v>102</v>
       </c>
     </row>
-    <row r="31" spans="4:5" x14ac:dyDescent="0.15">
+    <row r="31" spans="4:4">
       <c r="D31" s="1" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="32" spans="4:5" x14ac:dyDescent="0.15">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="32" spans="4:4">
       <c r="D32" s="1" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="33" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25" spans="4:6">
       <c r="D33" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E33" s="1">
         <v>105</v>
       </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="34" ht="14.25" spans="6:6">
       <c r="F34"/>
     </row>
-    <row r="35" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="35" ht="14.25" spans="6:6">
       <c r="F35"/>
     </row>
-    <row r="36" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="36" ht="14.25" spans="6:6">
       <c r="F36"/>
     </row>
-    <row r="37" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="37" ht="14.25" spans="6:6">
       <c r="F37"/>
     </row>
-    <row r="38" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="38" ht="14.25" spans="6:6">
       <c r="F38"/>
     </row>
-    <row r="39" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="39" ht="14.25" spans="6:6">
       <c r="F39"/>
     </row>
-    <row r="40" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="40" ht="14.25" spans="6:6">
       <c r="F40"/>
     </row>
-    <row r="41" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="41" ht="14.25" spans="6:6">
       <c r="F41"/>
     </row>
-    <row r="42" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="42" ht="14.25" spans="6:6">
       <c r="F42"/>
     </row>
-    <row r="43" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="43" ht="14.25" spans="6:6">
       <c r="F43"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -1636,7 +1636,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1724,12 +1724,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2056,64 +2050,64 @@
     <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5543,7 +5537,7 @@
         <v>264</v>
       </c>
       <c r="W31" s="13">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="X31" s="13" t="s">
         <v>78</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -5537,7 +5537,7 @@
         <v>264</v>
       </c>
       <c r="W31" s="13">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="X31" s="13" t="s">
         <v>78</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7964A3E6-1F18-4E36-BADD-A7D202EA37CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -23,8 +29,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -32,32 +36,34 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>pe</author>
     <author>cltx</author>
   </authors>
   <commentList>
-    <comment ref="C4" authorId="0">
+    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>数字越大，优先级越高</t>
         </r>
       </text>
     </comment>
-    <comment ref="K4" authorId="1">
+    <comment ref="K4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>cltx:</t>
@@ -66,6 +72,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -75,12 +82,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="0">
+    <comment ref="U4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">&gt;0，持续时间
@@ -95,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="442">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1406,19 +1414,33 @@
   </si>
   <si>
     <t>冰冻</t>
+  </si>
+  <si>
+    <t>冰球概率附加冰冻</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰球冰冻状态（无法攻击和移动），持续时间【参数5】毫秒，状态命中率【参数6】</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>5001511:1</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>5001512:1</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>5001501:1</t>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="31">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1430,30 +1452,35 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF9C5700"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <color theme="0" tint="-0.0499893185216834"/>
+      <color theme="0" tint="-4.9989318521683403E-2"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1461,12 +1488,14 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1474,169 +1503,60 @@
       <sz val="9"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1645,13 +1565,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.349986266670736"/>
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799676503799554"/>
+        <fgColor theme="8" tint="0.79964598529007846"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1669,31 +1589,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1703,146 +1599,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1880,241 +1638,23 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2129,8 +1669,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="24" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2138,80 +1678,36 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="23" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="24" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="24" applyFont="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="5">
+    <cellStyle name="差" xfId="2" builtinId="27"/>
+    <cellStyle name="差 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="差 2" xfId="49"/>
+    <cellStyle name="适中" xfId="3" builtinId="28"/>
+    <cellStyle name="输入" xfId="1" builtinId="20"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2489,14 +1985,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:AG35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AG36"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -2527,7 +2023,7 @@
     <col min="33" max="33" width="17.125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2560,7 +2056,7 @@
       <c r="AB1" s="4"/>
       <c r="AC1" s="4"/>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -2597,13 +2093,13 @@
       <c r="L2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="M2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="N2" s="16" t="s">
+      <c r="N2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="16" t="s">
+      <c r="O2" s="15" t="s">
         <v>2</v>
       </c>
       <c r="P2" s="4" t="s">
@@ -2615,7 +2111,7 @@
       <c r="R2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="S2" s="16" t="s">
+      <c r="S2" s="15" t="s">
         <v>5</v>
       </c>
       <c r="T2" s="4" t="s">
@@ -2639,29 +2135,29 @@
       <c r="Z2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="AA2" s="16" t="s">
+      <c r="AA2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="AB2" s="16" t="s">
+      <c r="AB2" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="AC2" s="16" t="s">
+      <c r="AC2" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="AD2" s="20" t="s">
+      <c r="AD2" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="AE2" s="20" t="s">
+      <c r="AE2" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="AF2" s="20" t="s">
+      <c r="AF2" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="AG2" s="20" t="s">
+      <c r="AG2" s="19" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:33">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
@@ -2698,13 +2194,13 @@
       <c r="L3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="M3" s="16" t="s">
+      <c r="M3" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="16" t="s">
+      <c r="N3" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="16" t="s">
+      <c r="O3" s="15" t="s">
         <v>22</v>
       </c>
       <c r="P3" s="4" t="s">
@@ -2716,7 +2212,7 @@
       <c r="R3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="S3" s="16" t="s">
+      <c r="S3" s="15" t="s">
         <v>26</v>
       </c>
       <c r="T3" s="4" t="s">
@@ -2740,29 +2236,29 @@
       <c r="Z3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="AA3" s="16" t="s">
+      <c r="AA3" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="AB3" s="16" t="s">
+      <c r="AB3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="AC3" s="16" t="s">
+      <c r="AC3" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="AD3" s="20" t="s">
+      <c r="AD3" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="AE3" s="20" t="s">
+      <c r="AE3" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="AF3" s="20" t="s">
+      <c r="AF3" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="AG3" s="20" t="s">
+      <c r="AG3" s="19" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:33">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>41</v>
       </c>
@@ -2799,13 +2295,13 @@
       <c r="L4" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="M4" s="16" t="s">
+      <c r="M4" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="N4" s="16" t="s">
+      <c r="N4" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="O4" s="16" t="s">
+      <c r="O4" s="15" t="s">
         <v>55</v>
       </c>
       <c r="P4" s="4" t="s">
@@ -2817,7 +2313,7 @@
       <c r="R4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="S4" s="16" t="s">
+      <c r="S4" s="15" t="s">
         <v>59</v>
       </c>
       <c r="T4" s="4" t="s">
@@ -2841,29 +2337,29 @@
       <c r="Z4" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AA4" s="16" t="s">
+      <c r="AA4" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="AB4" s="16" t="s">
+      <c r="AB4" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="AC4" s="16" t="s">
+      <c r="AC4" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="AD4" s="20" t="s">
+      <c r="AD4" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="AE4" s="20" t="s">
+      <c r="AE4" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="AF4" s="20" t="s">
+      <c r="AF4" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="AG4" s="20" t="s">
+      <c r="AG4" s="19" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:33">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>1000001</v>
       </c>
@@ -2891,7 +2387,7 @@
       <c r="I5" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="J5" s="21" t="s">
+      <c r="J5" s="20" t="s">
         <v>78</v>
       </c>
       <c r="K5" s="6">
@@ -2900,16 +2396,16 @@
       <c r="L5" s="6">
         <v>400000</v>
       </c>
-      <c r="M5" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="N5" s="17">
-        <v>1</v>
-      </c>
-      <c r="O5" s="17">
-        <v>0</v>
-      </c>
-      <c r="P5" s="21" t="s">
+      <c r="M5" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="N5" s="16">
+        <v>1</v>
+      </c>
+      <c r="O5" s="16">
+        <v>0</v>
+      </c>
+      <c r="P5" s="20" t="s">
         <v>78</v>
       </c>
       <c r="Q5" s="6">
@@ -2918,16 +2414,16 @@
       <c r="R5" s="6">
         <v>0</v>
       </c>
-      <c r="S5" s="18">
-        <v>0</v>
-      </c>
-      <c r="T5" s="21" t="s">
+      <c r="S5" s="17">
+        <v>0</v>
+      </c>
+      <c r="T5" s="20" t="s">
         <v>78</v>
       </c>
       <c r="U5" s="6">
         <v>0</v>
       </c>
-      <c r="V5" s="21" t="s">
+      <c r="V5" s="20" t="s">
         <v>78</v>
       </c>
       <c r="W5" s="6">
@@ -2942,13 +2438,13 @@
       <c r="Z5" s="6">
         <v>0</v>
       </c>
-      <c r="AA5" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB5" s="17">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="17">
+      <c r="AA5" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB5" s="16">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="16">
         <v>0</v>
       </c>
       <c r="AD5" s="8" t="s">
@@ -2964,7 +2460,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:33">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>2000001</v>
       </c>
@@ -3010,7 +2506,7 @@
       <c r="O6" s="7">
         <v>0</v>
       </c>
-      <c r="P6" s="23" t="s">
+      <c r="P6" s="22" t="s">
         <v>78</v>
       </c>
       <c r="Q6" s="7">
@@ -3019,22 +2515,22 @@
       <c r="R6" s="7">
         <v>0</v>
       </c>
-      <c r="S6" s="19">
-        <v>0</v>
-      </c>
-      <c r="T6" s="23" t="s">
+      <c r="S6" s="18">
+        <v>0</v>
+      </c>
+      <c r="T6" s="22" t="s">
         <v>78</v>
       </c>
       <c r="U6" s="7">
         <v>0</v>
       </c>
-      <c r="V6" s="23" t="s">
+      <c r="V6" s="22" t="s">
         <v>78</v>
       </c>
       <c r="W6" s="7">
         <v>10000</v>
       </c>
-      <c r="X6" s="23" t="s">
+      <c r="X6" s="22" t="s">
         <v>78</v>
       </c>
       <c r="Y6" s="7">
@@ -3065,7 +2561,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:33">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>54010001</v>
       </c>
@@ -3166,7 +2662,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="1:33">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
         <v>54020001</v>
       </c>
@@ -3267,7 +2763,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:33">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>54030001</v>
       </c>
@@ -3368,7 +2864,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:33">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A10" s="8">
         <v>54040001</v>
       </c>
@@ -3469,7 +2965,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:33">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>54050001</v>
       </c>
@@ -3570,7 +3066,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:33">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>54060001</v>
       </c>
@@ -3671,7 +3167,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="13" spans="1:33">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>54070001</v>
       </c>
@@ -3772,7 +3268,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:33">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>54080001</v>
       </c>
@@ -3873,7 +3369,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="15" spans="1:33">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>54090001</v>
       </c>
@@ -3974,7 +3470,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="16" spans="1:33">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A16" s="8">
         <v>54100001</v>
       </c>
@@ -4075,7 +3571,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="17" spans="1:33">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A17" s="8">
         <v>54110001</v>
       </c>
@@ -4176,7 +3672,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="18" spans="1:33">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A18" s="8">
         <v>54120001</v>
       </c>
@@ -4277,7 +3773,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="19" spans="1:33">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A19" s="8">
         <v>54130001</v>
       </c>
@@ -4378,7 +3874,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="20" spans="1:33">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A20" s="8">
         <v>54140001</v>
       </c>
@@ -4479,7 +3975,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="21" spans="1:33">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A21" s="8">
         <v>54150001</v>
       </c>
@@ -4580,7 +4076,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="22" spans="1:33">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A22" s="10">
         <v>59130001</v>
       </c>
@@ -4677,7 +4173,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" spans="1:33">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A23" s="10">
         <v>59140001</v>
       </c>
@@ -4774,7 +4270,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:33">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A24" s="13">
         <v>85001500</v>
       </c>
@@ -4873,7 +4369,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:33">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A25" s="13">
         <v>85101100</v>
       </c>
@@ -4974,7 +4470,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:33">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A26" s="13">
         <v>85200700</v>
       </c>
@@ -5073,7 +4569,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:33">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A27" s="13">
         <v>820001</v>
       </c>
@@ -5174,7 +4670,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:33">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A28" s="13">
         <v>820011</v>
       </c>
@@ -5273,7 +4769,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:33">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A29" s="13">
         <v>820031</v>
       </c>
@@ -5372,7 +4868,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:33">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A30" s="13">
         <v>820034</v>
       </c>
@@ -5471,7 +4967,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="31" spans="1:33">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>820051</v>
       </c>
@@ -5570,7 +5066,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:33">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A32" s="13">
         <v>820054</v>
       </c>
@@ -5669,7 +5165,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" spans="1:33">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>820061</v>
       </c>
@@ -5768,12 +5264,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="34" spans="1:33">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>821061</v>
       </c>
       <c r="B34" s="13">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C34" s="14">
         <v>1</v>
@@ -5831,7 +5327,7 @@
         <v>1000</v>
       </c>
       <c r="V34" s="13" t="s">
-        <v>269</v>
+        <v>441</v>
       </c>
       <c r="W34" s="13">
         <v>0</v>
@@ -5867,7 +5363,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35" spans="1:33">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A35" s="13">
         <v>820072</v>
       </c>
@@ -5880,7 +5376,7 @@
       <c r="D35" s="14">
         <v>0</v>
       </c>
-      <c r="E35" s="15">
+      <c r="E35" s="13">
         <v>820072</v>
       </c>
       <c r="F35" s="4" t="s">
@@ -5966,18 +5462,116 @@
         <v>78</v>
       </c>
     </row>
+    <row r="36" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A36" s="4">
+        <v>820081</v>
+      </c>
+      <c r="B36" s="13">
+        <v>105</v>
+      </c>
+      <c r="C36" s="14">
+        <v>1</v>
+      </c>
+      <c r="D36" s="14">
+        <v>0</v>
+      </c>
+      <c r="E36" s="13">
+        <v>5001600</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13" t="s">
+        <v>438</v>
+      </c>
+      <c r="J36" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="K36" s="13">
+        <v>1</v>
+      </c>
+      <c r="L36" s="13">
+        <v>0</v>
+      </c>
+      <c r="M36" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="N36" s="13">
+        <v>1</v>
+      </c>
+      <c r="O36" s="13">
+        <v>0</v>
+      </c>
+      <c r="P36" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q36" s="13">
+        <v>1</v>
+      </c>
+      <c r="R36" s="13">
+        <v>0</v>
+      </c>
+      <c r="S36" s="14">
+        <v>0</v>
+      </c>
+      <c r="T36" s="13" t="s">
+        <v>440</v>
+      </c>
+      <c r="U36" s="13">
+        <v>1000</v>
+      </c>
+      <c r="V36" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="W36" s="13">
+        <v>0</v>
+      </c>
+      <c r="X36" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y36" s="13">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="13">
+        <v>1</v>
+      </c>
+      <c r="AA36" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB36" s="13">
+        <v>1</v>
+      </c>
+      <c r="AC36" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE36" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF36" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG36" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="E7:S71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
     <col min="5" max="5" width="27.25" style="1" customWidth="1"/>
@@ -5990,7 +5584,7 @@
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="5:6">
+    <row r="7" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E7" s="1" t="s">
         <v>8</v>
       </c>
@@ -5998,7 +5592,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="5:6">
+    <row r="8" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E8" s="1" t="s">
         <v>9</v>
       </c>
@@ -6006,7 +5600,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="5:6">
+    <row r="9" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E9" s="1" t="s">
         <v>10</v>
       </c>
@@ -6014,7 +5608,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="5:6">
+    <row r="10" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E10" s="1" t="s">
         <v>11</v>
       </c>
@@ -6022,7 +5616,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="11" spans="5:6">
+    <row r="11" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E11" s="1" t="s">
         <v>12</v>
       </c>
@@ -6030,7 +5624,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="5:6">
+    <row r="12" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E12" s="1" t="s">
         <v>13</v>
       </c>
@@ -6038,7 +5632,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="5:19">
+    <row r="13" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E13" s="1" t="s">
         <v>14</v>
       </c>
@@ -6052,7 +5646,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="14" spans="5:12">
+    <row r="14" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E14" s="1" t="s">
         <v>15</v>
       </c>
@@ -6072,7 +5666,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="15" spans="5:19">
+    <row r="15" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E15" s="1" t="s">
         <v>16</v>
       </c>
@@ -6092,7 +5686,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="16" spans="5:19">
+    <row r="16" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E16" s="1" t="s">
         <v>17</v>
       </c>
@@ -6115,7 +5709,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="17" spans="5:19">
+    <row r="17" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E17" s="1" t="s">
         <v>18</v>
       </c>
@@ -6138,7 +5732,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="18" spans="5:19">
+    <row r="18" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E18" s="1" t="s">
         <v>19</v>
       </c>
@@ -6161,7 +5755,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="19" spans="5:19">
+    <row r="19" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E19" s="1" t="s">
         <v>20</v>
       </c>
@@ -6191,7 +5785,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="20" spans="5:19">
+    <row r="20" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E20" s="1" t="s">
         <v>21</v>
       </c>
@@ -6221,7 +5815,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="21" spans="5:19">
+    <row r="21" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E21" s="1" t="s">
         <v>22</v>
       </c>
@@ -6251,7 +5845,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="22" spans="5:19">
+    <row r="22" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E22" s="1" t="s">
         <v>23</v>
       </c>
@@ -6281,7 +5875,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="23" spans="5:19">
+    <row r="23" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E23" s="1" t="s">
         <v>24</v>
       </c>
@@ -6311,7 +5905,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="24" spans="5:19">
+    <row r="24" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E24" s="1" t="s">
         <v>25</v>
       </c>
@@ -6341,7 +5935,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="25" spans="5:19">
+    <row r="25" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E25" s="1" t="s">
         <v>26</v>
       </c>
@@ -6371,7 +5965,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="26" spans="5:19">
+    <row r="26" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E26" s="1" t="s">
         <v>27</v>
       </c>
@@ -6401,7 +5995,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="27" spans="5:19">
+    <row r="27" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E27" s="1" t="s">
         <v>28</v>
       </c>
@@ -6431,7 +6025,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="28" spans="5:12">
+    <row r="28" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E28" s="1" t="s">
         <v>29</v>
       </c>
@@ -6458,7 +6052,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="29" spans="5:19">
+    <row r="29" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E29" s="1" t="s">
         <v>30</v>
       </c>
@@ -6488,7 +6082,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="30" spans="5:19">
+    <row r="30" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E30" s="1" t="s">
         <v>31</v>
       </c>
@@ -6518,7 +6112,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="31" spans="5:19">
+    <row r="31" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E31" s="1" t="s">
         <v>32</v>
       </c>
@@ -6548,7 +6142,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="32" spans="5:12">
+    <row r="32" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E32" s="1" t="s">
         <v>33</v>
       </c>
@@ -6575,7 +6169,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="33" spans="5:9">
+    <row r="33" spans="5:9" x14ac:dyDescent="0.15">
       <c r="E33" s="1" t="s">
         <v>34</v>
       </c>
@@ -6593,7 +6187,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="34" spans="5:9">
+    <row r="34" spans="5:9" x14ac:dyDescent="0.15">
       <c r="E34" s="1" t="s">
         <v>35</v>
       </c>
@@ -6611,7 +6205,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="35" spans="5:9">
+    <row r="35" spans="5:9" x14ac:dyDescent="0.15">
       <c r="E35" s="1" t="s">
         <v>36</v>
       </c>
@@ -6629,7 +6223,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="36" spans="7:9">
+    <row r="36" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G36" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数21-技能增加-万分比</v>
@@ -6641,7 +6235,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="37" spans="7:9">
+    <row r="37" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G37" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数22-技能增加-普通攻击范围万分比</v>
@@ -6653,7 +6247,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="38" spans="7:9">
+    <row r="38" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G38" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数25LIST-攻击提高-攻击的元素类型</v>
@@ -6665,7 +6259,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="39" spans="7:9">
+    <row r="39" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G39" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数25LIST-攻击提高-固定值</v>
@@ -6677,7 +6271,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="40" spans="7:9">
+    <row r="40" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G40" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数25LIST-攻击提高-万分比</v>
@@ -6689,7 +6283,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="41" spans="7:9">
+    <row r="41" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G41" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数28-防御提高-固定值</v>
@@ -6701,7 +6295,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="42" spans="7:9">
+    <row r="42" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G42" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数29-防御提高-万分比</v>
@@ -6713,7 +6307,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="43" spans="7:9">
+    <row r="43" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G43" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数30-生命上限提高-固定值</v>
@@ -6725,7 +6319,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="44" spans="7:9">
+    <row r="44" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G44" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数31-生命上限提高-百万分比</v>
@@ -6737,7 +6331,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="45" spans="7:9">
+    <row r="45" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G45" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数32-攻击速度提高-万分比</v>
@@ -6749,7 +6343,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="46" spans="7:9">
+    <row r="46" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G46" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数33-移动速度提高-万分比</v>
@@ -6761,7 +6355,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="47" spans="7:9">
+    <row r="47" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G47" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数34-攻击范围提高-万分比</v>
@@ -6773,7 +6367,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="48" spans="7:9">
+    <row r="48" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G48" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数35-攻击目标数量提高-固定值</v>
@@ -6785,7 +6379,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="49" spans="7:8">
+    <row r="49" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G49" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数36-</v>
@@ -6794,7 +6388,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="50" spans="7:8">
+    <row r="50" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G50" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数37-</v>
@@ -6803,7 +6397,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="51" spans="7:8">
+    <row r="51" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G51" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数38-</v>
@@ -6812,7 +6406,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="52" spans="7:8">
+    <row r="52" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G52" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数39-</v>
@@ -6821,7 +6415,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="53" spans="7:8">
+    <row r="53" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G53" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数40-</v>
@@ -6830,7 +6424,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="54" spans="7:8">
+    <row r="54" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G54" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数41-</v>
@@ -6839,7 +6433,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="55" spans="7:8">
+    <row r="55" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G55" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数42-</v>
@@ -6848,7 +6442,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="56" spans="7:8">
+    <row r="56" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G56" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数41-</v>
@@ -6857,7 +6451,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="57" spans="7:8">
+    <row r="57" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G57" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数42-</v>
@@ -6866,7 +6460,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="58" spans="7:8">
+    <row r="58" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G58" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数43-</v>
@@ -6875,7 +6469,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="59" spans="7:8">
+    <row r="59" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G59" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数44-</v>
@@ -6884,7 +6478,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="60" spans="7:8">
+    <row r="60" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G60" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数45-</v>
@@ -6893,7 +6487,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="61" spans="7:8">
+    <row r="61" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G61" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数46-</v>
@@ -6902,7 +6496,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="62" spans="7:8">
+    <row r="62" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G62" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数47-</v>
@@ -6911,7 +6505,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="63" spans="7:8">
+    <row r="63" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G63" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数48-</v>
@@ -6920,7 +6514,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="64" spans="7:8">
+    <row r="64" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G64" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数49-</v>
@@ -6929,7 +6523,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="65" spans="7:8">
+    <row r="65" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G65" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数50-</v>
@@ -6938,7 +6532,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="66" spans="7:8">
+    <row r="66" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G66" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数51-</v>
@@ -6947,7 +6541,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="67" spans="7:8">
+    <row r="67" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G67" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数52-</v>
@@ -6956,7 +6550,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="68" spans="7:8">
+    <row r="68" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G68" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数53-</v>
@@ -6965,7 +6559,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="69" spans="7:8">
+    <row r="69" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G69" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数54-</v>
@@ -6974,7 +6568,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="70" spans="7:8">
+    <row r="70" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G70" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数55-</v>
@@ -6983,7 +6577,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="71" spans="7:8">
+    <row r="71" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G71" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数56-</v>
@@ -6993,16 +6587,15 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="D6:F43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="11.25" style="1" customWidth="1"/>
@@ -7012,13 +6605,13 @@
     <col min="23" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="4:5">
+    <row r="6" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D6" s="2" t="s">
         <v>415</v>
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="4:5">
+    <row r="7" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D7" s="2">
         <v>1</v>
       </c>
@@ -7026,11 +6619,11 @@
         <v>416</v>
       </c>
     </row>
-    <row r="8" spans="4:5">
+    <row r="8" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="4:5">
+    <row r="9" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D9" s="2">
         <v>2</v>
       </c>
@@ -7038,7 +6631,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="10" spans="4:5">
+    <row r="10" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D10" s="2">
         <v>2.1</v>
       </c>
@@ -7046,7 +6639,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="11" spans="4:5">
+    <row r="11" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D11" s="2" t="s">
         <v>419</v>
       </c>
@@ -7054,7 +6647,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="12" spans="4:5">
+    <row r="12" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D12" s="2" t="s">
         <v>421</v>
       </c>
@@ -7062,7 +6655,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="13" spans="4:5">
+    <row r="13" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D13" s="2" t="s">
         <v>423</v>
       </c>
@@ -7070,19 +6663,19 @@
         <v>424</v>
       </c>
     </row>
-    <row r="14" spans="4:5">
+    <row r="14" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="4:5">
+    <row r="15" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D15" s="2">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="16" spans="4:5">
+    <row r="16" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D16" s="2" t="s">
         <v>426</v>
       </c>
@@ -7090,7 +6683,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="17" spans="4:5">
+    <row r="17" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D17" s="2" t="s">
         <v>427</v>
       </c>
@@ -7098,7 +6691,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="18" spans="4:5">
+    <row r="18" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D18" s="2" t="s">
         <v>429</v>
       </c>
@@ -7106,12 +6699,12 @@
         <v>430</v>
       </c>
     </row>
-    <row r="28" spans="4:4">
+    <row r="28" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D28" s="1" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="29" spans="4:5">
+    <row r="29" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D29" s="1" t="s">
         <v>432</v>
       </c>
@@ -7119,7 +6712,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="30" spans="4:5">
+    <row r="30" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D30" s="1" t="s">
         <v>433</v>
       </c>
@@ -7127,17 +6720,17 @@
         <v>102</v>
       </c>
     </row>
-    <row r="31" spans="4:4">
+    <row r="31" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D31" s="1" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="32" spans="4:4">
+    <row r="32" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D32" s="1" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="33" ht="14.25" spans="4:6">
+    <row r="33" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="D33" s="1" t="s">
         <v>436</v>
       </c>
@@ -7146,38 +6739,38 @@
       </c>
       <c r="F33"/>
     </row>
-    <row r="34" ht="14.25" spans="6:6">
+    <row r="34" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F34"/>
     </row>
-    <row r="35" ht="14.25" spans="6:6">
+    <row r="35" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F35"/>
     </row>
-    <row r="36" ht="14.25" spans="6:6">
+    <row r="36" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F36"/>
     </row>
-    <row r="37" ht="14.25" spans="6:6">
+    <row r="37" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F37"/>
     </row>
-    <row r="38" ht="14.25" spans="6:6">
+    <row r="38" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F38"/>
     </row>
-    <row r="39" ht="14.25" spans="6:6">
+    <row r="39" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F39"/>
     </row>
-    <row r="40" ht="14.25" spans="6:6">
+    <row r="40" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F40"/>
     </row>
-    <row r="41" ht="14.25" spans="6:6">
+    <row r="41" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F41"/>
     </row>
-    <row r="42" ht="14.25" spans="6:6">
+    <row r="42" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F42"/>
     </row>
-    <row r="43" ht="14.25" spans="6:6">
+    <row r="43" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F43"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7964A3E6-1F18-4E36-BADD-A7D202EA37CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F0852AE-B75D-4277-B215-B24707064619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="446">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1433,6 +1433,22 @@
   </si>
   <si>
     <t>5001501:1</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀敌人时召唤一个冰球（释放技能）【参数4】</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>极寒领域-冰冻立即死亡</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>被冰冻的怪物将会立即死亡</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>极寒领域-召唤冰球</t>
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
@@ -1991,7 +2007,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG36"/>
+  <dimension ref="A1:AG38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -5561,6 +5577,204 @@
         <v>78</v>
       </c>
     </row>
+    <row r="37" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A37" s="13">
+        <v>820082</v>
+      </c>
+      <c r="B37" s="13">
+        <v>20082</v>
+      </c>
+      <c r="C37" s="14">
+        <v>1</v>
+      </c>
+      <c r="D37" s="14">
+        <v>0</v>
+      </c>
+      <c r="E37" s="13">
+        <v>820082</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>443</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13" t="s">
+        <v>444</v>
+      </c>
+      <c r="J37" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="K37" s="13">
+        <v>1</v>
+      </c>
+      <c r="L37" s="13">
+        <v>0</v>
+      </c>
+      <c r="M37" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="N37" s="13">
+        <v>1</v>
+      </c>
+      <c r="O37" s="13">
+        <v>0</v>
+      </c>
+      <c r="P37" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q37" s="13">
+        <v>1</v>
+      </c>
+      <c r="R37" s="13">
+        <v>0</v>
+      </c>
+      <c r="S37" s="14">
+        <v>0</v>
+      </c>
+      <c r="T37" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="U37" s="13">
+        <v>-1</v>
+      </c>
+      <c r="V37" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="W37" s="13">
+        <v>10000</v>
+      </c>
+      <c r="X37" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y37" s="13">
+        <v>1</v>
+      </c>
+      <c r="Z37" s="13">
+        <v>1</v>
+      </c>
+      <c r="AA37" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB37" s="13">
+        <v>1</v>
+      </c>
+      <c r="AC37" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE37" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF37" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG37" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A38" s="13">
+        <v>820083</v>
+      </c>
+      <c r="B38" s="13">
+        <v>20083</v>
+      </c>
+      <c r="C38" s="14">
+        <v>1</v>
+      </c>
+      <c r="D38" s="14">
+        <v>0</v>
+      </c>
+      <c r="E38" s="13">
+        <v>820083</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13" t="s">
+        <v>442</v>
+      </c>
+      <c r="J38" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="K38" s="13">
+        <v>1</v>
+      </c>
+      <c r="L38" s="13">
+        <v>0</v>
+      </c>
+      <c r="M38" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="N38" s="13">
+        <v>1</v>
+      </c>
+      <c r="O38" s="13">
+        <v>0</v>
+      </c>
+      <c r="P38" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q38" s="13">
+        <v>1</v>
+      </c>
+      <c r="R38" s="13">
+        <v>0</v>
+      </c>
+      <c r="S38" s="14">
+        <v>20083</v>
+      </c>
+      <c r="T38" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="U38" s="13">
+        <v>-1</v>
+      </c>
+      <c r="V38" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="W38" s="13">
+        <v>10000</v>
+      </c>
+      <c r="X38" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y38" s="13">
+        <v>1</v>
+      </c>
+      <c r="Z38" s="13">
+        <v>1</v>
+      </c>
+      <c r="AA38" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB38" s="13">
+        <v>1</v>
+      </c>
+      <c r="AC38" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE38" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF38" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG38" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F0852AE-B75D-4277-B215-B24707064619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0030A0A-19E0-4AC6-81A7-25D9C8A46589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="461">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1449,6 +1449,66 @@
   </si>
   <si>
     <t>极寒领域-召唤冰球</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀敌人时释放超级暴风雪技能【参数4】</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰风暴</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰刃概率附加减速</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰刃减速状态（万分比降低攻速【参数1】和移速【参数2】），持续时间【参数5】毫秒，状态命中率【参数6】</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>5001715:1</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>5001716:1</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>5001711:1</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>5001712:1</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰雪领域冰冻状态（无法攻击和移动），持续时间【参数5】毫秒，状态命中率【参数6】</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰雪领域附加冰冻</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>5001522:1</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>5001521:1</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰雪领域-触发技能</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>减速时概率【参数1】触发冰雪领域（释放技能）【参数4】</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>8200861:1</t>
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
@@ -1670,7 +1730,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1708,6 +1768,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="差" xfId="2" builtinId="27"/>
@@ -2007,7 +2068,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG38"/>
+  <dimension ref="A1:AG42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -5211,7 +5272,7 @@
         <v>269</v>
       </c>
       <c r="K33" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L33" s="13">
         <v>2000</v>
@@ -5220,7 +5281,7 @@
         <v>270</v>
       </c>
       <c r="N33" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O33" s="13">
         <v>2000</v>
@@ -5479,11 +5540,11 @@
       </c>
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A36" s="4">
-        <v>820081</v>
+      <c r="A36" s="13">
+        <v>820073</v>
       </c>
       <c r="B36" s="13">
-        <v>105</v>
+        <v>20073</v>
       </c>
       <c r="C36" s="14">
         <v>1</v>
@@ -5492,17 +5553,17 @@
         <v>0</v>
       </c>
       <c r="E36" s="13">
-        <v>5001600</v>
+        <v>820073</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="G36" s="12" t="s">
         <v>228</v>
       </c>
       <c r="H36" s="13"/>
       <c r="I36" s="13" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="J36" s="13" t="s">
         <v>78</v>
@@ -5532,19 +5593,19 @@
         <v>0</v>
       </c>
       <c r="S36" s="14">
-        <v>0</v>
+        <v>20074</v>
       </c>
       <c r="T36" s="13" t="s">
-        <v>440</v>
+        <v>78</v>
       </c>
       <c r="U36" s="13">
-        <v>1000</v>
+        <v>-1</v>
       </c>
       <c r="V36" s="13" t="s">
-        <v>439</v>
+        <v>78</v>
       </c>
       <c r="W36" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X36" s="13" t="s">
         <v>78</v>
@@ -5578,11 +5639,11 @@
       </c>
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A37" s="13">
-        <v>820082</v>
+      <c r="A37" s="4">
+        <v>820080</v>
       </c>
       <c r="B37" s="13">
-        <v>20082</v>
+        <v>102</v>
       </c>
       <c r="C37" s="14">
         <v>1</v>
@@ -5591,35 +5652,35 @@
         <v>0</v>
       </c>
       <c r="E37" s="13">
-        <v>820082</v>
+        <v>5001800</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="G37" s="12" t="s">
         <v>228</v>
       </c>
       <c r="H37" s="13"/>
       <c r="I37" s="13" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>78</v>
+        <v>452</v>
       </c>
       <c r="K37" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L37" s="13">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="M37" s="13" t="s">
-        <v>78</v>
+        <v>453</v>
       </c>
       <c r="N37" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O37" s="13">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="P37" s="13" t="s">
         <v>78</v>
@@ -5634,16 +5695,16 @@
         <v>0</v>
       </c>
       <c r="T37" s="13" t="s">
-        <v>78</v>
+        <v>450</v>
       </c>
       <c r="U37" s="13">
-        <v>-1</v>
+        <v>3000</v>
       </c>
       <c r="V37" s="13" t="s">
-        <v>78</v>
+        <v>451</v>
       </c>
       <c r="W37" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X37" s="13" t="s">
         <v>78</v>
@@ -5677,11 +5738,11 @@
       </c>
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A38" s="13">
-        <v>820083</v>
+      <c r="A38" s="4">
+        <v>820081</v>
       </c>
       <c r="B38" s="13">
-        <v>20083</v>
+        <v>105</v>
       </c>
       <c r="C38" s="14">
         <v>1</v>
@@ -5690,88 +5751,484 @@
         <v>0</v>
       </c>
       <c r="E38" s="13">
-        <v>820083</v>
+        <v>5001600</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="G38" s="12" t="s">
         <v>228</v>
       </c>
       <c r="H38" s="13"/>
       <c r="I38" s="13" t="s">
+        <v>438</v>
+      </c>
+      <c r="J38" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="K38" s="13">
+        <v>1</v>
+      </c>
+      <c r="L38" s="13">
+        <v>0</v>
+      </c>
+      <c r="M38" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="N38" s="13">
+        <v>1</v>
+      </c>
+      <c r="O38" s="13">
+        <v>0</v>
+      </c>
+      <c r="P38" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q38" s="13">
+        <v>1</v>
+      </c>
+      <c r="R38" s="13">
+        <v>0</v>
+      </c>
+      <c r="S38" s="14">
+        <v>0</v>
+      </c>
+      <c r="T38" s="13" t="s">
+        <v>440</v>
+      </c>
+      <c r="U38" s="13">
+        <v>1000</v>
+      </c>
+      <c r="V38" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="W38" s="13">
+        <v>0</v>
+      </c>
+      <c r="X38" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y38" s="13">
+        <v>1</v>
+      </c>
+      <c r="Z38" s="13">
+        <v>1</v>
+      </c>
+      <c r="AA38" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB38" s="13">
+        <v>1</v>
+      </c>
+      <c r="AC38" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE38" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF38" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG38" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A39" s="13">
+        <v>820082</v>
+      </c>
+      <c r="B39" s="13">
+        <v>20082</v>
+      </c>
+      <c r="C39" s="14">
+        <v>1</v>
+      </c>
+      <c r="D39" s="14">
+        <v>0</v>
+      </c>
+      <c r="E39" s="13">
+        <v>820082</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>443</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13" t="s">
+        <v>444</v>
+      </c>
+      <c r="J39" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="K39" s="13">
+        <v>1</v>
+      </c>
+      <c r="L39" s="13">
+        <v>0</v>
+      </c>
+      <c r="M39" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="N39" s="13">
+        <v>1</v>
+      </c>
+      <c r="O39" s="13">
+        <v>0</v>
+      </c>
+      <c r="P39" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q39" s="13">
+        <v>1</v>
+      </c>
+      <c r="R39" s="13">
+        <v>0</v>
+      </c>
+      <c r="S39" s="14">
+        <v>0</v>
+      </c>
+      <c r="T39" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="U39" s="13">
+        <v>-1</v>
+      </c>
+      <c r="V39" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="W39" s="13">
+        <v>10000</v>
+      </c>
+      <c r="X39" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y39" s="13">
+        <v>1</v>
+      </c>
+      <c r="Z39" s="13">
+        <v>1</v>
+      </c>
+      <c r="AA39" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB39" s="13">
+        <v>1</v>
+      </c>
+      <c r="AC39" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE39" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF39" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG39" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A40" s="13">
+        <v>820083</v>
+      </c>
+      <c r="B40" s="13">
+        <v>20083</v>
+      </c>
+      <c r="C40" s="14">
+        <v>1</v>
+      </c>
+      <c r="D40" s="14">
+        <v>0</v>
+      </c>
+      <c r="E40" s="13">
+        <v>820083</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="G40" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13" t="s">
         <v>442</v>
       </c>
-      <c r="J38" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="K38" s="13">
-        <v>1</v>
-      </c>
-      <c r="L38" s="13">
-        <v>0</v>
-      </c>
-      <c r="M38" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="N38" s="13">
-        <v>1</v>
-      </c>
-      <c r="O38" s="13">
-        <v>0</v>
-      </c>
-      <c r="P38" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q38" s="13">
-        <v>1</v>
-      </c>
-      <c r="R38" s="13">
-        <v>0</v>
-      </c>
-      <c r="S38" s="14">
+      <c r="J40" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="K40" s="13">
+        <v>1</v>
+      </c>
+      <c r="L40" s="13">
+        <v>0</v>
+      </c>
+      <c r="M40" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="N40" s="13">
+        <v>1</v>
+      </c>
+      <c r="O40" s="13">
+        <v>0</v>
+      </c>
+      <c r="P40" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q40" s="13">
+        <v>1</v>
+      </c>
+      <c r="R40" s="13">
+        <v>0</v>
+      </c>
+      <c r="S40" s="14">
         <v>20083</v>
       </c>
-      <c r="T38" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="U38" s="13">
+      <c r="T40" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="U40" s="13">
         <v>-1</v>
       </c>
-      <c r="V38" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="W38" s="13">
+      <c r="V40" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="W40" s="13">
         <v>10000</v>
       </c>
-      <c r="X38" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y38" s="13">
-        <v>1</v>
-      </c>
-      <c r="Z38" s="13">
-        <v>1</v>
-      </c>
-      <c r="AA38" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB38" s="13">
-        <v>1</v>
-      </c>
-      <c r="AC38" s="13">
-        <v>0</v>
-      </c>
-      <c r="AD38" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="AE38" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF38" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG38" s="8" t="s">
+      <c r="X40" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y40" s="13">
+        <v>1</v>
+      </c>
+      <c r="Z40" s="13">
+        <v>1</v>
+      </c>
+      <c r="AA40" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB40" s="13">
+        <v>1</v>
+      </c>
+      <c r="AC40" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE40" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF40" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG40" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A41" s="4">
+        <v>820085</v>
+      </c>
+      <c r="B41" s="13">
+        <v>105</v>
+      </c>
+      <c r="C41" s="14">
+        <v>1</v>
+      </c>
+      <c r="D41" s="14">
+        <v>0</v>
+      </c>
+      <c r="E41" s="13">
+        <v>5001600</v>
+      </c>
+      <c r="F41" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13" t="s">
+        <v>454</v>
+      </c>
+      <c r="J41" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="K41" s="13">
+        <v>1</v>
+      </c>
+      <c r="L41" s="13">
+        <v>0</v>
+      </c>
+      <c r="M41" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="N41" s="13">
+        <v>1</v>
+      </c>
+      <c r="O41" s="13">
+        <v>0</v>
+      </c>
+      <c r="P41" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q41" s="13">
+        <v>1</v>
+      </c>
+      <c r="R41" s="13">
+        <v>0</v>
+      </c>
+      <c r="S41" s="14">
+        <v>0</v>
+      </c>
+      <c r="T41" s="13" t="s">
+        <v>456</v>
+      </c>
+      <c r="U41" s="13">
+        <v>1000</v>
+      </c>
+      <c r="V41" s="13" t="s">
+        <v>457</v>
+      </c>
+      <c r="W41" s="13">
+        <v>10000</v>
+      </c>
+      <c r="X41" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y41" s="13">
+        <v>1</v>
+      </c>
+      <c r="Z41" s="13">
+        <v>1</v>
+      </c>
+      <c r="AA41" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB41" s="13">
+        <v>1</v>
+      </c>
+      <c r="AC41" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE41" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF41" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG41" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="42" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A42" s="13">
+        <v>820086</v>
+      </c>
+      <c r="B42" s="13">
+        <v>20086</v>
+      </c>
+      <c r="C42" s="14">
+        <v>1</v>
+      </c>
+      <c r="D42" s="14">
+        <v>0</v>
+      </c>
+      <c r="E42" s="13">
+        <v>820086</v>
+      </c>
+      <c r="F42" s="13" t="s">
+        <v>458</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13" t="s">
+        <v>459</v>
+      </c>
+      <c r="J42" s="23" t="s">
+        <v>460</v>
+      </c>
+      <c r="K42" s="13">
+        <v>2</v>
+      </c>
+      <c r="L42" s="13">
+        <v>5000</v>
+      </c>
+      <c r="M42" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="N42" s="13">
+        <v>1</v>
+      </c>
+      <c r="O42" s="13">
+        <v>0</v>
+      </c>
+      <c r="P42" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q42" s="13">
+        <v>1</v>
+      </c>
+      <c r="R42" s="13">
+        <v>0</v>
+      </c>
+      <c r="S42" s="14">
+        <v>20085</v>
+      </c>
+      <c r="T42" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="U42" s="13">
+        <v>-1</v>
+      </c>
+      <c r="V42" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="W42" s="13">
+        <v>10000</v>
+      </c>
+      <c r="X42" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y42" s="13">
+        <v>1</v>
+      </c>
+      <c r="Z42" s="13">
+        <v>1</v>
+      </c>
+      <c r="AA42" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB42" s="13">
+        <v>1</v>
+      </c>
+      <c r="AC42" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE42" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF42" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG42" s="8" t="s">
         <v>78</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0030A0A-19E0-4AC6-81A7-25D9C8A46589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -29,6 +23,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,34 +32,32 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>pe</author>
     <author>cltx</author>
   </authors>
   <commentList>
-    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="C4" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>数字越大，优先级越高</t>
         </r>
       </text>
     </comment>
-    <comment ref="K4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="K4" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>cltx:</t>
@@ -72,7 +66,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -82,13 +75,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="U4" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">&gt;0，持续时间
@@ -103,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="460">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -936,6 +928,75 @@
     <t>冰冻状态结束时触发冰爆技能【参数4】</t>
   </si>
   <si>
+    <t>冰风暴</t>
+  </si>
+  <si>
+    <t>击杀敌人时释放超级暴风雪技能【参数4】</t>
+  </si>
+  <si>
+    <t>冰刃概率附加减速</t>
+  </si>
+  <si>
+    <t>冰刃减速状态（万分比降低攻速【参数1】和移速【参数2】），持续时间【参数5】毫秒，状态命中率【参数6】</t>
+  </si>
+  <si>
+    <t>5001711:1</t>
+  </si>
+  <si>
+    <t>5001712:1</t>
+  </si>
+  <si>
+    <t>5001715:1</t>
+  </si>
+  <si>
+    <t>5001716:1</t>
+  </si>
+  <si>
+    <t>冰球概率附加冰冻</t>
+  </si>
+  <si>
+    <t>冰球冰冻状态（无法攻击和移动），持续时间【参数5】毫秒，状态命中率【参数6】</t>
+  </si>
+  <si>
+    <t>5001512:1</t>
+  </si>
+  <si>
+    <t>5001511:1</t>
+  </si>
+  <si>
+    <t>极寒领域-冰冻立即死亡</t>
+  </si>
+  <si>
+    <t>被冰冻的怪物将会立即死亡</t>
+  </si>
+  <si>
+    <t>极寒领域-召唤冰球</t>
+  </si>
+  <si>
+    <t>击杀敌人时召唤一个冰球（释放技能）【参数4】</t>
+  </si>
+  <si>
+    <t>冰雪领域附加冰冻</t>
+  </si>
+  <si>
+    <t>冰雪领域冰冻状态（无法攻击和移动），持续时间【参数5】毫秒，状态命中率【参数6】</t>
+  </si>
+  <si>
+    <t>5001522:1</t>
+  </si>
+  <si>
+    <t>5001521:1</t>
+  </si>
+  <si>
+    <t>冰雪领域-触发技能</t>
+  </si>
+  <si>
+    <t>减速时概率【参数1】触发冰雪领域（释放技能）【参数4】</t>
+  </si>
+  <si>
+    <t>8200861:1</t>
+  </si>
+  <si>
     <t>重复中buff组的cd时间（毫秒）</t>
   </si>
   <si>
@@ -1414,109 +1475,19 @@
   </si>
   <si>
     <t>冰冻</t>
-  </si>
-  <si>
-    <t>冰球概率附加冰冻</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰球冰冻状态（无法攻击和移动），持续时间【参数5】毫秒，状态命中率【参数6】</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>5001511:1</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>5001512:1</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>5001501:1</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀敌人时召唤一个冰球（释放技能）【参数4】</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>极寒领域-冰冻立即死亡</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>被冰冻的怪物将会立即死亡</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>极寒领域-召唤冰球</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀敌人时释放超级暴风雪技能【参数4】</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰风暴</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰刃概率附加减速</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰刃减速状态（万分比降低攻速【参数1】和移速【参数2】），持续时间【参数5】毫秒，状态命中率【参数6】</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>5001715:1</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>5001716:1</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>5001711:1</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>5001712:1</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰雪领域冰冻状态（无法攻击和移动），持续时间【参数5】毫秒，状态命中率【参数6】</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰雪领域附加冰冻</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>5001522:1</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>5001521:1</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰雪领域-触发技能</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>减速时概率【参数1】触发冰雪领域（释放技能）【参数4】</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
-    <t>8200861:1</t>
-    <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1528,35 +1499,30 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF9C5700"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <color theme="0" tint="-4.9989318521683403E-2"/>
+      <color theme="0" tint="-0.0499893185216834"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1564,14 +1530,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1579,60 +1543,169 @@
       <sz val="9"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1641,13 +1714,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <fgColor theme="0" tint="-0.349986266670736"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79964598529007846"/>
+        <fgColor theme="8" tint="0.799645985290078"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1665,7 +1738,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1675,8 +1772,152 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1714,23 +1955,241 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1745,8 +2204,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="24" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1754,37 +2213,78 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="23" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="24" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="24" applyFont="1" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="5">
-    <cellStyle name="差" xfId="2" builtinId="27"/>
-    <cellStyle name="差 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="适中" xfId="3" builtinId="28"/>
-    <cellStyle name="输入" xfId="1" builtinId="20"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="差 2" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2062,14 +2562,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AG42"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -2100,7 +2600,7 @@
     <col min="33" max="33" width="17.125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2133,7 +2633,7 @@
       <c r="AB1" s="4"/>
       <c r="AC1" s="4"/>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:33">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -2221,20 +2721,20 @@
       <c r="AC2" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="AD2" s="19" t="s">
+      <c r="AD2" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="AE2" s="19" t="s">
+      <c r="AE2" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="AF2" s="19" t="s">
+      <c r="AF2" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="AG2" s="19" t="s">
+      <c r="AG2" s="20" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:33">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
@@ -2322,20 +2822,20 @@
       <c r="AC3" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="AD3" s="19" t="s">
+      <c r="AD3" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="AE3" s="19" t="s">
+      <c r="AE3" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="AF3" s="19" t="s">
+      <c r="AF3" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="AG3" s="19" t="s">
+      <c r="AG3" s="20" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:33">
       <c r="A4" s="4" t="s">
         <v>41</v>
       </c>
@@ -2423,20 +2923,20 @@
       <c r="AC4" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="AD4" s="19" t="s">
+      <c r="AD4" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="AE4" s="19" t="s">
+      <c r="AE4" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="AF4" s="19" t="s">
+      <c r="AF4" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="AG4" s="19" t="s">
+      <c r="AG4" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33">
       <c r="A5" s="6">
         <v>1000001</v>
       </c>
@@ -2464,7 +2964,7 @@
       <c r="I5" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="J5" s="20" t="s">
+      <c r="J5" s="21" t="s">
         <v>78</v>
       </c>
       <c r="K5" s="6">
@@ -2473,7 +2973,7 @@
       <c r="L5" s="6">
         <v>400000</v>
       </c>
-      <c r="M5" s="21" t="s">
+      <c r="M5" s="22" t="s">
         <v>78</v>
       </c>
       <c r="N5" s="16">
@@ -2482,7 +2982,7 @@
       <c r="O5" s="16">
         <v>0</v>
       </c>
-      <c r="P5" s="20" t="s">
+      <c r="P5" s="21" t="s">
         <v>78</v>
       </c>
       <c r="Q5" s="6">
@@ -2491,16 +2991,16 @@
       <c r="R5" s="6">
         <v>0</v>
       </c>
-      <c r="S5" s="17">
-        <v>0</v>
-      </c>
-      <c r="T5" s="20" t="s">
+      <c r="S5" s="18">
+        <v>0</v>
+      </c>
+      <c r="T5" s="21" t="s">
         <v>78</v>
       </c>
       <c r="U5" s="6">
         <v>0</v>
       </c>
-      <c r="V5" s="20" t="s">
+      <c r="V5" s="21" t="s">
         <v>78</v>
       </c>
       <c r="W5" s="6">
@@ -2515,7 +3015,7 @@
       <c r="Z5" s="6">
         <v>0</v>
       </c>
-      <c r="AA5" s="21" t="s">
+      <c r="AA5" s="22" t="s">
         <v>78</v>
       </c>
       <c r="AB5" s="16">
@@ -2537,7 +3037,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33">
       <c r="A6" s="7">
         <v>2000001</v>
       </c>
@@ -2583,7 +3083,7 @@
       <c r="O6" s="7">
         <v>0</v>
       </c>
-      <c r="P6" s="22" t="s">
+      <c r="P6" s="23" t="s">
         <v>78</v>
       </c>
       <c r="Q6" s="7">
@@ -2592,22 +3092,22 @@
       <c r="R6" s="7">
         <v>0</v>
       </c>
-      <c r="S6" s="18">
-        <v>0</v>
-      </c>
-      <c r="T6" s="22" t="s">
+      <c r="S6" s="19">
+        <v>0</v>
+      </c>
+      <c r="T6" s="23" t="s">
         <v>78</v>
       </c>
       <c r="U6" s="7">
         <v>0</v>
       </c>
-      <c r="V6" s="22" t="s">
+      <c r="V6" s="23" t="s">
         <v>78</v>
       </c>
       <c r="W6" s="7">
         <v>10000</v>
       </c>
-      <c r="X6" s="22" t="s">
+      <c r="X6" s="23" t="s">
         <v>78</v>
       </c>
       <c r="Y6" s="7">
@@ -2638,7 +3138,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33">
       <c r="A7" s="8">
         <v>54010001</v>
       </c>
@@ -2739,7 +3239,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33">
       <c r="A8" s="8">
         <v>54020001</v>
       </c>
@@ -2840,7 +3340,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33">
       <c r="A9" s="8">
         <v>54030001</v>
       </c>
@@ -2941,7 +3441,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33">
       <c r="A10" s="8">
         <v>54040001</v>
       </c>
@@ -3042,7 +3542,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33">
       <c r="A11" s="8">
         <v>54050001</v>
       </c>
@@ -3143,7 +3643,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:33">
       <c r="A12" s="8">
         <v>54060001</v>
       </c>
@@ -3244,7 +3744,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33">
       <c r="A13" s="8">
         <v>54070001</v>
       </c>
@@ -3345,7 +3845,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:33">
       <c r="A14" s="8">
         <v>54080001</v>
       </c>
@@ -3446,7 +3946,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33">
       <c r="A15" s="8">
         <v>54090001</v>
       </c>
@@ -3547,7 +4047,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33">
       <c r="A16" s="8">
         <v>54100001</v>
       </c>
@@ -3648,7 +4148,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:33">
       <c r="A17" s="8">
         <v>54110001</v>
       </c>
@@ -3749,7 +4249,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:33">
       <c r="A18" s="8">
         <v>54120001</v>
       </c>
@@ -3850,7 +4350,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:33">
       <c r="A19" s="8">
         <v>54130001</v>
       </c>
@@ -3951,7 +4451,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:33">
       <c r="A20" s="8">
         <v>54140001</v>
       </c>
@@ -4052,7 +4552,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:33">
       <c r="A21" s="8">
         <v>54150001</v>
       </c>
@@ -4153,7 +4653,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:33">
       <c r="A22" s="10">
         <v>59130001</v>
       </c>
@@ -4250,7 +4750,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:33">
       <c r="A23" s="10">
         <v>59140001</v>
       </c>
@@ -4347,7 +4847,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:33">
       <c r="A24" s="13">
         <v>85001500</v>
       </c>
@@ -4407,7 +4907,7 @@
         <v>230</v>
       </c>
       <c r="U24" s="13">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="V24" s="13" t="s">
         <v>231</v>
@@ -4446,7 +4946,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:33">
       <c r="A25" s="13">
         <v>85101100</v>
       </c>
@@ -4547,7 +5047,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:33">
       <c r="A26" s="13">
         <v>85200700</v>
       </c>
@@ -4646,7 +5146,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:33">
       <c r="A27" s="13">
         <v>820001</v>
       </c>
@@ -4747,7 +5247,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:33">
       <c r="A28" s="13">
         <v>820011</v>
       </c>
@@ -4846,7 +5346,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:33">
       <c r="A29" s="13">
         <v>820031</v>
       </c>
@@ -4945,7 +5445,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:33">
       <c r="A30" s="13">
         <v>820034</v>
       </c>
@@ -5044,7 +5544,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:33">
       <c r="A31" s="4">
         <v>820051</v>
       </c>
@@ -5143,7 +5643,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:33">
       <c r="A32" s="13">
         <v>820054</v>
       </c>
@@ -5242,7 +5742,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:33">
       <c r="A33" s="4">
         <v>820061</v>
       </c>
@@ -5341,7 +5841,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:33">
       <c r="A34" s="4">
         <v>821061</v>
       </c>
@@ -5401,10 +5901,10 @@
         <v>230</v>
       </c>
       <c r="U34" s="13">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="V34" s="13" t="s">
-        <v>441</v>
+        <v>231</v>
       </c>
       <c r="W34" s="13">
         <v>0</v>
@@ -5440,7 +5940,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:33">
       <c r="A35" s="13">
         <v>820072</v>
       </c>
@@ -5539,7 +6039,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:33">
       <c r="A36" s="13">
         <v>820073</v>
       </c>
@@ -5556,14 +6056,14 @@
         <v>820073</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>447</v>
+        <v>277</v>
       </c>
       <c r="G36" s="12" t="s">
         <v>228</v>
       </c>
       <c r="H36" s="13"/>
       <c r="I36" s="13" t="s">
-        <v>446</v>
+        <v>278</v>
       </c>
       <c r="J36" s="13" t="s">
         <v>78</v>
@@ -5638,7 +6138,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:33">
       <c r="A37" s="4">
         <v>820080</v>
       </c>
@@ -5655,17 +6155,17 @@
         <v>5001800</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>448</v>
+        <v>279</v>
       </c>
       <c r="G37" s="12" t="s">
         <v>228</v>
       </c>
       <c r="H37" s="13"/>
       <c r="I37" s="13" t="s">
-        <v>449</v>
+        <v>280</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>452</v>
+        <v>281</v>
       </c>
       <c r="K37" s="13">
         <v>2</v>
@@ -5674,7 +6174,7 @@
         <v>2000</v>
       </c>
       <c r="M37" s="13" t="s">
-        <v>453</v>
+        <v>282</v>
       </c>
       <c r="N37" s="13">
         <v>2</v>
@@ -5695,13 +6195,13 @@
         <v>0</v>
       </c>
       <c r="T37" s="13" t="s">
-        <v>450</v>
+        <v>283</v>
       </c>
       <c r="U37" s="13">
         <v>3000</v>
       </c>
       <c r="V37" s="13" t="s">
-        <v>451</v>
+        <v>284</v>
       </c>
       <c r="W37" s="13">
         <v>0</v>
@@ -5737,7 +6237,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:33">
       <c r="A38" s="4">
         <v>820081</v>
       </c>
@@ -5754,14 +6254,14 @@
         <v>5001600</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>437</v>
+        <v>285</v>
       </c>
       <c r="G38" s="12" t="s">
         <v>228</v>
       </c>
       <c r="H38" s="13"/>
       <c r="I38" s="13" t="s">
-        <v>438</v>
+        <v>286</v>
       </c>
       <c r="J38" s="13" t="s">
         <v>78</v>
@@ -5794,13 +6294,13 @@
         <v>0</v>
       </c>
       <c r="T38" s="13" t="s">
-        <v>440</v>
+        <v>287</v>
       </c>
       <c r="U38" s="13">
         <v>1000</v>
       </c>
       <c r="V38" s="13" t="s">
-        <v>439</v>
+        <v>288</v>
       </c>
       <c r="W38" s="13">
         <v>0</v>
@@ -5836,7 +6336,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:33">
       <c r="A39" s="13">
         <v>820082</v>
       </c>
@@ -5853,14 +6353,14 @@
         <v>820082</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>443</v>
+        <v>289</v>
       </c>
       <c r="G39" s="12" t="s">
         <v>228</v>
       </c>
       <c r="H39" s="13"/>
       <c r="I39" s="13" t="s">
-        <v>444</v>
+        <v>290</v>
       </c>
       <c r="J39" s="13" t="s">
         <v>78</v>
@@ -5935,7 +6435,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:33">
       <c r="A40" s="13">
         <v>820083</v>
       </c>
@@ -5952,14 +6452,14 @@
         <v>820083</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>445</v>
+        <v>291</v>
       </c>
       <c r="G40" s="12" t="s">
         <v>228</v>
       </c>
       <c r="H40" s="13"/>
       <c r="I40" s="13" t="s">
-        <v>442</v>
+        <v>292</v>
       </c>
       <c r="J40" s="13" t="s">
         <v>78</v>
@@ -6034,7 +6534,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:33">
       <c r="A41" s="4">
         <v>820085</v>
       </c>
@@ -6051,14 +6551,14 @@
         <v>5001600</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>455</v>
+        <v>293</v>
       </c>
       <c r="G41" s="12" t="s">
         <v>228</v>
       </c>
       <c r="H41" s="13"/>
       <c r="I41" s="13" t="s">
-        <v>454</v>
+        <v>294</v>
       </c>
       <c r="J41" s="13" t="s">
         <v>78</v>
@@ -6091,13 +6591,13 @@
         <v>0</v>
       </c>
       <c r="T41" s="13" t="s">
-        <v>456</v>
+        <v>295</v>
       </c>
       <c r="U41" s="13">
         <v>1000</v>
       </c>
       <c r="V41" s="13" t="s">
-        <v>457</v>
+        <v>296</v>
       </c>
       <c r="W41" s="13">
         <v>10000</v>
@@ -6133,7 +6633,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:33">
       <c r="A42" s="13">
         <v>820086</v>
       </c>
@@ -6150,17 +6650,17 @@
         <v>820086</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>458</v>
+        <v>297</v>
       </c>
       <c r="G42" s="12" t="s">
         <v>228</v>
       </c>
       <c r="H42" s="13"/>
       <c r="I42" s="13" t="s">
-        <v>459</v>
-      </c>
-      <c r="J42" s="23" t="s">
-        <v>460</v>
+        <v>298</v>
+      </c>
+      <c r="J42" s="17" t="s">
+        <v>299</v>
       </c>
       <c r="K42" s="13">
         <v>2</v>
@@ -6233,16 +6733,17 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="E7:S71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
     <col min="5" max="5" width="27.25" style="1" customWidth="1"/>
@@ -6255,7 +6756,7 @@
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="5:19" x14ac:dyDescent="0.15">
+    <row r="7" spans="5:6">
       <c r="E7" s="1" t="s">
         <v>8</v>
       </c>
@@ -6263,7 +6764,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="5:19" x14ac:dyDescent="0.15">
+    <row r="8" spans="5:6">
       <c r="E8" s="1" t="s">
         <v>9</v>
       </c>
@@ -6271,7 +6772,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="5:19" x14ac:dyDescent="0.15">
+    <row r="9" spans="5:6">
       <c r="E9" s="1" t="s">
         <v>10</v>
       </c>
@@ -6279,15 +6780,15 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="5:19" x14ac:dyDescent="0.15">
+    <row r="10" spans="5:6">
       <c r="E10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="11" spans="5:19" x14ac:dyDescent="0.15">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="11" spans="5:6">
       <c r="E11" s="1" t="s">
         <v>12</v>
       </c>
@@ -6295,7 +6796,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="5:19" x14ac:dyDescent="0.15">
+    <row r="12" spans="5:6">
       <c r="E12" s="1" t="s">
         <v>13</v>
       </c>
@@ -6303,7 +6804,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="5:19" x14ac:dyDescent="0.15">
+    <row r="13" spans="5:19">
       <c r="E13" s="1" t="s">
         <v>14</v>
       </c>
@@ -6311,13 +6812,13 @@
         <v>47</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>278</v>
+        <v>301</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="14" spans="5:19" x14ac:dyDescent="0.15">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="14" spans="5:12">
       <c r="E14" s="1" t="s">
         <v>15</v>
       </c>
@@ -6331,13 +6832,13 @@
         <v>1</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="15" spans="5:19" x14ac:dyDescent="0.15">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="15" spans="5:19">
       <c r="E15" s="1" t="s">
         <v>16</v>
       </c>
@@ -6348,16 +6849,16 @@
         <v>3</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="16" spans="5:19" x14ac:dyDescent="0.15">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="16" spans="5:19">
       <c r="E16" s="1" t="s">
         <v>17</v>
       </c>
@@ -6371,16 +6872,16 @@
         <v>7</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>286</v>
+        <v>309</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="17" spans="5:19" x14ac:dyDescent="0.15">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="17" spans="5:19">
       <c r="E17" s="1" t="s">
         <v>18</v>
       </c>
@@ -6394,16 +6895,16 @@
         <v>7</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="18" spans="5:19" x14ac:dyDescent="0.15">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="18" spans="5:19">
       <c r="E18" s="1" t="s">
         <v>19</v>
       </c>
@@ -6417,16 +6918,16 @@
         <v>7</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>291</v>
+        <v>314</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="19" spans="5:19" x14ac:dyDescent="0.15">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="19" spans="5:19">
       <c r="E19" s="1" t="s">
         <v>20</v>
       </c>
@@ -6438,25 +6939,25 @@
         <v>参数4LIST-触发的技能id</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="20" spans="5:19" x14ac:dyDescent="0.15">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="20" spans="5:19">
       <c r="E20" s="1" t="s">
         <v>21</v>
       </c>
@@ -6468,25 +6969,25 @@
         <v>参数5-持续时间（毫秒）</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>301</v>
+        <v>324</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="21" spans="5:19" x14ac:dyDescent="0.15">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="21" spans="5:19">
       <c r="E21" s="1" t="s">
         <v>22</v>
       </c>
@@ -6498,25 +6999,25 @@
         <v>参数6-效果基础命中率（万分比）</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>305</v>
+        <v>328</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>306</v>
+        <v>329</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>308</v>
+        <v>331</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="22" spans="5:19" x14ac:dyDescent="0.15">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="22" spans="5:19">
       <c r="E22" s="1" t="s">
         <v>23</v>
       </c>
@@ -6531,22 +7032,22 @@
         <v>66</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>311</v>
+        <v>334</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="23" spans="5:19" x14ac:dyDescent="0.15">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="23" spans="5:19">
       <c r="E23" s="1" t="s">
         <v>24</v>
       </c>
@@ -6558,25 +7059,25 @@
         <v>参数8-效果触发间隔（毫秒）</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>316</v>
+        <v>339</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="24" spans="5:19" x14ac:dyDescent="0.15">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="24" spans="5:19">
       <c r="E24" s="1" t="s">
         <v>25</v>
       </c>
@@ -6588,25 +7089,25 @@
         <v>参数9-击中回复生命值-固定值</v>
       </c>
       <c r="H24" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="J24" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="I24" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="K24" s="1" t="s">
-        <v>321</v>
+        <v>344</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>322</v>
+        <v>345</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="25" spans="5:19" x14ac:dyDescent="0.15">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="25" spans="5:19">
       <c r="E25" s="1" t="s">
         <v>26</v>
       </c>
@@ -6618,25 +7119,25 @@
         <v>参数10-击中回复生命值-自身最大生命值百万分比</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>324</v>
+        <v>347</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>327</v>
+        <v>350</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="26" spans="5:19" x14ac:dyDescent="0.15">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="26" spans="5:19">
       <c r="E26" s="1" t="s">
         <v>27</v>
       </c>
@@ -6648,25 +7149,25 @@
         <v>参数11-击中回复效果提高万分比</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>329</v>
+        <v>352</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>330</v>
+        <v>353</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>331</v>
+        <v>354</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>332</v>
+        <v>355</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="27" spans="5:19" x14ac:dyDescent="0.15">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="27" spans="5:19">
       <c r="E27" s="1" t="s">
         <v>28</v>
       </c>
@@ -6678,25 +7179,25 @@
         <v>参数12-击杀回复生命-固定值</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>334</v>
+        <v>357</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>335</v>
+        <v>358</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>336</v>
+        <v>359</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="28" spans="5:19" x14ac:dyDescent="0.15">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="28" spans="5:12">
       <c r="E28" s="1" t="s">
         <v>29</v>
       </c>
@@ -6708,22 +7209,22 @@
         <v>参数13-击杀回复生命-自身最大生命值百万分比</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>339</v>
+        <v>362</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>340</v>
+        <v>363</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>341</v>
+        <v>364</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="29" spans="5:19" x14ac:dyDescent="0.15">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="29" spans="5:19">
       <c r="E29" s="1" t="s">
         <v>30</v>
       </c>
@@ -6735,25 +7236,25 @@
         <v>参数14-击杀回复生命-目标最大生命值百万分比</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>344</v>
+        <v>367</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>346</v>
+        <v>369</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="30" spans="5:19" x14ac:dyDescent="0.15">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="30" spans="5:19">
       <c r="E30" s="1" t="s">
         <v>31</v>
       </c>
@@ -6765,25 +7266,25 @@
         <v>参数15-击杀回复生命效果提高万分比</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="31" spans="5:19" x14ac:dyDescent="0.15">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="31" spans="5:19">
       <c r="E31" s="1" t="s">
         <v>32</v>
       </c>
@@ -6795,52 +7296,52 @@
         <v>参数16-获得护盾-固定值</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>354</v>
+        <v>377</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>356</v>
+        <v>379</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="32" spans="5:19" x14ac:dyDescent="0.15">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="32" spans="5:12">
       <c r="E32" s="1" t="s">
         <v>33</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="G32" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数17-获得护盾-自身生命百万分比</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>361</v>
+        <v>384</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="33" spans="5:9" x14ac:dyDescent="0.15">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="33" spans="5:9">
       <c r="E33" s="1" t="s">
         <v>34</v>
       </c>
@@ -6852,13 +7353,13 @@
         <v>参数18-获得护盾-自身已损失生命万分比</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="34" spans="5:9" x14ac:dyDescent="0.15">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="34" spans="5:9">
       <c r="E34" s="1" t="s">
         <v>35</v>
       </c>
@@ -6870,403 +7371,404 @@
         <v>参数19-获得护盾效果提高万分比</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>365</v>
+        <v>388</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="35" spans="5:9" x14ac:dyDescent="0.15">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="35" spans="5:9">
       <c r="E35" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>367</v>
+        <v>390</v>
       </c>
       <c r="G35" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数20-技能增加-固定值</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>368</v>
+        <v>391</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="36" spans="5:9" x14ac:dyDescent="0.15">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="36" spans="7:9">
       <c r="G36" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数21-技能增加-万分比</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>370</v>
+        <v>393</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="37" spans="5:9" x14ac:dyDescent="0.15">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="37" spans="7:9">
       <c r="G37" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数22-技能增加-普通攻击范围万分比</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>372</v>
+        <v>395</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="38" spans="5:9" x14ac:dyDescent="0.15">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="38" spans="7:9">
       <c r="G38" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数25LIST-攻击提高-攻击的元素类型</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>374</v>
+        <v>397</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="39" spans="5:9" x14ac:dyDescent="0.15">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="39" spans="7:9">
       <c r="G39" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数25LIST-攻击提高-固定值</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>374</v>
+        <v>397</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="40" spans="5:9" x14ac:dyDescent="0.15">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="40" spans="7:9">
       <c r="G40" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数25LIST-攻击提高-万分比</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>374</v>
+        <v>397</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="41" spans="5:9" x14ac:dyDescent="0.15">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="41" spans="7:9">
       <c r="G41" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数28-防御提高-固定值</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>378</v>
+        <v>401</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="42" spans="5:9" x14ac:dyDescent="0.15">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="42" spans="7:9">
       <c r="G42" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数29-防御提高-万分比</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>380</v>
+        <v>403</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="43" spans="5:9" x14ac:dyDescent="0.15">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="43" spans="7:9">
       <c r="G43" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数30-生命上限提高-固定值</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>382</v>
+        <v>405</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="44" spans="5:9" x14ac:dyDescent="0.15">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="44" spans="7:9">
       <c r="G44" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数31-生命上限提高-百万分比</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="45" spans="5:9" x14ac:dyDescent="0.15">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="45" spans="7:9">
       <c r="G45" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数32-攻击速度提高-万分比</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>386</v>
+        <v>409</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="46" spans="5:9" x14ac:dyDescent="0.15">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="46" spans="7:9">
       <c r="G46" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数33-移动速度提高-万分比</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>388</v>
+        <v>411</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="47" spans="5:9" x14ac:dyDescent="0.15">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="47" spans="7:9">
       <c r="G47" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数34-攻击范围提高-万分比</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>390</v>
+        <v>413</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="48" spans="5:9" x14ac:dyDescent="0.15">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="48" spans="7:9">
       <c r="G48" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数35-攻击目标数量提高-固定值</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>392</v>
+        <v>415</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="49" spans="7:8" x14ac:dyDescent="0.15">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="49" spans="7:8">
       <c r="G49" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数36-</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="50" spans="7:8" x14ac:dyDescent="0.15">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="50" spans="7:8">
       <c r="G50" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数37-</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="51" spans="7:8" x14ac:dyDescent="0.15">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="51" spans="7:8">
       <c r="G51" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数38-</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="52" spans="7:8" x14ac:dyDescent="0.15">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="52" spans="7:8">
       <c r="G52" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数39-</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="53" spans="7:8" x14ac:dyDescent="0.15">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="53" spans="7:8">
       <c r="G53" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数40-</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="54" spans="7:8" x14ac:dyDescent="0.15">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="54" spans="7:8">
       <c r="G54" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数41-</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="55" spans="7:8" x14ac:dyDescent="0.15">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="55" spans="7:8">
       <c r="G55" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数42-</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="56" spans="7:8" x14ac:dyDescent="0.15">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="56" spans="7:8">
       <c r="G56" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数41-</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="57" spans="7:8" x14ac:dyDescent="0.15">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="57" spans="7:8">
       <c r="G57" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数42-</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="58" spans="7:8" x14ac:dyDescent="0.15">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="58" spans="7:8">
       <c r="G58" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数43-</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="59" spans="7:8" x14ac:dyDescent="0.15">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="59" spans="7:8">
       <c r="G59" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数44-</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="60" spans="7:8" x14ac:dyDescent="0.15">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="60" spans="7:8">
       <c r="G60" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数45-</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="61" spans="7:8" x14ac:dyDescent="0.15">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="61" spans="7:8">
       <c r="G61" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数46-</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="62" spans="7:8" x14ac:dyDescent="0.15">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="62" spans="7:8">
       <c r="G62" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数47-</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="63" spans="7:8" x14ac:dyDescent="0.15">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="63" spans="7:8">
       <c r="G63" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数48-</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="64" spans="7:8" x14ac:dyDescent="0.15">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="64" spans="7:8">
       <c r="G64" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数49-</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="65" spans="7:8" x14ac:dyDescent="0.15">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="65" spans="7:8">
       <c r="G65" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数50-</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="66" spans="7:8" x14ac:dyDescent="0.15">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="66" spans="7:8">
       <c r="G66" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数51-</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="67" spans="7:8" x14ac:dyDescent="0.15">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="67" spans="7:8">
       <c r="G67" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数52-</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="68" spans="7:8" x14ac:dyDescent="0.15">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="68" spans="7:8">
       <c r="G68" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数53-</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="69" spans="7:8" x14ac:dyDescent="0.15">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="69" spans="7:8">
       <c r="G69" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数54-</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="70" spans="7:8" x14ac:dyDescent="0.15">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="70" spans="7:8">
       <c r="G70" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数55-</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="71" spans="7:8" x14ac:dyDescent="0.15">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="71" spans="7:8">
       <c r="G71" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数56-</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>414</v>
+        <v>437</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="D6:F43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="11.25" style="1" customWidth="1"/>
@@ -7276,172 +7778,172 @@
     <col min="23" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="4:5" x14ac:dyDescent="0.15">
+    <row r="6" spans="4:5">
       <c r="D6" s="2" t="s">
-        <v>415</v>
+        <v>438</v>
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="4:5" x14ac:dyDescent="0.15">
+    <row r="7" spans="4:5">
       <c r="D7" s="2">
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="8" spans="4:5" x14ac:dyDescent="0.15">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="8" spans="4:5">
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="4:5" x14ac:dyDescent="0.15">
+    <row r="9" spans="4:5">
       <c r="D9" s="2">
         <v>2</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="10" spans="4:5" x14ac:dyDescent="0.15">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="10" spans="4:5">
       <c r="D10" s="2">
         <v>2.1</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="11" spans="4:5" x14ac:dyDescent="0.15">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="11" spans="4:5">
       <c r="D11" s="2" t="s">
-        <v>419</v>
+        <v>442</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="12" spans="4:5" x14ac:dyDescent="0.15">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="12" spans="4:5">
       <c r="D12" s="2" t="s">
-        <v>421</v>
+        <v>444</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="13" spans="4:5" x14ac:dyDescent="0.15">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="13" spans="4:5">
       <c r="D13" s="2" t="s">
-        <v>423</v>
+        <v>446</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="14" spans="4:5" x14ac:dyDescent="0.15">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="14" spans="4:5">
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="4:5" x14ac:dyDescent="0.15">
+    <row r="15" spans="4:5">
       <c r="D15" s="2">
-        <v>2.2000000000000002</v>
+        <v>2.2</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="16" spans="4:5" x14ac:dyDescent="0.15">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="16" spans="4:5">
       <c r="D16" s="2" t="s">
-        <v>426</v>
+        <v>449</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.15">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="17" spans="4:5">
       <c r="D17" s="2" t="s">
-        <v>427</v>
+        <v>450</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.15">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="18" spans="4:5">
       <c r="D18" s="2" t="s">
-        <v>429</v>
+        <v>452</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="28" spans="4:5" x14ac:dyDescent="0.15">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="28" spans="4:4">
       <c r="D28" s="1" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="29" spans="4:5" x14ac:dyDescent="0.15">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="29" spans="4:5">
       <c r="D29" s="1" t="s">
-        <v>432</v>
+        <v>455</v>
       </c>
       <c r="E29" s="1">
         <v>101</v>
       </c>
     </row>
-    <row r="30" spans="4:5" x14ac:dyDescent="0.15">
+    <row r="30" spans="4:5">
       <c r="D30" s="1" t="s">
-        <v>433</v>
+        <v>456</v>
       </c>
       <c r="E30" s="1">
         <v>102</v>
       </c>
     </row>
-    <row r="31" spans="4:5" x14ac:dyDescent="0.15">
+    <row r="31" spans="4:4">
       <c r="D31" s="1" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="32" spans="4:5" x14ac:dyDescent="0.15">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="32" spans="4:4">
       <c r="D32" s="1" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="33" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25" spans="4:6">
       <c r="D33" s="1" t="s">
-        <v>436</v>
+        <v>459</v>
       </c>
       <c r="E33" s="1">
         <v>105</v>
       </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="34" ht="14.25" spans="6:6">
       <c r="F34"/>
     </row>
-    <row r="35" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="35" ht="14.25" spans="6:6">
       <c r="F35"/>
     </row>
-    <row r="36" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="36" ht="14.25" spans="6:6">
       <c r="F36"/>
     </row>
-    <row r="37" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="37" ht="14.25" spans="6:6">
       <c r="F37"/>
     </row>
-    <row r="38" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="38" ht="14.25" spans="6:6">
       <c r="F38"/>
     </row>
-    <row r="39" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="39" ht="14.25" spans="6:6">
       <c r="F39"/>
     </row>
-    <row r="40" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="40" ht="14.25" spans="6:6">
       <c r="F40"/>
     </row>
-    <row r="41" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="41" ht="14.25" spans="6:6">
       <c r="F41"/>
     </row>
-    <row r="42" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="42" ht="14.25" spans="6:6">
       <c r="F42"/>
     </row>
-    <row r="43" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="43" ht="14.25" spans="6:6">
       <c r="F43"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -877,7 +877,7 @@
     <t>暴风雪概率附加减速</t>
   </si>
   <si>
-    <t>暴风雪减速状态（万分比降低攻速【参数1】和移速【参数2】），持续时间【参数5】毫秒，状态命中率【参数6】</t>
+    <t>暴风雪减速状态（万分比降低移速【参数1】和攻速【参数2】），持续时间【参数5】毫秒，状态命中率【参数6】</t>
   </si>
   <si>
     <t>5001701:1</t>
@@ -1496,15 +1496,15 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1665,12 +1665,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1685,6 +1685,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.349986266670736"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799615466780602"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1692,12 +1698,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.349986266670736"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2172,30 +2172,30 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="23" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="23" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2256,13 +2256,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2544,7 +2537,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AG41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -2554,7 +2547,7 @@
     <col min="6" max="6" width="29.75" customWidth="1"/>
     <col min="7" max="7" width="12.5" customWidth="1"/>
     <col min="8" max="8" width="10.5" customWidth="1"/>
-    <col min="9" max="9" width="210.428571428571" customWidth="1"/>
+    <col min="9" max="9" width="30.125" customWidth="1"/>
     <col min="10" max="11" width="15.125" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="14" width="15.125" customWidth="1"/>
@@ -2583,10 +2576,10 @@
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
@@ -2624,16 +2617,16 @@
       <c r="E2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="5" t="s">
         <v>3</v>
       </c>
       <c r="J2" s="4" t="s">
@@ -2645,13 +2638,13 @@
       <c r="L2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="M2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="N2" s="15" t="s">
+      <c r="N2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="15" t="s">
+      <c r="O2" s="14" t="s">
         <v>2</v>
       </c>
       <c r="P2" s="4" t="s">
@@ -2663,7 +2656,7 @@
       <c r="R2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="S2" s="15" t="s">
+      <c r="S2" s="14" t="s">
         <v>5</v>
       </c>
       <c r="T2" s="4" t="s">
@@ -2687,13 +2680,13 @@
       <c r="Z2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="AA2" s="15" t="s">
+      <c r="AA2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="AB2" s="15" t="s">
+      <c r="AB2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="AC2" s="15" t="s">
+      <c r="AC2" s="14" t="s">
         <v>7</v>
       </c>
       <c r="AD2" s="18" t="s">
@@ -2725,16 +2718,16 @@
       <c r="E3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="5" t="s">
         <v>16</v>
       </c>
       <c r="J3" s="4" t="s">
@@ -2746,13 +2739,13 @@
       <c r="L3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="15" t="s">
+      <c r="N3" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="15" t="s">
+      <c r="O3" s="14" t="s">
         <v>22</v>
       </c>
       <c r="P3" s="4" t="s">
@@ -2764,7 +2757,7 @@
       <c r="R3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="S3" s="15" t="s">
+      <c r="S3" s="14" t="s">
         <v>26</v>
       </c>
       <c r="T3" s="4" t="s">
@@ -2788,13 +2781,13 @@
       <c r="Z3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="AA3" s="15" t="s">
+      <c r="AA3" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="AB3" s="15" t="s">
+      <c r="AB3" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="AC3" s="15" t="s">
+      <c r="AC3" s="14" t="s">
         <v>36</v>
       </c>
       <c r="AD3" s="18" t="s">
@@ -2826,16 +2819,16 @@
       <c r="E4" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="5" t="s">
         <v>49</v>
       </c>
       <c r="J4" s="4" t="s">
@@ -2847,13 +2840,13 @@
       <c r="L4" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="M4" s="15" t="s">
+      <c r="M4" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="N4" s="15" t="s">
+      <c r="N4" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="O4" s="15" t="s">
+      <c r="O4" s="14" t="s">
         <v>55</v>
       </c>
       <c r="P4" s="4" t="s">
@@ -2865,7 +2858,7 @@
       <c r="R4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="S4" s="15" t="s">
+      <c r="S4" s="14" t="s">
         <v>59</v>
       </c>
       <c r="T4" s="4" t="s">
@@ -2889,13 +2882,13 @@
       <c r="Z4" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AA4" s="15" t="s">
+      <c r="AA4" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="AB4" s="15" t="s">
+      <c r="AB4" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="AC4" s="15" t="s">
+      <c r="AC4" s="14" t="s">
         <v>69</v>
       </c>
       <c r="AD4" s="18" t="s">
@@ -2912,58 +2905,58 @@
       </c>
     </row>
     <row r="5" spans="1:33">
-      <c r="A5" s="5">
+      <c r="A5" s="6">
         <v>1000001</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="6">
         <v>100</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="6">
         <v>2</v>
       </c>
-      <c r="D5" s="5">
-        <v>0</v>
-      </c>
-      <c r="E5" s="5">
+      <c r="D5" s="6">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6">
         <v>890001</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="5" t="s">
         <v>77</v>
       </c>
       <c r="J5" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="6">
         <v>3</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5" s="6">
         <v>300000</v>
       </c>
       <c r="M5" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="N5" s="16">
-        <v>1</v>
-      </c>
-      <c r="O5" s="16">
+      <c r="N5" s="15">
+        <v>1</v>
+      </c>
+      <c r="O5" s="15">
         <v>0</v>
       </c>
       <c r="P5" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="Q5" s="5">
-        <v>1</v>
-      </c>
-      <c r="R5" s="5">
+      <c r="Q5" s="6">
+        <v>1</v>
+      </c>
+      <c r="R5" s="6">
         <v>0</v>
       </c>
       <c r="S5" s="17">
@@ -2972,2449 +2965,2449 @@
       <c r="T5" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="U5" s="5">
+      <c r="U5" s="6">
         <v>0</v>
       </c>
       <c r="V5" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="W5" s="5">
+      <c r="W5" s="6">
         <v>10000</v>
       </c>
-      <c r="X5" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y5" s="5">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="5">
+      <c r="X5" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y5" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="6">
         <v>0</v>
       </c>
       <c r="AA5" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="AB5" s="16">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="16">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE5" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF5" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG5" s="6" t="s">
+      <c r="AB5" s="15">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="15">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE5" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF5" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG5" s="7" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:33">
-      <c r="A6" s="6">
+      <c r="A6" s="7">
         <v>54010001</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <v>5401</v>
       </c>
-      <c r="C6" s="6">
-        <v>1</v>
-      </c>
-      <c r="D6" s="6">
-        <v>0</v>
-      </c>
-      <c r="E6" s="6">
+      <c r="C6" s="7">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7">
+        <v>0</v>
+      </c>
+      <c r="E6" s="7">
         <v>3540200</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="7">
         <v>2</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="7">
         <v>2000</v>
       </c>
-      <c r="M6" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="N6" s="6">
-        <v>1</v>
-      </c>
-      <c r="O6" s="6">
-        <v>0</v>
-      </c>
-      <c r="P6" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>1</v>
-      </c>
-      <c r="R6" s="6">
-        <v>0</v>
-      </c>
-      <c r="S6" s="6">
-        <v>0</v>
-      </c>
-      <c r="T6" s="6" t="s">
+      <c r="M6" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="N6" s="7">
+        <v>1</v>
+      </c>
+      <c r="O6" s="7">
+        <v>0</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>1</v>
+      </c>
+      <c r="R6" s="7">
+        <v>0</v>
+      </c>
+      <c r="S6" s="7">
+        <v>0</v>
+      </c>
+      <c r="T6" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="U6" s="6">
+      <c r="U6" s="7">
         <v>7200000</v>
       </c>
-      <c r="V6" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="W6" s="6">
+      <c r="V6" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="W6" s="7">
         <v>10000</v>
       </c>
-      <c r="X6" s="6" t="s">
+      <c r="X6" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="Y6" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="6">
+      <c r="Y6" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="7">
         <v>3</v>
       </c>
-      <c r="AA6" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB6" s="6">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="6" t="s">
+      <c r="AA6" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB6" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="AE6" s="6" t="s">
+      <c r="AE6" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="AF6" s="6" t="s">
+      <c r="AF6" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="AG6" s="6" t="s">
+      <c r="AG6" s="7" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:33">
-      <c r="A7" s="6">
+      <c r="A7" s="7">
         <v>54020001</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <v>5402</v>
       </c>
-      <c r="C7" s="6">
-        <v>1</v>
-      </c>
-      <c r="D7" s="6">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6">
+      <c r="C7" s="7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="7">
+        <v>0</v>
+      </c>
+      <c r="E7" s="7">
         <v>3540400</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="7">
         <v>2</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="7">
         <v>2000</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="M7" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="N7" s="6">
-        <v>1</v>
-      </c>
-      <c r="O7" s="6">
-        <v>0</v>
-      </c>
-      <c r="P7" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>1</v>
-      </c>
-      <c r="R7" s="6">
-        <v>0</v>
-      </c>
-      <c r="S7" s="6">
-        <v>0</v>
-      </c>
-      <c r="T7" s="6" t="s">
+      <c r="N7" s="7">
+        <v>1</v>
+      </c>
+      <c r="O7" s="7">
+        <v>0</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>1</v>
+      </c>
+      <c r="R7" s="7">
+        <v>0</v>
+      </c>
+      <c r="S7" s="7">
+        <v>0</v>
+      </c>
+      <c r="T7" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="U7" s="6">
+      <c r="U7" s="7">
         <v>7200000</v>
       </c>
-      <c r="V7" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="W7" s="6">
+      <c r="V7" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="W7" s="7">
         <v>10000</v>
       </c>
-      <c r="X7" s="6" t="s">
+      <c r="X7" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="Y7" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="6">
+      <c r="Y7" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="7">
         <v>3</v>
       </c>
-      <c r="AA7" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB7" s="6">
-        <v>1</v>
-      </c>
-      <c r="AC7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="6" t="s">
+      <c r="AA7" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB7" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="AE7" s="6" t="s">
+      <c r="AE7" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="AF7" s="6" t="s">
+      <c r="AF7" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="AG7" s="6" t="s">
+      <c r="AG7" s="7" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:33">
-      <c r="A8" s="6">
+      <c r="A8" s="7">
         <v>54030001</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="7">
         <v>5403</v>
       </c>
-      <c r="C8" s="6">
-        <v>1</v>
-      </c>
-      <c r="D8" s="6">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6">
+      <c r="C8" s="7">
+        <v>1</v>
+      </c>
+      <c r="D8" s="7">
+        <v>0</v>
+      </c>
+      <c r="E8" s="7">
         <v>3540600</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="I8" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="7">
         <v>2</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="7">
         <v>2000</v>
       </c>
-      <c r="M8" s="6" t="s">
+      <c r="M8" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="N8" s="6">
-        <v>1</v>
-      </c>
-      <c r="O8" s="6">
-        <v>0</v>
-      </c>
-      <c r="P8" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>1</v>
-      </c>
-      <c r="R8" s="6">
-        <v>0</v>
-      </c>
-      <c r="S8" s="6">
-        <v>0</v>
-      </c>
-      <c r="T8" s="6" t="s">
+      <c r="N8" s="7">
+        <v>1</v>
+      </c>
+      <c r="O8" s="7">
+        <v>0</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>1</v>
+      </c>
+      <c r="R8" s="7">
+        <v>0</v>
+      </c>
+      <c r="S8" s="7">
+        <v>0</v>
+      </c>
+      <c r="T8" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="U8" s="6">
+      <c r="U8" s="7">
         <v>7200000</v>
       </c>
-      <c r="V8" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="W8" s="6">
+      <c r="V8" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="W8" s="7">
         <v>10000</v>
       </c>
-      <c r="X8" s="6" t="s">
+      <c r="X8" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="Y8" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="6">
+      <c r="Y8" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="7">
         <v>3</v>
       </c>
-      <c r="AA8" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB8" s="6">
-        <v>1</v>
-      </c>
-      <c r="AC8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="6" t="s">
+      <c r="AA8" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB8" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="AE8" s="6" t="s">
+      <c r="AE8" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="AF8" s="6" t="s">
+      <c r="AF8" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="AG8" s="6" t="s">
+      <c r="AG8" s="7" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:33">
-      <c r="A9" s="6">
+      <c r="A9" s="7">
         <v>54040001</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="7">
         <v>5404</v>
       </c>
-      <c r="C9" s="6">
-        <v>1</v>
-      </c>
-      <c r="D9" s="6">
-        <v>0</v>
-      </c>
-      <c r="E9" s="6">
+      <c r="C9" s="7">
+        <v>1</v>
+      </c>
+      <c r="D9" s="7">
+        <v>0</v>
+      </c>
+      <c r="E9" s="7">
         <v>3540800</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="7">
         <v>2</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="7">
         <v>2000</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="M9" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="N9" s="6">
-        <v>1</v>
-      </c>
-      <c r="O9" s="6">
-        <v>0</v>
-      </c>
-      <c r="P9" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q9" s="6">
-        <v>1</v>
-      </c>
-      <c r="R9" s="6">
-        <v>0</v>
-      </c>
-      <c r="S9" s="6">
-        <v>0</v>
-      </c>
-      <c r="T9" s="6" t="s">
+      <c r="N9" s="7">
+        <v>1</v>
+      </c>
+      <c r="O9" s="7">
+        <v>0</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>1</v>
+      </c>
+      <c r="R9" s="7">
+        <v>0</v>
+      </c>
+      <c r="S9" s="7">
+        <v>0</v>
+      </c>
+      <c r="T9" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="U9" s="6">
+      <c r="U9" s="7">
         <v>7200000</v>
       </c>
-      <c r="V9" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="W9" s="6">
+      <c r="V9" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="W9" s="7">
         <v>10000</v>
       </c>
-      <c r="X9" s="6" t="s">
+      <c r="X9" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="Y9" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="6">
+      <c r="Y9" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="7">
         <v>3</v>
       </c>
-      <c r="AA9" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB9" s="6">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="6" t="s">
+      <c r="AA9" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB9" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="AE9" s="6" t="s">
+      <c r="AE9" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="AF9" s="6" t="s">
+      <c r="AF9" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="AG9" s="6" t="s">
+      <c r="AG9" s="7" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:33">
-      <c r="A10" s="6">
+      <c r="A10" s="7">
         <v>54050001</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="7">
         <v>5405</v>
       </c>
-      <c r="C10" s="6">
-        <v>1</v>
-      </c>
-      <c r="D10" s="6">
-        <v>0</v>
-      </c>
-      <c r="E10" s="6">
+      <c r="C10" s="7">
+        <v>1</v>
+      </c>
+      <c r="D10" s="7">
+        <v>0</v>
+      </c>
+      <c r="E10" s="7">
         <v>3541000</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="7">
         <v>2</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="7">
         <v>500</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="M10" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="N10" s="6">
-        <v>1</v>
-      </c>
-      <c r="O10" s="6">
-        <v>0</v>
-      </c>
-      <c r="P10" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q10" s="6">
-        <v>1</v>
-      </c>
-      <c r="R10" s="6">
-        <v>0</v>
-      </c>
-      <c r="S10" s="6">
-        <v>0</v>
-      </c>
-      <c r="T10" s="6" t="s">
+      <c r="N10" s="7">
+        <v>1</v>
+      </c>
+      <c r="O10" s="7">
+        <v>0</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>1</v>
+      </c>
+      <c r="R10" s="7">
+        <v>0</v>
+      </c>
+      <c r="S10" s="7">
+        <v>0</v>
+      </c>
+      <c r="T10" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="U10" s="6">
+      <c r="U10" s="7">
         <v>4000</v>
       </c>
-      <c r="V10" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="W10" s="6">
+      <c r="V10" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="W10" s="7">
         <v>10000</v>
       </c>
-      <c r="X10" s="6" t="s">
+      <c r="X10" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="Y10" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="6">
+      <c r="Y10" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="7">
         <v>3</v>
       </c>
-      <c r="AA10" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB10" s="6">
-        <v>1</v>
-      </c>
-      <c r="AC10" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="6" t="s">
+      <c r="AA10" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB10" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="AE10" s="6" t="s">
+      <c r="AE10" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="AF10" s="6" t="s">
+      <c r="AF10" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="AG10" s="6" t="s">
+      <c r="AG10" s="7" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:33">
-      <c r="A11" s="6">
+      <c r="A11" s="7">
         <v>54060001</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="7">
         <v>5406</v>
       </c>
-      <c r="C11" s="6">
-        <v>1</v>
-      </c>
-      <c r="D11" s="6">
-        <v>0</v>
-      </c>
-      <c r="E11" s="6">
+      <c r="C11" s="7">
+        <v>1</v>
+      </c>
+      <c r="D11" s="7">
+        <v>0</v>
+      </c>
+      <c r="E11" s="7">
         <v>3541200</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="J11" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="7">
         <v>2</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="7">
         <v>2000</v>
       </c>
-      <c r="M11" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="N11" s="6">
-        <v>1</v>
-      </c>
-      <c r="O11" s="6">
-        <v>0</v>
-      </c>
-      <c r="P11" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q11" s="6">
-        <v>1</v>
-      </c>
-      <c r="R11" s="6">
-        <v>0</v>
-      </c>
-      <c r="S11" s="6">
-        <v>0</v>
-      </c>
-      <c r="T11" s="6" t="s">
+      <c r="M11" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="N11" s="7">
+        <v>1</v>
+      </c>
+      <c r="O11" s="7">
+        <v>0</v>
+      </c>
+      <c r="P11" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>1</v>
+      </c>
+      <c r="R11" s="7">
+        <v>0</v>
+      </c>
+      <c r="S11" s="7">
+        <v>0</v>
+      </c>
+      <c r="T11" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="U11" s="6">
+      <c r="U11" s="7">
         <v>7200000</v>
       </c>
-      <c r="V11" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="W11" s="6">
+      <c r="V11" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="W11" s="7">
         <v>10000</v>
       </c>
-      <c r="X11" s="6" t="s">
+      <c r="X11" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="Y11" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="6">
+      <c r="Y11" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="7">
         <v>3</v>
       </c>
-      <c r="AA11" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB11" s="6">
-        <v>1</v>
-      </c>
-      <c r="AC11" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="6" t="s">
+      <c r="AA11" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB11" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="AE11" s="6" t="s">
+      <c r="AE11" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="AF11" s="6" t="s">
+      <c r="AF11" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="AG11" s="6" t="s">
+      <c r="AG11" s="7" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:33">
-      <c r="A12" s="6">
+      <c r="A12" s="7">
         <v>54070001</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="7">
         <v>5407</v>
       </c>
-      <c r="C12" s="6">
-        <v>1</v>
-      </c>
-      <c r="D12" s="6">
-        <v>0</v>
-      </c>
-      <c r="E12" s="6">
+      <c r="C12" s="7">
+        <v>1</v>
+      </c>
+      <c r="D12" s="7">
+        <v>0</v>
+      </c>
+      <c r="E12" s="7">
         <v>3541400</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="I12" s="12" t="s">
+      <c r="I12" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="J12" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="7">
         <v>2</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="7">
         <v>500</v>
       </c>
-      <c r="M12" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="N12" s="6">
-        <v>1</v>
-      </c>
-      <c r="O12" s="6">
-        <v>0</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q12" s="6">
-        <v>1</v>
-      </c>
-      <c r="R12" s="6">
-        <v>0</v>
-      </c>
-      <c r="S12" s="6">
-        <v>0</v>
-      </c>
-      <c r="T12" s="6" t="s">
+      <c r="M12" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="N12" s="7">
+        <v>1</v>
+      </c>
+      <c r="O12" s="7">
+        <v>0</v>
+      </c>
+      <c r="P12" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>1</v>
+      </c>
+      <c r="R12" s="7">
+        <v>0</v>
+      </c>
+      <c r="S12" s="7">
+        <v>0</v>
+      </c>
+      <c r="T12" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="U12" s="6">
+      <c r="U12" s="7">
         <v>4000</v>
       </c>
-      <c r="V12" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="W12" s="6">
+      <c r="V12" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="W12" s="7">
         <v>10000</v>
       </c>
-      <c r="X12" s="6" t="s">
+      <c r="X12" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="Y12" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="6">
+      <c r="Y12" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="7">
         <v>3</v>
       </c>
-      <c r="AA12" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB12" s="6">
-        <v>1</v>
-      </c>
-      <c r="AC12" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="6" t="s">
+      <c r="AA12" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB12" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="AE12" s="6" t="s">
+      <c r="AE12" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="AF12" s="6" t="s">
+      <c r="AF12" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="AG12" s="6" t="s">
+      <c r="AG12" s="7" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:33">
-      <c r="A13" s="6">
+      <c r="A13" s="7">
         <v>54080001</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="7">
         <v>5408</v>
       </c>
-      <c r="C13" s="6">
-        <v>1</v>
-      </c>
-      <c r="D13" s="6">
-        <v>0</v>
-      </c>
-      <c r="E13" s="6">
+      <c r="C13" s="7">
+        <v>1</v>
+      </c>
+      <c r="D13" s="7">
+        <v>0</v>
+      </c>
+      <c r="E13" s="7">
         <v>3541600</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="G13" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="H13" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="I13" s="12" t="s">
+      <c r="I13" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="J13" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="7">
         <v>2</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="7">
         <v>500</v>
       </c>
-      <c r="M13" s="6" t="s">
+      <c r="M13" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="N13" s="6">
-        <v>1</v>
-      </c>
-      <c r="O13" s="6">
-        <v>0</v>
-      </c>
-      <c r="P13" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q13" s="6">
-        <v>1</v>
-      </c>
-      <c r="R13" s="6">
-        <v>0</v>
-      </c>
-      <c r="S13" s="6">
-        <v>0</v>
-      </c>
-      <c r="T13" s="6" t="s">
+      <c r="N13" s="7">
+        <v>1</v>
+      </c>
+      <c r="O13" s="7">
+        <v>0</v>
+      </c>
+      <c r="P13" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>1</v>
+      </c>
+      <c r="R13" s="7">
+        <v>0</v>
+      </c>
+      <c r="S13" s="7">
+        <v>0</v>
+      </c>
+      <c r="T13" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="U13" s="6">
+      <c r="U13" s="7">
         <v>4000</v>
       </c>
-      <c r="V13" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="W13" s="6">
+      <c r="V13" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="W13" s="7">
         <v>10000</v>
       </c>
-      <c r="X13" s="6" t="s">
+      <c r="X13" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="Y13" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z13" s="6">
+      <c r="Y13" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="7">
         <v>3</v>
       </c>
-      <c r="AA13" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB13" s="6">
-        <v>1</v>
-      </c>
-      <c r="AC13" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="6" t="s">
+      <c r="AA13" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB13" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC13" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="AE13" s="6" t="s">
+      <c r="AE13" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="AF13" s="6" t="s">
+      <c r="AF13" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="AG13" s="6" t="s">
+      <c r="AG13" s="7" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:33">
-      <c r="A14" s="6">
+      <c r="A14" s="7">
         <v>54090001</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="7">
         <v>5409</v>
       </c>
-      <c r="C14" s="6">
-        <v>1</v>
-      </c>
-      <c r="D14" s="6">
-        <v>0</v>
-      </c>
-      <c r="E14" s="6">
+      <c r="C14" s="7">
+        <v>1</v>
+      </c>
+      <c r="D14" s="7">
+        <v>0</v>
+      </c>
+      <c r="E14" s="7">
         <v>3541800</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="H14" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="J14" s="6" t="s">
+      <c r="J14" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="7">
         <v>2</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="7">
         <v>500</v>
       </c>
-      <c r="M14" s="6" t="s">
+      <c r="M14" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="N14" s="6">
-        <v>1</v>
-      </c>
-      <c r="O14" s="6">
-        <v>0</v>
-      </c>
-      <c r="P14" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q14" s="6">
-        <v>1</v>
-      </c>
-      <c r="R14" s="6">
-        <v>0</v>
-      </c>
-      <c r="S14" s="6">
-        <v>0</v>
-      </c>
-      <c r="T14" s="6" t="s">
+      <c r="N14" s="7">
+        <v>1</v>
+      </c>
+      <c r="O14" s="7">
+        <v>0</v>
+      </c>
+      <c r="P14" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q14" s="7">
+        <v>1</v>
+      </c>
+      <c r="R14" s="7">
+        <v>0</v>
+      </c>
+      <c r="S14" s="7">
+        <v>0</v>
+      </c>
+      <c r="T14" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="U14" s="6">
+      <c r="U14" s="7">
         <v>4000</v>
       </c>
-      <c r="V14" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="W14" s="6">
+      <c r="V14" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="W14" s="7">
         <v>10000</v>
       </c>
-      <c r="X14" s="6" t="s">
+      <c r="X14" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="Y14" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z14" s="6">
+      <c r="Y14" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="7">
         <v>3</v>
       </c>
-      <c r="AA14" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB14" s="6">
-        <v>1</v>
-      </c>
-      <c r="AC14" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="6" t="s">
+      <c r="AA14" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB14" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="AE14" s="6" t="s">
+      <c r="AE14" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="AF14" s="6" t="s">
+      <c r="AF14" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="AG14" s="6" t="s">
+      <c r="AG14" s="7" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="15" spans="1:33">
-      <c r="A15" s="6">
+      <c r="A15" s="7">
         <v>54100001</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="7">
         <v>5410</v>
       </c>
-      <c r="C15" s="6">
-        <v>1</v>
-      </c>
-      <c r="D15" s="6">
-        <v>0</v>
-      </c>
-      <c r="E15" s="6">
+      <c r="C15" s="7">
+        <v>1</v>
+      </c>
+      <c r="D15" s="7">
+        <v>0</v>
+      </c>
+      <c r="E15" s="7">
         <v>3542000</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="G15" s="12" t="s">
+      <c r="G15" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="H15" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="I15" s="12" t="s">
+      <c r="I15" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="J15" s="6" t="s">
+      <c r="J15" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="7">
         <v>2</v>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="7">
         <v>500</v>
       </c>
-      <c r="M15" s="6" t="s">
+      <c r="M15" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="N15" s="6">
-        <v>1</v>
-      </c>
-      <c r="O15" s="6">
-        <v>0</v>
-      </c>
-      <c r="P15" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q15" s="6">
-        <v>1</v>
-      </c>
-      <c r="R15" s="6">
-        <v>0</v>
-      </c>
-      <c r="S15" s="6">
-        <v>0</v>
-      </c>
-      <c r="T15" s="6" t="s">
+      <c r="N15" s="7">
+        <v>1</v>
+      </c>
+      <c r="O15" s="7">
+        <v>0</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q15" s="7">
+        <v>1</v>
+      </c>
+      <c r="R15" s="7">
+        <v>0</v>
+      </c>
+      <c r="S15" s="7">
+        <v>0</v>
+      </c>
+      <c r="T15" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="U15" s="6">
+      <c r="U15" s="7">
         <v>4000</v>
       </c>
-      <c r="V15" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="W15" s="6">
+      <c r="V15" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="W15" s="7">
         <v>10000</v>
       </c>
-      <c r="X15" s="6" t="s">
+      <c r="X15" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="Y15" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="6">
+      <c r="Y15" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="7">
         <v>3</v>
       </c>
-      <c r="AA15" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB15" s="6">
-        <v>1</v>
-      </c>
-      <c r="AC15" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="6" t="s">
+      <c r="AA15" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB15" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC15" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="AE15" s="6" t="s">
+      <c r="AE15" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="AF15" s="6" t="s">
+      <c r="AF15" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="AG15" s="6" t="s">
+      <c r="AG15" s="7" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="16" spans="1:33">
-      <c r="A16" s="6">
+      <c r="A16" s="7">
         <v>54110001</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="7">
         <v>5411</v>
       </c>
-      <c r="C16" s="6">
-        <v>1</v>
-      </c>
-      <c r="D16" s="6">
-        <v>0</v>
-      </c>
-      <c r="E16" s="6">
+      <c r="C16" s="7">
+        <v>1</v>
+      </c>
+      <c r="D16" s="7">
+        <v>0</v>
+      </c>
+      <c r="E16" s="7">
         <v>3542200</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="I16" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="J16" s="6" t="s">
+      <c r="J16" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="7">
         <v>2</v>
       </c>
-      <c r="L16" s="6">
+      <c r="L16" s="7">
         <v>500</v>
       </c>
-      <c r="M16" s="6" t="s">
+      <c r="M16" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="N16" s="6">
-        <v>1</v>
-      </c>
-      <c r="O16" s="6">
-        <v>0</v>
-      </c>
-      <c r="P16" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q16" s="6">
-        <v>1</v>
-      </c>
-      <c r="R16" s="6">
-        <v>0</v>
-      </c>
-      <c r="S16" s="6">
-        <v>0</v>
-      </c>
-      <c r="T16" s="6" t="s">
+      <c r="N16" s="7">
+        <v>1</v>
+      </c>
+      <c r="O16" s="7">
+        <v>0</v>
+      </c>
+      <c r="P16" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q16" s="7">
+        <v>1</v>
+      </c>
+      <c r="R16" s="7">
+        <v>0</v>
+      </c>
+      <c r="S16" s="7">
+        <v>0</v>
+      </c>
+      <c r="T16" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="U16" s="6">
+      <c r="U16" s="7">
         <v>4000</v>
       </c>
-      <c r="V16" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="W16" s="6">
+      <c r="V16" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="W16" s="7">
         <v>10000</v>
       </c>
-      <c r="X16" s="6" t="s">
+      <c r="X16" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="Y16" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z16" s="6">
+      <c r="Y16" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="7">
         <v>3</v>
       </c>
-      <c r="AA16" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB16" s="6">
-        <v>1</v>
-      </c>
-      <c r="AC16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD16" s="6" t="s">
+      <c r="AA16" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB16" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC16" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="AE16" s="6" t="s">
+      <c r="AE16" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="AF16" s="6" t="s">
+      <c r="AF16" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="AG16" s="6" t="s">
+      <c r="AG16" s="7" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:33">
-      <c r="A17" s="6">
+      <c r="A17" s="7">
         <v>54120001</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="7">
         <v>5412</v>
       </c>
-      <c r="C17" s="6">
-        <v>1</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0</v>
-      </c>
-      <c r="E17" s="6">
+      <c r="C17" s="7">
+        <v>1</v>
+      </c>
+      <c r="D17" s="7">
+        <v>0</v>
+      </c>
+      <c r="E17" s="7">
         <v>3542400</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="G17" s="12" t="s">
+      <c r="G17" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="H17" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="I17" s="12" t="s">
+      <c r="I17" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="J17" s="6" t="s">
+      <c r="J17" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="K17" s="6">
+      <c r="K17" s="7">
         <v>2</v>
       </c>
-      <c r="L17" s="6">
+      <c r="L17" s="7">
         <v>500</v>
       </c>
-      <c r="M17" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="N17" s="6">
-        <v>1</v>
-      </c>
-      <c r="O17" s="6">
-        <v>0</v>
-      </c>
-      <c r="P17" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q17" s="6">
-        <v>1</v>
-      </c>
-      <c r="R17" s="6">
-        <v>0</v>
-      </c>
-      <c r="S17" s="6">
-        <v>0</v>
-      </c>
-      <c r="T17" s="6" t="s">
+      <c r="M17" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="N17" s="7">
+        <v>1</v>
+      </c>
+      <c r="O17" s="7">
+        <v>0</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q17" s="7">
+        <v>1</v>
+      </c>
+      <c r="R17" s="7">
+        <v>0</v>
+      </c>
+      <c r="S17" s="7">
+        <v>0</v>
+      </c>
+      <c r="T17" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="U17" s="6">
+      <c r="U17" s="7">
         <v>4000</v>
       </c>
-      <c r="V17" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="W17" s="6">
+      <c r="V17" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="W17" s="7">
         <v>10000</v>
       </c>
-      <c r="X17" s="6" t="s">
+      <c r="X17" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="Y17" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z17" s="6">
+      <c r="Y17" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="7">
         <v>3</v>
       </c>
-      <c r="AA17" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB17" s="6">
-        <v>1</v>
-      </c>
-      <c r="AC17" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="6" t="s">
+      <c r="AA17" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB17" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="AE17" s="6" t="s">
+      <c r="AE17" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="AF17" s="6" t="s">
+      <c r="AF17" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="AG17" s="6" t="s">
+      <c r="AG17" s="7" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="18" spans="1:33">
-      <c r="A18" s="6">
+      <c r="A18" s="7">
         <v>54130001</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="7">
         <v>5413</v>
       </c>
-      <c r="C18" s="6">
-        <v>1</v>
-      </c>
-      <c r="D18" s="6">
-        <v>0</v>
-      </c>
-      <c r="E18" s="6">
+      <c r="C18" s="7">
+        <v>1</v>
+      </c>
+      <c r="D18" s="7">
+        <v>0</v>
+      </c>
+      <c r="E18" s="7">
         <v>3542600</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="G18" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="H18" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="I18" s="12" t="s">
+      <c r="I18" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="J18" s="6" t="s">
+      <c r="J18" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="K18" s="6">
+      <c r="K18" s="7">
         <v>2</v>
       </c>
-      <c r="L18" s="6">
+      <c r="L18" s="7">
         <v>500</v>
       </c>
-      <c r="M18" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="N18" s="6">
-        <v>1</v>
-      </c>
-      <c r="O18" s="6">
-        <v>0</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q18" s="6">
-        <v>1</v>
-      </c>
-      <c r="R18" s="6">
-        <v>0</v>
-      </c>
-      <c r="S18" s="6">
-        <v>0</v>
-      </c>
-      <c r="T18" s="6" t="s">
+      <c r="M18" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="N18" s="7">
+        <v>1</v>
+      </c>
+      <c r="O18" s="7">
+        <v>0</v>
+      </c>
+      <c r="P18" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q18" s="7">
+        <v>1</v>
+      </c>
+      <c r="R18" s="7">
+        <v>0</v>
+      </c>
+      <c r="S18" s="7">
+        <v>0</v>
+      </c>
+      <c r="T18" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="U18" s="6">
+      <c r="U18" s="7">
         <v>4000</v>
       </c>
-      <c r="V18" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="W18" s="6">
+      <c r="V18" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="W18" s="7">
         <v>10000</v>
       </c>
-      <c r="X18" s="6" t="s">
+      <c r="X18" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="Y18" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="6">
+      <c r="Y18" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="7">
         <v>3</v>
       </c>
-      <c r="AA18" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB18" s="6">
-        <v>1</v>
-      </c>
-      <c r="AC18" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD18" s="6" t="s">
+      <c r="AA18" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB18" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="AE18" s="6" t="s">
+      <c r="AE18" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="AF18" s="6" t="s">
+      <c r="AF18" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="AG18" s="6" t="s">
+      <c r="AG18" s="7" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="19" spans="1:33">
-      <c r="A19" s="6">
+      <c r="A19" s="7">
         <v>54140001</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="7">
         <v>5414</v>
       </c>
-      <c r="C19" s="6">
-        <v>1</v>
-      </c>
-      <c r="D19" s="6">
-        <v>0</v>
-      </c>
-      <c r="E19" s="6">
+      <c r="C19" s="7">
+        <v>1</v>
+      </c>
+      <c r="D19" s="7">
+        <v>0</v>
+      </c>
+      <c r="E19" s="7">
         <v>3542800</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="G19" s="12" t="s">
+      <c r="G19" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="H19" s="12" t="s">
+      <c r="H19" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="I19" s="12" t="s">
+      <c r="I19" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="J19" s="6" t="s">
+      <c r="J19" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="K19" s="6">
+      <c r="K19" s="7">
         <v>2</v>
       </c>
-      <c r="L19" s="6">
+      <c r="L19" s="7">
         <v>5000</v>
       </c>
-      <c r="M19" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="N19" s="6">
-        <v>1</v>
-      </c>
-      <c r="O19" s="6">
-        <v>0</v>
-      </c>
-      <c r="P19" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q19" s="6">
-        <v>1</v>
-      </c>
-      <c r="R19" s="6">
-        <v>0</v>
-      </c>
-      <c r="S19" s="6">
-        <v>0</v>
-      </c>
-      <c r="T19" s="6" t="s">
+      <c r="M19" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="N19" s="7">
+        <v>1</v>
+      </c>
+      <c r="O19" s="7">
+        <v>0</v>
+      </c>
+      <c r="P19" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q19" s="7">
+        <v>1</v>
+      </c>
+      <c r="R19" s="7">
+        <v>0</v>
+      </c>
+      <c r="S19" s="7">
+        <v>0</v>
+      </c>
+      <c r="T19" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="U19" s="6">
+      <c r="U19" s="7">
         <v>-1</v>
       </c>
-      <c r="V19" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="W19" s="6">
+      <c r="V19" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="W19" s="7">
         <v>10000</v>
       </c>
-      <c r="X19" s="6" t="s">
+      <c r="X19" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="Y19" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z19" s="6">
+      <c r="Y19" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="7">
         <v>3</v>
       </c>
-      <c r="AA19" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB19" s="6">
-        <v>1</v>
-      </c>
-      <c r="AC19" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD19" s="6" t="s">
+      <c r="AA19" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB19" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="AE19" s="6" t="s">
+      <c r="AE19" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="AF19" s="6" t="s">
+      <c r="AF19" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="AG19" s="6" t="s">
+      <c r="AG19" s="7" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="20" spans="1:33">
-      <c r="A20" s="6">
+      <c r="A20" s="7">
         <v>54150001</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="7">
         <v>5415</v>
       </c>
-      <c r="C20" s="6">
-        <v>1</v>
-      </c>
-      <c r="D20" s="6">
-        <v>0</v>
-      </c>
-      <c r="E20" s="6">
+      <c r="C20" s="7">
+        <v>1</v>
+      </c>
+      <c r="D20" s="7">
+        <v>0</v>
+      </c>
+      <c r="E20" s="7">
         <v>3543000</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="G20" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="H20" s="12" t="s">
+      <c r="H20" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="I20" s="12" t="s">
+      <c r="I20" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="J20" s="6" t="s">
+      <c r="J20" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="K20" s="6">
+      <c r="K20" s="7">
         <v>2</v>
       </c>
-      <c r="L20" s="6">
+      <c r="L20" s="7">
         <v>3500</v>
       </c>
-      <c r="M20" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="N20" s="6">
-        <v>1</v>
-      </c>
-      <c r="O20" s="6">
-        <v>0</v>
-      </c>
-      <c r="P20" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q20" s="6">
-        <v>1</v>
-      </c>
-      <c r="R20" s="6">
-        <v>0</v>
-      </c>
-      <c r="S20" s="6">
-        <v>0</v>
-      </c>
-      <c r="T20" s="6" t="s">
+      <c r="M20" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="N20" s="7">
+        <v>1</v>
+      </c>
+      <c r="O20" s="7">
+        <v>0</v>
+      </c>
+      <c r="P20" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q20" s="7">
+        <v>1</v>
+      </c>
+      <c r="R20" s="7">
+        <v>0</v>
+      </c>
+      <c r="S20" s="7">
+        <v>0</v>
+      </c>
+      <c r="T20" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="U20" s="6">
+      <c r="U20" s="7">
         <v>-1</v>
       </c>
-      <c r="V20" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="W20" s="6">
+      <c r="V20" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="W20" s="7">
         <v>10000</v>
       </c>
-      <c r="X20" s="6" t="s">
+      <c r="X20" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="Y20" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="6">
-        <v>1</v>
-      </c>
-      <c r="AA20" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB20" s="6">
-        <v>1</v>
-      </c>
-      <c r="AC20" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="6" t="s">
+      <c r="Y20" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="7">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB20" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="AE20" s="6" t="s">
+      <c r="AE20" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="AF20" s="6" t="s">
+      <c r="AF20" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="AG20" s="6" t="s">
+      <c r="AG20" s="7" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="21" spans="1:33">
-      <c r="A21" s="7">
+      <c r="A21" s="9">
         <v>59130001</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="10">
         <v>5913</v>
       </c>
-      <c r="C21" s="8">
-        <v>1</v>
-      </c>
-      <c r="D21" s="8">
-        <v>0</v>
-      </c>
-      <c r="E21" s="8">
+      <c r="C21" s="10">
+        <v>1</v>
+      </c>
+      <c r="D21" s="10">
+        <v>0</v>
+      </c>
+      <c r="E21" s="10">
         <v>3591000</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="F21" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="G21" s="13" t="s">
+      <c r="G21" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="K21" s="8">
-        <v>1</v>
-      </c>
-      <c r="L21" s="8">
-        <v>0</v>
-      </c>
-      <c r="M21" s="8" t="s">
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="K21" s="10">
+        <v>1</v>
+      </c>
+      <c r="L21" s="10">
+        <v>0</v>
+      </c>
+      <c r="M21" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="N21" s="8">
-        <v>1</v>
-      </c>
-      <c r="O21" s="8">
-        <v>0</v>
-      </c>
-      <c r="P21" s="8" t="s">
+      <c r="N21" s="10">
+        <v>1</v>
+      </c>
+      <c r="O21" s="10">
+        <v>0</v>
+      </c>
+      <c r="P21" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="Q21" s="8">
+      <c r="Q21" s="10">
         <v>3</v>
       </c>
-      <c r="R21" s="8">
-        <v>0</v>
-      </c>
-      <c r="S21" s="8">
-        <v>0</v>
-      </c>
-      <c r="T21" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="U21" s="8">
+      <c r="R21" s="10">
+        <v>0</v>
+      </c>
+      <c r="S21" s="10">
+        <v>0</v>
+      </c>
+      <c r="T21" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="U21" s="10">
         <v>-1</v>
       </c>
-      <c r="V21" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="W21" s="8">
+      <c r="V21" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="W21" s="10">
         <v>10000</v>
       </c>
-      <c r="X21" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y21" s="8">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="8">
-        <v>1</v>
-      </c>
-      <c r="AA21" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB21" s="8">
-        <v>1</v>
-      </c>
-      <c r="AC21" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD21" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE21" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF21" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG21" s="6" t="s">
+      <c r="X21" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y21" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="10">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB21" s="10">
+        <v>1</v>
+      </c>
+      <c r="AC21" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE21" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF21" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG21" s="7" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:33">
-      <c r="A22" s="7">
+      <c r="A22" s="9">
         <v>59140001</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="10">
         <v>5914</v>
       </c>
-      <c r="C22" s="8">
-        <v>1</v>
-      </c>
-      <c r="D22" s="8">
-        <v>0</v>
-      </c>
-      <c r="E22" s="8">
+      <c r="C22" s="10">
+        <v>1</v>
+      </c>
+      <c r="D22" s="10">
+        <v>0</v>
+      </c>
+      <c r="E22" s="10">
         <v>3592400</v>
       </c>
-      <c r="F22" s="13" t="s">
+      <c r="F22" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="G22" s="13" t="s">
+      <c r="G22" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="8" t="s">
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="K22" s="8">
+      <c r="K22" s="10">
         <v>2</v>
       </c>
-      <c r="L22" s="8">
-        <v>0</v>
-      </c>
-      <c r="M22" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="N22" s="8">
-        <v>1</v>
-      </c>
-      <c r="O22" s="8">
-        <v>0</v>
-      </c>
-      <c r="P22" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q22" s="8">
-        <v>1</v>
-      </c>
-      <c r="R22" s="8">
-        <v>0</v>
-      </c>
-      <c r="S22" s="8">
-        <v>0</v>
-      </c>
-      <c r="T22" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="U22" s="8">
+      <c r="L22" s="10">
+        <v>0</v>
+      </c>
+      <c r="M22" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="N22" s="10">
+        <v>1</v>
+      </c>
+      <c r="O22" s="10">
+        <v>0</v>
+      </c>
+      <c r="P22" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q22" s="10">
+        <v>1</v>
+      </c>
+      <c r="R22" s="10">
+        <v>0</v>
+      </c>
+      <c r="S22" s="10">
+        <v>0</v>
+      </c>
+      <c r="T22" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="U22" s="10">
         <v>-1</v>
       </c>
-      <c r="V22" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="W22" s="8">
+      <c r="V22" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="W22" s="10">
         <v>10000</v>
       </c>
-      <c r="X22" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y22" s="8">
-        <v>1</v>
-      </c>
-      <c r="Z22" s="8">
-        <v>1</v>
-      </c>
-      <c r="AA22" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB22" s="8">
-        <v>1</v>
-      </c>
-      <c r="AC22" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE22" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF22" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG22" s="6" t="s">
+      <c r="X22" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y22" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="10">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB22" s="10">
+        <v>1</v>
+      </c>
+      <c r="AC22" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE22" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF22" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG22" s="7" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:33">
-      <c r="A23" s="9">
+      <c r="A23" s="12">
         <v>85001500</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="12">
         <v>5501</v>
       </c>
-      <c r="C23" s="10">
-        <v>1</v>
-      </c>
-      <c r="D23" s="10">
-        <v>0</v>
-      </c>
-      <c r="E23" s="9">
+      <c r="C23" s="13">
+        <v>1</v>
+      </c>
+      <c r="D23" s="13">
+        <v>0</v>
+      </c>
+      <c r="E23" s="12">
         <v>5001600</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="G23" s="13" t="s">
+      <c r="G23" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9" t="s">
+      <c r="H23" s="12"/>
+      <c r="I23" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="J23" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="K23" s="9">
-        <v>1</v>
-      </c>
-      <c r="L23" s="9">
-        <v>0</v>
-      </c>
-      <c r="M23" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="N23" s="9">
-        <v>1</v>
-      </c>
-      <c r="O23" s="9">
-        <v>0</v>
-      </c>
-      <c r="P23" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q23" s="9">
-        <v>1</v>
-      </c>
-      <c r="R23" s="9">
-        <v>0</v>
-      </c>
-      <c r="S23" s="10">
-        <v>0</v>
-      </c>
-      <c r="T23" s="9" t="s">
+      <c r="J23" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K23" s="12">
+        <v>1</v>
+      </c>
+      <c r="L23" s="12">
+        <v>0</v>
+      </c>
+      <c r="M23" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="N23" s="12">
+        <v>1</v>
+      </c>
+      <c r="O23" s="12">
+        <v>0</v>
+      </c>
+      <c r="P23" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q23" s="12">
+        <v>1</v>
+      </c>
+      <c r="R23" s="12">
+        <v>0</v>
+      </c>
+      <c r="S23" s="13">
+        <v>0</v>
+      </c>
+      <c r="T23" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="U23" s="9">
+      <c r="U23" s="12">
         <v>2000</v>
       </c>
-      <c r="V23" s="9" t="s">
+      <c r="V23" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="W23" s="9">
-        <v>0</v>
-      </c>
-      <c r="X23" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y23" s="9">
-        <v>1</v>
-      </c>
-      <c r="Z23" s="9">
-        <v>1</v>
-      </c>
-      <c r="AA23" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB23" s="9">
-        <v>1</v>
-      </c>
-      <c r="AC23" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD23" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE23" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF23" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG23" s="6" t="s">
+      <c r="W23" s="12">
+        <v>0</v>
+      </c>
+      <c r="X23" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y23" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB23" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE23" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF23" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG23" s="7" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:33">
-      <c r="A24" s="9">
+      <c r="A24" s="12">
         <v>85101100</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B24" s="12">
         <v>5601</v>
       </c>
-      <c r="C24" s="10">
-        <v>1</v>
-      </c>
-      <c r="D24" s="10">
-        <v>0</v>
-      </c>
-      <c r="E24" s="9">
+      <c r="C24" s="13">
+        <v>1</v>
+      </c>
+      <c r="D24" s="13">
+        <v>0</v>
+      </c>
+      <c r="E24" s="12">
         <v>5101200</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="G24" s="13" t="s">
+      <c r="G24" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="H24" s="9" t="s">
+      <c r="H24" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="I24" s="9" t="s">
+      <c r="I24" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="J24" s="9" t="s">
+      <c r="J24" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="K24" s="9">
+      <c r="K24" s="12">
         <v>2</v>
       </c>
-      <c r="L24" s="9">
-        <v>0</v>
-      </c>
-      <c r="M24" s="9" t="s">
+      <c r="L24" s="12">
+        <v>0</v>
+      </c>
+      <c r="M24" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="N24" s="9">
-        <v>1</v>
-      </c>
-      <c r="O24" s="9">
-        <v>0</v>
-      </c>
-      <c r="P24" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q24" s="9">
-        <v>1</v>
-      </c>
-      <c r="R24" s="9">
-        <v>0</v>
-      </c>
-      <c r="S24" s="10">
-        <v>0</v>
-      </c>
-      <c r="T24" s="9" t="s">
+      <c r="N24" s="12">
+        <v>1</v>
+      </c>
+      <c r="O24" s="12">
+        <v>0</v>
+      </c>
+      <c r="P24" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q24" s="12">
+        <v>1</v>
+      </c>
+      <c r="R24" s="12">
+        <v>0</v>
+      </c>
+      <c r="S24" s="13">
+        <v>0</v>
+      </c>
+      <c r="T24" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="U24" s="9">
-        <v>0</v>
-      </c>
-      <c r="V24" s="9" t="s">
+      <c r="U24" s="12">
+        <v>0</v>
+      </c>
+      <c r="V24" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="W24" s="9">
+      <c r="W24" s="12">
         <v>10000</v>
       </c>
-      <c r="X24" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y24" s="9">
-        <v>1</v>
-      </c>
-      <c r="Z24" s="9">
-        <v>1</v>
-      </c>
-      <c r="AA24" s="9" t="s">
+      <c r="X24" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y24" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA24" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="AB24" s="9">
-        <v>1</v>
-      </c>
-      <c r="AC24" s="9">
+      <c r="AB24" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC24" s="12">
         <v>1000</v>
       </c>
-      <c r="AD24" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE24" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF24" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG24" s="6" t="s">
+      <c r="AD24" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE24" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF24" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG24" s="7" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:33">
-      <c r="A25" s="9">
+      <c r="A25" s="12">
         <v>85200700</v>
       </c>
-      <c r="B25" s="9">
+      <c r="B25" s="12">
         <v>5701</v>
       </c>
-      <c r="C25" s="10">
-        <v>1</v>
-      </c>
-      <c r="D25" s="10">
-        <v>0</v>
-      </c>
-      <c r="E25" s="9">
+      <c r="C25" s="13">
+        <v>1</v>
+      </c>
+      <c r="D25" s="13">
+        <v>0</v>
+      </c>
+      <c r="E25" s="12">
         <v>5200800</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="G25" s="13" t="s">
+      <c r="G25" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9" t="s">
+      <c r="H25" s="12"/>
+      <c r="I25" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="J25" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="K25" s="9">
-        <v>1</v>
-      </c>
-      <c r="L25" s="9">
-        <v>0</v>
-      </c>
-      <c r="M25" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="N25" s="9">
-        <v>1</v>
-      </c>
-      <c r="O25" s="9">
-        <v>0</v>
-      </c>
-      <c r="P25" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q25" s="9">
-        <v>1</v>
-      </c>
-      <c r="R25" s="9">
-        <v>0</v>
-      </c>
-      <c r="S25" s="10">
-        <v>0</v>
-      </c>
-      <c r="T25" s="9" t="s">
+      <c r="J25" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K25" s="12">
+        <v>1</v>
+      </c>
+      <c r="L25" s="12">
+        <v>0</v>
+      </c>
+      <c r="M25" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="N25" s="12">
+        <v>1</v>
+      </c>
+      <c r="O25" s="12">
+        <v>0</v>
+      </c>
+      <c r="P25" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q25" s="12">
+        <v>1</v>
+      </c>
+      <c r="R25" s="12">
+        <v>0</v>
+      </c>
+      <c r="S25" s="13">
+        <v>0</v>
+      </c>
+      <c r="T25" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="U25" s="9">
-        <v>0</v>
-      </c>
-      <c r="V25" s="9" t="s">
+      <c r="U25" s="12">
+        <v>0</v>
+      </c>
+      <c r="V25" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="W25" s="9">
-        <v>0</v>
-      </c>
-      <c r="X25" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y25" s="9">
-        <v>1</v>
-      </c>
-      <c r="Z25" s="9">
-        <v>1</v>
-      </c>
-      <c r="AA25" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB25" s="9">
-        <v>1</v>
-      </c>
-      <c r="AC25" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD25" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE25" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF25" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG25" s="6" t="s">
+      <c r="W25" s="12">
+        <v>0</v>
+      </c>
+      <c r="X25" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y25" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z25" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA25" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB25" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC25" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE25" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF25" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG25" s="7" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:33">
-      <c r="A26" s="9">
+      <c r="A26" s="12">
         <v>820001</v>
       </c>
-      <c r="B26" s="9">
+      <c r="B26" s="12">
         <v>20001</v>
       </c>
-      <c r="C26" s="10">
-        <v>1</v>
-      </c>
-      <c r="D26" s="10">
-        <v>0</v>
-      </c>
-      <c r="E26" s="9">
+      <c r="C26" s="13">
+        <v>1</v>
+      </c>
+      <c r="D26" s="13">
+        <v>0</v>
+      </c>
+      <c r="E26" s="12">
         <v>820001</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="G26" s="13" t="s">
+      <c r="G26" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="H26" s="9" t="s">
+      <c r="H26" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="I26" s="9" t="s">
+      <c r="I26" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="J26" s="9" t="s">
+      <c r="J26" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="K26" s="9">
+      <c r="K26" s="12">
         <v>2</v>
       </c>
-      <c r="L26" s="9">
+      <c r="L26" s="12">
         <v>5000</v>
       </c>
-      <c r="M26" s="9" t="s">
+      <c r="M26" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="N26" s="9">
-        <v>1</v>
-      </c>
-      <c r="O26" s="9">
-        <v>0</v>
-      </c>
-      <c r="P26" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q26" s="9">
-        <v>1</v>
-      </c>
-      <c r="R26" s="9">
-        <v>0</v>
-      </c>
-      <c r="S26" s="10">
-        <v>0</v>
-      </c>
-      <c r="T26" s="9" t="s">
+      <c r="N26" s="12">
+        <v>1</v>
+      </c>
+      <c r="O26" s="12">
+        <v>0</v>
+      </c>
+      <c r="P26" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q26" s="12">
+        <v>1</v>
+      </c>
+      <c r="R26" s="12">
+        <v>0</v>
+      </c>
+      <c r="S26" s="13">
+        <v>0</v>
+      </c>
+      <c r="T26" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="U26" s="9">
+      <c r="U26" s="12">
         <v>1200</v>
       </c>
-      <c r="V26" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="W26" s="9">
+      <c r="V26" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="W26" s="12">
         <v>10000</v>
       </c>
-      <c r="X26" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y26" s="9">
-        <v>1</v>
-      </c>
-      <c r="Z26" s="9">
-        <v>1</v>
-      </c>
-      <c r="AA26" s="9" t="s">
+      <c r="X26" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y26" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA26" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="AB26" s="9">
-        <v>1</v>
-      </c>
-      <c r="AC26" s="9">
+      <c r="AB26" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC26" s="12">
         <v>1000</v>
       </c>
-      <c r="AD26" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE26" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF26" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG26" s="6" t="s">
+      <c r="AD26" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE26" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF26" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG26" s="7" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:33">
-      <c r="A27" s="9">
+      <c r="A27" s="12">
         <v>820011</v>
       </c>
-      <c r="B27" s="9">
+      <c r="B27" s="12">
         <v>20011</v>
       </c>
-      <c r="C27" s="10">
-        <v>1</v>
-      </c>
-      <c r="D27" s="10">
-        <v>0</v>
-      </c>
-      <c r="E27" s="9">
+      <c r="C27" s="13">
+        <v>1</v>
+      </c>
+      <c r="D27" s="13">
+        <v>0</v>
+      </c>
+      <c r="E27" s="12">
         <v>820011</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="G27" s="13" t="s">
+      <c r="G27" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9" t="s">
+      <c r="H27" s="12"/>
+      <c r="I27" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="J27" s="9" t="s">
+      <c r="J27" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="K27" s="9">
+      <c r="K27" s="12">
         <v>2</v>
       </c>
-      <c r="L27" s="9">
+      <c r="L27" s="12">
         <v>2500</v>
       </c>
-      <c r="M27" s="9" t="s">
+      <c r="M27" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="N27" s="9">
-        <v>1</v>
-      </c>
-      <c r="O27" s="9">
-        <v>0</v>
-      </c>
-      <c r="P27" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q27" s="9">
-        <v>1</v>
-      </c>
-      <c r="R27" s="9">
-        <v>0</v>
-      </c>
-      <c r="S27" s="10">
+      <c r="N27" s="12">
+        <v>1</v>
+      </c>
+      <c r="O27" s="12">
+        <v>0</v>
+      </c>
+      <c r="P27" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q27" s="12">
+        <v>1</v>
+      </c>
+      <c r="R27" s="12">
+        <v>0</v>
+      </c>
+      <c r="S27" s="13">
         <v>20012</v>
       </c>
-      <c r="T27" s="9" t="s">
+      <c r="T27" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="U27" s="9">
+      <c r="U27" s="12">
         <v>4000</v>
       </c>
-      <c r="V27" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="W27" s="9">
+      <c r="V27" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="W27" s="12">
         <v>10000</v>
       </c>
-      <c r="X27" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y27" s="9">
-        <v>1</v>
-      </c>
-      <c r="Z27" s="9">
-        <v>1</v>
-      </c>
-      <c r="AA27" s="9" t="s">
+      <c r="X27" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y27" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA27" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="AB27" s="9">
-        <v>1</v>
-      </c>
-      <c r="AC27" s="9">
+      <c r="AB27" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC27" s="12">
         <v>1000</v>
       </c>
-      <c r="AD27" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE27" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF27" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG27" s="6" t="s">
+      <c r="AD27" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE27" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF27" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG27" s="7" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:33">
-      <c r="A28" s="9">
+      <c r="A28" s="12">
         <v>820031</v>
       </c>
-      <c r="B28" s="9">
+      <c r="B28" s="12">
         <v>101</v>
       </c>
-      <c r="C28" s="10">
-        <v>1</v>
-      </c>
-      <c r="D28" s="10">
-        <v>0</v>
-      </c>
-      <c r="E28" s="9">
+      <c r="C28" s="13">
+        <v>1</v>
+      </c>
+      <c r="D28" s="13">
+        <v>0</v>
+      </c>
+      <c r="E28" s="12">
         <v>5200800</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F28" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="G28" s="13" t="s">
+      <c r="G28" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9" t="s">
+      <c r="H28" s="12"/>
+      <c r="I28" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="J28" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="K28" s="9">
-        <v>1</v>
-      </c>
-      <c r="L28" s="9">
-        <v>0</v>
-      </c>
-      <c r="M28" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="N28" s="9">
-        <v>1</v>
-      </c>
-      <c r="O28" s="9">
-        <v>0</v>
-      </c>
-      <c r="P28" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q28" s="9">
-        <v>1</v>
-      </c>
-      <c r="R28" s="9">
-        <v>0</v>
-      </c>
-      <c r="S28" s="10">
-        <v>0</v>
-      </c>
-      <c r="T28" s="9" t="s">
+      <c r="J28" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K28" s="12">
+        <v>1</v>
+      </c>
+      <c r="L28" s="12">
+        <v>0</v>
+      </c>
+      <c r="M28" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="N28" s="12">
+        <v>1</v>
+      </c>
+      <c r="O28" s="12">
+        <v>0</v>
+      </c>
+      <c r="P28" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q28" s="12">
+        <v>1</v>
+      </c>
+      <c r="R28" s="12">
+        <v>0</v>
+      </c>
+      <c r="S28" s="13">
+        <v>0</v>
+      </c>
+      <c r="T28" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="U28" s="9">
+      <c r="U28" s="12">
         <v>1000</v>
       </c>
-      <c r="V28" s="9" t="s">
+      <c r="V28" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="W28" s="9">
+      <c r="W28" s="12">
         <v>2000</v>
       </c>
-      <c r="X28" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y28" s="9">
-        <v>1</v>
-      </c>
-      <c r="Z28" s="9">
-        <v>1</v>
-      </c>
-      <c r="AA28" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB28" s="9">
-        <v>1</v>
-      </c>
-      <c r="AC28" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD28" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE28" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF28" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG28" s="6" t="s">
+      <c r="X28" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y28" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z28" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA28" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB28" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC28" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE28" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF28" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG28" s="7" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:33">
-      <c r="A29" s="9">
+      <c r="A29" s="12">
         <v>820034</v>
       </c>
-      <c r="B29" s="9">
+      <c r="B29" s="12">
         <v>20034</v>
       </c>
-      <c r="C29" s="10">
-        <v>1</v>
-      </c>
-      <c r="D29" s="10">
-        <v>0</v>
-      </c>
-      <c r="E29" s="9">
+      <c r="C29" s="13">
+        <v>1</v>
+      </c>
+      <c r="D29" s="13">
+        <v>0</v>
+      </c>
+      <c r="E29" s="12">
         <v>820034</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F29" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="G29" s="13" t="s">
+      <c r="G29" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9" t="s">
+      <c r="H29" s="12"/>
+      <c r="I29" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="J29" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="K29" s="9">
-        <v>1</v>
-      </c>
-      <c r="L29" s="9">
-        <v>0</v>
-      </c>
-      <c r="M29" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="N29" s="9">
-        <v>1</v>
-      </c>
-      <c r="O29" s="9">
-        <v>0</v>
-      </c>
-      <c r="P29" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q29" s="9">
-        <v>1</v>
-      </c>
-      <c r="R29" s="9">
-        <v>0</v>
-      </c>
-      <c r="S29" s="10">
+      <c r="J29" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K29" s="12">
+        <v>1</v>
+      </c>
+      <c r="L29" s="12">
+        <v>0</v>
+      </c>
+      <c r="M29" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="N29" s="12">
+        <v>1</v>
+      </c>
+      <c r="O29" s="12">
+        <v>0</v>
+      </c>
+      <c r="P29" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q29" s="12">
+        <v>1</v>
+      </c>
+      <c r="R29" s="12">
+        <v>0</v>
+      </c>
+      <c r="S29" s="13">
         <v>20031</v>
       </c>
-      <c r="T29" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="U29" s="9">
+      <c r="T29" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="U29" s="12">
         <v>-1</v>
       </c>
-      <c r="V29" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="W29" s="9">
+      <c r="V29" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="W29" s="12">
         <v>10000</v>
       </c>
-      <c r="X29" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y29" s="9">
-        <v>1</v>
-      </c>
-      <c r="Z29" s="9">
-        <v>1</v>
-      </c>
-      <c r="AA29" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB29" s="9">
-        <v>1</v>
-      </c>
-      <c r="AC29" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE29" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF29" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG29" s="6" t="s">
+      <c r="X29" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y29" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z29" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA29" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB29" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC29" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE29" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF29" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG29" s="7" t="s">
         <v>79</v>
       </c>
     </row>
@@ -5422,197 +5415,197 @@
       <c r="A30" s="4">
         <v>820051</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B30" s="12">
         <v>101</v>
       </c>
-      <c r="C30" s="10">
-        <v>1</v>
-      </c>
-      <c r="D30" s="10">
-        <v>0</v>
-      </c>
-      <c r="E30" s="9">
+      <c r="C30" s="13">
+        <v>1</v>
+      </c>
+      <c r="D30" s="13">
+        <v>0</v>
+      </c>
+      <c r="E30" s="12">
         <v>5200800</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="F30" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="G30" s="13" t="s">
+      <c r="G30" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9" t="s">
+      <c r="H30" s="12"/>
+      <c r="I30" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="J30" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="K30" s="9">
-        <v>1</v>
-      </c>
-      <c r="L30" s="9">
-        <v>0</v>
-      </c>
-      <c r="M30" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="N30" s="9">
-        <v>1</v>
-      </c>
-      <c r="O30" s="9">
-        <v>0</v>
-      </c>
-      <c r="P30" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q30" s="9">
-        <v>1</v>
-      </c>
-      <c r="R30" s="9">
-        <v>0</v>
-      </c>
-      <c r="S30" s="10">
-        <v>0</v>
-      </c>
-      <c r="T30" s="9" t="s">
+      <c r="J30" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K30" s="12">
+        <v>1</v>
+      </c>
+      <c r="L30" s="12">
+        <v>0</v>
+      </c>
+      <c r="M30" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="N30" s="12">
+        <v>1</v>
+      </c>
+      <c r="O30" s="12">
+        <v>0</v>
+      </c>
+      <c r="P30" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q30" s="12">
+        <v>1</v>
+      </c>
+      <c r="R30" s="12">
+        <v>0</v>
+      </c>
+      <c r="S30" s="13">
+        <v>0</v>
+      </c>
+      <c r="T30" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="U30" s="9">
+      <c r="U30" s="12">
         <v>1000</v>
       </c>
-      <c r="V30" s="9" t="s">
+      <c r="V30" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="W30" s="9">
-        <v>0</v>
-      </c>
-      <c r="X30" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y30" s="9">
-        <v>1</v>
-      </c>
-      <c r="Z30" s="9">
-        <v>1</v>
-      </c>
-      <c r="AA30" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB30" s="9">
-        <v>1</v>
-      </c>
-      <c r="AC30" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD30" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE30" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF30" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG30" s="6" t="s">
+      <c r="W30" s="12">
+        <v>0</v>
+      </c>
+      <c r="X30" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y30" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z30" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA30" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB30" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC30" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE30" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF30" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG30" s="7" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:33">
-      <c r="A31" s="9">
+      <c r="A31" s="12">
         <v>820054</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B31" s="12">
         <v>20054</v>
       </c>
-      <c r="C31" s="10">
-        <v>1</v>
-      </c>
-      <c r="D31" s="10">
-        <v>0</v>
-      </c>
-      <c r="E31" s="9">
+      <c r="C31" s="13">
+        <v>1</v>
+      </c>
+      <c r="D31" s="13">
+        <v>0</v>
+      </c>
+      <c r="E31" s="12">
         <v>820054</v>
       </c>
-      <c r="F31" s="9" t="s">
+      <c r="F31" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="G31" s="13" t="s">
+      <c r="G31" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9" t="s">
+      <c r="H31" s="12"/>
+      <c r="I31" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="J31" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="K31" s="9">
-        <v>1</v>
-      </c>
-      <c r="L31" s="9">
-        <v>0</v>
-      </c>
-      <c r="M31" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="N31" s="9">
-        <v>1</v>
-      </c>
-      <c r="O31" s="9">
-        <v>0</v>
-      </c>
-      <c r="P31" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q31" s="9">
-        <v>1</v>
-      </c>
-      <c r="R31" s="9">
-        <v>0</v>
-      </c>
-      <c r="S31" s="10">
+      <c r="J31" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K31" s="12">
+        <v>1</v>
+      </c>
+      <c r="L31" s="12">
+        <v>0</v>
+      </c>
+      <c r="M31" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="N31" s="12">
+        <v>1</v>
+      </c>
+      <c r="O31" s="12">
+        <v>0</v>
+      </c>
+      <c r="P31" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q31" s="12">
+        <v>1</v>
+      </c>
+      <c r="R31" s="12">
+        <v>0</v>
+      </c>
+      <c r="S31" s="13">
         <v>20053</v>
       </c>
-      <c r="T31" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="U31" s="9">
+      <c r="T31" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="U31" s="12">
         <v>-1</v>
       </c>
-      <c r="V31" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="W31" s="9">
+      <c r="V31" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="W31" s="12">
         <v>10000</v>
       </c>
-      <c r="X31" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y31" s="9">
-        <v>1</v>
-      </c>
-      <c r="Z31" s="9">
-        <v>1</v>
-      </c>
-      <c r="AA31" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB31" s="9">
-        <v>1</v>
-      </c>
-      <c r="AC31" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD31" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE31" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF31" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG31" s="6" t="s">
+      <c r="X31" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y31" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z31" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA31" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB31" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC31" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE31" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF31" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG31" s="7" t="s">
         <v>79</v>
       </c>
     </row>
@@ -5620,98 +5613,98 @@
       <c r="A32" s="4">
         <v>820061</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32" s="12">
         <v>102</v>
       </c>
-      <c r="C32" s="10">
-        <v>1</v>
-      </c>
-      <c r="D32" s="10">
-        <v>0</v>
-      </c>
-      <c r="E32" s="9">
+      <c r="C32" s="13">
+        <v>1</v>
+      </c>
+      <c r="D32" s="13">
+        <v>0</v>
+      </c>
+      <c r="E32" s="12">
         <v>5001800</v>
       </c>
-      <c r="F32" s="9" t="s">
+      <c r="F32" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="G32" s="13" t="s">
+      <c r="G32" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9" t="s">
+      <c r="H32" s="12"/>
+      <c r="I32" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="J32" s="9" t="s">
+      <c r="J32" s="12" t="s">
         <v>261</v>
       </c>
-      <c r="K32" s="9">
+      <c r="K32" s="12">
         <v>2</v>
       </c>
-      <c r="L32" s="9">
+      <c r="L32" s="12">
         <v>2000</v>
       </c>
-      <c r="M32" s="9" t="s">
+      <c r="M32" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="N32" s="9">
+      <c r="N32" s="12">
         <v>2</v>
       </c>
-      <c r="O32" s="9">
+      <c r="O32" s="12">
         <v>2000</v>
       </c>
-      <c r="P32" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q32" s="9">
-        <v>1</v>
-      </c>
-      <c r="R32" s="9">
-        <v>0</v>
-      </c>
-      <c r="S32" s="10">
-        <v>0</v>
-      </c>
-      <c r="T32" s="9" t="s">
+      <c r="P32" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q32" s="12">
+        <v>1</v>
+      </c>
+      <c r="R32" s="12">
+        <v>0</v>
+      </c>
+      <c r="S32" s="13">
+        <v>0</v>
+      </c>
+      <c r="T32" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="U32" s="9">
+      <c r="U32" s="12">
         <v>3000</v>
       </c>
-      <c r="V32" s="9" t="s">
+      <c r="V32" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="W32" s="9">
+      <c r="W32" s="12">
         <v>2000</v>
       </c>
-      <c r="X32" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y32" s="9">
-        <v>1</v>
-      </c>
-      <c r="Z32" s="9">
-        <v>1</v>
-      </c>
-      <c r="AA32" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB32" s="9">
-        <v>1</v>
-      </c>
-      <c r="AC32" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE32" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF32" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG32" s="6" t="s">
+      <c r="X32" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y32" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z32" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA32" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB32" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC32" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE32" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF32" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG32" s="7" t="s">
         <v>79</v>
       </c>
     </row>
@@ -5719,296 +5712,296 @@
       <c r="A33" s="4">
         <v>821061</v>
       </c>
-      <c r="B33" s="9">
+      <c r="B33" s="12">
         <v>105</v>
       </c>
-      <c r="C33" s="10">
-        <v>1</v>
-      </c>
-      <c r="D33" s="10">
-        <v>0</v>
-      </c>
-      <c r="E33" s="9">
+      <c r="C33" s="13">
+        <v>1</v>
+      </c>
+      <c r="D33" s="13">
+        <v>0</v>
+      </c>
+      <c r="E33" s="12">
         <v>5001600</v>
       </c>
-      <c r="F33" s="9" t="s">
+      <c r="F33" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="G33" s="13" t="s">
+      <c r="G33" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9" t="s">
+      <c r="H33" s="12"/>
+      <c r="I33" s="12" t="s">
         <v>266</v>
       </c>
-      <c r="J33" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="K33" s="9">
-        <v>1</v>
-      </c>
-      <c r="L33" s="9">
-        <v>0</v>
-      </c>
-      <c r="M33" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="N33" s="9">
-        <v>1</v>
-      </c>
-      <c r="O33" s="9">
-        <v>0</v>
-      </c>
-      <c r="P33" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q33" s="9">
-        <v>1</v>
-      </c>
-      <c r="R33" s="9">
-        <v>0</v>
-      </c>
-      <c r="S33" s="10">
-        <v>0</v>
-      </c>
-      <c r="T33" s="9" t="s">
+      <c r="J33" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K33" s="12">
+        <v>1</v>
+      </c>
+      <c r="L33" s="12">
+        <v>0</v>
+      </c>
+      <c r="M33" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="N33" s="12">
+        <v>1</v>
+      </c>
+      <c r="O33" s="12">
+        <v>0</v>
+      </c>
+      <c r="P33" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q33" s="12">
+        <v>1</v>
+      </c>
+      <c r="R33" s="12">
+        <v>0</v>
+      </c>
+      <c r="S33" s="13">
+        <v>0</v>
+      </c>
+      <c r="T33" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="U33" s="9">
+      <c r="U33" s="12">
         <v>2000</v>
       </c>
-      <c r="V33" s="9" t="s">
+      <c r="V33" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="W33" s="9">
-        <v>0</v>
-      </c>
-      <c r="X33" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y33" s="9">
-        <v>1</v>
-      </c>
-      <c r="Z33" s="9">
-        <v>1</v>
-      </c>
-      <c r="AA33" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB33" s="9">
-        <v>1</v>
-      </c>
-      <c r="AC33" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD33" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE33" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF33" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG33" s="6" t="s">
+      <c r="W33" s="12">
+        <v>0</v>
+      </c>
+      <c r="X33" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y33" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z33" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA33" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB33" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC33" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE33" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF33" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG33" s="7" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:33">
-      <c r="A34" s="9">
+      <c r="A34" s="12">
         <v>820072</v>
       </c>
-      <c r="B34" s="9">
+      <c r="B34" s="12">
         <v>20072</v>
       </c>
-      <c r="C34" s="10">
-        <v>1</v>
-      </c>
-      <c r="D34" s="10">
-        <v>0</v>
-      </c>
-      <c r="E34" s="9">
+      <c r="C34" s="13">
+        <v>1</v>
+      </c>
+      <c r="D34" s="13">
+        <v>0</v>
+      </c>
+      <c r="E34" s="12">
         <v>820072</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="G34" s="13" t="s">
+      <c r="G34" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9" t="s">
+      <c r="H34" s="12"/>
+      <c r="I34" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="J34" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="K34" s="9">
-        <v>1</v>
-      </c>
-      <c r="L34" s="9">
-        <v>0</v>
-      </c>
-      <c r="M34" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="N34" s="9">
-        <v>1</v>
-      </c>
-      <c r="O34" s="9">
-        <v>0</v>
-      </c>
-      <c r="P34" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q34" s="9">
-        <v>1</v>
-      </c>
-      <c r="R34" s="9">
-        <v>0</v>
-      </c>
-      <c r="S34" s="10">
+      <c r="J34" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K34" s="12">
+        <v>1</v>
+      </c>
+      <c r="L34" s="12">
+        <v>0</v>
+      </c>
+      <c r="M34" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="N34" s="12">
+        <v>1</v>
+      </c>
+      <c r="O34" s="12">
+        <v>0</v>
+      </c>
+      <c r="P34" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q34" s="12">
+        <v>1</v>
+      </c>
+      <c r="R34" s="12">
+        <v>0</v>
+      </c>
+      <c r="S34" s="13">
         <v>20071</v>
       </c>
-      <c r="T34" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="U34" s="9">
+      <c r="T34" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="U34" s="12">
         <v>-1</v>
       </c>
-      <c r="V34" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="W34" s="9">
+      <c r="V34" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="W34" s="12">
         <v>10000</v>
       </c>
-      <c r="X34" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y34" s="9">
-        <v>1</v>
-      </c>
-      <c r="Z34" s="9">
-        <v>1</v>
-      </c>
-      <c r="AA34" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB34" s="9">
-        <v>1</v>
-      </c>
-      <c r="AC34" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD34" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE34" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF34" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG34" s="6" t="s">
+      <c r="X34" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y34" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z34" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA34" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB34" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC34" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE34" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF34" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG34" s="7" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:33">
-      <c r="A35" s="9">
+      <c r="A35" s="12">
         <v>820073</v>
       </c>
-      <c r="B35" s="9">
+      <c r="B35" s="12">
         <v>20073</v>
       </c>
-      <c r="C35" s="10">
-        <v>1</v>
-      </c>
-      <c r="D35" s="10">
-        <v>0</v>
-      </c>
-      <c r="E35" s="9">
+      <c r="C35" s="13">
+        <v>1</v>
+      </c>
+      <c r="D35" s="13">
+        <v>0</v>
+      </c>
+      <c r="E35" s="12">
         <v>820073</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="F35" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="G35" s="13" t="s">
+      <c r="G35" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9" t="s">
+      <c r="H35" s="12"/>
+      <c r="I35" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="J35" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="K35" s="9">
-        <v>1</v>
-      </c>
-      <c r="L35" s="9">
-        <v>0</v>
-      </c>
-      <c r="M35" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="N35" s="9">
-        <v>1</v>
-      </c>
-      <c r="O35" s="9">
-        <v>0</v>
-      </c>
-      <c r="P35" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q35" s="9">
-        <v>1</v>
-      </c>
-      <c r="R35" s="9">
-        <v>0</v>
-      </c>
-      <c r="S35" s="10">
+      <c r="J35" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K35" s="12">
+        <v>1</v>
+      </c>
+      <c r="L35" s="12">
+        <v>0</v>
+      </c>
+      <c r="M35" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="N35" s="12">
+        <v>1</v>
+      </c>
+      <c r="O35" s="12">
+        <v>0</v>
+      </c>
+      <c r="P35" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q35" s="12">
+        <v>1</v>
+      </c>
+      <c r="R35" s="12">
+        <v>0</v>
+      </c>
+      <c r="S35" s="13">
         <v>20074</v>
       </c>
-      <c r="T35" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="U35" s="9">
+      <c r="T35" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="U35" s="12">
         <v>-1</v>
       </c>
-      <c r="V35" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="W35" s="9">
+      <c r="V35" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="W35" s="12">
         <v>10000</v>
       </c>
-      <c r="X35" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y35" s="9">
-        <v>1</v>
-      </c>
-      <c r="Z35" s="9">
-        <v>1</v>
-      </c>
-      <c r="AA35" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB35" s="9">
-        <v>1</v>
-      </c>
-      <c r="AC35" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD35" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE35" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF35" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG35" s="6" t="s">
+      <c r="X35" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y35" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z35" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA35" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB35" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC35" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE35" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF35" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG35" s="7" t="s">
         <v>79</v>
       </c>
     </row>
@@ -6016,98 +6009,98 @@
       <c r="A36" s="4">
         <v>820080</v>
       </c>
-      <c r="B36" s="9">
+      <c r="B36" s="12">
         <v>102</v>
       </c>
-      <c r="C36" s="10">
-        <v>1</v>
-      </c>
-      <c r="D36" s="10">
-        <v>0</v>
-      </c>
-      <c r="E36" s="9">
+      <c r="C36" s="13">
+        <v>1</v>
+      </c>
+      <c r="D36" s="13">
+        <v>0</v>
+      </c>
+      <c r="E36" s="12">
         <v>5001800</v>
       </c>
-      <c r="F36" s="9" t="s">
+      <c r="F36" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="G36" s="13" t="s">
+      <c r="G36" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9" t="s">
+      <c r="H36" s="12"/>
+      <c r="I36" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="J36" s="9" t="s">
+      <c r="J36" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="K36" s="9">
+      <c r="K36" s="12">
         <v>2</v>
       </c>
-      <c r="L36" s="9">
-        <v>10000</v>
-      </c>
-      <c r="M36" s="9" t="s">
+      <c r="L36" s="12">
+        <v>2000</v>
+      </c>
+      <c r="M36" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="N36" s="9">
+      <c r="N36" s="12">
         <v>2</v>
       </c>
-      <c r="O36" s="9">
-        <v>10000</v>
-      </c>
-      <c r="P36" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q36" s="9">
-        <v>1</v>
-      </c>
-      <c r="R36" s="9">
-        <v>0</v>
-      </c>
-      <c r="S36" s="10">
-        <v>0</v>
-      </c>
-      <c r="T36" s="9" t="s">
+      <c r="O36" s="12">
+        <v>2000</v>
+      </c>
+      <c r="P36" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q36" s="12">
+        <v>1</v>
+      </c>
+      <c r="R36" s="12">
+        <v>0</v>
+      </c>
+      <c r="S36" s="13">
+        <v>0</v>
+      </c>
+      <c r="T36" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="U36" s="9">
+      <c r="U36" s="12">
         <v>3000</v>
       </c>
-      <c r="V36" s="9" t="s">
+      <c r="V36" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="W36" s="9">
-        <v>0</v>
-      </c>
-      <c r="X36" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y36" s="9">
-        <v>1</v>
-      </c>
-      <c r="Z36" s="9">
-        <v>1</v>
-      </c>
-      <c r="AA36" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB36" s="9">
-        <v>1</v>
-      </c>
-      <c r="AC36" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD36" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE36" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF36" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG36" s="6" t="s">
+      <c r="W36" s="12">
+        <v>0</v>
+      </c>
+      <c r="X36" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y36" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA36" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB36" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC36" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE36" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF36" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG36" s="7" t="s">
         <v>79</v>
       </c>
     </row>
@@ -6115,296 +6108,296 @@
       <c r="A37" s="4">
         <v>820081</v>
       </c>
-      <c r="B37" s="9">
+      <c r="B37" s="12">
         <v>105</v>
       </c>
-      <c r="C37" s="10">
-        <v>1</v>
-      </c>
-      <c r="D37" s="10">
-        <v>0</v>
-      </c>
-      <c r="E37" s="9">
+      <c r="C37" s="13">
+        <v>1</v>
+      </c>
+      <c r="D37" s="13">
+        <v>0</v>
+      </c>
+      <c r="E37" s="12">
         <v>5001600</v>
       </c>
-      <c r="F37" s="9" t="s">
+      <c r="F37" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="G37" s="13" t="s">
+      <c r="G37" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9" t="s">
+      <c r="H37" s="12"/>
+      <c r="I37" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="J37" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="K37" s="9">
-        <v>1</v>
-      </c>
-      <c r="L37" s="9">
-        <v>0</v>
-      </c>
-      <c r="M37" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="N37" s="9">
-        <v>1</v>
-      </c>
-      <c r="O37" s="9">
-        <v>0</v>
-      </c>
-      <c r="P37" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q37" s="9">
-        <v>1</v>
-      </c>
-      <c r="R37" s="9">
-        <v>0</v>
-      </c>
-      <c r="S37" s="10">
-        <v>0</v>
-      </c>
-      <c r="T37" s="9" t="s">
+      <c r="J37" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K37" s="12">
+        <v>1</v>
+      </c>
+      <c r="L37" s="12">
+        <v>0</v>
+      </c>
+      <c r="M37" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="N37" s="12">
+        <v>1</v>
+      </c>
+      <c r="O37" s="12">
+        <v>0</v>
+      </c>
+      <c r="P37" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q37" s="12">
+        <v>1</v>
+      </c>
+      <c r="R37" s="12">
+        <v>0</v>
+      </c>
+      <c r="S37" s="13">
+        <v>0</v>
+      </c>
+      <c r="T37" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="U37" s="9">
+      <c r="U37" s="12">
         <v>1000</v>
       </c>
-      <c r="V37" s="9" t="s">
+      <c r="V37" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="W37" s="9">
-        <v>0</v>
-      </c>
-      <c r="X37" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y37" s="9">
-        <v>1</v>
-      </c>
-      <c r="Z37" s="9">
-        <v>1</v>
-      </c>
-      <c r="AA37" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB37" s="9">
-        <v>1</v>
-      </c>
-      <c r="AC37" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD37" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE37" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF37" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG37" s="6" t="s">
+      <c r="W37" s="12">
+        <v>0</v>
+      </c>
+      <c r="X37" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y37" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z37" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA37" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB37" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC37" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE37" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF37" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG37" s="7" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="38" spans="1:33">
-      <c r="A38" s="9">
+      <c r="A38" s="12">
         <v>820082</v>
       </c>
-      <c r="B38" s="9">
+      <c r="B38" s="12">
         <v>20082</v>
       </c>
-      <c r="C38" s="10">
-        <v>1</v>
-      </c>
-      <c r="D38" s="10">
-        <v>0</v>
-      </c>
-      <c r="E38" s="9">
+      <c r="C38" s="13">
+        <v>1</v>
+      </c>
+      <c r="D38" s="13">
+        <v>0</v>
+      </c>
+      <c r="E38" s="12">
         <v>820082</v>
       </c>
-      <c r="F38" s="9" t="s">
+      <c r="F38" s="12" t="s">
         <v>281</v>
       </c>
-      <c r="G38" s="13" t="s">
+      <c r="G38" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9" t="s">
+      <c r="H38" s="12"/>
+      <c r="I38" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="J38" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="K38" s="9">
-        <v>1</v>
-      </c>
-      <c r="L38" s="9">
-        <v>0</v>
-      </c>
-      <c r="M38" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="N38" s="9">
-        <v>1</v>
-      </c>
-      <c r="O38" s="9">
-        <v>0</v>
-      </c>
-      <c r="P38" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q38" s="9">
-        <v>1</v>
-      </c>
-      <c r="R38" s="9">
-        <v>0</v>
-      </c>
-      <c r="S38" s="10">
-        <v>0</v>
-      </c>
-      <c r="T38" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="U38" s="9">
+      <c r="J38" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K38" s="12">
+        <v>1</v>
+      </c>
+      <c r="L38" s="12">
+        <v>0</v>
+      </c>
+      <c r="M38" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="N38" s="12">
+        <v>1</v>
+      </c>
+      <c r="O38" s="12">
+        <v>0</v>
+      </c>
+      <c r="P38" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q38" s="12">
+        <v>1</v>
+      </c>
+      <c r="R38" s="12">
+        <v>0</v>
+      </c>
+      <c r="S38" s="13">
+        <v>0</v>
+      </c>
+      <c r="T38" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="U38" s="12">
         <v>-1</v>
       </c>
-      <c r="V38" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="W38" s="9">
+      <c r="V38" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="W38" s="12">
         <v>10000</v>
       </c>
-      <c r="X38" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y38" s="9">
-        <v>1</v>
-      </c>
-      <c r="Z38" s="9">
-        <v>1</v>
-      </c>
-      <c r="AA38" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB38" s="9">
-        <v>1</v>
-      </c>
-      <c r="AC38" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD38" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE38" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF38" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG38" s="6" t="s">
+      <c r="X38" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y38" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z38" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA38" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB38" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC38" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE38" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF38" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG38" s="7" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:33">
-      <c r="A39" s="9">
+      <c r="A39" s="12">
         <v>820083</v>
       </c>
-      <c r="B39" s="9">
+      <c r="B39" s="12">
         <v>20083</v>
       </c>
-      <c r="C39" s="10">
-        <v>1</v>
-      </c>
-      <c r="D39" s="10">
-        <v>0</v>
-      </c>
-      <c r="E39" s="9">
+      <c r="C39" s="13">
+        <v>1</v>
+      </c>
+      <c r="D39" s="13">
+        <v>0</v>
+      </c>
+      <c r="E39" s="12">
         <v>820083</v>
       </c>
-      <c r="F39" s="9" t="s">
+      <c r="F39" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="G39" s="13" t="s">
+      <c r="G39" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="H39" s="9"/>
-      <c r="I39" s="9" t="s">
+      <c r="H39" s="12"/>
+      <c r="I39" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="J39" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="K39" s="9">
-        <v>1</v>
-      </c>
-      <c r="L39" s="9">
-        <v>0</v>
-      </c>
-      <c r="M39" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="N39" s="9">
-        <v>1</v>
-      </c>
-      <c r="O39" s="9">
-        <v>0</v>
-      </c>
-      <c r="P39" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q39" s="9">
-        <v>1</v>
-      </c>
-      <c r="R39" s="9">
-        <v>0</v>
-      </c>
-      <c r="S39" s="10">
+      <c r="J39" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K39" s="12">
+        <v>1</v>
+      </c>
+      <c r="L39" s="12">
+        <v>0</v>
+      </c>
+      <c r="M39" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="N39" s="12">
+        <v>1</v>
+      </c>
+      <c r="O39" s="12">
+        <v>0</v>
+      </c>
+      <c r="P39" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q39" s="12">
+        <v>1</v>
+      </c>
+      <c r="R39" s="12">
+        <v>0</v>
+      </c>
+      <c r="S39" s="13">
         <v>20083</v>
       </c>
-      <c r="T39" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="U39" s="9">
+      <c r="T39" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="U39" s="12">
         <v>-1</v>
       </c>
-      <c r="V39" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="W39" s="9">
+      <c r="V39" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="W39" s="12">
         <v>10000</v>
       </c>
-      <c r="X39" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y39" s="9">
-        <v>1</v>
-      </c>
-      <c r="Z39" s="9">
-        <v>1</v>
-      </c>
-      <c r="AA39" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB39" s="9">
-        <v>1</v>
-      </c>
-      <c r="AC39" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD39" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE39" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF39" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG39" s="6" t="s">
+      <c r="X39" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y39" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z39" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA39" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB39" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC39" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE39" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF39" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG39" s="7" t="s">
         <v>79</v>
       </c>
     </row>
@@ -6412,197 +6405,197 @@
       <c r="A40" s="4">
         <v>820085</v>
       </c>
-      <c r="B40" s="9">
+      <c r="B40" s="12">
         <v>105</v>
       </c>
-      <c r="C40" s="10">
-        <v>1</v>
-      </c>
-      <c r="D40" s="10">
-        <v>0</v>
-      </c>
-      <c r="E40" s="9">
+      <c r="C40" s="13">
+        <v>1</v>
+      </c>
+      <c r="D40" s="13">
+        <v>0</v>
+      </c>
+      <c r="E40" s="12">
         <v>5001600</v>
       </c>
-      <c r="F40" s="9" t="s">
+      <c r="F40" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="G40" s="13" t="s">
+      <c r="G40" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="H40" s="9"/>
-      <c r="I40" s="9" t="s">
+      <c r="H40" s="12"/>
+      <c r="I40" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="J40" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="K40" s="9">
-        <v>1</v>
-      </c>
-      <c r="L40" s="9">
-        <v>0</v>
-      </c>
-      <c r="M40" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="N40" s="9">
-        <v>1</v>
-      </c>
-      <c r="O40" s="9">
-        <v>0</v>
-      </c>
-      <c r="P40" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q40" s="9">
-        <v>1</v>
-      </c>
-      <c r="R40" s="9">
-        <v>0</v>
-      </c>
-      <c r="S40" s="10">
-        <v>0</v>
-      </c>
-      <c r="T40" s="9" t="s">
+      <c r="J40" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K40" s="12">
+        <v>1</v>
+      </c>
+      <c r="L40" s="12">
+        <v>0</v>
+      </c>
+      <c r="M40" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="N40" s="12">
+        <v>1</v>
+      </c>
+      <c r="O40" s="12">
+        <v>0</v>
+      </c>
+      <c r="P40" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q40" s="12">
+        <v>1</v>
+      </c>
+      <c r="R40" s="12">
+        <v>0</v>
+      </c>
+      <c r="S40" s="13">
+        <v>0</v>
+      </c>
+      <c r="T40" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="U40" s="9">
+      <c r="U40" s="12">
         <v>1000</v>
       </c>
-      <c r="V40" s="9" t="s">
+      <c r="V40" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="W40" s="9">
+      <c r="W40" s="12">
         <v>10000</v>
       </c>
-      <c r="X40" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y40" s="9">
-        <v>1</v>
-      </c>
-      <c r="Z40" s="9">
-        <v>1</v>
-      </c>
-      <c r="AA40" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB40" s="9">
-        <v>1</v>
-      </c>
-      <c r="AC40" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD40" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE40" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF40" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG40" s="6" t="s">
+      <c r="X40" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y40" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z40" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA40" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB40" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC40" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE40" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF40" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG40" s="7" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:33">
-      <c r="A41" s="9">
+      <c r="A41" s="12">
         <v>820086</v>
       </c>
-      <c r="B41" s="9">
+      <c r="B41" s="12">
         <v>20086</v>
       </c>
-      <c r="C41" s="10">
-        <v>1</v>
-      </c>
-      <c r="D41" s="10">
-        <v>0</v>
-      </c>
-      <c r="E41" s="9">
+      <c r="C41" s="13">
+        <v>1</v>
+      </c>
+      <c r="D41" s="13">
+        <v>0</v>
+      </c>
+      <c r="E41" s="12">
         <v>820086</v>
       </c>
-      <c r="F41" s="9" t="s">
+      <c r="F41" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="G41" s="13" t="s">
+      <c r="G41" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9" t="s">
+      <c r="H41" s="12"/>
+      <c r="I41" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="J41" s="14" t="s">
+      <c r="J41" s="16" t="s">
         <v>291</v>
       </c>
-      <c r="K41" s="9">
+      <c r="K41" s="12">
         <v>2</v>
       </c>
-      <c r="L41" s="9">
+      <c r="L41" s="12">
         <v>5000</v>
       </c>
-      <c r="M41" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="N41" s="9">
-        <v>1</v>
-      </c>
-      <c r="O41" s="9">
-        <v>0</v>
-      </c>
-      <c r="P41" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q41" s="9">
-        <v>1</v>
-      </c>
-      <c r="R41" s="9">
-        <v>0</v>
-      </c>
-      <c r="S41" s="10">
+      <c r="M41" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="N41" s="12">
+        <v>1</v>
+      </c>
+      <c r="O41" s="12">
+        <v>0</v>
+      </c>
+      <c r="P41" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q41" s="12">
+        <v>1</v>
+      </c>
+      <c r="R41" s="12">
+        <v>0</v>
+      </c>
+      <c r="S41" s="13">
         <v>20085</v>
       </c>
-      <c r="T41" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="U41" s="9">
+      <c r="T41" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="U41" s="12">
         <v>-1</v>
       </c>
-      <c r="V41" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="W41" s="9">
+      <c r="V41" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="W41" s="12">
         <v>10000</v>
       </c>
-      <c r="X41" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y41" s="9">
-        <v>1</v>
-      </c>
-      <c r="Z41" s="9">
-        <v>1</v>
-      </c>
-      <c r="AA41" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB41" s="9">
-        <v>1</v>
-      </c>
-      <c r="AC41" s="9">
-        <v>0</v>
-      </c>
-      <c r="AD41" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE41" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF41" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG41" s="6" t="s">
+      <c r="X41" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y41" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z41" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA41" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB41" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC41" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE41" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF41" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG41" s="7" t="s">
         <v>79</v>
       </c>
     </row>
@@ -6617,7 +6610,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="E7:S71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
     <col min="5" max="5" width="27.25" style="1" customWidth="1"/>
@@ -7642,7 +7635,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="D6:F43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="11.25" style="1" customWidth="1"/>
@@ -7777,7 +7770,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="33" spans="4:6">
+    <row r="33" ht="14.25" spans="4:6">
       <c r="D33" s="1" t="s">
         <v>451</v>
       </c>
@@ -7786,34 +7779,34 @@
       </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="6:6">
+    <row r="34" ht="14.25" spans="6:6">
       <c r="F34"/>
     </row>
-    <row r="35" spans="6:6">
+    <row r="35" ht="14.25" spans="6:6">
       <c r="F35"/>
     </row>
-    <row r="36" spans="6:6">
+    <row r="36" ht="14.25" spans="6:6">
       <c r="F36"/>
     </row>
-    <row r="37" spans="6:6">
+    <row r="37" ht="14.25" spans="6:6">
       <c r="F37"/>
     </row>
-    <row r="38" spans="6:6">
+    <row r="38" ht="14.25" spans="6:6">
       <c r="F38"/>
     </row>
-    <row r="39" spans="6:6">
+    <row r="39" ht="14.25" spans="6:6">
       <c r="F39"/>
     </row>
-    <row r="40" spans="6:6">
+    <row r="40" ht="14.25" spans="6:6">
       <c r="F40"/>
     </row>
-    <row r="41" spans="6:6">
+    <row r="41" ht="14.25" spans="6:6">
       <c r="F41"/>
     </row>
-    <row r="42" spans="6:6">
+    <row r="42" ht="14.25" spans="6:6">
       <c r="F42"/>
     </row>
-    <row r="43" spans="6:6">
+    <row r="43" ht="14.25" spans="6:6">
       <c r="F43"/>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -1676,7 +1676,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1764,12 +1764,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2096,64 +2090,64 @@
     <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5642,7 +5636,7 @@
         <v>2</v>
       </c>
       <c r="L32" s="12">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="M32" s="12" t="s">
         <v>262</v>
@@ -5651,7 +5645,7 @@
         <v>2</v>
       </c>
       <c r="O32" s="12">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="P32" s="12" t="s">
         <v>79</v>
@@ -5768,7 +5762,7 @@
         <v>222</v>
       </c>
       <c r="U33" s="12">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="V33" s="12" t="s">
         <v>223</v>
@@ -6038,7 +6032,7 @@
         <v>2</v>
       </c>
       <c r="L36" s="12">
-        <v>2000</v>
+        <v>4500</v>
       </c>
       <c r="M36" s="12" t="s">
         <v>274</v>
@@ -6047,7 +6041,7 @@
         <v>2</v>
       </c>
       <c r="O36" s="12">
-        <v>2000</v>
+        <v>4500</v>
       </c>
       <c r="P36" s="12" t="s">
         <v>79</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -5762,7 +5762,7 @@
         <v>222</v>
       </c>
       <c r="U33" s="12">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="V33" s="12" t="s">
         <v>223</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA2087D6-1641-4145-B9ED-F82F959E93B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -23,8 +29,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -32,32 +36,34 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>pe</author>
     <author>cltx</author>
   </authors>
   <commentList>
-    <comment ref="C4" authorId="0">
+    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>数字越大，优先级越高</t>
         </r>
       </text>
     </comment>
-    <comment ref="K4" authorId="1">
+    <comment ref="K4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>cltx:</t>
@@ -66,6 +72,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -75,12 +82,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="0">
+    <comment ref="U4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">&gt;0，持续时间
@@ -95,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="455">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1451,19 +1459,25 @@
   </si>
   <si>
     <t>冰冻</t>
+  </si>
+  <si>
+    <t>每【参数8】（默认1000）毫秒，造成{[火元素直接伤害]【参数1万分比】（默认X%）}，【参数2】（默认0）的[额外火元素持续伤害]，效果持续【参数5】（默认3000）毫秒，最大可叠加【参数7】（默认1）层</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>天火被动</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石落地点燃地面，释放技能天火【参数4】</t>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="30">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1475,24 +1489,28 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <color theme="0" tint="-0.0499893185216834"/>
+      <color theme="0" tint="-4.9989318521683403E-2"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1500,12 +1518,14 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1513,154 +1533,28 @@
       <sz val="9"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1668,15 +1562,24 @@
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1685,13 +1588,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.349986266670736"/>
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799615466780602"/>
+        <fgColor theme="8" tint="0.79958494827112647"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1703,31 +1606,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1737,152 +1616,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1920,241 +1655,20 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2169,7 +1683,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2177,76 +1691,34 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="23" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="4">
+    <cellStyle name="差" xfId="2" builtinId="27"/>
+    <cellStyle name="差 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="差 2" xfId="49"/>
+    <cellStyle name="输入" xfId="1" builtinId="20"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2524,14 +1996,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:AG41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AG43"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -2562,7 +2034,7 @@
     <col min="33" max="33" width="17.125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2595,7 +2067,7 @@
       <c r="AB1" s="4"/>
       <c r="AC1" s="4"/>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -2696,7 +2168,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:33">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
@@ -2797,7 +2269,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:33">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>41</v>
       </c>
@@ -2898,7 +2370,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:33">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>1000001</v>
       </c>
@@ -2999,7 +2471,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:33">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>54010001</v>
       </c>
@@ -3100,7 +2572,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:33">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>54020001</v>
       </c>
@@ -3201,7 +2673,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:33">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>54030001</v>
       </c>
@@ -3302,7 +2774,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="9" spans="1:33">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>54040001</v>
       </c>
@@ -3403,7 +2875,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="10" spans="1:33">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>54050001</v>
       </c>
@@ -3504,7 +2976,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:33">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>54060001</v>
       </c>
@@ -3605,7 +3077,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:33">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>54070001</v>
       </c>
@@ -3706,7 +3178,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="13" spans="1:33">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>54080001</v>
       </c>
@@ -3807,7 +3279,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="14" spans="1:33">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>54090001</v>
       </c>
@@ -3908,7 +3380,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="15" spans="1:33">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>54100001</v>
       </c>
@@ -4009,7 +3481,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="16" spans="1:33">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>54110001</v>
       </c>
@@ -4110,7 +3582,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="17" spans="1:33">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>54120001</v>
       </c>
@@ -4211,7 +3683,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="18" spans="1:33">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>54130001</v>
       </c>
@@ -4312,7 +3784,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="19" spans="1:33">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
         <v>54140001</v>
       </c>
@@ -4413,7 +3885,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="20" spans="1:33">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>54150001</v>
       </c>
@@ -4514,7 +3986,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="21" spans="1:33">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A21" s="9">
         <v>59130001</v>
       </c>
@@ -4611,7 +4083,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="1:33">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A22" s="9">
         <v>59140001</v>
       </c>
@@ -4708,7 +4180,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="1:33">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A23" s="12">
         <v>85001500</v>
       </c>
@@ -4807,7 +4279,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" spans="1:33">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A24" s="12">
         <v>85101100</v>
       </c>
@@ -4908,7 +4380,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:33">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A25" s="12">
         <v>85200700</v>
       </c>
@@ -5007,7 +4479,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:33">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>820001</v>
       </c>
@@ -5108,7 +4580,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="1:33">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>820011</v>
       </c>
@@ -5207,7 +4679,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="28" spans="1:33">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>820031</v>
       </c>
@@ -5306,7 +4778,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:33">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>820034</v>
       </c>
@@ -5405,7 +4877,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" spans="1:33">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>820051</v>
       </c>
@@ -5504,7 +4976,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" spans="1:33">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>820054</v>
       </c>
@@ -5603,7 +5075,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32" spans="1:33">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>820061</v>
       </c>
@@ -5702,7 +5174,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" spans="1:33">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>821061</v>
       </c>
@@ -5801,7 +5273,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="34" spans="1:33">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>820072</v>
       </c>
@@ -5900,7 +5372,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" spans="1:33">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>820073</v>
       </c>
@@ -5999,7 +5471,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36" spans="1:33">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>820080</v>
       </c>
@@ -6098,7 +5570,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="37" spans="1:33">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>820081</v>
       </c>
@@ -6197,7 +5669,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38" spans="1:33">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>820082</v>
       </c>
@@ -6296,7 +5768,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="39" spans="1:33">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>820083</v>
       </c>
@@ -6395,7 +5867,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="40" spans="1:33">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>820085</v>
       </c>
@@ -6494,7 +5966,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:33">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <v>820086</v>
       </c>
@@ -6593,18 +6065,217 @@
         <v>79</v>
       </c>
     </row>
+    <row r="42" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A42" s="12">
+        <v>820091</v>
+      </c>
+      <c r="B42" s="12">
+        <v>103</v>
+      </c>
+      <c r="C42" s="13">
+        <v>1</v>
+      </c>
+      <c r="D42" s="13">
+        <v>0</v>
+      </c>
+      <c r="E42" s="12">
+        <v>5101200</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="H42" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="I42" s="12" t="s">
+        <v>452</v>
+      </c>
+      <c r="J42" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="K42" s="12">
+        <v>2</v>
+      </c>
+      <c r="L42" s="12">
+        <v>3000</v>
+      </c>
+      <c r="M42" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="N42" s="12">
+        <v>1</v>
+      </c>
+      <c r="O42" s="12">
+        <v>0</v>
+      </c>
+      <c r="P42" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q42" s="12">
+        <v>1</v>
+      </c>
+      <c r="R42" s="12">
+        <v>0</v>
+      </c>
+      <c r="S42" s="13">
+        <v>0</v>
+      </c>
+      <c r="T42" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="U42" s="12">
+        <v>3000</v>
+      </c>
+      <c r="V42" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="W42" s="12">
+        <v>10000</v>
+      </c>
+      <c r="X42" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y42" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z42" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA42" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="AB42" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC42" s="12">
+        <v>1000</v>
+      </c>
+      <c r="AD42" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE42" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF42" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG42" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="43" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A43" s="12">
+        <v>820093</v>
+      </c>
+      <c r="B43" s="12">
+        <v>20093</v>
+      </c>
+      <c r="C43" s="13">
+        <v>1</v>
+      </c>
+      <c r="D43" s="13">
+        <v>0</v>
+      </c>
+      <c r="E43" s="12">
+        <v>820093</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="H43" s="12"/>
+      <c r="I43" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="J43" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K43" s="12">
+        <v>1</v>
+      </c>
+      <c r="L43" s="12">
+        <v>0</v>
+      </c>
+      <c r="M43" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="N43" s="12">
+        <v>1</v>
+      </c>
+      <c r="O43" s="12">
+        <v>0</v>
+      </c>
+      <c r="P43" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q43" s="12">
+        <v>1</v>
+      </c>
+      <c r="R43" s="12">
+        <v>0</v>
+      </c>
+      <c r="S43" s="13">
+        <v>20092</v>
+      </c>
+      <c r="T43" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="U43" s="12">
+        <v>-1</v>
+      </c>
+      <c r="V43" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="W43" s="12">
+        <v>10000</v>
+      </c>
+      <c r="X43" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y43" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z43" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA43" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB43" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC43" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE43" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF43" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG43" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="E7:S71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
     <col min="5" max="5" width="27.25" style="1" customWidth="1"/>
@@ -6617,7 +6288,7 @@
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="5:6">
+    <row r="7" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E7" s="1" t="s">
         <v>8</v>
       </c>
@@ -6625,7 +6296,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="5:6">
+    <row r="8" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E8" s="1" t="s">
         <v>9</v>
       </c>
@@ -6633,7 +6304,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="5:6">
+    <row r="9" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E9" s="1" t="s">
         <v>10</v>
       </c>
@@ -6641,7 +6312,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="5:6">
+    <row r="10" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E10" s="1" t="s">
         <v>11</v>
       </c>
@@ -6649,7 +6320,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="11" spans="5:6">
+    <row r="11" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E11" s="1" t="s">
         <v>12</v>
       </c>
@@ -6657,7 +6328,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="5:6">
+    <row r="12" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E12" s="1" t="s">
         <v>13</v>
       </c>
@@ -6665,7 +6336,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="5:19">
+    <row r="13" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E13" s="1" t="s">
         <v>14</v>
       </c>
@@ -6679,7 +6350,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="14" spans="5:12">
+    <row r="14" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E14" s="1" t="s">
         <v>15</v>
       </c>
@@ -6699,7 +6370,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="15" spans="5:19">
+    <row r="15" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E15" s="1" t="s">
         <v>16</v>
       </c>
@@ -6719,7 +6390,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="16" spans="5:19">
+    <row r="16" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E16" s="1" t="s">
         <v>17</v>
       </c>
@@ -6742,7 +6413,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="17" spans="5:19">
+    <row r="17" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E17" s="1" t="s">
         <v>18</v>
       </c>
@@ -6765,7 +6436,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="18" spans="5:19">
+    <row r="18" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E18" s="1" t="s">
         <v>19</v>
       </c>
@@ -6788,7 +6459,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="19" spans="5:19">
+    <row r="19" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E19" s="1" t="s">
         <v>20</v>
       </c>
@@ -6818,7 +6489,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="20" spans="5:19">
+    <row r="20" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E20" s="1" t="s">
         <v>21</v>
       </c>
@@ -6848,7 +6519,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="21" spans="5:19">
+    <row r="21" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E21" s="1" t="s">
         <v>22</v>
       </c>
@@ -6878,7 +6549,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="22" spans="5:19">
+    <row r="22" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E22" s="1" t="s">
         <v>23</v>
       </c>
@@ -6908,7 +6579,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="23" spans="5:19">
+    <row r="23" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E23" s="1" t="s">
         <v>24</v>
       </c>
@@ -6938,7 +6609,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="24" spans="5:19">
+    <row r="24" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E24" s="1" t="s">
         <v>25</v>
       </c>
@@ -6968,7 +6639,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="25" spans="5:19">
+    <row r="25" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E25" s="1" t="s">
         <v>26</v>
       </c>
@@ -6998,7 +6669,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="26" spans="5:19">
+    <row r="26" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E26" s="1" t="s">
         <v>27</v>
       </c>
@@ -7028,7 +6699,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="27" spans="5:19">
+    <row r="27" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E27" s="1" t="s">
         <v>28</v>
       </c>
@@ -7058,7 +6729,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="28" spans="5:12">
+    <row r="28" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E28" s="1" t="s">
         <v>29</v>
       </c>
@@ -7085,7 +6756,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="29" spans="5:19">
+    <row r="29" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E29" s="1" t="s">
         <v>30</v>
       </c>
@@ -7115,7 +6786,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="30" spans="5:19">
+    <row r="30" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E30" s="1" t="s">
         <v>31</v>
       </c>
@@ -7145,7 +6816,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="31" spans="5:19">
+    <row r="31" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E31" s="1" t="s">
         <v>32</v>
       </c>
@@ -7175,7 +6846,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="32" spans="5:12">
+    <row r="32" spans="5:19" x14ac:dyDescent="0.15">
       <c r="E32" s="1" t="s">
         <v>33</v>
       </c>
@@ -7202,7 +6873,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="33" spans="5:9">
+    <row r="33" spans="5:9" x14ac:dyDescent="0.15">
       <c r="E33" s="1" t="s">
         <v>34</v>
       </c>
@@ -7220,7 +6891,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="34" spans="5:9">
+    <row r="34" spans="5:9" x14ac:dyDescent="0.15">
       <c r="E34" s="1" t="s">
         <v>35</v>
       </c>
@@ -7238,7 +6909,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="35" spans="5:9">
+    <row r="35" spans="5:9" x14ac:dyDescent="0.15">
       <c r="E35" s="1" t="s">
         <v>36</v>
       </c>
@@ -7256,7 +6927,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="36" spans="7:9">
+    <row r="36" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G36" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数21-技能增加-万分比</v>
@@ -7268,7 +6939,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="37" spans="7:9">
+    <row r="37" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G37" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数22-技能增加-普通攻击范围万分比</v>
@@ -7280,7 +6951,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="38" spans="7:9">
+    <row r="38" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G38" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数25LIST-攻击提高-攻击的元素类型</v>
@@ -7292,7 +6963,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="39" spans="7:9">
+    <row r="39" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G39" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数25LIST-攻击提高-固定值</v>
@@ -7304,7 +6975,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="40" spans="7:9">
+    <row r="40" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G40" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数25LIST-攻击提高-万分比</v>
@@ -7316,7 +6987,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="41" spans="7:9">
+    <row r="41" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G41" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数28-防御提高-固定值</v>
@@ -7328,7 +6999,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="42" spans="7:9">
+    <row r="42" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G42" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数29-防御提高-万分比</v>
@@ -7340,7 +7011,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="43" spans="7:9">
+    <row r="43" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G43" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数30-生命上限提高-固定值</v>
@@ -7352,7 +7023,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="44" spans="7:9">
+    <row r="44" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G44" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数31-生命上限提高-百万分比</v>
@@ -7364,7 +7035,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="45" spans="7:9">
+    <row r="45" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G45" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数32-攻击速度提高-万分比</v>
@@ -7376,7 +7047,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="46" spans="7:9">
+    <row r="46" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G46" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数33-移动速度提高-万分比</v>
@@ -7388,7 +7059,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="47" spans="7:9">
+    <row r="47" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G47" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数34-攻击范围提高-万分比</v>
@@ -7400,7 +7071,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="48" spans="7:9">
+    <row r="48" spans="5:9" x14ac:dyDescent="0.15">
       <c r="G48" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数35-攻击目标数量提高-固定值</v>
@@ -7412,7 +7083,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="49" spans="7:8">
+    <row r="49" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G49" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数36-</v>
@@ -7421,7 +7092,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="50" spans="7:8">
+    <row r="50" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G50" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数37-</v>
@@ -7430,7 +7101,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="51" spans="7:8">
+    <row r="51" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G51" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数38-</v>
@@ -7439,7 +7110,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="52" spans="7:8">
+    <row r="52" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G52" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数39-</v>
@@ -7448,7 +7119,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="53" spans="7:8">
+    <row r="53" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G53" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数40-</v>
@@ -7457,7 +7128,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="54" spans="7:8">
+    <row r="54" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G54" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数41-</v>
@@ -7466,7 +7137,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="55" spans="7:8">
+    <row r="55" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G55" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数42-</v>
@@ -7475,7 +7146,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="56" spans="7:8">
+    <row r="56" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G56" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数41-</v>
@@ -7484,7 +7155,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="57" spans="7:8">
+    <row r="57" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G57" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数42-</v>
@@ -7493,7 +7164,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="58" spans="7:8">
+    <row r="58" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G58" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数43-</v>
@@ -7502,7 +7173,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="59" spans="7:8">
+    <row r="59" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G59" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数44-</v>
@@ -7511,7 +7182,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="60" spans="7:8">
+    <row r="60" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G60" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数45-</v>
@@ -7520,7 +7191,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="61" spans="7:8">
+    <row r="61" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G61" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数46-</v>
@@ -7529,7 +7200,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="62" spans="7:8">
+    <row r="62" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G62" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数47-</v>
@@ -7538,7 +7209,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="63" spans="7:8">
+    <row r="63" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G63" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数48-</v>
@@ -7547,7 +7218,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="64" spans="7:8">
+    <row r="64" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G64" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数49-</v>
@@ -7556,7 +7227,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="65" spans="7:8">
+    <row r="65" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G65" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数50-</v>
@@ -7565,7 +7236,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="66" spans="7:8">
+    <row r="66" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G66" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数51-</v>
@@ -7574,7 +7245,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="67" spans="7:8">
+    <row r="67" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G67" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数52-</v>
@@ -7583,7 +7254,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="68" spans="7:8">
+    <row r="68" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G68" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数53-</v>
@@ -7592,7 +7263,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="69" spans="7:8">
+    <row r="69" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G69" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数54-</v>
@@ -7601,7 +7272,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="70" spans="7:8">
+    <row r="70" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G70" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数55-</v>
@@ -7610,7 +7281,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="71" spans="7:8">
+    <row r="71" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G71" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数56-</v>
@@ -7620,16 +7291,15 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="D6:F43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="11.25" style="1" customWidth="1"/>
@@ -7639,13 +7309,13 @@
     <col min="23" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="4:5">
+    <row r="6" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D6" s="2" t="s">
         <v>430</v>
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="4:5">
+    <row r="7" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D7" s="2">
         <v>1</v>
       </c>
@@ -7653,11 +7323,11 @@
         <v>431</v>
       </c>
     </row>
-    <row r="8" spans="4:5">
+    <row r="8" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="4:5">
+    <row r="9" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D9" s="2">
         <v>2</v>
       </c>
@@ -7665,7 +7335,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="10" spans="4:5">
+    <row r="10" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D10" s="2">
         <v>2.1</v>
       </c>
@@ -7673,7 +7343,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="11" spans="4:5">
+    <row r="11" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D11" s="2" t="s">
         <v>434</v>
       </c>
@@ -7681,7 +7351,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="12" spans="4:5">
+    <row r="12" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D12" s="2" t="s">
         <v>436</v>
       </c>
@@ -7689,7 +7359,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="13" spans="4:5">
+    <row r="13" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D13" s="2" t="s">
         <v>438</v>
       </c>
@@ -7697,19 +7367,19 @@
         <v>439</v>
       </c>
     </row>
-    <row r="14" spans="4:5">
+    <row r="14" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="4:5">
+    <row r="15" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D15" s="2">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="16" spans="4:5">
+    <row r="16" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D16" s="2" t="s">
         <v>441</v>
       </c>
@@ -7717,7 +7387,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="17" spans="4:5">
+    <row r="17" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D17" s="2" t="s">
         <v>442</v>
       </c>
@@ -7725,7 +7395,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="18" spans="4:5">
+    <row r="18" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D18" s="2" t="s">
         <v>444</v>
       </c>
@@ -7733,12 +7403,12 @@
         <v>445</v>
       </c>
     </row>
-    <row r="28" spans="4:4">
+    <row r="28" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D28" s="1" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="29" spans="4:5">
+    <row r="29" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D29" s="1" t="s">
         <v>447</v>
       </c>
@@ -7746,7 +7416,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="30" spans="4:5">
+    <row r="30" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D30" s="1" t="s">
         <v>448</v>
       </c>
@@ -7754,17 +7424,20 @@
         <v>102</v>
       </c>
     </row>
-    <row r="31" spans="4:4">
+    <row r="31" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D31" s="1" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="32" spans="4:4">
+      <c r="E31" s="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D32" s="1" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="33" ht="14.25" spans="4:6">
+    <row r="33" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="D33" s="1" t="s">
         <v>451</v>
       </c>
@@ -7773,38 +7446,38 @@
       </c>
       <c r="F33"/>
     </row>
-    <row r="34" ht="14.25" spans="6:6">
+    <row r="34" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F34"/>
     </row>
-    <row r="35" ht="14.25" spans="6:6">
+    <row r="35" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F35"/>
     </row>
-    <row r="36" ht="14.25" spans="6:6">
+    <row r="36" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F36"/>
     </row>
-    <row r="37" ht="14.25" spans="6:6">
+    <row r="37" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F37"/>
     </row>
-    <row r="38" ht="14.25" spans="6:6">
+    <row r="38" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F38"/>
     </row>
-    <row r="39" ht="14.25" spans="6:6">
+    <row r="39" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F39"/>
     </row>
-    <row r="40" ht="14.25" spans="6:6">
+    <row r="40" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F40"/>
     </row>
-    <row r="41" ht="14.25" spans="6:6">
+    <row r="41" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F41"/>
     </row>
-    <row r="42" ht="14.25" spans="6:6">
+    <row r="42" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F42"/>
     </row>
-    <row r="43" ht="14.25" spans="6:6">
+    <row r="43" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F43"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA2087D6-1641-4145-B9ED-F82F959E93B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DCCB1A3-3D1A-41D4-8B80-4F5F24A17835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="462">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1470,6 +1470,34 @@
   </si>
   <si>
     <t>陨石落地点燃地面，释放技能天火【参数4】</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石燃烧状态</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>火刃燃烧状态</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>5101215:1</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>5101116:1</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>5101218:2</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>5101211:1</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>5101212:1</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
@@ -2002,7 +2030,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG43"/>
+  <dimension ref="A1:AG44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -6082,7 +6110,7 @@
         <v>5101200</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>224</v>
+        <v>455</v>
       </c>
       <c r="G42" s="11" t="s">
         <v>225</v>
@@ -6133,7 +6161,7 @@
         <v>230</v>
       </c>
       <c r="W42" s="12">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X42" s="12" t="s">
         <v>79</v>
@@ -6262,6 +6290,107 @@
         <v>79</v>
       </c>
       <c r="AG43" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="44" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A44" s="12">
+        <v>820101</v>
+      </c>
+      <c r="B44" s="12">
+        <v>103</v>
+      </c>
+      <c r="C44" s="13">
+        <v>1</v>
+      </c>
+      <c r="D44" s="13">
+        <v>0</v>
+      </c>
+      <c r="E44" s="12">
+        <v>5101200</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>456</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="H44" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="I44" s="12" t="s">
+        <v>452</v>
+      </c>
+      <c r="J44" s="12" t="s">
+        <v>460</v>
+      </c>
+      <c r="K44" s="12">
+        <v>2</v>
+      </c>
+      <c r="L44" s="12">
+        <v>3000</v>
+      </c>
+      <c r="M44" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="N44" s="12">
+        <v>1</v>
+      </c>
+      <c r="O44" s="12">
+        <v>0</v>
+      </c>
+      <c r="P44" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q44" s="12">
+        <v>1</v>
+      </c>
+      <c r="R44" s="12">
+        <v>0</v>
+      </c>
+      <c r="S44" s="13">
+        <v>0</v>
+      </c>
+      <c r="T44" s="12" t="s">
+        <v>457</v>
+      </c>
+      <c r="U44" s="12">
+        <v>3000</v>
+      </c>
+      <c r="V44" s="12" t="s">
+        <v>458</v>
+      </c>
+      <c r="W44" s="12">
+        <v>0</v>
+      </c>
+      <c r="X44" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y44" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z44" s="12">
+        <v>1</v>
+      </c>
+      <c r="AA44" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="AB44" s="12">
+        <v>1</v>
+      </c>
+      <c r="AC44" s="12">
+        <v>1000</v>
+      </c>
+      <c r="AD44" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE44" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF44" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG44" s="7" t="s">
         <v>79</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DCCB1A3-3D1A-41D4-8B80-4F5F24A17835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{644BCFED-DC4B-4F8A-AE4D-38C0AAEFA939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -972,9 +972,6 @@
     <t>5001521:1</t>
   </si>
   <si>
-    <t>冰雪领域-触发技能</t>
-  </si>
-  <si>
     <t>减速时概率【参数1】触发冰雪领域（释放技能）【参数4】</t>
   </si>
   <si>
@@ -1465,14 +1462,6 @@
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
-    <t>天火被动</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>陨石落地点燃地面，释放技能天火【参数4】</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
     <t>陨石燃烧状态</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
@@ -1498,6 +1487,18 @@
   </si>
   <si>
     <t>5101212:1</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰雪领域-触发技能</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>毁天灭地-触发技能</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀敌人时释放爆炸火球技能【参数4】</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
@@ -6011,17 +6012,17 @@
         <v>820086</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>289</v>
+        <v>459</v>
       </c>
       <c r="G41" s="11" t="s">
         <v>220</v>
       </c>
       <c r="H41" s="12"/>
       <c r="I41" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="J41" s="16" t="s">
         <v>290</v>
-      </c>
-      <c r="J41" s="16" t="s">
-        <v>291</v>
       </c>
       <c r="K41" s="12">
         <v>2</v>
@@ -6110,7 +6111,7 @@
         <v>5101200</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="G42" s="11" t="s">
         <v>225</v>
@@ -6119,7 +6120,7 @@
         <v>224</v>
       </c>
       <c r="I42" s="12" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J42" s="12" t="s">
         <v>227</v>
@@ -6196,10 +6197,10 @@
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
-        <v>820093</v>
+        <v>820101</v>
       </c>
       <c r="B43" s="12">
-        <v>20093</v>
+        <v>103</v>
       </c>
       <c r="C43" s="13">
         <v>1</v>
@@ -6208,59 +6209,61 @@
         <v>0</v>
       </c>
       <c r="E43" s="12">
-        <v>820093</v>
-      </c>
-      <c r="F43" s="4" t="s">
+        <v>5101200</v>
+      </c>
+      <c r="F43" s="12" t="s">
         <v>453</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="H43" s="12"/>
+        <v>225</v>
+      </c>
+      <c r="H43" s="12" t="s">
+        <v>224</v>
+      </c>
       <c r="I43" s="12" t="s">
+        <v>451</v>
+      </c>
+      <c r="J43" s="12" t="s">
+        <v>457</v>
+      </c>
+      <c r="K43" s="12">
+        <v>2</v>
+      </c>
+      <c r="L43" s="12">
+        <v>3000</v>
+      </c>
+      <c r="M43" s="12" t="s">
+        <v>458</v>
+      </c>
+      <c r="N43" s="12">
+        <v>1</v>
+      </c>
+      <c r="O43" s="12">
+        <v>0</v>
+      </c>
+      <c r="P43" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q43" s="12">
+        <v>1</v>
+      </c>
+      <c r="R43" s="12">
+        <v>0</v>
+      </c>
+      <c r="S43" s="13">
+        <v>0</v>
+      </c>
+      <c r="T43" s="12" t="s">
         <v>454</v>
       </c>
-      <c r="J43" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="K43" s="12">
-        <v>1</v>
-      </c>
-      <c r="L43" s="12">
-        <v>0</v>
-      </c>
-      <c r="M43" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="N43" s="12">
-        <v>1</v>
-      </c>
-      <c r="O43" s="12">
-        <v>0</v>
-      </c>
-      <c r="P43" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q43" s="12">
-        <v>1</v>
-      </c>
-      <c r="R43" s="12">
-        <v>0</v>
-      </c>
-      <c r="S43" s="13">
-        <v>20092</v>
-      </c>
-      <c r="T43" s="12" t="s">
-        <v>79</v>
-      </c>
       <c r="U43" s="12">
-        <v>-1</v>
+        <v>3000</v>
       </c>
       <c r="V43" s="12" t="s">
-        <v>79</v>
+        <v>455</v>
       </c>
       <c r="W43" s="12">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X43" s="12" t="s">
         <v>79</v>
@@ -6272,13 +6275,13 @@
         <v>1</v>
       </c>
       <c r="AA43" s="12" t="s">
-        <v>79</v>
+        <v>456</v>
       </c>
       <c r="AB43" s="12">
         <v>1</v>
       </c>
       <c r="AC43" s="12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD43" s="7" t="s">
         <v>79</v>
@@ -6295,10 +6298,10 @@
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
-        <v>820101</v>
+        <v>820094</v>
       </c>
       <c r="B44" s="12">
-        <v>103</v>
+        <v>20094</v>
       </c>
       <c r="C44" s="13">
         <v>1</v>
@@ -6307,31 +6310,29 @@
         <v>0</v>
       </c>
       <c r="E44" s="12">
-        <v>5101200</v>
+        <v>820094</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="H44" s="12" t="s">
-        <v>224</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="H44" s="12"/>
       <c r="I44" s="12" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="J44" s="12" t="s">
-        <v>460</v>
+        <v>79</v>
       </c>
       <c r="K44" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L44" s="12">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="M44" s="12" t="s">
-        <v>461</v>
+        <v>79</v>
       </c>
       <c r="N44" s="12">
         <v>1</v>
@@ -6349,19 +6350,19 @@
         <v>0</v>
       </c>
       <c r="S44" s="13">
-        <v>0</v>
+        <v>20095</v>
       </c>
       <c r="T44" s="12" t="s">
-        <v>457</v>
+        <v>79</v>
       </c>
       <c r="U44" s="12">
-        <v>3000</v>
+        <v>-1</v>
       </c>
       <c r="V44" s="12" t="s">
-        <v>458</v>
+        <v>79</v>
       </c>
       <c r="W44" s="12">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X44" s="12" t="s">
         <v>79</v>
@@ -6373,13 +6374,13 @@
         <v>1</v>
       </c>
       <c r="AA44" s="12" t="s">
-        <v>459</v>
+        <v>79</v>
       </c>
       <c r="AB44" s="12">
         <v>1</v>
       </c>
       <c r="AC44" s="12">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD44" s="7" t="s">
         <v>79</v>
@@ -6446,7 +6447,7 @@
         <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11" spans="5:19" x14ac:dyDescent="0.15">
@@ -6473,10 +6474,10 @@
         <v>47</v>
       </c>
       <c r="J13" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="S13" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="14" spans="5:19" x14ac:dyDescent="0.15">
@@ -6493,10 +6494,10 @@
         <v>1</v>
       </c>
       <c r="K14" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="L14" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="15" spans="5:19" x14ac:dyDescent="0.15">
@@ -6510,13 +6511,13 @@
         <v>3</v>
       </c>
       <c r="K15" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="L15" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="S15" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="16" spans="5:19" x14ac:dyDescent="0.15">
@@ -6533,13 +6534,13 @@
         <v>7</v>
       </c>
       <c r="K16" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="L16" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="L16" s="1" t="s">
+      <c r="S16" s="1" t="s">
         <v>301</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="17" spans="5:19" x14ac:dyDescent="0.15">
@@ -6556,13 +6557,13 @@
         <v>7</v>
       </c>
       <c r="K17" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="L17" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="L17" s="1" t="s">
+      <c r="S17" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="S17" s="1" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="18" spans="5:19" x14ac:dyDescent="0.15">
@@ -6579,13 +6580,13 @@
         <v>7</v>
       </c>
       <c r="K18" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="L18" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="L18" s="1" t="s">
+      <c r="S18" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="S18" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="19" spans="5:19" x14ac:dyDescent="0.15">
@@ -6600,22 +6601,22 @@
         <v>参数4LIST-触发的技能id</v>
       </c>
       <c r="H19" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="I19" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="J19" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="K19" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="L19" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="L19" s="1" t="s">
+      <c r="S19" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="20" spans="5:19" x14ac:dyDescent="0.15">
@@ -6630,22 +6631,22 @@
         <v>参数5-持续时间（毫秒）</v>
       </c>
       <c r="H20" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="I20" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="J20" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="K20" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="K20" s="1" t="s">
+      <c r="L20" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="L20" s="1" t="s">
+      <c r="S20" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="21" spans="5:19" x14ac:dyDescent="0.15">
@@ -6660,22 +6661,22 @@
         <v>参数6-效果基础命中率（万分比）</v>
       </c>
       <c r="H21" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>321</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K21" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="L21" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="L21" s="1" t="s">
+      <c r="S21" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="22" spans="5:19" x14ac:dyDescent="0.15">
@@ -6693,19 +6694,19 @@
         <v>66</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K22" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="L22" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="L22" s="1" t="s">
+      <c r="S22" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="S22" s="1" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="23" spans="5:19" x14ac:dyDescent="0.15">
@@ -6720,22 +6721,22 @@
         <v>参数8-效果触发间隔（毫秒）</v>
       </c>
       <c r="H23" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="I23" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>330</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K23" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="L23" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="L23" s="1" t="s">
+      <c r="S23" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="S23" s="1" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="24" spans="5:19" x14ac:dyDescent="0.15">
@@ -6750,22 +6751,22 @@
         <v>参数9-击中回复生命值-固定值</v>
       </c>
       <c r="H24" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="I24" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="J24" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="K24" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="J24" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="K24" s="1" t="s">
+      <c r="L24" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="L24" s="1" t="s">
+      <c r="S24" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="S24" s="1" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="25" spans="5:19" x14ac:dyDescent="0.15">
@@ -6780,22 +6781,22 @@
         <v>参数10-击中回复生命值-自身最大生命值百万分比</v>
       </c>
       <c r="H25" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="I25" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>340</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K25" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="L25" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="L25" s="1" t="s">
+      <c r="S25" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="S25" s="1" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="26" spans="5:19" x14ac:dyDescent="0.15">
@@ -6810,22 +6811,22 @@
         <v>参数11-击中回复效果提高万分比</v>
       </c>
       <c r="H26" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="I26" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="J26" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="K26" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="J26" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="K26" s="1" t="s">
+      <c r="L26" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="L26" s="1" t="s">
+      <c r="S26" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="S26" s="1" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="27" spans="5:19" x14ac:dyDescent="0.15">
@@ -6840,22 +6841,22 @@
         <v>参数12-击杀回复生命-固定值</v>
       </c>
       <c r="H27" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="I27" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>350</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K27" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="L27" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="L27" s="1" t="s">
+      <c r="S27" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="S27" s="1" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="28" spans="5:19" x14ac:dyDescent="0.15">
@@ -6870,19 +6871,19 @@
         <v>参数13-击杀回复生命-自身最大生命值百万分比</v>
       </c>
       <c r="H28" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="I28" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>355</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K28" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="L28" s="1" t="s">
         <v>356</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="29" spans="5:19" x14ac:dyDescent="0.15">
@@ -6897,22 +6898,22 @@
         <v>参数14-击杀回复生命-目标最大生命值百万分比</v>
       </c>
       <c r="H29" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="I29" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>359</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K29" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="L29" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="L29" s="1" t="s">
+      <c r="S29" s="1" t="s">
         <v>361</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="30" spans="5:19" x14ac:dyDescent="0.15">
@@ -6927,22 +6928,22 @@
         <v>参数15-击杀回复生命效果提高万分比</v>
       </c>
       <c r="H30" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="I30" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>364</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K30" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="L30" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="L30" s="1" t="s">
+      <c r="S30" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="31" spans="5:19" x14ac:dyDescent="0.15">
@@ -6957,22 +6958,22 @@
         <v>参数16-获得护盾-固定值</v>
       </c>
       <c r="H31" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="I31" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>369</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="K31" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="L31" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="L31" s="1" t="s">
+      <c r="S31" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="S31" s="1" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="32" spans="5:19" x14ac:dyDescent="0.15">
@@ -6980,26 +6981,26 @@
         <v>33</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G32" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数17-获得护盾-自身生命百万分比</v>
       </c>
       <c r="H32" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="I32" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="J32" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="K32" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="J32" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="K32" s="1" t="s">
+      <c r="L32" s="1" t="s">
         <v>376</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="33" spans="5:9" x14ac:dyDescent="0.15">
@@ -7014,10 +7015,10 @@
         <v>参数18-获得护盾-自身已损失生命万分比</v>
       </c>
       <c r="H33" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="I33" s="1" t="s">
         <v>378</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="34" spans="5:9" x14ac:dyDescent="0.15">
@@ -7032,10 +7033,10 @@
         <v>参数19-获得护盾效果提高万分比</v>
       </c>
       <c r="H34" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="I34" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="35" spans="5:9" x14ac:dyDescent="0.15">
@@ -7043,17 +7044,17 @@
         <v>36</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G35" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数20-技能增加-固定值</v>
       </c>
       <c r="H35" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="I35" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="36" spans="5:9" x14ac:dyDescent="0.15">
@@ -7062,10 +7063,10 @@
         <v>参数21-技能增加-万分比</v>
       </c>
       <c r="H36" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I36" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="37" spans="5:9" x14ac:dyDescent="0.15">
@@ -7074,10 +7075,10 @@
         <v>参数22-技能增加-普通攻击范围万分比</v>
       </c>
       <c r="H37" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="I37" s="1" t="s">
         <v>387</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="38" spans="5:9" x14ac:dyDescent="0.15">
@@ -7086,10 +7087,10 @@
         <v>参数25LIST-攻击提高-攻击的元素类型</v>
       </c>
       <c r="H38" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>389</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="39" spans="5:9" x14ac:dyDescent="0.15">
@@ -7098,10 +7099,10 @@
         <v>参数25LIST-攻击提高-固定值</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="40" spans="5:9" x14ac:dyDescent="0.15">
@@ -7110,10 +7111,10 @@
         <v>参数25LIST-攻击提高-万分比</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="41" spans="5:9" x14ac:dyDescent="0.15">
@@ -7122,10 +7123,10 @@
         <v>参数28-防御提高-固定值</v>
       </c>
       <c r="H41" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="I41" s="1" t="s">
         <v>393</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="42" spans="5:9" x14ac:dyDescent="0.15">
@@ -7134,10 +7135,10 @@
         <v>参数29-防御提高-万分比</v>
       </c>
       <c r="H42" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="I42" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="43" spans="5:9" x14ac:dyDescent="0.15">
@@ -7146,10 +7147,10 @@
         <v>参数30-生命上限提高-固定值</v>
       </c>
       <c r="H43" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="I43" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="44" spans="5:9" x14ac:dyDescent="0.15">
@@ -7158,10 +7159,10 @@
         <v>参数31-生命上限提高-百万分比</v>
       </c>
       <c r="H44" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="I44" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="45" spans="5:9" x14ac:dyDescent="0.15">
@@ -7170,10 +7171,10 @@
         <v>参数32-攻击速度提高-万分比</v>
       </c>
       <c r="H45" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="I45" s="1" t="s">
         <v>401</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="46" spans="5:9" x14ac:dyDescent="0.15">
@@ -7182,10 +7183,10 @@
         <v>参数33-移动速度提高-万分比</v>
       </c>
       <c r="H46" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="I46" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="47" spans="5:9" x14ac:dyDescent="0.15">
@@ -7194,10 +7195,10 @@
         <v>参数34-攻击范围提高-万分比</v>
       </c>
       <c r="H47" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="I47" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="48" spans="5:9" x14ac:dyDescent="0.15">
@@ -7206,10 +7207,10 @@
         <v>参数35-攻击目标数量提高-固定值</v>
       </c>
       <c r="H48" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="I48" s="1" t="s">
         <v>407</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="49" spans="7:8" x14ac:dyDescent="0.15">
@@ -7218,7 +7219,7 @@
         <v>参数36-</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="50" spans="7:8" x14ac:dyDescent="0.15">
@@ -7227,7 +7228,7 @@
         <v>参数37-</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="51" spans="7:8" x14ac:dyDescent="0.15">
@@ -7236,7 +7237,7 @@
         <v>参数38-</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="52" spans="7:8" x14ac:dyDescent="0.15">
@@ -7245,7 +7246,7 @@
         <v>参数39-</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="53" spans="7:8" x14ac:dyDescent="0.15">
@@ -7254,7 +7255,7 @@
         <v>参数40-</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="54" spans="7:8" x14ac:dyDescent="0.15">
@@ -7263,7 +7264,7 @@
         <v>参数41-</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="55" spans="7:8" x14ac:dyDescent="0.15">
@@ -7272,7 +7273,7 @@
         <v>参数42-</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="56" spans="7:8" x14ac:dyDescent="0.15">
@@ -7281,7 +7282,7 @@
         <v>参数41-</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="57" spans="7:8" x14ac:dyDescent="0.15">
@@ -7290,7 +7291,7 @@
         <v>参数42-</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="58" spans="7:8" x14ac:dyDescent="0.15">
@@ -7299,7 +7300,7 @@
         <v>参数43-</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="59" spans="7:8" x14ac:dyDescent="0.15">
@@ -7308,7 +7309,7 @@
         <v>参数44-</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="60" spans="7:8" x14ac:dyDescent="0.15">
@@ -7317,7 +7318,7 @@
         <v>参数45-</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="61" spans="7:8" x14ac:dyDescent="0.15">
@@ -7326,7 +7327,7 @@
         <v>参数46-</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="62" spans="7:8" x14ac:dyDescent="0.15">
@@ -7335,7 +7336,7 @@
         <v>参数47-</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="63" spans="7:8" x14ac:dyDescent="0.15">
@@ -7344,7 +7345,7 @@
         <v>参数48-</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="64" spans="7:8" x14ac:dyDescent="0.15">
@@ -7353,7 +7354,7 @@
         <v>参数49-</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="65" spans="7:8" x14ac:dyDescent="0.15">
@@ -7362,7 +7363,7 @@
         <v>参数50-</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="66" spans="7:8" x14ac:dyDescent="0.15">
@@ -7371,7 +7372,7 @@
         <v>参数51-</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="67" spans="7:8" x14ac:dyDescent="0.15">
@@ -7380,7 +7381,7 @@
         <v>参数52-</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="68" spans="7:8" x14ac:dyDescent="0.15">
@@ -7389,7 +7390,7 @@
         <v>参数53-</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="69" spans="7:8" x14ac:dyDescent="0.15">
@@ -7398,7 +7399,7 @@
         <v>参数54-</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="70" spans="7:8" x14ac:dyDescent="0.15">
@@ -7407,7 +7408,7 @@
         <v>参数55-</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="71" spans="7:8" x14ac:dyDescent="0.15">
@@ -7416,7 +7417,7 @@
         <v>参数56-</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -7440,7 +7441,7 @@
   <sheetData>
     <row r="6" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D6" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -7449,7 +7450,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="8" spans="4:5" x14ac:dyDescent="0.15">
@@ -7461,7 +7462,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="10" spans="4:5" x14ac:dyDescent="0.15">
@@ -7469,31 +7470,31 @@
         <v>2.1</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="11" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D11" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>434</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="12" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D12" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>436</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="13" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D13" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>438</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="14" spans="4:5" x14ac:dyDescent="0.15">
@@ -7505,41 +7506,41 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="16" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D16" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="17" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D17" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>442</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="18" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D18" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>444</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="28" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D28" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="29" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D29" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E29" s="1">
         <v>101</v>
@@ -7547,7 +7548,7 @@
     </row>
     <row r="30" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D30" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E30" s="1">
         <v>102</v>
@@ -7555,7 +7556,7 @@
     </row>
     <row r="31" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D31" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E31" s="1">
         <v>103</v>
@@ -7563,12 +7564,12 @@
     </row>
     <row r="32" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D32" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="33" spans="4:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="D33" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E33" s="1">
         <v>105</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{644BCFED-DC4B-4F8A-AE4D-38C0AAEFA939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -29,6 +23,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,34 +32,32 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>pe</author>
     <author>cltx</author>
   </authors>
   <commentList>
-    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="C4" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>数字越大，优先级越高</t>
         </r>
       </text>
     </comment>
-    <comment ref="K4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="K4" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>cltx:</t>
@@ -72,7 +66,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -82,13 +75,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="U4" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">&gt;0，持续时间
@@ -972,12 +964,45 @@
     <t>5001521:1</t>
   </si>
   <si>
+    <t>冰雪领域-触发技能</t>
+  </si>
+  <si>
     <t>减速时概率【参数1】触发冰雪领域（释放技能）【参数4】</t>
   </si>
   <si>
     <t>8200861:1</t>
   </si>
   <si>
+    <t>陨石燃烧状态</t>
+  </si>
+  <si>
+    <t>每【参数8】（默认1000）毫秒，造成{[火元素直接伤害]【参数1万分比】（默认X%）}，【参数2】（默认0）的[额外火元素持续伤害]，效果持续【参数5】（默认3000）毫秒，最大可叠加【参数7】（默认1）层，状态命中率【参数6】</t>
+  </si>
+  <si>
+    <t>火刃燃烧状态</t>
+  </si>
+  <si>
+    <t>5101211:1</t>
+  </si>
+  <si>
+    <t>5101212:1</t>
+  </si>
+  <si>
+    <t>5101215:1</t>
+  </si>
+  <si>
+    <t>5101116:1</t>
+  </si>
+  <si>
+    <t>5101218:2</t>
+  </si>
+  <si>
+    <t>毁天灭地-触发技能</t>
+  </si>
+  <si>
+    <t>击杀敌人时释放爆炸火球技能【参数4】</t>
+  </si>
+  <si>
     <t>重复中buff组的cd时间（毫秒）</t>
   </si>
   <si>
@@ -1456,57 +1481,19 @@
   </si>
   <si>
     <t>冰冻</t>
-  </si>
-  <si>
-    <t>每【参数8】（默认1000）毫秒，造成{[火元素直接伤害]【参数1万分比】（默认X%）}，【参数2】（默认0）的[额外火元素持续伤害]，效果持续【参数5】（默认3000）毫秒，最大可叠加【参数7】（默认1）层</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>陨石燃烧状态</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>火刃燃烧状态</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>5101215:1</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>5101116:1</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>5101218:2</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>5101211:1</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>5101212:1</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰雪领域-触发技能</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>毁天灭地-触发技能</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀敌人时释放爆炸火球技能【参数4】</t>
-    <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1518,28 +1505,24 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <color theme="0" tint="-4.9989318521683403E-2"/>
+      <color theme="0" tint="-0.0499893185216834"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1547,14 +1530,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1562,28 +1543,154 @@
       <sz val="9"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1591,24 +1698,15 @@
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1617,13 +1715,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <fgColor theme="0" tint="-0.349986266670736"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79958494827112647"/>
+        <fgColor theme="8" tint="0.799584948271126"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1635,7 +1733,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1645,8 +1767,158 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1684,20 +1956,241 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1712,7 +2205,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1720,34 +2213,76 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="16" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="23" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="16" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="4">
-    <cellStyle name="差" xfId="2" builtinId="27"/>
-    <cellStyle name="差 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="输入" xfId="1" builtinId="20"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="差 2" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2025,14 +2560,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadshe